--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-21600" yWindow="-20980" windowWidth="38400" windowHeight="20980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-21600" yWindow="-19300" windowWidth="21600" windowHeight="20980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Card Types" sheetId="1" state="visible" r:id="rId1"/>
@@ -40,13 +40,6 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
       <strike val="1"/>
-      <color indexed="8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-      <i val="1"/>
       <color indexed="8"/>
       <sz val="10"/>
     </font>
@@ -125,8 +118,16 @@
       <color indexed="8"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color indexed="8"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -163,8 +164,14 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="54">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -498,19 +505,6 @@
       <left style="thin">
         <color indexed="10"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
       <right style="thin">
         <color indexed="10"/>
       </right>
@@ -557,17 +551,6 @@
       <right style="thin">
         <color indexed="10"/>
       </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color indexed="10"/>
       </top>
@@ -605,30 +588,6 @@
         <color indexed="10"/>
       </left>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -793,19 +752,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="10"/>
@@ -822,16 +768,14 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="10"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="10"/>
       </top>
@@ -851,16 +795,18 @@
       <left/>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color indexed="10"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -871,13 +817,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -902,16 +845,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -932,16 +878,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -992,301 +935,259 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2412,169 +2313,168 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col width="26.5" customWidth="1" style="1" min="1" max="1"/>
-    <col width="41.83203125" customWidth="1" style="1" min="2" max="2"/>
-    <col width="38.1640625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="16.33203125" customWidth="1" style="1" min="4" max="6"/>
-    <col width="16.33203125" customWidth="1" style="1" min="7" max="16384"/>
+    <col width="26.5" customWidth="1" style="72" min="1" max="1"/>
+    <col width="41.83203125" customWidth="1" style="72" min="2" max="2"/>
+    <col width="38.1640625" customWidth="1" style="72" min="3" max="3"/>
+    <col width="16.33203125" customWidth="1" style="72" min="4" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="114">
-      <c r="A1" s="40" t="inlineStr">
+    <row r="1" ht="27.75" customHeight="1" s="72">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>Card Types</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20.25" customHeight="1" s="114">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="20.25" customHeight="1" s="72">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Types</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="32.25" customHeight="1" s="114">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="32.25" customHeight="1" s="72">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Move cards that usually result in an attempted shot after applying an effect</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" s="114">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="72">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Interfere with opposing players</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1" s="114">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="72">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Varying effects. Most increase Shot %</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="56" customHeight="1" s="114">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="56" customHeight="1" s="72">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>The most plentiful card type. Usually changes possession of the ball while increasing Shot %. If a player scores following a turn you gave them possession, you gain +1 AST</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="32" customHeight="1" s="114">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1" s="72">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Similar to Clamps, but have broader game-altering effects</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="44" customHeight="1" s="114">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="44" customHeight="1" s="72">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Play these immediately when dealt. These cards grant passive effects and persist for the remainder of the match unless removed with another card’s effect</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="114">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1" s="72">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Play these immediately when dealt. One-off effects</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-    </row>
-    <row r="10" ht="32" customHeight="1" s="114">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="32" customHeight="1" s="72">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Injury Game Break</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>These have one-off negative effects but do not reshuffle into the deck each round</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-    </row>
-    <row r="11" ht="32" customHeight="1" s="114">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1" s="72">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Devastating Injury Game Break</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Same as above but also have effects that linger through the rounds </t>
         </is>
       </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2602,654 +2502,659 @@
   <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
-    <col width="15.5" customWidth="1" style="9" min="1" max="1"/>
-    <col width="13" customWidth="1" style="9" min="2" max="2"/>
-    <col width="15.1640625" customWidth="1" style="9" min="3" max="3"/>
-    <col width="20.83203125" customWidth="1" style="9" min="4" max="4"/>
-    <col width="20.1640625" customWidth="1" style="9" min="5" max="7"/>
-    <col width="15" customWidth="1" style="114" min="6" max="6"/>
-    <col width="14.6640625" customWidth="1" style="9" min="8" max="8"/>
-    <col width="14.6640625" customWidth="1" style="9" min="9" max="9"/>
-    <col width="48.5" customWidth="1" style="1" min="10" max="10"/>
-    <col width="19.1640625" customWidth="1" style="1" min="11" max="11"/>
-    <col width="13" customWidth="1" style="1" min="12" max="12"/>
-    <col width="16.33203125" customWidth="1" style="1" min="13" max="13"/>
-    <col width="84.6640625" customWidth="1" style="1" min="14" max="14"/>
-    <col width="30.83203125" customWidth="1" style="1" min="15" max="17"/>
-    <col width="16.33203125" customWidth="1" style="114" min="16" max="16"/>
-    <col width="16.33203125" customWidth="1" style="1" min="18" max="16384"/>
-    <col width="16.33203125" customWidth="1" style="114" min="19" max="19"/>
+    <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
+    <col width="13" customWidth="1" style="8" min="2" max="2"/>
+    <col width="15.1640625" customWidth="1" style="8" min="3" max="3"/>
+    <col width="20.83203125" customWidth="1" style="8" min="4" max="4"/>
+    <col width="20.1640625" customWidth="1" style="8" min="5" max="5"/>
+    <col width="15" customWidth="1" style="72" min="6" max="6"/>
+    <col width="20.1640625" customWidth="1" style="8" min="7" max="7"/>
+    <col width="14.6640625" customWidth="1" style="8" min="8" max="9"/>
+    <col width="48.5" customWidth="1" style="72" min="10" max="10"/>
+    <col width="19.1640625" customWidth="1" style="72" min="11" max="11"/>
+    <col width="13" customWidth="1" style="72" min="12" max="12"/>
+    <col width="16.33203125" customWidth="1" style="72" min="13" max="13"/>
+    <col width="84.6640625" customWidth="1" style="72" min="14" max="14"/>
+    <col width="30.83203125" customWidth="1" style="72" min="15" max="15"/>
+    <col width="16.33203125" customWidth="1" style="72" min="16" max="16"/>
+    <col width="30.83203125" customWidth="1" style="72" min="17" max="17"/>
+    <col width="16.33203125" customWidth="1" style="72" min="18" max="18"/>
+    <col width="16.33203125" customWidth="1" style="72" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.75" customHeight="1" s="114">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="26.75" customHeight="1" s="72">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Card Types</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="J1" s="12" t="n"/>
-    </row>
-    <row r="2" ht="29.75" customHeight="1" s="114">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="J1" s="11" t="n"/>
+    </row>
+    <row r="2" ht="29.75" customHeight="1" s="72">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
+      <c r="B2" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C2" s="14" t="n">
+      <c r="C2" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="18" t="n">
+      <c r="G2" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="H2" s="19" t="n">
+      <c r="H2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="20" t="n">
+      <c r="I2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="20" t="n"/>
-    </row>
-    <row r="4" ht="20.75" customHeight="1" s="114" thickBot="1">
-      <c r="A4" s="115" t="inlineStr">
+      <c r="J2" s="19" t="n"/>
+    </row>
+    <row r="4" ht="20.75" customHeight="1" s="72" thickBot="1">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="116" t="n"/>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="B4" s="109" t="n"/>
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Effect</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Bonus Effect</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Number in Deck</t>
         </is>
       </c>
-      <c r="G4" s="90" t="inlineStr">
+      <c r="G4" s="125" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="H4" s="117" t="n"/>
-      <c r="I4" s="117" t="n"/>
-      <c r="J4" s="117" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1" s="114">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="H4" s="115" t="n"/>
+      <c r="I4" s="115" t="n"/>
+      <c r="J4" s="115" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="72">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="118" t="n"/>
-      <c r="G5" s="88" t="n"/>
-      <c r="H5" s="119" t="n"/>
-      <c r="I5" s="119" t="n"/>
-      <c r="J5" s="119" t="n"/>
-    </row>
-    <row r="6" ht="56" customHeight="1" s="114">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="73" t="n"/>
+      <c r="G5" s="98" t="n"/>
+      <c r="H5" s="99" t="n"/>
+      <c r="I5" s="99" t="n"/>
+      <c r="J5" s="99" t="n"/>
+    </row>
+    <row r="6" ht="56" customHeight="1" s="72">
+      <c r="A6" s="24" t="n"/>
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>Behind-the-Back</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Pass back to player who passed to you. If ball not received from a player, TOV +1</t>
         </is>
       </c>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="120" t="n">
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="78" t="n"/>
-      <c r="H6" s="121" t="n"/>
-      <c r="I6" s="121" t="n"/>
-      <c r="J6" s="121" t="n"/>
-    </row>
-    <row r="7" ht="28" customHeight="1" s="114">
-      <c r="A7" s="30" t="n"/>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="G6" s="103" t="n"/>
+      <c r="H6" s="104" t="n"/>
+      <c r="I6" s="104" t="n"/>
+      <c r="J6" s="104" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1" s="72">
+      <c r="A7" s="29" t="n"/>
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>Dime</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Pass to player of choice. SHOT +10%</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>If new player scores that turn: AST +1</t>
         </is>
       </c>
-      <c r="F7" s="122" t="n">
+      <c r="F7" s="75" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="80" t="n"/>
-      <c r="H7" s="121" t="n"/>
-      <c r="I7" s="121" t="n"/>
-      <c r="J7" s="121" t="n"/>
-    </row>
-    <row r="8" ht="56" customHeight="1" s="114">
-      <c r="A8" s="30" t="n"/>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="G7" s="110" t="n"/>
+      <c r="H7" s="104" t="n"/>
+      <c r="I7" s="104" t="n"/>
+      <c r="J7" s="104" t="n"/>
+    </row>
+    <row r="8" ht="56" customHeight="1" s="72">
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Lob</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>Shot +10%. Pass to player of choice. They must attempt a shot as their first action.</t>
-        </is>
-      </c>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="123" t="n"/>
-      <c r="G8" s="78" t="n"/>
-      <c r="H8" s="121" t="n"/>
-      <c r="I8" s="121" t="n"/>
-      <c r="J8" s="121" t="n"/>
-    </row>
-    <row r="9" ht="56" customHeight="1" s="114">
-      <c r="A9" s="30" t="n"/>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="D8" s="95" t="inlineStr">
+        <is>
+          <t>SHOT +10%. Pass to player of choice. They must attempt a shot as their first action.</t>
+        </is>
+      </c>
+      <c r="E8" s="34" t="n"/>
+      <c r="F8" s="76" t="n"/>
+      <c r="G8" s="103" t="n"/>
+      <c r="H8" s="104" t="n"/>
+      <c r="I8" s="104" t="n"/>
+      <c r="J8" s="104" t="n"/>
+    </row>
+    <row r="9" ht="56" customHeight="1" s="72">
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>Nutmeg</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Pass Left or Right. Move 1 card from new player to next player in same direction. SHOT +5%</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="124" t="n"/>
-      <c r="G9" s="80" t="n"/>
-      <c r="H9" s="121" t="n"/>
-      <c r="I9" s="121" t="n"/>
-      <c r="J9" s="121" t="n"/>
-    </row>
-    <row r="10" ht="14" customHeight="1" s="114">
-      <c r="A10" s="30" t="n"/>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="77" t="n"/>
+      <c r="G9" s="110" t="n"/>
+      <c r="H9" s="104" t="n"/>
+      <c r="I9" s="104" t="n"/>
+      <c r="J9" s="104" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1" s="72">
+      <c r="A10" s="29" t="n"/>
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>Skip Pass</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Pass Across. SHOT +5%</t>
         </is>
       </c>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="123" t="n">
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="76" t="n">
         <v>20</v>
       </c>
-      <c r="G10" s="78" t="n"/>
-      <c r="H10" s="121" t="n"/>
-      <c r="I10" s="121" t="n"/>
-      <c r="J10" s="121" t="n"/>
-    </row>
-    <row r="11" ht="14" customHeight="1" s="114">
-      <c r="A11" s="30" t="n"/>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="G10" s="103" t="n"/>
+      <c r="H10" s="104" t="n"/>
+      <c r="I10" s="104" t="n"/>
+      <c r="J10" s="104" t="n"/>
+    </row>
+    <row r="11" ht="14" customHeight="1" s="72">
+      <c r="A11" s="29" t="n"/>
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>Swing Left</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Pass Left. SHOT +5%</t>
         </is>
       </c>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="124" t="n">
-        <v>31</v>
-      </c>
-      <c r="G11" s="80" t="n"/>
-      <c r="H11" s="121" t="n"/>
-      <c r="I11" s="121" t="n"/>
-      <c r="J11" s="121" t="n"/>
-    </row>
-    <row r="12" ht="14" customHeight="1" s="114">
-      <c r="A12" s="30" t="n"/>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="77" t="n">
+        <v>28</v>
+      </c>
+      <c r="G11" s="110" t="n"/>
+      <c r="H11" s="104" t="n"/>
+      <c r="I11" s="104" t="n"/>
+      <c r="J11" s="104" t="n"/>
+    </row>
+    <row r="12" ht="14" customHeight="1" s="72">
+      <c r="A12" s="29" t="n"/>
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>Swing Right</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>Pass Right. SHOT +5%</t>
         </is>
       </c>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="123" t="n">
-        <v>31</v>
-      </c>
-      <c r="G12" s="78" t="n"/>
-      <c r="H12" s="121" t="n"/>
-      <c r="I12" s="121" t="n"/>
-      <c r="J12" s="121" t="n"/>
-    </row>
-    <row r="13" ht="28" customHeight="1" s="114">
-      <c r="A13" s="30" t="n"/>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="76" t="n">
+        <v>28</v>
+      </c>
+      <c r="G12" s="103" t="n"/>
+      <c r="H12" s="104" t="n"/>
+      <c r="I12" s="104" t="n"/>
+      <c r="J12" s="104" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1" s="72">
+      <c r="A13" s="29" t="n"/>
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>No-Look</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Pass to random other player. SHOT +5%</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="124" t="n">
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="77" t="n">
         <v>15</v>
       </c>
-      <c r="G13" s="80" t="n"/>
-      <c r="H13" s="121" t="n"/>
-      <c r="I13" s="121" t="n"/>
-      <c r="J13" s="121" t="n"/>
-    </row>
-    <row r="14" ht="29" customHeight="1" s="114" thickBot="1">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="G13" s="110" t="n"/>
+      <c r="H13" s="104" t="n"/>
+      <c r="I13" s="104" t="n"/>
+      <c r="J13" s="104" t="n"/>
+    </row>
+    <row r="14" ht="29" customHeight="1" s="72" thickBot="1">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Bullet Pass</t>
         </is>
       </c>
-      <c r="D14" s="39" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>Pass to player of choice. SHOT +5%</t>
         </is>
       </c>
-      <c r="E14" s="39" t="inlineStr">
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>New players discards 1 card at random</t>
         </is>
       </c>
-      <c r="F14" s="125" t="n">
+      <c r="F14" s="78" t="n">
         <v>12</v>
       </c>
-      <c r="G14" s="126" t="n"/>
-      <c r="H14" s="117" t="n"/>
-      <c r="I14" s="117" t="n"/>
-      <c r="J14" s="117" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" s="114">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="G14" s="114" t="n"/>
+      <c r="H14" s="115" t="n"/>
+      <c r="I14" s="115" t="n"/>
+      <c r="J14" s="115" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="72">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="B15" s="42" t="n">
+      <c r="B15" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="43" t="n"/>
-      <c r="E15" s="43" t="n"/>
-      <c r="F15" s="127" t="n"/>
-      <c r="G15" s="88" t="n"/>
-      <c r="H15" s="119" t="n"/>
-      <c r="I15" s="119" t="n"/>
-      <c r="J15" s="119" t="n"/>
-    </row>
-    <row r="16" ht="14" customHeight="1" s="114">
-      <c r="A16" s="47" t="n"/>
-      <c r="B16" s="48" t="inlineStr">
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="41" t="n"/>
+      <c r="E15" s="41" t="n"/>
+      <c r="F15" s="79" t="n"/>
+      <c r="G15" s="98" t="n"/>
+      <c r="H15" s="99" t="n"/>
+      <c r="I15" s="99" t="n"/>
+      <c r="J15" s="99" t="n"/>
+    </row>
+    <row r="16" ht="14" customHeight="1" s="72">
+      <c r="A16" s="45" t="n"/>
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>Dribble</t>
         </is>
       </c>
-      <c r="D16" s="50" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>Draw 1 card. SHOT -10%</t>
         </is>
       </c>
-      <c r="E16" s="51" t="n"/>
-      <c r="F16" s="128" t="n">
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="80" t="n">
         <v>15</v>
       </c>
-      <c r="G16" s="94" t="n"/>
-      <c r="H16" s="129" t="n"/>
-      <c r="I16" s="129" t="n"/>
-      <c r="J16" s="129" t="n"/>
-    </row>
-    <row r="17" ht="28" customHeight="1" s="114">
-      <c r="A17" s="30" t="n"/>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="G16" s="122" t="n"/>
+      <c r="H16" s="123" t="n"/>
+      <c r="I16" s="123" t="n"/>
+      <c r="J16" s="123" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" s="72">
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Following Dribble: SHOT +10%</t>
         </is>
       </c>
-      <c r="F17" s="122" t="n">
+      <c r="F17" s="75" t="n">
         <v>7</v>
       </c>
-      <c r="G17" s="92" t="n"/>
-      <c r="H17" s="130" t="n"/>
-      <c r="I17" s="130" t="n"/>
-      <c r="J17" s="130" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1" s="114">
-      <c r="A18" s="30" t="n"/>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="G17" s="100" t="n"/>
+      <c r="H17" s="101" t="n"/>
+      <c r="I17" s="101" t="n"/>
+      <c r="J17" s="101" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" s="72">
+      <c r="A18" s="29" t="n"/>
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C18" s="33" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>Ankle Breaker</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Target player discards 1 card. SHOT +10%</t>
         </is>
       </c>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="123" t="n">
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="76" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="96" t="n"/>
-      <c r="H18" s="130" t="n"/>
-      <c r="I18" s="130" t="n"/>
-      <c r="J18" s="130" t="n"/>
-    </row>
-    <row r="19" ht="56" customHeight="1" s="114">
-      <c r="A19" s="30" t="n"/>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="G18" s="105" t="n"/>
+      <c r="H18" s="101" t="n"/>
+      <c r="I18" s="101" t="n"/>
+      <c r="J18" s="101" t="n"/>
+    </row>
+    <row r="19" ht="56" customHeight="1" s="72">
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" s="91" t="inlineStr">
         <is>
           <t>Flop</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Take 1 FT attempt for each Clamp on you and cancel it. If no Clamps on you,  </t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="124" t="n"/>
-      <c r="G19" s="92" t="n"/>
-      <c r="H19" s="130" t="n"/>
-      <c r="I19" s="130" t="n"/>
-      <c r="J19" s="130" t="n"/>
-    </row>
-    <row r="20" ht="14" customHeight="1" s="114">
-      <c r="A20" s="30" t="n"/>
-      <c r="B20" s="31" t="inlineStr">
+      <c r="D19" s="92" t="inlineStr">
+        <is>
+          <t>Cancel Clamps. Take 1 FT for each. If no Clamps on you, TOV +1</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="77" t="n"/>
+      <c r="G19" s="102" t="inlineStr">
+        <is>
+          <t>Take 1 FT attempt for each Clamp on you and cancel it. If no Clamps on you, TOV +1</t>
+        </is>
+      </c>
+      <c r="H19" s="101" t="n"/>
+      <c r="I19" s="101" t="n"/>
+      <c r="J19" s="101" t="n"/>
+    </row>
+    <row r="20" ht="14" customHeight="1" s="72">
+      <c r="A20" s="29" t="n"/>
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C20" s="33" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
         <is>
           <t>Hesi</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>Shot Clock -1</t>
         </is>
       </c>
-      <c r="F20" s="131" t="n">
+      <c r="F20" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="G20" s="96" t="n"/>
-      <c r="H20" s="130" t="n"/>
-      <c r="I20" s="130" t="n"/>
-      <c r="J20" s="130" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" s="114">
-      <c r="A21" s="30" t="n"/>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="G20" s="105" t="n"/>
+      <c r="H20" s="101" t="n"/>
+      <c r="I20" s="101" t="n"/>
+      <c r="J20" s="101" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="72">
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C21" s="32" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
         <is>
           <t>Pump Fake</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Cancel all Clamps on you</t>
         </is>
       </c>
-      <c r="F21" s="122" t="n">
+      <c r="F21" s="75" t="n">
         <v>12</v>
       </c>
-      <c r="G21" s="92" t="n"/>
-      <c r="H21" s="130" t="n"/>
-      <c r="I21" s="130" t="n"/>
-      <c r="J21" s="130" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" s="114">
-      <c r="A22" s="30" t="n"/>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="G21" s="100" t="n"/>
+      <c r="H21" s="101" t="n"/>
+      <c r="I21" s="101" t="n"/>
+      <c r="J21" s="101" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" s="72">
+      <c r="A22" s="29" t="n"/>
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C22" s="33" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>Rhythm Dribble</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>Draw 1 card. SHOT +10%. Shot Clock -1</t>
         </is>
       </c>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="123" t="n">
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="96" t="n"/>
-      <c r="H22" s="130" t="n"/>
-      <c r="I22" s="130" t="n"/>
-      <c r="J22" s="130" t="n"/>
-    </row>
-    <row r="23" ht="14" customHeight="1" s="114">
-      <c r="A23" s="30" t="n"/>
-      <c r="B23" s="31" t="inlineStr">
+      <c r="G22" s="105" t="n"/>
+      <c r="H22" s="101" t="n"/>
+      <c r="I22" s="101" t="n"/>
+      <c r="J22" s="101" t="n"/>
+    </row>
+    <row r="23" ht="14" customHeight="1" s="72">
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="C23" s="31" t="inlineStr">
         <is>
           <t>Stepback</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Discard 1: SHOT +10%</t>
         </is>
       </c>
-      <c r="F23" s="122" t="n">
+      <c r="F23" s="75" t="n">
         <v>12</v>
       </c>
-      <c r="G23" s="92" t="inlineStr">
+      <c r="G23" s="100" t="inlineStr">
         <is>
           <t>The discard is an optional prompt.</t>
         </is>
       </c>
-      <c r="H23" s="130" t="n"/>
-      <c r="I23" s="130" t="n"/>
-      <c r="J23" s="130" t="n"/>
-    </row>
-    <row r="24" ht="71" customHeight="1" s="114" thickBot="1">
-      <c r="A24" s="64" t="n"/>
-      <c r="B24" s="65" t="inlineStr">
+      <c r="H23" s="101" t="n"/>
+      <c r="I23" s="101" t="n"/>
+      <c r="J23" s="101" t="n"/>
+    </row>
+    <row r="24" ht="71" customHeight="1" s="72" thickBot="1">
+      <c r="A24" s="62" t="n"/>
+      <c r="B24" s="63" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C24" s="66" t="inlineStr">
+      <c r="C24" s="64" t="inlineStr">
         <is>
           <t>Triple Threat</t>
         </is>
       </c>
-      <c r="D24" s="67" t="inlineStr">
+      <c r="D24" s="65" t="inlineStr">
         <is>
           <t>Choose 1:
 Draw 1 card
@@ -3257,1884 +3162,1892 @@
 SHOT +10%</t>
         </is>
       </c>
-      <c r="E24" s="67" t="inlineStr">
+      <c r="E24" s="65" t="inlineStr">
         <is>
           <t>Cannot use further Move cards</t>
         </is>
       </c>
-      <c r="F24" s="132" t="n">
+      <c r="F24" s="82" t="n">
         <v>15</v>
       </c>
-      <c r="G24" s="104" t="inlineStr">
+      <c r="G24" s="121" t="inlineStr">
         <is>
           <t>Cannot use further Move cards applies to that possession only.</t>
         </is>
       </c>
-      <c r="H24" s="133" t="n"/>
-      <c r="I24" s="133" t="n"/>
-      <c r="J24" s="133" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1" s="114">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="H24" s="107" t="n"/>
+      <c r="I24" s="107" t="n"/>
+      <c r="J24" s="107" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="72">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="B25" s="45" t="n">
+      <c r="B25" s="43" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
-      <c r="E25" s="46" t="n"/>
-      <c r="F25" s="134" t="n"/>
-      <c r="G25" s="88" t="n"/>
-      <c r="H25" s="119" t="n"/>
-      <c r="I25" s="119" t="n"/>
-      <c r="J25" s="119" t="n"/>
-    </row>
-    <row r="26" ht="42" customHeight="1" s="114">
-      <c r="A26" s="25" t="n"/>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="C25" s="44" t="n"/>
+      <c r="D25" s="44" t="n"/>
+      <c r="E25" s="44" t="n"/>
+      <c r="F25" s="83" t="n"/>
+      <c r="G25" s="98" t="n"/>
+      <c r="H25" s="99" t="n"/>
+      <c r="I25" s="99" t="n"/>
+      <c r="J25" s="99" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1" s="72">
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C26" s="27" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Bankshot</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Flip a coin:
 Heads: SHOT +10%
 Tails: SHOT -10%</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F26" s="135" t="n"/>
-      <c r="G26" s="78" t="n"/>
-      <c r="H26" s="121" t="n"/>
-      <c r="I26" s="121" t="n"/>
-      <c r="J26" s="121" t="n"/>
-    </row>
-    <row r="27" ht="14" customHeight="1" s="114">
-      <c r="A27" s="30" t="n"/>
-      <c r="B27" s="31" t="inlineStr">
+      <c r="F26" s="84" t="n"/>
+      <c r="G26" s="103" t="n"/>
+      <c r="H26" s="104" t="n"/>
+      <c r="I26" s="104" t="n"/>
+      <c r="J26" s="104" t="n"/>
+    </row>
+    <row r="27" ht="14" customHeight="1" s="72">
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>Buzzer Beater</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>SHOT = 100%</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F27" s="122" t="n">
+      <c r="F27" s="75" t="n">
         <v>4</v>
       </c>
-      <c r="G27" s="76" t="inlineStr">
+      <c r="G27" s="116" t="inlineStr">
         <is>
           <t>Can only play with Shot Clock at 1</t>
         </is>
       </c>
-      <c r="H27" s="121" t="n"/>
-      <c r="I27" s="121" t="n"/>
-      <c r="J27" s="121" t="n"/>
-    </row>
-    <row r="28" ht="28" customHeight="1" s="114">
-      <c r="A28" s="30" t="n"/>
-      <c r="B28" s="31" t="inlineStr">
+      <c r="H27" s="104" t="n"/>
+      <c r="I27" s="104" t="n"/>
+      <c r="J27" s="104" t="n"/>
+    </row>
+    <row r="28" ht="28" customHeight="1" s="72">
+      <c r="A28" s="29" t="n"/>
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C28" s="33" t="inlineStr">
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>Dagger Three</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>SHOT -20%.</t>
         </is>
       </c>
-      <c r="E28" s="34" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F28" s="131" t="n"/>
-      <c r="G28" s="78" t="n"/>
-      <c r="H28" s="121" t="n"/>
-      <c r="I28" s="121" t="n"/>
-      <c r="J28" s="121" t="n"/>
-    </row>
-    <row r="29" ht="14" customHeight="1" s="114">
-      <c r="A29" s="30" t="n"/>
-      <c r="B29" s="31" t="inlineStr">
+      <c r="F28" s="81" t="n"/>
+      <c r="G28" s="103" t="n"/>
+      <c r="H28" s="104" t="n"/>
+      <c r="I28" s="104" t="n"/>
+      <c r="J28" s="104" t="n"/>
+    </row>
+    <row r="29" ht="14" customHeight="1" s="72">
+      <c r="A29" s="29" t="n"/>
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>Fadeaway</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>SHOT -10%. Draw 1 card</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Shoot the ball.</t>
         </is>
       </c>
-      <c r="F29" s="122" t="n">
+      <c r="F29" s="75" t="n">
         <v>10</v>
       </c>
-      <c r="G29" s="80" t="n"/>
-      <c r="H29" s="121" t="n"/>
-      <c r="I29" s="121" t="n"/>
-      <c r="J29" s="121" t="n"/>
-    </row>
-    <row r="30" ht="28" customHeight="1" s="114">
-      <c r="A30" s="30" t="n"/>
-      <c r="B30" s="31" t="inlineStr">
+      <c r="G29" s="110" t="n"/>
+      <c r="H29" s="104" t="n"/>
+      <c r="I29" s="104" t="n"/>
+      <c r="J29" s="104" t="n"/>
+    </row>
+    <row r="30" ht="28" customHeight="1" s="72">
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
+      <c r="C30" s="32" t="inlineStr">
         <is>
           <t>From the Hash</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>SHOT -30%</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F30" s="131" t="n">
+      <c r="F30" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="78" t="n"/>
-      <c r="H30" s="121" t="n"/>
-      <c r="I30" s="121" t="n"/>
-      <c r="J30" s="121" t="n"/>
-    </row>
-    <row r="31" ht="28" customHeight="1" s="114">
-      <c r="A31" s="30" t="n"/>
-      <c r="B31" s="31" t="inlineStr">
+      <c r="G30" s="103" t="n"/>
+      <c r="H30" s="104" t="n"/>
+      <c r="I30" s="104" t="n"/>
+      <c r="J30" s="104" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1" s="72">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>From the Logo</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>SHOT -50%</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F31" s="122" t="n">
+      <c r="F31" s="75" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="80" t="n"/>
-      <c r="H31" s="121" t="n"/>
-      <c r="I31" s="121" t="n"/>
-      <c r="J31" s="121" t="n"/>
-    </row>
-    <row r="32" ht="28" customHeight="1" s="114">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="31" t="inlineStr">
+      <c r="G31" s="110" t="n"/>
+      <c r="H31" s="104" t="n"/>
+      <c r="I31" s="104" t="n"/>
+      <c r="J31" s="104" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1" s="72">
+      <c r="A32" s="29" t="n"/>
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C32" s="33" t="inlineStr">
+      <c r="C32" s="32" t="inlineStr">
         <is>
           <t>Full-Court Heave</t>
         </is>
       </c>
-      <c r="D32" s="34" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>SHOT = 10%</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F32" s="131" t="n">
+      <c r="F32" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="78" t="n"/>
-      <c r="H32" s="121" t="n"/>
-      <c r="I32" s="121" t="n"/>
-      <c r="J32" s="121" t="n"/>
-    </row>
-    <row r="33" ht="42" customHeight="1" s="114">
-      <c r="A33" s="30" t="n"/>
-      <c r="B33" s="31" t="inlineStr">
+      <c r="G32" s="103" t="n"/>
+      <c r="H32" s="104" t="n"/>
+      <c r="I32" s="104" t="n"/>
+      <c r="J32" s="104" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1" s="72">
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>Putback Tip</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Shoot the ball. After a missed shot: SHOT = 100%</t>
         </is>
       </c>
-      <c r="F33" s="122" t="n">
+      <c r="F33" s="75" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="80" t="n"/>
-      <c r="H33" s="121" t="n"/>
-      <c r="I33" s="121" t="n"/>
-      <c r="J33" s="121" t="n"/>
-    </row>
-    <row r="34" ht="28" customHeight="1" s="114">
-      <c r="A34" s="30" t="n"/>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="G33" s="110" t="n"/>
+      <c r="H33" s="104" t="n"/>
+      <c r="I33" s="104" t="n"/>
+      <c r="J33" s="104" t="n"/>
+    </row>
+    <row r="34" ht="28" customHeight="1" s="72">
+      <c r="A34" s="29" t="n"/>
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C34" s="33" t="inlineStr">
+      <c r="C34" s="32" t="inlineStr">
         <is>
           <t>Skyhook</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
+      <c r="E34" s="33" t="inlineStr">
         <is>
           <t>Shot is unaffected by Clamps</t>
         </is>
       </c>
-      <c r="F34" s="131" t="n"/>
-      <c r="G34" s="78" t="n"/>
-      <c r="H34" s="121" t="n"/>
-      <c r="I34" s="121" t="n"/>
-      <c r="J34" s="121" t="n"/>
-    </row>
-    <row r="35" ht="28" customHeight="1" s="114">
-      <c r="A35" s="30" t="n"/>
-      <c r="B35" s="31" t="inlineStr">
+      <c r="F34" s="81" t="n"/>
+      <c r="G34" s="103" t="n"/>
+      <c r="H34" s="104" t="n"/>
+      <c r="I34" s="104" t="n"/>
+      <c r="J34" s="104" t="n"/>
+    </row>
+    <row r="35" ht="28" customHeight="1" s="72">
+      <c r="A35" s="29" t="n"/>
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>Slam Dunk</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>SHOT +10%. SHOT = 100% if SHOT &gt;= 70%</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F35" s="122" t="n"/>
-      <c r="G35" s="80" t="n"/>
-      <c r="H35" s="121" t="n"/>
-      <c r="I35" s="121" t="n"/>
-      <c r="J35" s="121" t="n"/>
-    </row>
-    <row r="36" ht="42" customHeight="1" s="114">
-      <c r="A36" s="54" t="n"/>
-      <c r="B36" s="55" t="inlineStr">
+      <c r="F35" s="75" t="n"/>
+      <c r="G35" s="110" t="n"/>
+      <c r="H35" s="104" t="n"/>
+      <c r="I35" s="104" t="n"/>
+      <c r="J35" s="104" t="n"/>
+    </row>
+    <row r="36" ht="42" customHeight="1" s="72">
+      <c r="A36" s="52" t="n"/>
+      <c r="B36" s="53" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C36" s="74" t="inlineStr">
+      <c r="C36" s="70" t="inlineStr">
         <is>
           <t>Turnaround Three</t>
         </is>
       </c>
-      <c r="D36" s="75" t="inlineStr">
+      <c r="D36" s="71" t="inlineStr">
         <is>
           <t>Discard any number of cards. SHOT +10% for each</t>
         </is>
       </c>
-      <c r="E36" s="75" t="inlineStr">
+      <c r="E36" s="71" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F36" s="136" t="n">
+      <c r="F36" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="82" t="inlineStr">
+      <c r="G36" s="127" t="inlineStr">
         <is>
           <t>Only 1 in deck</t>
         </is>
       </c>
-      <c r="H36" s="121" t="n"/>
-      <c r="I36" s="121" t="n"/>
-      <c r="J36" s="121" t="n"/>
-    </row>
-    <row r="37" ht="57" customHeight="1" s="114" thickBot="1">
-      <c r="A37" s="64" t="n"/>
-      <c r="B37" s="65" t="inlineStr">
+      <c r="H36" s="104" t="n"/>
+      <c r="I36" s="104" t="n"/>
+      <c r="J36" s="104" t="n"/>
+    </row>
+    <row r="37" ht="57" customHeight="1" s="72" thickBot="1">
+      <c r="A37" s="62" t="n"/>
+      <c r="B37" s="63" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C37" s="71" t="inlineStr">
+      <c r="C37" s="67" t="inlineStr">
         <is>
           <t>Euro Step</t>
         </is>
       </c>
-      <c r="D37" s="72" t="inlineStr">
+      <c r="D37" s="68" t="inlineStr">
         <is>
           <t>Flip a coin until you get Tails. For each Heads, SHOT +5% and Draw 1 card</t>
         </is>
       </c>
-      <c r="E37" s="73" t="n"/>
-      <c r="F37" s="137" t="n">
+      <c r="E37" s="69" t="n"/>
+      <c r="F37" s="86" t="n">
         <v>5</v>
       </c>
-      <c r="G37" s="138" t="n"/>
-      <c r="H37" s="117" t="n"/>
-      <c r="I37" s="117" t="n"/>
-      <c r="J37" s="117" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1" s="114">
-      <c r="A38" s="61" t="inlineStr">
+      <c r="G37" s="126" t="n"/>
+      <c r="H37" s="115" t="n"/>
+      <c r="I37" s="115" t="n"/>
+      <c r="J37" s="115" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1" s="72">
+      <c r="A38" s="59" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B38" s="62" t="n">
+      <c r="B38" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="C38" s="63" t="n"/>
-      <c r="D38" s="63" t="n"/>
-      <c r="E38" s="63" t="n"/>
-      <c r="F38" s="139" t="n"/>
-      <c r="G38" s="100" t="n"/>
-      <c r="H38" s="140" t="n"/>
-      <c r="I38" s="140" t="n"/>
-      <c r="J38" s="140" t="n"/>
-    </row>
-    <row r="39" ht="28" customHeight="1" s="114">
-      <c r="A39" s="30" t="n"/>
-      <c r="B39" s="31" t="inlineStr">
+      <c r="C38" s="61" t="n"/>
+      <c r="D38" s="61" t="n"/>
+      <c r="E38" s="61" t="n"/>
+      <c r="F38" s="87" t="n"/>
+      <c r="G38" s="119" t="n"/>
+      <c r="H38" s="120" t="n"/>
+      <c r="I38" s="120" t="n"/>
+      <c r="J38" s="120" t="n"/>
+    </row>
+    <row r="39" ht="28" customHeight="1" s="72">
+      <c r="A39" s="29" t="n"/>
+      <c r="B39" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C39" s="31" t="inlineStr">
         <is>
           <t>Contest</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Next player SHOT -25% if they shoot</t>
         </is>
       </c>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="124" t="n">
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="G39" s="92" t="n"/>
-      <c r="H39" s="130" t="n"/>
-      <c r="I39" s="130" t="n"/>
-      <c r="J39" s="130" t="n"/>
-    </row>
-    <row r="40" ht="28" customHeight="1" s="114">
-      <c r="A40" s="30" t="n"/>
-      <c r="B40" s="31" t="inlineStr">
+      <c r="G39" s="100" t="n"/>
+      <c r="H39" s="101" t="n"/>
+      <c r="I39" s="101" t="n"/>
+      <c r="J39" s="101" t="n"/>
+    </row>
+    <row r="40" ht="28" customHeight="1" s="72">
+      <c r="A40" s="29" t="n"/>
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C40" s="33" t="inlineStr">
+      <c r="C40" s="32" t="inlineStr">
         <is>
           <t>Double-Team</t>
         </is>
       </c>
-      <c r="D40" s="34" t="inlineStr">
+      <c r="D40" s="33" t="inlineStr">
         <is>
           <t>Next Player cannot play 2 random cards from hand.</t>
         </is>
       </c>
-      <c r="E40" s="35" t="n"/>
-      <c r="F40" s="123" t="n"/>
-      <c r="G40" s="96" t="n"/>
-      <c r="H40" s="130" t="n"/>
-      <c r="I40" s="130" t="n"/>
-      <c r="J40" s="130" t="n"/>
-    </row>
-    <row r="41" ht="42" customHeight="1" s="114">
-      <c r="A41" s="30" t="n"/>
-      <c r="B41" s="31" t="inlineStr">
+      <c r="E40" s="34" t="n"/>
+      <c r="F40" s="76" t="n"/>
+      <c r="G40" s="105" t="n"/>
+      <c r="H40" s="101" t="n"/>
+      <c r="I40" s="101" t="n"/>
+      <c r="J40" s="101" t="n"/>
+    </row>
+    <row r="41" ht="42" customHeight="1" s="72">
+      <c r="A41" s="29" t="n"/>
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C41" s="32" t="inlineStr">
+      <c r="C41" s="31" t="inlineStr">
         <is>
           <t>Full-Court Press</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Next player discards 2 cards at the start of their turn</t>
         </is>
       </c>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="124" t="n">
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="G41" s="92" t="n"/>
-      <c r="H41" s="130" t="n"/>
-      <c r="I41" s="130" t="n"/>
-      <c r="J41" s="130" t="n"/>
-    </row>
-    <row r="42" ht="42" customHeight="1" s="114">
-      <c r="A42" s="30" t="n"/>
-      <c r="B42" s="31" t="inlineStr">
+      <c r="G41" s="100" t="n"/>
+      <c r="H41" s="101" t="n"/>
+      <c r="I41" s="101" t="n"/>
+      <c r="J41" s="101" t="n"/>
+    </row>
+    <row r="42" ht="42" customHeight="1" s="72">
+      <c r="A42" s="29" t="n"/>
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C42" s="33" t="inlineStr">
+      <c r="C42" s="32" t="inlineStr">
         <is>
           <t>Trap</t>
         </is>
       </c>
-      <c r="D42" s="34" t="inlineStr">
+      <c r="D42" s="33" t="inlineStr">
         <is>
           <t>Next player can only play Pass cards during their turn</t>
         </is>
       </c>
-      <c r="E42" s="35" t="n"/>
-      <c r="F42" s="123" t="n"/>
-      <c r="G42" s="96" t="n"/>
-      <c r="H42" s="130" t="n"/>
-      <c r="I42" s="130" t="n"/>
-      <c r="J42" s="130" t="n"/>
-    </row>
-    <row r="43" ht="29" customHeight="1" s="114" thickBot="1">
-      <c r="A43" s="64" t="n"/>
-      <c r="B43" s="65" t="inlineStr">
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="76" t="n"/>
+      <c r="G42" s="105" t="n"/>
+      <c r="H42" s="101" t="n"/>
+      <c r="I42" s="101" t="n"/>
+      <c r="J42" s="101" t="n"/>
+    </row>
+    <row r="43" ht="29" customHeight="1" s="72" thickBot="1">
+      <c r="A43" s="62" t="n"/>
+      <c r="B43" s="63" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C43" s="71" t="inlineStr">
+      <c r="C43" s="67" t="inlineStr">
         <is>
           <t>Triple-Team</t>
         </is>
       </c>
-      <c r="D43" s="72" t="inlineStr">
+      <c r="D43" s="68" t="inlineStr">
         <is>
           <t>Next player cannot play 3 random cards from hand.</t>
         </is>
       </c>
-      <c r="E43" s="73" t="n"/>
-      <c r="F43" s="137" t="n"/>
-      <c r="G43" s="98" t="n"/>
-      <c r="H43" s="133" t="n"/>
-      <c r="I43" s="133" t="n"/>
-      <c r="J43" s="133" t="n"/>
-    </row>
-    <row r="44" ht="20" customHeight="1" s="114">
-      <c r="A44" s="61" t="inlineStr">
+      <c r="E43" s="69" t="n"/>
+      <c r="F43" s="86" t="n"/>
+      <c r="G43" s="106" t="n"/>
+      <c r="H43" s="107" t="n"/>
+      <c r="I43" s="107" t="n"/>
+      <c r="J43" s="107" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="72">
+      <c r="A44" s="59" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="B44" s="62" t="n">
+      <c r="B44" s="60" t="n">
         <v>16</v>
       </c>
-      <c r="C44" s="63" t="n"/>
-      <c r="D44" s="63" t="n"/>
-      <c r="E44" s="63" t="n"/>
-      <c r="F44" s="139" t="n"/>
-      <c r="G44" s="100" t="n"/>
-      <c r="H44" s="140" t="n"/>
-      <c r="I44" s="140" t="n"/>
-      <c r="J44" s="140" t="n"/>
-    </row>
-    <row r="45" ht="56" customHeight="1" s="114">
-      <c r="A45" s="30" t="n"/>
-      <c r="B45" s="31" t="inlineStr">
+      <c r="C44" s="61" t="n"/>
+      <c r="D44" s="61" t="n"/>
+      <c r="E44" s="61" t="n"/>
+      <c r="F44" s="87" t="n"/>
+      <c r="G44" s="119" t="n"/>
+      <c r="H44" s="120" t="n"/>
+      <c r="I44" s="120" t="n"/>
+      <c r="J44" s="120" t="n"/>
+    </row>
+    <row r="45" ht="56" customHeight="1" s="72">
+      <c r="A45" s="29" t="n"/>
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C45" s="32" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
         <is>
           <t>Back Court Violation</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
         </is>
       </c>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="124" t="n">
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="92" t="inlineStr">
+      <c r="G45" s="100" t="inlineStr">
         <is>
           <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
         </is>
       </c>
-      <c r="H45" s="130" t="n"/>
-      <c r="I45" s="130" t="n"/>
-      <c r="J45" s="130" t="n"/>
-    </row>
-    <row r="46" ht="14" customHeight="1" s="114">
-      <c r="A46" s="30" t="n"/>
-      <c r="B46" s="31" t="inlineStr">
+      <c r="H45" s="101" t="n"/>
+      <c r="I45" s="101" t="n"/>
+      <c r="J45" s="101" t="n"/>
+    </row>
+    <row r="46" ht="47" customHeight="1" s="72">
+      <c r="A46" s="29" t="n"/>
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C46" s="33" t="inlineStr">
+      <c r="C46" s="91" t="inlineStr">
         <is>
           <t>Blocking Foul</t>
         </is>
       </c>
-      <c r="D46" s="35" t="n"/>
-      <c r="E46" s="35" t="n"/>
-      <c r="F46" s="123" t="n"/>
-      <c r="G46" s="96" t="n"/>
-      <c r="H46" s="130" t="n"/>
-      <c r="I46" s="130" t="n"/>
-      <c r="J46" s="130" t="n"/>
-    </row>
-    <row r="47" ht="14" customHeight="1" s="114">
-      <c r="A47" s="30" t="n"/>
-      <c r="B47" s="31" t="inlineStr">
+      <c r="D46" s="94" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
+        </is>
+      </c>
+      <c r="E46" s="34" t="n"/>
+      <c r="F46" s="76" t="n"/>
+      <c r="G46" s="105" t="n"/>
+      <c r="H46" s="101" t="n"/>
+      <c r="I46" s="101" t="n"/>
+      <c r="J46" s="101" t="n"/>
+    </row>
+    <row r="47" ht="54" customHeight="1" s="72">
+      <c r="A47" s="29" t="n"/>
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C47" s="32" t="inlineStr">
+      <c r="C47" s="31" t="inlineStr">
         <is>
           <t>Charge</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="124" t="n"/>
-      <c r="G47" s="92" t="n"/>
-      <c r="H47" s="130" t="n"/>
-      <c r="I47" s="130" t="n"/>
-      <c r="J47" s="130" t="n"/>
-    </row>
-    <row r="48" ht="28" customHeight="1" s="114">
-      <c r="A48" s="30" t="n"/>
-      <c r="B48" s="31" t="inlineStr">
+      <c r="D47" s="93" t="inlineStr">
+        <is>
+          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="77" t="n"/>
+      <c r="G47" s="100" t="n"/>
+      <c r="H47" s="101" t="n"/>
+      <c r="I47" s="101" t="n"/>
+      <c r="J47" s="101" t="n"/>
+    </row>
+    <row r="48" ht="28" customHeight="1" s="72">
+      <c r="A48" s="29" t="n"/>
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C48" s="33" t="inlineStr">
+      <c r="C48" s="32" t="inlineStr">
         <is>
           <t>Cleared to Play</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D48" s="33" t="inlineStr">
         <is>
           <t>Injury Card Played: Cancel card.</t>
         </is>
       </c>
-      <c r="E48" s="35" t="n"/>
-      <c r="F48" s="123" t="n"/>
-      <c r="G48" s="96" t="n"/>
-      <c r="H48" s="130" t="n"/>
-      <c r="I48" s="130" t="n"/>
-      <c r="J48" s="130" t="n"/>
-    </row>
-    <row r="49" ht="28" customHeight="1" s="114">
-      <c r="A49" s="30" t="n"/>
-      <c r="B49" s="31" t="inlineStr">
+      <c r="E48" s="34" t="n"/>
+      <c r="F48" s="76" t="n"/>
+      <c r="G48" s="105" t="n"/>
+      <c r="H48" s="101" t="n"/>
+      <c r="I48" s="101" t="n"/>
+      <c r="J48" s="101" t="n"/>
+    </row>
+    <row r="49" ht="28" customHeight="1" s="72">
+      <c r="A49" s="29" t="n"/>
+      <c r="B49" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C49" s="32" t="inlineStr">
+      <c r="C49" s="31" t="inlineStr">
         <is>
           <t>Coach’s Challenge</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Any Whistle Card Played: Cancel card.</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Pull a Timeout from the discards, if one is there, and take it</t>
         </is>
       </c>
-      <c r="F49" s="124" t="n">
+      <c r="F49" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="G49" s="92" t="n"/>
-      <c r="H49" s="130" t="n"/>
-      <c r="I49" s="130" t="n"/>
-      <c r="J49" s="130" t="n"/>
-    </row>
-    <row r="50" ht="28" customHeight="1" s="114">
-      <c r="A50" s="30" t="n"/>
-      <c r="B50" s="31" t="inlineStr">
+      <c r="G49" s="100" t="n"/>
+      <c r="H49" s="101" t="n"/>
+      <c r="I49" s="101" t="n"/>
+      <c r="J49" s="101" t="n"/>
+    </row>
+    <row r="50" ht="28" customHeight="1" s="72">
+      <c r="A50" s="29" t="n"/>
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C50" s="33" t="inlineStr">
+      <c r="C50" s="91" t="inlineStr">
         <is>
           <t>Delay-of-Game Warning</t>
         </is>
       </c>
-      <c r="D50" s="34" t="inlineStr">
-        <is>
-          <t>Turn Start: All other players discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E50" s="34" t="inlineStr">
-        <is>
-          <t>If 2nd time activated this round: Take 1 FT</t>
-        </is>
-      </c>
-      <c r="F50" s="131" t="n">
+      <c r="D50" s="33" t="inlineStr">
+        <is>
+          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
+        </is>
+      </c>
+      <c r="E50" s="33" t="inlineStr">
+        <is>
+          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
+        </is>
+      </c>
+      <c r="F50" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="G50" s="113" t="inlineStr">
+        <is>
+          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
+        </is>
+      </c>
+      <c r="H50" s="101" t="n"/>
+      <c r="I50" s="101" t="n"/>
+      <c r="J50" s="101" t="n"/>
+    </row>
+    <row r="51" ht="42" customHeight="1" s="72">
+      <c r="A51" s="29" t="n"/>
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>Double Dribble</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="100" t="inlineStr">
+        <is>
+          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+        </is>
+      </c>
+      <c r="H51" s="101" t="n"/>
+      <c r="I51" s="101" t="n"/>
+      <c r="J51" s="101" t="n"/>
+    </row>
+    <row r="52" ht="40" customHeight="1" s="72">
+      <c r="A52" s="29" t="n"/>
+      <c r="B52" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C52" s="91" t="inlineStr">
+        <is>
+          <t>Flagrant Foul</t>
+        </is>
+      </c>
+      <c r="D52" s="95" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
+        </is>
+      </c>
+      <c r="E52" s="34" t="n"/>
+      <c r="F52" s="76" t="n"/>
+      <c r="G52" s="105" t="n"/>
+      <c r="H52" s="101" t="n"/>
+      <c r="I52" s="101" t="n"/>
+      <c r="J52" s="101" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1" s="72">
+      <c r="A53" s="29" t="n"/>
+      <c r="B53" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C53" s="91" t="inlineStr">
+        <is>
+          <t>Flagrant Foul II</t>
+        </is>
+      </c>
+      <c r="D53" s="92" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="77" t="n"/>
+      <c r="G53" s="100" t="n"/>
+      <c r="H53" s="101" t="n"/>
+      <c r="I53" s="101" t="n"/>
+      <c r="J53" s="101" t="n"/>
+    </row>
+    <row r="54" ht="56" customHeight="1" s="72">
+      <c r="A54" s="29" t="n"/>
+      <c r="B54" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>Goaltending</t>
+        </is>
+      </c>
+      <c r="D54" s="33" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
+        </is>
+      </c>
+      <c r="E54" s="34" t="n"/>
+      <c r="F54" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" s="105" t="n"/>
+      <c r="H54" s="101" t="n"/>
+      <c r="I54" s="101" t="n"/>
+      <c r="J54" s="101" t="n"/>
+    </row>
+    <row r="55" ht="42" customHeight="1" s="72">
+      <c r="A55" s="29" t="n"/>
+      <c r="B55" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>Inadvertent Whistle</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Any Non-Whistle Card Played: Cancel that card. Turn player draws 1 card.</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" s="100" t="n"/>
+      <c r="H55" s="101" t="n"/>
+      <c r="I55" s="101" t="n"/>
+      <c r="J55" s="101" t="n"/>
+    </row>
+    <row r="56" ht="42" customHeight="1" s="72">
+      <c r="A56" s="29" t="n"/>
+      <c r="B56" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>Official Review</t>
+        </is>
+      </c>
+      <c r="D56" s="33" t="inlineStr">
+        <is>
+          <t>Intangible Played: Discard all Intangibles from player.</t>
+        </is>
+      </c>
+      <c r="E56" s="34" t="n"/>
+      <c r="F56" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" s="105" t="n"/>
+      <c r="H56" s="101" t="n"/>
+      <c r="I56" s="101" t="n"/>
+      <c r="J56" s="101" t="n"/>
+    </row>
+    <row r="57" ht="42" customHeight="1" s="72">
+      <c r="A57" s="29" t="n"/>
+      <c r="B57" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>Shot Clock Violation</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Shot Attempt: Cancel the shot. TOV +1. Ball OOB</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" s="100" t="inlineStr">
+        <is>
+          <t>This inbound does NOT increment the round.</t>
+        </is>
+      </c>
+      <c r="H57" s="101" t="n"/>
+      <c r="I57" s="101" t="n"/>
+      <c r="J57" s="101" t="n"/>
+    </row>
+    <row r="58" ht="28" customHeight="1" s="72">
+      <c r="A58" s="29" t="n"/>
+      <c r="B58" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>Technical Foul</t>
+        </is>
+      </c>
+      <c r="D58" s="33" t="inlineStr">
+        <is>
+          <t>Any Non-Whistle Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E58" s="34" t="n"/>
+      <c r="F58" s="76" t="n"/>
+      <c r="G58" s="105" t="n"/>
+      <c r="H58" s="101" t="n"/>
+      <c r="I58" s="101" t="n"/>
+      <c r="J58" s="101" t="n"/>
+    </row>
+    <row r="59" ht="42" customHeight="1" s="72">
+      <c r="A59" s="29" t="n"/>
+      <c r="B59" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C59" s="31" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Immediate: Reset Shot Clock. All players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" s="100" t="n"/>
+      <c r="H59" s="101" t="n"/>
+      <c r="I59" s="101" t="n"/>
+      <c r="J59" s="101" t="n"/>
+    </row>
+    <row r="60" ht="29" customHeight="1" s="72" thickBot="1">
+      <c r="A60" s="62" t="n"/>
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C60" s="64" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D60" s="65" t="inlineStr">
+        <is>
+          <t>Move card played: Cancel card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E60" s="66" t="n"/>
+      <c r="F60" s="88" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" s="121" t="n"/>
+      <c r="H60" s="107" t="n"/>
+      <c r="I60" s="107" t="n"/>
+      <c r="J60" s="107" t="n"/>
+    </row>
+    <row r="61" ht="20" customHeight="1" s="72">
+      <c r="A61" s="59" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="B61" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" s="61" t="n"/>
+      <c r="D61" s="61" t="n"/>
+      <c r="E61" s="61" t="n"/>
+      <c r="F61" s="87" t="n"/>
+      <c r="G61" s="119" t="n"/>
+      <c r="H61" s="120" t="n"/>
+      <c r="I61" s="120" t="n"/>
+      <c r="J61" s="120" t="n"/>
+    </row>
+    <row r="62" ht="28" customHeight="1" s="72">
+      <c r="A62" s="29" t="n"/>
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
+        </is>
+      </c>
+      <c r="D62" s="33" t="inlineStr">
+        <is>
+          <t>All players discard down to 2 or fewer cards</t>
+        </is>
+      </c>
+      <c r="E62" s="34" t="n"/>
+      <c r="F62" s="76" t="n">
         <v>2</v>
       </c>
-      <c r="G50" s="102" t="inlineStr">
-        <is>
-          <t>Only 2 in deck</t>
-        </is>
-      </c>
-      <c r="H50" s="130" t="n"/>
-      <c r="I50" s="130" t="n"/>
-      <c r="J50" s="130" t="n"/>
-    </row>
-    <row r="51" ht="42" customHeight="1" s="114">
-      <c r="A51" s="30" t="n"/>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>Double Dribble</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="124" t="n">
+      <c r="G62" s="105" t="n"/>
+      <c r="H62" s="101" t="n"/>
+      <c r="I62" s="101" t="n"/>
+      <c r="J62" s="101" t="n"/>
+    </row>
+    <row r="63" ht="28" customHeight="1" s="72">
+      <c r="A63" s="29" t="n"/>
+      <c r="B63" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>Benched</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Immediately give ball to any other player.</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="G51" s="92" t="inlineStr">
-        <is>
-          <t>The dribbling player inbounds. The round is NOT incremented.</t>
-        </is>
-      </c>
-      <c r="H51" s="130" t="n"/>
-      <c r="I51" s="130" t="n"/>
-      <c r="J51" s="130" t="n"/>
-    </row>
-    <row r="52" ht="14" customHeight="1" s="114">
-      <c r="A52" s="30" t="n"/>
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C52" s="33" t="inlineStr">
-        <is>
-          <t>Flagrant Foul</t>
-        </is>
-      </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clamp Card Played: </t>
-        </is>
-      </c>
-      <c r="E52" s="35" t="n"/>
-      <c r="F52" s="123" t="n"/>
-      <c r="G52" s="96" t="n"/>
-      <c r="H52" s="130" t="n"/>
-      <c r="I52" s="130" t="n"/>
-      <c r="J52" s="130" t="n"/>
-    </row>
-    <row r="53" ht="14" customHeight="1" s="114">
-      <c r="A53" s="30" t="n"/>
-      <c r="B53" s="31" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C53" s="32" t="inlineStr">
-        <is>
-          <t>Flagrant Foul II</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clamp Card Played: </t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="124" t="n"/>
-      <c r="G53" s="92" t="n"/>
-      <c r="H53" s="130" t="n"/>
-      <c r="I53" s="130" t="n"/>
-      <c r="J53" s="130" t="n"/>
-    </row>
-    <row r="54" ht="56" customHeight="1" s="114">
-      <c r="A54" s="30" t="n"/>
-      <c r="B54" s="31" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C54" s="33" t="inlineStr">
-        <is>
-          <t>Goaltending</t>
-        </is>
-      </c>
-      <c r="D54" s="34" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
-        </is>
-      </c>
-      <c r="E54" s="35" t="n"/>
-      <c r="F54" s="123" t="n">
+      <c r="G63" s="112" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
+      <c r="H63" s="101" t="n"/>
+      <c r="I63" s="101" t="n"/>
+      <c r="J63" s="101" t="n"/>
+    </row>
+    <row r="64" ht="14" customHeight="1" s="72">
+      <c r="A64" s="29" t="n"/>
+      <c r="B64" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
+        </is>
+      </c>
+      <c r="D64" s="33" t="inlineStr">
+        <is>
+          <t>Discard 1 card.</t>
+        </is>
+      </c>
+      <c r="E64" s="34" t="n"/>
+      <c r="F64" s="76" t="n">
+        <v>14</v>
+      </c>
+      <c r="G64" s="105" t="n"/>
+      <c r="H64" s="101" t="n"/>
+      <c r="I64" s="101" t="n"/>
+      <c r="J64" s="101" t="n"/>
+    </row>
+    <row r="65" ht="14" customHeight="1" s="72">
+      <c r="A65" s="29" t="n"/>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>Designed Play</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Draw up to a hand of 5</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="G65" s="100" t="n"/>
+      <c r="H65" s="101" t="n"/>
+      <c r="I65" s="101" t="n"/>
+      <c r="J65" s="101" t="n"/>
+    </row>
+    <row r="66" ht="14" customHeight="1" s="72">
+      <c r="A66" s="29" t="n"/>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C66" s="91" t="inlineStr">
+        <is>
+          <t>Foul</t>
+        </is>
+      </c>
+      <c r="D66" s="33" t="inlineStr">
+        <is>
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E66" s="34" t="n"/>
+      <c r="F66" s="76" t="n"/>
+      <c r="G66" s="105" t="n"/>
+      <c r="H66" s="101" t="n"/>
+      <c r="I66" s="101" t="n"/>
+      <c r="J66" s="101" t="n"/>
+    </row>
+    <row r="67" ht="28" customHeight="1" s="72">
+      <c r="A67" s="29" t="n"/>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>MVP Vote</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Draw 3 cards up to a hand of 7</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G67" s="100" t="n"/>
+      <c r="H67" s="101" t="n"/>
+      <c r="I67" s="101" t="n"/>
+      <c r="J67" s="101" t="n"/>
+    </row>
+    <row r="68" ht="28" customHeight="1" s="72">
+      <c r="A68" s="29" t="n"/>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D68" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E68" s="34" t="n"/>
+      <c r="F68" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G54" s="96" t="n"/>
-      <c r="H54" s="130" t="n"/>
-      <c r="I54" s="130" t="n"/>
-      <c r="J54" s="130" t="n"/>
-    </row>
-    <row r="55" ht="42" customHeight="1" s="114">
-      <c r="A55" s="30" t="n"/>
-      <c r="B55" s="31" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C55" s="32" t="inlineStr">
-        <is>
-          <t>Inadvertent Whistle</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Any Non-Whistle Card Played: Cancel that card. Turn player draws 1 card.</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="124" t="n">
+      <c r="G68" s="105" t="n"/>
+      <c r="H68" s="101" t="n"/>
+      <c r="I68" s="101" t="n"/>
+      <c r="J68" s="101" t="n"/>
+    </row>
+    <row r="69" ht="28" customHeight="1" s="72">
+      <c r="A69" s="29" t="n"/>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C69" s="31" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F69" s="75" t="n">
         <v>5</v>
       </c>
-      <c r="G55" s="92" t="n"/>
-      <c r="H55" s="130" t="n"/>
-      <c r="I55" s="130" t="n"/>
-      <c r="J55" s="130" t="n"/>
-    </row>
-    <row r="56" ht="42" customHeight="1" s="114">
-      <c r="A56" s="30" t="n"/>
-      <c r="B56" s="31" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C56" s="33" t="inlineStr">
-        <is>
-          <t>Official Review</t>
-        </is>
-      </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>Intangible Played: Discard all Intangibles from player.</t>
-        </is>
-      </c>
-      <c r="E56" s="35" t="n"/>
-      <c r="F56" s="123" t="n">
-        <v>5</v>
-      </c>
-      <c r="G56" s="96" t="n"/>
-      <c r="H56" s="130" t="n"/>
-      <c r="I56" s="130" t="n"/>
-      <c r="J56" s="130" t="n"/>
-    </row>
-    <row r="57" ht="42" customHeight="1" s="114">
-      <c r="A57" s="30" t="n"/>
-      <c r="B57" s="31" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C57" s="32" t="inlineStr">
-        <is>
-          <t>Shot Clock Violation</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Shot Attempt: Cancel the shot. TOV +1. Ball OOB</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="124" t="n">
-        <v>5</v>
-      </c>
-      <c r="G57" s="92" t="inlineStr">
-        <is>
-          <t>This inbound does NOT increment the round.</t>
-        </is>
-      </c>
-      <c r="H57" s="130" t="n"/>
-      <c r="I57" s="130" t="n"/>
-      <c r="J57" s="130" t="n"/>
-    </row>
-    <row r="58" ht="28" customHeight="1" s="114">
-      <c r="A58" s="30" t="n"/>
-      <c r="B58" s="31" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C58" s="33" t="inlineStr">
-        <is>
-          <t>Technical Foul</t>
-        </is>
-      </c>
-      <c r="D58" s="34" t="inlineStr">
-        <is>
-          <t>Any Non-Whistle Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E58" s="35" t="n"/>
-      <c r="F58" s="123" t="n"/>
-      <c r="G58" s="96" t="n"/>
-      <c r="H58" s="130" t="n"/>
-      <c r="I58" s="130" t="n"/>
-      <c r="J58" s="130" t="n"/>
-    </row>
-    <row r="59" ht="42" customHeight="1" s="114">
-      <c r="A59" s="30" t="n"/>
-      <c r="B59" s="31" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C59" s="32" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Immediate: Reset Shot Clock. All players draw 1 card</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="124" t="n">
-        <v>5</v>
-      </c>
-      <c r="G59" s="92" t="n"/>
-      <c r="H59" s="130" t="n"/>
-      <c r="I59" s="130" t="n"/>
-      <c r="J59" s="130" t="n"/>
-    </row>
-    <row r="60" ht="29" customHeight="1" s="114" thickBot="1">
-      <c r="A60" s="64" t="n"/>
-      <c r="B60" s="65" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C60" s="66" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D60" s="67" t="inlineStr">
-        <is>
-          <t>Move card played: Cancel card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E60" s="68" t="n"/>
-      <c r="F60" s="141" t="n">
-        <v>5</v>
-      </c>
-      <c r="G60" s="104" t="n"/>
-      <c r="H60" s="133" t="n"/>
-      <c r="I60" s="133" t="n"/>
-      <c r="J60" s="133" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1" s="114">
-      <c r="A61" s="61" t="inlineStr">
+      <c r="G69" s="100" t="n"/>
+      <c r="H69" s="101" t="n"/>
+      <c r="I69" s="101" t="n"/>
+      <c r="J69" s="101" t="n"/>
+    </row>
+    <row r="70" ht="42" customHeight="1" s="72">
+      <c r="A70" s="29" t="n"/>
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B61" s="62" t="n">
-        <v>10</v>
-      </c>
-      <c r="C61" s="63" t="n"/>
-      <c r="D61" s="63" t="n"/>
-      <c r="E61" s="63" t="n"/>
-      <c r="F61" s="139" t="n"/>
-      <c r="G61" s="100" t="n"/>
-      <c r="H61" s="140" t="n"/>
-      <c r="I61" s="140" t="n"/>
-      <c r="J61" s="140" t="n"/>
-    </row>
-    <row r="62" ht="28" customHeight="1" s="114">
-      <c r="A62" s="30" t="n"/>
-      <c r="B62" s="31" t="inlineStr">
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D70" s="33" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is 50% or higher</t>
+        </is>
+      </c>
+      <c r="E70" s="33" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F70" s="81" t="n"/>
+      <c r="G70" s="105" t="n"/>
+      <c r="H70" s="101" t="n"/>
+      <c r="I70" s="101" t="n"/>
+      <c r="J70" s="101" t="n"/>
+    </row>
+    <row r="71" ht="28" customHeight="1" s="72">
+      <c r="A71" s="29" t="n"/>
+      <c r="B71" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C62" s="33" t="inlineStr">
-        <is>
-          <t>2-Minute Warning</t>
-        </is>
-      </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>All players discard down to 2 or fewer cards</t>
-        </is>
-      </c>
-      <c r="E62" s="35" t="n"/>
-      <c r="F62" s="123" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" s="96" t="n"/>
-      <c r="H62" s="130" t="n"/>
-      <c r="I62" s="130" t="n"/>
-      <c r="J62" s="130" t="n"/>
-    </row>
-    <row r="63" ht="28" customHeight="1" s="114">
-      <c r="A63" s="30" t="n"/>
-      <c r="B63" s="31" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C63" s="32" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="124" t="n">
-        <v>5</v>
-      </c>
-      <c r="G63" s="106" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
-      <c r="H63" s="130" t="n"/>
-      <c r="I63" s="130" t="n"/>
-      <c r="J63" s="130" t="n"/>
-    </row>
-    <row r="64" ht="14" customHeight="1" s="114">
-      <c r="A64" s="30" t="n"/>
-      <c r="B64" s="31" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C64" s="33" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E64" s="35" t="n"/>
-      <c r="F64" s="123" t="n">
-        <v>14</v>
-      </c>
-      <c r="G64" s="96" t="n"/>
-      <c r="H64" s="130" t="n"/>
-      <c r="I64" s="130" t="n"/>
-      <c r="J64" s="130" t="n"/>
-    </row>
-    <row r="65" ht="14" customHeight="1" s="114">
-      <c r="A65" s="30" t="n"/>
-      <c r="B65" s="31" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C65" s="32" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="n"/>
-      <c r="F65" s="124" t="n">
-        <v>10</v>
-      </c>
-      <c r="G65" s="92" t="n"/>
-      <c r="H65" s="130" t="n"/>
-      <c r="I65" s="130" t="n"/>
-      <c r="J65" s="130" t="n"/>
-    </row>
-    <row r="66" ht="14" customHeight="1" s="114">
-      <c r="A66" s="30" t="n"/>
-      <c r="B66" s="31" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C66" s="33" t="inlineStr">
-        <is>
-          <t>Foul</t>
-        </is>
-      </c>
-      <c r="D66" s="34" t="inlineStr">
-        <is>
-          <t>Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E66" s="35" t="n"/>
-      <c r="F66" s="123" t="n"/>
-      <c r="G66" s="96" t="n"/>
-      <c r="H66" s="130" t="n"/>
-      <c r="I66" s="130" t="n"/>
-      <c r="J66" s="130" t="n"/>
-    </row>
-    <row r="67" ht="28" customHeight="1" s="114">
-      <c r="A67" s="30" t="n"/>
-      <c r="B67" s="31" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C67" s="32" t="inlineStr">
-        <is>
-          <t>MVP Vote</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 7</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="n"/>
-      <c r="F67" s="124" t="n">
-        <v>5</v>
-      </c>
-      <c r="G67" s="92" t="n"/>
-      <c r="H67" s="130" t="n"/>
-      <c r="I67" s="130" t="n"/>
-      <c r="J67" s="130" t="n"/>
-    </row>
-    <row r="68" ht="28" customHeight="1" s="114">
-      <c r="A68" s="30" t="n"/>
-      <c r="B68" s="31" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C68" s="33" t="inlineStr">
-        <is>
-          <t>Off Night</t>
-        </is>
-      </c>
-      <c r="D68" s="34" t="inlineStr">
-        <is>
-          <t>SHOT -20% this possession</t>
-        </is>
-      </c>
-      <c r="E68" s="35" t="n"/>
-      <c r="F68" s="123" t="n">
-        <v>3</v>
-      </c>
-      <c r="G68" s="96" t="n"/>
-      <c r="H68" s="130" t="n"/>
-      <c r="I68" s="130" t="n"/>
-      <c r="J68" s="130" t="n"/>
-    </row>
-    <row r="69" ht="28" customHeight="1" s="114">
-      <c r="A69" s="30" t="n"/>
-      <c r="B69" s="31" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>Swallowed Whistle</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F69" s="122" t="n">
-        <v>5</v>
-      </c>
-      <c r="G69" s="92" t="n"/>
-      <c r="H69" s="130" t="n"/>
-      <c r="I69" s="130" t="n"/>
-      <c r="J69" s="130" t="n"/>
-    </row>
-    <row r="70" ht="42" customHeight="1" s="114">
-      <c r="A70" s="30" t="n"/>
-      <c r="B70" s="31" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C70" s="33" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
-        </is>
-      </c>
-      <c r="D70" s="34" t="inlineStr">
-        <is>
-          <t>Players cannot shoot when SHOT is 50% or higher</t>
-        </is>
-      </c>
-      <c r="E70" s="34" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F70" s="131" t="n"/>
-      <c r="G70" s="96" t="n"/>
-      <c r="H70" s="130" t="n"/>
-      <c r="I70" s="130" t="n"/>
-      <c r="J70" s="130" t="n"/>
-    </row>
-    <row r="71" ht="28" customHeight="1" s="114">
-      <c r="A71" s="30" t="n"/>
-      <c r="B71" s="31" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
+      <c r="C71" s="31" t="inlineStr">
         <is>
           <t>Traded Mid-Game</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>Swap positions with random other player</t>
         </is>
       </c>
-      <c r="E71" s="8" t="n"/>
-      <c r="F71" s="124" t="n"/>
-      <c r="G71" s="106" t="inlineStr">
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="77" t="n"/>
+      <c r="G71" s="112" t="inlineStr">
         <is>
           <t>Applies to rest of game</t>
         </is>
       </c>
-      <c r="H71" s="130" t="n"/>
-      <c r="I71" s="130" t="n"/>
-      <c r="J71" s="130" t="n"/>
-    </row>
-    <row r="72" ht="20" customHeight="1" s="114">
-      <c r="A72" s="57" t="inlineStr">
+      <c r="H71" s="101" t="n"/>
+      <c r="I71" s="101" t="n"/>
+      <c r="J71" s="101" t="n"/>
+    </row>
+    <row r="72" ht="20" customHeight="1" s="72">
+      <c r="A72" s="55" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="B72" s="58" t="n">
+      <c r="B72" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="59" t="n"/>
-      <c r="D72" s="59" t="n"/>
-      <c r="E72" s="59" t="n"/>
-      <c r="F72" s="142" t="n"/>
-      <c r="G72" s="108" t="n"/>
-      <c r="H72" s="130" t="n"/>
-      <c r="I72" s="130" t="n"/>
-      <c r="J72" s="130" t="n"/>
-    </row>
-    <row r="73" ht="28" customHeight="1" s="114">
-      <c r="A73" s="30" t="n"/>
-      <c r="B73" s="31" t="inlineStr">
+      <c r="C72" s="57" t="n"/>
+      <c r="D72" s="57" t="n"/>
+      <c r="E72" s="57" t="n"/>
+      <c r="F72" s="89" t="n"/>
+      <c r="G72" s="124" t="n"/>
+      <c r="H72" s="101" t="n"/>
+      <c r="I72" s="101" t="n"/>
+      <c r="J72" s="101" t="n"/>
+    </row>
+    <row r="73" ht="28" customHeight="1" s="72">
+      <c r="A73" s="29" t="n"/>
+      <c r="B73" s="30" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="C73" s="32" t="inlineStr">
+      <c r="C73" s="31" t="inlineStr">
         <is>
           <t>Bone Bruise</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Discard 1 card at the start of each turn</t>
         </is>
       </c>
-      <c r="E73" s="8" t="n"/>
-      <c r="F73" s="124" t="n"/>
-      <c r="G73" s="92" t="n"/>
-      <c r="H73" s="130" t="n"/>
-      <c r="I73" s="130" t="n"/>
-      <c r="J73" s="130" t="n"/>
-    </row>
-    <row r="74" ht="20" customHeight="1" s="114">
-      <c r="A74" s="57" t="inlineStr">
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="77" t="n"/>
+      <c r="G73" s="100" t="n"/>
+      <c r="H73" s="101" t="n"/>
+      <c r="I73" s="101" t="n"/>
+      <c r="J73" s="101" t="n"/>
+    </row>
+    <row r="74" ht="20" customHeight="1" s="72">
+      <c r="A74" s="55" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B74" s="58" t="n">
+      <c r="B74" s="56" t="n">
         <v>21</v>
       </c>
-      <c r="C74" s="59" t="n"/>
-      <c r="D74" s="59" t="n"/>
-      <c r="E74" s="59" t="n"/>
-      <c r="F74" s="142" t="n"/>
-      <c r="G74" s="108" t="n"/>
-      <c r="H74" s="130" t="n"/>
-      <c r="I74" s="130" t="n"/>
-      <c r="J74" s="130" t="n"/>
-    </row>
-    <row r="75" ht="42" customHeight="1" s="114">
-      <c r="A75" s="30" t="n"/>
-      <c r="B75" s="31" t="inlineStr">
+      <c r="C74" s="57" t="n"/>
+      <c r="D74" s="57" t="n"/>
+      <c r="E74" s="57" t="n"/>
+      <c r="F74" s="89" t="n"/>
+      <c r="G74" s="124" t="n"/>
+      <c r="H74" s="101" t="n"/>
+      <c r="I74" s="101" t="n"/>
+      <c r="J74" s="101" t="n"/>
+    </row>
+    <row r="75" ht="42" customHeight="1" s="72">
+      <c r="A75" s="97" t="inlineStr">
+        <is>
+          <t>All intangibles are limited to 1</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C75" s="32" t="inlineStr">
+      <c r="C75" s="31" t="inlineStr">
         <is>
           <t>Board-Crasher</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>SHOT +10% upon Rebounding your own missed shot</t>
         </is>
       </c>
-      <c r="E75" s="8" t="n"/>
-      <c r="F75" s="124" t="n"/>
-      <c r="G75" s="92" t="n"/>
-      <c r="H75" s="130" t="n"/>
-      <c r="I75" s="130" t="n"/>
-      <c r="J75" s="130" t="n"/>
-    </row>
-    <row r="76" ht="28" customHeight="1" s="114">
-      <c r="A76" s="30" t="n"/>
-      <c r="B76" s="31" t="inlineStr">
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="77" t="n"/>
+      <c r="G75" s="100" t="n"/>
+      <c r="H75" s="101" t="n"/>
+      <c r="I75" s="101" t="n"/>
+      <c r="J75" s="101" t="n"/>
+    </row>
+    <row r="76" ht="28" customHeight="1" s="72">
+      <c r="A76" s="29" t="n"/>
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C76" s="33" t="inlineStr">
+      <c r="C76" s="32" t="inlineStr">
         <is>
           <t>Catch &amp; Shoot Specialist</t>
         </is>
       </c>
-      <c r="D76" s="34" t="inlineStr">
+      <c r="D76" s="33" t="inlineStr">
         <is>
           <t>Additional SHOT +10% on all received passes</t>
         </is>
       </c>
-      <c r="E76" s="35" t="n"/>
-      <c r="F76" s="123" t="n"/>
-      <c r="G76" s="96" t="n"/>
-      <c r="H76" s="130" t="n"/>
-      <c r="I76" s="130" t="n"/>
-      <c r="J76" s="130" t="n"/>
-    </row>
-    <row r="77" ht="56" customHeight="1" s="114">
-      <c r="A77" s="30" t="n"/>
-      <c r="B77" s="31" t="inlineStr">
+      <c r="E76" s="34" t="n"/>
+      <c r="F76" s="76" t="n"/>
+      <c r="G76" s="105" t="n"/>
+      <c r="H76" s="101" t="n"/>
+      <c r="I76" s="101" t="n"/>
+      <c r="J76" s="101" t="n"/>
+    </row>
+    <row r="77" ht="56" customHeight="1" s="72">
+      <c r="A77" s="29" t="n"/>
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C77" s="32" t="inlineStr">
+      <c r="C77" s="31" t="inlineStr">
         <is>
           <t>Clutch Gene</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
         </is>
       </c>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="124" t="n"/>
-      <c r="G77" s="92" t="n"/>
-      <c r="H77" s="130" t="n"/>
-      <c r="I77" s="130" t="n"/>
-      <c r="J77" s="130" t="n"/>
-    </row>
-    <row r="78" ht="42" customHeight="1" s="114">
-      <c r="A78" s="30" t="n"/>
-      <c r="B78" s="31" t="inlineStr">
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="77" t="n"/>
+      <c r="G77" s="100" t="n"/>
+      <c r="H77" s="101" t="n"/>
+      <c r="I77" s="101" t="n"/>
+      <c r="J77" s="101" t="n"/>
+    </row>
+    <row r="78" ht="42" customHeight="1" s="72">
+      <c r="A78" s="29" t="n"/>
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C78" s="33" t="inlineStr">
+      <c r="C78" s="32" t="inlineStr">
         <is>
           <t>Floor General</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
+      <c r="D78" s="33" t="inlineStr">
         <is>
           <t>You decide all targets for direct targeting passes this round</t>
         </is>
       </c>
-      <c r="E78" s="35" t="n"/>
-      <c r="F78" s="123" t="n"/>
-      <c r="G78" s="96" t="n"/>
-      <c r="H78" s="130" t="n"/>
-      <c r="I78" s="130" t="n"/>
-      <c r="J78" s="130" t="n"/>
-    </row>
-    <row r="79" ht="42" customHeight="1" s="114">
-      <c r="A79" s="30" t="n"/>
-      <c r="B79" s="31" t="inlineStr">
+      <c r="E78" s="34" t="n"/>
+      <c r="F78" s="76" t="n"/>
+      <c r="G78" s="105" t="n"/>
+      <c r="H78" s="101" t="n"/>
+      <c r="I78" s="101" t="n"/>
+      <c r="J78" s="101" t="n"/>
+    </row>
+    <row r="79" ht="42" customHeight="1" s="72">
+      <c r="A79" s="29" t="n"/>
+      <c r="B79" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C79" s="32" t="inlineStr">
+      <c r="C79" s="31" t="inlineStr">
         <is>
           <t>Fox-Like First Step</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>Your Move cards are unaffected by opponents</t>
         </is>
       </c>
-      <c r="F79" s="122" t="n"/>
-      <c r="G79" s="92" t="n"/>
-      <c r="H79" s="130" t="n"/>
-      <c r="I79" s="130" t="n"/>
-      <c r="J79" s="130" t="n"/>
-    </row>
-    <row r="80" ht="28" customHeight="1" s="114">
-      <c r="A80" s="30" t="n"/>
-      <c r="B80" s="31" t="inlineStr">
+      <c r="F79" s="75" t="n"/>
+      <c r="G79" s="100" t="n"/>
+      <c r="H79" s="101" t="n"/>
+      <c r="I79" s="101" t="n"/>
+      <c r="J79" s="101" t="n"/>
+    </row>
+    <row r="80" ht="28" customHeight="1" s="72">
+      <c r="A80" s="29" t="n"/>
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C80" s="33" t="inlineStr">
+      <c r="C80" s="91" t="inlineStr">
         <is>
           <t>Freethrow Merchant</t>
         </is>
       </c>
-      <c r="D80" s="34" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT</t>
-        </is>
-      </c>
-      <c r="E80" s="35" t="n"/>
-      <c r="F80" s="123" t="n"/>
-      <c r="G80" s="96" t="n"/>
-      <c r="H80" s="130" t="n"/>
-      <c r="I80" s="130" t="n"/>
-      <c r="J80" s="130" t="n"/>
-    </row>
-    <row r="81" ht="28" customHeight="1" s="114">
-      <c r="A81" s="30" t="n"/>
-      <c r="B81" s="31" t="inlineStr">
+      <c r="D80" s="95" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
+        </is>
+      </c>
+      <c r="E80" s="34" t="n"/>
+      <c r="F80" s="76" t="n"/>
+      <c r="G80" s="111" t="n"/>
+      <c r="H80" s="101" t="n"/>
+      <c r="I80" s="101" t="n"/>
+      <c r="J80" s="101" t="n"/>
+    </row>
+    <row r="81" ht="28" customHeight="1" s="72">
+      <c r="A81" s="29" t="n"/>
+      <c r="B81" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C81" s="32" t="inlineStr">
+      <c r="C81" s="91" t="inlineStr">
         <is>
           <t>Generational Whistle</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D81" s="92" t="inlineStr">
         <is>
           <t>Take 1 additional FT</t>
         </is>
       </c>
-      <c r="E81" s="8" t="n"/>
-      <c r="F81" s="124" t="n"/>
-      <c r="G81" s="92" t="n"/>
-      <c r="H81" s="130" t="n"/>
-      <c r="I81" s="130" t="n"/>
-      <c r="J81" s="130" t="n"/>
-    </row>
-    <row r="82" ht="56" customHeight="1" s="114">
-      <c r="A82" s="30" t="n"/>
-      <c r="B82" s="31" t="inlineStr">
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="77" t="n"/>
+      <c r="G81" s="100" t="n"/>
+      <c r="H81" s="101" t="n"/>
+      <c r="I81" s="101" t="n"/>
+      <c r="J81" s="101" t="n"/>
+    </row>
+    <row r="82" ht="56" customHeight="1" s="72">
+      <c r="A82" s="29" t="n"/>
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C82" s="33" t="inlineStr">
+      <c r="C82" s="32" t="inlineStr">
         <is>
           <t>Gravity</t>
         </is>
       </c>
-      <c r="D82" s="34" t="inlineStr">
+      <c r="D82" s="33" t="inlineStr">
         <is>
           <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
         </is>
       </c>
-      <c r="E82" s="35" t="n"/>
-      <c r="F82" s="123" t="n"/>
-      <c r="G82" s="96" t="n"/>
-      <c r="H82" s="130" t="n"/>
-      <c r="I82" s="130" t="n"/>
-      <c r="J82" s="130" t="n"/>
-    </row>
-    <row r="83" ht="56" customHeight="1" s="114">
-      <c r="A83" s="30" t="n"/>
-      <c r="B83" s="31" t="inlineStr">
+      <c r="E82" s="34" t="n"/>
+      <c r="F82" s="76" t="n"/>
+      <c r="G82" s="105" t="n"/>
+      <c r="H82" s="101" t="n"/>
+      <c r="I82" s="101" t="n"/>
+      <c r="J82" s="101" t="n"/>
+    </row>
+    <row r="83" ht="56" customHeight="1" s="72">
+      <c r="A83" s="29" t="n"/>
+      <c r="B83" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C83" s="32" t="inlineStr">
+      <c r="C83" s="31" t="inlineStr">
         <is>
           <t>Great Conditioning</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
         </is>
       </c>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="124" t="n"/>
-      <c r="G83" s="92" t="n"/>
-      <c r="H83" s="130" t="n"/>
-      <c r="I83" s="130" t="n"/>
-      <c r="J83" s="130" t="n"/>
-    </row>
-    <row r="84" ht="28" customHeight="1" s="114">
-      <c r="A84" s="30" t="n"/>
-      <c r="B84" s="31" t="inlineStr">
+      <c r="E83" s="7" t="n"/>
+      <c r="F83" s="77" t="n"/>
+      <c r="G83" s="100" t="n"/>
+      <c r="H83" s="101" t="n"/>
+      <c r="I83" s="101" t="n"/>
+      <c r="J83" s="101" t="n"/>
+    </row>
+    <row r="84" ht="28" customHeight="1" s="72">
+      <c r="A84" s="29" t="n"/>
+      <c r="B84" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C84" s="33" t="inlineStr">
+      <c r="C84" s="32" t="inlineStr">
         <is>
           <t>Hot Hand</t>
         </is>
       </c>
-      <c r="D84" s="34" t="inlineStr">
+      <c r="D84" s="33" t="inlineStr">
         <is>
           <t>SHOT +20% if you scored last round.</t>
         </is>
       </c>
-      <c r="E84" s="35" t="n"/>
-      <c r="F84" s="123" t="n">
+      <c r="E84" s="34" t="n"/>
+      <c r="F84" s="76" t="n"/>
+      <c r="G84" s="105" t="n"/>
+      <c r="H84" s="101" t="n"/>
+      <c r="I84" s="101" t="n"/>
+      <c r="J84" s="101" t="n"/>
+    </row>
+    <row r="85" ht="42" customHeight="1" s="72">
+      <c r="A85" s="29" t="n"/>
+      <c r="B85" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C85" s="31" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D85" s="92" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="77" t="n"/>
+      <c r="G85" s="100" t="n"/>
+      <c r="H85" s="101" t="n"/>
+      <c r="I85" s="101" t="n"/>
+      <c r="J85" s="101" t="n"/>
+    </row>
+    <row r="86" ht="28" customHeight="1" s="72">
+      <c r="A86" s="29" t="n"/>
+      <c r="B86" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>No Bag</t>
+        </is>
+      </c>
+      <c r="D86" s="33" t="inlineStr">
+        <is>
+          <t>Cannot activate Move cards this round</t>
+        </is>
+      </c>
+      <c r="E86" s="34" t="n"/>
+      <c r="F86" s="76" t="n"/>
+      <c r="G86" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
+      <c r="H86" s="101" t="n"/>
+      <c r="I86" s="101" t="n"/>
+      <c r="J86" s="101" t="n"/>
+    </row>
+    <row r="87" ht="42" customHeight="1" s="72">
+      <c r="A87" s="29" t="n"/>
+      <c r="B87" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C87" s="31" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes this round</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="77" t="n"/>
+      <c r="G87" s="100" t="n"/>
+      <c r="H87" s="101" t="n"/>
+      <c r="I87" s="101" t="n"/>
+      <c r="J87" s="101" t="n"/>
+    </row>
+    <row r="88" ht="14" customHeight="1" s="72">
+      <c r="A88" s="29" t="n"/>
+      <c r="B88" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C88" s="32" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D88" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E88" s="34" t="n"/>
+      <c r="F88" s="76" t="n"/>
+      <c r="G88" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
+      <c r="H88" s="101" t="n"/>
+      <c r="I88" s="101" t="n"/>
+      <c r="J88" s="101" t="n"/>
+    </row>
+    <row r="89" ht="28" customHeight="1" s="72">
+      <c r="A89" s="29" t="n"/>
+      <c r="B89" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C89" s="31" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="n"/>
+      <c r="F89" s="77" t="n"/>
+      <c r="G89" s="100" t="n"/>
+      <c r="H89" s="101" t="n"/>
+      <c r="I89" s="101" t="n"/>
+      <c r="J89" s="101" t="n"/>
+    </row>
+    <row r="90" ht="28" customHeight="1" s="72">
+      <c r="A90" s="29" t="n"/>
+      <c r="B90" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D90" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E90" s="34" t="n"/>
+      <c r="F90" s="76" t="n"/>
+      <c r="G90" s="105" t="n"/>
+      <c r="H90" s="101" t="n"/>
+      <c r="I90" s="101" t="n"/>
+      <c r="J90" s="101" t="n"/>
+    </row>
+    <row r="91" ht="28" customHeight="1" s="72">
+      <c r="A91" s="29" t="n"/>
+      <c r="B91" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C91" s="31" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="n"/>
+      <c r="F91" s="77" t="n"/>
+      <c r="G91" s="100" t="n"/>
+      <c r="H91" s="101" t="n"/>
+      <c r="I91" s="101" t="n"/>
+      <c r="J91" s="101" t="n"/>
+    </row>
+    <row r="92" ht="28" customHeight="1" s="72">
+      <c r="A92" s="29" t="n"/>
+      <c r="B92" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D92" s="33" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E92" s="34" t="n"/>
+      <c r="F92" s="76" t="n"/>
+      <c r="G92" s="105" t="n"/>
+      <c r="H92" s="101" t="n"/>
+      <c r="I92" s="101" t="n"/>
+      <c r="J92" s="101" t="n"/>
+    </row>
+    <row r="93" ht="42" customHeight="1" s="72">
+      <c r="A93" s="29" t="n"/>
+      <c r="B93" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C93" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D93" s="92" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="77" t="n"/>
+      <c r="G93" s="100" t="n"/>
+      <c r="H93" s="101" t="n"/>
+      <c r="I93" s="101" t="n"/>
+      <c r="J93" s="101" t="n"/>
+    </row>
+    <row r="94" ht="56" customHeight="1" s="72">
+      <c r="A94" s="29" t="n"/>
+      <c r="B94" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D94" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E94" s="34" t="n"/>
+      <c r="F94" s="76" t="n"/>
+      <c r="G94" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H94" s="101" t="n"/>
+      <c r="I94" s="101" t="n"/>
+      <c r="J94" s="101" t="n"/>
+    </row>
+    <row r="95" ht="57" customHeight="1" s="72" thickBot="1">
+      <c r="A95" s="62" t="n"/>
+      <c r="B95" s="63" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C95" s="67" t="inlineStr">
+        <is>
+          <t>Ball Pounder</t>
+        </is>
+      </c>
+      <c r="D95" s="96" t="inlineStr">
+        <is>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
+        </is>
+      </c>
+      <c r="E95" s="69" t="n"/>
+      <c r="F95" s="86" t="n"/>
+      <c r="G95" s="106" t="n"/>
+      <c r="H95" s="107" t="n"/>
+      <c r="I95" s="107" t="n"/>
+      <c r="J95" s="107" t="n"/>
+    </row>
+    <row r="96" ht="20" customHeight="1" s="72">
+      <c r="A96" s="59" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="B96" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="G84" s="96" t="n"/>
-      <c r="H84" s="130" t="n"/>
-      <c r="I84" s="130" t="n"/>
-      <c r="J84" s="130" t="n"/>
-    </row>
-    <row r="85" ht="42" customHeight="1" s="114">
-      <c r="A85" s="30" t="n"/>
-      <c r="B85" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C85" s="32" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>SHOT cannot be reduced during your possessions this round</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="124" t="n"/>
-      <c r="G85" s="92" t="n"/>
-      <c r="H85" s="130" t="n"/>
-      <c r="I85" s="130" t="n"/>
-      <c r="J85" s="130" t="n"/>
-    </row>
-    <row r="86" ht="28" customHeight="1" s="114">
-      <c r="A86" s="30" t="n"/>
-      <c r="B86" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C86" s="33" t="inlineStr">
-        <is>
-          <t>No Bag</t>
-        </is>
-      </c>
-      <c r="D86" s="34" t="inlineStr">
-        <is>
-          <t>Cannot activate Move cards this round</t>
-        </is>
-      </c>
-      <c r="E86" s="35" t="n"/>
-      <c r="F86" s="123" t="n"/>
-      <c r="G86" s="102" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
-      <c r="H86" s="130" t="n"/>
-      <c r="I86" s="130" t="n"/>
-      <c r="J86" s="130" t="n"/>
-    </row>
-    <row r="87" ht="42" customHeight="1" s="114">
-      <c r="A87" s="30" t="n"/>
-      <c r="B87" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C87" s="32" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes this round</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="n"/>
-      <c r="F87" s="124" t="n"/>
-      <c r="G87" s="92" t="n"/>
-      <c r="H87" s="130" t="n"/>
-      <c r="I87" s="130" t="n"/>
-      <c r="J87" s="130" t="n"/>
-    </row>
-    <row r="88" ht="14" customHeight="1" s="114">
-      <c r="A88" s="30" t="n"/>
-      <c r="B88" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C88" s="33" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D88" s="34" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
-        </is>
-      </c>
-      <c r="E88" s="35" t="n"/>
-      <c r="F88" s="123" t="n"/>
-      <c r="G88" s="102" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
-      <c r="H88" s="130" t="n"/>
-      <c r="I88" s="130" t="n"/>
-      <c r="J88" s="130" t="n"/>
-    </row>
-    <row r="89" ht="28" customHeight="1" s="114">
-      <c r="A89" s="30" t="n"/>
-      <c r="B89" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C89" s="32" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="n"/>
-      <c r="F89" s="124" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="92" t="n"/>
-      <c r="H89" s="130" t="n"/>
-      <c r="I89" s="130" t="n"/>
-      <c r="J89" s="130" t="n"/>
-    </row>
-    <row r="90" ht="28" customHeight="1" s="114">
-      <c r="A90" s="30" t="n"/>
-      <c r="B90" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C90" s="33" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D90" s="34" t="inlineStr">
-        <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
-        </is>
-      </c>
-      <c r="E90" s="35" t="n"/>
-      <c r="F90" s="123" t="n"/>
-      <c r="G90" s="96" t="n"/>
-      <c r="H90" s="130" t="n"/>
-      <c r="I90" s="130" t="n"/>
-      <c r="J90" s="130" t="n"/>
-    </row>
-    <row r="91" ht="28" customHeight="1" s="114">
-      <c r="A91" s="30" t="n"/>
-      <c r="B91" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C91" s="32" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="n"/>
-      <c r="F91" s="124" t="n"/>
-      <c r="G91" s="92" t="n"/>
-      <c r="H91" s="130" t="n"/>
-      <c r="I91" s="130" t="n"/>
-      <c r="J91" s="130" t="n"/>
-    </row>
-    <row r="92" ht="28" customHeight="1" s="114">
-      <c r="A92" s="30" t="n"/>
-      <c r="B92" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C92" s="33" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D92" s="34" t="inlineStr">
-        <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E92" s="35" t="n"/>
-      <c r="F92" s="123" t="n"/>
-      <c r="G92" s="96" t="n"/>
-      <c r="H92" s="130" t="n"/>
-      <c r="I92" s="130" t="n"/>
-      <c r="J92" s="130" t="n"/>
-    </row>
-    <row r="93" ht="42" customHeight="1" s="114">
-      <c r="A93" s="30" t="n"/>
-      <c r="B93" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C93" s="32" t="inlineStr">
-        <is>
-          <t>Unguardable</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on shots taken this round</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="n"/>
-      <c r="F93" s="124" t="n"/>
-      <c r="G93" s="92" t="n"/>
-      <c r="H93" s="130" t="n"/>
-      <c r="I93" s="130" t="n"/>
-      <c r="J93" s="130" t="n"/>
-    </row>
-    <row r="94" ht="56" customHeight="1" s="114">
-      <c r="A94" s="30" t="n"/>
-      <c r="B94" s="31" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C94" s="33" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D94" s="34" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
-        </is>
-      </c>
-      <c r="E94" s="35" t="n"/>
-      <c r="F94" s="123" t="n"/>
-      <c r="G94" s="102" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
-      <c r="H94" s="130" t="n"/>
-      <c r="I94" s="130" t="n"/>
-      <c r="J94" s="130" t="n"/>
-    </row>
-    <row r="95" ht="57" customHeight="1" s="114" thickBot="1">
-      <c r="A95" s="64" t="n"/>
-      <c r="B95" s="65" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C95" s="71" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D95" s="72" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw and additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E95" s="73" t="n"/>
-      <c r="F95" s="137" t="n"/>
-      <c r="G95" s="98" t="n"/>
-      <c r="H95" s="133" t="n"/>
-      <c r="I95" s="133" t="n"/>
-      <c r="J95" s="133" t="n"/>
-    </row>
-    <row r="96" ht="20" customHeight="1" s="114">
-      <c r="A96" s="61" t="inlineStr">
+      <c r="C96" s="61" t="n"/>
+      <c r="D96" s="61" t="n"/>
+      <c r="E96" s="61" t="n"/>
+      <c r="F96" s="87" t="n"/>
+      <c r="G96" s="119" t="n"/>
+      <c r="H96" s="120" t="n"/>
+      <c r="I96" s="120" t="n"/>
+      <c r="J96" s="120" t="n"/>
+    </row>
+    <row r="97" ht="28" customHeight="1" s="72">
+      <c r="A97" s="50" t="n"/>
+      <c r="B97" s="51" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="B96" s="62" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" s="63" t="n"/>
-      <c r="D96" s="63" t="n"/>
-      <c r="E96" s="63" t="n"/>
-      <c r="F96" s="139" t="n"/>
-      <c r="G96" s="100" t="n"/>
-      <c r="H96" s="140" t="n"/>
-      <c r="I96" s="140" t="n"/>
-      <c r="J96" s="140" t="n"/>
-    </row>
-    <row r="97" ht="28" customHeight="1" s="114">
-      <c r="A97" s="52" t="n"/>
-      <c r="B97" s="53" t="inlineStr">
-        <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="C97" s="60" t="n"/>
-      <c r="D97" s="56" t="n"/>
-      <c r="E97" s="56" t="n"/>
-      <c r="F97" s="143" t="n"/>
-      <c r="G97" s="110" t="n"/>
-      <c r="H97" s="144" t="n"/>
-      <c r="I97" s="144" t="n"/>
-      <c r="J97" s="144" t="n"/>
+      <c r="C97" s="58" t="n"/>
+      <c r="D97" s="54" t="n"/>
+      <c r="E97" s="54" t="n"/>
+      <c r="F97" s="90" t="n"/>
+      <c r="G97" s="117" t="n"/>
+      <c r="H97" s="118" t="n"/>
+      <c r="I97" s="118" t="n"/>
+      <c r="J97" s="118" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="95">
@@ -5165,9 +5078,9 @@
     <mergeCell ref="G85:J85"/>
     <mergeCell ref="G94:J94"/>
     <mergeCell ref="G84:J84"/>
-    <mergeCell ref="G44:J44"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G44:J44"/>
     <mergeCell ref="G31:J31"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -3716,7 +3716,11 @@
       <c r="J44" s="120" t="n"/>
     </row>
     <row r="45" ht="56" customHeight="1" s="72">
-      <c r="A45" s="29" t="n"/>
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>All whistles are limited to 1</t>
+        </is>
+      </c>
       <c r="B45" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
@@ -3733,9 +3737,7 @@
         </is>
       </c>
       <c r="E45" s="7" t="n"/>
-      <c r="F45" s="77" t="n">
-        <v>5</v>
-      </c>
+      <c r="F45" s="77" t="n"/>
       <c r="G45" s="100" t="inlineStr">
         <is>
           <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
@@ -3839,9 +3841,7 @@
           <t>Pull a Timeout from the discards, if one is there, and take it</t>
         </is>
       </c>
-      <c r="F49" s="77" t="n">
-        <v>5</v>
-      </c>
+      <c r="F49" s="77" t="n"/>
       <c r="G49" s="100" t="n"/>
       <c r="H49" s="101" t="n"/>
       <c r="I49" s="101" t="n"/>
@@ -3869,9 +3869,7 @@
           <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
         </is>
       </c>
-      <c r="F50" s="81" t="n">
-        <v>6</v>
-      </c>
+      <c r="F50" s="81" t="n"/>
       <c r="G50" s="113" t="inlineStr">
         <is>
           <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
@@ -3899,9 +3897,7 @@
         </is>
       </c>
       <c r="E51" s="7" t="n"/>
-      <c r="F51" s="77" t="n">
-        <v>5</v>
-      </c>
+      <c r="F51" s="77" t="n"/>
       <c r="G51" s="100" t="inlineStr">
         <is>
           <t>The dribbling player inbounds. The round is NOT incremented.</t>
@@ -3977,9 +3973,7 @@
         </is>
       </c>
       <c r="E54" s="34" t="n"/>
-      <c r="F54" s="76" t="n">
-        <v>3</v>
-      </c>
+      <c r="F54" s="76" t="n"/>
       <c r="G54" s="105" t="n"/>
       <c r="H54" s="101" t="n"/>
       <c r="I54" s="101" t="n"/>
@@ -4003,9 +3997,7 @@
         </is>
       </c>
       <c r="E55" s="7" t="n"/>
-      <c r="F55" s="77" t="n">
-        <v>5</v>
-      </c>
+      <c r="F55" s="77" t="n"/>
       <c r="G55" s="100" t="n"/>
       <c r="H55" s="101" t="n"/>
       <c r="I55" s="101" t="n"/>
@@ -4029,9 +4021,7 @@
         </is>
       </c>
       <c r="E56" s="34" t="n"/>
-      <c r="F56" s="76" t="n">
-        <v>5</v>
-      </c>
+      <c r="F56" s="76" t="n"/>
       <c r="G56" s="105" t="n"/>
       <c r="H56" s="101" t="n"/>
       <c r="I56" s="101" t="n"/>
@@ -4055,9 +4045,7 @@
         </is>
       </c>
       <c r="E57" s="7" t="n"/>
-      <c r="F57" s="77" t="n">
-        <v>5</v>
-      </c>
+      <c r="F57" s="77" t="n"/>
       <c r="G57" s="100" t="inlineStr">
         <is>
           <t>This inbound does NOT increment the round.</t>
@@ -4109,9 +4097,7 @@
         </is>
       </c>
       <c r="E59" s="7" t="n"/>
-      <c r="F59" s="77" t="n">
-        <v>5</v>
-      </c>
+      <c r="F59" s="77" t="n"/>
       <c r="G59" s="100" t="n"/>
       <c r="H59" s="101" t="n"/>
       <c r="I59" s="101" t="n"/>
@@ -4135,9 +4121,7 @@
         </is>
       </c>
       <c r="E60" s="66" t="n"/>
-      <c r="F60" s="88" t="n">
-        <v>5</v>
-      </c>
+      <c r="F60" s="88" t="n"/>
       <c r="G60" s="121" t="n"/>
       <c r="H60" s="107" t="n"/>
       <c r="I60" s="107" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/azurin/My iOS Projects/Games/Project CardCourt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C870F15-6E3C-AB49-9BE4-C4D0C4703429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753C752E-7F30-3240-BB51-4F82ECF8D32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="-19300" windowWidth="21600" windowHeight="20980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="660" windowWidth="21600" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card Types" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="235">
   <si>
     <t>Card Types</t>
   </si>
@@ -271,9 +271,6 @@
     <t>Skyhook</t>
   </si>
   <si>
-    <t>Shot is unaffected by Clamps</t>
-  </si>
-  <si>
     <t>Slam Dunk</t>
   </si>
   <si>
@@ -721,7 +718,19 @@
     <t>All players draw 2 cards</t>
   </si>
   <si>
-    <t>They can still shoot as another option</t>
+    <t>Shoot the ball. Shot is unaffected by Clamps</t>
+  </si>
+  <si>
+    <t>1 def</t>
+  </si>
+  <si>
+    <t>2 def</t>
+  </si>
+  <si>
+    <t>They can still shoot as another option; 3 def</t>
+  </si>
+  <si>
+    <t>3 def</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1503,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1877,6 +1886,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3029,10 +3041,10 @@
     </row>
     <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3043,7 +3055,7 @@
         <v>59</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -3054,7 +3066,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -3065,7 +3077,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3076,7 +3088,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -3087,7 +3099,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -3098,7 +3110,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -3109,7 +3121,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -3117,10 +3129,10 @@
     </row>
     <row r="10" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -3128,10 +3140,10 @@
     </row>
     <row r="11" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -3624,10 +3636,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="134" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D23" s="95" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E23" s="34"/>
       <c r="F23" s="76">
@@ -3644,17 +3656,17 @@
         <v>2</v>
       </c>
       <c r="C24" s="134" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D24" s="95" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E24" s="34"/>
       <c r="F24" s="76">
         <v>10</v>
       </c>
       <c r="G24" s="100" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H24" s="98"/>
       <c r="I24" s="98"/>
@@ -3666,17 +3678,17 @@
         <v>2</v>
       </c>
       <c r="C25" s="134" t="s">
+        <v>226</v>
+      </c>
+      <c r="D25" s="95" t="s">
         <v>227</v>
-      </c>
-      <c r="D25" s="95" t="s">
-        <v>228</v>
       </c>
       <c r="E25" s="34"/>
       <c r="F25" s="76">
         <v>5</v>
       </c>
       <c r="G25" s="100" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H25" s="98"/>
       <c r="I25" s="98"/>
@@ -3931,8 +3943,8 @@
       <c r="D37" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="33" t="s">
-        <v>81</v>
+      <c r="E37" s="95" t="s">
+        <v>230</v>
       </c>
       <c r="F37" s="81"/>
       <c r="G37" s="106"/>
@@ -3946,10 +3958,10 @@
         <v>59</v>
       </c>
       <c r="C38" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>62</v>
@@ -3966,10 +3978,10 @@
         <v>59</v>
       </c>
       <c r="C39" s="70" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="71" t="s">
         <v>84</v>
-      </c>
-      <c r="D39" s="71" t="s">
-        <v>85</v>
       </c>
       <c r="E39" s="71" t="s">
         <v>68</v>
@@ -3978,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="130" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H39" s="107"/>
       <c r="I39" s="107"/>
@@ -3990,10 +4002,10 @@
         <v>59</v>
       </c>
       <c r="C40" s="67" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="68" t="s">
         <v>87</v>
-      </c>
-      <c r="D40" s="68" t="s">
-        <v>88</v>
       </c>
       <c r="E40" s="69"/>
       <c r="F40" s="86">
@@ -4026,16 +4038,18 @@
         <v>3</v>
       </c>
       <c r="C42" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="77">
         <v>10</v>
       </c>
-      <c r="G42" s="102"/>
+      <c r="G42" s="131" t="s">
+        <v>231</v>
+      </c>
       <c r="H42" s="103"/>
       <c r="I42" s="103"/>
       <c r="J42" s="103"/>
@@ -4046,16 +4060,18 @@
         <v>3</v>
       </c>
       <c r="C43" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="33" t="s">
         <v>91</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>92</v>
       </c>
       <c r="E43" s="34"/>
       <c r="F43" s="76">
         <v>4</v>
       </c>
-      <c r="G43" s="108"/>
+      <c r="G43" s="126" t="s">
+        <v>232</v>
+      </c>
       <c r="H43" s="103"/>
       <c r="I43" s="103"/>
       <c r="J43" s="103"/>
@@ -4066,16 +4082,18 @@
         <v>3</v>
       </c>
       <c r="C44" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="77">
         <v>3</v>
       </c>
-      <c r="G44" s="102"/>
+      <c r="G44" s="131" t="s">
+        <v>231</v>
+      </c>
       <c r="H44" s="103"/>
       <c r="I44" s="103"/>
       <c r="J44" s="103"/>
@@ -4086,17 +4104,17 @@
         <v>3</v>
       </c>
       <c r="C45" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="95" t="s">
         <v>95</v>
-      </c>
-      <c r="D45" s="95" t="s">
-        <v>96</v>
       </c>
       <c r="E45" s="34"/>
       <c r="F45" s="76">
         <v>5</v>
       </c>
       <c r="G45" s="126" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H45" s="103"/>
       <c r="I45" s="103"/>
@@ -4108,16 +4126,18 @@
         <v>3</v>
       </c>
       <c r="C46" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" s="68" t="s">
         <v>97</v>
-      </c>
-      <c r="D46" s="68" t="s">
-        <v>98</v>
       </c>
       <c r="E46" s="69"/>
       <c r="F46" s="86">
         <v>2</v>
       </c>
-      <c r="G46" s="127"/>
+      <c r="G46" s="136" t="s">
+        <v>234</v>
+      </c>
       <c r="H46" s="118"/>
       <c r="I46" s="118"/>
       <c r="J46" s="118"/>
@@ -4140,21 +4160,21 @@
     </row>
     <row r="48" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B48" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="77"/>
       <c r="G48" s="102" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H48" s="103"/>
       <c r="I48" s="103"/>
@@ -4166,10 +4186,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="94" t="s">
         <v>103</v>
-      </c>
-      <c r="D49" s="94" t="s">
-        <v>104</v>
       </c>
       <c r="E49" s="34"/>
       <c r="F49" s="76"/>
@@ -4184,10 +4204,10 @@
         <v>4</v>
       </c>
       <c r="C50" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="93" t="s">
         <v>105</v>
-      </c>
-      <c r="D50" s="93" t="s">
-        <v>106</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="77"/>
@@ -4202,10 +4222,10 @@
         <v>4</v>
       </c>
       <c r="C51" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="33" t="s">
         <v>107</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>108</v>
       </c>
       <c r="E51" s="34"/>
       <c r="F51" s="76"/>
@@ -4220,13 +4240,13 @@
         <v>4</v>
       </c>
       <c r="C52" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="E52" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="F52" s="77"/>
       <c r="G52" s="102"/>
@@ -4240,17 +4260,17 @@
         <v>4</v>
       </c>
       <c r="C53" s="91" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="D53" s="33" t="s">
+      <c r="E53" s="33" t="s">
         <v>113</v>
-      </c>
-      <c r="E53" s="33" t="s">
-        <v>114</v>
       </c>
       <c r="F53" s="81"/>
       <c r="G53" s="114" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H53" s="103"/>
       <c r="I53" s="103"/>
@@ -4262,15 +4282,15 @@
         <v>4</v>
       </c>
       <c r="C54" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="77"/>
       <c r="G54" s="102" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H54" s="103"/>
       <c r="I54" s="103"/>
@@ -4282,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C55" s="91" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55" s="95" t="s">
         <v>119</v>
-      </c>
-      <c r="D55" s="95" t="s">
-        <v>120</v>
       </c>
       <c r="E55" s="34"/>
       <c r="F55" s="76"/>
@@ -4300,10 +4320,10 @@
         <v>4</v>
       </c>
       <c r="C56" s="91" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="92" t="s">
         <v>121</v>
-      </c>
-      <c r="D56" s="92" t="s">
-        <v>122</v>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="77"/>
@@ -4318,10 +4338,10 @@
         <v>4</v>
       </c>
       <c r="C57" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D57" s="33" t="s">
         <v>123</v>
-      </c>
-      <c r="D57" s="33" t="s">
-        <v>124</v>
       </c>
       <c r="E57" s="34"/>
       <c r="F57" s="76"/>
@@ -4336,10 +4356,10 @@
         <v>4</v>
       </c>
       <c r="C58" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="77"/>
@@ -4354,10 +4374,10 @@
         <v>4</v>
       </c>
       <c r="C59" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="33" t="s">
         <v>127</v>
-      </c>
-      <c r="D59" s="33" t="s">
-        <v>128</v>
       </c>
       <c r="E59" s="34"/>
       <c r="F59" s="76"/>
@@ -4372,15 +4392,15 @@
         <v>4</v>
       </c>
       <c r="C60" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="77"/>
       <c r="G60" s="102" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H60" s="103"/>
       <c r="I60" s="103"/>
@@ -4392,10 +4412,10 @@
         <v>4</v>
       </c>
       <c r="C61" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="D61" s="33" t="s">
         <v>132</v>
-      </c>
-      <c r="D61" s="33" t="s">
-        <v>133</v>
       </c>
       <c r="E61" s="34"/>
       <c r="F61" s="76"/>
@@ -4410,10 +4430,10 @@
         <v>4</v>
       </c>
       <c r="C62" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="77"/>
@@ -4428,10 +4448,10 @@
         <v>4</v>
       </c>
       <c r="C63" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" s="65" t="s">
         <v>136</v>
-      </c>
-      <c r="D63" s="65" t="s">
-        <v>137</v>
       </c>
       <c r="E63" s="66"/>
       <c r="F63" s="88"/>
@@ -4462,10 +4482,10 @@
         <v>5</v>
       </c>
       <c r="C65" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" s="33" t="s">
         <v>138</v>
-      </c>
-      <c r="D65" s="33" t="s">
-        <v>139</v>
       </c>
       <c r="E65" s="34"/>
       <c r="F65" s="76">
@@ -4482,17 +4502,17 @@
         <v>5</v>
       </c>
       <c r="C66" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="77">
         <v>5</v>
       </c>
       <c r="G66" s="112" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H66" s="103"/>
       <c r="I66" s="103"/>
@@ -4504,10 +4524,10 @@
         <v>5</v>
       </c>
       <c r="C67" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="D67" s="33" t="s">
         <v>143</v>
-      </c>
-      <c r="D67" s="33" t="s">
-        <v>144</v>
       </c>
       <c r="E67" s="34"/>
       <c r="F67" s="76">
@@ -4524,10 +4544,10 @@
         <v>5</v>
       </c>
       <c r="C68" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="E68" s="7"/>
       <c r="F68" s="77">
@@ -4544,10 +4564,10 @@
         <v>5</v>
       </c>
       <c r="C69" s="91" t="s">
+        <v>146</v>
+      </c>
+      <c r="D69" s="33" t="s">
         <v>147</v>
-      </c>
-      <c r="D69" s="33" t="s">
-        <v>148</v>
       </c>
       <c r="E69" s="34"/>
       <c r="F69" s="76"/>
@@ -4562,10 +4582,10 @@
         <v>5</v>
       </c>
       <c r="C70" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="D70" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="77">
@@ -4582,10 +4602,10 @@
         <v>5</v>
       </c>
       <c r="C71" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="D71" s="33" t="s">
         <v>151</v>
-      </c>
-      <c r="D71" s="33" t="s">
-        <v>152</v>
       </c>
       <c r="E71" s="34"/>
       <c r="F71" s="76">
@@ -4602,13 +4622,13 @@
         <v>5</v>
       </c>
       <c r="C72" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="D72" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="E72" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="F72" s="75">
         <v>5</v>
@@ -4624,13 +4644,13 @@
         <v>5</v>
       </c>
       <c r="C73" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="D73" s="33" t="s">
-        <v>157</v>
-      </c>
       <c r="E73" s="33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F73" s="81"/>
       <c r="G73" s="108"/>
@@ -4644,15 +4664,15 @@
         <v>5</v>
       </c>
       <c r="C74" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D74" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="77"/>
       <c r="G74" s="112" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H74" s="103"/>
       <c r="I74" s="103"/>
@@ -4664,10 +4684,10 @@
         <v>5</v>
       </c>
       <c r="C75" s="135" t="s">
+        <v>228</v>
+      </c>
+      <c r="D75" s="92" t="s">
         <v>229</v>
-      </c>
-      <c r="D75" s="92" t="s">
-        <v>230</v>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="77">
@@ -4700,10 +4720,10 @@
         <v>7</v>
       </c>
       <c r="C77" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D77" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="E77" s="7"/>
       <c r="F77" s="77"/>
@@ -4730,16 +4750,16 @@
     </row>
     <row r="79" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="97" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B79" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="D79" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="77"/>
@@ -4754,10 +4774,10 @@
         <v>6</v>
       </c>
       <c r="C80" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="D80" s="33" t="s">
         <v>166</v>
-      </c>
-      <c r="D80" s="33" t="s">
-        <v>167</v>
       </c>
       <c r="E80" s="34"/>
       <c r="F80" s="76"/>
@@ -4772,10 +4792,10 @@
         <v>6</v>
       </c>
       <c r="C81" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D81" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="77"/>
@@ -4790,10 +4810,10 @@
         <v>6</v>
       </c>
       <c r="C82" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="D82" s="33" t="s">
         <v>170</v>
-      </c>
-      <c r="D82" s="33" t="s">
-        <v>171</v>
       </c>
       <c r="E82" s="34"/>
       <c r="F82" s="76"/>
@@ -4808,13 +4828,13 @@
         <v>6</v>
       </c>
       <c r="C83" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="D83" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="E83" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="F83" s="75"/>
       <c r="G83" s="102"/>
@@ -4828,10 +4848,10 @@
         <v>6</v>
       </c>
       <c r="C84" s="91" t="s">
+        <v>174</v>
+      </c>
+      <c r="D84" s="95" t="s">
         <v>175</v>
-      </c>
-      <c r="D84" s="95" t="s">
-        <v>176</v>
       </c>
       <c r="E84" s="34"/>
       <c r="F84" s="76"/>
@@ -4846,10 +4866,10 @@
         <v>6</v>
       </c>
       <c r="C85" s="91" t="s">
+        <v>176</v>
+      </c>
+      <c r="D85" s="92" t="s">
         <v>177</v>
-      </c>
-      <c r="D85" s="92" t="s">
-        <v>178</v>
       </c>
       <c r="E85" s="7"/>
       <c r="F85" s="77"/>
@@ -4864,10 +4884,10 @@
         <v>6</v>
       </c>
       <c r="C86" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="D86" s="33" t="s">
         <v>179</v>
-      </c>
-      <c r="D86" s="33" t="s">
-        <v>180</v>
       </c>
       <c r="E86" s="34"/>
       <c r="F86" s="76"/>
@@ -4882,10 +4902,10 @@
         <v>6</v>
       </c>
       <c r="C87" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="D87" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="E87" s="7"/>
       <c r="F87" s="77"/>
@@ -4900,10 +4920,10 @@
         <v>6</v>
       </c>
       <c r="C88" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="D88" s="33" t="s">
         <v>183</v>
-      </c>
-      <c r="D88" s="33" t="s">
-        <v>184</v>
       </c>
       <c r="E88" s="34"/>
       <c r="F88" s="76"/>
@@ -4918,10 +4938,10 @@
         <v>6</v>
       </c>
       <c r="C89" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="D89" s="92" t="s">
         <v>185</v>
-      </c>
-      <c r="D89" s="92" t="s">
-        <v>186</v>
       </c>
       <c r="E89" s="7"/>
       <c r="F89" s="77"/>
@@ -4936,15 +4956,15 @@
         <v>6</v>
       </c>
       <c r="C90" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D90" s="33" t="s">
         <v>187</v>
-      </c>
-      <c r="D90" s="33" t="s">
-        <v>188</v>
       </c>
       <c r="E90" s="34"/>
       <c r="F90" s="76"/>
       <c r="G90" s="114" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H90" s="103"/>
       <c r="I90" s="103"/>
@@ -4956,10 +4976,10 @@
         <v>6</v>
       </c>
       <c r="C91" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="77"/>
@@ -4974,15 +4994,15 @@
         <v>6</v>
       </c>
       <c r="C92" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="D92" s="33" t="s">
         <v>192</v>
-      </c>
-      <c r="D92" s="33" t="s">
-        <v>193</v>
       </c>
       <c r="E92" s="34"/>
       <c r="F92" s="76"/>
       <c r="G92" s="114" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H92" s="103"/>
       <c r="I92" s="103"/>
@@ -4994,10 +5014,10 @@
         <v>6</v>
       </c>
       <c r="C93" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D93" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="77"/>
@@ -5012,10 +5032,10 @@
         <v>6</v>
       </c>
       <c r="C94" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="D94" s="33" t="s">
         <v>196</v>
-      </c>
-      <c r="D94" s="33" t="s">
-        <v>197</v>
       </c>
       <c r="E94" s="34"/>
       <c r="F94" s="76"/>
@@ -5030,10 +5050,10 @@
         <v>6</v>
       </c>
       <c r="C95" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="D95" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="77"/>
@@ -5048,10 +5068,10 @@
         <v>6</v>
       </c>
       <c r="C96" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="D96" s="33" t="s">
         <v>200</v>
-      </c>
-      <c r="D96" s="33" t="s">
-        <v>201</v>
       </c>
       <c r="E96" s="34"/>
       <c r="F96" s="76"/>
@@ -5066,10 +5086,10 @@
         <v>6</v>
       </c>
       <c r="C97" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" s="92" t="s">
         <v>202</v>
-      </c>
-      <c r="D97" s="92" t="s">
-        <v>203</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="77"/>
@@ -5084,15 +5104,15 @@
         <v>6</v>
       </c>
       <c r="C98" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="D98" s="33" t="s">
         <v>204</v>
-      </c>
-      <c r="D98" s="33" t="s">
-        <v>205</v>
       </c>
       <c r="E98" s="34"/>
       <c r="F98" s="76"/>
       <c r="G98" s="114" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H98" s="103"/>
       <c r="I98" s="103"/>
@@ -5104,10 +5124,10 @@
         <v>6</v>
       </c>
       <c r="C99" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="D99" s="96" t="s">
         <v>207</v>
-      </c>
-      <c r="D99" s="96" t="s">
-        <v>208</v>
       </c>
       <c r="E99" s="69"/>
       <c r="F99" s="86"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/azurin/My iOS Projects/Games/Project CardCourt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753C752E-7F30-3240-BB51-4F82ECF8D32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB988D6-4DC7-6043-894F-7E1B259B8990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="660" windowWidth="21600" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8540" yWindow="1900" windowWidth="21600" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Card Types" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="240">
   <si>
     <t>Card Types</t>
   </si>
@@ -229,9 +229,6 @@
     <t>Dagger Three</t>
   </si>
   <si>
-    <t>SHOT -20%.</t>
-  </si>
-  <si>
     <t>Shoot the ball. +1 Point on make</t>
   </si>
   <si>
@@ -253,9 +250,6 @@
     <t>From the Logo</t>
   </si>
   <si>
-    <t>SHOT -50%</t>
-  </si>
-  <si>
     <t>Full-Court Heave</t>
   </si>
   <si>
@@ -403,9 +397,6 @@
     <t>Inadvertent Whistle</t>
   </si>
   <si>
-    <t>Any Non-Whistle Card Played: Cancel that card. Turn player draws 1 card.</t>
-  </si>
-  <si>
     <t>Official Review</t>
   </si>
   <si>
@@ -415,24 +406,15 @@
     <t>Shot Clock Violation</t>
   </si>
   <si>
-    <t>Shot Attempt: Cancel the shot. TOV +1. Ball OOB</t>
-  </si>
-  <si>
     <t>This inbound does NOT increment the round.</t>
   </si>
   <si>
     <t>Technical Foul</t>
   </si>
   <si>
-    <t>Any Non-Whistle Card Played: Cancel card.</t>
-  </si>
-  <si>
     <t>Timeout</t>
   </si>
   <si>
-    <t>Immediate: Reset Shot Clock. All players draw 1 card</t>
-  </si>
-  <si>
     <t>Travel</t>
   </si>
   <si>
@@ -511,9 +493,6 @@
     <t>Bone Bruise</t>
   </si>
   <si>
-    <t>Discard 1 card at the start of each turn</t>
-  </si>
-  <si>
     <t>All intangibles are limited to 1</t>
   </si>
   <si>
@@ -731,6 +710,42 @@
   </si>
   <si>
     <t>3 def</t>
+  </si>
+  <si>
+    <t>Shot Clock is changed: TOV +1. Ball OOB</t>
+  </si>
+  <si>
+    <t>SHOT -20%</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
+  </si>
+  <si>
+    <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+  </si>
+  <si>
+    <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+  </si>
+  <si>
+    <t>Torn Achilles</t>
+  </si>
+  <si>
+    <t>Hand is locked every turn except 1 card (randomly)</t>
+  </si>
+  <si>
+    <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
+  </si>
+  <si>
+    <t>* add</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1518,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1677,9 +1692,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1889,6 +1901,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3024,27 +3042,27 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="26.5" style="72" customWidth="1"/>
-    <col min="2" max="2" width="41.83203125" style="72" customWidth="1"/>
-    <col min="3" max="3" width="38.1640625" style="72" customWidth="1"/>
-    <col min="4" max="7" width="16.33203125" style="72" customWidth="1"/>
+    <col min="1" max="1" width="26.5" style="71" customWidth="1"/>
+    <col min="2" max="2" width="41.83203125" style="71" customWidth="1"/>
+    <col min="3" max="3" width="38.1640625" style="71" customWidth="1"/>
+    <col min="4" max="7" width="16.33203125" style="71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
     </row>
     <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -3055,7 +3073,7 @@
         <v>59</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -3066,7 +3084,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -3077,7 +3095,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3088,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -3099,7 +3117,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -3110,7 +3128,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -3121,7 +3139,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -3129,10 +3147,10 @@
     </row>
     <row r="10" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="6" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -3140,10 +3158,10 @@
     </row>
     <row r="11" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="6" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -3162,33 +3180,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S101"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1" ns3:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15.5" style="8" customWidth="1"/>
     <col min="2" max="2" width="13" style="8" customWidth="1"/>
     <col min="3" max="3" width="15.1640625" style="8" customWidth="1"/>
     <col min="4" max="4" width="20.83203125" style="8" customWidth="1"/>
     <col min="5" max="5" width="20.1640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="15" style="72" customWidth="1"/>
+    <col min="6" max="6" width="15" style="71" customWidth="1"/>
     <col min="7" max="7" width="20.1640625" style="8" customWidth="1"/>
     <col min="8" max="9" width="14.6640625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="48.5" style="72" customWidth="1"/>
-    <col min="11" max="11" width="19.1640625" style="72" customWidth="1"/>
-    <col min="12" max="12" width="13" style="72" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" style="72" customWidth="1"/>
-    <col min="14" max="14" width="84.6640625" style="72" customWidth="1"/>
-    <col min="15" max="15" width="30.83203125" style="72" customWidth="1"/>
-    <col min="16" max="16" width="16.33203125" style="72" customWidth="1"/>
-    <col min="17" max="17" width="30.83203125" style="72" customWidth="1"/>
-    <col min="18" max="19" width="16.33203125" style="72" customWidth="1"/>
+    <col min="10" max="10" width="48.5" style="71" customWidth="1"/>
+    <col min="11" max="11" width="19.1640625" style="71" customWidth="1"/>
+    <col min="12" max="12" width="13" style="71" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" style="71" customWidth="1"/>
+    <col min="14" max="14" width="84.6640625" style="71" customWidth="1"/>
+    <col min="15" max="15" width="30.83203125" style="71" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" style="71" customWidth="1"/>
+    <col min="17" max="17" width="30.83203125" style="71" customWidth="1"/>
+    <col min="18" max="19" width="16.33203125" style="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" ht="26.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -3208,17 +3226,17 @@
         <v>5</v>
       </c>
       <c r="G1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" s="11"/>
     </row>
-    <row r="2" spans="1:10" ht="29.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" ht="29.75" customHeight="1" ns3:dyDescent="0.15">
       <c r="A2" s="9" t="s">
         <v>9</v>
       </c>
@@ -3237,22 +3255,22 @@
       <c r="F2" s="16">
         <v>10</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="18">
+        <v>1</v>
+      </c>
+      <c r="H2" s="19">
+        <v>1</v>
+      </c>
+      <c r="I2" s="17">
         <v>21</v>
       </c>
-      <c r="H2" s="18">
-        <v>1</v>
-      </c>
-      <c r="I2" s="19">
-        <v>1</v>
-      </c>
       <c r="J2" s="19"/>
     </row>
-    <row r="4" spans="1:10" ht="20.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="124" t="s">
+    <row r="4" spans="1:10" ht="20.75" customHeight="1" thickBot="1" ns3:dyDescent="0.2">
+      <c r="A4" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="125"/>
+      <c r="B4" s="124"/>
       <c r="C4" s="20" t="s">
         <v>11</v>
       </c>
@@ -3265,14 +3283,14 @@
       <c r="F4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="104" t="s">
+      <c r="G4" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-    </row>
-    <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+    </row>
+    <row r="5" spans="1:10" ht="20" customHeight="1" ns3:dyDescent="0.15">
       <c r="A5" s="21" t="s">
         <v>1</v>
       </c>
@@ -3282,13 +3300,13 @@
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
-    </row>
-    <row r="6" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F5" s="72"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
+    </row>
+    <row r="6" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
       <c r="A6" s="24"/>
       <c r="B6" s="25" t="s">
         <v>1</v>
@@ -3300,15 +3318,15 @@
         <v>17</v>
       </c>
       <c r="E6" s="28"/>
-      <c r="F6" s="74">
+      <c r="F6" s="73">
         <v>5</v>
       </c>
-      <c r="G6" s="106"/>
-      <c r="H6" s="107"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="107"/>
-    </row>
-    <row r="7" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G6" s="105"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
+    </row>
+    <row r="7" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A7" s="29"/>
       <c r="B7" s="30" t="s">
         <v>1</v>
@@ -3322,15 +3340,15 @@
       <c r="E7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="74">
         <v>10</v>
       </c>
-      <c r="G7" s="113"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="107"/>
-    </row>
-    <row r="8" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G7" s="112"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+    </row>
+    <row r="8" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
       <c r="A8" s="29"/>
       <c r="B8" s="30" t="s">
         <v>1</v>
@@ -3338,17 +3356,17 @@
       <c r="C8" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="95" t="s">
+      <c r="D8" s="94" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="34"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="107"/>
-    </row>
-    <row r="9" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F8" s="75"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="106"/>
+    </row>
+    <row r="9" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
       <c r="A9" s="29"/>
       <c r="B9" s="30" t="s">
         <v>1</v>
@@ -3360,13 +3378,13 @@
         <v>24</v>
       </c>
       <c r="E9" s="7"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="113"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="107"/>
-    </row>
-    <row r="10" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F9" s="76"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="106"/>
+    </row>
+    <row r="10" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A10" s="29"/>
       <c r="B10" s="30" t="s">
         <v>1</v>
@@ -3378,15 +3396,15 @@
         <v>26</v>
       </c>
       <c r="E10" s="34"/>
-      <c r="F10" s="76">
+      <c r="F10" s="75">
         <v>20</v>
       </c>
-      <c r="G10" s="106"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="107"/>
-      <c r="J10" s="107"/>
-    </row>
-    <row r="11" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G10" s="105"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
+    </row>
+    <row r="11" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A11" s="29"/>
       <c r="B11" s="30" t="s">
         <v>1</v>
@@ -3398,15 +3416,15 @@
         <v>28</v>
       </c>
       <c r="E11" s="7"/>
-      <c r="F11" s="77">
+      <c r="F11" s="76">
         <v>28</v>
       </c>
-      <c r="G11" s="113"/>
-      <c r="H11" s="107"/>
-      <c r="I11" s="107"/>
-      <c r="J11" s="107"/>
-    </row>
-    <row r="12" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G11" s="112"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="106"/>
+    </row>
+    <row r="12" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A12" s="29"/>
       <c r="B12" s="30" t="s">
         <v>1</v>
@@ -3418,15 +3436,15 @@
         <v>30</v>
       </c>
       <c r="E12" s="34"/>
-      <c r="F12" s="76">
+      <c r="F12" s="75">
         <v>28</v>
       </c>
-      <c r="G12" s="106"/>
-      <c r="H12" s="107"/>
-      <c r="I12" s="107"/>
-      <c r="J12" s="107"/>
-    </row>
-    <row r="13" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G12" s="105"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="106"/>
+    </row>
+    <row r="13" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A13" s="29"/>
       <c r="B13" s="30" t="s">
         <v>1</v>
@@ -3438,15 +3456,15 @@
         <v>32</v>
       </c>
       <c r="E13" s="7"/>
-      <c r="F13" s="77">
+      <c r="F13" s="76">
         <v>15</v>
       </c>
-      <c r="G13" s="113"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="107"/>
-    </row>
-    <row r="14" spans="1:10" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="G13" s="112"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="106"/>
+    </row>
+    <row r="14" spans="1:10" ht="29" customHeight="1" thickBot="1" ns3:dyDescent="0.2">
       <c r="A14" s="35"/>
       <c r="B14" s="36" t="s">
         <v>1</v>
@@ -3460,15 +3478,15 @@
       <c r="E14" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="78">
+      <c r="F14" s="77">
         <v>12</v>
       </c>
-      <c r="G14" s="128"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="105"/>
-    </row>
-    <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G14" s="127"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+    </row>
+    <row r="15" spans="1:10" ht="20" customHeight="1" ns3:dyDescent="0.15">
       <c r="A15" s="39" t="s">
         <v>2</v>
       </c>
@@ -3478,13 +3496,13 @@
       <c r="C15" s="41"/>
       <c r="D15" s="41"/>
       <c r="E15" s="41"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="122"/>
-    </row>
-    <row r="16" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F15" s="78"/>
+      <c r="G15" s="120"/>
+      <c r="H15" s="121"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="121"/>
+    </row>
+    <row r="16" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A16" s="45"/>
       <c r="B16" s="46" t="s">
         <v>2</v>
@@ -3496,15 +3514,15 @@
         <v>37</v>
       </c>
       <c r="E16" s="49"/>
-      <c r="F16" s="80">
+      <c r="F16" s="79">
         <v>15</v>
       </c>
-      <c r="G16" s="119"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="120"/>
-      <c r="J16" s="120"/>
-    </row>
-    <row r="17" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G16" s="118"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+    </row>
+    <row r="17" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A17" s="29"/>
       <c r="B17" s="30" t="s">
         <v>2</v>
@@ -3518,15 +3536,15 @@
       <c r="E17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="75">
+      <c r="F17" s="74">
         <v>7</v>
       </c>
-      <c r="G17" s="102"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="103"/>
-    </row>
-    <row r="18" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G17" s="101"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="102"/>
+    </row>
+    <row r="18" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A18" s="29"/>
       <c r="B18" s="30" t="s">
         <v>2</v>
@@ -3538,35 +3556,35 @@
         <v>42</v>
       </c>
       <c r="E18" s="34"/>
-      <c r="F18" s="76">
+      <c r="F18" s="75">
         <v>10</v>
       </c>
-      <c r="G18" s="108"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="103"/>
-    </row>
-    <row r="19" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G18" s="107"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="102"/>
+    </row>
+    <row r="19" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
       <c r="A19" s="29"/>
       <c r="B19" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="92" t="s">
+      <c r="D19" s="91" t="s">
         <v>44</v>
       </c>
       <c r="E19" s="7"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="131" t="s">
+      <c r="F19" s="76"/>
+      <c r="G19" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="H19" s="103"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="103"/>
-    </row>
-    <row r="20" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
+    </row>
+    <row r="20" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A20" s="29"/>
       <c r="B20" s="30" t="s">
         <v>2</v>
@@ -3580,15 +3598,15 @@
       <c r="E20" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="81">
+      <c r="F20" s="80">
         <v>15</v>
       </c>
-      <c r="G20" s="108"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="103"/>
-    </row>
-    <row r="21" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G20" s="107"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="102"/>
+    </row>
+    <row r="21" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A21" s="29"/>
       <c r="B21" s="30" t="s">
         <v>2</v>
@@ -3602,15 +3620,15 @@
       <c r="E21" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="75">
+      <c r="F21" s="74">
         <v>12</v>
       </c>
-      <c r="G21" s="102"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="103"/>
-    </row>
-    <row r="22" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G21" s="101"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="102"/>
+      <c r="J21" s="102"/>
+    </row>
+    <row r="22" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A22" s="29"/>
       <c r="B22" s="30" t="s">
         <v>2</v>
@@ -3622,79 +3640,79 @@
         <v>51</v>
       </c>
       <c r="E22" s="34"/>
-      <c r="F22" s="76">
+      <c r="F22" s="75">
         <v>5</v>
       </c>
-      <c r="G22" s="108"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="103"/>
-    </row>
-    <row r="23" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G22" s="107"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="102"/>
+    </row>
+    <row r="23" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A23" s="29"/>
       <c r="B23" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="134" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" s="95" t="s">
-        <v>223</v>
+      <c r="C23" s="133" t="s">
+        <v>214</v>
+      </c>
+      <c r="D23" s="94" t="s">
+        <v>216</v>
       </c>
       <c r="E23" s="34"/>
-      <c r="F23" s="76">
+      <c r="F23" s="75">
         <v>5</v>
       </c>
-      <c r="G23" s="99"/>
-      <c r="H23" s="98"/>
-      <c r="I23" s="98"/>
-      <c r="J23" s="98"/>
-    </row>
-    <row r="24" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G23" s="98"/>
+      <c r="H23" s="97"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="97"/>
+    </row>
+    <row r="24" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A24" s="29"/>
       <c r="B24" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="134" t="s">
-        <v>222</v>
-      </c>
-      <c r="D24" s="95" t="s">
-        <v>224</v>
+      <c r="C24" s="133" t="s">
+        <v>215</v>
+      </c>
+      <c r="D24" s="94" t="s">
+        <v>217</v>
       </c>
       <c r="E24" s="34"/>
-      <c r="F24" s="76">
+      <c r="F24" s="75">
         <v>10</v>
       </c>
-      <c r="G24" s="100" t="s">
-        <v>225</v>
-      </c>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="98"/>
-    </row>
-    <row r="25" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G24" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="H24" s="97"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="97"/>
+    </row>
+    <row r="25" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A25" s="29"/>
       <c r="B25" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="134" t="s">
-        <v>226</v>
-      </c>
-      <c r="D25" s="95" t="s">
-        <v>227</v>
+      <c r="C25" s="133" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" s="94" t="s">
+        <v>220</v>
       </c>
       <c r="E25" s="34"/>
-      <c r="F25" s="76">
+      <c r="F25" s="75">
         <v>5</v>
       </c>
-      <c r="G25" s="100" t="s">
-        <v>225</v>
-      </c>
-      <c r="H25" s="98"/>
-      <c r="I25" s="98"/>
-      <c r="J25" s="98"/>
-    </row>
-    <row r="26" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G25" s="99" t="s">
+        <v>218</v>
+      </c>
+      <c r="H25" s="97"/>
+      <c r="I25" s="97"/>
+      <c r="J25" s="97"/>
+    </row>
+    <row r="26" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A26" s="29"/>
       <c r="B26" s="30" t="s">
         <v>2</v>
@@ -3708,41 +3726,41 @@
       <c r="E26" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F26" s="75">
+      <c r="F26" s="74">
         <v>12</v>
       </c>
-      <c r="G26" s="102" t="s">
+      <c r="G26" s="101" t="s">
         <v>54</v>
       </c>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="103"/>
-    </row>
-    <row r="27" spans="1:10" ht="71" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="62"/>
-      <c r="B27" s="63" t="s">
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="102"/>
+    </row>
+    <row r="27" spans="1:10" ht="71" customHeight="1" thickBot="1" ns3:dyDescent="0.2">
+      <c r="A27" s="61"/>
+      <c r="B27" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="64" t="s">
+      <c r="C27" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="65" t="s">
+      <c r="D27" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="E27" s="65" t="s">
+      <c r="E27" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="82">
+      <c r="F27" s="81">
         <v>15</v>
       </c>
-      <c r="G27" s="117" t="s">
+      <c r="G27" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="H27" s="118"/>
-      <c r="I27" s="118"/>
-      <c r="J27" s="118"/>
-    </row>
-    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H27" s="117"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="117"/>
+    </row>
+    <row r="28" spans="1:10" ht="20" customHeight="1" ns3:dyDescent="0.15">
       <c r="A28" s="42" t="s">
         <v>59</v>
       </c>
@@ -3752,13 +3770,13 @@
       <c r="C28" s="44"/>
       <c r="D28" s="44"/>
       <c r="E28" s="44"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="121"/>
-      <c r="H28" s="122"/>
-      <c r="I28" s="122"/>
-      <c r="J28" s="122"/>
-    </row>
-    <row r="29" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F28" s="82"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="121"/>
+      <c r="I28" s="121"/>
+      <c r="J28" s="121"/>
+    </row>
+    <row r="29" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A29" s="24"/>
       <c r="B29" s="25" t="s">
         <v>59</v>
@@ -3772,13 +3790,13 @@
       <c r="E29" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="F29" s="84"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="107"/>
-      <c r="I29" s="107"/>
-      <c r="J29" s="107"/>
-    </row>
-    <row r="30" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F29" s="83"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="106"/>
+      <c r="J29" s="106"/>
+    </row>
+    <row r="30" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A30" s="29"/>
       <c r="B30" s="30" t="s">
         <v>59</v>
@@ -3792,913 +3810,905 @@
       <c r="E30" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="75">
+      <c r="F30" s="74">
         <v>4</v>
       </c>
-      <c r="G30" s="129" t="s">
+      <c r="G30" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="H30" s="107"/>
-      <c r="I30" s="107"/>
-      <c r="J30" s="107"/>
-    </row>
-    <row r="31" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="29"/>
+      <c r="H30" s="106"/>
+      <c r="I30" s="106"/>
+      <c r="J30" s="106"/>
+    </row>
+    <row r="31" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="B31" s="30" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="94" t="s">
+        <v>238</v>
+      </c>
+      <c r="E31" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E31" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F31" s="81"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="107"/>
-      <c r="I31" s="107"/>
-      <c r="J31" s="107"/>
-    </row>
-    <row r="32" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F31" s="80"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="106"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="106"/>
+    </row>
+    <row r="32" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A32" s="29"/>
       <c r="B32" s="30" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="E32" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F32" s="75">
+      <c r="F32" s="74">
         <v>10</v>
       </c>
-      <c r="G32" s="113"/>
-      <c r="H32" s="107"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107"/>
-    </row>
-    <row r="33" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="29"/>
+      <c r="G32" s="112"/>
+      <c r="H32" s="106"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="106"/>
+    </row>
+    <row r="33" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="B33" s="30" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="D33" s="94" t="s">
+        <v>229</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F33" s="81">
+        <v>67</v>
+      </c>
+      <c r="F33" s="80">
         <v>3</v>
       </c>
-      <c r="G33" s="106"/>
-      <c r="H33" s="107"/>
-      <c r="I33" s="107"/>
-      <c r="J33" s="107"/>
-    </row>
-    <row r="34" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="29"/>
+      <c r="G33" s="105"/>
+      <c r="H33" s="106"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="106"/>
+    </row>
+    <row r="34" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="B34" s="30" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="D34" s="91" t="s">
+        <v>72</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="75">
+        <v>67</v>
+      </c>
+      <c r="F34" s="74">
         <v>3</v>
       </c>
-      <c r="G34" s="113"/>
-      <c r="H34" s="107"/>
-      <c r="I34" s="107"/>
-      <c r="J34" s="107"/>
-    </row>
-    <row r="35" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G34" s="112"/>
+      <c r="H34" s="106"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="106"/>
+    </row>
+    <row r="35" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A35" s="29"/>
       <c r="B35" s="30" t="s">
         <v>59</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="81">
+        <v>67</v>
+      </c>
+      <c r="F35" s="80">
         <v>3</v>
       </c>
-      <c r="G35" s="106"/>
-      <c r="H35" s="107"/>
-      <c r="I35" s="107"/>
-      <c r="J35" s="107"/>
-    </row>
-    <row r="36" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G35" s="105"/>
+      <c r="H35" s="106"/>
+      <c r="I35" s="106"/>
+      <c r="J35" s="106"/>
+    </row>
+    <row r="36" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A36" s="29"/>
       <c r="B36" s="30" t="s">
         <v>59</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F36" s="75">
+        <v>77</v>
+      </c>
+      <c r="F36" s="74">
         <v>3</v>
       </c>
-      <c r="G36" s="113"/>
-      <c r="H36" s="107"/>
-      <c r="I36" s="107"/>
-      <c r="J36" s="107"/>
-    </row>
-    <row r="37" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G36" s="112"/>
+      <c r="H36" s="106"/>
+      <c r="I36" s="106"/>
+      <c r="J36" s="106"/>
+    </row>
+    <row r="37" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A37" s="29"/>
       <c r="B37" s="30" t="s">
         <v>59</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D37" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="95" t="s">
-        <v>230</v>
-      </c>
-      <c r="F37" s="81"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="107"/>
-      <c r="I37" s="107"/>
-      <c r="J37" s="107"/>
-    </row>
-    <row r="38" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E37" s="94" t="s">
+        <v>223</v>
+      </c>
+      <c r="F37" s="80"/>
+      <c r="G37" s="105"/>
+      <c r="H37" s="106"/>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+    </row>
+    <row r="38" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A38" s="29"/>
       <c r="B38" s="30" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F38" s="75"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="107"/>
-      <c r="I38" s="107"/>
-      <c r="J38" s="107"/>
-    </row>
-    <row r="39" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F38" s="74"/>
+      <c r="G38" s="112"/>
+      <c r="H38" s="106"/>
+      <c r="I38" s="106"/>
+      <c r="J38" s="106"/>
+    </row>
+    <row r="39" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A39" s="52"/>
       <c r="B39" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="70" t="s">
+      <c r="C39" s="69" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="70" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39" s="84">
+        <v>1</v>
+      </c>
+      <c r="G39" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="71" t="s">
+      <c r="H39" s="106"/>
+      <c r="I39" s="106"/>
+      <c r="J39" s="106"/>
+    </row>
+    <row r="40" spans="1:10" ht="57" customHeight="1" thickBot="1" ns3:dyDescent="0.2">
+      <c r="A40" s="61"/>
+      <c r="B40" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="E39" s="71" t="s">
-        <v>68</v>
-      </c>
-      <c r="F39" s="85">
-        <v>1</v>
-      </c>
-      <c r="G39" s="130" t="s">
+      <c r="D40" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="H39" s="107"/>
-      <c r="I39" s="107"/>
-      <c r="J39" s="107"/>
-    </row>
-    <row r="40" spans="1:10" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="62"/>
-      <c r="B40" s="63" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="67" t="s">
-        <v>86</v>
-      </c>
-      <c r="D40" s="68" t="s">
-        <v>87</v>
-      </c>
-      <c r="E40" s="69"/>
-      <c r="F40" s="86">
+      <c r="E40" s="68"/>
+      <c r="F40" s="85">
         <v>5</v>
       </c>
-      <c r="G40" s="123"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="105"/>
-      <c r="J40" s="105"/>
-    </row>
-    <row r="41" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="59" t="s">
+      <c r="G40" s="122"/>
+      <c r="H40" s="104"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="104"/>
+    </row>
+    <row r="41" spans="1:10" ht="20" customHeight="1" ns3:dyDescent="0.15">
+      <c r="A41" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="60">
+      <c r="B41" s="59">
         <v>5</v>
       </c>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="110"/>
-      <c r="H41" s="111"/>
-      <c r="I41" s="111"/>
-      <c r="J41" s="111"/>
-    </row>
-    <row r="42" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="109"/>
+      <c r="H41" s="110"/>
+      <c r="I41" s="110"/>
+      <c r="J41" s="110"/>
+    </row>
+    <row r="42" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A42" s="29"/>
       <c r="B42" s="30" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E42" s="7"/>
-      <c r="F42" s="77">
+      <c r="F42" s="76">
         <v>10</v>
       </c>
-      <c r="G42" s="131" t="s">
-        <v>231</v>
-      </c>
-      <c r="H42" s="103"/>
-      <c r="I42" s="103"/>
-      <c r="J42" s="103"/>
-    </row>
-    <row r="43" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G42" s="130" t="s">
+        <v>224</v>
+      </c>
+      <c r="H42" s="102"/>
+      <c r="I42" s="102"/>
+      <c r="J42" s="102"/>
+    </row>
+    <row r="43" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A43" s="29"/>
       <c r="B43" s="30" t="s">
         <v>3</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E43" s="34"/>
-      <c r="F43" s="76">
+      <c r="F43" s="75">
         <v>4</v>
       </c>
-      <c r="G43" s="126" t="s">
-        <v>232</v>
-      </c>
-      <c r="H43" s="103"/>
-      <c r="I43" s="103"/>
-      <c r="J43" s="103"/>
-    </row>
-    <row r="44" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G43" s="125" t="s">
+        <v>225</v>
+      </c>
+      <c r="H43" s="102"/>
+      <c r="I43" s="102"/>
+      <c r="J43" s="102"/>
+    </row>
+    <row r="44" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A44" s="29"/>
       <c r="B44" s="30" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E44" s="7"/>
-      <c r="F44" s="77">
+      <c r="F44" s="76">
         <v>3</v>
       </c>
-      <c r="G44" s="131" t="s">
-        <v>231</v>
-      </c>
-      <c r="H44" s="103"/>
-      <c r="I44" s="103"/>
-      <c r="J44" s="103"/>
-    </row>
-    <row r="45" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G44" s="130" t="s">
+        <v>224</v>
+      </c>
+      <c r="H44" s="102"/>
+      <c r="I44" s="102"/>
+      <c r="J44" s="102"/>
+    </row>
+    <row r="45" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A45" s="29"/>
       <c r="B45" s="30" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="94" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="34"/>
+      <c r="F45" s="75">
+        <v>5</v>
+      </c>
+      <c r="G45" s="125" t="s">
+        <v>226</v>
+      </c>
+      <c r="H45" s="102"/>
+      <c r="I45" s="102"/>
+      <c r="J45" s="102"/>
+    </row>
+    <row r="46" spans="1:10" ht="29" customHeight="1" thickBot="1" ns3:dyDescent="0.2">
+      <c r="A46" s="61"/>
+      <c r="B46" s="62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="95" t="s">
+      <c r="D46" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="34"/>
-      <c r="F45" s="76">
-        <v>5</v>
-      </c>
-      <c r="G45" s="126" t="s">
-        <v>233</v>
-      </c>
-      <c r="H45" s="103"/>
-      <c r="I45" s="103"/>
-      <c r="J45" s="103"/>
-    </row>
-    <row r="46" spans="1:10" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="62"/>
-      <c r="B46" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="67" t="s">
+      <c r="E46" s="68"/>
+      <c r="F46" s="85">
+        <v>2</v>
+      </c>
+      <c r="G46" s="135" t="s">
+        <v>227</v>
+      </c>
+      <c r="H46" s="117"/>
+      <c r="I46" s="117"/>
+      <c r="J46" s="117"/>
+    </row>
+    <row r="47" spans="1:10" ht="20" customHeight="1" ns3:dyDescent="0.15">
+      <c r="A47" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="59">
+        <v>16</v>
+      </c>
+      <c r="C47" s="60"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="86"/>
+      <c r="G47" s="109"/>
+      <c r="H47" s="110"/>
+      <c r="I47" s="110"/>
+      <c r="J47" s="110"/>
+    </row>
+    <row r="48" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
+      <c r="A48" s="29" t="s">
         <v>96</v>
-      </c>
-      <c r="D46" s="68" t="s">
-        <v>97</v>
-      </c>
-      <c r="E46" s="69"/>
-      <c r="F46" s="86">
-        <v>2</v>
-      </c>
-      <c r="G46" s="136" t="s">
-        <v>234</v>
-      </c>
-      <c r="H46" s="118"/>
-      <c r="I46" s="118"/>
-      <c r="J46" s="118"/>
-    </row>
-    <row r="47" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="60">
-        <v>16</v>
-      </c>
-      <c r="C47" s="61"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="87"/>
-      <c r="G47" s="110"/>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-    </row>
-    <row r="48" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="29" t="s">
-        <v>98</v>
       </c>
       <c r="B48" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="101" t="s">
         <v>99</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="102" t="s">
-        <v>101</v>
-      </c>
-      <c r="H48" s="103"/>
-      <c r="I48" s="103"/>
-      <c r="J48" s="103"/>
-    </row>
-    <row r="49" spans="1:10" ht="47" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H48" s="102"/>
+      <c r="I48" s="102"/>
+      <c r="J48" s="102"/>
+    </row>
+    <row r="49" spans="1:10" ht="47" customHeight="1" ns3:dyDescent="0.15">
       <c r="A49" s="29"/>
       <c r="B49" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C49" s="91" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="94" t="s">
-        <v>103</v>
+      <c r="C49" s="90" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" s="93" t="s">
+        <v>101</v>
       </c>
       <c r="E49" s="34"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="108"/>
-      <c r="H49" s="103"/>
-      <c r="I49" s="103"/>
-      <c r="J49" s="103"/>
-    </row>
-    <row r="50" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F49" s="75"/>
+      <c r="G49" s="107"/>
+      <c r="H49" s="102"/>
+      <c r="I49" s="102"/>
+      <c r="J49" s="102"/>
+    </row>
+    <row r="50" spans="1:10" ht="54" customHeight="1" ns3:dyDescent="0.15">
       <c r="A50" s="29"/>
       <c r="B50" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C50" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" s="93" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="D50" s="92" t="s">
+        <v>103</v>
       </c>
       <c r="E50" s="7"/>
-      <c r="F50" s="77"/>
-      <c r="G50" s="102"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="103"/>
-      <c r="J50" s="103"/>
-    </row>
-    <row r="51" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F50" s="76"/>
+      <c r="G50" s="101"/>
+      <c r="H50" s="102"/>
+      <c r="I50" s="102"/>
+      <c r="J50" s="102"/>
+    </row>
+    <row r="51" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A51" s="29"/>
       <c r="B51" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D51" s="33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E51" s="34"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="108"/>
-      <c r="H51" s="103"/>
-      <c r="I51" s="103"/>
-      <c r="J51" s="103"/>
-    </row>
-    <row r="52" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F51" s="75"/>
+      <c r="G51" s="107"/>
+      <c r="H51" s="102"/>
+      <c r="I51" s="102"/>
+      <c r="J51" s="102"/>
+    </row>
+    <row r="52" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A52" s="29"/>
       <c r="B52" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C52" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52" s="77"/>
-      <c r="G52" s="102"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="103"/>
-      <c r="J52" s="103"/>
-    </row>
-    <row r="53" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F52" s="76"/>
+      <c r="G52" s="101"/>
+      <c r="H52" s="102"/>
+      <c r="I52" s="102"/>
+      <c r="J52" s="102"/>
+    </row>
+    <row r="53" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A53" s="29"/>
       <c r="B53" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="91" t="s">
+      <c r="C53" s="90" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53" s="94" t="s">
+        <v>110</v>
+      </c>
+      <c r="E53" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="D53" s="33" t="s">
+      <c r="F53" s="80"/>
+      <c r="G53" s="113" t="s">
         <v>112</v>
       </c>
-      <c r="E53" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="F53" s="81"/>
-      <c r="G53" s="114" t="s">
-        <v>114</v>
-      </c>
-      <c r="H53" s="103"/>
-      <c r="I53" s="103"/>
-      <c r="J53" s="103"/>
-    </row>
-    <row r="54" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H53" s="102"/>
+      <c r="I53" s="102"/>
+      <c r="J53" s="102"/>
+    </row>
+    <row r="54" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A54" s="29"/>
       <c r="B54" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C54" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54" s="7"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="101" t="s">
         <v>115</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="77"/>
-      <c r="G54" s="102" t="s">
-        <v>117</v>
-      </c>
-      <c r="H54" s="103"/>
-      <c r="I54" s="103"/>
-      <c r="J54" s="103"/>
-    </row>
-    <row r="55" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H54" s="102"/>
+      <c r="I54" s="102"/>
+      <c r="J54" s="102"/>
+    </row>
+    <row r="55" spans="1:10" ht="40" customHeight="1" ns3:dyDescent="0.15">
       <c r="A55" s="29"/>
       <c r="B55" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="91" t="s">
-        <v>118</v>
-      </c>
-      <c r="D55" s="95" t="s">
-        <v>119</v>
+      <c r="C55" s="90" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="94" t="s">
+        <v>117</v>
       </c>
       <c r="E55" s="34"/>
-      <c r="F55" s="76"/>
-      <c r="G55" s="108"/>
-      <c r="H55" s="103"/>
-      <c r="I55" s="103"/>
-      <c r="J55" s="103"/>
-    </row>
-    <row r="56" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F55" s="75"/>
+      <c r="G55" s="107"/>
+      <c r="H55" s="102"/>
+      <c r="I55" s="102"/>
+      <c r="J55" s="102"/>
+    </row>
+    <row r="56" spans="1:10" ht="30" customHeight="1" ns3:dyDescent="0.15">
       <c r="A56" s="29"/>
       <c r="B56" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C56" s="91" t="s">
-        <v>120</v>
-      </c>
-      <c r="D56" s="92" t="s">
-        <v>121</v>
+      <c r="C56" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="91" t="s">
+        <v>119</v>
       </c>
       <c r="E56" s="7"/>
-      <c r="F56" s="77"/>
-      <c r="G56" s="102"/>
-      <c r="H56" s="103"/>
-      <c r="I56" s="103"/>
-      <c r="J56" s="103"/>
-    </row>
-    <row r="57" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F56" s="76"/>
+      <c r="G56" s="101"/>
+      <c r="H56" s="102"/>
+      <c r="I56" s="102"/>
+      <c r="J56" s="102"/>
+    </row>
+    <row r="57" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
       <c r="A57" s="29"/>
       <c r="B57" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D57" s="33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E57" s="34"/>
-      <c r="F57" s="76"/>
-      <c r="G57" s="108"/>
-      <c r="H57" s="103"/>
-      <c r="I57" s="103"/>
-      <c r="J57" s="103"/>
-    </row>
-    <row r="58" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="29"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="107"/>
+      <c r="H57" s="102"/>
+      <c r="I57" s="102"/>
+      <c r="J57" s="102"/>
+    </row>
+    <row r="58" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="B58" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C58" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="D58" s="91" t="s">
+        <v>231</v>
       </c>
       <c r="E58" s="7"/>
-      <c r="F58" s="77"/>
-      <c r="G58" s="102"/>
-      <c r="H58" s="103"/>
-      <c r="I58" s="103"/>
-      <c r="J58" s="103"/>
-    </row>
-    <row r="59" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="29"/>
+      <c r="F58" s="76"/>
+      <c r="G58" s="101"/>
+      <c r="H58" s="102"/>
+      <c r="I58" s="102"/>
+      <c r="J58" s="102"/>
+    </row>
+    <row r="59" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="B59" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="D59" s="33" t="s">
-        <v>127</v>
+        <v>123</v>
+      </c>
+      <c r="D59" s="94" t="s">
+        <v>124</v>
       </c>
       <c r="E59" s="34"/>
-      <c r="F59" s="76"/>
-      <c r="G59" s="108"/>
-      <c r="H59" s="103"/>
-      <c r="I59" s="103"/>
-      <c r="J59" s="103"/>
-    </row>
-    <row r="60" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="29"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="107"/>
+      <c r="H59" s="102"/>
+      <c r="I59" s="102"/>
+      <c r="J59" s="102"/>
+    </row>
+    <row r="60" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="B60" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C60" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
+      </c>
+      <c r="D60" s="91" t="s">
+        <v>228</v>
       </c>
       <c r="E60" s="7"/>
-      <c r="F60" s="77"/>
-      <c r="G60" s="102" t="s">
-        <v>130</v>
-      </c>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-    </row>
-    <row r="61" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="29"/>
+      <c r="F60" s="76"/>
+      <c r="G60" s="101" t="s">
+        <v>126</v>
+      </c>
+      <c r="H60" s="102"/>
+      <c r="I60" s="102"/>
+      <c r="J60" s="102"/>
+    </row>
+    <row r="61" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="B61" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="D61" s="33" t="s">
-        <v>132</v>
+        <v>127</v>
+      </c>
+      <c r="D61" s="94" t="s">
+        <v>233</v>
       </c>
       <c r="E61" s="34"/>
-      <c r="F61" s="76"/>
-      <c r="G61" s="108"/>
-      <c r="H61" s="103"/>
-      <c r="I61" s="103"/>
-      <c r="J61" s="103"/>
-    </row>
-    <row r="62" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="29"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="107"/>
+      <c r="H61" s="102"/>
+      <c r="I61" s="102"/>
+      <c r="J61" s="102"/>
+    </row>
+    <row r="62" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="B62" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C62" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
+      </c>
+      <c r="D62" s="91" t="s">
+        <v>234</v>
       </c>
       <c r="E62" s="7"/>
-      <c r="F62" s="77"/>
-      <c r="G62" s="102"/>
-      <c r="H62" s="103"/>
-      <c r="I62" s="103"/>
-      <c r="J62" s="103"/>
-    </row>
-    <row r="63" spans="1:10" ht="29" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="62"/>
-      <c r="B63" s="63" t="s">
+      <c r="F62" s="76"/>
+      <c r="G62" s="101"/>
+      <c r="H62" s="102"/>
+      <c r="I62" s="102"/>
+      <c r="J62" s="102"/>
+    </row>
+    <row r="63" spans="1:10" ht="29" customHeight="1" thickBot="1" ns3:dyDescent="0.2">
+      <c r="A63" s="61"/>
+      <c r="B63" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="C63" s="64" t="s">
-        <v>135</v>
-      </c>
-      <c r="D63" s="65" t="s">
-        <v>136</v>
-      </c>
-      <c r="E63" s="66"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="117"/>
-      <c r="H63" s="118"/>
-      <c r="I63" s="118"/>
-      <c r="J63" s="118"/>
-    </row>
-    <row r="64" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="59" t="s">
+      <c r="C63" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="E63" s="65"/>
+      <c r="F63" s="87"/>
+      <c r="G63" s="116"/>
+      <c r="H63" s="117"/>
+      <c r="I63" s="117"/>
+      <c r="J63" s="117"/>
+    </row>
+    <row r="64" spans="1:10" ht="20" customHeight="1" ns3:dyDescent="0.15">
+      <c r="A64" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="B64" s="60">
+      <c r="B64" s="59">
         <v>10</v>
       </c>
-      <c r="C64" s="61"/>
-      <c r="D64" s="61"/>
-      <c r="E64" s="61"/>
-      <c r="F64" s="87"/>
-      <c r="G64" s="110"/>
-      <c r="H64" s="111"/>
-      <c r="I64" s="111"/>
-      <c r="J64" s="111"/>
-    </row>
-    <row r="65" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C64" s="60"/>
+      <c r="D64" s="60"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="86"/>
+      <c r="G64" s="109"/>
+      <c r="H64" s="110"/>
+      <c r="I64" s="110"/>
+      <c r="J64" s="110"/>
+    </row>
+    <row r="65" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A65" s="29"/>
       <c r="B65" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D65" s="33" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E65" s="34"/>
-      <c r="F65" s="76">
+      <c r="F65" s="75">
         <v>2</v>
       </c>
-      <c r="G65" s="108"/>
-      <c r="H65" s="103"/>
-      <c r="I65" s="103"/>
-      <c r="J65" s="103"/>
-    </row>
-    <row r="66" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G65" s="107"/>
+      <c r="H65" s="102"/>
+      <c r="I65" s="102"/>
+      <c r="J65" s="102"/>
+    </row>
+    <row r="66" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A66" s="29"/>
       <c r="B66" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E66" s="7"/>
-      <c r="F66" s="77">
+      <c r="F66" s="76">
         <v>5</v>
       </c>
-      <c r="G66" s="112" t="s">
-        <v>141</v>
-      </c>
-      <c r="H66" s="103"/>
-      <c r="I66" s="103"/>
-      <c r="J66" s="103"/>
-    </row>
-    <row r="67" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G66" s="111" t="s">
+        <v>135</v>
+      </c>
+      <c r="H66" s="102"/>
+      <c r="I66" s="102"/>
+      <c r="J66" s="102"/>
+    </row>
+    <row r="67" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A67" s="29"/>
       <c r="B67" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C67" s="32" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D67" s="33" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E67" s="34"/>
-      <c r="F67" s="76">
+      <c r="F67" s="75">
         <v>14</v>
       </c>
-      <c r="G67" s="108"/>
-      <c r="H67" s="103"/>
-      <c r="I67" s="103"/>
-      <c r="J67" s="103"/>
-    </row>
-    <row r="68" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G67" s="107"/>
+      <c r="H67" s="102"/>
+      <c r="I67" s="102"/>
+      <c r="J67" s="102"/>
+    </row>
+    <row r="68" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A68" s="29"/>
       <c r="B68" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C68" s="31" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E68" s="7"/>
-      <c r="F68" s="77">
+      <c r="F68" s="76">
         <v>10</v>
       </c>
-      <c r="G68" s="102"/>
-      <c r="H68" s="103"/>
-      <c r="I68" s="103"/>
-      <c r="J68" s="103"/>
-    </row>
-    <row r="69" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G68" s="101"/>
+      <c r="H68" s="102"/>
+      <c r="I68" s="102"/>
+      <c r="J68" s="102"/>
+    </row>
+    <row r="69" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A69" s="29"/>
       <c r="B69" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C69" s="91" t="s">
-        <v>146</v>
+      <c r="C69" s="90" t="s">
+        <v>140</v>
       </c>
       <c r="D69" s="33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E69" s="34"/>
-      <c r="F69" s="76"/>
-      <c r="G69" s="108"/>
-      <c r="H69" s="103"/>
-      <c r="I69" s="103"/>
-      <c r="J69" s="103"/>
-    </row>
-    <row r="70" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F69" s="75"/>
+      <c r="G69" s="107"/>
+      <c r="H69" s="102"/>
+      <c r="I69" s="102"/>
+      <c r="J69" s="102"/>
+    </row>
+    <row r="70" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A70" s="29"/>
       <c r="B70" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E70" s="7"/>
-      <c r="F70" s="77">
+      <c r="F70" s="76">
         <v>5</v>
       </c>
-      <c r="G70" s="102"/>
-      <c r="H70" s="103"/>
-      <c r="I70" s="103"/>
-      <c r="J70" s="103"/>
-    </row>
-    <row r="71" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G70" s="101"/>
+      <c r="H70" s="102"/>
+      <c r="I70" s="102"/>
+      <c r="J70" s="102"/>
+    </row>
+    <row r="71" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A71" s="29"/>
       <c r="B71" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C71" s="32" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D71" s="33" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E71" s="34"/>
-      <c r="F71" s="76">
+      <c r="F71" s="75">
         <v>3</v>
       </c>
-      <c r="G71" s="108"/>
-      <c r="H71" s="103"/>
-      <c r="I71" s="103"/>
-      <c r="J71" s="103"/>
-    </row>
-    <row r="72" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G71" s="107"/>
+      <c r="H71" s="102"/>
+      <c r="I71" s="102"/>
+      <c r="J71" s="102"/>
+    </row>
+    <row r="72" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A72" s="29"/>
       <c r="B72" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C72" s="31" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F72" s="75">
+        <v>148</v>
+      </c>
+      <c r="F72" s="74">
         <v>5</v>
       </c>
-      <c r="G72" s="102"/>
-      <c r="H72" s="103"/>
-      <c r="I72" s="103"/>
-      <c r="J72" s="103"/>
-    </row>
-    <row r="73" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G72" s="101"/>
+      <c r="H72" s="102"/>
+      <c r="I72" s="102"/>
+      <c r="J72" s="102"/>
+    </row>
+    <row r="73" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A73" s="29"/>
       <c r="B73" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C73" s="32" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D73" s="33" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="F73" s="81"/>
-      <c r="G73" s="108"/>
-      <c r="H73" s="103"/>
-      <c r="I73" s="103"/>
-      <c r="J73" s="103"/>
-    </row>
-    <row r="74" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+        <v>148</v>
+      </c>
+      <c r="F73" s="80"/>
+      <c r="G73" s="107"/>
+      <c r="H73" s="102"/>
+      <c r="I73" s="102"/>
+      <c r="J73" s="102"/>
+    </row>
+    <row r="74" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A74" s="29"/>
       <c r="B74" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C74" s="31" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E74" s="7"/>
-      <c r="F74" s="77"/>
-      <c r="G74" s="112" t="s">
-        <v>159</v>
-      </c>
-      <c r="H74" s="103"/>
-      <c r="I74" s="103"/>
-      <c r="J74" s="103"/>
-    </row>
-    <row r="75" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F74" s="76"/>
+      <c r="G74" s="111" t="s">
+        <v>153</v>
+      </c>
+      <c r="H74" s="102"/>
+      <c r="I74" s="102"/>
+      <c r="J74" s="102"/>
+    </row>
+    <row r="75" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A75" s="29"/>
       <c r="B75" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C75" s="135" t="s">
-        <v>228</v>
-      </c>
-      <c r="D75" s="92" t="s">
-        <v>229</v>
+      <c r="C75" s="134" t="s">
+        <v>221</v>
+      </c>
+      <c r="D75" s="91" t="s">
+        <v>222</v>
       </c>
       <c r="E75" s="7"/>
-      <c r="F75" s="77">
+      <c r="F75" s="76">
         <v>4</v>
       </c>
-      <c r="G75" s="101"/>
-      <c r="H75" s="98"/>
-      <c r="I75" s="98"/>
-      <c r="J75" s="98"/>
-    </row>
-    <row r="76" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G75" s="100"/>
+      <c r="H75" s="97"/>
+      <c r="I75" s="97"/>
+      <c r="J75" s="97"/>
+    </row>
+    <row r="76" spans="1:10" ht="20" customHeight="1" ns3:dyDescent="0.15">
       <c r="A76" s="55" t="s">
         <v>7</v>
       </c>
@@ -4708,463 +4718,467 @@
       <c r="C76" s="57"/>
       <c r="D76" s="57"/>
       <c r="E76" s="57"/>
-      <c r="F76" s="89"/>
-      <c r="G76" s="109"/>
-      <c r="H76" s="103"/>
-      <c r="I76" s="103"/>
-      <c r="J76" s="103"/>
-    </row>
-    <row r="77" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="29"/>
+      <c r="F76" s="88"/>
+      <c r="G76" s="108"/>
+      <c r="H76" s="102"/>
+      <c r="I76" s="102"/>
+      <c r="J76" s="102"/>
+    </row>
+    <row r="77" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="B77" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C77" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>161</v>
+        <v>154</v>
+      </c>
+      <c r="D77" s="91" t="s">
+        <v>235</v>
       </c>
       <c r="E77" s="7"/>
-      <c r="F77" s="77"/>
-      <c r="G77" s="102"/>
-      <c r="H77" s="103"/>
-      <c r="I77" s="103"/>
-      <c r="J77" s="103"/>
-    </row>
-    <row r="78" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="55" t="s">
+      <c r="F77" s="76">
+        <v>3</v>
+      </c>
+      <c r="G77" s="101"/>
+      <c r="H77" s="102"/>
+      <c r="I77" s="102"/>
+      <c r="J77" s="102"/>
+    </row>
+    <row r="78" spans="1:10" ht="20" customHeight="1" ns3:dyDescent="0.15">
+      <c r="A78" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="59">
+        <v>1</v>
+      </c>
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="60"/>
+      <c r="F78" s="86"/>
+      <c r="G78" s="109"/>
+      <c r="H78" s="110"/>
+      <c r="I78" s="110"/>
+      <c r="J78" s="110"/>
+    </row>
+    <row r="79" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
+      <c r="B79" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="136" t="s">
+        <v>236</v>
+      </c>
+      <c r="D79" s="137" t="s">
+        <v>237</v>
+      </c>
+      <c r="E79" s="54"/>
+      <c r="F79" s="89"/>
+      <c r="G79" s="114"/>
+      <c r="H79" s="115"/>
+      <c r="I79" s="115"/>
+      <c r="J79" s="115"/>
+    </row>
+    <row r="80" spans="1:10" ht="20" customHeight="1" ns3:dyDescent="0.15">
+      <c r="A80" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B78" s="56">
+      <c r="B80" s="56">
         <v>21</v>
       </c>
-      <c r="C78" s="57"/>
-      <c r="D78" s="57"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="89"/>
-      <c r="G78" s="109"/>
-      <c r="H78" s="103"/>
-      <c r="I78" s="103"/>
-      <c r="J78" s="103"/>
-    </row>
-    <row r="79" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="97" t="s">
-        <v>162</v>
-      </c>
-      <c r="B79" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E79" s="7"/>
-      <c r="F79" s="77"/>
-      <c r="G79" s="102"/>
-      <c r="H79" s="103"/>
-      <c r="I79" s="103"/>
-      <c r="J79" s="103"/>
-    </row>
-    <row r="80" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="29"/>
-      <c r="B80" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D80" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="E80" s="34"/>
-      <c r="F80" s="76"/>
+      <c r="C80" s="57"/>
+      <c r="D80" s="57"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="88"/>
       <c r="G80" s="108"/>
-      <c r="H80" s="103"/>
-      <c r="I80" s="103"/>
-      <c r="J80" s="103"/>
-    </row>
-    <row r="81" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="29"/>
+      <c r="H80" s="102"/>
+      <c r="I80" s="102"/>
+      <c r="J80" s="102"/>
+    </row>
+    <row r="81" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
+      <c r="A81" s="96" t="s">
+        <v>155</v>
+      </c>
       <c r="B81" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="31" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E81" s="7"/>
-      <c r="F81" s="77"/>
-      <c r="G81" s="102"/>
-      <c r="H81" s="103"/>
-      <c r="I81" s="103"/>
-      <c r="J81" s="103"/>
-    </row>
-    <row r="82" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F81" s="76"/>
+      <c r="G81" s="101"/>
+      <c r="H81" s="102"/>
+      <c r="I81" s="102"/>
+      <c r="J81" s="102"/>
+    </row>
+    <row r="82" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A82" s="29"/>
       <c r="B82" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="32" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="E82" s="34"/>
-      <c r="F82" s="76"/>
-      <c r="G82" s="108"/>
-      <c r="H82" s="103"/>
-      <c r="I82" s="103"/>
-      <c r="J82" s="103"/>
-    </row>
-    <row r="83" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F82" s="75"/>
+      <c r="G82" s="107"/>
+      <c r="H82" s="102"/>
+      <c r="I82" s="102"/>
+      <c r="J82" s="102"/>
+    </row>
+    <row r="83" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
       <c r="A83" s="29"/>
       <c r="B83" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F83" s="75"/>
-      <c r="G83" s="102"/>
-      <c r="H83" s="103"/>
-      <c r="I83" s="103"/>
-      <c r="J83" s="103"/>
-    </row>
-    <row r="84" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+        <v>161</v>
+      </c>
+      <c r="E83" s="7"/>
+      <c r="F83" s="76"/>
+      <c r="G83" s="101"/>
+      <c r="H83" s="102"/>
+      <c r="I83" s="102"/>
+      <c r="J83" s="102"/>
+    </row>
+    <row r="84" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A84" s="29"/>
       <c r="B84" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C84" s="91" t="s">
-        <v>174</v>
-      </c>
-      <c r="D84" s="95" t="s">
-        <v>175</v>
+      <c r="C84" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="D84" s="33" t="s">
+        <v>163</v>
       </c>
       <c r="E84" s="34"/>
-      <c r="F84" s="76"/>
-      <c r="G84" s="126"/>
-      <c r="H84" s="103"/>
-      <c r="I84" s="103"/>
-      <c r="J84" s="103"/>
-    </row>
-    <row r="85" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F84" s="75"/>
+      <c r="G84" s="107"/>
+      <c r="H84" s="102"/>
+      <c r="I84" s="102"/>
+      <c r="J84" s="102"/>
+    </row>
+    <row r="85" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A85" s="29"/>
       <c r="B85" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C85" s="91" t="s">
-        <v>176</v>
-      </c>
-      <c r="D85" s="92" t="s">
-        <v>177</v>
-      </c>
-      <c r="E85" s="7"/>
-      <c r="F85" s="77"/>
-      <c r="G85" s="102"/>
-      <c r="H85" s="103"/>
-      <c r="I85" s="103"/>
-      <c r="J85" s="103"/>
-    </row>
-    <row r="86" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C85" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F85" s="74"/>
+      <c r="G85" s="101"/>
+      <c r="H85" s="102"/>
+      <c r="I85" s="102"/>
+      <c r="J85" s="102"/>
+    </row>
+    <row r="86" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A86" s="29"/>
       <c r="B86" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="D86" s="33" t="s">
-        <v>179</v>
+      <c r="C86" s="90" t="s">
+        <v>167</v>
+      </c>
+      <c r="D86" s="94" t="s">
+        <v>168</v>
       </c>
       <c r="E86" s="34"/>
-      <c r="F86" s="76"/>
-      <c r="G86" s="108"/>
-      <c r="H86" s="103"/>
-      <c r="I86" s="103"/>
-      <c r="J86" s="103"/>
-    </row>
-    <row r="87" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F86" s="75"/>
+      <c r="G86" s="125"/>
+      <c r="H86" s="102"/>
+      <c r="I86" s="102"/>
+      <c r="J86" s="102"/>
+    </row>
+    <row r="87" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A87" s="29"/>
       <c r="B87" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>181</v>
+      <c r="C87" s="90" t="s">
+        <v>169</v>
+      </c>
+      <c r="D87" s="91" t="s">
+        <v>170</v>
       </c>
       <c r="E87" s="7"/>
-      <c r="F87" s="77"/>
-      <c r="G87" s="102"/>
-      <c r="H87" s="103"/>
-      <c r="I87" s="103"/>
-      <c r="J87" s="103"/>
-    </row>
-    <row r="88" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F87" s="76"/>
+      <c r="G87" s="101"/>
+      <c r="H87" s="102"/>
+      <c r="I87" s="102"/>
+      <c r="J87" s="102"/>
+    </row>
+    <row r="88" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
       <c r="A88" s="29"/>
       <c r="B88" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="32" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D88" s="33" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="E88" s="34"/>
-      <c r="F88" s="76"/>
-      <c r="G88" s="108"/>
-      <c r="H88" s="103"/>
-      <c r="I88" s="103"/>
-      <c r="J88" s="103"/>
-    </row>
-    <row r="89" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F88" s="75"/>
+      <c r="G88" s="107"/>
+      <c r="H88" s="102"/>
+      <c r="I88" s="102"/>
+      <c r="J88" s="102"/>
+    </row>
+    <row r="89" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
       <c r="A89" s="29"/>
       <c r="B89" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="D89" s="92" t="s">
-        <v>185</v>
+        <v>173</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="E89" s="7"/>
-      <c r="F89" s="77"/>
-      <c r="G89" s="102"/>
-      <c r="H89" s="103"/>
-      <c r="I89" s="103"/>
-      <c r="J89" s="103"/>
-    </row>
-    <row r="90" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F89" s="76"/>
+      <c r="G89" s="101"/>
+      <c r="H89" s="102"/>
+      <c r="I89" s="102"/>
+      <c r="J89" s="102"/>
+    </row>
+    <row r="90" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A90" s="29"/>
       <c r="B90" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="32" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D90" s="33" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E90" s="34"/>
-      <c r="F90" s="76"/>
-      <c r="G90" s="114" t="s">
-        <v>188</v>
-      </c>
-      <c r="H90" s="103"/>
-      <c r="I90" s="103"/>
-      <c r="J90" s="103"/>
-    </row>
-    <row r="91" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F90" s="75"/>
+      <c r="G90" s="107"/>
+      <c r="H90" s="102"/>
+      <c r="I90" s="102"/>
+      <c r="J90" s="102"/>
+    </row>
+    <row r="91" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A91" s="29"/>
       <c r="B91" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>190</v>
+        <v>177</v>
+      </c>
+      <c r="D91" s="91" t="s">
+        <v>178</v>
       </c>
       <c r="E91" s="7"/>
-      <c r="F91" s="77"/>
-      <c r="G91" s="102"/>
-      <c r="H91" s="103"/>
-      <c r="I91" s="103"/>
-      <c r="J91" s="103"/>
-    </row>
-    <row r="92" spans="1:10" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F91" s="76"/>
+      <c r="G91" s="101"/>
+      <c r="H91" s="102"/>
+      <c r="I91" s="102"/>
+      <c r="J91" s="102"/>
+    </row>
+    <row r="92" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A92" s="29"/>
       <c r="B92" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="32" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D92" s="33" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E92" s="34"/>
-      <c r="F92" s="76"/>
-      <c r="G92" s="114" t="s">
-        <v>188</v>
-      </c>
-      <c r="H92" s="103"/>
-      <c r="I92" s="103"/>
-      <c r="J92" s="103"/>
-    </row>
-    <row r="93" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F92" s="75"/>
+      <c r="G92" s="113" t="s">
+        <v>181</v>
+      </c>
+      <c r="H92" s="102"/>
+      <c r="I92" s="102"/>
+      <c r="J92" s="102"/>
+    </row>
+    <row r="93" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
       <c r="A93" s="29"/>
       <c r="B93" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E93" s="7"/>
-      <c r="F93" s="77"/>
-      <c r="G93" s="102"/>
-      <c r="H93" s="103"/>
-      <c r="I93" s="103"/>
-      <c r="J93" s="103"/>
-    </row>
-    <row r="94" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F93" s="76"/>
+      <c r="G93" s="101"/>
+      <c r="H93" s="102"/>
+      <c r="I93" s="102"/>
+      <c r="J93" s="102"/>
+    </row>
+    <row r="94" spans="1:10" ht="14" customHeight="1" ns3:dyDescent="0.15">
       <c r="A94" s="29"/>
       <c r="B94" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C94" s="32" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D94" s="33" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="E94" s="34"/>
-      <c r="F94" s="76"/>
-      <c r="G94" s="108"/>
-      <c r="H94" s="103"/>
-      <c r="I94" s="103"/>
-      <c r="J94" s="103"/>
-    </row>
-    <row r="95" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F94" s="75"/>
+      <c r="G94" s="113" t="s">
+        <v>181</v>
+      </c>
+      <c r="H94" s="102"/>
+      <c r="I94" s="102"/>
+      <c r="J94" s="102"/>
+    </row>
+    <row r="95" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A95" s="29"/>
       <c r="B95" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="31" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E95" s="7"/>
-      <c r="F95" s="77"/>
-      <c r="G95" s="102"/>
-      <c r="H95" s="103"/>
-      <c r="I95" s="103"/>
-      <c r="J95" s="103"/>
-    </row>
-    <row r="96" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F95" s="76"/>
+      <c r="G95" s="101"/>
+      <c r="H95" s="102"/>
+      <c r="I95" s="102"/>
+      <c r="J95" s="102"/>
+    </row>
+    <row r="96" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A96" s="29"/>
       <c r="B96" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="32" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D96" s="33" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="E96" s="34"/>
-      <c r="F96" s="76"/>
-      <c r="G96" s="108"/>
-      <c r="H96" s="103"/>
-      <c r="I96" s="103"/>
-      <c r="J96" s="103"/>
-    </row>
-    <row r="97" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F96" s="75"/>
+      <c r="G96" s="107"/>
+      <c r="H96" s="102"/>
+      <c r="I96" s="102"/>
+      <c r="J96" s="102"/>
+    </row>
+    <row r="97" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A97" s="29"/>
       <c r="B97" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="D97" s="92" t="s">
-        <v>202</v>
+        <v>190</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="E97" s="7"/>
-      <c r="F97" s="77"/>
-      <c r="G97" s="102"/>
-      <c r="H97" s="103"/>
-      <c r="I97" s="103"/>
-      <c r="J97" s="103"/>
-    </row>
-    <row r="98" spans="1:10" ht="56" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F97" s="76"/>
+      <c r="G97" s="101"/>
+      <c r="H97" s="102"/>
+      <c r="I97" s="102"/>
+      <c r="J97" s="102"/>
+    </row>
+    <row r="98" spans="1:10" ht="28" customHeight="1" ns3:dyDescent="0.15">
       <c r="A98" s="29"/>
       <c r="B98" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="32" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D98" s="33" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E98" s="34"/>
-      <c r="F98" s="76"/>
-      <c r="G98" s="114" t="s">
-        <v>205</v>
-      </c>
-      <c r="H98" s="103"/>
-      <c r="I98" s="103"/>
-      <c r="J98" s="103"/>
-    </row>
-    <row r="99" spans="1:10" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="62"/>
-      <c r="B99" s="63" t="s">
+      <c r="F98" s="75"/>
+      <c r="G98" s="107"/>
+      <c r="H98" s="102"/>
+      <c r="I98" s="102"/>
+      <c r="J98" s="102"/>
+    </row>
+    <row r="99" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.15">
+      <c r="A99" s="29"/>
+      <c r="B99" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C99" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="D99" s="96" t="s">
-        <v>207</v>
-      </c>
-      <c r="E99" s="69"/>
-      <c r="F99" s="86"/>
-      <c r="G99" s="127"/>
-      <c r="H99" s="118"/>
-      <c r="I99" s="118"/>
-      <c r="J99" s="118"/>
-    </row>
-    <row r="100" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="B100" s="60">
-        <v>1</v>
-      </c>
-      <c r="C100" s="61"/>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61"/>
-      <c r="F100" s="87"/>
-      <c r="G100" s="110"/>
-      <c r="H100" s="111"/>
-      <c r="I100" s="111"/>
-      <c r="J100" s="111"/>
-    </row>
-    <row r="101" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="50"/>
-      <c r="B101" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C101" s="58"/>
-      <c r="D101" s="54"/>
-      <c r="E101" s="54"/>
-      <c r="F101" s="90"/>
-      <c r="G101" s="115"/>
-      <c r="H101" s="116"/>
-      <c r="I101" s="116"/>
-      <c r="J101" s="116"/>
+      <c r="C99" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="D99" s="91" t="s">
+        <v>195</v>
+      </c>
+      <c r="E99" s="7"/>
+      <c r="F99" s="76"/>
+      <c r="G99" s="101"/>
+      <c r="H99" s="102"/>
+      <c r="I99" s="102"/>
+      <c r="J99" s="102"/>
+    </row>
+    <row r="100" spans="1:10" ht="56" customHeight="1" ns3:dyDescent="0.15">
+      <c r="A100" s="29"/>
+      <c r="B100" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="D100" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="E100" s="34"/>
+      <c r="F100" s="75"/>
+      <c r="G100" s="113" t="s">
+        <v>198</v>
+      </c>
+      <c r="H100" s="102"/>
+      <c r="I100" s="102"/>
+      <c r="J100" s="102"/>
+    </row>
+    <row r="101" spans="1:10" ht="57" customHeight="1" thickBot="1" ns3:dyDescent="0.2">
+      <c r="A101" s="61"/>
+      <c r="B101" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="66" t="s">
+        <v>199</v>
+      </c>
+      <c r="D101" s="95" t="s">
+        <v>200</v>
+      </c>
+      <c r="E101" s="68"/>
+      <c r="F101" s="85"/>
+      <c r="G101" s="126"/>
+      <c r="H101" s="117"/>
+      <c r="I101" s="117"/>
+      <c r="J101" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="95">
@@ -5172,23 +5186,23 @@
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G31:J31"/>
-    <mergeCell ref="G97:J97"/>
+    <mergeCell ref="G99:J99"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G72:J72"/>
-    <mergeCell ref="G87:J87"/>
-    <mergeCell ref="G96:J96"/>
+    <mergeCell ref="G89:J89"/>
+    <mergeCell ref="G98:J98"/>
     <mergeCell ref="G33:J33"/>
-    <mergeCell ref="G99:J99"/>
-    <mergeCell ref="G93:J93"/>
+    <mergeCell ref="G101:J101"/>
+    <mergeCell ref="G95:J95"/>
     <mergeCell ref="G67:J67"/>
-    <mergeCell ref="G83:J83"/>
+    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G77:J77"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G82:J82"/>
-    <mergeCell ref="G91:J91"/>
+    <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G93:J93"/>
     <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="G57:J57"/>
     <mergeCell ref="G66:J66"/>
@@ -5199,7 +5213,7 @@
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G30:J30"/>
-    <mergeCell ref="G101:J101"/>
+    <mergeCell ref="G79:J79"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G41:J41"/>
     <mergeCell ref="G65:J65"/>
@@ -5207,24 +5221,24 @@
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G68:J68"/>
-    <mergeCell ref="G92:J92"/>
+    <mergeCell ref="G94:J94"/>
     <mergeCell ref="G29:J29"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G80:J80"/>
+    <mergeCell ref="G82:J82"/>
     <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G94:J94"/>
+    <mergeCell ref="G96:J96"/>
     <mergeCell ref="G63:J63"/>
-    <mergeCell ref="G95:J95"/>
+    <mergeCell ref="G97:J97"/>
     <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G89:J89"/>
-    <mergeCell ref="G98:J98"/>
-    <mergeCell ref="G88:J88"/>
-    <mergeCell ref="G79:J79"/>
+    <mergeCell ref="G91:J91"/>
+    <mergeCell ref="G100:J100"/>
+    <mergeCell ref="G90:J90"/>
+    <mergeCell ref="G81:J81"/>
     <mergeCell ref="G47:J47"/>
     <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G81:J81"/>
-    <mergeCell ref="G90:J90"/>
+    <mergeCell ref="G83:J83"/>
+    <mergeCell ref="G92:J92"/>
     <mergeCell ref="G70:J70"/>
     <mergeCell ref="G64:J64"/>
     <mergeCell ref="G73:J73"/>
@@ -5232,18 +5246,18 @@
     <mergeCell ref="G62:J62"/>
     <mergeCell ref="G42:J42"/>
     <mergeCell ref="G76:J76"/>
-    <mergeCell ref="G85:J85"/>
-    <mergeCell ref="G100:J100"/>
+    <mergeCell ref="G87:J87"/>
+    <mergeCell ref="G78:J78"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G86:J86"/>
+    <mergeCell ref="G88:J88"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G56:J56"/>
     <mergeCell ref="G37:J37"/>
-    <mergeCell ref="G78:J78"/>
+    <mergeCell ref="G80:J80"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G61:J61"/>
     <mergeCell ref="G20:J20"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2626,35 +2626,35 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$107,"Pass")</f>
+        <f>COUNTIF($B$5:$B$113,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$107,"Move")+COUNTIF($B$5:$B$107,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$113,"Move")+COUNTIF($B$5:$B$113,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$107,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$113,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$107,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$113,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$107,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$113,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$107,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$113,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$107,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$113,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$107,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$113,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$107,"Pass")</f>
+        <f>COUNTIF($B$5:$B$113,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="23" t="n"/>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="B15" s="40">
-        <f>COUNTIF($B$5:$B$107,"Move")+COUNTIF($B$5:$B$107,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$113,"Move")+COUNTIF($B$5:$B$113,"Special Move")</f>
         <v/>
       </c>
       <c r="C15" s="41" t="n"/>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="B28" s="43">
-        <f>COUNTIF($B$5:$B$107,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$113,"Special Move")</f>
         <v/>
       </c>
       <c r="C28" s="44" t="n"/>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="B41" s="59">
-        <f>COUNTIF($B$5:$B$107,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$113,"Clamp")</f>
         <v/>
       </c>
       <c r="C41" s="60" t="n"/>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="B47" s="59">
-        <f>COUNTIF($B$5:$B$107,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$113,"Whistle")</f>
         <v/>
       </c>
       <c r="C47" s="60" t="n"/>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="B65" s="59">
-        <f>COUNTIF($B$5:$B$107,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$113,"Game Break")</f>
         <v/>
       </c>
       <c r="C65" s="60" t="n"/>
@@ -4769,20 +4769,31 @@
       <c r="J80" s="102" t="n"/>
     </row>
     <row r="81" ht="56" customHeight="1" s="132">
-      <c r="A81" s="55" t="inlineStr">
-        <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="B81" s="56">
-        <f>COUNTIF($B$5:$B$107,"Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C81" s="57" t="n"/>
-      <c r="D81" s="57" t="n"/>
-      <c r="E81" s="57" t="n"/>
-      <c r="F81" s="88" t="n"/>
-      <c r="G81" s="108" t="n"/>
+      <c r="A81" s="29" t="n"/>
+      <c r="B81" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C81" s="134" t="inlineStr">
+        <is>
+          <t>Wet Spot</t>
+        </is>
+      </c>
+      <c r="D81" s="91" t="inlineStr">
+        <is>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="111" t="inlineStr">
+        <is>
+          <t>Deck ones are shown face down</t>
+        </is>
+      </c>
       <c r="H81" s="102" t="n"/>
       <c r="I81" s="102" t="n"/>
       <c r="J81" s="102" t="n"/>
@@ -4791,186 +4802,193 @@
       <c r="A82" s="29" t="n"/>
       <c r="B82" s="30" t="inlineStr">
         <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="C82" s="31" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C82" s="134" t="inlineStr">
+        <is>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D82" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G82" s="101" t="n"/>
+      <c r="G82" s="111" t="inlineStr">
+        <is>
+          <t>This is a bad thing in the NBA</t>
+        </is>
+      </c>
       <c r="H82" s="102" t="n"/>
       <c r="I82" s="102" t="n"/>
       <c r="J82" s="102" t="n"/>
     </row>
     <row r="83" ht="42" customHeight="1" s="132">
-      <c r="A83" s="58" t="inlineStr">
-        <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="B83" s="59">
-        <f>COUNTIF($B$5:$B$107,"Devastating Injury GB")</f>
+      <c r="A83" s="29" t="n"/>
+      <c r="B83" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C83" s="134" t="inlineStr">
+        <is>
+          <t>Trade Deadline</t>
+        </is>
+      </c>
+      <c r="D83" s="91" t="inlineStr">
+        <is>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="n"/>
+      <c r="F83" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" s="111" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
+      <c r="H83" s="102" t="n"/>
+      <c r="I83" s="102" t="n"/>
+      <c r="J83" s="102" t="n"/>
+    </row>
+    <row r="84" ht="28" customHeight="1" s="132">
+      <c r="A84" s="55" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="B84" s="56">
+        <f>COUNTIF($B$5:$B$113,"Injury GB")</f>
         <v/>
       </c>
-      <c r="C83" s="60" t="n"/>
-      <c r="D83" s="60" t="n"/>
-      <c r="E83" s="60" t="n"/>
-      <c r="F83" s="86" t="n"/>
-      <c r="G83" s="109" t="n"/>
-      <c r="H83" s="110" t="n"/>
-      <c r="I83" s="110" t="n"/>
-      <c r="J83" s="110" t="n"/>
-    </row>
-    <row r="84" ht="28" customHeight="1" s="132">
-      <c r="A84" s="50" t="n"/>
-      <c r="B84" s="51" t="inlineStr">
-        <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="C84" s="136" t="inlineStr">
-        <is>
-          <t>Torn Achilles</t>
-        </is>
-      </c>
-      <c r="D84" s="137" t="inlineStr">
-        <is>
-          <t>Hand is locked every turn except 1 card (randomly)</t>
-        </is>
-      </c>
-      <c r="E84" s="54" t="n"/>
-      <c r="F84" s="141" t="n"/>
-      <c r="G84" s="114" t="n"/>
-      <c r="H84" s="115" t="n"/>
-      <c r="I84" s="115" t="n"/>
-      <c r="J84" s="115" t="n"/>
+      <c r="C84" s="57" t="n"/>
+      <c r="D84" s="57" t="n"/>
+      <c r="E84" s="57" t="n"/>
+      <c r="F84" s="88" t="n"/>
+      <c r="G84" s="108" t="n"/>
+      <c r="H84" s="102" t="n"/>
+      <c r="I84" s="102" t="n"/>
+      <c r="J84" s="102" t="n"/>
     </row>
     <row r="85" ht="28" customHeight="1" s="132">
-      <c r="A85" s="55" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="B85" s="56">
-        <f>COUNTIF($B$5:$B$107,"Intangible")</f>
-        <v/>
-      </c>
-      <c r="C85" s="57" t="n"/>
-      <c r="D85" s="57" t="n"/>
-      <c r="E85" s="57" t="n"/>
-      <c r="F85" s="88" t="n"/>
-      <c r="G85" s="108" t="n"/>
+      <c r="A85" s="29" t="n"/>
+      <c r="B85" s="30" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="C85" s="31" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D85" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" s="101" t="n"/>
       <c r="H85" s="102" t="n"/>
       <c r="I85" s="102" t="n"/>
       <c r="J85" s="102" t="n"/>
     </row>
     <row r="86" ht="56" customHeight="1" s="132">
-      <c r="A86" s="96" t="inlineStr">
-        <is>
-          <t>All intangibles are limited to 1</t>
-        </is>
-      </c>
-      <c r="B86" s="30" t="inlineStr">
+      <c r="A86" s="58" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="B86" s="59">
+        <f>COUNTIF($B$5:$B$113,"Devastating Injury GB")</f>
+        <v/>
+      </c>
+      <c r="C86" s="60" t="n"/>
+      <c r="D86" s="60" t="n"/>
+      <c r="E86" s="60" t="n"/>
+      <c r="F86" s="86" t="n"/>
+      <c r="G86" s="109" t="n"/>
+      <c r="H86" s="110" t="n"/>
+      <c r="I86" s="110" t="n"/>
+      <c r="J86" s="110" t="n"/>
+    </row>
+    <row r="87" ht="56" customHeight="1" s="132">
+      <c r="A87" s="50" t="n"/>
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="C87" s="136" t="inlineStr">
+        <is>
+          <t>Torn Achilles</t>
+        </is>
+      </c>
+      <c r="D87" s="137" t="inlineStr">
+        <is>
+          <t>Hand is locked every turn except 1 card (randomly)</t>
+        </is>
+      </c>
+      <c r="E87" s="54" t="n"/>
+      <c r="F87" s="141" t="n"/>
+      <c r="G87" s="114" t="n"/>
+      <c r="H87" s="115" t="n"/>
+      <c r="I87" s="115" t="n"/>
+      <c r="J87" s="115" t="n"/>
+    </row>
+    <row r="88" ht="28" customHeight="1" s="132">
+      <c r="A88" s="55" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C86" s="31" t="inlineStr">
-        <is>
-          <t>Board-Crasher</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% upon Rebounding your own missed shot</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="138" t="n"/>
-      <c r="G86" s="101" t="n"/>
-      <c r="H86" s="102" t="n"/>
-      <c r="I86" s="102" t="n"/>
-      <c r="J86" s="102" t="n"/>
-    </row>
-    <row r="87" ht="56" customHeight="1" s="132">
-      <c r="A87" s="29" t="n"/>
-      <c r="B87" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C87" s="32" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D87" s="33" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E87" s="34" t="n"/>
-      <c r="F87" s="138" t="n"/>
-      <c r="G87" s="107" t="n"/>
-      <c r="H87" s="102" t="n"/>
-      <c r="I87" s="102" t="n"/>
-      <c r="J87" s="102" t="n"/>
-    </row>
-    <row r="88" ht="28" customHeight="1" s="132">
-      <c r="A88" s="29" t="n"/>
-      <c r="B88" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C88" s="31" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="138" t="n"/>
-      <c r="G88" s="101" t="n"/>
+      <c r="B88" s="56">
+        <f>COUNTIF($B$5:$B$113,"Intangible")</f>
+        <v/>
+      </c>
+      <c r="C88" s="57" t="n"/>
+      <c r="D88" s="57" t="n"/>
+      <c r="E88" s="57" t="n"/>
+      <c r="F88" s="88" t="n"/>
+      <c r="G88" s="108" t="n"/>
       <c r="H88" s="102" t="n"/>
       <c r="I88" s="102" t="n"/>
       <c r="J88" s="102" t="n"/>
     </row>
     <row r="89" ht="42" customHeight="1" s="132">
-      <c r="A89" s="29" t="n"/>
+      <c r="A89" s="96" t="inlineStr">
+        <is>
+          <t>All intangibles are limited to 1</t>
+        </is>
+      </c>
       <c r="B89" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C89" s="32" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D89" s="33" t="inlineStr">
-        <is>
-          <t>You decide all targets for direct targeting passes this round</t>
-        </is>
-      </c>
-      <c r="E89" s="34" t="n"/>
+      <c r="C89" s="31" t="inlineStr">
+        <is>
+          <t>Board-Crasher</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% upon Rebounding your own missed shot</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="n"/>
       <c r="F89" s="138" t="n"/>
-      <c r="G89" s="107" t="n"/>
+      <c r="G89" s="101" t="n"/>
       <c r="H89" s="102" t="n"/>
       <c r="I89" s="102" t="n"/>
       <c r="J89" s="102" t="n"/>
@@ -4982,23 +5000,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C90" s="31" t="inlineStr">
-        <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F90" s="139" t="n"/>
-      <c r="G90" s="101" t="n"/>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D90" s="33" t="inlineStr">
+        <is>
+          <t>Additional SHOT +10% on all received passes</t>
+        </is>
+      </c>
+      <c r="E90" s="34" t="n"/>
+      <c r="F90" s="138" t="n"/>
+      <c r="G90" s="107" t="n"/>
       <c r="H90" s="102" t="n"/>
       <c r="I90" s="102" t="n"/>
       <c r="J90" s="102" t="n"/>
@@ -5010,19 +5024,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C91" s="90" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D91" s="94" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E91" s="34" t="n"/>
+      <c r="C91" s="31" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="n"/>
       <c r="F91" s="138" t="n"/>
-      <c r="G91" s="125" t="n"/>
+      <c r="G91" s="101" t="n"/>
       <c r="H91" s="102" t="n"/>
       <c r="I91" s="102" t="n"/>
       <c r="J91" s="102" t="n"/>
@@ -5034,19 +5048,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C92" s="90" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D92" s="91" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="n"/>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D92" s="33" t="inlineStr">
+        <is>
+          <t>You decide all targets for direct targeting passes</t>
+        </is>
+      </c>
+      <c r="E92" s="34" t="n"/>
       <c r="F92" s="138" t="n"/>
-      <c r="G92" s="101" t="n"/>
+      <c r="G92" s="107" t="n"/>
       <c r="H92" s="102" t="n"/>
       <c r="I92" s="102" t="n"/>
       <c r="J92" s="102" t="n"/>
@@ -5058,19 +5072,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C93" s="32" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D93" s="33" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E93" s="34" t="n"/>
-      <c r="F93" s="138" t="n"/>
-      <c r="G93" s="107" t="n"/>
+      <c r="C93" s="31" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F93" s="139" t="n"/>
+      <c r="G93" s="101" t="n"/>
       <c r="H93" s="102" t="n"/>
       <c r="I93" s="102" t="n"/>
       <c r="J93" s="102" t="n"/>
@@ -5082,19 +5100,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C94" s="31" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="n"/>
+      <c r="C94" s="90" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D94" s="94" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
+        </is>
+      </c>
+      <c r="E94" s="34" t="n"/>
       <c r="F94" s="138" t="n"/>
-      <c r="G94" s="101" t="n"/>
+      <c r="G94" s="125" t="n"/>
       <c r="H94" s="102" t="n"/>
       <c r="I94" s="102" t="n"/>
       <c r="J94" s="102" t="n"/>
@@ -5106,19 +5124,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C95" s="32" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D95" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +20% if you scored last round.</t>
-        </is>
-      </c>
-      <c r="E95" s="34" t="n"/>
+      <c r="C95" s="90" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D95" s="91" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="n"/>
       <c r="F95" s="138" t="n"/>
-      <c r="G95" s="107" t="n"/>
+      <c r="G95" s="101" t="n"/>
       <c r="H95" s="102" t="n"/>
       <c r="I95" s="102" t="n"/>
       <c r="J95" s="102" t="n"/>
@@ -5130,19 +5148,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C96" s="31" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D96" s="91" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="n"/>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="D96" s="33" t="inlineStr">
+        <is>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+        </is>
+      </c>
+      <c r="E96" s="34" t="n"/>
       <c r="F96" s="138" t="n"/>
-      <c r="G96" s="101" t="n"/>
+      <c r="G96" s="107" t="n"/>
       <c r="H96" s="102" t="n"/>
       <c r="I96" s="102" t="n"/>
       <c r="J96" s="102" t="n"/>
@@ -5154,23 +5172,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C97" s="32" t="inlineStr">
-        <is>
-          <t>No Bag</t>
-        </is>
-      </c>
-      <c r="D97" s="33" t="inlineStr">
-        <is>
-          <t>Cannot activate Move cards this round</t>
-        </is>
-      </c>
-      <c r="E97" s="34" t="n"/>
+      <c r="C97" s="31" t="inlineStr">
+        <is>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="n"/>
       <c r="F97" s="138" t="n"/>
-      <c r="G97" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G97" s="101" t="n"/>
       <c r="H97" s="102" t="n"/>
       <c r="I97" s="102" t="n"/>
       <c r="J97" s="102" t="n"/>
@@ -5182,19 +5196,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C98" s="31" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes this round</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="n"/>
+      <c r="C98" s="32" t="inlineStr">
+        <is>
+          <t>Hot Hand</t>
+        </is>
+      </c>
+      <c r="D98" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +20% if you scored last round.</t>
+        </is>
+      </c>
+      <c r="E98" s="34" t="n"/>
       <c r="F98" s="138" t="n"/>
-      <c r="G98" s="101" t="n"/>
+      <c r="G98" s="107" t="n"/>
       <c r="H98" s="102" t="n"/>
       <c r="I98" s="102" t="n"/>
       <c r="J98" s="102" t="n"/>
@@ -5206,23 +5220,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C99" s="32" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D99" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
-        </is>
-      </c>
-      <c r="E99" s="34" t="n"/>
+      <c r="C99" s="31" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D99" s="91" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="n"/>
       <c r="F99" s="138" t="n"/>
-      <c r="G99" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G99" s="101" t="n"/>
       <c r="H99" s="102" t="n"/>
       <c r="I99" s="102" t="n"/>
       <c r="J99" s="102" t="n"/>
@@ -5234,19 +5244,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C100" s="31" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="n"/>
+      <c r="C100" s="32" t="inlineStr">
+        <is>
+          <t>No Bag</t>
+        </is>
+      </c>
+      <c r="D100" s="33" t="inlineStr">
+        <is>
+          <t>Cannot activate Move cards this round</t>
+        </is>
+      </c>
+      <c r="E100" s="34" t="n"/>
       <c r="F100" s="138" t="n"/>
-      <c r="G100" s="101" t="n"/>
+      <c r="G100" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H100" s="102" t="n"/>
       <c r="I100" s="102" t="n"/>
       <c r="J100" s="102" t="n"/>
@@ -5258,19 +5272,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C101" s="32" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D101" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
-        </is>
-      </c>
-      <c r="E101" s="34" t="n"/>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="n"/>
       <c r="F101" s="138" t="n"/>
-      <c r="G101" s="107" t="n"/>
+      <c r="G101" s="101" t="n"/>
       <c r="H101" s="102" t="n"/>
       <c r="I101" s="102" t="n"/>
       <c r="J101" s="102" t="n"/>
@@ -5282,19 +5296,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C102" s="31" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="n"/>
+      <c r="C102" s="32" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D102" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E102" s="34" t="n"/>
       <c r="F102" s="138" t="n"/>
-      <c r="G102" s="101" t="n"/>
+      <c r="G102" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H102" s="102" t="n"/>
       <c r="I102" s="102" t="n"/>
       <c r="J102" s="102" t="n"/>
@@ -5306,19 +5324,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C103" s="32" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D103" s="33" t="inlineStr">
-        <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E103" s="34" t="n"/>
+      <c r="C103" s="31" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="n"/>
       <c r="F103" s="138" t="n"/>
-      <c r="G103" s="107" t="n"/>
+      <c r="G103" s="101" t="n"/>
       <c r="H103" s="102" t="n"/>
       <c r="I103" s="102" t="n"/>
       <c r="J103" s="102" t="n"/>
@@ -5330,19 +5348,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C104" s="31" t="inlineStr">
-        <is>
-          <t>Unguardable</t>
-        </is>
-      </c>
-      <c r="D104" s="91" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="n"/>
+      <c r="C104" s="32" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D104" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E104" s="34" t="n"/>
       <c r="F104" s="138" t="n"/>
-      <c r="G104" s="101" t="n"/>
+      <c r="G104" s="107" t="n"/>
       <c r="H104" s="102" t="n"/>
       <c r="I104" s="102" t="n"/>
       <c r="J104" s="102" t="n"/>
@@ -5354,89 +5372,236 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C105" s="32" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D105" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
-        </is>
-      </c>
-      <c r="E105" s="34" t="n"/>
+      <c r="C105" s="31" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="n"/>
       <c r="F105" s="138" t="n"/>
-      <c r="G105" s="113" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G105" s="101" t="n"/>
       <c r="H105" s="102" t="n"/>
       <c r="I105" s="102" t="n"/>
       <c r="J105" s="102" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="61" t="n"/>
-      <c r="B106" s="62" t="inlineStr">
+      <c r="A106" s="29" t="n"/>
+      <c r="B106" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C106" s="66" t="inlineStr">
+      <c r="C106" s="32" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D106" s="33" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E106" s="34" t="n"/>
+      <c r="F106" s="138" t="n"/>
+      <c r="G106" s="107" t="n"/>
+      <c r="H106" s="102" t="n"/>
+      <c r="I106" s="102" t="n"/>
+      <c r="J106" s="102" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="29" t="n"/>
+      <c r="B107" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C107" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D107" s="91" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="138" t="n"/>
+      <c r="G107" s="101" t="n"/>
+      <c r="H107" s="102" t="n"/>
+      <c r="I107" s="102" t="n"/>
+      <c r="J107" s="102" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="29" t="n"/>
+      <c r="B108" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D108" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E108" s="34" t="n"/>
+      <c r="F108" s="138" t="n"/>
+      <c r="G108" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H108" s="102" t="n"/>
+      <c r="I108" s="102" t="n"/>
+      <c r="J108" s="102" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="61" t="n"/>
+      <c r="B109" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C109" s="66" t="inlineStr">
         <is>
           <t>Ball Pounder</t>
         </is>
       </c>
-      <c r="D106" s="95" t="inlineStr">
+      <c r="D109" s="95" t="inlineStr">
         <is>
           <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
-      <c r="E106" s="68" t="n"/>
-      <c r="F106" s="140" t="n"/>
-      <c r="G106" s="126" t="n"/>
-      <c r="H106" s="117" t="n"/>
-      <c r="I106" s="117" t="n"/>
-      <c r="J106" s="117" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="61" t="n"/>
-      <c r="B107" s="62" t="inlineStr">
+      <c r="E109" s="68" t="n"/>
+      <c r="F109" s="140" t="n"/>
+      <c r="G109" s="126" t="n"/>
+      <c r="H109" s="117" t="n"/>
+      <c r="I109" s="117" t="n"/>
+      <c r="J109" s="117" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="61" t="n"/>
+      <c r="B110" s="62" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C107" s="66" t="inlineStr">
+      <c r="C110" s="66" t="inlineStr">
         <is>
           <t>Unselfish</t>
         </is>
       </c>
-      <c r="D107" s="95" t="inlineStr">
+      <c r="D110" s="95" t="inlineStr">
         <is>
           <t>Draw 1 card whenever you pass the ball at 50% SHOT or higher</t>
         </is>
       </c>
-      <c r="E107" s="68" t="n"/>
-      <c r="F107" s="140" t="n"/>
-      <c r="G107" s="126" t="n"/>
-      <c r="H107" s="117" t="n"/>
-      <c r="I107" s="117" t="n"/>
-      <c r="J107" s="117" t="n"/>
+      <c r="E110" s="68" t="n"/>
+      <c r="F110" s="140" t="n"/>
+      <c r="G110" s="126" t="n"/>
+      <c r="H110" s="117" t="n"/>
+      <c r="I110" s="117" t="n"/>
+      <c r="J110" s="117" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="61" t="n"/>
+      <c r="B111" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C111" s="66" t="inlineStr">
+        <is>
+          <t>Dirty Player</t>
+        </is>
+      </c>
+      <c r="D111" s="95" t="inlineStr">
+        <is>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+        </is>
+      </c>
+      <c r="E111" s="68" t="n"/>
+      <c r="F111" s="140" t="n"/>
+      <c r="G111" s="126" t="n"/>
+      <c r="H111" s="117" t="n"/>
+      <c r="I111" s="117" t="n"/>
+      <c r="J111" s="117" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="61" t="n"/>
+      <c r="B112" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C112" s="66" t="inlineStr">
+        <is>
+          <t>Villainous Reputation</t>
+        </is>
+      </c>
+      <c r="D112" s="95" t="inlineStr">
+        <is>
+          <t>Discard 1 whenever any Whistle triggers</t>
+        </is>
+      </c>
+      <c r="E112" s="68" t="n"/>
+      <c r="F112" s="140" t="n"/>
+      <c r="G112" s="126" t="inlineStr">
+        <is>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="61" t="n"/>
+      <c r="B113" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C113" s="66" t="inlineStr">
+        <is>
+          <t>Free Agent</t>
+        </is>
+      </c>
+      <c r="D113" s="95" t="inlineStr">
+        <is>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+        </is>
+      </c>
+      <c r="E113" s="68" t="n"/>
+      <c r="F113" s="140" t="n"/>
+      <c r="G113" s="126" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="98">
+  <mergeCells count="100">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>
+    <mergeCell ref="G111:J111"/>
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G82:J82"/>
     <mergeCell ref="G57:J57"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
@@ -5445,17 +5610,19 @@
     <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
+    <mergeCell ref="G108:J108"/>
     <mergeCell ref="G58:J58"/>
+    <mergeCell ref="G110:J110"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="G91:J91"/>
     <mergeCell ref="G29:J29"/>
     <mergeCell ref="G85:J85"/>
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G94:J94"/>
+    <mergeCell ref="G84:J84"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G84:J84"/>
     <mergeCell ref="G31:J31"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="G12:J12"/>
@@ -5518,7 +5685,6 @@
     <mergeCell ref="G93:J93"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
-    <mergeCell ref="G83:J83"/>
     <mergeCell ref="G92:J92"/>
     <mergeCell ref="G30:J30"/>
     <mergeCell ref="G5:J5"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2626,39 +2626,40 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$113,"Pass")</f>
+        <f>COUNTIF($B$5:$B$115,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$113,"Move")+COUNTIF($B$5:$B$113,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$115,"Move")+COUNTIF($B$5:$B$115,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$113,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$115,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$113,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$115,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$113,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$115,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$113,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$115,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$113,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$115,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$113,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$115,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="132" thickBot="1">
       <c r="A4" s="123" t="inlineStr">
         <is>
@@ -2702,7 +2703,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$113,"Pass")</f>
+        <f>COUNTIF($B$5:$B$115,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="23" t="n"/>
@@ -2959,7 +2960,7 @@
         </is>
       </c>
       <c r="B15" s="40">
-        <f>COUNTIF($B$5:$B$113,"Move")+COUNTIF($B$5:$B$113,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$115,"Move")+COUNTIF($B$5:$B$115,"Special Move")</f>
         <v/>
       </c>
       <c r="C15" s="41" t="n"/>
@@ -3333,7 +3334,7 @@
         </is>
       </c>
       <c r="B28" s="43">
-        <f>COUNTIF($B$5:$B$113,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$115,"Special Move")</f>
         <v/>
       </c>
       <c r="C28" s="44" t="n"/>
@@ -3718,7 +3719,7 @@
         </is>
       </c>
       <c r="B41" s="59">
-        <f>COUNTIF($B$5:$B$113,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$115,"Clamp")</f>
         <v/>
       </c>
       <c r="C41" s="60" t="n"/>
@@ -3887,7 +3888,7 @@
         </is>
       </c>
       <c r="B47" s="59">
-        <f>COUNTIF($B$5:$B$113,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$115,"Whistle")</f>
         <v/>
       </c>
       <c r="C47" s="60" t="n"/>
@@ -4346,7 +4347,7 @@
         </is>
       </c>
       <c r="B65" s="59">
-        <f>COUNTIF($B$5:$B$113,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$115,"Game Break")</f>
         <v/>
       </c>
       <c r="C65" s="60" t="n"/>
@@ -4859,20 +4860,27 @@
       <c r="J83" s="102" t="n"/>
     </row>
     <row r="84" ht="28" customHeight="1" s="132">
-      <c r="A84" s="55" t="inlineStr">
-        <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="B84" s="56">
-        <f>COUNTIF($B$5:$B$113,"Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C84" s="57" t="n"/>
-      <c r="D84" s="57" t="n"/>
-      <c r="E84" s="57" t="n"/>
-      <c r="F84" s="88" t="n"/>
-      <c r="G84" s="108" t="n"/>
+      <c r="A84" s="29" t="n"/>
+      <c r="B84" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C84" s="134" t="inlineStr">
+        <is>
+          <t>Floor Cleanup</t>
+        </is>
+      </c>
+      <c r="D84" s="91" t="inlineStr">
+        <is>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="n"/>
+      <c r="F84" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="111" t="n"/>
       <c r="H84" s="102" t="n"/>
       <c r="I84" s="102" t="n"/>
       <c r="J84" s="102" t="n"/>
@@ -4881,144 +4889,141 @@
       <c r="A85" s="29" t="n"/>
       <c r="B85" s="30" t="inlineStr">
         <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="C85" s="31" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C85" s="134" t="inlineStr">
+        <is>
+          <t>Official Timeout</t>
         </is>
       </c>
       <c r="D85" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+          <t>Discard all Injuries on all players</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G85" s="101" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G85" s="111" t="n"/>
       <c r="H85" s="102" t="n"/>
       <c r="I85" s="102" t="n"/>
       <c r="J85" s="102" t="n"/>
     </row>
     <row r="86" ht="56" customHeight="1" s="132">
-      <c r="A86" s="58" t="inlineStr">
+      <c r="A86" s="55" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="B86" s="56">
+        <f>COUNTIF($B$5:$B$115,"Injury GB")</f>
+        <v/>
+      </c>
+      <c r="C86" s="57" t="n"/>
+      <c r="D86" s="57" t="n"/>
+      <c r="E86" s="57" t="n"/>
+      <c r="F86" s="88" t="n"/>
+      <c r="G86" s="108" t="n"/>
+      <c r="H86" s="102" t="n"/>
+      <c r="I86" s="102" t="n"/>
+      <c r="J86" s="102" t="n"/>
+    </row>
+    <row r="87" ht="56" customHeight="1" s="132">
+      <c r="A87" s="29" t="n"/>
+      <c r="B87" s="30" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="C87" s="31" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D87" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G87" s="101" t="n"/>
+      <c r="H87" s="102" t="n"/>
+      <c r="I87" s="102" t="n"/>
+      <c r="J87" s="102" t="n"/>
+    </row>
+    <row r="88" ht="28" customHeight="1" s="132">
+      <c r="A88" s="58" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="B86" s="59">
-        <f>COUNTIF($B$5:$B$113,"Devastating Injury GB")</f>
+      <c r="B88" s="59">
+        <f>COUNTIF($B$5:$B$115,"Devastating Injury GB")</f>
         <v/>
       </c>
-      <c r="C86" s="60" t="n"/>
-      <c r="D86" s="60" t="n"/>
-      <c r="E86" s="60" t="n"/>
-      <c r="F86" s="86" t="n"/>
-      <c r="G86" s="109" t="n"/>
-      <c r="H86" s="110" t="n"/>
-      <c r="I86" s="110" t="n"/>
-      <c r="J86" s="110" t="n"/>
-    </row>
-    <row r="87" ht="56" customHeight="1" s="132">
-      <c r="A87" s="50" t="n"/>
-      <c r="B87" s="51" t="inlineStr">
+      <c r="C88" s="60" t="n"/>
+      <c r="D88" s="60" t="n"/>
+      <c r="E88" s="60" t="n"/>
+      <c r="F88" s="86" t="n"/>
+      <c r="G88" s="109" t="n"/>
+      <c r="H88" s="110" t="n"/>
+      <c r="I88" s="110" t="n"/>
+      <c r="J88" s="110" t="n"/>
+    </row>
+    <row r="89" ht="42" customHeight="1" s="132">
+      <c r="A89" s="50" t="n"/>
+      <c r="B89" s="51" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="C87" s="136" t="inlineStr">
+      <c r="C89" s="136" t="inlineStr">
         <is>
           <t>Torn Achilles</t>
         </is>
       </c>
-      <c r="D87" s="137" t="inlineStr">
+      <c r="D89" s="137" t="inlineStr">
         <is>
           <t>Hand is locked every turn except 1 card (randomly)</t>
         </is>
       </c>
-      <c r="E87" s="54" t="n"/>
-      <c r="F87" s="141" t="n"/>
-      <c r="G87" s="114" t="n"/>
-      <c r="H87" s="115" t="n"/>
-      <c r="I87" s="115" t="n"/>
-      <c r="J87" s="115" t="n"/>
-    </row>
-    <row r="88" ht="28" customHeight="1" s="132">
-      <c r="A88" s="55" t="inlineStr">
+      <c r="E89" s="54" t="n"/>
+      <c r="F89" s="141" t="n"/>
+      <c r="G89" s="114" t="n"/>
+      <c r="H89" s="115" t="n"/>
+      <c r="I89" s="115" t="n"/>
+      <c r="J89" s="115" t="n"/>
+    </row>
+    <row r="90" ht="28" customHeight="1" s="132">
+      <c r="A90" s="55" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B88" s="56">
-        <f>COUNTIF($B$5:$B$113,"Intangible")</f>
+      <c r="B90" s="56">
+        <f>COUNTIF($B$5:$B$115,"Intangible")</f>
         <v/>
       </c>
-      <c r="C88" s="57" t="n"/>
-      <c r="D88" s="57" t="n"/>
-      <c r="E88" s="57" t="n"/>
-      <c r="F88" s="88" t="n"/>
-      <c r="G88" s="108" t="n"/>
-      <c r="H88" s="102" t="n"/>
-      <c r="I88" s="102" t="n"/>
-      <c r="J88" s="102" t="n"/>
-    </row>
-    <row r="89" ht="42" customHeight="1" s="132">
-      <c r="A89" s="96" t="inlineStr">
-        <is>
-          <t>All intangibles are limited to 1</t>
-        </is>
-      </c>
-      <c r="B89" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C89" s="31" t="inlineStr">
-        <is>
-          <t>Board-Crasher</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% upon Rebounding your own missed shot</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="138" t="n"/>
-      <c r="G89" s="101" t="n"/>
-      <c r="H89" s="102" t="n"/>
-      <c r="I89" s="102" t="n"/>
-      <c r="J89" s="102" t="n"/>
-    </row>
-    <row r="90" ht="28" customHeight="1" s="132">
-      <c r="A90" s="29" t="n"/>
-      <c r="B90" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C90" s="32" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D90" s="33" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E90" s="34" t="n"/>
-      <c r="F90" s="138" t="n"/>
-      <c r="G90" s="107" t="n"/>
+      <c r="C90" s="57" t="n"/>
+      <c r="D90" s="57" t="n"/>
+      <c r="E90" s="57" t="n"/>
+      <c r="F90" s="88" t="n"/>
+      <c r="G90" s="108" t="n"/>
       <c r="H90" s="102" t="n"/>
       <c r="I90" s="102" t="n"/>
       <c r="J90" s="102" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1" s="132">
-      <c r="A91" s="29" t="n"/>
+      <c r="A91" s="96" t="inlineStr">
+        <is>
+          <t>All intangibles are limited to 1</t>
+        </is>
+      </c>
       <c r="B91" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
@@ -5026,12 +5031,12 @@
       </c>
       <c r="C91" s="31" t="inlineStr">
         <is>
-          <t>Clutch Gene</t>
+          <t>Board-Crasher</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+          <t>SHOT +10% upon Rebounding your own missed shot</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -5050,12 +5055,12 @@
       </c>
       <c r="C92" s="32" t="inlineStr">
         <is>
-          <t>Floor General</t>
+          <t>Catch &amp; Shoot Specialist</t>
         </is>
       </c>
       <c r="D92" s="33" t="inlineStr">
         <is>
-          <t>You decide all targets for direct targeting passes</t>
+          <t>Additional SHOT +10% on all received passes</t>
         </is>
       </c>
       <c r="E92" s="34" t="n"/>
@@ -5074,20 +5079,16 @@
       </c>
       <c r="C93" s="31" t="inlineStr">
         <is>
-          <t>Fox-Like First Step</t>
+          <t>Clutch Gene</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F93" s="139" t="n"/>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="138" t="n"/>
       <c r="G93" s="101" t="n"/>
       <c r="H93" s="102" t="n"/>
       <c r="I93" s="102" t="n"/>
@@ -5100,19 +5101,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C94" s="90" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D94" s="94" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D94" s="33" t="inlineStr">
+        <is>
+          <t>You decide all targets for direct targeting passes</t>
         </is>
       </c>
       <c r="E94" s="34" t="n"/>
       <c r="F94" s="138" t="n"/>
-      <c r="G94" s="125" t="n"/>
+      <c r="G94" s="107" t="n"/>
       <c r="H94" s="102" t="n"/>
       <c r="I94" s="102" t="n"/>
       <c r="J94" s="102" t="n"/>
@@ -5124,18 +5125,22 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C95" s="90" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D95" s="91" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="n"/>
-      <c r="F95" s="138" t="n"/>
+      <c r="C95" s="31" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F95" s="139" t="n"/>
       <c r="G95" s="101" t="n"/>
       <c r="H95" s="102" t="n"/>
       <c r="I95" s="102" t="n"/>
@@ -5148,19 +5153,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C96" s="32" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D96" s="33" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+      <c r="C96" s="90" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D96" s="94" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
         </is>
       </c>
       <c r="E96" s="34" t="n"/>
       <c r="F96" s="138" t="n"/>
-      <c r="G96" s="107" t="n"/>
+      <c r="G96" s="125" t="n"/>
       <c r="H96" s="102" t="n"/>
       <c r="I96" s="102" t="n"/>
       <c r="J96" s="102" t="n"/>
@@ -5172,14 +5177,14 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C97" s="31" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+      <c r="C97" s="90" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D97" s="91" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -5198,12 +5203,12 @@
       </c>
       <c r="C98" s="32" t="inlineStr">
         <is>
-          <t>Hot Hand</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="D98" s="33" t="inlineStr">
         <is>
-          <t>SHOT +20% if you scored last round.</t>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
         </is>
       </c>
       <c r="E98" s="34" t="n"/>
@@ -5222,12 +5227,12 @@
       </c>
       <c r="C99" s="31" t="inlineStr">
         <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D99" s="91" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -5246,21 +5251,17 @@
       </c>
       <c r="C100" s="32" t="inlineStr">
         <is>
-          <t>No Bag</t>
+          <t>Hot Hand</t>
         </is>
       </c>
       <c r="D100" s="33" t="inlineStr">
         <is>
-          <t>Cannot activate Move cards this round</t>
+          <t>SHOT +20% if you scored last round.</t>
         </is>
       </c>
       <c r="E100" s="34" t="n"/>
       <c r="F100" s="138" t="n"/>
-      <c r="G100" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G100" s="107" t="n"/>
       <c r="H100" s="102" t="n"/>
       <c r="I100" s="102" t="n"/>
       <c r="J100" s="102" t="n"/>
@@ -5274,12 +5275,12 @@
       </c>
       <c r="C101" s="31" t="inlineStr">
         <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D101" s="91" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -5298,12 +5299,12 @@
       </c>
       <c r="C102" s="32" t="inlineStr">
         <is>
-          <t>Shooting Slump</t>
+          <t>No Bag</t>
         </is>
       </c>
       <c r="D102" s="33" t="inlineStr">
         <is>
-          <t>SHOT -20% this round</t>
+          <t>Cannot activate Move cards this round</t>
         </is>
       </c>
       <c r="E102" s="34" t="n"/>
@@ -5326,12 +5327,12 @@
       </c>
       <c r="C103" s="31" t="inlineStr">
         <is>
-          <t>Shot Creator</t>
+          <t>Point God</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>Draw 1 additional card after every draw effect</t>
+          <t>Draw 1 card following each of your passes</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -5350,17 +5351,21 @@
       </c>
       <c r="C104" s="32" t="inlineStr">
         <is>
-          <t>Sixth Man</t>
+          <t>Shooting Slump</t>
         </is>
       </c>
       <c r="D104" s="33" t="inlineStr">
         <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
+          <t>SHOT -20% this round</t>
         </is>
       </c>
       <c r="E104" s="34" t="n"/>
       <c r="F104" s="138" t="n"/>
-      <c r="G104" s="107" t="n"/>
+      <c r="G104" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H104" s="102" t="n"/>
       <c r="I104" s="102" t="n"/>
       <c r="J104" s="102" t="n"/>
@@ -5374,12 +5379,12 @@
       </c>
       <c r="C105" s="31" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Shot Creator</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
+          <t>Draw 1 additional card after every draw effect</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -5398,12 +5403,12 @@
       </c>
       <c r="C106" s="32" t="inlineStr">
         <is>
-          <t>Splash Cousin</t>
+          <t>Sixth Man</t>
         </is>
       </c>
       <c r="D106" s="33" t="inlineStr">
         <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
         </is>
       </c>
       <c r="E106" s="34" t="n"/>
@@ -5422,12 +5427,12 @@
       </c>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>Unguardable</t>
-        </is>
-      </c>
-      <c r="D107" s="91" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
         </is>
       </c>
       <c r="E107" s="7" t="n"/>
@@ -5446,72 +5451,72 @@
       </c>
       <c r="C108" s="32" t="inlineStr">
         <is>
-          <t>Lethal Shooter</t>
+          <t>Splash Cousin</t>
         </is>
       </c>
       <c r="D108" s="33" t="inlineStr">
         <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
         </is>
       </c>
       <c r="E108" s="34" t="n"/>
       <c r="F108" s="138" t="n"/>
-      <c r="G108" s="113" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G108" s="107" t="n"/>
       <c r="H108" s="102" t="n"/>
       <c r="I108" s="102" t="n"/>
       <c r="J108" s="102" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="61" t="n"/>
-      <c r="B109" s="62" t="inlineStr">
+      <c r="A109" s="29" t="n"/>
+      <c r="B109" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C109" s="66" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D109" s="95" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E109" s="68" t="n"/>
-      <c r="F109" s="140" t="n"/>
-      <c r="G109" s="126" t="n"/>
-      <c r="H109" s="117" t="n"/>
-      <c r="I109" s="117" t="n"/>
-      <c r="J109" s="117" t="n"/>
+      <c r="C109" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D109" s="91" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="n"/>
+      <c r="F109" s="138" t="n"/>
+      <c r="G109" s="101" t="n"/>
+      <c r="H109" s="102" t="n"/>
+      <c r="I109" s="102" t="n"/>
+      <c r="J109" s="102" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="61" t="n"/>
-      <c r="B110" s="62" t="inlineStr">
+      <c r="A110" s="29" t="n"/>
+      <c r="B110" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C110" s="66" t="inlineStr">
-        <is>
-          <t>Unselfish</t>
-        </is>
-      </c>
-      <c r="D110" s="95" t="inlineStr">
-        <is>
-          <t>Draw 1 card whenever you pass the ball at 50% SHOT or higher</t>
-        </is>
-      </c>
-      <c r="E110" s="68" t="n"/>
-      <c r="F110" s="140" t="n"/>
-      <c r="G110" s="126" t="n"/>
-      <c r="H110" s="117" t="n"/>
-      <c r="I110" s="117" t="n"/>
-      <c r="J110" s="117" t="n"/>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D110" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E110" s="34" t="n"/>
+      <c r="F110" s="138" t="n"/>
+      <c r="G110" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H110" s="102" t="n"/>
+      <c r="I110" s="102" t="n"/>
+      <c r="J110" s="102" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="61" t="n"/>
@@ -5522,12 +5527,12 @@
       </c>
       <c r="C111" s="66" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D111" s="95" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E111" s="68" t="n"/>
@@ -5546,21 +5551,20 @@
       </c>
       <c r="C112" s="66" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D112" s="95" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>Draw 1 card whenever you pass the ball at 50% SHOT or higher</t>
         </is>
       </c>
       <c r="E112" s="68" t="n"/>
       <c r="F112" s="140" t="n"/>
-      <c r="G112" s="126" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="G112" s="126" t="n"/>
+      <c r="H112" s="117" t="n"/>
+      <c r="I112" s="117" t="n"/>
+      <c r="J112" s="117" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="61" t="n"/>
@@ -5571,24 +5575,73 @@
       </c>
       <c r="C113" s="66" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D113" s="95" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E113" s="68" t="n"/>
       <c r="F113" s="140" t="n"/>
-      <c r="G113" s="126" t="inlineStr">
+      <c r="G113" s="126" t="n"/>
+      <c r="H113" s="117" t="n"/>
+      <c r="I113" s="117" t="n"/>
+      <c r="J113" s="117" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="61" t="n"/>
+      <c r="B114" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C114" s="66" t="inlineStr">
+        <is>
+          <t>Villainous Reputation</t>
+        </is>
+      </c>
+      <c r="D114" s="95" t="inlineStr">
+        <is>
+          <t>Discard 1 whenever any Whistle triggers</t>
+        </is>
+      </c>
+      <c r="E114" s="68" t="n"/>
+      <c r="F114" s="140" t="n"/>
+      <c r="G114" s="126" t="inlineStr">
+        <is>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="61" t="n"/>
+      <c r="B115" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C115" s="66" t="inlineStr">
+        <is>
+          <t>Free Agent</t>
+        </is>
+      </c>
+      <c r="D115" s="95" t="inlineStr">
+        <is>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+        </is>
+      </c>
+      <c r="E115" s="68" t="n"/>
+      <c r="F115" s="140" t="n"/>
+      <c r="G115" s="126" t="inlineStr">
         <is>
           <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="100">
+  <mergeCells count="102">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G109:J109"/>
@@ -5600,6 +5653,7 @@
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
+    <mergeCell ref="G5:J5"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G57:J57"/>
@@ -5613,22 +5667,22 @@
     <mergeCell ref="G108:J108"/>
     <mergeCell ref="G58:J58"/>
     <mergeCell ref="G110:J110"/>
+    <mergeCell ref="G113:J113"/>
     <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G29:J29"/>
     <mergeCell ref="G91:J91"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G94:J94"/>
-    <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G102:J102"/>
     <mergeCell ref="G31:J31"/>
-    <mergeCell ref="G102:J102"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
+    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="G61:J61"/>
     <mergeCell ref="G70:J70"/>
@@ -5636,6 +5690,8 @@
     <mergeCell ref="G97:J97"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G38:J38"/>
+    <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G112:J112"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="G62:J62"/>
     <mergeCell ref="G49:J49"/>
@@ -5668,27 +5724,26 @@
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="G63:J63"/>
     <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G106:J106"/>
     <mergeCell ref="G50:J50"/>
-    <mergeCell ref="G106:J106"/>
     <mergeCell ref="G56:J56"/>
+    <mergeCell ref="G14:J14"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
+    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G93:J93"/>
     <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G93:J93"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G92:J92"/>
     <mergeCell ref="G30:J30"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G14:J14"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2659,7 +2659,6 @@
       </c>
       <c r="J2" s="19" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="132" thickBot="1">
       <c r="A4" s="123" t="inlineStr">
         <is>
@@ -4899,7 +4898,7 @@
       </c>
       <c r="D85" s="91" t="inlineStr">
         <is>
-          <t>Discard all Injuries on all players</t>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
@@ -5653,7 +5652,6 @@
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
-    <mergeCell ref="G5:J5"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G57:J57"/>
@@ -5669,20 +5667,21 @@
     <mergeCell ref="G110:J110"/>
     <mergeCell ref="G113:J113"/>
     <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G91:J91"/>
     <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G91:J91"/>
+    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G94:J94"/>
-    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G31:J31"/>
     <mergeCell ref="G102:J102"/>
-    <mergeCell ref="G31:J31"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
+    <mergeCell ref="G21:J21"/>
     <mergeCell ref="G86:J86"/>
-    <mergeCell ref="G21:J21"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="G61:J61"/>
     <mergeCell ref="G70:J70"/>
@@ -5690,7 +5689,6 @@
     <mergeCell ref="G97:J97"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G38:J38"/>
-    <mergeCell ref="G84:J84"/>
     <mergeCell ref="G112:J112"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="G62:J62"/>
@@ -5724,26 +5722,27 @@
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="G63:J63"/>
     <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G50:J50"/>
     <mergeCell ref="G106:J106"/>
-    <mergeCell ref="G50:J50"/>
     <mergeCell ref="G56:J56"/>
-    <mergeCell ref="G14:J14"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
-    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
+    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G28:J28"/>
     <mergeCell ref="G93:J93"/>
-    <mergeCell ref="G28:J28"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G92:J92"/>
     <mergeCell ref="G30:J30"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G14:J14"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2626,39 +2626,40 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$115,"Pass")</f>
+        <f>COUNTIF($B$5:$B$116,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$115,"Move")+COUNTIF($B$5:$B$115,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$116,"Move")+COUNTIF($B$5:$B$116,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$115,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$116,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$115,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$116,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$115,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$116,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$115,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$116,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$115,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$116,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$115,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$116,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="132" thickBot="1">
       <c r="A4" s="123" t="inlineStr">
         <is>
@@ -2702,7 +2703,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$115,"Pass")</f>
+        <f>COUNTIF($B$5:$B$116,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="23" t="n"/>
@@ -2959,7 +2960,7 @@
         </is>
       </c>
       <c r="B15" s="40">
-        <f>COUNTIF($B$5:$B$115,"Move")+COUNTIF($B$5:$B$115,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$116,"Move")+COUNTIF($B$5:$B$116,"Special Move")</f>
         <v/>
       </c>
       <c r="C15" s="41" t="n"/>
@@ -3333,7 +3334,7 @@
         </is>
       </c>
       <c r="B28" s="43">
-        <f>COUNTIF($B$5:$B$115,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$116,"Special Move")</f>
         <v/>
       </c>
       <c r="C28" s="44" t="n"/>
@@ -3718,7 +3719,7 @@
         </is>
       </c>
       <c r="B41" s="59">
-        <f>COUNTIF($B$5:$B$115,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$116,"Clamp")</f>
         <v/>
       </c>
       <c r="C41" s="60" t="n"/>
@@ -3887,7 +3888,7 @@
         </is>
       </c>
       <c r="B47" s="59">
-        <f>COUNTIF($B$5:$B$115,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$116,"Whistle")</f>
         <v/>
       </c>
       <c r="C47" s="60" t="n"/>
@@ -4346,7 +4347,7 @@
         </is>
       </c>
       <c r="B65" s="59">
-        <f>COUNTIF($B$5:$B$115,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$116,"Game Break")</f>
         <v/>
       </c>
       <c r="C65" s="60" t="n"/>
@@ -4917,7 +4918,7 @@
         </is>
       </c>
       <c r="B86" s="56">
-        <f>COUNTIF($B$5:$B$115,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$116,"Injury GB")</f>
         <v/>
       </c>
       <c r="C86" s="57" t="n"/>
@@ -4962,7 +4963,7 @@
         </is>
       </c>
       <c r="B88" s="59">
-        <f>COUNTIF($B$5:$B$115,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$116,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="C88" s="60" t="n"/>
@@ -5005,7 +5006,7 @@
         </is>
       </c>
       <c r="B90" s="56">
-        <f>COUNTIF($B$5:$B$115,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$116,"Intangible")</f>
         <v/>
       </c>
       <c r="C90" s="57" t="n"/>
@@ -5107,7 +5108,7 @@
       </c>
       <c r="D94" s="33" t="inlineStr">
         <is>
-          <t>You decide all targets for direct targeting passes</t>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
         </is>
       </c>
       <c r="E94" s="34" t="n"/>
@@ -5639,8 +5640,32 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="61" t="n"/>
+      <c r="B116" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C116" s="66" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D116" s="95" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E116" s="68" t="n"/>
+      <c r="F116" s="140" t="n"/>
+      <c r="G116" s="126" t="n"/>
+      <c r="H116" s="117" t="n"/>
+      <c r="I116" s="117" t="n"/>
+      <c r="J116" s="117" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="102">
+  <mergeCells count="103">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G109:J109"/>
@@ -5652,6 +5677,7 @@
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
+    <mergeCell ref="G5:J5"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G57:J57"/>
@@ -5708,6 +5734,7 @@
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="G101:J101"/>
+    <mergeCell ref="G116:J116"/>
     <mergeCell ref="G103:J103"/>
     <mergeCell ref="G37:J37"/>
     <mergeCell ref="A4:B4"/>
@@ -5725,6 +5752,7 @@
     <mergeCell ref="G50:J50"/>
     <mergeCell ref="G106:J106"/>
     <mergeCell ref="G56:J56"/>
+    <mergeCell ref="G14:J14"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
@@ -5741,8 +5769,6 @@
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G92:J92"/>
     <mergeCell ref="G30:J30"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G14:J14"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2626,35 +2626,35 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$116,"Pass")</f>
+        <f>COUNTIF($B$5:$B$117,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$116,"Move")+COUNTIF($B$5:$B$116,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$117,"Move")+COUNTIF($B$5:$B$117,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$116,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$117,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$116,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$117,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$116,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$117,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$116,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$117,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$116,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$117,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$116,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$117,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$116,"Pass")</f>
+        <f>COUNTIF($B$5:$B$117,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="23" t="n"/>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="B15" s="40">
-        <f>COUNTIF($B$5:$B$116,"Move")+COUNTIF($B$5:$B$116,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$117,"Move")+COUNTIF($B$5:$B$117,"Special Move")</f>
         <v/>
       </c>
       <c r="C15" s="41" t="n"/>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="B28" s="43">
-        <f>COUNTIF($B$5:$B$116,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$117,"Special Move")</f>
         <v/>
       </c>
       <c r="C28" s="44" t="n"/>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="B41" s="59">
-        <f>COUNTIF($B$5:$B$116,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$117,"Clamp")</f>
         <v/>
       </c>
       <c r="C41" s="60" t="n"/>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="B47" s="59">
-        <f>COUNTIF($B$5:$B$116,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$117,"Whistle")</f>
         <v/>
       </c>
       <c r="C47" s="60" t="n"/>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="B65" s="59">
-        <f>COUNTIF($B$5:$B$116,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$117,"Game Break")</f>
         <v/>
       </c>
       <c r="C65" s="60" t="n"/>
@@ -4912,160 +4912,162 @@
       <c r="J85" s="102" t="n"/>
     </row>
     <row r="86" ht="56" customHeight="1" s="132">
-      <c r="A86" s="55" t="inlineStr">
-        <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="B86" s="56">
-        <f>COUNTIF($B$5:$B$116,"Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C86" s="57" t="n"/>
-      <c r="D86" s="57" t="n"/>
-      <c r="E86" s="57" t="n"/>
-      <c r="F86" s="88" t="n"/>
-      <c r="G86" s="108" t="n"/>
+      <c r="A86" s="29" t="n"/>
+      <c r="B86" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C86" s="134" t="inlineStr">
+        <is>
+          <t>Team Doctor</t>
+        </is>
+      </c>
+      <c r="D86" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="n"/>
+      <c r="F86" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" s="111" t="n"/>
       <c r="H86" s="102" t="n"/>
       <c r="I86" s="102" t="n"/>
       <c r="J86" s="102" t="n"/>
     </row>
     <row r="87" ht="56" customHeight="1" s="132">
-      <c r="A87" s="29" t="n"/>
-      <c r="B87" s="30" t="inlineStr">
+      <c r="A87" s="55" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="C87" s="31" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
-        </is>
-      </c>
-      <c r="D87" s="91" t="inlineStr">
-        <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="n"/>
-      <c r="F87" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G87" s="101" t="n"/>
+      <c r="B87" s="56">
+        <f>COUNTIF($B$5:$B$117,"Injury GB")</f>
+        <v/>
+      </c>
+      <c r="C87" s="57" t="n"/>
+      <c r="D87" s="57" t="n"/>
+      <c r="E87" s="57" t="n"/>
+      <c r="F87" s="88" t="n"/>
+      <c r="G87" s="108" t="n"/>
       <c r="H87" s="102" t="n"/>
       <c r="I87" s="102" t="n"/>
       <c r="J87" s="102" t="n"/>
     </row>
     <row r="88" ht="28" customHeight="1" s="132">
-      <c r="A88" s="58" t="inlineStr">
+      <c r="A88" s="29" t="n"/>
+      <c r="B88" s="30" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="C88" s="31" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D88" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="n"/>
+      <c r="F88" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G88" s="101" t="n"/>
+      <c r="H88" s="102" t="n"/>
+      <c r="I88" s="102" t="n"/>
+      <c r="J88" s="102" t="n"/>
+    </row>
+    <row r="89" ht="42" customHeight="1" s="132">
+      <c r="A89" s="58" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="B88" s="59">
-        <f>COUNTIF($B$5:$B$116,"Devastating Injury GB")</f>
+      <c r="B89" s="59">
+        <f>COUNTIF($B$5:$B$117,"Devastating Injury GB")</f>
         <v/>
       </c>
-      <c r="C88" s="60" t="n"/>
-      <c r="D88" s="60" t="n"/>
-      <c r="E88" s="60" t="n"/>
-      <c r="F88" s="86" t="n"/>
-      <c r="G88" s="109" t="n"/>
-      <c r="H88" s="110" t="n"/>
-      <c r="I88" s="110" t="n"/>
-      <c r="J88" s="110" t="n"/>
-    </row>
-    <row r="89" ht="42" customHeight="1" s="132">
-      <c r="A89" s="50" t="n"/>
-      <c r="B89" s="51" t="inlineStr">
+      <c r="C89" s="60" t="n"/>
+      <c r="D89" s="60" t="n"/>
+      <c r="E89" s="60" t="n"/>
+      <c r="F89" s="86" t="n"/>
+      <c r="G89" s="109" t="n"/>
+      <c r="H89" s="110" t="n"/>
+      <c r="I89" s="110" t="n"/>
+      <c r="J89" s="110" t="n"/>
+    </row>
+    <row r="90" ht="28" customHeight="1" s="132">
+      <c r="A90" s="50" t="n"/>
+      <c r="B90" s="51" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="C89" s="136" t="inlineStr">
+      <c r="C90" s="136" t="inlineStr">
         <is>
           <t>Torn Achilles</t>
         </is>
       </c>
-      <c r="D89" s="137" t="inlineStr">
+      <c r="D90" s="137" t="inlineStr">
         <is>
           <t>Hand is locked every turn except 1 card (randomly)</t>
         </is>
       </c>
-      <c r="E89" s="54" t="n"/>
-      <c r="F89" s="141" t="n"/>
-      <c r="G89" s="114" t="n"/>
-      <c r="H89" s="115" t="n"/>
-      <c r="I89" s="115" t="n"/>
-      <c r="J89" s="115" t="n"/>
-    </row>
-    <row r="90" ht="28" customHeight="1" s="132">
-      <c r="A90" s="55" t="inlineStr">
+      <c r="E90" s="54" t="n"/>
+      <c r="F90" s="141" t="n"/>
+      <c r="G90" s="114" t="n"/>
+      <c r="H90" s="115" t="n"/>
+      <c r="I90" s="115" t="n"/>
+      <c r="J90" s="115" t="n"/>
+    </row>
+    <row r="91" ht="42" customHeight="1" s="132">
+      <c r="A91" s="55" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B90" s="56">
-        <f>COUNTIF($B$5:$B$116,"Intangible")</f>
+      <c r="B91" s="56">
+        <f>COUNTIF($B$5:$B$117,"Intangible")</f>
         <v/>
       </c>
-      <c r="C90" s="57" t="n"/>
-      <c r="D90" s="57" t="n"/>
-      <c r="E90" s="57" t="n"/>
-      <c r="F90" s="88" t="n"/>
-      <c r="G90" s="108" t="n"/>
-      <c r="H90" s="102" t="n"/>
-      <c r="I90" s="102" t="n"/>
-      <c r="J90" s="102" t="n"/>
-    </row>
-    <row r="91" ht="42" customHeight="1" s="132">
-      <c r="A91" s="96" t="inlineStr">
-        <is>
-          <t>All intangibles are limited to 1</t>
-        </is>
-      </c>
-      <c r="B91" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C91" s="31" t="inlineStr">
-        <is>
-          <t>Board-Crasher</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% upon Rebounding your own missed shot</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="138" t="n"/>
-      <c r="G91" s="101" t="n"/>
+      <c r="C91" s="57" t="n"/>
+      <c r="D91" s="57" t="n"/>
+      <c r="E91" s="57" t="n"/>
+      <c r="F91" s="88" t="n"/>
+      <c r="G91" s="108" t="n"/>
       <c r="H91" s="102" t="n"/>
       <c r="I91" s="102" t="n"/>
       <c r="J91" s="102" t="n"/>
     </row>
     <row r="92" ht="14" customHeight="1" s="132">
-      <c r="A92" s="29" t="n"/>
+      <c r="A92" s="96" t="inlineStr">
+        <is>
+          <t>All intangibles are limited to 1</t>
+        </is>
+      </c>
       <c r="B92" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C92" s="32" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D92" s="33" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E92" s="34" t="n"/>
+      <c r="C92" s="31" t="inlineStr">
+        <is>
+          <t>Board-Crasher</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% upon Rebounding your own missed shot</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="n"/>
       <c r="F92" s="138" t="n"/>
-      <c r="G92" s="107" t="n"/>
+      <c r="G92" s="101" t="n"/>
       <c r="H92" s="102" t="n"/>
       <c r="I92" s="102" t="n"/>
       <c r="J92" s="102" t="n"/>
@@ -5077,19 +5079,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C93" s="31" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="n"/>
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D93" s="33" t="inlineStr">
+        <is>
+          <t>Additional SHOT +10% on all received passes</t>
+        </is>
+      </c>
+      <c r="E93" s="34" t="n"/>
       <c r="F93" s="138" t="n"/>
-      <c r="G93" s="101" t="n"/>
+      <c r="G93" s="107" t="n"/>
       <c r="H93" s="102" t="n"/>
       <c r="I93" s="102" t="n"/>
       <c r="J93" s="102" t="n"/>
@@ -5101,19 +5103,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C94" s="32" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D94" s="33" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
-        </is>
-      </c>
-      <c r="E94" s="34" t="n"/>
+      <c r="C94" s="31" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="n"/>
       <c r="F94" s="138" t="n"/>
-      <c r="G94" s="107" t="n"/>
+      <c r="G94" s="101" t="n"/>
       <c r="H94" s="102" t="n"/>
       <c r="I94" s="102" t="n"/>
       <c r="J94" s="102" t="n"/>
@@ -5125,23 +5127,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C95" s="31" t="inlineStr">
-        <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F95" s="139" t="n"/>
-      <c r="G95" s="101" t="n"/>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D95" s="33" t="inlineStr">
+        <is>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
+        </is>
+      </c>
+      <c r="E95" s="34" t="n"/>
+      <c r="F95" s="138" t="n"/>
+      <c r="G95" s="107" t="n"/>
       <c r="H95" s="102" t="n"/>
       <c r="I95" s="102" t="n"/>
       <c r="J95" s="102" t="n"/>
@@ -5153,19 +5151,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C96" s="90" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D96" s="94" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E96" s="34" t="n"/>
-      <c r="F96" s="138" t="n"/>
-      <c r="G96" s="125" t="n"/>
+      <c r="C96" s="31" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F96" s="139" t="n"/>
+      <c r="G96" s="101" t="n"/>
       <c r="H96" s="102" t="n"/>
       <c r="I96" s="102" t="n"/>
       <c r="J96" s="102" t="n"/>
@@ -5179,17 +5181,17 @@
       </c>
       <c r="C97" s="90" t="inlineStr">
         <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D97" s="91" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="n"/>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D97" s="94" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
+        </is>
+      </c>
+      <c r="E97" s="34" t="n"/>
       <c r="F97" s="138" t="n"/>
-      <c r="G97" s="101" t="n"/>
+      <c r="G97" s="125" t="n"/>
       <c r="H97" s="102" t="n"/>
       <c r="I97" s="102" t="n"/>
       <c r="J97" s="102" t="n"/>
@@ -5201,19 +5203,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C98" s="32" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D98" s="33" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E98" s="34" t="n"/>
+      <c r="C98" s="90" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D98" s="91" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="n"/>
       <c r="F98" s="138" t="n"/>
-      <c r="G98" s="107" t="n"/>
+      <c r="G98" s="101" t="n"/>
       <c r="H98" s="102" t="n"/>
       <c r="I98" s="102" t="n"/>
       <c r="J98" s="102" t="n"/>
@@ -5225,19 +5227,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C99" s="31" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="n"/>
+      <c r="C99" s="32" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="D99" s="33" t="inlineStr">
+        <is>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+        </is>
+      </c>
+      <c r="E99" s="34" t="n"/>
       <c r="F99" s="138" t="n"/>
-      <c r="G99" s="101" t="n"/>
+      <c r="G99" s="107" t="n"/>
       <c r="H99" s="102" t="n"/>
       <c r="I99" s="102" t="n"/>
       <c r="J99" s="102" t="n"/>
@@ -5249,19 +5251,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C100" s="32" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D100" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +20% if you scored last round.</t>
-        </is>
-      </c>
-      <c r="E100" s="34" t="n"/>
+      <c r="C100" s="31" t="inlineStr">
+        <is>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="n"/>
       <c r="F100" s="138" t="n"/>
-      <c r="G100" s="107" t="n"/>
+      <c r="G100" s="101" t="n"/>
       <c r="H100" s="102" t="n"/>
       <c r="I100" s="102" t="n"/>
       <c r="J100" s="102" t="n"/>
@@ -5273,19 +5275,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C101" s="31" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D101" s="91" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="n"/>
+      <c r="C101" s="32" t="inlineStr">
+        <is>
+          <t>Hot Hand</t>
+        </is>
+      </c>
+      <c r="D101" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +20% if you scored last round.</t>
+        </is>
+      </c>
+      <c r="E101" s="34" t="n"/>
       <c r="F101" s="138" t="n"/>
-      <c r="G101" s="101" t="n"/>
+      <c r="G101" s="107" t="n"/>
       <c r="H101" s="102" t="n"/>
       <c r="I101" s="102" t="n"/>
       <c r="J101" s="102" t="n"/>
@@ -5297,23 +5299,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C102" s="32" t="inlineStr">
-        <is>
-          <t>No Bag</t>
-        </is>
-      </c>
-      <c r="D102" s="33" t="inlineStr">
-        <is>
-          <t>Cannot activate Move cards this round</t>
-        </is>
-      </c>
-      <c r="E102" s="34" t="n"/>
+      <c r="C102" s="31" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D102" s="91" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="n"/>
       <c r="F102" s="138" t="n"/>
-      <c r="G102" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G102" s="101" t="n"/>
       <c r="H102" s="102" t="n"/>
       <c r="I102" s="102" t="n"/>
       <c r="J102" s="102" t="n"/>
@@ -5325,19 +5323,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C103" s="31" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="n"/>
+      <c r="C103" s="32" t="inlineStr">
+        <is>
+          <t>No Bag</t>
+        </is>
+      </c>
+      <c r="D103" s="33" t="inlineStr">
+        <is>
+          <t>Cannot activate Move cards this round</t>
+        </is>
+      </c>
+      <c r="E103" s="34" t="n"/>
       <c r="F103" s="138" t="n"/>
-      <c r="G103" s="101" t="n"/>
+      <c r="G103" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H103" s="102" t="n"/>
       <c r="I103" s="102" t="n"/>
       <c r="J103" s="102" t="n"/>
@@ -5349,23 +5351,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C104" s="32" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D104" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
-        </is>
-      </c>
-      <c r="E104" s="34" t="n"/>
+      <c r="C104" s="31" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="n"/>
       <c r="F104" s="138" t="n"/>
-      <c r="G104" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G104" s="101" t="n"/>
       <c r="H104" s="102" t="n"/>
       <c r="I104" s="102" t="n"/>
       <c r="J104" s="102" t="n"/>
@@ -5377,19 +5375,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C105" s="31" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="n"/>
+      <c r="C105" s="32" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D105" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E105" s="34" t="n"/>
       <c r="F105" s="138" t="n"/>
-      <c r="G105" s="101" t="n"/>
+      <c r="G105" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H105" s="102" t="n"/>
       <c r="I105" s="102" t="n"/>
       <c r="J105" s="102" t="n"/>
@@ -5401,19 +5403,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C106" s="32" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D106" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
-        </is>
-      </c>
-      <c r="E106" s="34" t="n"/>
+      <c r="C106" s="31" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="n"/>
       <c r="F106" s="138" t="n"/>
-      <c r="G106" s="107" t="n"/>
+      <c r="G106" s="101" t="n"/>
       <c r="H106" s="102" t="n"/>
       <c r="I106" s="102" t="n"/>
       <c r="J106" s="102" t="n"/>
@@ -5425,19 +5427,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C107" s="31" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="n"/>
+      <c r="C107" s="32" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D107" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E107" s="34" t="n"/>
       <c r="F107" s="138" t="n"/>
-      <c r="G107" s="101" t="n"/>
+      <c r="G107" s="107" t="n"/>
       <c r="H107" s="102" t="n"/>
       <c r="I107" s="102" t="n"/>
       <c r="J107" s="102" t="n"/>
@@ -5449,19 +5451,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C108" s="32" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D108" s="33" t="inlineStr">
-        <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E108" s="34" t="n"/>
+      <c r="C108" s="31" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="n"/>
       <c r="F108" s="138" t="n"/>
-      <c r="G108" s="107" t="n"/>
+      <c r="G108" s="101" t="n"/>
       <c r="H108" s="102" t="n"/>
       <c r="I108" s="102" t="n"/>
       <c r="J108" s="102" t="n"/>
@@ -5473,19 +5475,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C109" s="31" t="inlineStr">
-        <is>
-          <t>Unguardable</t>
-        </is>
-      </c>
-      <c r="D109" s="91" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="n"/>
+      <c r="C109" s="32" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D109" s="33" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E109" s="34" t="n"/>
       <c r="F109" s="138" t="n"/>
-      <c r="G109" s="101" t="n"/>
+      <c r="G109" s="107" t="n"/>
       <c r="H109" s="102" t="n"/>
       <c r="I109" s="102" t="n"/>
       <c r="J109" s="102" t="n"/>
@@ -5497,50 +5499,50 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C110" s="32" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D110" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
-        </is>
-      </c>
-      <c r="E110" s="34" t="n"/>
+      <c r="C110" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D110" s="91" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="n"/>
       <c r="F110" s="138" t="n"/>
-      <c r="G110" s="113" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G110" s="101" t="n"/>
       <c r="H110" s="102" t="n"/>
       <c r="I110" s="102" t="n"/>
       <c r="J110" s="102" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="61" t="n"/>
-      <c r="B111" s="62" t="inlineStr">
+      <c r="A111" s="29" t="n"/>
+      <c r="B111" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C111" s="66" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D111" s="95" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E111" s="68" t="n"/>
-      <c r="F111" s="140" t="n"/>
-      <c r="G111" s="126" t="n"/>
-      <c r="H111" s="117" t="n"/>
-      <c r="I111" s="117" t="n"/>
-      <c r="J111" s="117" t="n"/>
+      <c r="C111" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D111" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E111" s="34" t="n"/>
+      <c r="F111" s="138" t="n"/>
+      <c r="G111" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H111" s="102" t="n"/>
+      <c r="I111" s="102" t="n"/>
+      <c r="J111" s="102" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="61" t="n"/>
@@ -5551,12 +5553,12 @@
       </c>
       <c r="C112" s="66" t="inlineStr">
         <is>
-          <t>Unselfish</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D112" s="95" t="inlineStr">
         <is>
-          <t>Draw 1 card whenever you pass the ball at 50% SHOT or higher</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E112" s="68" t="n"/>
@@ -5575,12 +5577,12 @@
       </c>
       <c r="C113" s="66" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D113" s="95" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E113" s="68" t="n"/>
@@ -5599,21 +5601,20 @@
       </c>
       <c r="C114" s="66" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D114" s="95" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E114" s="68" t="n"/>
       <c r="F114" s="140" t="n"/>
-      <c r="G114" s="126" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="G114" s="126" t="n"/>
+      <c r="H114" s="117" t="n"/>
+      <c r="I114" s="117" t="n"/>
+      <c r="J114" s="117" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="61" t="n"/>
@@ -5624,19 +5625,19 @@
       </c>
       <c r="C115" s="66" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Villainous Reputation</t>
         </is>
       </c>
       <c r="D115" s="95" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>Discard 1 whenever any Whistle triggers</t>
         </is>
       </c>
       <c r="E115" s="68" t="n"/>
       <c r="F115" s="140" t="n"/>
       <c r="G115" s="126" t="inlineStr">
         <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
         </is>
       </c>
     </row>
@@ -5649,23 +5650,48 @@
       </c>
       <c r="C116" s="66" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Free Agent</t>
         </is>
       </c>
       <c r="D116" s="95" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
       <c r="E116" s="68" t="n"/>
       <c r="F116" s="140" t="n"/>
-      <c r="G116" s="126" t="n"/>
-      <c r="H116" s="117" t="n"/>
-      <c r="I116" s="117" t="n"/>
-      <c r="J116" s="117" t="n"/>
+      <c r="G116" s="126" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="61" t="n"/>
+      <c r="B117" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C117" s="66" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D117" s="95" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E117" s="68" t="n"/>
+      <c r="F117" s="140" t="n"/>
+      <c r="G117" s="126" t="n"/>
+      <c r="H117" s="117" t="n"/>
+      <c r="I117" s="117" t="n"/>
+      <c r="J117" s="117" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="103">
+  <mergeCells count="104">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G109:J109"/>
@@ -5690,12 +5716,12 @@
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="G108:J108"/>
     <mergeCell ref="G58:J58"/>
+    <mergeCell ref="G114:J114"/>
     <mergeCell ref="G110:J110"/>
-    <mergeCell ref="G113:J113"/>
     <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G91:J91"/>
     <mergeCell ref="G29:J29"/>
     <mergeCell ref="G85:J85"/>
+    <mergeCell ref="G91:J91"/>
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G94:J94"/>
     <mergeCell ref="G75:J75"/>
@@ -5732,10 +5758,11 @@
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G117:J117"/>
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="G101:J101"/>
-    <mergeCell ref="G116:J116"/>
     <mergeCell ref="G103:J103"/>
+    <mergeCell ref="G113:J113"/>
     <mergeCell ref="G37:J37"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G13:J13"/>
@@ -5758,14 +5785,14 @@
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
+    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G6:J6"/>
     <mergeCell ref="G93:J93"/>
-    <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G92:J92"/>
     <mergeCell ref="G30:J30"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2626,35 +2626,35 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$117,"Pass")</f>
+        <f>COUNTIF($B$5:$B$118,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$117,"Move")+COUNTIF($B$5:$B$117,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$118,"Move")+COUNTIF($B$5:$B$118,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$117,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$118,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$117,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$118,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$117,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$118,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$117,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$118,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$117,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$118,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$117,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$118,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$117,"Pass")</f>
+        <f>COUNTIF($B$5:$B$118,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="23" t="n"/>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="B15" s="40">
-        <f>COUNTIF($B$5:$B$117,"Move")+COUNTIF($B$5:$B$117,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$118,"Move")+COUNTIF($B$5:$B$118,"Special Move")</f>
         <v/>
       </c>
       <c r="C15" s="41" t="n"/>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="B28" s="43">
-        <f>COUNTIF($B$5:$B$117,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$118,"Special Move")</f>
         <v/>
       </c>
       <c r="C28" s="44" t="n"/>
@@ -3713,53 +3713,57 @@
       <c r="J40" s="104" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="132">
-      <c r="A41" s="58" t="inlineStr">
+      <c r="A41" s="61" t="n"/>
+      <c r="B41" s="62" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C41" s="66" t="inlineStr">
+        <is>
+          <t>Wide-Open Three</t>
+        </is>
+      </c>
+      <c r="D41" s="67" t="inlineStr">
+        <is>
+          <t>Select any number of other players. SHOT +10% for each</t>
+        </is>
+      </c>
+      <c r="E41" s="68" t="inlineStr">
+        <is>
+          <t>Shoot the ball. +1 Point on make. Selected players receive +1 AST on a make</t>
+        </is>
+      </c>
+      <c r="F41" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="122" t="inlineStr">
+        <is>
+          <t>Selecting none rolls off current SHOT and is still a three</t>
+        </is>
+      </c>
+      <c r="H41" s="104" t="n"/>
+      <c r="I41" s="104" t="n"/>
+      <c r="J41" s="104" t="n"/>
+    </row>
+    <row r="42" ht="28" customHeight="1" s="132">
+      <c r="A42" s="58" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B41" s="59">
-        <f>COUNTIF($B$5:$B$117,"Clamp")</f>
+      <c r="B42" s="59">
+        <f>COUNTIF($B$5:$B$118,"Clamp")</f>
         <v/>
       </c>
-      <c r="C41" s="60" t="n"/>
-      <c r="D41" s="60" t="n"/>
-      <c r="E41" s="60" t="n"/>
-      <c r="F41" s="86" t="n"/>
-      <c r="G41" s="109" t="n"/>
-      <c r="H41" s="110" t="n"/>
-      <c r="I41" s="110" t="n"/>
-      <c r="J41" s="110" t="n"/>
-    </row>
-    <row r="42" ht="28" customHeight="1" s="132">
-      <c r="A42" s="29" t="n"/>
-      <c r="B42" s="30" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C42" s="31" t="inlineStr">
-        <is>
-          <t>Contest</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Next player SHOT -25% if they shoot</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G42" s="130" t="inlineStr">
-        <is>
-          <t>1 def</t>
-        </is>
-      </c>
-      <c r="H42" s="102" t="n"/>
-      <c r="I42" s="102" t="n"/>
-      <c r="J42" s="102" t="n"/>
+      <c r="C42" s="60" t="n"/>
+      <c r="D42" s="60" t="n"/>
+      <c r="E42" s="60" t="n"/>
+      <c r="F42" s="86" t="n"/>
+      <c r="G42" s="109" t="n"/>
+      <c r="H42" s="110" t="n"/>
+      <c r="I42" s="110" t="n"/>
+      <c r="J42" s="110" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1" s="132">
       <c r="A43" s="29" t="n"/>
@@ -3768,23 +3772,23 @@
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C43" s="32" t="inlineStr">
-        <is>
-          <t>Double-Team</t>
-        </is>
-      </c>
-      <c r="D43" s="33" t="inlineStr">
-        <is>
-          <t>Next Player cannot play 2 random cards from hand.</t>
-        </is>
-      </c>
-      <c r="E43" s="34" t="n"/>
-      <c r="F43" s="75" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" s="125" t="inlineStr">
-        <is>
-          <t>2 def</t>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>Contest</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Next player SHOT -25% if they shoot</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="130" t="inlineStr">
+        <is>
+          <t>1 def</t>
         </is>
       </c>
       <c r="H43" s="102" t="n"/>
@@ -3798,23 +3802,23 @@
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C44" s="31" t="inlineStr">
-        <is>
-          <t>Full-Court Press</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Next player discards 2 cards at the start of their turn</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G44" s="130" t="inlineStr">
-        <is>
-          <t>1 def</t>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>Double-Team</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>Next Player cannot play 2 random cards from hand.</t>
+        </is>
+      </c>
+      <c r="E44" s="34" t="n"/>
+      <c r="F44" s="75" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" s="125" t="inlineStr">
+        <is>
+          <t>2 def</t>
         </is>
       </c>
       <c r="H44" s="102" t="n"/>
@@ -3828,23 +3832,23 @@
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C45" s="32" t="inlineStr">
-        <is>
-          <t>Trap</t>
-        </is>
-      </c>
-      <c r="D45" s="94" t="inlineStr">
-        <is>
-          <t>Next player can only play Pass cards during their turn</t>
-        </is>
-      </c>
-      <c r="E45" s="34" t="n"/>
-      <c r="F45" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G45" s="125" t="inlineStr">
-        <is>
-          <t>They can still shoot as another option; 3 def</t>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Full-Court Press</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Next player discards 2 cards at the start of their turn</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="130" t="inlineStr">
+        <is>
+          <t>1 def</t>
         </is>
       </c>
       <c r="H45" s="102" t="n"/>
@@ -3852,106 +3856,112 @@
       <c r="J45" s="102" t="n"/>
     </row>
     <row r="46" ht="29" customHeight="1" s="132" thickBot="1">
-      <c r="A46" s="61" t="n"/>
-      <c r="B46" s="62" t="inlineStr">
+      <c r="A46" s="29" t="n"/>
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C46" s="66" t="inlineStr">
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>Trap</t>
+        </is>
+      </c>
+      <c r="D46" s="94" t="inlineStr">
+        <is>
+          <t>Next player can only play Pass cards during their turn</t>
+        </is>
+      </c>
+      <c r="E46" s="34" t="n"/>
+      <c r="F46" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" s="125" t="inlineStr">
+        <is>
+          <t>They can still shoot as another option; 3 def</t>
+        </is>
+      </c>
+      <c r="H46" s="102" t="n"/>
+      <c r="I46" s="102" t="n"/>
+      <c r="J46" s="102" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1" s="132">
+      <c r="A47" s="61" t="n"/>
+      <c r="B47" s="62" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C47" s="66" t="inlineStr">
         <is>
           <t>Triple-Team</t>
         </is>
       </c>
-      <c r="D46" s="67" t="inlineStr">
+      <c r="D47" s="67" t="inlineStr">
         <is>
           <t>Next player cannot play 3 random cards from hand.</t>
         </is>
       </c>
-      <c r="E46" s="68" t="n"/>
-      <c r="F46" s="85" t="n">
+      <c r="E47" s="68" t="n"/>
+      <c r="F47" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="G46" s="135" t="inlineStr">
+      <c r="G47" s="135" t="inlineStr">
         <is>
           <t>3 def</t>
         </is>
       </c>
-      <c r="H46" s="117" t="n"/>
-      <c r="I46" s="117" t="n"/>
-      <c r="J46" s="117" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1" s="132">
-      <c r="A47" s="58" t="inlineStr">
+      <c r="H47" s="117" t="n"/>
+      <c r="I47" s="117" t="n"/>
+      <c r="J47" s="117" t="n"/>
+    </row>
+    <row r="48" ht="56" customHeight="1" s="132">
+      <c r="A48" s="58" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="B47" s="59">
-        <f>COUNTIF($B$5:$B$117,"Whistle")</f>
+      <c r="B48" s="59">
+        <f>COUNTIF($B$5:$B$118,"Whistle")</f>
         <v/>
       </c>
-      <c r="C47" s="60" t="n"/>
-      <c r="D47" s="60" t="n"/>
-      <c r="E47" s="60" t="n"/>
-      <c r="F47" s="86" t="n"/>
-      <c r="G47" s="109" t="n"/>
-      <c r="H47" s="110" t="n"/>
-      <c r="I47" s="110" t="n"/>
-      <c r="J47" s="110" t="n"/>
-    </row>
-    <row r="48" ht="56" customHeight="1" s="132">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="C48" s="60" t="n"/>
+      <c r="D48" s="60" t="n"/>
+      <c r="E48" s="60" t="n"/>
+      <c r="F48" s="86" t="n"/>
+      <c r="G48" s="109" t="n"/>
+      <c r="H48" s="110" t="n"/>
+      <c r="I48" s="110" t="n"/>
+      <c r="J48" s="110" t="n"/>
+    </row>
+    <row r="49" ht="47" customHeight="1" s="132">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t>All whistles are limited to 1</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B49" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C48" s="31" t="inlineStr">
+      <c r="C49" s="31" t="inlineStr">
         <is>
           <t>Back Court Violation</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
         </is>
       </c>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="138" t="n"/>
-      <c r="G48" s="101" t="inlineStr">
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="138" t="n"/>
+      <c r="G49" s="101" t="inlineStr">
         <is>
           <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
         </is>
       </c>
-      <c r="H48" s="102" t="n"/>
-      <c r="I48" s="102" t="n"/>
-      <c r="J48" s="102" t="n"/>
-    </row>
-    <row r="49" ht="47" customHeight="1" s="132">
-      <c r="A49" s="29" t="n"/>
-      <c r="B49" s="30" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C49" s="90" t="inlineStr">
-        <is>
-          <t>Blocking Foul</t>
-        </is>
-      </c>
-      <c r="D49" s="93" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
-        </is>
-      </c>
-      <c r="E49" s="34" t="n"/>
-      <c r="F49" s="138" t="n"/>
-      <c r="G49" s="107" t="n"/>
       <c r="H49" s="102" t="n"/>
       <c r="I49" s="102" t="n"/>
       <c r="J49" s="102" t="n"/>
@@ -3963,19 +3973,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C50" s="31" t="inlineStr">
-        <is>
-          <t>Charge</t>
-        </is>
-      </c>
-      <c r="D50" s="92" t="inlineStr">
-        <is>
-          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="n"/>
+      <c r="C50" s="90" t="inlineStr">
+        <is>
+          <t>Blocking Foul</t>
+        </is>
+      </c>
+      <c r="D50" s="93" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
+        </is>
+      </c>
+      <c r="E50" s="34" t="n"/>
       <c r="F50" s="138" t="n"/>
-      <c r="G50" s="101" t="n"/>
+      <c r="G50" s="107" t="n"/>
       <c r="H50" s="102" t="n"/>
       <c r="I50" s="102" t="n"/>
       <c r="J50" s="102" t="n"/>
@@ -3987,19 +3997,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>Cleared to Play</t>
-        </is>
-      </c>
-      <c r="D51" s="33" t="inlineStr">
-        <is>
-          <t>Injury Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E51" s="34" t="n"/>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="D51" s="92" t="inlineStr">
+        <is>
+          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="n"/>
       <c r="F51" s="138" t="n"/>
-      <c r="G51" s="107" t="n"/>
+      <c r="G51" s="101" t="n"/>
       <c r="H51" s="102" t="n"/>
       <c r="I51" s="102" t="n"/>
       <c r="J51" s="102" t="n"/>
@@ -4011,23 +4021,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C52" s="31" t="inlineStr">
-        <is>
-          <t>Coach’s Challenge</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Any Whistle Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>Pull a Timeout from the discards, if one is there, and take it</t>
-        </is>
-      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>Cleared to Play</t>
+        </is>
+      </c>
+      <c r="D52" s="33" t="inlineStr">
+        <is>
+          <t>Injury Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E52" s="34" t="n"/>
       <c r="F52" s="138" t="n"/>
-      <c r="G52" s="101" t="n"/>
+      <c r="G52" s="107" t="n"/>
       <c r="H52" s="102" t="n"/>
       <c r="I52" s="102" t="n"/>
       <c r="J52" s="102" t="n"/>
@@ -4039,27 +4045,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C53" s="90" t="inlineStr">
-        <is>
-          <t>Delay-of-Game Warning</t>
-        </is>
-      </c>
-      <c r="D53" s="94" t="inlineStr">
-        <is>
-          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
-        </is>
-      </c>
-      <c r="E53" s="33" t="inlineStr">
-        <is>
-          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
-        </is>
-      </c>
-      <c r="F53" s="139" t="n"/>
-      <c r="G53" s="113" t="inlineStr">
-        <is>
-          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
-        </is>
-      </c>
+      <c r="C53" s="31" t="inlineStr">
+        <is>
+          <t>Coach’s Challenge</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Any Whistle Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Pull a Timeout from the discards, if one is there, and take it</t>
+        </is>
+      </c>
+      <c r="F53" s="138" t="n"/>
+      <c r="G53" s="101" t="n"/>
       <c r="H53" s="102" t="n"/>
       <c r="I53" s="102" t="n"/>
       <c r="J53" s="102" t="n"/>
@@ -4071,21 +4073,25 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C54" s="31" t="inlineStr">
-        <is>
-          <t>Double Dribble</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="138" t="n"/>
-      <c r="G54" s="101" t="inlineStr">
-        <is>
-          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+      <c r="C54" s="90" t="inlineStr">
+        <is>
+          <t>Delay-of-Game Warning</t>
+        </is>
+      </c>
+      <c r="D54" s="94" t="inlineStr">
+        <is>
+          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
+        </is>
+      </c>
+      <c r="E54" s="33" t="inlineStr">
+        <is>
+          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
+        </is>
+      </c>
+      <c r="F54" s="139" t="n"/>
+      <c r="G54" s="113" t="inlineStr">
+        <is>
+          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
         </is>
       </c>
       <c r="H54" s="102" t="n"/>
@@ -4099,19 +4105,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C55" s="90" t="inlineStr">
-        <is>
-          <t>Flagrant Foul</t>
-        </is>
-      </c>
-      <c r="D55" s="94" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E55" s="34" t="n"/>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>Double Dribble</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="n"/>
       <c r="F55" s="138" t="n"/>
-      <c r="G55" s="107" t="n"/>
+      <c r="G55" s="101" t="inlineStr">
+        <is>
+          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+        </is>
+      </c>
       <c r="H55" s="102" t="n"/>
       <c r="I55" s="102" t="n"/>
       <c r="J55" s="102" t="n"/>
@@ -4125,17 +4135,17 @@
       </c>
       <c r="C56" s="90" t="inlineStr">
         <is>
-          <t>Flagrant Foul II</t>
-        </is>
-      </c>
-      <c r="D56" s="91" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="n"/>
+          <t>Flagrant Foul</t>
+        </is>
+      </c>
+      <c r="D56" s="94" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
+        </is>
+      </c>
+      <c r="E56" s="34" t="n"/>
       <c r="F56" s="138" t="n"/>
-      <c r="G56" s="101" t="n"/>
+      <c r="G56" s="107" t="n"/>
       <c r="H56" s="102" t="n"/>
       <c r="I56" s="102" t="n"/>
       <c r="J56" s="102" t="n"/>
@@ -4147,19 +4157,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C57" s="32" t="inlineStr">
-        <is>
-          <t>Goaltending</t>
-        </is>
-      </c>
-      <c r="D57" s="33" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
-        </is>
-      </c>
-      <c r="E57" s="34" t="n"/>
+      <c r="C57" s="90" t="inlineStr">
+        <is>
+          <t>Flagrant Foul II</t>
+        </is>
+      </c>
+      <c r="D57" s="91" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="n"/>
       <c r="F57" s="138" t="n"/>
-      <c r="G57" s="107" t="n"/>
+      <c r="G57" s="101" t="n"/>
       <c r="H57" s="102" t="n"/>
       <c r="I57" s="102" t="n"/>
       <c r="J57" s="102" t="n"/>
@@ -4171,19 +4181,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C58" s="31" t="inlineStr">
-        <is>
-          <t>Inadvertent Whistle</t>
-        </is>
-      </c>
-      <c r="D58" s="91" t="inlineStr">
-        <is>
-          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="n"/>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>Goaltending</t>
+        </is>
+      </c>
+      <c r="D58" s="33" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
+        </is>
+      </c>
+      <c r="E58" s="34" t="n"/>
       <c r="F58" s="138" t="n"/>
-      <c r="G58" s="101" t="n"/>
+      <c r="G58" s="107" t="n"/>
       <c r="H58" s="102" t="n"/>
       <c r="I58" s="102" t="n"/>
       <c r="J58" s="102" t="n"/>
@@ -4195,19 +4205,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C59" s="32" t="inlineStr">
-        <is>
-          <t>Official Review</t>
-        </is>
-      </c>
-      <c r="D59" s="94" t="inlineStr">
-        <is>
-          <t>Intangible Played: Discard all Intangibles from player.</t>
-        </is>
-      </c>
-      <c r="E59" s="34" t="n"/>
+      <c r="C59" s="31" t="inlineStr">
+        <is>
+          <t>Inadvertent Whistle</t>
+        </is>
+      </c>
+      <c r="D59" s="91" t="inlineStr">
+        <is>
+          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="n"/>
       <c r="F59" s="138" t="n"/>
-      <c r="G59" s="107" t="n"/>
+      <c r="G59" s="101" t="n"/>
       <c r="H59" s="102" t="n"/>
       <c r="I59" s="102" t="n"/>
       <c r="J59" s="102" t="n"/>
@@ -4219,23 +4229,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C60" s="31" t="inlineStr">
-        <is>
-          <t>Shot Clock Violation</t>
-        </is>
-      </c>
-      <c r="D60" s="91" t="inlineStr">
-        <is>
-          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="n"/>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>Official Review</t>
+        </is>
+      </c>
+      <c r="D60" s="94" t="inlineStr">
+        <is>
+          <t>Intangible Played: Discard all Intangibles from player.</t>
+        </is>
+      </c>
+      <c r="E60" s="34" t="n"/>
       <c r="F60" s="138" t="n"/>
-      <c r="G60" s="101" t="inlineStr">
-        <is>
-          <t>This inbound does NOT increment the round.</t>
-        </is>
-      </c>
+      <c r="G60" s="107" t="n"/>
       <c r="H60" s="102" t="n"/>
       <c r="I60" s="102" t="n"/>
       <c r="J60" s="102" t="n"/>
@@ -4247,19 +4253,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t>Technical Foul</t>
-        </is>
-      </c>
-      <c r="D61" s="94" t="inlineStr">
-        <is>
-          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E61" s="34" t="n"/>
+      <c r="C61" s="31" t="inlineStr">
+        <is>
+          <t>Shot Clock Violation</t>
+        </is>
+      </c>
+      <c r="D61" s="91" t="inlineStr">
+        <is>
+          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="n"/>
       <c r="F61" s="138" t="n"/>
-      <c r="G61" s="107" t="n"/>
+      <c r="G61" s="101" t="inlineStr">
+        <is>
+          <t>This inbound does NOT increment the round.</t>
+        </is>
+      </c>
       <c r="H61" s="102" t="n"/>
       <c r="I61" s="102" t="n"/>
       <c r="J61" s="102" t="n"/>
@@ -4271,46 +4281,46 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C62" s="31" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
-      <c r="D62" s="91" t="inlineStr">
-        <is>
-          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="n"/>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>Technical Foul</t>
+        </is>
+      </c>
+      <c r="D62" s="94" t="inlineStr">
+        <is>
+          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E62" s="34" t="n"/>
       <c r="F62" s="138" t="n"/>
-      <c r="G62" s="101" t="n"/>
+      <c r="G62" s="107" t="n"/>
       <c r="H62" s="102" t="n"/>
       <c r="I62" s="102" t="n"/>
       <c r="J62" s="102" t="n"/>
     </row>
     <row r="63" ht="29" customHeight="1" s="132" thickBot="1">
-      <c r="A63" s="61" t="n"/>
-      <c r="B63" s="62" t="inlineStr">
+      <c r="A63" s="29" t="n"/>
+      <c r="B63" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C63" s="63" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D63" s="64" t="inlineStr">
-        <is>
-          <t>Move card played: Cancel card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E63" s="65" t="n"/>
-      <c r="F63" s="140" t="n"/>
-      <c r="G63" s="116" t="n"/>
-      <c r="H63" s="117" t="n"/>
-      <c r="I63" s="117" t="n"/>
-      <c r="J63" s="117" t="n"/>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D63" s="91" t="inlineStr">
+        <is>
+          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="138" t="n"/>
+      <c r="G63" s="101" t="n"/>
+      <c r="H63" s="102" t="n"/>
+      <c r="I63" s="102" t="n"/>
+      <c r="J63" s="102" t="n"/>
     </row>
     <row r="64" ht="20" customHeight="1" s="132">
       <c r="A64" s="61" t="n"/>
@@ -4321,69 +4331,67 @@
       </c>
       <c r="C64" s="63" t="inlineStr">
         <is>
-          <t>Clear Path Foul</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D64" s="64" t="inlineStr">
         <is>
-          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
+          <t>Move card played: Cancel card. TOV +1</t>
         </is>
       </c>
       <c r="E64" s="65" t="n"/>
       <c r="F64" s="140" t="n"/>
-      <c r="G64" s="116" t="inlineStr">
-        <is>
-          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
-        </is>
-      </c>
+      <c r="G64" s="116" t="n"/>
       <c r="H64" s="117" t="n"/>
       <c r="I64" s="117" t="n"/>
       <c r="J64" s="117" t="n"/>
     </row>
     <row r="65" ht="28" customHeight="1" s="132">
-      <c r="A65" s="58" t="inlineStr">
+      <c r="A65" s="61" t="n"/>
+      <c r="B65" s="62" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C65" s="63" t="inlineStr">
+        <is>
+          <t>Clear Path Foul</t>
+        </is>
+      </c>
+      <c r="D65" s="64" t="inlineStr">
+        <is>
+          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E65" s="65" t="n"/>
+      <c r="F65" s="140" t="n"/>
+      <c r="G65" s="116" t="inlineStr">
+        <is>
+          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
+        </is>
+      </c>
+      <c r="H65" s="117" t="n"/>
+      <c r="I65" s="117" t="n"/>
+      <c r="J65" s="117" t="n"/>
+    </row>
+    <row r="66" ht="28" customHeight="1" s="132">
+      <c r="A66" s="58" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B65" s="59">
-        <f>COUNTIF($B$5:$B$117,"Game Break")</f>
+      <c r="B66" s="59">
+        <f>COUNTIF($B$5:$B$118,"Game Break")</f>
         <v/>
       </c>
-      <c r="C65" s="60" t="n"/>
-      <c r="D65" s="60" t="n"/>
-      <c r="E65" s="60" t="n"/>
-      <c r="F65" s="86" t="n"/>
-      <c r="G65" s="109" t="n"/>
-      <c r="H65" s="110" t="n"/>
-      <c r="I65" s="110" t="n"/>
-      <c r="J65" s="110" t="n"/>
-    </row>
-    <row r="66" ht="28" customHeight="1" s="132">
-      <c r="A66" s="29" t="n"/>
-      <c r="B66" s="30" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C66" s="32" t="inlineStr">
-        <is>
-          <t>2-Minute Warning</t>
-        </is>
-      </c>
-      <c r="D66" s="33" t="inlineStr">
-        <is>
-          <t>All players discard down to 2 or fewer cards</t>
-        </is>
-      </c>
-      <c r="E66" s="34" t="n"/>
-      <c r="F66" s="75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G66" s="107" t="n"/>
-      <c r="H66" s="102" t="n"/>
-      <c r="I66" s="102" t="n"/>
-      <c r="J66" s="102" t="n"/>
+      <c r="C66" s="60" t="n"/>
+      <c r="D66" s="60" t="n"/>
+      <c r="E66" s="60" t="n"/>
+      <c r="F66" s="86" t="n"/>
+      <c r="G66" s="109" t="n"/>
+      <c r="H66" s="110" t="n"/>
+      <c r="I66" s="110" t="n"/>
+      <c r="J66" s="110" t="n"/>
     </row>
     <row r="67" ht="14" customHeight="1" s="132">
       <c r="A67" s="29" t="n"/>
@@ -4392,25 +4400,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C67" s="31" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G67" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
+        </is>
+      </c>
+      <c r="D67" s="33" t="inlineStr">
+        <is>
+          <t>All players discard down to 2 or fewer cards</t>
+        </is>
+      </c>
+      <c r="E67" s="34" t="n"/>
+      <c r="F67" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="107" t="n"/>
       <c r="H67" s="102" t="n"/>
       <c r="I67" s="102" t="n"/>
       <c r="J67" s="102" t="n"/>
@@ -4422,21 +4426,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C68" s="32" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D68" s="33" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E68" s="34" t="n"/>
-      <c r="F68" s="75" t="n">
-        <v>14</v>
-      </c>
-      <c r="G68" s="107" t="n"/>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>Benched</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Immediately give ball to any other player.</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G68" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H68" s="102" t="n"/>
       <c r="I68" s="102" t="n"/>
       <c r="J68" s="102" t="n"/>
@@ -4448,21 +4456,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C69" s="31" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G69" s="101" t="n"/>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
+        </is>
+      </c>
+      <c r="D69" s="33" t="inlineStr">
+        <is>
+          <t>Discard 1 card.</t>
+        </is>
+      </c>
+      <c r="E69" s="34" t="n"/>
+      <c r="F69" s="75" t="n">
+        <v>14</v>
+      </c>
+      <c r="G69" s="107" t="n"/>
       <c r="H69" s="102" t="n"/>
       <c r="I69" s="102" t="n"/>
       <c r="J69" s="102" t="n"/>
@@ -4474,21 +4482,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C70" s="90" t="inlineStr">
-        <is>
-          <t>Foul</t>
-        </is>
-      </c>
-      <c r="D70" s="33" t="inlineStr">
-        <is>
-          <t>Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E70" s="34" t="n"/>
-      <c r="F70" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G70" s="107" t="n"/>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>Designed Play</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Draw up to a hand of 5</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G70" s="101" t="n"/>
       <c r="H70" s="102" t="n"/>
       <c r="I70" s="102" t="n"/>
       <c r="J70" s="102" t="n"/>
@@ -4500,21 +4508,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C71" s="31" t="inlineStr">
-        <is>
-          <t>MVP Vote</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards up to a hand of 7</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="n"/>
-      <c r="F71" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="101" t="n"/>
+      <c r="C71" s="90" t="inlineStr">
+        <is>
+          <t>Foul</t>
+        </is>
+      </c>
+      <c r="D71" s="33" t="inlineStr">
+        <is>
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E71" s="34" t="n"/>
+      <c r="F71" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" s="107" t="n"/>
       <c r="H71" s="102" t="n"/>
       <c r="I71" s="102" t="n"/>
       <c r="J71" s="102" t="n"/>
@@ -4526,21 +4534,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>Off Night</t>
-        </is>
-      </c>
-      <c r="D72" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this possession</t>
-        </is>
-      </c>
-      <c r="E72" s="34" t="n"/>
-      <c r="F72" s="75" t="n">
-        <v>3</v>
-      </c>
-      <c r="G72" s="107" t="n"/>
+      <c r="C72" s="31" t="inlineStr">
+        <is>
+          <t>MVP Vote</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Draw 3 cards up to a hand of 7</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="101" t="n"/>
       <c r="H72" s="102" t="n"/>
       <c r="I72" s="102" t="n"/>
       <c r="J72" s="102" t="n"/>
@@ -4552,25 +4560,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C73" s="31" t="inlineStr">
-        <is>
-          <t>Swallowed Whistle</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F73" s="74" t="n">
-        <v>5</v>
-      </c>
-      <c r="G73" s="101" t="n"/>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D73" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E73" s="34" t="n"/>
+      <c r="F73" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" s="107" t="n"/>
       <c r="H73" s="102" t="n"/>
       <c r="I73" s="102" t="n"/>
       <c r="J73" s="102" t="n"/>
@@ -4582,23 +4586,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
-        </is>
-      </c>
-      <c r="D74" s="33" t="inlineStr">
-        <is>
-          <t>Players cannot shoot when SHOT is 50% or higher</t>
-        </is>
-      </c>
-      <c r="E74" s="33" t="inlineStr">
+      <c r="C74" s="31" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>Remains for remainder of round</t>
         </is>
       </c>
-      <c r="F74" s="80" t="n"/>
-      <c r="G74" s="107" t="n"/>
+      <c r="F74" s="74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" s="101" t="n"/>
       <c r="H74" s="102" t="n"/>
       <c r="I74" s="102" t="n"/>
       <c r="J74" s="102" t="n"/>
@@ -4610,23 +4616,23 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C75" s="31" t="inlineStr">
-        <is>
-          <t>Traded Mid-Game</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>Swap positions with random other player</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="76" t="n"/>
-      <c r="G75" s="111" t="inlineStr">
-        <is>
-          <t>Applies to rest of game</t>
-        </is>
-      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D75" s="33" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is 50% or higher</t>
+        </is>
+      </c>
+      <c r="E75" s="33" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F75" s="80" t="n"/>
+      <c r="G75" s="107" t="n"/>
       <c r="H75" s="102" t="n"/>
       <c r="I75" s="102" t="n"/>
       <c r="J75" s="102" t="n"/>
@@ -4638,21 +4644,23 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C76" s="134" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D76" s="91" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
+      <c r="C76" s="31" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Swap positions with random other player</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G76" s="111" t="n"/>
+      <c r="F76" s="76" t="n"/>
+      <c r="G76" s="111" t="inlineStr">
+        <is>
+          <t>Applies to rest of game</t>
+        </is>
+      </c>
       <c r="H76" s="102" t="n"/>
       <c r="I76" s="102" t="n"/>
       <c r="J76" s="102" t="n"/>
@@ -4666,23 +4674,19 @@
       </c>
       <c r="C77" s="134" t="inlineStr">
         <is>
-          <t>All-Swissh Selection</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D77" s="91" t="inlineStr">
         <is>
-          <t>Draw 3 cards after your next make</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" s="111" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G77" s="111" t="n"/>
       <c r="H77" s="102" t="n"/>
       <c r="I77" s="102" t="n"/>
       <c r="J77" s="102" t="n"/>
@@ -4696,19 +4700,23 @@
       </c>
       <c r="C78" s="134" t="inlineStr">
         <is>
-          <t>All Star Selection</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D78" s="91" t="inlineStr">
         <is>
-          <t>Draw 2 cards</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E78" s="7" t="n"/>
       <c r="F78" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G78" s="111" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G78" s="111" t="inlineStr">
+        <is>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
+        </is>
+      </c>
       <c r="H78" s="102" t="n"/>
       <c r="I78" s="102" t="n"/>
       <c r="J78" s="102" t="n"/>
@@ -4722,23 +4730,19 @@
       </c>
       <c r="C79" s="134" t="inlineStr">
         <is>
-          <t>Hit the Bike</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D79" s="91" t="inlineStr">
         <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
       <c r="F79" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G79" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="G79" s="111" t="n"/>
       <c r="H79" s="102" t="n"/>
       <c r="I79" s="102" t="n"/>
       <c r="J79" s="102" t="n"/>
@@ -4752,19 +4756,23 @@
       </c>
       <c r="C80" s="134" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D80" s="91" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
       <c r="F80" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G80" s="111" t="n"/>
+      <c r="G80" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H80" s="102" t="n"/>
       <c r="I80" s="102" t="n"/>
       <c r="J80" s="102" t="n"/>
@@ -4778,23 +4786,19 @@
       </c>
       <c r="C81" s="134" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D81" s="91" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G81" s="111" t="inlineStr">
-        <is>
-          <t>Deck ones are shown face down</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G81" s="111" t="n"/>
       <c r="H81" s="102" t="n"/>
       <c r="I81" s="102" t="n"/>
       <c r="J81" s="102" t="n"/>
@@ -4808,21 +4812,21 @@
       </c>
       <c r="C82" s="134" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D82" s="91" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" s="111" t="inlineStr">
         <is>
-          <t>This is a bad thing in the NBA</t>
+          <t>Deck ones are shown face down</t>
         </is>
       </c>
       <c r="H82" s="102" t="n"/>
@@ -4838,12 +4842,12 @@
       </c>
       <c r="C83" s="134" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D83" s="91" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
@@ -4852,7 +4856,7 @@
       </c>
       <c r="G83" s="111" t="inlineStr">
         <is>
-          <t>The hex travels in the declared direction too</t>
+          <t>This is a bad thing in the NBA</t>
         </is>
       </c>
       <c r="H83" s="102" t="n"/>
@@ -4868,19 +4872,23 @@
       </c>
       <c r="C84" s="134" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D84" s="91" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G84" s="111" t="n"/>
+      <c r="G84" s="111" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H84" s="102" t="n"/>
       <c r="I84" s="102" t="n"/>
       <c r="J84" s="102" t="n"/>
@@ -4894,17 +4902,17 @@
       </c>
       <c r="C85" s="134" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D85" s="91" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G85" s="111" t="n"/>
       <c r="H85" s="102" t="n"/>
@@ -4920,17 +4928,17 @@
       </c>
       <c r="C86" s="134" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Official Timeout</t>
         </is>
       </c>
       <c r="D86" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G86" s="111" t="n"/>
       <c r="H86" s="102" t="n"/>
@@ -4938,160 +4946,162 @@
       <c r="J86" s="102" t="n"/>
     </row>
     <row r="87" ht="56" customHeight="1" s="132">
-      <c r="A87" s="55" t="inlineStr">
-        <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="B87" s="56">
-        <f>COUNTIF($B$5:$B$117,"Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C87" s="57" t="n"/>
-      <c r="D87" s="57" t="n"/>
-      <c r="E87" s="57" t="n"/>
-      <c r="F87" s="88" t="n"/>
-      <c r="G87" s="108" t="n"/>
+      <c r="A87" s="29" t="n"/>
+      <c r="B87" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C87" s="134" t="inlineStr">
+        <is>
+          <t>Team Doctor</t>
+        </is>
+      </c>
+      <c r="D87" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G87" s="111" t="n"/>
       <c r="H87" s="102" t="n"/>
       <c r="I87" s="102" t="n"/>
       <c r="J87" s="102" t="n"/>
     </row>
     <row r="88" ht="28" customHeight="1" s="132">
-      <c r="A88" s="29" t="n"/>
-      <c r="B88" s="30" t="inlineStr">
+      <c r="A88" s="55" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="C88" s="31" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
-        </is>
-      </c>
-      <c r="D88" s="91" t="inlineStr">
-        <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G88" s="101" t="n"/>
+      <c r="B88" s="56">
+        <f>COUNTIF($B$5:$B$118,"Injury GB")</f>
+        <v/>
+      </c>
+      <c r="C88" s="57" t="n"/>
+      <c r="D88" s="57" t="n"/>
+      <c r="E88" s="57" t="n"/>
+      <c r="F88" s="88" t="n"/>
+      <c r="G88" s="108" t="n"/>
       <c r="H88" s="102" t="n"/>
       <c r="I88" s="102" t="n"/>
       <c r="J88" s="102" t="n"/>
     </row>
     <row r="89" ht="42" customHeight="1" s="132">
-      <c r="A89" s="58" t="inlineStr">
+      <c r="A89" s="29" t="n"/>
+      <c r="B89" s="30" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="C89" s="31" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D89" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="n"/>
+      <c r="F89" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" s="101" t="n"/>
+      <c r="H89" s="102" t="n"/>
+      <c r="I89" s="102" t="n"/>
+      <c r="J89" s="102" t="n"/>
+    </row>
+    <row r="90" ht="28" customHeight="1" s="132">
+      <c r="A90" s="58" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="B89" s="59">
-        <f>COUNTIF($B$5:$B$117,"Devastating Injury GB")</f>
+      <c r="B90" s="59">
+        <f>COUNTIF($B$5:$B$118,"Devastating Injury GB")</f>
         <v/>
       </c>
-      <c r="C89" s="60" t="n"/>
-      <c r="D89" s="60" t="n"/>
-      <c r="E89" s="60" t="n"/>
-      <c r="F89" s="86" t="n"/>
-      <c r="G89" s="109" t="n"/>
-      <c r="H89" s="110" t="n"/>
-      <c r="I89" s="110" t="n"/>
-      <c r="J89" s="110" t="n"/>
-    </row>
-    <row r="90" ht="28" customHeight="1" s="132">
-      <c r="A90" s="50" t="n"/>
-      <c r="B90" s="51" t="inlineStr">
+      <c r="C90" s="60" t="n"/>
+      <c r="D90" s="60" t="n"/>
+      <c r="E90" s="60" t="n"/>
+      <c r="F90" s="86" t="n"/>
+      <c r="G90" s="109" t="n"/>
+      <c r="H90" s="110" t="n"/>
+      <c r="I90" s="110" t="n"/>
+      <c r="J90" s="110" t="n"/>
+    </row>
+    <row r="91" ht="42" customHeight="1" s="132">
+      <c r="A91" s="50" t="n"/>
+      <c r="B91" s="51" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="C90" s="136" t="inlineStr">
+      <c r="C91" s="136" t="inlineStr">
         <is>
           <t>Torn Achilles</t>
         </is>
       </c>
-      <c r="D90" s="137" t="inlineStr">
+      <c r="D91" s="137" t="inlineStr">
         <is>
           <t>Hand is locked every turn except 1 card (randomly)</t>
         </is>
       </c>
-      <c r="E90" s="54" t="n"/>
-      <c r="F90" s="141" t="n"/>
-      <c r="G90" s="114" t="n"/>
-      <c r="H90" s="115" t="n"/>
-      <c r="I90" s="115" t="n"/>
-      <c r="J90" s="115" t="n"/>
-    </row>
-    <row r="91" ht="42" customHeight="1" s="132">
-      <c r="A91" s="55" t="inlineStr">
+      <c r="E91" s="54" t="n"/>
+      <c r="F91" s="141" t="n"/>
+      <c r="G91" s="114" t="n"/>
+      <c r="H91" s="115" t="n"/>
+      <c r="I91" s="115" t="n"/>
+      <c r="J91" s="115" t="n"/>
+    </row>
+    <row r="92" ht="14" customHeight="1" s="132">
+      <c r="A92" s="55" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B91" s="56">
-        <f>COUNTIF($B$5:$B$117,"Intangible")</f>
+      <c r="B92" s="56">
+        <f>COUNTIF($B$5:$B$118,"Intangible")</f>
         <v/>
       </c>
-      <c r="C91" s="57" t="n"/>
-      <c r="D91" s="57" t="n"/>
-      <c r="E91" s="57" t="n"/>
-      <c r="F91" s="88" t="n"/>
-      <c r="G91" s="108" t="n"/>
-      <c r="H91" s="102" t="n"/>
-      <c r="I91" s="102" t="n"/>
-      <c r="J91" s="102" t="n"/>
-    </row>
-    <row r="92" ht="14" customHeight="1" s="132">
-      <c r="A92" s="96" t="inlineStr">
-        <is>
-          <t>All intangibles are limited to 1</t>
-        </is>
-      </c>
-      <c r="B92" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C92" s="31" t="inlineStr">
-        <is>
-          <t>Board-Crasher</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% upon Rebounding your own missed shot</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="n"/>
-      <c r="F92" s="138" t="n"/>
-      <c r="G92" s="101" t="n"/>
+      <c r="C92" s="57" t="n"/>
+      <c r="D92" s="57" t="n"/>
+      <c r="E92" s="57" t="n"/>
+      <c r="F92" s="88" t="n"/>
+      <c r="G92" s="108" t="n"/>
       <c r="H92" s="102" t="n"/>
       <c r="I92" s="102" t="n"/>
       <c r="J92" s="102" t="n"/>
     </row>
     <row r="93" ht="28" customHeight="1" s="132">
-      <c r="A93" s="29" t="n"/>
+      <c r="A93" s="96" t="inlineStr">
+        <is>
+          <t>All intangibles are limited to 1</t>
+        </is>
+      </c>
       <c r="B93" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C93" s="32" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D93" s="33" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E93" s="34" t="n"/>
+      <c r="C93" s="31" t="inlineStr">
+        <is>
+          <t>Board-Crasher</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% upon Rebounding your own missed shot</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="n"/>
       <c r="F93" s="138" t="n"/>
-      <c r="G93" s="107" t="n"/>
+      <c r="G93" s="101" t="n"/>
       <c r="H93" s="102" t="n"/>
       <c r="I93" s="102" t="n"/>
       <c r="J93" s="102" t="n"/>
@@ -5103,19 +5113,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C94" s="31" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="n"/>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D94" s="33" t="inlineStr">
+        <is>
+          <t>Additional SHOT +10% on all received passes</t>
+        </is>
+      </c>
+      <c r="E94" s="34" t="n"/>
       <c r="F94" s="138" t="n"/>
-      <c r="G94" s="101" t="n"/>
+      <c r="G94" s="107" t="n"/>
       <c r="H94" s="102" t="n"/>
       <c r="I94" s="102" t="n"/>
       <c r="J94" s="102" t="n"/>
@@ -5127,19 +5137,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C95" s="32" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D95" s="33" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
-        </is>
-      </c>
-      <c r="E95" s="34" t="n"/>
+      <c r="C95" s="31" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="n"/>
       <c r="F95" s="138" t="n"/>
-      <c r="G95" s="107" t="n"/>
+      <c r="G95" s="101" t="n"/>
       <c r="H95" s="102" t="n"/>
       <c r="I95" s="102" t="n"/>
       <c r="J95" s="102" t="n"/>
@@ -5151,23 +5161,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C96" s="31" t="inlineStr">
-        <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F96" s="139" t="n"/>
-      <c r="G96" s="101" t="n"/>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D96" s="33" t="inlineStr">
+        <is>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
+        </is>
+      </c>
+      <c r="E96" s="34" t="n"/>
+      <c r="F96" s="138" t="n"/>
+      <c r="G96" s="107" t="n"/>
       <c r="H96" s="102" t="n"/>
       <c r="I96" s="102" t="n"/>
       <c r="J96" s="102" t="n"/>
@@ -5179,19 +5185,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C97" s="90" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D97" s="94" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E97" s="34" t="n"/>
-      <c r="F97" s="138" t="n"/>
-      <c r="G97" s="125" t="n"/>
+      <c r="C97" s="31" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F97" s="139" t="n"/>
+      <c r="G97" s="101" t="n"/>
       <c r="H97" s="102" t="n"/>
       <c r="I97" s="102" t="n"/>
       <c r="J97" s="102" t="n"/>
@@ -5205,17 +5215,17 @@
       </c>
       <c r="C98" s="90" t="inlineStr">
         <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D98" s="91" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="n"/>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D98" s="94" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
+        </is>
+      </c>
+      <c r="E98" s="34" t="n"/>
       <c r="F98" s="138" t="n"/>
-      <c r="G98" s="101" t="n"/>
+      <c r="G98" s="125" t="n"/>
       <c r="H98" s="102" t="n"/>
       <c r="I98" s="102" t="n"/>
       <c r="J98" s="102" t="n"/>
@@ -5227,19 +5237,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C99" s="32" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D99" s="33" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E99" s="34" t="n"/>
+      <c r="C99" s="90" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D99" s="91" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="n"/>
       <c r="F99" s="138" t="n"/>
-      <c r="G99" s="107" t="n"/>
+      <c r="G99" s="101" t="n"/>
       <c r="H99" s="102" t="n"/>
       <c r="I99" s="102" t="n"/>
       <c r="J99" s="102" t="n"/>
@@ -5251,19 +5261,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C100" s="31" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="n"/>
+      <c r="C100" s="32" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="D100" s="33" t="inlineStr">
+        <is>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+        </is>
+      </c>
+      <c r="E100" s="34" t="n"/>
       <c r="F100" s="138" t="n"/>
-      <c r="G100" s="101" t="n"/>
+      <c r="G100" s="107" t="n"/>
       <c r="H100" s="102" t="n"/>
       <c r="I100" s="102" t="n"/>
       <c r="J100" s="102" t="n"/>
@@ -5275,19 +5285,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C101" s="32" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D101" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +20% if you scored last round.</t>
-        </is>
-      </c>
-      <c r="E101" s="34" t="n"/>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="n"/>
       <c r="F101" s="138" t="n"/>
-      <c r="G101" s="107" t="n"/>
+      <c r="G101" s="101" t="n"/>
       <c r="H101" s="102" t="n"/>
       <c r="I101" s="102" t="n"/>
       <c r="J101" s="102" t="n"/>
@@ -5299,19 +5309,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C102" s="31" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D102" s="91" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="n"/>
+      <c r="C102" s="32" t="inlineStr">
+        <is>
+          <t>Hot Hand</t>
+        </is>
+      </c>
+      <c r="D102" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +20% if you scored last round.</t>
+        </is>
+      </c>
+      <c r="E102" s="34" t="n"/>
       <c r="F102" s="138" t="n"/>
-      <c r="G102" s="101" t="n"/>
+      <c r="G102" s="107" t="n"/>
       <c r="H102" s="102" t="n"/>
       <c r="I102" s="102" t="n"/>
       <c r="J102" s="102" t="n"/>
@@ -5323,23 +5333,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C103" s="32" t="inlineStr">
-        <is>
-          <t>No Bag</t>
-        </is>
-      </c>
-      <c r="D103" s="33" t="inlineStr">
-        <is>
-          <t>Cannot activate Move cards this round</t>
-        </is>
-      </c>
-      <c r="E103" s="34" t="n"/>
+      <c r="C103" s="31" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D103" s="91" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="n"/>
       <c r="F103" s="138" t="n"/>
-      <c r="G103" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G103" s="101" t="n"/>
       <c r="H103" s="102" t="n"/>
       <c r="I103" s="102" t="n"/>
       <c r="J103" s="102" t="n"/>
@@ -5351,19 +5357,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C104" s="31" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="n"/>
+      <c r="C104" s="32" t="inlineStr">
+        <is>
+          <t>No Bag</t>
+        </is>
+      </c>
+      <c r="D104" s="33" t="inlineStr">
+        <is>
+          <t>Cannot activate Move cards this round</t>
+        </is>
+      </c>
+      <c r="E104" s="34" t="n"/>
       <c r="F104" s="138" t="n"/>
-      <c r="G104" s="101" t="n"/>
+      <c r="G104" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H104" s="102" t="n"/>
       <c r="I104" s="102" t="n"/>
       <c r="J104" s="102" t="n"/>
@@ -5375,23 +5385,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C105" s="32" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D105" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
-        </is>
-      </c>
-      <c r="E105" s="34" t="n"/>
+      <c r="C105" s="31" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="n"/>
       <c r="F105" s="138" t="n"/>
-      <c r="G105" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G105" s="101" t="n"/>
       <c r="H105" s="102" t="n"/>
       <c r="I105" s="102" t="n"/>
       <c r="J105" s="102" t="n"/>
@@ -5403,19 +5409,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C106" s="31" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="n"/>
+      <c r="C106" s="32" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D106" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E106" s="34" t="n"/>
       <c r="F106" s="138" t="n"/>
-      <c r="G106" s="101" t="n"/>
+      <c r="G106" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H106" s="102" t="n"/>
       <c r="I106" s="102" t="n"/>
       <c r="J106" s="102" t="n"/>
@@ -5427,19 +5437,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C107" s="32" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D107" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
-        </is>
-      </c>
-      <c r="E107" s="34" t="n"/>
+      <c r="C107" s="31" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="n"/>
       <c r="F107" s="138" t="n"/>
-      <c r="G107" s="107" t="n"/>
+      <c r="G107" s="101" t="n"/>
       <c r="H107" s="102" t="n"/>
       <c r="I107" s="102" t="n"/>
       <c r="J107" s="102" t="n"/>
@@ -5451,19 +5461,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C108" s="31" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="n"/>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D108" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E108" s="34" t="n"/>
       <c r="F108" s="138" t="n"/>
-      <c r="G108" s="101" t="n"/>
+      <c r="G108" s="107" t="n"/>
       <c r="H108" s="102" t="n"/>
       <c r="I108" s="102" t="n"/>
       <c r="J108" s="102" t="n"/>
@@ -5475,19 +5485,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C109" s="32" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D109" s="33" t="inlineStr">
-        <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E109" s="34" t="n"/>
+      <c r="C109" s="31" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="n"/>
       <c r="F109" s="138" t="n"/>
-      <c r="G109" s="107" t="n"/>
+      <c r="G109" s="101" t="n"/>
       <c r="H109" s="102" t="n"/>
       <c r="I109" s="102" t="n"/>
       <c r="J109" s="102" t="n"/>
@@ -5499,19 +5509,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C110" s="31" t="inlineStr">
-        <is>
-          <t>Unguardable</t>
-        </is>
-      </c>
-      <c r="D110" s="91" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="n"/>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D110" s="33" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E110" s="34" t="n"/>
       <c r="F110" s="138" t="n"/>
-      <c r="G110" s="101" t="n"/>
+      <c r="G110" s="107" t="n"/>
       <c r="H110" s="102" t="n"/>
       <c r="I110" s="102" t="n"/>
       <c r="J110" s="102" t="n"/>
@@ -5523,50 +5533,50 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C111" s="32" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D111" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
-        </is>
-      </c>
-      <c r="E111" s="34" t="n"/>
+      <c r="C111" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D111" s="91" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="n"/>
       <c r="F111" s="138" t="n"/>
-      <c r="G111" s="113" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G111" s="101" t="n"/>
       <c r="H111" s="102" t="n"/>
       <c r="I111" s="102" t="n"/>
       <c r="J111" s="102" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="61" t="n"/>
-      <c r="B112" s="62" t="inlineStr">
+      <c r="A112" s="29" t="n"/>
+      <c r="B112" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C112" s="66" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D112" s="95" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E112" s="68" t="n"/>
-      <c r="F112" s="140" t="n"/>
-      <c r="G112" s="126" t="n"/>
-      <c r="H112" s="117" t="n"/>
-      <c r="I112" s="117" t="n"/>
-      <c r="J112" s="117" t="n"/>
+      <c r="C112" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D112" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E112" s="34" t="n"/>
+      <c r="F112" s="138" t="n"/>
+      <c r="G112" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H112" s="102" t="n"/>
+      <c r="I112" s="102" t="n"/>
+      <c r="J112" s="102" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="61" t="n"/>
@@ -5577,12 +5587,12 @@
       </c>
       <c r="C113" s="66" t="inlineStr">
         <is>
-          <t>Unselfish</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D113" s="95" t="inlineStr">
         <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E113" s="68" t="n"/>
@@ -5601,12 +5611,12 @@
       </c>
       <c r="C114" s="66" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D114" s="95" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E114" s="68" t="n"/>
@@ -5625,21 +5635,20 @@
       </c>
       <c r="C115" s="66" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D115" s="95" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E115" s="68" t="n"/>
       <c r="F115" s="140" t="n"/>
-      <c r="G115" s="126" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="G115" s="126" t="n"/>
+      <c r="H115" s="117" t="n"/>
+      <c r="I115" s="117" t="n"/>
+      <c r="J115" s="117" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="61" t="n"/>
@@ -5650,19 +5659,19 @@
       </c>
       <c r="C116" s="66" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Villainous Reputation</t>
         </is>
       </c>
       <c r="D116" s="95" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>Discard 1 whenever any Whistle triggers</t>
         </is>
       </c>
       <c r="E116" s="68" t="n"/>
       <c r="F116" s="140" t="n"/>
       <c r="G116" s="126" t="inlineStr">
         <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
         </is>
       </c>
     </row>
@@ -5675,23 +5684,48 @@
       </c>
       <c r="C117" s="66" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Free Agent</t>
         </is>
       </c>
       <c r="D117" s="95" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
       <c r="E117" s="68" t="n"/>
       <c r="F117" s="140" t="n"/>
-      <c r="G117" s="126" t="n"/>
-      <c r="H117" s="117" t="n"/>
-      <c r="I117" s="117" t="n"/>
-      <c r="J117" s="117" t="n"/>
+      <c r="G117" s="126" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="61" t="n"/>
+      <c r="B118" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C118" s="66" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D118" s="95" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E118" s="68" t="n"/>
+      <c r="F118" s="140" t="n"/>
+      <c r="G118" s="126" t="n"/>
+      <c r="H118" s="117" t="n"/>
+      <c r="I118" s="117" t="n"/>
+      <c r="J118" s="117" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="104">
+  <mergeCells count="105">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G109:J109"/>
@@ -5701,11 +5735,11 @@
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
     <mergeCell ref="G72:J72"/>
-    <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G82:J82"/>
     <mergeCell ref="G57:J57"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
@@ -5725,15 +5759,12 @@
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G94:J94"/>
     <mergeCell ref="G75:J75"/>
-    <mergeCell ref="G44:J44"/>
     <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G84:J84"/>
     <mergeCell ref="G31:J31"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="G12:J12"/>
-    <mergeCell ref="G77:J77"/>
+    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="G61:J61"/>
     <mergeCell ref="G70:J70"/>
@@ -5752,13 +5783,14 @@
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="G35:J35"/>
     <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G76:J76"/>
     <mergeCell ref="G90:J90"/>
     <mergeCell ref="G99:J99"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G59:J59"/>
+    <mergeCell ref="G115:J115"/>
     <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G117:J117"/>
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="G101:J101"/>
     <mergeCell ref="G103:J103"/>
@@ -5766,8 +5798,11 @@
     <mergeCell ref="G37:J37"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G78:J78"/>
+    <mergeCell ref="G118:J118"/>
     <mergeCell ref="G87:J87"/>
     <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G44:J44"/>
     <mergeCell ref="G95:J95"/>
     <mergeCell ref="G89:J89"/>
     <mergeCell ref="G64:J64"/>
@@ -5785,9 +5820,9 @@
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
+    <mergeCell ref="G42:J42"/>
     <mergeCell ref="G107:J107"/>
     <mergeCell ref="G36:J36"/>
-    <mergeCell ref="G42:J42"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G28:J28"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2626,35 +2626,35 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$118,"Pass")</f>
+        <f>COUNTIF($B$5:$B$122,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$118,"Move")+COUNTIF($B$5:$B$118,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$122,"Move")+COUNTIF($B$5:$B$122,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$118,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$122,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$118,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$122,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$118,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$122,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$118,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$122,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$118,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$122,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$118,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$122,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$118,"Pass")</f>
+        <f>COUNTIF($B$5:$B$122,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="23" t="n"/>
@@ -2954,165 +2954,177 @@
       <c r="J14" s="104" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="132">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="inlineStr">
+        <is>
+          <t>Alley-Oop</t>
+        </is>
+      </c>
+      <c r="D15" s="38" t="inlineStr">
+        <is>
+          <t>SHOT +20%. Pass to player of choice</t>
+        </is>
+      </c>
+      <c r="E15" s="38" t="inlineStr">
+        <is>
+          <t>Receiving player shoots immediately after drawing for turn</t>
+        </is>
+      </c>
+      <c r="F15" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="127" t="n"/>
+      <c r="H15" s="104" t="n"/>
+      <c r="I15" s="104" t="n"/>
+      <c r="J15" s="104" t="n"/>
+    </row>
+    <row r="16" ht="14" customHeight="1" s="132">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="inlineStr">
+        <is>
+          <t>Hand-Off</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="inlineStr">
+        <is>
+          <t>SHOT +5%. Pass to player to Left or Right. Draw 1 card</t>
+        </is>
+      </c>
+      <c r="E16" s="38" t="inlineStr">
+        <is>
+          <t>If played following a Dribble: draw 1 additional and SHOT +5% more</t>
+        </is>
+      </c>
+      <c r="F16" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="127" t="inlineStr">
+        <is>
+          <t>This is the Dribble Hand-Off</t>
+        </is>
+      </c>
+      <c r="H16" s="104" t="n"/>
+      <c r="I16" s="104" t="n"/>
+      <c r="J16" s="104" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" s="132">
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>Outlet Pass</t>
+        </is>
+      </c>
+      <c r="D17" s="38" t="inlineStr">
+        <is>
+          <t>SHOT +10%. Shot Clock +01. Pass to player of choice</t>
+        </is>
+      </c>
+      <c r="E17" s="38" t="n"/>
+      <c r="F17" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="127" t="inlineStr">
+        <is>
+          <t>The clock increments instead of decrementing — it does not break even</t>
+        </is>
+      </c>
+      <c r="H17" s="104" t="n"/>
+      <c r="I17" s="104" t="n"/>
+      <c r="J17" s="104" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" s="132">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>Kick-Out</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="inlineStr">
+        <is>
+          <t>SHOT +10%. Upgraded to 3pt. Pass to player of choice</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="inlineStr">
+        <is>
+          <t>Following Drive: draw 1. Following a Dribble Drive: gain 1 AST also</t>
+        </is>
+      </c>
+      <c r="F18" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="127" t="inlineStr">
+        <is>
+          <t>The most it grants is a draw and 1 AST</t>
+        </is>
+      </c>
+      <c r="H18" s="104" t="n"/>
+      <c r="I18" s="104" t="n"/>
+      <c r="J18" s="104" t="n"/>
+    </row>
+    <row r="19" ht="56" customHeight="1" s="132">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="B15" s="40">
-        <f>COUNTIF($B$5:$B$118,"Move")+COUNTIF($B$5:$B$118,"Special Move")</f>
+      <c r="B19" s="40">
+        <f>COUNTIF($B$5:$B$122,"Move")+COUNTIF($B$5:$B$122,"Special Move")</f>
         <v/>
       </c>
-      <c r="C15" s="41" t="n"/>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="41" t="n"/>
-      <c r="F15" s="78" t="n"/>
-      <c r="G15" s="120" t="n"/>
-      <c r="H15" s="121" t="n"/>
-      <c r="I15" s="121" t="n"/>
-      <c r="J15" s="121" t="n"/>
-    </row>
-    <row r="16" ht="14" customHeight="1" s="132">
-      <c r="A16" s="45" t="n"/>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="41" t="n"/>
+      <c r="E19" s="41" t="n"/>
+      <c r="F19" s="78" t="n"/>
+      <c r="G19" s="120" t="n"/>
+      <c r="H19" s="121" t="n"/>
+      <c r="I19" s="121" t="n"/>
+      <c r="J19" s="121" t="n"/>
+    </row>
+    <row r="20" ht="14" customHeight="1" s="132">
+      <c r="A20" s="45" t="n"/>
+      <c r="B20" s="46" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C20" s="47" t="inlineStr">
         <is>
           <t>Dribble</t>
         </is>
       </c>
-      <c r="D16" s="48" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>Draw 1 card. SHOT -10%</t>
         </is>
       </c>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="79" t="n">
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="79" t="n">
         <v>15</v>
       </c>
-      <c r="G16" s="118" t="n"/>
-      <c r="H16" s="119" t="n"/>
-      <c r="I16" s="119" t="n"/>
-      <c r="J16" s="119" t="n"/>
-    </row>
-    <row r="17" ht="28" customHeight="1" s="132">
-      <c r="A17" s="29" t="n"/>
-      <c r="B17" s="30" t="inlineStr">
-        <is>
-          <t>Move</t>
-        </is>
-      </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Following Dribble: SHOT +10%</t>
-        </is>
-      </c>
-      <c r="F17" s="74" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="101" t="n"/>
-      <c r="H17" s="102" t="n"/>
-      <c r="I17" s="102" t="n"/>
-      <c r="J17" s="102" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1" s="132">
-      <c r="A18" s="29" t="n"/>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Move</t>
-        </is>
-      </c>
-      <c r="C18" s="32" t="inlineStr">
-        <is>
-          <t>Ankle Breaker</t>
-        </is>
-      </c>
-      <c r="D18" s="33" t="inlineStr">
-        <is>
-          <t>Target player discards 1 card. SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E18" s="34" t="n"/>
-      <c r="F18" s="75" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" s="107" t="n"/>
-      <c r="H18" s="102" t="n"/>
-      <c r="I18" s="102" t="n"/>
-      <c r="J18" s="102" t="n"/>
-    </row>
-    <row r="19" ht="56" customHeight="1" s="132">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>Move</t>
-        </is>
-      </c>
-      <c r="C19" s="90" t="inlineStr">
-        <is>
-          <t>Flop</t>
-        </is>
-      </c>
-      <c r="D19" s="91" t="inlineStr">
-        <is>
-          <t>Cancel Clamps. Take 1 FT for each. If no Clamps on you, TOV +1</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" s="130" t="inlineStr">
-        <is>
-          <t>Take 1 FT attempt for each Clamp on you and cancel it. If no Clamps on you, TOV +1</t>
-        </is>
-      </c>
-      <c r="H19" s="102" t="n"/>
-      <c r="I19" s="102" t="n"/>
-      <c r="J19" s="102" t="n"/>
-    </row>
-    <row r="20" ht="14" customHeight="1" s="132">
-      <c r="A20" s="29" t="n"/>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>Move</t>
-        </is>
-      </c>
-      <c r="C20" s="32" t="inlineStr">
-        <is>
-          <t>Hesi</t>
-        </is>
-      </c>
-      <c r="D20" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E20" s="33" t="inlineStr">
-        <is>
-          <t>Shot Clock -1</t>
-        </is>
-      </c>
-      <c r="F20" s="80" t="n">
-        <v>15</v>
-      </c>
-      <c r="G20" s="107" t="n"/>
-      <c r="H20" s="102" t="n"/>
-      <c r="I20" s="102" t="n"/>
-      <c r="J20" s="102" t="n"/>
+      <c r="G20" s="118" t="n"/>
+      <c r="H20" s="119" t="n"/>
+      <c r="I20" s="119" t="n"/>
+      <c r="J20" s="119" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1" s="132">
       <c r="A21" s="29" t="n"/>
@@ -3123,7 +3135,7 @@
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>Pump Fake</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -3133,11 +3145,11 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Cancel all Clamps on you</t>
+          <t>Following Dribble: SHOT +10%</t>
         </is>
       </c>
       <c r="F21" s="74" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G21" s="101" t="n"/>
       <c r="H21" s="102" t="n"/>
@@ -3153,17 +3165,17 @@
       </c>
       <c r="C22" s="32" t="inlineStr">
         <is>
-          <t>Rhythm Dribble</t>
+          <t>Ankle Breaker</t>
         </is>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
-          <t>Draw 1 card. SHOT +10%. Shot Clock -1</t>
+          <t>Target player discards 1 card. SHOT +10%</t>
         </is>
       </c>
       <c r="E22" s="34" t="n"/>
       <c r="F22" s="75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G22" s="107" t="n"/>
       <c r="H22" s="102" t="n"/>
@@ -3177,21 +3189,25 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C23" s="133" t="inlineStr">
-        <is>
-          <t>Pound Dribble</t>
-        </is>
-      </c>
-      <c r="D23" s="94" t="inlineStr">
-        <is>
-          <t>Draw 2 cards then Discard 1. SHOT +10% Shot Clock -1</t>
-        </is>
-      </c>
-      <c r="E23" s="34" t="n"/>
-      <c r="F23" s="75" t="n">
+      <c r="C23" s="90" t="inlineStr">
+        <is>
+          <t>Flop</t>
+        </is>
+      </c>
+      <c r="D23" s="91" t="inlineStr">
+        <is>
+          <t>Cancel Clamps. Take 1 FT for each. If no Clamps on you, TOV +1</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="107" t="n"/>
+      <c r="G23" s="130" t="inlineStr">
+        <is>
+          <t>Take 1 FT attempt for each Clamp on you and cancel it. If no Clamps on you, TOV +1</t>
+        </is>
+      </c>
       <c r="H23" s="102" t="n"/>
       <c r="I23" s="102" t="n"/>
       <c r="J23" s="102" t="n"/>
@@ -3203,25 +3219,25 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C24" s="133" t="inlineStr">
-        <is>
-          <t>Spin Move</t>
-        </is>
-      </c>
-      <c r="D24" s="94" t="inlineStr">
-        <is>
-          <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +10% for each</t>
-        </is>
-      </c>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="75" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" s="125" t="inlineStr">
-        <is>
-          <t>isDribble = true</t>
-        </is>
-      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>Hesi</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>Shot Clock -1</t>
+        </is>
+      </c>
+      <c r="F24" s="80" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" s="107" t="n"/>
       <c r="H24" s="102" t="n"/>
       <c r="I24" s="102" t="n"/>
       <c r="J24" s="102" t="n"/>
@@ -3233,25 +3249,25 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C25" s="133" t="inlineStr">
-        <is>
-          <t>Crossover</t>
-        </is>
-      </c>
-      <c r="D25" s="94" t="inlineStr">
-        <is>
-          <t>Draw 1 Card. SHOT +10%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="n"/>
-      <c r="F25" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="125" t="inlineStr">
-        <is>
-          <t>isDribble = true</t>
-        </is>
-      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Pump Fake</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Cancel all Clamps on you</t>
+        </is>
+      </c>
+      <c r="F25" s="74" t="n">
+        <v>12</v>
+      </c>
+      <c r="G25" s="101" t="n"/>
       <c r="H25" s="102" t="n"/>
       <c r="I25" s="102" t="n"/>
       <c r="J25" s="102" t="n"/>
@@ -3263,46 +3279,158 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>Stepback</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Discard 1: SHOT +10%</t>
-        </is>
-      </c>
-      <c r="F26" s="74" t="n">
-        <v>12</v>
-      </c>
-      <c r="G26" s="101" t="inlineStr">
-        <is>
-          <t>The discard is an optional prompt.</t>
-        </is>
-      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>Rhythm Dribble</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>Draw 1 card. SHOT +10%. Shot Clock -1</t>
+        </is>
+      </c>
+      <c r="E26" s="34" t="n"/>
+      <c r="F26" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="107" t="n"/>
       <c r="H26" s="102" t="n"/>
       <c r="I26" s="102" t="n"/>
       <c r="J26" s="102" t="n"/>
     </row>
     <row r="27" ht="71" customHeight="1" s="132" thickBot="1">
-      <c r="A27" s="61" t="n"/>
-      <c r="B27" s="62" t="inlineStr">
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C27" s="63" t="inlineStr">
+      <c r="C27" s="133" t="inlineStr">
+        <is>
+          <t>Pound Dribble</t>
+        </is>
+      </c>
+      <c r="D27" s="94" t="inlineStr">
+        <is>
+          <t>Draw 2 cards then Discard 1. SHOT +10% Shot Clock -1</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="107" t="n"/>
+      <c r="H27" s="102" t="n"/>
+      <c r="I27" s="102" t="n"/>
+      <c r="J27" s="102" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" s="132">
+      <c r="A28" s="29" t="n"/>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="C28" s="133" t="inlineStr">
+        <is>
+          <t>Spin Move</t>
+        </is>
+      </c>
+      <c r="D28" s="94" t="inlineStr">
+        <is>
+          <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +10% for each</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="n"/>
+      <c r="F28" s="75" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="125" t="inlineStr">
+        <is>
+          <t>isDribble = true</t>
+        </is>
+      </c>
+      <c r="H28" s="102" t="n"/>
+      <c r="I28" s="102" t="n"/>
+      <c r="J28" s="102" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1" s="132">
+      <c r="A29" s="29" t="n"/>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="C29" s="133" t="inlineStr">
+        <is>
+          <t>Crossover</t>
+        </is>
+      </c>
+      <c r="D29" s="94" t="inlineStr">
+        <is>
+          <t>Draw 1 Card. SHOT +10%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="125" t="inlineStr">
+        <is>
+          <t>isDribble = true</t>
+        </is>
+      </c>
+      <c r="H29" s="102" t="n"/>
+      <c r="I29" s="102" t="n"/>
+      <c r="J29" s="102" t="n"/>
+    </row>
+    <row r="30" ht="14" customHeight="1" s="132">
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>Stepback</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Discard 1: SHOT +10%</t>
+        </is>
+      </c>
+      <c r="F30" s="74" t="n">
+        <v>12</v>
+      </c>
+      <c r="G30" s="101" t="inlineStr">
+        <is>
+          <t>The discard is an optional prompt.</t>
+        </is>
+      </c>
+      <c r="H30" s="102" t="n"/>
+      <c r="I30" s="102" t="n"/>
+      <c r="J30" s="102" t="n"/>
+    </row>
+    <row r="31" ht="28" customHeight="1" s="132">
+      <c r="A31" s="61" t="n"/>
+      <c r="B31" s="62" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
         <is>
           <t>Triple Threat</t>
         </is>
       </c>
-      <c r="D27" s="64" t="inlineStr">
+      <c r="D31" s="64" t="inlineStr">
         <is>
           <t>Choose 1:
 Draw 1 card
@@ -3310,192 +3438,68 @@
 SHOT +10%</t>
         </is>
       </c>
-      <c r="E27" s="64" t="inlineStr">
+      <c r="E31" s="64" t="inlineStr">
         <is>
           <t>Cannot use further Move cards</t>
         </is>
       </c>
-      <c r="F27" s="81" t="n">
+      <c r="F31" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="G27" s="116" t="inlineStr">
+      <c r="G31" s="116" t="inlineStr">
         <is>
           <t>Cannot use further Move cards applies to that possession only.</t>
         </is>
       </c>
-      <c r="H27" s="117" t="n"/>
-      <c r="I27" s="117" t="n"/>
-      <c r="J27" s="117" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1" s="132">
-      <c r="A28" s="42" t="inlineStr">
+      <c r="H31" s="117" t="n"/>
+      <c r="I31" s="117" t="n"/>
+      <c r="J31" s="117" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1" s="132">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="B28" s="43">
-        <f>COUNTIF($B$5:$B$118,"Special Move")</f>
+      <c r="B32" s="43">
+        <f>COUNTIF($B$5:$B$122,"Special Move")</f>
         <v/>
       </c>
-      <c r="C28" s="44" t="n"/>
-      <c r="D28" s="44" t="n"/>
-      <c r="E28" s="44" t="n"/>
-      <c r="F28" s="82" t="n"/>
-      <c r="G28" s="120" t="n"/>
-      <c r="H28" s="121" t="n"/>
-      <c r="I28" s="121" t="n"/>
-      <c r="J28" s="121" t="n"/>
-    </row>
-    <row r="29" ht="42" customHeight="1" s="132">
-      <c r="A29" s="24" t="n"/>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="C32" s="44" t="n"/>
+      <c r="D32" s="44" t="n"/>
+      <c r="E32" s="44" t="n"/>
+      <c r="F32" s="82" t="n"/>
+      <c r="G32" s="120" t="n"/>
+      <c r="H32" s="121" t="n"/>
+      <c r="I32" s="121" t="n"/>
+      <c r="J32" s="121" t="n"/>
+    </row>
+    <row r="33" ht="28" customHeight="1" s="132">
+      <c r="A33" s="24" t="n"/>
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Bankshot</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D33" s="27" t="inlineStr">
         <is>
           <t>Flip a coin:
 Heads: SHOT +10%
 Tails: SHOT -10%</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F29" s="83" t="n">
+      <c r="F33" s="83" t="n">
         <v>4</v>
-      </c>
-      <c r="G29" s="105" t="n"/>
-      <c r="H29" s="106" t="n"/>
-      <c r="I29" s="106" t="n"/>
-      <c r="J29" s="106" t="n"/>
-    </row>
-    <row r="30" ht="14" customHeight="1" s="132">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>Special Move</t>
-        </is>
-      </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>Buzzer Beater</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
-      <c r="F30" s="74" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" s="128" t="inlineStr">
-        <is>
-          <t>Can only play with Shot Clock at 1</t>
-        </is>
-      </c>
-      <c r="H30" s="106" t="n"/>
-      <c r="I30" s="106" t="n"/>
-      <c r="J30" s="106" t="n"/>
-    </row>
-    <row r="31" ht="28" customHeight="1" s="132">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>Special Move</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>Dagger Three</t>
-        </is>
-      </c>
-      <c r="D31" s="94" t="inlineStr">
-        <is>
-          <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
-        </is>
-      </c>
-      <c r="E31" s="33" t="inlineStr">
-        <is>
-          <t>Shoot the ball. +1 Point on make</t>
-        </is>
-      </c>
-      <c r="F31" s="80" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" s="105" t="n"/>
-      <c r="H31" s="106" t="n"/>
-      <c r="I31" s="106" t="n"/>
-      <c r="J31" s="106" t="n"/>
-    </row>
-    <row r="32" ht="14" customHeight="1" s="132">
-      <c r="A32" s="29" t="n"/>
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>Special Move</t>
-        </is>
-      </c>
-      <c r="C32" s="31" t="inlineStr">
-        <is>
-          <t>Fadeaway</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>SHOT -10%. Draw 1 card</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball.</t>
-        </is>
-      </c>
-      <c r="F32" s="74" t="n">
-        <v>10</v>
-      </c>
-      <c r="G32" s="112" t="n"/>
-      <c r="H32" s="106" t="n"/>
-      <c r="I32" s="106" t="n"/>
-      <c r="J32" s="106" t="n"/>
-    </row>
-    <row r="33" ht="28" customHeight="1" s="132">
-      <c r="A33" s="29" t="n"/>
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>Special Move</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>From the Hash</t>
-        </is>
-      </c>
-      <c r="D33" s="94" t="inlineStr">
-        <is>
-          <t>SHOT -20%</t>
-        </is>
-      </c>
-      <c r="E33" s="33" t="inlineStr">
-        <is>
-          <t>Shoot the ball. +1 Point on make</t>
-        </is>
-      </c>
-      <c r="F33" s="80" t="n">
-        <v>3</v>
       </c>
       <c r="G33" s="105" t="n"/>
       <c r="H33" s="106" t="n"/>
@@ -3511,23 +3515,27 @@
       </c>
       <c r="C34" s="31" t="inlineStr">
         <is>
-          <t>From the Logo</t>
-        </is>
-      </c>
-      <c r="D34" s="91" t="inlineStr">
-        <is>
-          <t>SHOT -30%</t>
+          <t>Buzzer Beater</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>SHOT = 100%</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball. +1 Point on make</t>
+          <t>Shoot the ball</t>
         </is>
       </c>
       <c r="F34" s="74" t="n">
-        <v>3</v>
-      </c>
-      <c r="G34" s="112" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="G34" s="128" t="inlineStr">
+        <is>
+          <t>Can only play with Shot Clock at 1</t>
+        </is>
+      </c>
       <c r="H34" s="106" t="n"/>
       <c r="I34" s="106" t="n"/>
       <c r="J34" s="106" t="n"/>
@@ -3541,12 +3549,12 @@
       </c>
       <c r="C35" s="32" t="inlineStr">
         <is>
-          <t>Full-Court Heave</t>
-        </is>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 10%</t>
+          <t>Dagger Three</t>
+        </is>
+      </c>
+      <c r="D35" s="94" t="inlineStr">
+        <is>
+          <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
         </is>
       </c>
       <c r="E35" s="33" t="inlineStr">
@@ -3555,7 +3563,7 @@
         </is>
       </c>
       <c r="F35" s="80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="105" t="n"/>
       <c r="H35" s="106" t="n"/>
@@ -3571,21 +3579,21 @@
       </c>
       <c r="C36" s="31" t="inlineStr">
         <is>
-          <t>Putback Tip</t>
+          <t>Fadeaway</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
+          <t>SHOT -10%. Draw 1 card</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball. After a missed shot: SHOT = 100%</t>
+          <t>Shoot the ball.</t>
         </is>
       </c>
       <c r="F36" s="74" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G36" s="112" t="n"/>
       <c r="H36" s="106" t="n"/>
@@ -3601,21 +3609,21 @@
       </c>
       <c r="C37" s="32" t="inlineStr">
         <is>
-          <t>Skyhook</t>
-        </is>
-      </c>
-      <c r="D37" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E37" s="94" t="inlineStr">
-        <is>
-          <t>Shoot the ball. Shot is unaffected by Clamps</t>
+          <t>From the Hash</t>
+        </is>
+      </c>
+      <c r="D37" s="94" t="inlineStr">
+        <is>
+          <t>SHOT -20%</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="inlineStr">
+        <is>
+          <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
       <c r="F37" s="80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G37" s="105" t="n"/>
       <c r="H37" s="106" t="n"/>
@@ -3631,21 +3639,21 @@
       </c>
       <c r="C38" s="31" t="inlineStr">
         <is>
-          <t>Slam Dunk</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%. SHOT = 100% if SHOT &gt;= 70%</t>
+          <t>From the Logo</t>
+        </is>
+      </c>
+      <c r="D38" s="91" t="inlineStr">
+        <is>
+          <t>SHOT -30%</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball</t>
+          <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
       <c r="F38" s="74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" s="112" t="n"/>
       <c r="H38" s="106" t="n"/>
@@ -3653,313 +3661,322 @@
       <c r="J38" s="106" t="n"/>
     </row>
     <row r="39" ht="42" customHeight="1" s="132">
-      <c r="A39" s="52" t="n"/>
-      <c r="B39" s="53" t="inlineStr">
+      <c r="A39" s="29" t="n"/>
+      <c r="B39" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C39" s="69" t="inlineStr">
-        <is>
-          <t>Turnaround Three</t>
-        </is>
-      </c>
-      <c r="D39" s="70" t="inlineStr">
-        <is>
-          <t>Discard any number of cards. SHOT +10% for each</t>
-        </is>
-      </c>
-      <c r="E39" s="70" t="inlineStr">
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>Full-Court Heave</t>
+        </is>
+      </c>
+      <c r="D39" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 10%</t>
+        </is>
+      </c>
+      <c r="E39" s="33" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F39" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="129" t="inlineStr">
-        <is>
-          <t>Only 1 in deck</t>
-        </is>
-      </c>
+      <c r="F39" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="105" t="n"/>
       <c r="H39" s="106" t="n"/>
       <c r="I39" s="106" t="n"/>
       <c r="J39" s="106" t="n"/>
     </row>
     <row r="40" ht="57" customHeight="1" s="132" thickBot="1">
-      <c r="A40" s="61" t="n"/>
-      <c r="B40" s="62" t="inlineStr">
+      <c r="A40" s="29" t="n"/>
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C40" s="66" t="inlineStr">
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>Putback Tip</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Shoot the ball. After a missed shot: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="F40" s="74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="112" t="n"/>
+      <c r="H40" s="106" t="n"/>
+      <c r="I40" s="106" t="n"/>
+      <c r="J40" s="106" t="n"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" s="132">
+      <c r="A41" s="29" t="n"/>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>Skyhook</t>
+        </is>
+      </c>
+      <c r="D41" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E41" s="94" t="inlineStr">
+        <is>
+          <t>Shoot the ball. Shot is unaffected by Clamps</t>
+        </is>
+      </c>
+      <c r="F41" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" s="105" t="n"/>
+      <c r="H41" s="106" t="n"/>
+      <c r="I41" s="106" t="n"/>
+      <c r="J41" s="106" t="n"/>
+    </row>
+    <row r="42" ht="28" customHeight="1" s="132">
+      <c r="A42" s="29" t="n"/>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>Slam Dunk</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%. SHOT = 100% if SHOT &gt;= 70%</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Shoot the ball</t>
+        </is>
+      </c>
+      <c r="F42" s="74" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="112" t="n"/>
+      <c r="H42" s="106" t="n"/>
+      <c r="I42" s="106" t="n"/>
+      <c r="J42" s="106" t="n"/>
+    </row>
+    <row r="43" ht="28" customHeight="1" s="132">
+      <c r="A43" s="52" t="n"/>
+      <c r="B43" s="53" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C43" s="69" t="inlineStr">
+        <is>
+          <t>Turnaround Three</t>
+        </is>
+      </c>
+      <c r="D43" s="70" t="inlineStr">
+        <is>
+          <t>Discard any number of cards. SHOT +10% for each</t>
+        </is>
+      </c>
+      <c r="E43" s="70" t="inlineStr">
+        <is>
+          <t>Shoot the ball. +1 Point on make</t>
+        </is>
+      </c>
+      <c r="F43" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="129" t="inlineStr">
+        <is>
+          <t>Only 1 in deck</t>
+        </is>
+      </c>
+      <c r="H43" s="106" t="n"/>
+      <c r="I43" s="106" t="n"/>
+      <c r="J43" s="106" t="n"/>
+    </row>
+    <row r="44" ht="42" customHeight="1" s="132">
+      <c r="A44" s="61" t="n"/>
+      <c r="B44" s="62" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C44" s="66" t="inlineStr">
         <is>
           <t>Euro Step</t>
         </is>
       </c>
-      <c r="D40" s="67" t="inlineStr">
+      <c r="D44" s="67" t="inlineStr">
         <is>
           <t>Flip a coin until you get Tails. For each Heads, SHOT +5% and Draw 1 card</t>
         </is>
       </c>
-      <c r="E40" s="68" t="n"/>
-      <c r="F40" s="85" t="n">
+      <c r="E44" s="68" t="n"/>
+      <c r="F44" s="85" t="n">
         <v>5</v>
       </c>
-      <c r="G40" s="122" t="n"/>
-      <c r="H40" s="104" t="n"/>
-      <c r="I40" s="104" t="n"/>
-      <c r="J40" s="104" t="n"/>
-    </row>
-    <row r="41" ht="20" customHeight="1" s="132">
-      <c r="A41" s="61" t="n"/>
-      <c r="B41" s="62" t="inlineStr">
+      <c r="G44" s="122" t="n"/>
+      <c r="H44" s="104" t="n"/>
+      <c r="I44" s="104" t="n"/>
+      <c r="J44" s="104" t="n"/>
+    </row>
+    <row r="45" ht="42" customHeight="1" s="132">
+      <c r="A45" s="61" t="n"/>
+      <c r="B45" s="62" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C41" s="66" t="inlineStr">
+      <c r="C45" s="66" t="inlineStr">
         <is>
           <t>Wide-Open Three</t>
         </is>
       </c>
-      <c r="D41" s="67" t="inlineStr">
+      <c r="D45" s="67" t="inlineStr">
         <is>
           <t>Select any number of other players. SHOT +10% for each</t>
         </is>
       </c>
-      <c r="E41" s="68" t="inlineStr">
+      <c r="E45" s="68" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make. Selected players receive +1 AST on a make</t>
         </is>
       </c>
-      <c r="F41" s="85" t="n">
+      <c r="F45" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="122" t="inlineStr">
+      <c r="G45" s="122" t="inlineStr">
         <is>
           <t>Selecting none rolls off current SHOT and is still a three</t>
         </is>
       </c>
-      <c r="H41" s="104" t="n"/>
-      <c r="I41" s="104" t="n"/>
-      <c r="J41" s="104" t="n"/>
-    </row>
-    <row r="42" ht="28" customHeight="1" s="132">
-      <c r="A42" s="58" t="inlineStr">
+      <c r="H45" s="104" t="n"/>
+      <c r="I45" s="104" t="n"/>
+      <c r="J45" s="104" t="n"/>
+    </row>
+    <row r="46" ht="29" customHeight="1" s="132" thickBot="1">
+      <c r="A46" s="58" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B42" s="59">
-        <f>COUNTIF($B$5:$B$118,"Clamp")</f>
+      <c r="B46" s="59">
+        <f>COUNTIF($B$5:$B$122,"Clamp")</f>
         <v/>
       </c>
-      <c r="C42" s="60" t="n"/>
-      <c r="D42" s="60" t="n"/>
-      <c r="E42" s="60" t="n"/>
-      <c r="F42" s="86" t="n"/>
-      <c r="G42" s="109" t="n"/>
-      <c r="H42" s="110" t="n"/>
-      <c r="I42" s="110" t="n"/>
-      <c r="J42" s="110" t="n"/>
-    </row>
-    <row r="43" ht="28" customHeight="1" s="132">
-      <c r="A43" s="29" t="n"/>
-      <c r="B43" s="30" t="inlineStr">
+      <c r="C46" s="60" t="n"/>
+      <c r="D46" s="60" t="n"/>
+      <c r="E46" s="60" t="n"/>
+      <c r="F46" s="86" t="n"/>
+      <c r="G46" s="109" t="n"/>
+      <c r="H46" s="110" t="n"/>
+      <c r="I46" s="110" t="n"/>
+      <c r="J46" s="110" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1" s="132">
+      <c r="A47" s="29" t="n"/>
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C43" s="31" t="inlineStr">
+      <c r="C47" s="31" t="inlineStr">
         <is>
           <t>Contest</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Next player SHOT -25% if they shoot</t>
         </is>
       </c>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="76" t="n">
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="76" t="n">
         <v>10</v>
       </c>
-      <c r="G43" s="130" t="inlineStr">
+      <c r="G47" s="130" t="inlineStr">
         <is>
           <t>1 def</t>
         </is>
       </c>
-      <c r="H43" s="102" t="n"/>
-      <c r="I43" s="102" t="n"/>
-      <c r="J43" s="102" t="n"/>
-    </row>
-    <row r="44" ht="42" customHeight="1" s="132">
-      <c r="A44" s="29" t="n"/>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="H47" s="102" t="n"/>
+      <c r="I47" s="102" t="n"/>
+      <c r="J47" s="102" t="n"/>
+    </row>
+    <row r="48" ht="56" customHeight="1" s="132">
+      <c r="A48" s="29" t="n"/>
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C44" s="32" t="inlineStr">
+      <c r="C48" s="32" t="inlineStr">
         <is>
           <t>Double-Team</t>
         </is>
       </c>
-      <c r="D44" s="33" t="inlineStr">
+      <c r="D48" s="33" t="inlineStr">
         <is>
           <t>Next Player cannot play 2 random cards from hand.</t>
         </is>
       </c>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="75" t="n">
+      <c r="E48" s="34" t="n"/>
+      <c r="F48" s="75" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="125" t="inlineStr">
+      <c r="G48" s="125" t="inlineStr">
         <is>
           <t>2 def</t>
         </is>
       </c>
-      <c r="H44" s="102" t="n"/>
-      <c r="I44" s="102" t="n"/>
-      <c r="J44" s="102" t="n"/>
-    </row>
-    <row r="45" ht="42" customHeight="1" s="132">
-      <c r="A45" s="29" t="n"/>
-      <c r="B45" s="30" t="inlineStr">
+      <c r="H48" s="102" t="n"/>
+      <c r="I48" s="102" t="n"/>
+      <c r="J48" s="102" t="n"/>
+    </row>
+    <row r="49" ht="47" customHeight="1" s="132">
+      <c r="A49" s="29" t="n"/>
+      <c r="B49" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C45" s="31" t="inlineStr">
+      <c r="C49" s="31" t="inlineStr">
         <is>
           <t>Full-Court Press</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Next player discards 2 cards at the start of their turn</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="76" t="n">
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="130" t="inlineStr">
+      <c r="G49" s="130" t="inlineStr">
         <is>
           <t>1 def</t>
-        </is>
-      </c>
-      <c r="H45" s="102" t="n"/>
-      <c r="I45" s="102" t="n"/>
-      <c r="J45" s="102" t="n"/>
-    </row>
-    <row r="46" ht="29" customHeight="1" s="132" thickBot="1">
-      <c r="A46" s="29" t="n"/>
-      <c r="B46" s="30" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C46" s="32" t="inlineStr">
-        <is>
-          <t>Trap</t>
-        </is>
-      </c>
-      <c r="D46" s="94" t="inlineStr">
-        <is>
-          <t>Next player can only play Pass cards during their turn</t>
-        </is>
-      </c>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G46" s="125" t="inlineStr">
-        <is>
-          <t>They can still shoot as another option; 3 def</t>
-        </is>
-      </c>
-      <c r="H46" s="102" t="n"/>
-      <c r="I46" s="102" t="n"/>
-      <c r="J46" s="102" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1" s="132">
-      <c r="A47" s="61" t="n"/>
-      <c r="B47" s="62" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C47" s="66" t="inlineStr">
-        <is>
-          <t>Triple-Team</t>
-        </is>
-      </c>
-      <c r="D47" s="67" t="inlineStr">
-        <is>
-          <t>Next player cannot play 3 random cards from hand.</t>
-        </is>
-      </c>
-      <c r="E47" s="68" t="n"/>
-      <c r="F47" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="G47" s="135" t="inlineStr">
-        <is>
-          <t>3 def</t>
-        </is>
-      </c>
-      <c r="H47" s="117" t="n"/>
-      <c r="I47" s="117" t="n"/>
-      <c r="J47" s="117" t="n"/>
-    </row>
-    <row r="48" ht="56" customHeight="1" s="132">
-      <c r="A48" s="58" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="B48" s="59">
-        <f>COUNTIF($B$5:$B$118,"Whistle")</f>
-        <v/>
-      </c>
-      <c r="C48" s="60" t="n"/>
-      <c r="D48" s="60" t="n"/>
-      <c r="E48" s="60" t="n"/>
-      <c r="F48" s="86" t="n"/>
-      <c r="G48" s="109" t="n"/>
-      <c r="H48" s="110" t="n"/>
-      <c r="I48" s="110" t="n"/>
-      <c r="J48" s="110" t="n"/>
-    </row>
-    <row r="49" ht="47" customHeight="1" s="132">
-      <c r="A49" s="29" t="inlineStr">
-        <is>
-          <t>All whistles are limited to 1</t>
-        </is>
-      </c>
-      <c r="B49" s="30" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C49" s="31" t="inlineStr">
-        <is>
-          <t>Back Court Violation</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="138" t="n"/>
-      <c r="G49" s="101" t="inlineStr">
-        <is>
-          <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
         </is>
       </c>
       <c r="H49" s="102" t="n"/>
@@ -3970,98 +3987,109 @@
       <c r="A50" s="29" t="n"/>
       <c r="B50" s="30" t="inlineStr">
         <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C50" s="90" t="inlineStr">
-        <is>
-          <t>Blocking Foul</t>
-        </is>
-      </c>
-      <c r="D50" s="93" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr">
+        <is>
+          <t>Trap</t>
+        </is>
+      </c>
+      <c r="D50" s="94" t="inlineStr">
+        <is>
+          <t>Next player can only play Pass cards during their turn</t>
         </is>
       </c>
       <c r="E50" s="34" t="n"/>
-      <c r="F50" s="138" t="n"/>
-      <c r="G50" s="107" t="n"/>
+      <c r="F50" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" s="125" t="inlineStr">
+        <is>
+          <t>They can still shoot as another option; 3 def</t>
+        </is>
+      </c>
       <c r="H50" s="102" t="n"/>
       <c r="I50" s="102" t="n"/>
       <c r="J50" s="102" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1" s="132">
-      <c r="A51" s="29" t="n"/>
-      <c r="B51" s="30" t="inlineStr">
+      <c r="A51" s="61" t="n"/>
+      <c r="B51" s="62" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C51" s="66" t="inlineStr">
+        <is>
+          <t>Triple-Team</t>
+        </is>
+      </c>
+      <c r="D51" s="67" t="inlineStr">
+        <is>
+          <t>Next player cannot play 3 random cards from hand.</t>
+        </is>
+      </c>
+      <c r="E51" s="68" t="n"/>
+      <c r="F51" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="135" t="inlineStr">
+        <is>
+          <t>3 def</t>
+        </is>
+      </c>
+      <c r="H51" s="117" t="n"/>
+      <c r="I51" s="117" t="n"/>
+      <c r="J51" s="117" t="n"/>
+    </row>
+    <row r="52" ht="28" customHeight="1" s="132">
+      <c r="A52" s="58" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C51" s="31" t="inlineStr">
-        <is>
-          <t>Charge</t>
-        </is>
-      </c>
-      <c r="D51" s="92" t="inlineStr">
-        <is>
-          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="138" t="n"/>
-      <c r="G51" s="101" t="n"/>
-      <c r="H51" s="102" t="n"/>
-      <c r="I51" s="102" t="n"/>
-      <c r="J51" s="102" t="n"/>
-    </row>
-    <row r="52" ht="28" customHeight="1" s="132">
-      <c r="A52" s="29" t="n"/>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="B52" s="59">
+        <f>COUNTIF($B$5:$B$122,"Whistle")</f>
+        <v/>
+      </c>
+      <c r="C52" s="60" t="n"/>
+      <c r="D52" s="60" t="n"/>
+      <c r="E52" s="60" t="n"/>
+      <c r="F52" s="86" t="n"/>
+      <c r="G52" s="109" t="n"/>
+      <c r="H52" s="110" t="n"/>
+      <c r="I52" s="110" t="n"/>
+      <c r="J52" s="110" t="n"/>
+    </row>
+    <row r="53" ht="28" customHeight="1" s="132">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>All whistles are limited to 1</t>
+        </is>
+      </c>
+      <c r="B53" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>Cleared to Play</t>
-        </is>
-      </c>
-      <c r="D52" s="33" t="inlineStr">
-        <is>
-          <t>Injury Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E52" s="34" t="n"/>
-      <c r="F52" s="138" t="n"/>
-      <c r="G52" s="107" t="n"/>
-      <c r="H52" s="102" t="n"/>
-      <c r="I52" s="102" t="n"/>
-      <c r="J52" s="102" t="n"/>
-    </row>
-    <row r="53" ht="28" customHeight="1" s="132">
-      <c r="A53" s="29" t="n"/>
-      <c r="B53" s="30" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>Coach’s Challenge</t>
+          <t>Back Court Violation</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Any Whistle Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>Pull a Timeout from the discards, if one is there, and take it</t>
-        </is>
-      </c>
+          <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="n"/>
       <c r="F53" s="138" t="n"/>
-      <c r="G53" s="101" t="n"/>
+      <c r="G53" s="101" t="inlineStr">
+        <is>
+          <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
+        </is>
+      </c>
       <c r="H53" s="102" t="n"/>
       <c r="I53" s="102" t="n"/>
       <c r="J53" s="102" t="n"/>
@@ -4075,25 +4103,17 @@
       </c>
       <c r="C54" s="90" t="inlineStr">
         <is>
-          <t>Delay-of-Game Warning</t>
-        </is>
-      </c>
-      <c r="D54" s="94" t="inlineStr">
-        <is>
-          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
-        </is>
-      </c>
-      <c r="E54" s="33" t="inlineStr">
-        <is>
-          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
-        </is>
-      </c>
-      <c r="F54" s="139" t="n"/>
-      <c r="G54" s="113" t="inlineStr">
-        <is>
-          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
-        </is>
-      </c>
+          <t>Blocking Foul</t>
+        </is>
+      </c>
+      <c r="D54" s="93" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
+        </is>
+      </c>
+      <c r="E54" s="34" t="n"/>
+      <c r="F54" s="138" t="n"/>
+      <c r="G54" s="107" t="n"/>
       <c r="H54" s="102" t="n"/>
       <c r="I54" s="102" t="n"/>
       <c r="J54" s="102" t="n"/>
@@ -4107,21 +4127,17 @@
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>Double Dribble</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="D55" s="92" t="inlineStr">
+        <is>
+          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
         </is>
       </c>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="138" t="n"/>
-      <c r="G55" s="101" t="inlineStr">
-        <is>
-          <t>The dribbling player inbounds. The round is NOT incremented.</t>
-        </is>
-      </c>
+      <c r="G55" s="101" t="n"/>
       <c r="H55" s="102" t="n"/>
       <c r="I55" s="102" t="n"/>
       <c r="J55" s="102" t="n"/>
@@ -4133,14 +4149,14 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C56" s="90" t="inlineStr">
-        <is>
-          <t>Flagrant Foul</t>
-        </is>
-      </c>
-      <c r="D56" s="94" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>Cleared to Play</t>
+        </is>
+      </c>
+      <c r="D56" s="33" t="inlineStr">
+        <is>
+          <t>Injury Card Played: Cancel card.</t>
         </is>
       </c>
       <c r="E56" s="34" t="n"/>
@@ -4157,17 +4173,21 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C57" s="90" t="inlineStr">
-        <is>
-          <t>Flagrant Foul II</t>
-        </is>
-      </c>
-      <c r="D57" s="91" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="n"/>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>Coach’s Challenge</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Any Whistle Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Pull a Timeout from the discards, if one is there, and take it</t>
+        </is>
+      </c>
       <c r="F57" s="138" t="n"/>
       <c r="G57" s="101" t="n"/>
       <c r="H57" s="102" t="n"/>
@@ -4181,19 +4201,27 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C58" s="32" t="inlineStr">
-        <is>
-          <t>Goaltending</t>
-        </is>
-      </c>
-      <c r="D58" s="33" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
-        </is>
-      </c>
-      <c r="E58" s="34" t="n"/>
-      <c r="F58" s="138" t="n"/>
-      <c r="G58" s="107" t="n"/>
+      <c r="C58" s="90" t="inlineStr">
+        <is>
+          <t>Delay-of-Game Warning</t>
+        </is>
+      </c>
+      <c r="D58" s="94" t="inlineStr">
+        <is>
+          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
+        </is>
+      </c>
+      <c r="E58" s="33" t="inlineStr">
+        <is>
+          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
+        </is>
+      </c>
+      <c r="F58" s="139" t="n"/>
+      <c r="G58" s="113" t="inlineStr">
+        <is>
+          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
+        </is>
+      </c>
       <c r="H58" s="102" t="n"/>
       <c r="I58" s="102" t="n"/>
       <c r="J58" s="102" t="n"/>
@@ -4207,17 +4235,21 @@
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>Inadvertent Whistle</t>
-        </is>
-      </c>
-      <c r="D59" s="91" t="inlineStr">
-        <is>
-          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
+          <t>Double Dribble</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
         </is>
       </c>
       <c r="E59" s="7" t="n"/>
       <c r="F59" s="138" t="n"/>
-      <c r="G59" s="101" t="n"/>
+      <c r="G59" s="101" t="inlineStr">
+        <is>
+          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+        </is>
+      </c>
       <c r="H59" s="102" t="n"/>
       <c r="I59" s="102" t="n"/>
       <c r="J59" s="102" t="n"/>
@@ -4229,14 +4261,14 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C60" s="32" t="inlineStr">
-        <is>
-          <t>Official Review</t>
+      <c r="C60" s="90" t="inlineStr">
+        <is>
+          <t>Flagrant Foul</t>
         </is>
       </c>
       <c r="D60" s="94" t="inlineStr">
         <is>
-          <t>Intangible Played: Discard all Intangibles from player.</t>
+          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
         </is>
       </c>
       <c r="E60" s="34" t="n"/>
@@ -4253,23 +4285,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C61" s="31" t="inlineStr">
-        <is>
-          <t>Shot Clock Violation</t>
+      <c r="C61" s="90" t="inlineStr">
+        <is>
+          <t>Flagrant Foul II</t>
         </is>
       </c>
       <c r="D61" s="91" t="inlineStr">
         <is>
-          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
+          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
         </is>
       </c>
       <c r="E61" s="7" t="n"/>
       <c r="F61" s="138" t="n"/>
-      <c r="G61" s="101" t="inlineStr">
-        <is>
-          <t>This inbound does NOT increment the round.</t>
-        </is>
-      </c>
+      <c r="G61" s="101" t="n"/>
       <c r="H61" s="102" t="n"/>
       <c r="I61" s="102" t="n"/>
       <c r="J61" s="102" t="n"/>
@@ -4283,12 +4311,12 @@
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>Technical Foul</t>
-        </is>
-      </c>
-      <c r="D62" s="94" t="inlineStr">
-        <is>
-          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
+          <t>Goaltending</t>
+        </is>
+      </c>
+      <c r="D62" s="33" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
         </is>
       </c>
       <c r="E62" s="34" t="n"/>
@@ -4307,12 +4335,12 @@
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>Inadvertent Whistle</t>
         </is>
       </c>
       <c r="D63" s="91" t="inlineStr">
         <is>
-          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
         </is>
       </c>
       <c r="E63" s="7" t="n"/>
@@ -4323,183 +4351,175 @@
       <c r="J63" s="102" t="n"/>
     </row>
     <row r="64" ht="20" customHeight="1" s="132">
-      <c r="A64" s="61" t="n"/>
-      <c r="B64" s="62" t="inlineStr">
+      <c r="A64" s="29" t="n"/>
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C64" s="63" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D64" s="64" t="inlineStr">
-        <is>
-          <t>Move card played: Cancel card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E64" s="65" t="n"/>
-      <c r="F64" s="140" t="n"/>
-      <c r="G64" s="116" t="n"/>
-      <c r="H64" s="117" t="n"/>
-      <c r="I64" s="117" t="n"/>
-      <c r="J64" s="117" t="n"/>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>Official Review</t>
+        </is>
+      </c>
+      <c r="D64" s="94" t="inlineStr">
+        <is>
+          <t>Intangible Played: Discard all Intangibles from player.</t>
+        </is>
+      </c>
+      <c r="E64" s="34" t="n"/>
+      <c r="F64" s="138" t="n"/>
+      <c r="G64" s="107" t="n"/>
+      <c r="H64" s="102" t="n"/>
+      <c r="I64" s="102" t="n"/>
+      <c r="J64" s="102" t="n"/>
     </row>
     <row r="65" ht="28" customHeight="1" s="132">
-      <c r="A65" s="61" t="n"/>
-      <c r="B65" s="62" t="inlineStr">
+      <c r="A65" s="29" t="n"/>
+      <c r="B65" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C65" s="63" t="inlineStr">
-        <is>
-          <t>Clear Path Foul</t>
-        </is>
-      </c>
-      <c r="D65" s="64" t="inlineStr">
-        <is>
-          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E65" s="65" t="n"/>
-      <c r="F65" s="140" t="n"/>
-      <c r="G65" s="116" t="inlineStr">
-        <is>
-          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
-        </is>
-      </c>
-      <c r="H65" s="117" t="n"/>
-      <c r="I65" s="117" t="n"/>
-      <c r="J65" s="117" t="n"/>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>Shot Clock Violation</t>
+        </is>
+      </c>
+      <c r="D65" s="91" t="inlineStr">
+        <is>
+          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="138" t="n"/>
+      <c r="G65" s="101" t="inlineStr">
+        <is>
+          <t>This inbound does NOT increment the round.</t>
+        </is>
+      </c>
+      <c r="H65" s="102" t="n"/>
+      <c r="I65" s="102" t="n"/>
+      <c r="J65" s="102" t="n"/>
     </row>
     <row r="66" ht="28" customHeight="1" s="132">
-      <c r="A66" s="58" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="B66" s="59">
-        <f>COUNTIF($B$5:$B$118,"Game Break")</f>
-        <v/>
-      </c>
-      <c r="C66" s="60" t="n"/>
-      <c r="D66" s="60" t="n"/>
-      <c r="E66" s="60" t="n"/>
-      <c r="F66" s="86" t="n"/>
-      <c r="G66" s="109" t="n"/>
-      <c r="H66" s="110" t="n"/>
-      <c r="I66" s="110" t="n"/>
-      <c r="J66" s="110" t="n"/>
+      <c r="A66" s="29" t="n"/>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>Technical Foul</t>
+        </is>
+      </c>
+      <c r="D66" s="94" t="inlineStr">
+        <is>
+          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E66" s="34" t="n"/>
+      <c r="F66" s="138" t="n"/>
+      <c r="G66" s="107" t="n"/>
+      <c r="H66" s="102" t="n"/>
+      <c r="I66" s="102" t="n"/>
+      <c r="J66" s="102" t="n"/>
     </row>
     <row r="67" ht="14" customHeight="1" s="132">
       <c r="A67" s="29" t="n"/>
       <c r="B67" s="30" t="inlineStr">
         <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C67" s="32" t="inlineStr">
-        <is>
-          <t>2-Minute Warning</t>
-        </is>
-      </c>
-      <c r="D67" s="33" t="inlineStr">
-        <is>
-          <t>All players discard down to 2 or fewer cards</t>
-        </is>
-      </c>
-      <c r="E67" s="34" t="n"/>
-      <c r="F67" s="75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G67" s="107" t="n"/>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D67" s="91" t="inlineStr">
+        <is>
+          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="138" t="n"/>
+      <c r="G67" s="101" t="n"/>
       <c r="H67" s="102" t="n"/>
       <c r="I67" s="102" t="n"/>
       <c r="J67" s="102" t="n"/>
     </row>
     <row r="68" ht="14" customHeight="1" s="132">
-      <c r="A68" s="29" t="n"/>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="A68" s="61" t="n"/>
+      <c r="B68" s="62" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C68" s="63" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D68" s="64" t="inlineStr">
+        <is>
+          <t>Move card played: Cancel card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E68" s="65" t="n"/>
+      <c r="F68" s="140" t="n"/>
+      <c r="G68" s="116" t="n"/>
+      <c r="H68" s="117" t="n"/>
+      <c r="I68" s="117" t="n"/>
+      <c r="J68" s="117" t="n"/>
+    </row>
+    <row r="69" ht="14" customHeight="1" s="132">
+      <c r="A69" s="61" t="n"/>
+      <c r="B69" s="62" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C69" s="63" t="inlineStr">
+        <is>
+          <t>Clear Path Foul</t>
+        </is>
+      </c>
+      <c r="D69" s="64" t="inlineStr">
+        <is>
+          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E69" s="65" t="n"/>
+      <c r="F69" s="140" t="n"/>
+      <c r="G69" s="116" t="inlineStr">
+        <is>
+          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
+        </is>
+      </c>
+      <c r="H69" s="117" t="n"/>
+      <c r="I69" s="117" t="n"/>
+      <c r="J69" s="117" t="n"/>
+    </row>
+    <row r="70" ht="28" customHeight="1" s="132">
+      <c r="A70" s="58" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C68" s="31" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="n"/>
-      <c r="F68" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G68" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
-      <c r="H68" s="102" t="n"/>
-      <c r="I68" s="102" t="n"/>
-      <c r="J68" s="102" t="n"/>
-    </row>
-    <row r="69" ht="14" customHeight="1" s="132">
-      <c r="A69" s="29" t="n"/>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D69" s="33" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E69" s="34" t="n"/>
-      <c r="F69" s="75" t="n">
-        <v>14</v>
-      </c>
-      <c r="G69" s="107" t="n"/>
-      <c r="H69" s="102" t="n"/>
-      <c r="I69" s="102" t="n"/>
-      <c r="J69" s="102" t="n"/>
-    </row>
-    <row r="70" ht="28" customHeight="1" s="132">
-      <c r="A70" s="29" t="n"/>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C70" s="31" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="n"/>
-      <c r="F70" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G70" s="101" t="n"/>
-      <c r="H70" s="102" t="n"/>
-      <c r="I70" s="102" t="n"/>
-      <c r="J70" s="102" t="n"/>
+      <c r="B70" s="59">
+        <f>COUNTIF($B$5:$B$122,"Game Break")</f>
+        <v/>
+      </c>
+      <c r="C70" s="60" t="n"/>
+      <c r="D70" s="60" t="n"/>
+      <c r="E70" s="60" t="n"/>
+      <c r="F70" s="86" t="n"/>
+      <c r="G70" s="109" t="n"/>
+      <c r="H70" s="110" t="n"/>
+      <c r="I70" s="110" t="n"/>
+      <c r="J70" s="110" t="n"/>
     </row>
     <row r="71" ht="28" customHeight="1" s="132">
       <c r="A71" s="29" t="n"/>
@@ -4508,19 +4528,19 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C71" s="90" t="inlineStr">
-        <is>
-          <t>Foul</t>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>Take 1 FT</t>
+          <t>All players discard down to 2 or fewer cards</t>
         </is>
       </c>
       <c r="E71" s="34" t="n"/>
       <c r="F71" s="75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G71" s="107" t="n"/>
       <c r="H71" s="102" t="n"/>
@@ -4536,19 +4556,23 @@
       </c>
       <c r="C72" s="31" t="inlineStr">
         <is>
-          <t>MVP Vote</t>
+          <t>Benched</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Draw 3 cards up to a hand of 7</t>
+          <t>Immediately give ball to any other player.</t>
         </is>
       </c>
       <c r="E72" s="7" t="n"/>
       <c r="F72" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="101" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="G72" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H72" s="102" t="n"/>
       <c r="I72" s="102" t="n"/>
       <c r="J72" s="102" t="n"/>
@@ -4562,17 +4586,17 @@
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
-          <t>Off Night</t>
+          <t>Crowd Noise</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
         <is>
-          <t>SHOT -20% this possession</t>
+          <t>Discard 1 card.</t>
         </is>
       </c>
       <c r="E73" s="34" t="n"/>
       <c r="F73" s="75" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G73" s="107" t="n"/>
       <c r="H73" s="102" t="n"/>
@@ -4588,21 +4612,17 @@
       </c>
       <c r="C74" s="31" t="inlineStr">
         <is>
-          <t>Swallowed Whistle</t>
+          <t>Designed Play</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F74" s="74" t="n">
-        <v>5</v>
+          <t>Draw up to a hand of 5</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="n"/>
+      <c r="F74" s="76" t="n">
+        <v>10</v>
       </c>
       <c r="G74" s="101" t="n"/>
       <c r="H74" s="102" t="n"/>
@@ -4616,22 +4636,20 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C75" s="32" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
+      <c r="C75" s="90" t="inlineStr">
+        <is>
+          <t>Foul</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>Players cannot shoot when SHOT is 50% or higher</t>
-        </is>
-      </c>
-      <c r="E75" s="33" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F75" s="80" t="n"/>
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E75" s="34" t="n"/>
+      <c r="F75" s="75" t="n">
+        <v>5</v>
+      </c>
       <c r="G75" s="107" t="n"/>
       <c r="H75" s="102" t="n"/>
       <c r="I75" s="102" t="n"/>
@@ -4646,21 +4664,19 @@
       </c>
       <c r="C76" s="31" t="inlineStr">
         <is>
-          <t>Traded Mid-Game</t>
+          <t>MVP Vote</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Swap positions with random other player</t>
+          <t>Draw 3 cards up to a hand of 7</t>
         </is>
       </c>
       <c r="E76" s="7" t="n"/>
-      <c r="F76" s="76" t="n"/>
-      <c r="G76" s="111" t="inlineStr">
-        <is>
-          <t>Applies to rest of game</t>
-        </is>
-      </c>
+      <c r="F76" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="101" t="n"/>
       <c r="H76" s="102" t="n"/>
       <c r="I76" s="102" t="n"/>
       <c r="J76" s="102" t="n"/>
@@ -4672,21 +4688,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C77" s="134" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D77" s="91" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" s="111" t="n"/>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D77" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E77" s="34" t="n"/>
+      <c r="F77" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="107" t="n"/>
       <c r="H77" s="102" t="n"/>
       <c r="I77" s="102" t="n"/>
       <c r="J77" s="102" t="n"/>
@@ -4698,25 +4714,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C78" s="134" t="inlineStr">
-        <is>
-          <t>All-Swissh Selection</t>
-        </is>
-      </c>
-      <c r="D78" s="91" t="inlineStr">
-        <is>
-          <t>Draw 3 cards after your next make</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="n"/>
-      <c r="F78" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G78" s="111" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+      <c r="C78" s="31" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F78" s="74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" s="101" t="n"/>
       <c r="H78" s="102" t="n"/>
       <c r="I78" s="102" t="n"/>
       <c r="J78" s="102" t="n"/>
@@ -4728,21 +4744,23 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C79" s="134" t="inlineStr">
-        <is>
-          <t>All Star Selection</t>
-        </is>
-      </c>
-      <c r="D79" s="91" t="inlineStr">
-        <is>
-          <t>Draw 2 cards</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="n"/>
-      <c r="F79" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G79" s="111" t="n"/>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D79" s="33" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is 50% or higher</t>
+        </is>
+      </c>
+      <c r="E79" s="33" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F79" s="80" t="n"/>
+      <c r="G79" s="107" t="n"/>
       <c r="H79" s="102" t="n"/>
       <c r="I79" s="102" t="n"/>
       <c r="J79" s="102" t="n"/>
@@ -4754,23 +4772,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C80" s="134" t="inlineStr">
-        <is>
-          <t>Hit the Bike</t>
-        </is>
-      </c>
-      <c r="D80" s="91" t="inlineStr">
-        <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+      <c r="C80" s="31" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Swap positions with random other player</t>
         </is>
       </c>
       <c r="E80" s="7" t="n"/>
-      <c r="F80" s="76" t="n">
-        <v>5</v>
-      </c>
+      <c r="F80" s="76" t="n"/>
       <c r="G80" s="111" t="inlineStr">
         <is>
-          <t>This is not a pass</t>
+          <t>Applies to rest of game</t>
         </is>
       </c>
       <c r="H80" s="102" t="n"/>
@@ -4786,17 +4802,17 @@
       </c>
       <c r="C81" s="134" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D81" s="91" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G81" s="111" t="n"/>
       <c r="H81" s="102" t="n"/>
@@ -4812,21 +4828,21 @@
       </c>
       <c r="C82" s="134" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D82" s="91" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G82" s="111" t="inlineStr">
         <is>
-          <t>Deck ones are shown face down</t>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
         </is>
       </c>
       <c r="H82" s="102" t="n"/>
@@ -4842,23 +4858,19 @@
       </c>
       <c r="C83" s="134" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D83" s="91" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G83" s="111" t="inlineStr">
-        <is>
-          <t>This is a bad thing in the NBA</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G83" s="111" t="n"/>
       <c r="H83" s="102" t="n"/>
       <c r="I83" s="102" t="n"/>
       <c r="J83" s="102" t="n"/>
@@ -4872,21 +4884,21 @@
       </c>
       <c r="C84" s="134" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D84" s="91" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G84" s="111" t="inlineStr">
         <is>
-          <t>The hex travels in the declared direction too</t>
+          <t>This is not a pass</t>
         </is>
       </c>
       <c r="H84" s="102" t="n"/>
@@ -4902,17 +4914,17 @@
       </c>
       <c r="C85" s="134" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D85" s="91" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G85" s="111" t="n"/>
       <c r="H85" s="102" t="n"/>
@@ -4928,19 +4940,23 @@
       </c>
       <c r="C86" s="134" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D86" s="91" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="76" t="n">
         <v>2</v>
       </c>
-      <c r="G86" s="111" t="n"/>
+      <c r="G86" s="111" t="inlineStr">
+        <is>
+          <t>Deck ones are shown face down</t>
+        </is>
+      </c>
       <c r="H86" s="102" t="n"/>
       <c r="I86" s="102" t="n"/>
       <c r="J86" s="102" t="n"/>
@@ -4954,38 +4970,53 @@
       </c>
       <c r="C87" s="134" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D87" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G87" s="111" t="n"/>
+      <c r="G87" s="111" t="inlineStr">
+        <is>
+          <t>This is a bad thing in the NBA</t>
+        </is>
+      </c>
       <c r="H87" s="102" t="n"/>
       <c r="I87" s="102" t="n"/>
       <c r="J87" s="102" t="n"/>
     </row>
     <row r="88" ht="28" customHeight="1" s="132">
-      <c r="A88" s="55" t="inlineStr">
-        <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="B88" s="56">
-        <f>COUNTIF($B$5:$B$118,"Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C88" s="57" t="n"/>
-      <c r="D88" s="57" t="n"/>
-      <c r="E88" s="57" t="n"/>
-      <c r="F88" s="88" t="n"/>
-      <c r="G88" s="108" t="n"/>
+      <c r="A88" s="29" t="n"/>
+      <c r="B88" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C88" s="134" t="inlineStr">
+        <is>
+          <t>Trade Deadline</t>
+        </is>
+      </c>
+      <c r="D88" s="91" t="inlineStr">
+        <is>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="n"/>
+      <c r="F88" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G88" s="111" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H88" s="102" t="n"/>
       <c r="I88" s="102" t="n"/>
       <c r="J88" s="102" t="n"/>
@@ -4994,79 +5025,88 @@
       <c r="A89" s="29" t="n"/>
       <c r="B89" s="30" t="inlineStr">
         <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="C89" s="31" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C89" s="134" t="inlineStr">
+        <is>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D89" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G89" s="101" t="n"/>
+      <c r="G89" s="111" t="n"/>
       <c r="H89" s="102" t="n"/>
       <c r="I89" s="102" t="n"/>
       <c r="J89" s="102" t="n"/>
     </row>
     <row r="90" ht="28" customHeight="1" s="132">
-      <c r="A90" s="58" t="inlineStr">
-        <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="B90" s="59">
-        <f>COUNTIF($B$5:$B$118,"Devastating Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C90" s="60" t="n"/>
-      <c r="D90" s="60" t="n"/>
-      <c r="E90" s="60" t="n"/>
-      <c r="F90" s="86" t="n"/>
-      <c r="G90" s="109" t="n"/>
-      <c r="H90" s="110" t="n"/>
-      <c r="I90" s="110" t="n"/>
-      <c r="J90" s="110" t="n"/>
+      <c r="A90" s="29" t="n"/>
+      <c r="B90" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C90" s="134" t="inlineStr">
+        <is>
+          <t>Official Timeout</t>
+        </is>
+      </c>
+      <c r="D90" s="91" t="inlineStr">
+        <is>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="n"/>
+      <c r="F90" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="111" t="n"/>
+      <c r="H90" s="102" t="n"/>
+      <c r="I90" s="102" t="n"/>
+      <c r="J90" s="102" t="n"/>
     </row>
     <row r="91" ht="42" customHeight="1" s="132">
-      <c r="A91" s="50" t="n"/>
-      <c r="B91" s="51" t="inlineStr">
-        <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="C91" s="136" t="inlineStr">
-        <is>
-          <t>Torn Achilles</t>
-        </is>
-      </c>
-      <c r="D91" s="137" t="inlineStr">
-        <is>
-          <t>Hand is locked every turn except 1 card (randomly)</t>
-        </is>
-      </c>
-      <c r="E91" s="54" t="n"/>
-      <c r="F91" s="141" t="n"/>
-      <c r="G91" s="114" t="n"/>
-      <c r="H91" s="115" t="n"/>
-      <c r="I91" s="115" t="n"/>
-      <c r="J91" s="115" t="n"/>
+      <c r="A91" s="29" t="n"/>
+      <c r="B91" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C91" s="134" t="inlineStr">
+        <is>
+          <t>Team Doctor</t>
+        </is>
+      </c>
+      <c r="D91" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="n"/>
+      <c r="F91" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" s="111" t="n"/>
+      <c r="H91" s="102" t="n"/>
+      <c r="I91" s="102" t="n"/>
+      <c r="J91" s="102" t="n"/>
     </row>
     <row r="92" ht="14" customHeight="1" s="132">
       <c r="A92" s="55" t="inlineStr">
         <is>
-          <t>Intangible</t>
+          <t>Injury GB</t>
         </is>
       </c>
       <c r="B92" s="56">
-        <f>COUNTIF($B$5:$B$118,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$122,"Injury GB")</f>
         <v/>
       </c>
       <c r="C92" s="57" t="n"/>
@@ -5079,107 +5119,99 @@
       <c r="J92" s="102" t="n"/>
     </row>
     <row r="93" ht="28" customHeight="1" s="132">
-      <c r="A93" s="96" t="inlineStr">
-        <is>
-          <t>All intangibles are limited to 1</t>
-        </is>
-      </c>
+      <c r="A93" s="29" t="n"/>
       <c r="B93" s="30" t="inlineStr">
         <is>
-          <t>Intangible</t>
+          <t>Injury GB</t>
         </is>
       </c>
       <c r="C93" s="31" t="inlineStr">
         <is>
-          <t>Board-Crasher</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% upon Rebounding your own missed shot</t>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D93" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="138" t="n"/>
+      <c r="F93" s="76" t="n">
+        <v>3</v>
+      </c>
       <c r="G93" s="101" t="n"/>
       <c r="H93" s="102" t="n"/>
       <c r="I93" s="102" t="n"/>
       <c r="J93" s="102" t="n"/>
     </row>
     <row r="94" ht="28" customHeight="1" s="132">
-      <c r="A94" s="29" t="n"/>
-      <c r="B94" s="30" t="inlineStr">
+      <c r="A94" s="58" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="B94" s="59">
+        <f>COUNTIF($B$5:$B$122,"Devastating Injury GB")</f>
+        <v/>
+      </c>
+      <c r="C94" s="60" t="n"/>
+      <c r="D94" s="60" t="n"/>
+      <c r="E94" s="60" t="n"/>
+      <c r="F94" s="86" t="n"/>
+      <c r="G94" s="109" t="n"/>
+      <c r="H94" s="110" t="n"/>
+      <c r="I94" s="110" t="n"/>
+      <c r="J94" s="110" t="n"/>
+    </row>
+    <row r="95" ht="28" customHeight="1" s="132">
+      <c r="A95" s="50" t="n"/>
+      <c r="B95" s="51" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="C95" s="136" t="inlineStr">
+        <is>
+          <t>Torn Achilles</t>
+        </is>
+      </c>
+      <c r="D95" s="137" t="inlineStr">
+        <is>
+          <t>Hand is locked every turn except 1 card (randomly)</t>
+        </is>
+      </c>
+      <c r="E95" s="54" t="n"/>
+      <c r="F95" s="141" t="n"/>
+      <c r="G95" s="114" t="n"/>
+      <c r="H95" s="115" t="n"/>
+      <c r="I95" s="115" t="n"/>
+      <c r="J95" s="115" t="n"/>
+    </row>
+    <row r="96" ht="28" customHeight="1" s="132">
+      <c r="A96" s="55" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C94" s="32" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D94" s="33" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E94" s="34" t="n"/>
-      <c r="F94" s="138" t="n"/>
-      <c r="G94" s="107" t="n"/>
-      <c r="H94" s="102" t="n"/>
-      <c r="I94" s="102" t="n"/>
-      <c r="J94" s="102" t="n"/>
-    </row>
-    <row r="95" ht="28" customHeight="1" s="132">
-      <c r="A95" s="29" t="n"/>
-      <c r="B95" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C95" s="31" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="n"/>
-      <c r="F95" s="138" t="n"/>
-      <c r="G95" s="101" t="n"/>
-      <c r="H95" s="102" t="n"/>
-      <c r="I95" s="102" t="n"/>
-      <c r="J95" s="102" t="n"/>
-    </row>
-    <row r="96" ht="28" customHeight="1" s="132">
-      <c r="A96" s="29" t="n"/>
-      <c r="B96" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C96" s="32" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D96" s="33" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
-        </is>
-      </c>
-      <c r="E96" s="34" t="n"/>
-      <c r="F96" s="138" t="n"/>
-      <c r="G96" s="107" t="n"/>
+      <c r="B96" s="56">
+        <f>COUNTIF($B$5:$B$122,"Intangible")</f>
+        <v/>
+      </c>
+      <c r="C96" s="57" t="n"/>
+      <c r="D96" s="57" t="n"/>
+      <c r="E96" s="57" t="n"/>
+      <c r="F96" s="88" t="n"/>
+      <c r="G96" s="108" t="n"/>
       <c r="H96" s="102" t="n"/>
       <c r="I96" s="102" t="n"/>
       <c r="J96" s="102" t="n"/>
     </row>
     <row r="97" ht="42" customHeight="1" s="132">
-      <c r="A97" s="29" t="n"/>
+      <c r="A97" s="96" t="inlineStr">
+        <is>
+          <t>All intangibles are limited to 1</t>
+        </is>
+      </c>
       <c r="B97" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
@@ -5187,20 +5219,16 @@
       </c>
       <c r="C97" s="31" t="inlineStr">
         <is>
-          <t>Fox-Like First Step</t>
+          <t>Board-Crasher</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F97" s="139" t="n"/>
+          <t>SHOT +10% upon Rebounding your own missed shot</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="138" t="n"/>
       <c r="G97" s="101" t="n"/>
       <c r="H97" s="102" t="n"/>
       <c r="I97" s="102" t="n"/>
@@ -5213,19 +5241,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C98" s="90" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D98" s="94" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
+      <c r="C98" s="32" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D98" s="33" t="inlineStr">
+        <is>
+          <t>Additional SHOT +10% on all received passes</t>
         </is>
       </c>
       <c r="E98" s="34" t="n"/>
       <c r="F98" s="138" t="n"/>
-      <c r="G98" s="125" t="n"/>
+      <c r="G98" s="107" t="n"/>
       <c r="H98" s="102" t="n"/>
       <c r="I98" s="102" t="n"/>
       <c r="J98" s="102" t="n"/>
@@ -5237,14 +5265,14 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C99" s="90" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D99" s="91" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
+      <c r="C99" s="31" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -5263,12 +5291,12 @@
       </c>
       <c r="C100" s="32" t="inlineStr">
         <is>
-          <t>Gravity</t>
+          <t>Floor General</t>
         </is>
       </c>
       <c r="D100" s="33" t="inlineStr">
         <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
         </is>
       </c>
       <c r="E100" s="34" t="n"/>
@@ -5287,16 +5315,20 @@
       </c>
       <c r="C101" s="31" t="inlineStr">
         <is>
-          <t>Great Conditioning</t>
+          <t>Fox-Like First Step</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="n"/>
-      <c r="F101" s="138" t="n"/>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F101" s="139" t="n"/>
       <c r="G101" s="101" t="n"/>
       <c r="H101" s="102" t="n"/>
       <c r="I101" s="102" t="n"/>
@@ -5309,19 +5341,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C102" s="32" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D102" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +20% if you scored last round.</t>
+      <c r="C102" s="90" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D102" s="94" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
         </is>
       </c>
       <c r="E102" s="34" t="n"/>
       <c r="F102" s="138" t="n"/>
-      <c r="G102" s="107" t="n"/>
+      <c r="G102" s="125" t="n"/>
       <c r="H102" s="102" t="n"/>
       <c r="I102" s="102" t="n"/>
       <c r="J102" s="102" t="n"/>
@@ -5333,14 +5365,14 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C103" s="31" t="inlineStr">
-        <is>
-          <t>Like That</t>
+      <c r="C103" s="90" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
         </is>
       </c>
       <c r="D103" s="91" t="inlineStr">
         <is>
-          <t>Your SHOT % cannot be reduced</t>
+          <t>Take 1 additional FT</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -5359,21 +5391,17 @@
       </c>
       <c r="C104" s="32" t="inlineStr">
         <is>
-          <t>No Bag</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="D104" s="33" t="inlineStr">
         <is>
-          <t>Cannot activate Move cards this round</t>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
         </is>
       </c>
       <c r="E104" s="34" t="n"/>
       <c r="F104" s="138" t="n"/>
-      <c r="G104" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G104" s="107" t="n"/>
       <c r="H104" s="102" t="n"/>
       <c r="I104" s="102" t="n"/>
       <c r="J104" s="102" t="n"/>
@@ -5387,12 +5415,12 @@
       </c>
       <c r="C105" s="31" t="inlineStr">
         <is>
-          <t>Point God</t>
+          <t>Great Conditioning</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>Draw 1 card following each of your passes</t>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -5411,21 +5439,17 @@
       </c>
       <c r="C106" s="32" t="inlineStr">
         <is>
-          <t>Shooting Slump</t>
+          <t>Hot Hand</t>
         </is>
       </c>
       <c r="D106" s="33" t="inlineStr">
         <is>
-          <t>SHOT -20% this round</t>
+          <t>SHOT +20% if you scored last round.</t>
         </is>
       </c>
       <c r="E106" s="34" t="n"/>
       <c r="F106" s="138" t="n"/>
-      <c r="G106" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G106" s="107" t="n"/>
       <c r="H106" s="102" t="n"/>
       <c r="I106" s="102" t="n"/>
       <c r="J106" s="102" t="n"/>
@@ -5439,12 +5463,12 @@
       </c>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D107" s="91" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
         </is>
       </c>
       <c r="E107" s="7" t="n"/>
@@ -5463,17 +5487,21 @@
       </c>
       <c r="C108" s="32" t="inlineStr">
         <is>
-          <t>Sixth Man</t>
+          <t>No Bag</t>
         </is>
       </c>
       <c r="D108" s="33" t="inlineStr">
         <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
+          <t>Cannot activate Move cards this round</t>
         </is>
       </c>
       <c r="E108" s="34" t="n"/>
       <c r="F108" s="138" t="n"/>
-      <c r="G108" s="107" t="n"/>
+      <c r="G108" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H108" s="102" t="n"/>
       <c r="I108" s="102" t="n"/>
       <c r="J108" s="102" t="n"/>
@@ -5487,12 +5515,12 @@
       </c>
       <c r="C109" s="31" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Point God</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
+          <t>Draw 1 card following each of your passes</t>
         </is>
       </c>
       <c r="E109" s="7" t="n"/>
@@ -5511,17 +5539,21 @@
       </c>
       <c r="C110" s="32" t="inlineStr">
         <is>
-          <t>Splash Cousin</t>
+          <t>Shooting Slump</t>
         </is>
       </c>
       <c r="D110" s="33" t="inlineStr">
         <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
+          <t>SHOT -20% this round</t>
         </is>
       </c>
       <c r="E110" s="34" t="n"/>
       <c r="F110" s="138" t="n"/>
-      <c r="G110" s="107" t="n"/>
+      <c r="G110" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H110" s="102" t="n"/>
       <c r="I110" s="102" t="n"/>
       <c r="J110" s="102" t="n"/>
@@ -5535,12 +5567,12 @@
       </c>
       <c r="C111" s="31" t="inlineStr">
         <is>
-          <t>Unguardable</t>
-        </is>
-      </c>
-      <c r="D111" s="91" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
         </is>
       </c>
       <c r="E111" s="7" t="n"/>
@@ -5559,121 +5591,120 @@
       </c>
       <c r="C112" s="32" t="inlineStr">
         <is>
-          <t>Lethal Shooter</t>
+          <t>Sixth Man</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
         </is>
       </c>
       <c r="E112" s="34" t="n"/>
       <c r="F112" s="138" t="n"/>
-      <c r="G112" s="113" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G112" s="107" t="n"/>
       <c r="H112" s="102" t="n"/>
       <c r="I112" s="102" t="n"/>
       <c r="J112" s="102" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="61" t="n"/>
-      <c r="B113" s="62" t="inlineStr">
+      <c r="A113" s="29" t="n"/>
+      <c r="B113" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C113" s="66" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D113" s="95" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E113" s="68" t="n"/>
-      <c r="F113" s="140" t="n"/>
-      <c r="G113" s="126" t="n"/>
-      <c r="H113" s="117" t="n"/>
-      <c r="I113" s="117" t="n"/>
-      <c r="J113" s="117" t="n"/>
+      <c r="C113" s="31" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="138" t="n"/>
+      <c r="G113" s="101" t="n"/>
+      <c r="H113" s="102" t="n"/>
+      <c r="I113" s="102" t="n"/>
+      <c r="J113" s="102" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="61" t="n"/>
-      <c r="B114" s="62" t="inlineStr">
+      <c r="A114" s="29" t="n"/>
+      <c r="B114" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C114" s="66" t="inlineStr">
-        <is>
-          <t>Unselfish</t>
-        </is>
-      </c>
-      <c r="D114" s="95" t="inlineStr">
-        <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
-        </is>
-      </c>
-      <c r="E114" s="68" t="n"/>
-      <c r="F114" s="140" t="n"/>
-      <c r="G114" s="126" t="n"/>
-      <c r="H114" s="117" t="n"/>
-      <c r="I114" s="117" t="n"/>
-      <c r="J114" s="117" t="n"/>
+      <c r="C114" s="32" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D114" s="33" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E114" s="34" t="n"/>
+      <c r="F114" s="138" t="n"/>
+      <c r="G114" s="107" t="n"/>
+      <c r="H114" s="102" t="n"/>
+      <c r="I114" s="102" t="n"/>
+      <c r="J114" s="102" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="61" t="n"/>
-      <c r="B115" s="62" t="inlineStr">
+      <c r="A115" s="29" t="n"/>
+      <c r="B115" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C115" s="66" t="inlineStr">
-        <is>
-          <t>Dirty Player</t>
-        </is>
-      </c>
-      <c r="D115" s="95" t="inlineStr">
-        <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
-        </is>
-      </c>
-      <c r="E115" s="68" t="n"/>
-      <c r="F115" s="140" t="n"/>
-      <c r="G115" s="126" t="n"/>
-      <c r="H115" s="117" t="n"/>
-      <c r="I115" s="117" t="n"/>
-      <c r="J115" s="117" t="n"/>
+      <c r="C115" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D115" s="91" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="138" t="n"/>
+      <c r="G115" s="101" t="n"/>
+      <c r="H115" s="102" t="n"/>
+      <c r="I115" s="102" t="n"/>
+      <c r="J115" s="102" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="61" t="n"/>
-      <c r="B116" s="62" t="inlineStr">
+      <c r="A116" s="29" t="n"/>
+      <c r="B116" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C116" s="66" t="inlineStr">
-        <is>
-          <t>Villainous Reputation</t>
-        </is>
-      </c>
-      <c r="D116" s="95" t="inlineStr">
-        <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
-        </is>
-      </c>
-      <c r="E116" s="68" t="n"/>
-      <c r="F116" s="140" t="n"/>
-      <c r="G116" s="126" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="C116" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D116" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E116" s="34" t="n"/>
+      <c r="F116" s="138" t="n"/>
+      <c r="G116" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H116" s="102" t="n"/>
+      <c r="I116" s="102" t="n"/>
+      <c r="J116" s="102" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="61" t="n"/>
@@ -5684,21 +5715,20 @@
       </c>
       <c r="C117" s="66" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D117" s="95" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E117" s="68" t="n"/>
       <c r="F117" s="140" t="n"/>
-      <c r="G117" s="126" t="inlineStr">
-        <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
-        </is>
-      </c>
+      <c r="G117" s="126" t="n"/>
+      <c r="H117" s="117" t="n"/>
+      <c r="I117" s="117" t="n"/>
+      <c r="J117" s="117" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="61" t="n"/>
@@ -5709,12 +5739,12 @@
       </c>
       <c r="C118" s="66" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D118" s="95" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E118" s="68" t="n"/>
@@ -5724,12 +5754,111 @@
       <c r="I118" s="117" t="n"/>
       <c r="J118" s="117" t="n"/>
     </row>
+    <row r="119">
+      <c r="A119" s="61" t="n"/>
+      <c r="B119" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C119" s="66" t="inlineStr">
+        <is>
+          <t>Dirty Player</t>
+        </is>
+      </c>
+      <c r="D119" s="95" t="inlineStr">
+        <is>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+        </is>
+      </c>
+      <c r="E119" s="68" t="n"/>
+      <c r="F119" s="140" t="n"/>
+      <c r="G119" s="126" t="n"/>
+      <c r="H119" s="117" t="n"/>
+      <c r="I119" s="117" t="n"/>
+      <c r="J119" s="117" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="61" t="n"/>
+      <c r="B120" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C120" s="66" t="inlineStr">
+        <is>
+          <t>Villainous Reputation</t>
+        </is>
+      </c>
+      <c r="D120" s="95" t="inlineStr">
+        <is>
+          <t>Discard 1 whenever any Whistle triggers</t>
+        </is>
+      </c>
+      <c r="E120" s="68" t="n"/>
+      <c r="F120" s="140" t="n"/>
+      <c r="G120" s="126" t="inlineStr">
+        <is>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="61" t="n"/>
+      <c r="B121" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C121" s="66" t="inlineStr">
+        <is>
+          <t>Free Agent</t>
+        </is>
+      </c>
+      <c r="D121" s="95" t="inlineStr">
+        <is>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+        </is>
+      </c>
+      <c r="E121" s="68" t="n"/>
+      <c r="F121" s="140" t="n"/>
+      <c r="G121" s="126" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="61" t="n"/>
+      <c r="B122" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C122" s="66" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D122" s="95" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E122" s="68" t="n"/>
+      <c r="F122" s="140" t="n"/>
+      <c r="G122" s="126" t="n"/>
+      <c r="H122" s="117" t="n"/>
+      <c r="I122" s="117" t="n"/>
+      <c r="J122" s="117" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="109">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G119:J119"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>
@@ -5743,47 +5872,50 @@
     <mergeCell ref="G57:J57"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
+    <mergeCell ref="G53:J53"/>
     <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G53:J53"/>
     <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="G108:J108"/>
+    <mergeCell ref="G114:J114"/>
     <mergeCell ref="G58:J58"/>
-    <mergeCell ref="G114:J114"/>
     <mergeCell ref="G110:J110"/>
+    <mergeCell ref="G113:J113"/>
+    <mergeCell ref="G100:J100"/>
     <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="G85:J85"/>
+    <mergeCell ref="G94:J94"/>
     <mergeCell ref="G91:J91"/>
-    <mergeCell ref="G100:J100"/>
-    <mergeCell ref="G94:J94"/>
+    <mergeCell ref="G44:J44"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="G31:J31"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G77:J77"/>
     <mergeCell ref="G86:J86"/>
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="G61:J61"/>
     <mergeCell ref="G70:J70"/>
     <mergeCell ref="G48:J48"/>
+    <mergeCell ref="G23:J23"/>
     <mergeCell ref="G97:J97"/>
+    <mergeCell ref="G38:J38"/>
     <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G38:J38"/>
     <mergeCell ref="G112:J112"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="G62:J62"/>
     <mergeCell ref="G49:J49"/>
+    <mergeCell ref="G24:J24"/>
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="G104:J104"/>
     <mergeCell ref="G65:J65"/>
-    <mergeCell ref="G88:J88"/>
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="G35:J35"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G76:J76"/>
+    <mergeCell ref="G25:J25"/>
     <mergeCell ref="G90:J90"/>
     <mergeCell ref="G99:J99"/>
     <mergeCell ref="G60:J60"/>
@@ -5791,20 +5923,22 @@
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G117:J117"/>
     <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G101:J101"/>
+    <mergeCell ref="G116:J116"/>
+    <mergeCell ref="G37:J37"/>
     <mergeCell ref="G103:J103"/>
-    <mergeCell ref="G113:J113"/>
-    <mergeCell ref="G37:J37"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
-    <mergeCell ref="G87:J87"/>
     <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="G80:J80"/>
     <mergeCell ref="G95:J95"/>
     <mergeCell ref="G89:J89"/>
+    <mergeCell ref="G79:J79"/>
     <mergeCell ref="G64:J64"/>
     <mergeCell ref="G73:J73"/>
     <mergeCell ref="G51:J51"/>
@@ -5818,16 +5952,14 @@
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
-    <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
+    <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
     <mergeCell ref="G107:J107"/>
-    <mergeCell ref="G36:J36"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G93:J93"/>
     <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G93:J93"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G92:J92"/>
     <mergeCell ref="G30:J30"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2626,35 +2626,35 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$122,"Pass")</f>
+        <f>COUNTIF($B$5:$B$123,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$122,"Move")+COUNTIF($B$5:$B$122,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$123,"Move")+COUNTIF($B$5:$B$123,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$122,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$123,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$122,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$123,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$122,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$123,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$122,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$123,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$122,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$123,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$122,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$123,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$122,"Pass")</f>
+        <f>COUNTIF($B$5:$B$123,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="23" t="n"/>
@@ -3082,79 +3082,79 @@
       <c r="J18" s="104" t="n"/>
     </row>
     <row r="19" ht="56" customHeight="1" s="132">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>Right Back</t>
+        </is>
+      </c>
+      <c r="D19" s="38" t="inlineStr">
+        <is>
+          <t>SHOT +5%. Pass to player of choice. They immediately pass it back</t>
+        </is>
+      </c>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" s="127" t="inlineStr">
+        <is>
+          <t>Results in a draw for each player and SHOT +10% overall. Whatever the trip costs them happens in between</t>
+        </is>
+      </c>
+      <c r="H19" s="104" t="n"/>
+      <c r="I19" s="104" t="n"/>
+      <c r="J19" s="104" t="n"/>
+    </row>
+    <row r="20" ht="14" customHeight="1" s="132">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="B19" s="40">
-        <f>COUNTIF($B$5:$B$122,"Move")+COUNTIF($B$5:$B$122,"Special Move")</f>
+      <c r="B20" s="40">
+        <f>COUNTIF($B$5:$B$123,"Move")+COUNTIF($B$5:$B$123,"Special Move")</f>
         <v/>
       </c>
-      <c r="C19" s="41" t="n"/>
-      <c r="D19" s="41" t="n"/>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="78" t="n"/>
-      <c r="G19" s="120" t="n"/>
-      <c r="H19" s="121" t="n"/>
-      <c r="I19" s="121" t="n"/>
-      <c r="J19" s="121" t="n"/>
-    </row>
-    <row r="20" ht="14" customHeight="1" s="132">
-      <c r="A20" s="45" t="n"/>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="C20" s="41" t="n"/>
+      <c r="D20" s="41" t="n"/>
+      <c r="E20" s="41" t="n"/>
+      <c r="F20" s="78" t="n"/>
+      <c r="G20" s="120" t="n"/>
+      <c r="H20" s="121" t="n"/>
+      <c r="I20" s="121" t="n"/>
+      <c r="J20" s="121" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1" s="132">
+      <c r="A21" s="45" t="n"/>
+      <c r="B21" s="46" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>Dribble</t>
         </is>
       </c>
-      <c r="D20" s="48" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>Draw 1 card. SHOT -10%</t>
         </is>
       </c>
-      <c r="E20" s="49" t="n"/>
-      <c r="F20" s="79" t="n">
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="79" t="n">
         <v>15</v>
       </c>
-      <c r="G20" s="118" t="n"/>
-      <c r="H20" s="119" t="n"/>
-      <c r="I20" s="119" t="n"/>
-      <c r="J20" s="119" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" s="132">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>Move</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Following Dribble: SHOT +10%</t>
-        </is>
-      </c>
-      <c r="F21" s="74" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="101" t="n"/>
-      <c r="H21" s="102" t="n"/>
-      <c r="I21" s="102" t="n"/>
-      <c r="J21" s="102" t="n"/>
+      <c r="G21" s="118" t="n"/>
+      <c r="H21" s="119" t="n"/>
+      <c r="I21" s="119" t="n"/>
+      <c r="J21" s="119" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1" s="132">
       <c r="A22" s="29" t="n"/>
@@ -3163,21 +3163,25 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
-        <is>
-          <t>Ankle Breaker</t>
-        </is>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>Target player discards 1 card. SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E22" s="34" t="n"/>
-      <c r="F22" s="75" t="n">
-        <v>10</v>
-      </c>
-      <c r="G22" s="107" t="n"/>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Following Dribble: SHOT +10%</t>
+        </is>
+      </c>
+      <c r="F22" s="74" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" s="101" t="n"/>
       <c r="H22" s="102" t="n"/>
       <c r="I22" s="102" t="n"/>
       <c r="J22" s="102" t="n"/>
@@ -3189,25 +3193,21 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C23" s="90" t="inlineStr">
-        <is>
-          <t>Flop</t>
-        </is>
-      </c>
-      <c r="D23" s="91" t="inlineStr">
-        <is>
-          <t>Cancel Clamps. Take 1 FT for each. If no Clamps on you, TOV +1</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" s="130" t="inlineStr">
-        <is>
-          <t>Take 1 FT attempt for each Clamp on you and cancel it. If no Clamps on you, TOV +1</t>
-        </is>
-      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>Ankle Breaker</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Target player discards 1 card. SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="75" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" s="107" t="n"/>
       <c r="H23" s="102" t="n"/>
       <c r="I23" s="102" t="n"/>
       <c r="J23" s="102" t="n"/>
@@ -3219,25 +3219,25 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
-        <is>
-          <t>Hesi</t>
-        </is>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>Shot Clock -1</t>
-        </is>
-      </c>
-      <c r="F24" s="80" t="n">
-        <v>15</v>
-      </c>
-      <c r="G24" s="107" t="n"/>
+      <c r="C24" s="90" t="inlineStr">
+        <is>
+          <t>Flop</t>
+        </is>
+      </c>
+      <c r="D24" s="91" t="inlineStr">
+        <is>
+          <t>Cancel Clamps. Take 1 FT for each. If no Clamps on you, TOV +1</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="130" t="inlineStr">
+        <is>
+          <t>Take 1 FT attempt for each Clamp on you and cancel it. If no Clamps on you, TOV +1</t>
+        </is>
+      </c>
       <c r="H24" s="102" t="n"/>
       <c r="I24" s="102" t="n"/>
       <c r="J24" s="102" t="n"/>
@@ -3249,25 +3249,25 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>Pump Fake</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>Hesi</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Cancel all Clamps on you</t>
-        </is>
-      </c>
-      <c r="F25" s="74" t="n">
-        <v>12</v>
-      </c>
-      <c r="G25" s="101" t="n"/>
+      <c r="E25" s="33" t="inlineStr">
+        <is>
+          <t>Shot Clock -1</t>
+        </is>
+      </c>
+      <c r="F25" s="80" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" s="107" t="n"/>
       <c r="H25" s="102" t="n"/>
       <c r="I25" s="102" t="n"/>
       <c r="J25" s="102" t="n"/>
@@ -3279,21 +3279,25 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
-        <is>
-          <t>Rhythm Dribble</t>
-        </is>
-      </c>
-      <c r="D26" s="33" t="inlineStr">
-        <is>
-          <t>Draw 1 card. SHOT +10%. Shot Clock -1</t>
-        </is>
-      </c>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" s="107" t="n"/>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>Pump Fake</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Cancel all Clamps on you</t>
+        </is>
+      </c>
+      <c r="F26" s="74" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" s="101" t="n"/>
       <c r="H26" s="102" t="n"/>
       <c r="I26" s="102" t="n"/>
       <c r="J26" s="102" t="n"/>
@@ -3305,14 +3309,14 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C27" s="133" t="inlineStr">
-        <is>
-          <t>Pound Dribble</t>
-        </is>
-      </c>
-      <c r="D27" s="94" t="inlineStr">
-        <is>
-          <t>Draw 2 cards then Discard 1. SHOT +10% Shot Clock -1</t>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>Rhythm Dribble</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>Draw 1 card. SHOT +10%. Shot Clock -1</t>
         </is>
       </c>
       <c r="E27" s="34" t="n"/>
@@ -3333,23 +3337,19 @@
       </c>
       <c r="C28" s="133" t="inlineStr">
         <is>
-          <t>Spin Move</t>
+          <t>Pound Dribble</t>
         </is>
       </c>
       <c r="D28" s="94" t="inlineStr">
         <is>
-          <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +10% for each</t>
+          <t>Draw 2 cards then Discard 1. SHOT +10% Shot Clock -1</t>
         </is>
       </c>
       <c r="E28" s="34" t="n"/>
       <c r="F28" s="75" t="n">
-        <v>10</v>
-      </c>
-      <c r="G28" s="125" t="inlineStr">
-        <is>
-          <t>isDribble = true</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G28" s="107" t="n"/>
       <c r="H28" s="102" t="n"/>
       <c r="I28" s="102" t="n"/>
       <c r="J28" s="102" t="n"/>
@@ -3363,17 +3363,17 @@
       </c>
       <c r="C29" s="133" t="inlineStr">
         <is>
-          <t>Crossover</t>
+          <t>Spin Move</t>
         </is>
       </c>
       <c r="D29" s="94" t="inlineStr">
         <is>
-          <t>Draw 1 Card. SHOT +10%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
+          <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +10% for each</t>
         </is>
       </c>
       <c r="E29" s="34" t="n"/>
       <c r="F29" s="75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G29" s="125" t="inlineStr">
         <is>
@@ -3391,27 +3391,23 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>Stepback</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Discard 1: SHOT +10%</t>
-        </is>
-      </c>
-      <c r="F30" s="74" t="n">
-        <v>12</v>
-      </c>
-      <c r="G30" s="101" t="inlineStr">
-        <is>
-          <t>The discard is an optional prompt.</t>
+      <c r="C30" s="133" t="inlineStr">
+        <is>
+          <t>Crossover</t>
+        </is>
+      </c>
+      <c r="D30" s="94" t="inlineStr">
+        <is>
+          <t>Draw 1 Card. SHOT +10%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="125" t="inlineStr">
+        <is>
+          <t>isDribble = true</t>
         </is>
       </c>
       <c r="H30" s="102" t="n"/>
@@ -3419,18 +3415,52 @@
       <c r="J30" s="102" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1" s="132">
-      <c r="A31" s="61" t="n"/>
-      <c r="B31" s="62" t="inlineStr">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C31" s="63" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Stepback</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Discard 1: SHOT +10%</t>
+        </is>
+      </c>
+      <c r="F31" s="74" t="n">
+        <v>12</v>
+      </c>
+      <c r="G31" s="101" t="inlineStr">
+        <is>
+          <t>The discard is an optional prompt.</t>
+        </is>
+      </c>
+      <c r="H31" s="102" t="n"/>
+      <c r="I31" s="102" t="n"/>
+      <c r="J31" s="102" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1" s="132">
+      <c r="A32" s="61" t="n"/>
+      <c r="B32" s="62" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
         <is>
           <t>Triple Threat</t>
         </is>
       </c>
-      <c r="D31" s="64" t="inlineStr">
+      <c r="D32" s="64" t="inlineStr">
         <is>
           <t>Choose 1:
 Draw 1 card
@@ -3438,104 +3468,70 @@
 SHOT +10%</t>
         </is>
       </c>
-      <c r="E31" s="64" t="inlineStr">
+      <c r="E32" s="64" t="inlineStr">
         <is>
           <t>Cannot use further Move cards</t>
         </is>
       </c>
-      <c r="F31" s="81" t="n">
+      <c r="F32" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="G31" s="116" t="inlineStr">
+      <c r="G32" s="116" t="inlineStr">
         <is>
           <t>Cannot use further Move cards applies to that possession only.</t>
         </is>
       </c>
-      <c r="H31" s="117" t="n"/>
-      <c r="I31" s="117" t="n"/>
-      <c r="J31" s="117" t="n"/>
-    </row>
-    <row r="32" ht="14" customHeight="1" s="132">
-      <c r="A32" s="42" t="inlineStr">
+      <c r="H32" s="117" t="n"/>
+      <c r="I32" s="117" t="n"/>
+      <c r="J32" s="117" t="n"/>
+    </row>
+    <row r="33" ht="28" customHeight="1" s="132">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="B32" s="43">
-        <f>COUNTIF($B$5:$B$122,"Special Move")</f>
+      <c r="B33" s="43">
+        <f>COUNTIF($B$5:$B$123,"Special Move")</f>
         <v/>
       </c>
-      <c r="C32" s="44" t="n"/>
-      <c r="D32" s="44" t="n"/>
-      <c r="E32" s="44" t="n"/>
-      <c r="F32" s="82" t="n"/>
-      <c r="G32" s="120" t="n"/>
-      <c r="H32" s="121" t="n"/>
-      <c r="I32" s="121" t="n"/>
-      <c r="J32" s="121" t="n"/>
-    </row>
-    <row r="33" ht="28" customHeight="1" s="132">
-      <c r="A33" s="24" t="n"/>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="C33" s="44" t="n"/>
+      <c r="D33" s="44" t="n"/>
+      <c r="E33" s="44" t="n"/>
+      <c r="F33" s="82" t="n"/>
+      <c r="G33" s="120" t="n"/>
+      <c r="H33" s="121" t="n"/>
+      <c r="I33" s="121" t="n"/>
+      <c r="J33" s="121" t="n"/>
+    </row>
+    <row r="34" ht="28" customHeight="1" s="132">
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Bankshot</t>
         </is>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>Flip a coin:
 Heads: SHOT +10%
 Tails: SHOT -10%</t>
         </is>
       </c>
-      <c r="E33" s="27" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F33" s="83" t="n">
+      <c r="F34" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="G33" s="105" t="n"/>
-      <c r="H33" s="106" t="n"/>
-      <c r="I33" s="106" t="n"/>
-      <c r="J33" s="106" t="n"/>
-    </row>
-    <row r="34" ht="28" customHeight="1" s="132">
-      <c r="A34" s="29" t="n"/>
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>Special Move</t>
-        </is>
-      </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>Buzzer Beater</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
-      <c r="F34" s="74" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" s="128" t="inlineStr">
-        <is>
-          <t>Can only play with Shot Clock at 1</t>
-        </is>
-      </c>
+      <c r="G34" s="105" t="n"/>
       <c r="H34" s="106" t="n"/>
       <c r="I34" s="106" t="n"/>
       <c r="J34" s="106" t="n"/>
@@ -3547,25 +3543,29 @@
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
-        <is>
-          <t>Dagger Three</t>
-        </is>
-      </c>
-      <c r="D35" s="94" t="inlineStr">
-        <is>
-          <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
-        </is>
-      </c>
-      <c r="E35" s="33" t="inlineStr">
-        <is>
-          <t>Shoot the ball. +1 Point on make</t>
-        </is>
-      </c>
-      <c r="F35" s="80" t="n">
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>Buzzer Beater</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Shoot the ball</t>
+        </is>
+      </c>
+      <c r="F35" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="105" t="n"/>
+      <c r="G35" s="128" t="inlineStr">
+        <is>
+          <t>Can only play with Shot Clock at 1</t>
+        </is>
+      </c>
       <c r="H35" s="106" t="n"/>
       <c r="I35" s="106" t="n"/>
       <c r="J35" s="106" t="n"/>
@@ -3577,25 +3577,25 @@
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C36" s="31" t="inlineStr">
-        <is>
-          <t>Fadeaway</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>SHOT -10%. Draw 1 card</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball.</t>
-        </is>
-      </c>
-      <c r="F36" s="74" t="n">
-        <v>10</v>
-      </c>
-      <c r="G36" s="112" t="n"/>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>Dagger Three</t>
+        </is>
+      </c>
+      <c r="D36" s="94" t="inlineStr">
+        <is>
+          <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
+        </is>
+      </c>
+      <c r="E36" s="33" t="inlineStr">
+        <is>
+          <t>Shoot the ball. +1 Point on make</t>
+        </is>
+      </c>
+      <c r="F36" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="105" t="n"/>
       <c r="H36" s="106" t="n"/>
       <c r="I36" s="106" t="n"/>
       <c r="J36" s="106" t="n"/>
@@ -3607,25 +3607,25 @@
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C37" s="32" t="inlineStr">
-        <is>
-          <t>From the Hash</t>
-        </is>
-      </c>
-      <c r="D37" s="94" t="inlineStr">
-        <is>
-          <t>SHOT -20%</t>
-        </is>
-      </c>
-      <c r="E37" s="33" t="inlineStr">
-        <is>
-          <t>Shoot the ball. +1 Point on make</t>
-        </is>
-      </c>
-      <c r="F37" s="80" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" s="105" t="n"/>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>Fadeaway</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>SHOT -10%. Draw 1 card</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Shoot the ball.</t>
+        </is>
+      </c>
+      <c r="F37" s="74" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" s="112" t="n"/>
       <c r="H37" s="106" t="n"/>
       <c r="I37" s="106" t="n"/>
       <c r="J37" s="106" t="n"/>
@@ -3637,25 +3637,25 @@
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C38" s="31" t="inlineStr">
-        <is>
-          <t>From the Logo</t>
-        </is>
-      </c>
-      <c r="D38" s="91" t="inlineStr">
-        <is>
-          <t>SHOT -30%</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>From the Hash</t>
+        </is>
+      </c>
+      <c r="D38" s="94" t="inlineStr">
+        <is>
+          <t>SHOT -20%</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F38" s="74" t="n">
+      <c r="F38" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="112" t="n"/>
+      <c r="G38" s="105" t="n"/>
       <c r="H38" s="106" t="n"/>
       <c r="I38" s="106" t="n"/>
       <c r="J38" s="106" t="n"/>
@@ -3667,25 +3667,25 @@
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
-        <is>
-          <t>Full-Court Heave</t>
-        </is>
-      </c>
-      <c r="D39" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 10%</t>
-        </is>
-      </c>
-      <c r="E39" s="33" t="inlineStr">
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>From the Logo</t>
+        </is>
+      </c>
+      <c r="D39" s="91" t="inlineStr">
+        <is>
+          <t>SHOT -30%</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F39" s="80" t="n">
+      <c r="F39" s="74" t="n">
         <v>3</v>
       </c>
-      <c r="G39" s="105" t="n"/>
+      <c r="G39" s="112" t="n"/>
       <c r="H39" s="106" t="n"/>
       <c r="I39" s="106" t="n"/>
       <c r="J39" s="106" t="n"/>
@@ -3697,25 +3697,25 @@
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C40" s="31" t="inlineStr">
-        <is>
-          <t>Putback Tip</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball. After a missed shot: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="F40" s="74" t="n">
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>Full-Court Heave</t>
+        </is>
+      </c>
+      <c r="D40" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 10%</t>
+        </is>
+      </c>
+      <c r="E40" s="33" t="inlineStr">
+        <is>
+          <t>Shoot the ball. +1 Point on make</t>
+        </is>
+      </c>
+      <c r="F40" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="G40" s="112" t="n"/>
+      <c r="G40" s="105" t="n"/>
       <c r="H40" s="106" t="n"/>
       <c r="I40" s="106" t="n"/>
       <c r="J40" s="106" t="n"/>
@@ -3727,25 +3727,25 @@
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C41" s="32" t="inlineStr">
-        <is>
-          <t>Skyhook</t>
-        </is>
-      </c>
-      <c r="D41" s="33" t="inlineStr">
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>Putback Tip</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E41" s="94" t="inlineStr">
-        <is>
-          <t>Shoot the ball. Shot is unaffected by Clamps</t>
-        </is>
-      </c>
-      <c r="F41" s="80" t="n">
-        <v>4</v>
-      </c>
-      <c r="G41" s="105" t="n"/>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Shoot the ball. After a missed shot: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="F41" s="74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="112" t="n"/>
       <c r="H41" s="106" t="n"/>
       <c r="I41" s="106" t="n"/>
       <c r="J41" s="106" t="n"/>
@@ -3757,88 +3757,92 @@
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C42" s="31" t="inlineStr">
-        <is>
-          <t>Slam Dunk</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%. SHOT = 100% if SHOT &gt;= 70%</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
-      <c r="F42" s="74" t="n">
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>Skyhook</t>
+        </is>
+      </c>
+      <c r="D42" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E42" s="94" t="inlineStr">
+        <is>
+          <t>Shoot the ball. Shot is unaffected by Clamps</t>
+        </is>
+      </c>
+      <c r="F42" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="112" t="n"/>
+      <c r="G42" s="105" t="n"/>
       <c r="H42" s="106" t="n"/>
       <c r="I42" s="106" t="n"/>
       <c r="J42" s="106" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1" s="132">
-      <c r="A43" s="52" t="n"/>
-      <c r="B43" s="53" t="inlineStr">
+      <c r="A43" s="29" t="n"/>
+      <c r="B43" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C43" s="69" t="inlineStr">
-        <is>
-          <t>Turnaround Three</t>
-        </is>
-      </c>
-      <c r="D43" s="70" t="inlineStr">
-        <is>
-          <t>Discard any number of cards. SHOT +10% for each</t>
-        </is>
-      </c>
-      <c r="E43" s="70" t="inlineStr">
-        <is>
-          <t>Shoot the ball. +1 Point on make</t>
-        </is>
-      </c>
-      <c r="F43" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="129" t="inlineStr">
-        <is>
-          <t>Only 1 in deck</t>
-        </is>
-      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>Slam Dunk</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%. SHOT = 100% if SHOT &gt;= 70%</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Shoot the ball</t>
+        </is>
+      </c>
+      <c r="F43" s="74" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" s="112" t="n"/>
       <c r="H43" s="106" t="n"/>
       <c r="I43" s="106" t="n"/>
       <c r="J43" s="106" t="n"/>
     </row>
     <row r="44" ht="42" customHeight="1" s="132">
-      <c r="A44" s="61" t="n"/>
-      <c r="B44" s="62" t="inlineStr">
+      <c r="A44" s="52" t="n"/>
+      <c r="B44" s="53" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C44" s="66" t="inlineStr">
-        <is>
-          <t>Euro Step</t>
-        </is>
-      </c>
-      <c r="D44" s="67" t="inlineStr">
-        <is>
-          <t>Flip a coin until you get Tails. For each Heads, SHOT +5% and Draw 1 card</t>
-        </is>
-      </c>
-      <c r="E44" s="68" t="n"/>
-      <c r="F44" s="85" t="n">
-        <v>5</v>
-      </c>
-      <c r="G44" s="122" t="n"/>
-      <c r="H44" s="104" t="n"/>
-      <c r="I44" s="104" t="n"/>
-      <c r="J44" s="104" t="n"/>
+      <c r="C44" s="69" t="inlineStr">
+        <is>
+          <t>Turnaround Three</t>
+        </is>
+      </c>
+      <c r="D44" s="70" t="inlineStr">
+        <is>
+          <t>Discard any number of cards. SHOT +10% for each</t>
+        </is>
+      </c>
+      <c r="E44" s="70" t="inlineStr">
+        <is>
+          <t>Shoot the ball. +1 Point on make</t>
+        </is>
+      </c>
+      <c r="F44" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="129" t="inlineStr">
+        <is>
+          <t>Only 1 in deck</t>
+        </is>
+      </c>
+      <c r="H44" s="106" t="n"/>
+      <c r="I44" s="106" t="n"/>
+      <c r="J44" s="106" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1" s="132">
       <c r="A45" s="61" t="n"/>
@@ -3849,79 +3853,75 @@
       </c>
       <c r="C45" s="66" t="inlineStr">
         <is>
-          <t>Wide-Open Three</t>
+          <t>Euro Step</t>
         </is>
       </c>
       <c r="D45" s="67" t="inlineStr">
         <is>
-          <t>Select any number of other players. SHOT +10% for each</t>
-        </is>
-      </c>
-      <c r="E45" s="68" t="inlineStr">
-        <is>
-          <t>Shoot the ball. +1 Point on make. Selected players receive +1 AST on a make</t>
-        </is>
-      </c>
+          <t>Flip a coin until you get Tails. For each Heads, SHOT +5% and Draw 1 card</t>
+        </is>
+      </c>
+      <c r="E45" s="68" t="n"/>
       <c r="F45" s="85" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" s="122" t="inlineStr">
-        <is>
-          <t>Selecting none rolls off current SHOT and is still a three</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G45" s="122" t="n"/>
       <c r="H45" s="104" t="n"/>
       <c r="I45" s="104" t="n"/>
       <c r="J45" s="104" t="n"/>
     </row>
     <row r="46" ht="29" customHeight="1" s="132" thickBot="1">
-      <c r="A46" s="58" t="inlineStr">
+      <c r="A46" s="61" t="n"/>
+      <c r="B46" s="62" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C46" s="66" t="inlineStr">
+        <is>
+          <t>Wide-Open Three</t>
+        </is>
+      </c>
+      <c r="D46" s="67" t="inlineStr">
+        <is>
+          <t>Select any number of other players. SHOT +10% for each</t>
+        </is>
+      </c>
+      <c r="E46" s="68" t="inlineStr">
+        <is>
+          <t>Shoot the ball. +1 Point on make. Selected players receive +1 AST on a make</t>
+        </is>
+      </c>
+      <c r="F46" s="85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="122" t="inlineStr">
+        <is>
+          <t>Selecting none rolls off current SHOT and is still a three</t>
+        </is>
+      </c>
+      <c r="H46" s="104" t="n"/>
+      <c r="I46" s="104" t="n"/>
+      <c r="J46" s="104" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1" s="132">
+      <c r="A47" s="58" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B46" s="59">
-        <f>COUNTIF($B$5:$B$122,"Clamp")</f>
+      <c r="B47" s="59">
+        <f>COUNTIF($B$5:$B$123,"Clamp")</f>
         <v/>
       </c>
-      <c r="C46" s="60" t="n"/>
-      <c r="D46" s="60" t="n"/>
-      <c r="E46" s="60" t="n"/>
-      <c r="F46" s="86" t="n"/>
-      <c r="G46" s="109" t="n"/>
-      <c r="H46" s="110" t="n"/>
-      <c r="I46" s="110" t="n"/>
-      <c r="J46" s="110" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1" s="132">
-      <c r="A47" s="29" t="n"/>
-      <c r="B47" s="30" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C47" s="31" t="inlineStr">
-        <is>
-          <t>Contest</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Next player SHOT -25% if they shoot</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G47" s="130" t="inlineStr">
-        <is>
-          <t>1 def</t>
-        </is>
-      </c>
-      <c r="H47" s="102" t="n"/>
-      <c r="I47" s="102" t="n"/>
-      <c r="J47" s="102" t="n"/>
+      <c r="C47" s="60" t="n"/>
+      <c r="D47" s="60" t="n"/>
+      <c r="E47" s="60" t="n"/>
+      <c r="F47" s="86" t="n"/>
+      <c r="G47" s="109" t="n"/>
+      <c r="H47" s="110" t="n"/>
+      <c r="I47" s="110" t="n"/>
+      <c r="J47" s="110" t="n"/>
     </row>
     <row r="48" ht="56" customHeight="1" s="132">
       <c r="A48" s="29" t="n"/>
@@ -3930,23 +3930,23 @@
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C48" s="32" t="inlineStr">
-        <is>
-          <t>Double-Team</t>
-        </is>
-      </c>
-      <c r="D48" s="33" t="inlineStr">
-        <is>
-          <t>Next Player cannot play 2 random cards from hand.</t>
-        </is>
-      </c>
-      <c r="E48" s="34" t="n"/>
-      <c r="F48" s="75" t="n">
-        <v>4</v>
-      </c>
-      <c r="G48" s="125" t="inlineStr">
-        <is>
-          <t>2 def</t>
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>Contest</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Next player SHOT -25% if they shoot</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" s="130" t="inlineStr">
+        <is>
+          <t>1 def</t>
         </is>
       </c>
       <c r="H48" s="102" t="n"/>
@@ -3960,23 +3960,23 @@
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C49" s="31" t="inlineStr">
-        <is>
-          <t>Full-Court Press</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Next player discards 2 cards at the start of their turn</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" s="130" t="inlineStr">
-        <is>
-          <t>1 def</t>
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>Double-Team</t>
+        </is>
+      </c>
+      <c r="D49" s="33" t="inlineStr">
+        <is>
+          <t>Next Player cannot play 2 random cards from hand.</t>
+        </is>
+      </c>
+      <c r="E49" s="34" t="n"/>
+      <c r="F49" s="75" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="125" t="inlineStr">
+        <is>
+          <t>2 def</t>
         </is>
       </c>
       <c r="H49" s="102" t="n"/>
@@ -3990,23 +3990,23 @@
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C50" s="32" t="inlineStr">
-        <is>
-          <t>Trap</t>
-        </is>
-      </c>
-      <c r="D50" s="94" t="inlineStr">
-        <is>
-          <t>Next player can only play Pass cards during their turn</t>
-        </is>
-      </c>
-      <c r="E50" s="34" t="n"/>
-      <c r="F50" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G50" s="125" t="inlineStr">
-        <is>
-          <t>They can still shoot as another option; 3 def</t>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>Full-Court Press</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Next player discards 2 cards at the start of their turn</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="130" t="inlineStr">
+        <is>
+          <t>1 def</t>
         </is>
       </c>
       <c r="H50" s="102" t="n"/>
@@ -4014,106 +4014,112 @@
       <c r="J50" s="102" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1" s="132">
-      <c r="A51" s="61" t="n"/>
-      <c r="B51" s="62" t="inlineStr">
+      <c r="A51" s="29" t="n"/>
+      <c r="B51" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C51" s="66" t="inlineStr">
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>Trap</t>
+        </is>
+      </c>
+      <c r="D51" s="94" t="inlineStr">
+        <is>
+          <t>Next player can only play Pass cards during their turn</t>
+        </is>
+      </c>
+      <c r="E51" s="34" t="n"/>
+      <c r="F51" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="125" t="inlineStr">
+        <is>
+          <t>They can still shoot as another option; 3 def</t>
+        </is>
+      </c>
+      <c r="H51" s="102" t="n"/>
+      <c r="I51" s="102" t="n"/>
+      <c r="J51" s="102" t="n"/>
+    </row>
+    <row r="52" ht="28" customHeight="1" s="132">
+      <c r="A52" s="61" t="n"/>
+      <c r="B52" s="62" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C52" s="66" t="inlineStr">
         <is>
           <t>Triple-Team</t>
         </is>
       </c>
-      <c r="D51" s="67" t="inlineStr">
+      <c r="D52" s="67" t="inlineStr">
         <is>
           <t>Next player cannot play 3 random cards from hand.</t>
         </is>
       </c>
-      <c r="E51" s="68" t="n"/>
-      <c r="F51" s="85" t="n">
+      <c r="E52" s="68" t="n"/>
+      <c r="F52" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="135" t="inlineStr">
+      <c r="G52" s="135" t="inlineStr">
         <is>
           <t>3 def</t>
         </is>
       </c>
-      <c r="H51" s="117" t="n"/>
-      <c r="I51" s="117" t="n"/>
-      <c r="J51" s="117" t="n"/>
-    </row>
-    <row r="52" ht="28" customHeight="1" s="132">
-      <c r="A52" s="58" t="inlineStr">
+      <c r="H52" s="117" t="n"/>
+      <c r="I52" s="117" t="n"/>
+      <c r="J52" s="117" t="n"/>
+    </row>
+    <row r="53" ht="28" customHeight="1" s="132">
+      <c r="A53" s="58" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="B52" s="59">
-        <f>COUNTIF($B$5:$B$122,"Whistle")</f>
+      <c r="B53" s="59">
+        <f>COUNTIF($B$5:$B$123,"Whistle")</f>
         <v/>
       </c>
-      <c r="C52" s="60" t="n"/>
-      <c r="D52" s="60" t="n"/>
-      <c r="E52" s="60" t="n"/>
-      <c r="F52" s="86" t="n"/>
-      <c r="G52" s="109" t="n"/>
-      <c r="H52" s="110" t="n"/>
-      <c r="I52" s="110" t="n"/>
-      <c r="J52" s="110" t="n"/>
-    </row>
-    <row r="53" ht="28" customHeight="1" s="132">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="C53" s="60" t="n"/>
+      <c r="D53" s="60" t="n"/>
+      <c r="E53" s="60" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="109" t="n"/>
+      <c r="H53" s="110" t="n"/>
+      <c r="I53" s="110" t="n"/>
+      <c r="J53" s="110" t="n"/>
+    </row>
+    <row r="54" ht="42" customHeight="1" s="132">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>All whistles are limited to 1</t>
         </is>
       </c>
-      <c r="B53" s="30" t="inlineStr">
+      <c r="B54" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C53" s="31" t="inlineStr">
+      <c r="C54" s="31" t="inlineStr">
         <is>
           <t>Back Court Violation</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="138" t="n"/>
-      <c r="G53" s="101" t="inlineStr">
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="138" t="n"/>
+      <c r="G54" s="101" t="inlineStr">
         <is>
           <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
         </is>
       </c>
-      <c r="H53" s="102" t="n"/>
-      <c r="I53" s="102" t="n"/>
-      <c r="J53" s="102" t="n"/>
-    </row>
-    <row r="54" ht="42" customHeight="1" s="132">
-      <c r="A54" s="29" t="n"/>
-      <c r="B54" s="30" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C54" s="90" t="inlineStr">
-        <is>
-          <t>Blocking Foul</t>
-        </is>
-      </c>
-      <c r="D54" s="93" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
-        </is>
-      </c>
-      <c r="E54" s="34" t="n"/>
-      <c r="F54" s="138" t="n"/>
-      <c r="G54" s="107" t="n"/>
       <c r="H54" s="102" t="n"/>
       <c r="I54" s="102" t="n"/>
       <c r="J54" s="102" t="n"/>
@@ -4125,19 +4131,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C55" s="31" t="inlineStr">
-        <is>
-          <t>Charge</t>
-        </is>
-      </c>
-      <c r="D55" s="92" t="inlineStr">
-        <is>
-          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="n"/>
+      <c r="C55" s="90" t="inlineStr">
+        <is>
+          <t>Blocking Foul</t>
+        </is>
+      </c>
+      <c r="D55" s="93" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
+        </is>
+      </c>
+      <c r="E55" s="34" t="n"/>
       <c r="F55" s="138" t="n"/>
-      <c r="G55" s="101" t="n"/>
+      <c r="G55" s="107" t="n"/>
       <c r="H55" s="102" t="n"/>
       <c r="I55" s="102" t="n"/>
       <c r="J55" s="102" t="n"/>
@@ -4149,19 +4155,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C56" s="32" t="inlineStr">
-        <is>
-          <t>Cleared to Play</t>
-        </is>
-      </c>
-      <c r="D56" s="33" t="inlineStr">
-        <is>
-          <t>Injury Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E56" s="34" t="n"/>
+      <c r="C56" s="31" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="D56" s="92" t="inlineStr">
+        <is>
+          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="n"/>
       <c r="F56" s="138" t="n"/>
-      <c r="G56" s="107" t="n"/>
+      <c r="G56" s="101" t="n"/>
       <c r="H56" s="102" t="n"/>
       <c r="I56" s="102" t="n"/>
       <c r="J56" s="102" t="n"/>
@@ -4173,23 +4179,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C57" s="31" t="inlineStr">
-        <is>
-          <t>Coach’s Challenge</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Any Whistle Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>Pull a Timeout from the discards, if one is there, and take it</t>
-        </is>
-      </c>
+      <c r="C57" s="32" t="inlineStr">
+        <is>
+          <t>Cleared to Play</t>
+        </is>
+      </c>
+      <c r="D57" s="33" t="inlineStr">
+        <is>
+          <t>Injury Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E57" s="34" t="n"/>
       <c r="F57" s="138" t="n"/>
-      <c r="G57" s="101" t="n"/>
+      <c r="G57" s="107" t="n"/>
       <c r="H57" s="102" t="n"/>
       <c r="I57" s="102" t="n"/>
       <c r="J57" s="102" t="n"/>
@@ -4201,27 +4203,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C58" s="90" t="inlineStr">
-        <is>
-          <t>Delay-of-Game Warning</t>
-        </is>
-      </c>
-      <c r="D58" s="94" t="inlineStr">
-        <is>
-          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
-        </is>
-      </c>
-      <c r="E58" s="33" t="inlineStr">
-        <is>
-          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
-        </is>
-      </c>
-      <c r="F58" s="139" t="n"/>
-      <c r="G58" s="113" t="inlineStr">
-        <is>
-          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
-        </is>
-      </c>
+      <c r="C58" s="31" t="inlineStr">
+        <is>
+          <t>Coach’s Challenge</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Any Whistle Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Pull a Timeout from the discards, if one is there, and take it</t>
+        </is>
+      </c>
+      <c r="F58" s="138" t="n"/>
+      <c r="G58" s="101" t="n"/>
       <c r="H58" s="102" t="n"/>
       <c r="I58" s="102" t="n"/>
       <c r="J58" s="102" t="n"/>
@@ -4233,21 +4231,25 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C59" s="31" t="inlineStr">
-        <is>
-          <t>Double Dribble</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="138" t="n"/>
-      <c r="G59" s="101" t="inlineStr">
-        <is>
-          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+      <c r="C59" s="90" t="inlineStr">
+        <is>
+          <t>Delay-of-Game Warning</t>
+        </is>
+      </c>
+      <c r="D59" s="94" t="inlineStr">
+        <is>
+          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
+        </is>
+      </c>
+      <c r="E59" s="33" t="inlineStr">
+        <is>
+          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
+        </is>
+      </c>
+      <c r="F59" s="139" t="n"/>
+      <c r="G59" s="113" t="inlineStr">
+        <is>
+          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
         </is>
       </c>
       <c r="H59" s="102" t="n"/>
@@ -4261,19 +4263,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C60" s="90" t="inlineStr">
-        <is>
-          <t>Flagrant Foul</t>
-        </is>
-      </c>
-      <c r="D60" s="94" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E60" s="34" t="n"/>
+      <c r="C60" s="31" t="inlineStr">
+        <is>
+          <t>Double Dribble</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="n"/>
       <c r="F60" s="138" t="n"/>
-      <c r="G60" s="107" t="n"/>
+      <c r="G60" s="101" t="inlineStr">
+        <is>
+          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+        </is>
+      </c>
       <c r="H60" s="102" t="n"/>
       <c r="I60" s="102" t="n"/>
       <c r="J60" s="102" t="n"/>
@@ -4287,17 +4293,17 @@
       </c>
       <c r="C61" s="90" t="inlineStr">
         <is>
-          <t>Flagrant Foul II</t>
-        </is>
-      </c>
-      <c r="D61" s="91" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="n"/>
+          <t>Flagrant Foul</t>
+        </is>
+      </c>
+      <c r="D61" s="94" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
+        </is>
+      </c>
+      <c r="E61" s="34" t="n"/>
       <c r="F61" s="138" t="n"/>
-      <c r="G61" s="101" t="n"/>
+      <c r="G61" s="107" t="n"/>
       <c r="H61" s="102" t="n"/>
       <c r="I61" s="102" t="n"/>
       <c r="J61" s="102" t="n"/>
@@ -4309,19 +4315,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C62" s="32" t="inlineStr">
-        <is>
-          <t>Goaltending</t>
-        </is>
-      </c>
-      <c r="D62" s="33" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
-        </is>
-      </c>
-      <c r="E62" s="34" t="n"/>
+      <c r="C62" s="90" t="inlineStr">
+        <is>
+          <t>Flagrant Foul II</t>
+        </is>
+      </c>
+      <c r="D62" s="91" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="n"/>
       <c r="F62" s="138" t="n"/>
-      <c r="G62" s="107" t="n"/>
+      <c r="G62" s="101" t="n"/>
       <c r="H62" s="102" t="n"/>
       <c r="I62" s="102" t="n"/>
       <c r="J62" s="102" t="n"/>
@@ -4333,19 +4339,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C63" s="31" t="inlineStr">
-        <is>
-          <t>Inadvertent Whistle</t>
-        </is>
-      </c>
-      <c r="D63" s="91" t="inlineStr">
-        <is>
-          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="n"/>
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>Goaltending</t>
+        </is>
+      </c>
+      <c r="D63" s="33" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
+        </is>
+      </c>
+      <c r="E63" s="34" t="n"/>
       <c r="F63" s="138" t="n"/>
-      <c r="G63" s="101" t="n"/>
+      <c r="G63" s="107" t="n"/>
       <c r="H63" s="102" t="n"/>
       <c r="I63" s="102" t="n"/>
       <c r="J63" s="102" t="n"/>
@@ -4357,19 +4363,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C64" s="32" t="inlineStr">
-        <is>
-          <t>Official Review</t>
-        </is>
-      </c>
-      <c r="D64" s="94" t="inlineStr">
-        <is>
-          <t>Intangible Played: Discard all Intangibles from player.</t>
-        </is>
-      </c>
-      <c r="E64" s="34" t="n"/>
+      <c r="C64" s="31" t="inlineStr">
+        <is>
+          <t>Inadvertent Whistle</t>
+        </is>
+      </c>
+      <c r="D64" s="91" t="inlineStr">
+        <is>
+          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="n"/>
       <c r="F64" s="138" t="n"/>
-      <c r="G64" s="107" t="n"/>
+      <c r="G64" s="101" t="n"/>
       <c r="H64" s="102" t="n"/>
       <c r="I64" s="102" t="n"/>
       <c r="J64" s="102" t="n"/>
@@ -4381,23 +4387,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C65" s="31" t="inlineStr">
-        <is>
-          <t>Shot Clock Violation</t>
-        </is>
-      </c>
-      <c r="D65" s="91" t="inlineStr">
-        <is>
-          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="n"/>
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>Official Review</t>
+        </is>
+      </c>
+      <c r="D65" s="94" t="inlineStr">
+        <is>
+          <t>Intangible Played: Discard all Intangibles from player.</t>
+        </is>
+      </c>
+      <c r="E65" s="34" t="n"/>
       <c r="F65" s="138" t="n"/>
-      <c r="G65" s="101" t="inlineStr">
-        <is>
-          <t>This inbound does NOT increment the round.</t>
-        </is>
-      </c>
+      <c r="G65" s="107" t="n"/>
       <c r="H65" s="102" t="n"/>
       <c r="I65" s="102" t="n"/>
       <c r="J65" s="102" t="n"/>
@@ -4409,19 +4411,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C66" s="32" t="inlineStr">
-        <is>
-          <t>Technical Foul</t>
-        </is>
-      </c>
-      <c r="D66" s="94" t="inlineStr">
-        <is>
-          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E66" s="34" t="n"/>
+      <c r="C66" s="31" t="inlineStr">
+        <is>
+          <t>Shot Clock Violation</t>
+        </is>
+      </c>
+      <c r="D66" s="91" t="inlineStr">
+        <is>
+          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="n"/>
       <c r="F66" s="138" t="n"/>
-      <c r="G66" s="107" t="n"/>
+      <c r="G66" s="101" t="inlineStr">
+        <is>
+          <t>This inbound does NOT increment the round.</t>
+        </is>
+      </c>
       <c r="H66" s="102" t="n"/>
       <c r="I66" s="102" t="n"/>
       <c r="J66" s="102" t="n"/>
@@ -4433,46 +4439,46 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C67" s="31" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
-      <c r="D67" s="91" t="inlineStr">
-        <is>
-          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="n"/>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>Technical Foul</t>
+        </is>
+      </c>
+      <c r="D67" s="94" t="inlineStr">
+        <is>
+          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E67" s="34" t="n"/>
       <c r="F67" s="138" t="n"/>
-      <c r="G67" s="101" t="n"/>
+      <c r="G67" s="107" t="n"/>
       <c r="H67" s="102" t="n"/>
       <c r="I67" s="102" t="n"/>
       <c r="J67" s="102" t="n"/>
     </row>
     <row r="68" ht="14" customHeight="1" s="132">
-      <c r="A68" s="61" t="n"/>
-      <c r="B68" s="62" t="inlineStr">
+      <c r="A68" s="29" t="n"/>
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C68" s="63" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D68" s="64" t="inlineStr">
-        <is>
-          <t>Move card played: Cancel card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E68" s="65" t="n"/>
-      <c r="F68" s="140" t="n"/>
-      <c r="G68" s="116" t="n"/>
-      <c r="H68" s="117" t="n"/>
-      <c r="I68" s="117" t="n"/>
-      <c r="J68" s="117" t="n"/>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D68" s="91" t="inlineStr">
+        <is>
+          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="138" t="n"/>
+      <c r="G68" s="101" t="n"/>
+      <c r="H68" s="102" t="n"/>
+      <c r="I68" s="102" t="n"/>
+      <c r="J68" s="102" t="n"/>
     </row>
     <row r="69" ht="14" customHeight="1" s="132">
       <c r="A69" s="61" t="n"/>
@@ -4483,69 +4489,67 @@
       </c>
       <c r="C69" s="63" t="inlineStr">
         <is>
-          <t>Clear Path Foul</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D69" s="64" t="inlineStr">
         <is>
-          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
+          <t>Move card played: Cancel card. TOV +1</t>
         </is>
       </c>
       <c r="E69" s="65" t="n"/>
       <c r="F69" s="140" t="n"/>
-      <c r="G69" s="116" t="inlineStr">
-        <is>
-          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
-        </is>
-      </c>
+      <c r="G69" s="116" t="n"/>
       <c r="H69" s="117" t="n"/>
       <c r="I69" s="117" t="n"/>
       <c r="J69" s="117" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1" s="132">
-      <c r="A70" s="58" t="inlineStr">
+      <c r="A70" s="61" t="n"/>
+      <c r="B70" s="62" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C70" s="63" t="inlineStr">
+        <is>
+          <t>Clear Path Foul</t>
+        </is>
+      </c>
+      <c r="D70" s="64" t="inlineStr">
+        <is>
+          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E70" s="65" t="n"/>
+      <c r="F70" s="140" t="n"/>
+      <c r="G70" s="116" t="inlineStr">
+        <is>
+          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
+        </is>
+      </c>
+      <c r="H70" s="117" t="n"/>
+      <c r="I70" s="117" t="n"/>
+      <c r="J70" s="117" t="n"/>
+    </row>
+    <row r="71" ht="28" customHeight="1" s="132">
+      <c r="A71" s="58" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B70" s="59">
-        <f>COUNTIF($B$5:$B$122,"Game Break")</f>
+      <c r="B71" s="59">
+        <f>COUNTIF($B$5:$B$123,"Game Break")</f>
         <v/>
       </c>
-      <c r="C70" s="60" t="n"/>
-      <c r="D70" s="60" t="n"/>
-      <c r="E70" s="60" t="n"/>
-      <c r="F70" s="86" t="n"/>
-      <c r="G70" s="109" t="n"/>
-      <c r="H70" s="110" t="n"/>
-      <c r="I70" s="110" t="n"/>
-      <c r="J70" s="110" t="n"/>
-    </row>
-    <row r="71" ht="28" customHeight="1" s="132">
-      <c r="A71" s="29" t="n"/>
-      <c r="B71" s="30" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>2-Minute Warning</t>
-        </is>
-      </c>
-      <c r="D71" s="33" t="inlineStr">
-        <is>
-          <t>All players discard down to 2 or fewer cards</t>
-        </is>
-      </c>
-      <c r="E71" s="34" t="n"/>
-      <c r="F71" s="75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" s="107" t="n"/>
-      <c r="H71" s="102" t="n"/>
-      <c r="I71" s="102" t="n"/>
-      <c r="J71" s="102" t="n"/>
+      <c r="C71" s="60" t="n"/>
+      <c r="D71" s="60" t="n"/>
+      <c r="E71" s="60" t="n"/>
+      <c r="F71" s="86" t="n"/>
+      <c r="G71" s="109" t="n"/>
+      <c r="H71" s="110" t="n"/>
+      <c r="I71" s="110" t="n"/>
+      <c r="J71" s="110" t="n"/>
     </row>
     <row r="72" ht="28" customHeight="1" s="132">
       <c r="A72" s="29" t="n"/>
@@ -4554,25 +4558,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C72" s="31" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="n"/>
-      <c r="F72" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G72" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
+        </is>
+      </c>
+      <c r="D72" s="33" t="inlineStr">
+        <is>
+          <t>All players discard down to 2 or fewer cards</t>
+        </is>
+      </c>
+      <c r="E72" s="34" t="n"/>
+      <c r="F72" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" s="107" t="n"/>
       <c r="H72" s="102" t="n"/>
       <c r="I72" s="102" t="n"/>
       <c r="J72" s="102" t="n"/>
@@ -4584,21 +4584,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D73" s="33" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E73" s="34" t="n"/>
-      <c r="F73" s="75" t="n">
-        <v>14</v>
-      </c>
-      <c r="G73" s="107" t="n"/>
+      <c r="C73" s="31" t="inlineStr">
+        <is>
+          <t>Benched</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Immediately give ball to any other player.</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G73" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H73" s="102" t="n"/>
       <c r="I73" s="102" t="n"/>
       <c r="J73" s="102" t="n"/>
@@ -4610,21 +4614,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C74" s="31" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="n"/>
-      <c r="F74" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G74" s="101" t="n"/>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
+        </is>
+      </c>
+      <c r="D74" s="33" t="inlineStr">
+        <is>
+          <t>Discard 1 card.</t>
+        </is>
+      </c>
+      <c r="E74" s="34" t="n"/>
+      <c r="F74" s="75" t="n">
+        <v>14</v>
+      </c>
+      <c r="G74" s="107" t="n"/>
       <c r="H74" s="102" t="n"/>
       <c r="I74" s="102" t="n"/>
       <c r="J74" s="102" t="n"/>
@@ -4636,21 +4640,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C75" s="90" t="inlineStr">
-        <is>
-          <t>Foul</t>
-        </is>
-      </c>
-      <c r="D75" s="33" t="inlineStr">
-        <is>
-          <t>Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E75" s="34" t="n"/>
-      <c r="F75" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G75" s="107" t="n"/>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>Designed Play</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Draw up to a hand of 5</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G75" s="101" t="n"/>
       <c r="H75" s="102" t="n"/>
       <c r="I75" s="102" t="n"/>
       <c r="J75" s="102" t="n"/>
@@ -4662,21 +4666,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C76" s="31" t="inlineStr">
-        <is>
-          <t>MVP Vote</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards up to a hand of 7</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="101" t="n"/>
+      <c r="C76" s="90" t="inlineStr">
+        <is>
+          <t>Foul</t>
+        </is>
+      </c>
+      <c r="D76" s="33" t="inlineStr">
+        <is>
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E76" s="34" t="n"/>
+      <c r="F76" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G76" s="107" t="n"/>
       <c r="H76" s="102" t="n"/>
       <c r="I76" s="102" t="n"/>
       <c r="J76" s="102" t="n"/>
@@ -4688,21 +4692,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>Off Night</t>
-        </is>
-      </c>
-      <c r="D77" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this possession</t>
-        </is>
-      </c>
-      <c r="E77" s="34" t="n"/>
-      <c r="F77" s="75" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" s="107" t="n"/>
+      <c r="C77" s="31" t="inlineStr">
+        <is>
+          <t>MVP Vote</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Draw 3 cards up to a hand of 7</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="101" t="n"/>
       <c r="H77" s="102" t="n"/>
       <c r="I77" s="102" t="n"/>
       <c r="J77" s="102" t="n"/>
@@ -4714,25 +4718,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C78" s="31" t="inlineStr">
-        <is>
-          <t>Swallowed Whistle</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F78" s="74" t="n">
-        <v>5</v>
-      </c>
-      <c r="G78" s="101" t="n"/>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D78" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E78" s="34" t="n"/>
+      <c r="F78" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" s="107" t="n"/>
       <c r="H78" s="102" t="n"/>
       <c r="I78" s="102" t="n"/>
       <c r="J78" s="102" t="n"/>
@@ -4744,23 +4744,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
-        </is>
-      </c>
-      <c r="D79" s="33" t="inlineStr">
-        <is>
-          <t>Players cannot shoot when SHOT is 50% or higher</t>
-        </is>
-      </c>
-      <c r="E79" s="33" t="inlineStr">
+      <c r="C79" s="31" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>Remains for remainder of round</t>
         </is>
       </c>
-      <c r="F79" s="80" t="n"/>
-      <c r="G79" s="107" t="n"/>
+      <c r="F79" s="74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" s="101" t="n"/>
       <c r="H79" s="102" t="n"/>
       <c r="I79" s="102" t="n"/>
       <c r="J79" s="102" t="n"/>
@@ -4772,23 +4774,23 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C80" s="31" t="inlineStr">
-        <is>
-          <t>Traded Mid-Game</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>Swap positions with random other player</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="n"/>
-      <c r="F80" s="76" t="n"/>
-      <c r="G80" s="111" t="inlineStr">
-        <is>
-          <t>Applies to rest of game</t>
-        </is>
-      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D80" s="33" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is 50% or higher</t>
+        </is>
+      </c>
+      <c r="E80" s="33" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F80" s="80" t="n"/>
+      <c r="G80" s="107" t="n"/>
       <c r="H80" s="102" t="n"/>
       <c r="I80" s="102" t="n"/>
       <c r="J80" s="102" t="n"/>
@@ -4800,21 +4802,23 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C81" s="134" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D81" s="91" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
+      <c r="C81" s="31" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Swap positions with random other player</t>
         </is>
       </c>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G81" s="111" t="n"/>
+      <c r="F81" s="76" t="n"/>
+      <c r="G81" s="111" t="inlineStr">
+        <is>
+          <t>Applies to rest of game</t>
+        </is>
+      </c>
       <c r="H81" s="102" t="n"/>
       <c r="I81" s="102" t="n"/>
       <c r="J81" s="102" t="n"/>
@@ -4828,23 +4832,19 @@
       </c>
       <c r="C82" s="134" t="inlineStr">
         <is>
-          <t>All-Swissh Selection</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D82" s="91" t="inlineStr">
         <is>
-          <t>Draw 3 cards after your next make</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E82" s="7" t="n"/>
       <c r="F82" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G82" s="111" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G82" s="111" t="n"/>
       <c r="H82" s="102" t="n"/>
       <c r="I82" s="102" t="n"/>
       <c r="J82" s="102" t="n"/>
@@ -4858,19 +4858,23 @@
       </c>
       <c r="C83" s="134" t="inlineStr">
         <is>
-          <t>All Star Selection</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D83" s="91" t="inlineStr">
         <is>
-          <t>Draw 2 cards</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G83" s="111" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G83" s="111" t="inlineStr">
+        <is>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
+        </is>
+      </c>
       <c r="H83" s="102" t="n"/>
       <c r="I83" s="102" t="n"/>
       <c r="J83" s="102" t="n"/>
@@ -4884,23 +4888,19 @@
       </c>
       <c r="C84" s="134" t="inlineStr">
         <is>
-          <t>Hit the Bike</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D84" s="91" t="inlineStr">
         <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G84" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="G84" s="111" t="n"/>
       <c r="H84" s="102" t="n"/>
       <c r="I84" s="102" t="n"/>
       <c r="J84" s="102" t="n"/>
@@ -4914,19 +4914,23 @@
       </c>
       <c r="C85" s="134" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D85" s="91" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G85" s="111" t="n"/>
+      <c r="G85" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H85" s="102" t="n"/>
       <c r="I85" s="102" t="n"/>
       <c r="J85" s="102" t="n"/>
@@ -4940,23 +4944,19 @@
       </c>
       <c r="C86" s="134" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D86" s="91" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" s="111" t="inlineStr">
-        <is>
-          <t>Deck ones are shown face down</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G86" s="111" t="n"/>
       <c r="H86" s="102" t="n"/>
       <c r="I86" s="102" t="n"/>
       <c r="J86" s="102" t="n"/>
@@ -4970,21 +4970,21 @@
       </c>
       <c r="C87" s="134" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D87" s="91" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G87" s="111" t="inlineStr">
         <is>
-          <t>This is a bad thing in the NBA</t>
+          <t>Deck ones are shown face down</t>
         </is>
       </c>
       <c r="H87" s="102" t="n"/>
@@ -5000,12 +5000,12 @@
       </c>
       <c r="C88" s="134" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D88" s="91" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="G88" s="111" t="inlineStr">
         <is>
-          <t>The hex travels in the declared direction too</t>
+          <t>This is a bad thing in the NBA</t>
         </is>
       </c>
       <c r="H88" s="102" t="n"/>
@@ -5030,19 +5030,23 @@
       </c>
       <c r="C89" s="134" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D89" s="91" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G89" s="111" t="n"/>
+      <c r="G89" s="111" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H89" s="102" t="n"/>
       <c r="I89" s="102" t="n"/>
       <c r="J89" s="102" t="n"/>
@@ -5056,17 +5060,17 @@
       </c>
       <c r="C90" s="134" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D90" s="91" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G90" s="111" t="n"/>
       <c r="H90" s="102" t="n"/>
@@ -5082,17 +5086,17 @@
       </c>
       <c r="C91" s="134" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Official Timeout</t>
         </is>
       </c>
       <c r="D91" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G91" s="111" t="n"/>
       <c r="H91" s="102" t="n"/>
@@ -5100,160 +5104,162 @@
       <c r="J91" s="102" t="n"/>
     </row>
     <row r="92" ht="14" customHeight="1" s="132">
-      <c r="A92" s="55" t="inlineStr">
-        <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="B92" s="56">
-        <f>COUNTIF($B$5:$B$122,"Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C92" s="57" t="n"/>
-      <c r="D92" s="57" t="n"/>
-      <c r="E92" s="57" t="n"/>
-      <c r="F92" s="88" t="n"/>
-      <c r="G92" s="108" t="n"/>
+      <c r="A92" s="29" t="n"/>
+      <c r="B92" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C92" s="134" t="inlineStr">
+        <is>
+          <t>Team Doctor</t>
+        </is>
+      </c>
+      <c r="D92" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="n"/>
+      <c r="F92" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G92" s="111" t="n"/>
       <c r="H92" s="102" t="n"/>
       <c r="I92" s="102" t="n"/>
       <c r="J92" s="102" t="n"/>
     </row>
     <row r="93" ht="28" customHeight="1" s="132">
-      <c r="A93" s="29" t="n"/>
-      <c r="B93" s="30" t="inlineStr">
+      <c r="A93" s="55" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="C93" s="31" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
-        </is>
-      </c>
-      <c r="D93" s="91" t="inlineStr">
-        <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="n"/>
-      <c r="F93" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G93" s="101" t="n"/>
+      <c r="B93" s="56">
+        <f>COUNTIF($B$5:$B$123,"Injury GB")</f>
+        <v/>
+      </c>
+      <c r="C93" s="57" t="n"/>
+      <c r="D93" s="57" t="n"/>
+      <c r="E93" s="57" t="n"/>
+      <c r="F93" s="88" t="n"/>
+      <c r="G93" s="108" t="n"/>
       <c r="H93" s="102" t="n"/>
       <c r="I93" s="102" t="n"/>
       <c r="J93" s="102" t="n"/>
     </row>
     <row r="94" ht="28" customHeight="1" s="132">
-      <c r="A94" s="58" t="inlineStr">
+      <c r="A94" s="29" t="n"/>
+      <c r="B94" s="30" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="C94" s="31" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D94" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="n"/>
+      <c r="F94" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G94" s="101" t="n"/>
+      <c r="H94" s="102" t="n"/>
+      <c r="I94" s="102" t="n"/>
+      <c r="J94" s="102" t="n"/>
+    </row>
+    <row r="95" ht="28" customHeight="1" s="132">
+      <c r="A95" s="58" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="B94" s="59">
-        <f>COUNTIF($B$5:$B$122,"Devastating Injury GB")</f>
+      <c r="B95" s="59">
+        <f>COUNTIF($B$5:$B$123,"Devastating Injury GB")</f>
         <v/>
       </c>
-      <c r="C94" s="60" t="n"/>
-      <c r="D94" s="60" t="n"/>
-      <c r="E94" s="60" t="n"/>
-      <c r="F94" s="86" t="n"/>
-      <c r="G94" s="109" t="n"/>
-      <c r="H94" s="110" t="n"/>
-      <c r="I94" s="110" t="n"/>
-      <c r="J94" s="110" t="n"/>
-    </row>
-    <row r="95" ht="28" customHeight="1" s="132">
-      <c r="A95" s="50" t="n"/>
-      <c r="B95" s="51" t="inlineStr">
+      <c r="C95" s="60" t="n"/>
+      <c r="D95" s="60" t="n"/>
+      <c r="E95" s="60" t="n"/>
+      <c r="F95" s="86" t="n"/>
+      <c r="G95" s="109" t="n"/>
+      <c r="H95" s="110" t="n"/>
+      <c r="I95" s="110" t="n"/>
+      <c r="J95" s="110" t="n"/>
+    </row>
+    <row r="96" ht="28" customHeight="1" s="132">
+      <c r="A96" s="50" t="n"/>
+      <c r="B96" s="51" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="C95" s="136" t="inlineStr">
+      <c r="C96" s="136" t="inlineStr">
         <is>
           <t>Torn Achilles</t>
         </is>
       </c>
-      <c r="D95" s="137" t="inlineStr">
+      <c r="D96" s="137" t="inlineStr">
         <is>
           <t>Hand is locked every turn except 1 card (randomly)</t>
         </is>
       </c>
-      <c r="E95" s="54" t="n"/>
-      <c r="F95" s="141" t="n"/>
-      <c r="G95" s="114" t="n"/>
-      <c r="H95" s="115" t="n"/>
-      <c r="I95" s="115" t="n"/>
-      <c r="J95" s="115" t="n"/>
-    </row>
-    <row r="96" ht="28" customHeight="1" s="132">
-      <c r="A96" s="55" t="inlineStr">
+      <c r="E96" s="54" t="n"/>
+      <c r="F96" s="141" t="n"/>
+      <c r="G96" s="114" t="n"/>
+      <c r="H96" s="115" t="n"/>
+      <c r="I96" s="115" t="n"/>
+      <c r="J96" s="115" t="n"/>
+    </row>
+    <row r="97" ht="42" customHeight="1" s="132">
+      <c r="A97" s="55" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B96" s="56">
-        <f>COUNTIF($B$5:$B$122,"Intangible")</f>
+      <c r="B97" s="56">
+        <f>COUNTIF($B$5:$B$123,"Intangible")</f>
         <v/>
       </c>
-      <c r="C96" s="57" t="n"/>
-      <c r="D96" s="57" t="n"/>
-      <c r="E96" s="57" t="n"/>
-      <c r="F96" s="88" t="n"/>
-      <c r="G96" s="108" t="n"/>
-      <c r="H96" s="102" t="n"/>
-      <c r="I96" s="102" t="n"/>
-      <c r="J96" s="102" t="n"/>
-    </row>
-    <row r="97" ht="42" customHeight="1" s="132">
-      <c r="A97" s="96" t="inlineStr">
-        <is>
-          <t>All intangibles are limited to 1</t>
-        </is>
-      </c>
-      <c r="B97" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C97" s="31" t="inlineStr">
-        <is>
-          <t>Board-Crasher</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% upon Rebounding your own missed shot</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="n"/>
-      <c r="F97" s="138" t="n"/>
-      <c r="G97" s="101" t="n"/>
+      <c r="C97" s="57" t="n"/>
+      <c r="D97" s="57" t="n"/>
+      <c r="E97" s="57" t="n"/>
+      <c r="F97" s="88" t="n"/>
+      <c r="G97" s="108" t="n"/>
       <c r="H97" s="102" t="n"/>
       <c r="I97" s="102" t="n"/>
       <c r="J97" s="102" t="n"/>
     </row>
     <row r="98" ht="56" customHeight="1" s="132">
-      <c r="A98" s="29" t="n"/>
+      <c r="A98" s="96" t="inlineStr">
+        <is>
+          <t>All intangibles are limited to 1</t>
+        </is>
+      </c>
       <c r="B98" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C98" s="32" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D98" s="33" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E98" s="34" t="n"/>
+      <c r="C98" s="31" t="inlineStr">
+        <is>
+          <t>Board-Crasher</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% upon Rebounding your own missed shot</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="n"/>
       <c r="F98" s="138" t="n"/>
-      <c r="G98" s="107" t="n"/>
+      <c r="G98" s="101" t="n"/>
       <c r="H98" s="102" t="n"/>
       <c r="I98" s="102" t="n"/>
       <c r="J98" s="102" t="n"/>
@@ -5265,19 +5271,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C99" s="31" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="n"/>
+      <c r="C99" s="32" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D99" s="33" t="inlineStr">
+        <is>
+          <t>Additional SHOT +10% on all received passes</t>
+        </is>
+      </c>
+      <c r="E99" s="34" t="n"/>
       <c r="F99" s="138" t="n"/>
-      <c r="G99" s="101" t="n"/>
+      <c r="G99" s="107" t="n"/>
       <c r="H99" s="102" t="n"/>
       <c r="I99" s="102" t="n"/>
       <c r="J99" s="102" t="n"/>
@@ -5289,19 +5295,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C100" s="32" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D100" s="33" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
-        </is>
-      </c>
-      <c r="E100" s="34" t="n"/>
+      <c r="C100" s="31" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="n"/>
       <c r="F100" s="138" t="n"/>
-      <c r="G100" s="107" t="n"/>
+      <c r="G100" s="101" t="n"/>
       <c r="H100" s="102" t="n"/>
       <c r="I100" s="102" t="n"/>
       <c r="J100" s="102" t="n"/>
@@ -5313,23 +5319,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C101" s="31" t="inlineStr">
-        <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F101" s="139" t="n"/>
-      <c r="G101" s="101" t="n"/>
+      <c r="C101" s="32" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D101" s="33" t="inlineStr">
+        <is>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
+        </is>
+      </c>
+      <c r="E101" s="34" t="n"/>
+      <c r="F101" s="138" t="n"/>
+      <c r="G101" s="107" t="n"/>
       <c r="H101" s="102" t="n"/>
       <c r="I101" s="102" t="n"/>
       <c r="J101" s="102" t="n"/>
@@ -5341,19 +5343,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C102" s="90" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D102" s="94" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E102" s="34" t="n"/>
-      <c r="F102" s="138" t="n"/>
-      <c r="G102" s="125" t="n"/>
+      <c r="C102" s="31" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F102" s="139" t="n"/>
+      <c r="G102" s="101" t="n"/>
       <c r="H102" s="102" t="n"/>
       <c r="I102" s="102" t="n"/>
       <c r="J102" s="102" t="n"/>
@@ -5367,17 +5373,17 @@
       </c>
       <c r="C103" s="90" t="inlineStr">
         <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D103" s="91" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="n"/>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D103" s="94" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
+        </is>
+      </c>
+      <c r="E103" s="34" t="n"/>
       <c r="F103" s="138" t="n"/>
-      <c r="G103" s="101" t="n"/>
+      <c r="G103" s="125" t="n"/>
       <c r="H103" s="102" t="n"/>
       <c r="I103" s="102" t="n"/>
       <c r="J103" s="102" t="n"/>
@@ -5389,19 +5395,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C104" s="32" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D104" s="33" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E104" s="34" t="n"/>
+      <c r="C104" s="90" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D104" s="91" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="n"/>
       <c r="F104" s="138" t="n"/>
-      <c r="G104" s="107" t="n"/>
+      <c r="G104" s="101" t="n"/>
       <c r="H104" s="102" t="n"/>
       <c r="I104" s="102" t="n"/>
       <c r="J104" s="102" t="n"/>
@@ -5413,19 +5419,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C105" s="31" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="n"/>
+      <c r="C105" s="32" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="D105" s="33" t="inlineStr">
+        <is>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+        </is>
+      </c>
+      <c r="E105" s="34" t="n"/>
       <c r="F105" s="138" t="n"/>
-      <c r="G105" s="101" t="n"/>
+      <c r="G105" s="107" t="n"/>
       <c r="H105" s="102" t="n"/>
       <c r="I105" s="102" t="n"/>
       <c r="J105" s="102" t="n"/>
@@ -5437,19 +5443,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C106" s="32" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D106" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +20% if you scored last round.</t>
-        </is>
-      </c>
-      <c r="E106" s="34" t="n"/>
+      <c r="C106" s="31" t="inlineStr">
+        <is>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="n"/>
       <c r="F106" s="138" t="n"/>
-      <c r="G106" s="107" t="n"/>
+      <c r="G106" s="101" t="n"/>
       <c r="H106" s="102" t="n"/>
       <c r="I106" s="102" t="n"/>
       <c r="J106" s="102" t="n"/>
@@ -5461,19 +5467,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C107" s="31" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D107" s="91" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="n"/>
+      <c r="C107" s="32" t="inlineStr">
+        <is>
+          <t>Hot Hand</t>
+        </is>
+      </c>
+      <c r="D107" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +20% if you scored last round.</t>
+        </is>
+      </c>
+      <c r="E107" s="34" t="n"/>
       <c r="F107" s="138" t="n"/>
-      <c r="G107" s="101" t="n"/>
+      <c r="G107" s="107" t="n"/>
       <c r="H107" s="102" t="n"/>
       <c r="I107" s="102" t="n"/>
       <c r="J107" s="102" t="n"/>
@@ -5485,23 +5491,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C108" s="32" t="inlineStr">
-        <is>
-          <t>No Bag</t>
-        </is>
-      </c>
-      <c r="D108" s="33" t="inlineStr">
-        <is>
-          <t>Cannot activate Move cards this round</t>
-        </is>
-      </c>
-      <c r="E108" s="34" t="n"/>
+      <c r="C108" s="31" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D108" s="91" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="n"/>
       <c r="F108" s="138" t="n"/>
-      <c r="G108" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G108" s="101" t="n"/>
       <c r="H108" s="102" t="n"/>
       <c r="I108" s="102" t="n"/>
       <c r="J108" s="102" t="n"/>
@@ -5513,19 +5515,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C109" s="31" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="n"/>
+      <c r="C109" s="32" t="inlineStr">
+        <is>
+          <t>No Bag</t>
+        </is>
+      </c>
+      <c r="D109" s="33" t="inlineStr">
+        <is>
+          <t>Cannot activate Move cards this round</t>
+        </is>
+      </c>
+      <c r="E109" s="34" t="n"/>
       <c r="F109" s="138" t="n"/>
-      <c r="G109" s="101" t="n"/>
+      <c r="G109" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H109" s="102" t="n"/>
       <c r="I109" s="102" t="n"/>
       <c r="J109" s="102" t="n"/>
@@ -5537,23 +5543,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C110" s="32" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D110" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
-        </is>
-      </c>
-      <c r="E110" s="34" t="n"/>
+      <c r="C110" s="31" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="n"/>
       <c r="F110" s="138" t="n"/>
-      <c r="G110" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G110" s="101" t="n"/>
       <c r="H110" s="102" t="n"/>
       <c r="I110" s="102" t="n"/>
       <c r="J110" s="102" t="n"/>
@@ -5565,19 +5567,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C111" s="31" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="n"/>
+      <c r="C111" s="32" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D111" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E111" s="34" t="n"/>
       <c r="F111" s="138" t="n"/>
-      <c r="G111" s="101" t="n"/>
+      <c r="G111" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H111" s="102" t="n"/>
       <c r="I111" s="102" t="n"/>
       <c r="J111" s="102" t="n"/>
@@ -5589,19 +5595,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C112" s="32" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D112" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
-        </is>
-      </c>
-      <c r="E112" s="34" t="n"/>
+      <c r="C112" s="31" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="n"/>
       <c r="F112" s="138" t="n"/>
-      <c r="G112" s="107" t="n"/>
+      <c r="G112" s="101" t="n"/>
       <c r="H112" s="102" t="n"/>
       <c r="I112" s="102" t="n"/>
       <c r="J112" s="102" t="n"/>
@@ -5613,19 +5619,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C113" s="31" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="n"/>
+      <c r="C113" s="32" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D113" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E113" s="34" t="n"/>
       <c r="F113" s="138" t="n"/>
-      <c r="G113" s="101" t="n"/>
+      <c r="G113" s="107" t="n"/>
       <c r="H113" s="102" t="n"/>
       <c r="I113" s="102" t="n"/>
       <c r="J113" s="102" t="n"/>
@@ -5637,19 +5643,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C114" s="32" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D114" s="33" t="inlineStr">
-        <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E114" s="34" t="n"/>
+      <c r="C114" s="31" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="n"/>
       <c r="F114" s="138" t="n"/>
-      <c r="G114" s="107" t="n"/>
+      <c r="G114" s="101" t="n"/>
       <c r="H114" s="102" t="n"/>
       <c r="I114" s="102" t="n"/>
       <c r="J114" s="102" t="n"/>
@@ -5661,19 +5667,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C115" s="31" t="inlineStr">
-        <is>
-          <t>Unguardable</t>
-        </is>
-      </c>
-      <c r="D115" s="91" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="n"/>
+      <c r="C115" s="32" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D115" s="33" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E115" s="34" t="n"/>
       <c r="F115" s="138" t="n"/>
-      <c r="G115" s="101" t="n"/>
+      <c r="G115" s="107" t="n"/>
       <c r="H115" s="102" t="n"/>
       <c r="I115" s="102" t="n"/>
       <c r="J115" s="102" t="n"/>
@@ -5685,50 +5691,50 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C116" s="32" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D116" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
-        </is>
-      </c>
-      <c r="E116" s="34" t="n"/>
+      <c r="C116" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D116" s="91" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="n"/>
       <c r="F116" s="138" t="n"/>
-      <c r="G116" s="113" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G116" s="101" t="n"/>
       <c r="H116" s="102" t="n"/>
       <c r="I116" s="102" t="n"/>
       <c r="J116" s="102" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="61" t="n"/>
-      <c r="B117" s="62" t="inlineStr">
+      <c r="A117" s="29" t="n"/>
+      <c r="B117" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C117" s="66" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D117" s="95" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E117" s="68" t="n"/>
-      <c r="F117" s="140" t="n"/>
-      <c r="G117" s="126" t="n"/>
-      <c r="H117" s="117" t="n"/>
-      <c r="I117" s="117" t="n"/>
-      <c r="J117" s="117" t="n"/>
+      <c r="C117" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D117" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E117" s="34" t="n"/>
+      <c r="F117" s="138" t="n"/>
+      <c r="G117" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H117" s="102" t="n"/>
+      <c r="I117" s="102" t="n"/>
+      <c r="J117" s="102" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="61" t="n"/>
@@ -5739,12 +5745,12 @@
       </c>
       <c r="C118" s="66" t="inlineStr">
         <is>
-          <t>Unselfish</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D118" s="95" t="inlineStr">
         <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E118" s="68" t="n"/>
@@ -5763,12 +5769,12 @@
       </c>
       <c r="C119" s="66" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D119" s="95" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E119" s="68" t="n"/>
@@ -5787,21 +5793,20 @@
       </c>
       <c r="C120" s="66" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D120" s="95" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E120" s="68" t="n"/>
       <c r="F120" s="140" t="n"/>
-      <c r="G120" s="126" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="G120" s="126" t="n"/>
+      <c r="H120" s="117" t="n"/>
+      <c r="I120" s="117" t="n"/>
+      <c r="J120" s="117" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="61" t="n"/>
@@ -5812,19 +5817,19 @@
       </c>
       <c r="C121" s="66" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Villainous Reputation</t>
         </is>
       </c>
       <c r="D121" s="95" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>Discard 1 whenever any Whistle triggers</t>
         </is>
       </c>
       <c r="E121" s="68" t="n"/>
       <c r="F121" s="140" t="n"/>
       <c r="G121" s="126" t="inlineStr">
         <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
         </is>
       </c>
     </row>
@@ -5837,63 +5842,88 @@
       </c>
       <c r="C122" s="66" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Free Agent</t>
         </is>
       </c>
       <c r="D122" s="95" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
       <c r="E122" s="68" t="n"/>
       <c r="F122" s="140" t="n"/>
-      <c r="G122" s="126" t="n"/>
-      <c r="H122" s="117" t="n"/>
-      <c r="I122" s="117" t="n"/>
-      <c r="J122" s="117" t="n"/>
+      <c r="G122" s="126" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="61" t="n"/>
+      <c r="B123" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C123" s="66" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D123" s="95" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E123" s="68" t="n"/>
+      <c r="F123" s="140" t="n"/>
+      <c r="G123" s="126" t="n"/>
+      <c r="H123" s="117" t="n"/>
+      <c r="I123" s="117" t="n"/>
+      <c r="J123" s="117" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="109">
+  <mergeCells count="110">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G32:J32"/>
     <mergeCell ref="G119:J119"/>
-    <mergeCell ref="G32:J32"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
     <mergeCell ref="G72:J72"/>
+    <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G82:J82"/>
     <mergeCell ref="G57:J57"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
+    <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
-    <mergeCell ref="G18:J18"/>
     <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="G108:J108"/>
+    <mergeCell ref="G58:J58"/>
     <mergeCell ref="G114:J114"/>
-    <mergeCell ref="G58:J58"/>
+    <mergeCell ref="G123:J123"/>
     <mergeCell ref="G110:J110"/>
     <mergeCell ref="G113:J113"/>
+    <mergeCell ref="G91:J91"/>
+    <mergeCell ref="G20:J20"/>
     <mergeCell ref="G100:J100"/>
-    <mergeCell ref="G20:J20"/>
     <mergeCell ref="G94:J94"/>
-    <mergeCell ref="G91:J91"/>
-    <mergeCell ref="G44:J44"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G44:J44"/>
     <mergeCell ref="G31:J31"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
-    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="G61:J61"/>
@@ -5901,8 +5931,8 @@
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="G23:J23"/>
     <mergeCell ref="G97:J97"/>
+    <mergeCell ref="G7:J7"/>
     <mergeCell ref="G38:J38"/>
-    <mergeCell ref="G7:J7"/>
     <mergeCell ref="G112:J112"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="G62:J62"/>
@@ -5925,19 +5955,18 @@
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
     <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G101:J101"/>
     <mergeCell ref="G116:J116"/>
+    <mergeCell ref="G103:J103"/>
     <mergeCell ref="G37:J37"/>
-    <mergeCell ref="G103:J103"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
+    <mergeCell ref="G87:J87"/>
     <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G95:J95"/>
     <mergeCell ref="G80:J80"/>
-    <mergeCell ref="G95:J95"/>
-    <mergeCell ref="G89:J89"/>
     <mergeCell ref="G79:J79"/>
     <mergeCell ref="G64:J64"/>
     <mergeCell ref="G73:J73"/>
@@ -5952,17 +5981,19 @@
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
+    <mergeCell ref="G120:J120"/>
+    <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
     <mergeCell ref="G107:J107"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G6:J6"/>
     <mergeCell ref="G93:J93"/>
-    <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
+    <mergeCell ref="G83:J83"/>
     <mergeCell ref="G92:J92"/>
-    <mergeCell ref="G30:J30"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2626,41 +2626,40 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$123,"Pass")</f>
+        <f>COUNTIF($B$5:$B$131,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$123,"Move")+COUNTIF($B$5:$B$123,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$131,"Move")+COUNTIF($B$5:$B$131,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$123,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$131,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$123,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$131,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$123,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$131,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$123,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$131,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$123,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$131,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$123,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$131,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
     </row>
-    <row r="3"/>
-    <row r="4" ht="20.75" customHeight="1" s="132" thickBot="1">
+    <row r="4" ht="20.75" customHeight="1" s="132">
       <c r="A4" s="123" t="inlineStr">
         <is>
           <t>Type</t>
@@ -2703,7 +2702,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$123,"Pass")</f>
+        <f>COUNTIF($B$5:$B$131,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="23" t="n"/>
@@ -2923,7 +2922,7 @@
       <c r="I13" s="106" t="n"/>
       <c r="J13" s="106" t="n"/>
     </row>
-    <row r="14" ht="29" customHeight="1" s="132" thickBot="1">
+    <row r="14" ht="29" customHeight="1" s="132">
       <c r="A14" s="35" t="n"/>
       <c r="B14" s="36" t="inlineStr">
         <is>
@@ -3111,80 +3110,76 @@
       <c r="I19" s="104" t="n"/>
       <c r="J19" s="104" t="n"/>
     </row>
-    <row r="20" ht="14" customHeight="1" s="132">
-      <c r="A20" s="39" t="inlineStr">
+    <row r="20" ht="56" customHeight="1" s="132">
+      <c r="A20" s="35" t="n"/>
+      <c r="B20" s="36" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>Touch Pass</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="inlineStr">
+        <is>
+          <t>SHOT +5%. Pass to player of choice. If played as first action, draw 2 cards</t>
+        </is>
+      </c>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="127" t="n"/>
+      <c r="H20" s="104" t="n"/>
+      <c r="I20" s="104" t="n"/>
+      <c r="J20" s="104" t="n"/>
+    </row>
+    <row r="21" ht="14" customHeight="1" s="132">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="B20" s="40">
-        <f>COUNTIF($B$5:$B$123,"Move")+COUNTIF($B$5:$B$123,"Special Move")</f>
+      <c r="B21" s="40">
+        <f>COUNTIF($B$5:$B$131,"Move")+COUNTIF($B$5:$B$131,"Special Move")</f>
         <v/>
       </c>
-      <c r="C20" s="41" t="n"/>
-      <c r="D20" s="41" t="n"/>
-      <c r="E20" s="41" t="n"/>
-      <c r="F20" s="78" t="n"/>
-      <c r="G20" s="120" t="n"/>
-      <c r="H20" s="121" t="n"/>
-      <c r="I20" s="121" t="n"/>
-      <c r="J20" s="121" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1" s="132">
-      <c r="A21" s="45" t="n"/>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="C21" s="41" t="n"/>
+      <c r="D21" s="41" t="n"/>
+      <c r="E21" s="41" t="n"/>
+      <c r="F21" s="78" t="n"/>
+      <c r="G21" s="120" t="n"/>
+      <c r="H21" s="121" t="n"/>
+      <c r="I21" s="121" t="n"/>
+      <c r="J21" s="121" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" s="132">
+      <c r="A22" s="45" t="n"/>
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>Dribble</t>
         </is>
       </c>
-      <c r="D21" s="48" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>Draw 1 card. SHOT -10%</t>
         </is>
       </c>
-      <c r="E21" s="49" t="n"/>
-      <c r="F21" s="79" t="n">
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="79" t="n">
         <v>15</v>
       </c>
-      <c r="G21" s="118" t="n"/>
-      <c r="H21" s="119" t="n"/>
-      <c r="I21" s="119" t="n"/>
-      <c r="J21" s="119" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" s="132">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="30" t="inlineStr">
-        <is>
-          <t>Move</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Following Dribble: SHOT +10%</t>
-        </is>
-      </c>
-      <c r="F22" s="74" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" s="101" t="n"/>
-      <c r="H22" s="102" t="n"/>
-      <c r="I22" s="102" t="n"/>
-      <c r="J22" s="102" t="n"/>
+      <c r="G22" s="118" t="n"/>
+      <c r="H22" s="119" t="n"/>
+      <c r="I22" s="119" t="n"/>
+      <c r="J22" s="119" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1" s="132">
       <c r="A23" s="29" t="n"/>
@@ -3193,21 +3188,25 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>Ankle Breaker</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>Target player discards 1 card. SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E23" s="34" t="n"/>
-      <c r="F23" s="75" t="n">
-        <v>10</v>
-      </c>
-      <c r="G23" s="107" t="n"/>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Following Dribble: SHOT +10%</t>
+        </is>
+      </c>
+      <c r="F23" s="74" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="101" t="n"/>
       <c r="H23" s="102" t="n"/>
       <c r="I23" s="102" t="n"/>
       <c r="J23" s="102" t="n"/>
@@ -3219,25 +3218,21 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C24" s="90" t="inlineStr">
-        <is>
-          <t>Flop</t>
-        </is>
-      </c>
-      <c r="D24" s="91" t="inlineStr">
-        <is>
-          <t>Cancel Clamps. Take 1 FT for each. If no Clamps on you, TOV +1</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="130" t="inlineStr">
-        <is>
-          <t>Take 1 FT attempt for each Clamp on you and cancel it. If no Clamps on you, TOV +1</t>
-        </is>
-      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>Ankle Breaker</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Target player discards 1 card. SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="75" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="107" t="n"/>
       <c r="H24" s="102" t="n"/>
       <c r="I24" s="102" t="n"/>
       <c r="J24" s="102" t="n"/>
@@ -3249,100 +3244,104 @@
           <t>Move</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
-        <is>
-          <t>Hesi</t>
-        </is>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E25" s="33" t="inlineStr">
-        <is>
-          <t>Shot Clock -1</t>
-        </is>
-      </c>
-      <c r="F25" s="80" t="n">
-        <v>15</v>
-      </c>
-      <c r="G25" s="107" t="n"/>
+      <c r="C25" s="90" t="inlineStr">
+        <is>
+          <t>Flop</t>
+        </is>
+      </c>
+      <c r="D25" s="91" t="inlineStr">
+        <is>
+          <t>Cancel Clamps. Take 1 FT for each. If no Clamps on you, TOV +1</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="130" t="inlineStr">
+        <is>
+          <t>Take 1 FT attempt for each Clamp on you and cancel it. If no Clamps on you, TOV +1</t>
+        </is>
+      </c>
       <c r="H25" s="102" t="n"/>
       <c r="I25" s="102" t="n"/>
       <c r="J25" s="102" t="n"/>
     </row>
-    <row r="26" ht="14" customHeight="1" s="132">
+    <row r="26" ht="28" customHeight="1" s="132">
       <c r="A26" s="29" t="n"/>
       <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>Pump Fake</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>Hesi</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Cancel all Clamps on you</t>
-        </is>
-      </c>
-      <c r="F26" s="74" t="n">
-        <v>12</v>
-      </c>
-      <c r="G26" s="101" t="n"/>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>Shot Clock -1</t>
+        </is>
+      </c>
+      <c r="F26" s="80" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="107" t="n"/>
       <c r="H26" s="102" t="n"/>
       <c r="I26" s="102" t="n"/>
       <c r="J26" s="102" t="n"/>
     </row>
-    <row r="27" ht="71" customHeight="1" s="132" thickBot="1">
+    <row r="27" ht="14" customHeight="1" s="132">
       <c r="A27" s="29" t="n"/>
       <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>Rhythm Dribble</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="inlineStr">
-        <is>
-          <t>Draw 1 card. SHOT +10%. Shot Clock -1</t>
-        </is>
-      </c>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" s="107" t="n"/>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>Pump Fake</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Cancel all Clamps on you</t>
+        </is>
+      </c>
+      <c r="F27" s="74" t="n">
+        <v>12</v>
+      </c>
+      <c r="G27" s="101" t="n"/>
       <c r="H27" s="102" t="n"/>
       <c r="I27" s="102" t="n"/>
       <c r="J27" s="102" t="n"/>
     </row>
-    <row r="28" ht="20" customHeight="1" s="132">
+    <row r="28" ht="71" customHeight="1" s="132">
       <c r="A28" s="29" t="n"/>
       <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C28" s="133" t="inlineStr">
-        <is>
-          <t>Pound Dribble</t>
-        </is>
-      </c>
-      <c r="D28" s="94" t="inlineStr">
-        <is>
-          <t>Draw 2 cards then Discard 1. SHOT +10% Shot Clock -1</t>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>Rhythm Dribble</t>
+        </is>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>Draw 1 card. SHOT +10%. Shot Clock -1</t>
         </is>
       </c>
       <c r="E28" s="34" t="n"/>
@@ -3354,7 +3353,7 @@
       <c r="I28" s="102" t="n"/>
       <c r="J28" s="102" t="n"/>
     </row>
-    <row r="29" ht="42" customHeight="1" s="132">
+    <row r="29" ht="20" customHeight="1" s="132">
       <c r="A29" s="29" t="n"/>
       <c r="B29" s="30" t="inlineStr">
         <is>
@@ -3363,28 +3362,24 @@
       </c>
       <c r="C29" s="133" t="inlineStr">
         <is>
-          <t>Spin Move</t>
+          <t>Pound Dribble</t>
         </is>
       </c>
       <c r="D29" s="94" t="inlineStr">
         <is>
-          <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +10% for each</t>
+          <t>Draw 2 cards then Discard 1. SHOT +10% Shot Clock -1</t>
         </is>
       </c>
       <c r="E29" s="34" t="n"/>
       <c r="F29" s="75" t="n">
-        <v>10</v>
-      </c>
-      <c r="G29" s="125" t="inlineStr">
-        <is>
-          <t>isDribble = true</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G29" s="107" t="n"/>
       <c r="H29" s="102" t="n"/>
       <c r="I29" s="102" t="n"/>
       <c r="J29" s="102" t="n"/>
     </row>
-    <row r="30" ht="14" customHeight="1" s="132">
+    <row r="30" ht="42" customHeight="1" s="132">
       <c r="A30" s="29" t="n"/>
       <c r="B30" s="30" t="inlineStr">
         <is>
@@ -3393,17 +3388,17 @@
       </c>
       <c r="C30" s="133" t="inlineStr">
         <is>
-          <t>Crossover</t>
+          <t>Spin Move</t>
         </is>
       </c>
       <c r="D30" s="94" t="inlineStr">
         <is>
-          <t>Draw 1 Card. SHOT +10%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
+          <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +10% for each</t>
         </is>
       </c>
       <c r="E30" s="34" t="n"/>
       <c r="F30" s="75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G30" s="125" t="inlineStr">
         <is>
@@ -3414,53 +3409,83 @@
       <c r="I30" s="102" t="n"/>
       <c r="J30" s="102" t="n"/>
     </row>
-    <row r="31" ht="28" customHeight="1" s="132">
+    <row r="31" ht="14" customHeight="1" s="132">
       <c r="A31" s="29" t="n"/>
       <c r="B31" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>Stepback</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Discard 1: SHOT +10%</t>
-        </is>
-      </c>
-      <c r="F31" s="74" t="n">
-        <v>12</v>
-      </c>
-      <c r="G31" s="101" t="inlineStr">
-        <is>
-          <t>The discard is an optional prompt.</t>
+      <c r="C31" s="133" t="inlineStr">
+        <is>
+          <t>Crossover</t>
+        </is>
+      </c>
+      <c r="D31" s="94" t="inlineStr">
+        <is>
+          <t>Draw 1 Card. SHOT +10%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="n"/>
+      <c r="F31" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="125" t="inlineStr">
+        <is>
+          <t>isDribble = true</t>
         </is>
       </c>
       <c r="H31" s="102" t="n"/>
       <c r="I31" s="102" t="n"/>
       <c r="J31" s="102" t="n"/>
     </row>
-    <row r="32" ht="14" customHeight="1" s="132">
-      <c r="A32" s="61" t="n"/>
-      <c r="B32" s="62" t="inlineStr">
+    <row r="32" ht="28" customHeight="1" s="132">
+      <c r="A32" s="29" t="n"/>
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C32" s="63" t="inlineStr">
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>Stepback</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Discard 1: SHOT +10%</t>
+        </is>
+      </c>
+      <c r="F32" s="74" t="n">
+        <v>12</v>
+      </c>
+      <c r="G32" s="101" t="inlineStr">
+        <is>
+          <t>The discard is an optional prompt.</t>
+        </is>
+      </c>
+      <c r="H32" s="102" t="n"/>
+      <c r="I32" s="102" t="n"/>
+      <c r="J32" s="102" t="n"/>
+    </row>
+    <row r="33" ht="14" customHeight="1" s="132">
+      <c r="A33" s="61" t="n"/>
+      <c r="B33" s="62" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="C33" s="63" t="inlineStr">
         <is>
           <t>Triple Threat</t>
         </is>
       </c>
-      <c r="D32" s="64" t="inlineStr">
+      <c r="D33" s="64" t="inlineStr">
         <is>
           <t>Choose 1:
 Draw 1 card
@@ -3468,131 +3493,93 @@
 SHOT +10%</t>
         </is>
       </c>
-      <c r="E32" s="64" t="inlineStr">
+      <c r="E33" s="64" t="inlineStr">
         <is>
           <t>Cannot use further Move cards</t>
         </is>
       </c>
-      <c r="F32" s="81" t="n">
+      <c r="F33" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="G32" s="116" t="inlineStr">
+      <c r="G33" s="116" t="inlineStr">
         <is>
           <t>Cannot use further Move cards applies to that possession only.</t>
         </is>
       </c>
-      <c r="H32" s="117" t="n"/>
-      <c r="I32" s="117" t="n"/>
-      <c r="J32" s="117" t="n"/>
-    </row>
-    <row r="33" ht="28" customHeight="1" s="132">
-      <c r="A33" s="42" t="inlineStr">
+      <c r="H33" s="117" t="n"/>
+      <c r="I33" s="117" t="n"/>
+      <c r="J33" s="117" t="n"/>
+    </row>
+    <row r="34" ht="14" customHeight="1" s="132">
+      <c r="A34" s="61" t="n"/>
+      <c r="B34" s="62" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="C34" s="63" t="inlineStr">
+        <is>
+          <t>Clear Out</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>First action only. The next pass to a side goes past you. One that named you is a TOV and ends the round</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="n"/>
+      <c r="F34" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" s="116" t="n"/>
+      <c r="H34" s="117" t="n"/>
+      <c r="I34" s="117" t="n"/>
+      <c r="J34" s="117" t="n"/>
+    </row>
+    <row r="35" ht="28" customHeight="1" s="132">
+      <c r="A35" s="42" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="B33" s="43">
-        <f>COUNTIF($B$5:$B$123,"Special Move")</f>
+      <c r="B35" s="43">
+        <f>COUNTIF($B$5:$B$131,"Special Move")</f>
         <v/>
       </c>
-      <c r="C33" s="44" t="n"/>
-      <c r="D33" s="44" t="n"/>
-      <c r="E33" s="44" t="n"/>
-      <c r="F33" s="82" t="n"/>
-      <c r="G33" s="120" t="n"/>
-      <c r="H33" s="121" t="n"/>
-      <c r="I33" s="121" t="n"/>
-      <c r="J33" s="121" t="n"/>
-    </row>
-    <row r="34" ht="28" customHeight="1" s="132">
-      <c r="A34" s="24" t="n"/>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="C35" s="44" t="n"/>
+      <c r="D35" s="44" t="n"/>
+      <c r="E35" s="44" t="n"/>
+      <c r="F35" s="82" t="n"/>
+      <c r="G35" s="120" t="n"/>
+      <c r="H35" s="121" t="n"/>
+      <c r="I35" s="121" t="n"/>
+      <c r="J35" s="121" t="n"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" s="132">
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Bankshot</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>Flip a coin:
 Heads: SHOT +10%
 Tails: SHOT -10%</t>
         </is>
       </c>
-      <c r="E34" s="27" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F34" s="83" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" s="105" t="n"/>
-      <c r="H34" s="106" t="n"/>
-      <c r="I34" s="106" t="n"/>
-      <c r="J34" s="106" t="n"/>
-    </row>
-    <row r="35" ht="28" customHeight="1" s="132">
-      <c r="A35" s="29" t="n"/>
-      <c r="B35" s="30" t="inlineStr">
-        <is>
-          <t>Special Move</t>
-        </is>
-      </c>
-      <c r="C35" s="31" t="inlineStr">
-        <is>
-          <t>Buzzer Beater</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
-      <c r="F35" s="74" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" s="128" t="inlineStr">
-        <is>
-          <t>Can only play with Shot Clock at 1</t>
-        </is>
-      </c>
-      <c r="H35" s="106" t="n"/>
-      <c r="I35" s="106" t="n"/>
-      <c r="J35" s="106" t="n"/>
-    </row>
-    <row r="36" ht="42" customHeight="1" s="132">
-      <c r="A36" s="29" t="n"/>
-      <c r="B36" s="30" t="inlineStr">
-        <is>
-          <t>Special Move</t>
-        </is>
-      </c>
-      <c r="C36" s="32" t="inlineStr">
-        <is>
-          <t>Dagger Three</t>
-        </is>
-      </c>
-      <c r="D36" s="94" t="inlineStr">
-        <is>
-          <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
-        </is>
-      </c>
-      <c r="E36" s="33" t="inlineStr">
-        <is>
-          <t>Shoot the ball. +1 Point on make</t>
-        </is>
-      </c>
-      <c r="F36" s="80" t="n">
+      <c r="F36" s="83" t="n">
         <v>4</v>
       </c>
       <c r="G36" s="105" t="n"/>
@@ -3609,28 +3596,32 @@
       </c>
       <c r="C37" s="31" t="inlineStr">
         <is>
-          <t>Fadeaway</t>
+          <t>Buzzer Beater</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>SHOT -10%. Draw 1 card</t>
+          <t>SHOT = 100%</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball.</t>
+          <t>Shoot the ball</t>
         </is>
       </c>
       <c r="F37" s="74" t="n">
-        <v>10</v>
-      </c>
-      <c r="G37" s="112" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="G37" s="128" t="inlineStr">
+        <is>
+          <t>Can only play with Shot Clock at 1</t>
+        </is>
+      </c>
       <c r="H37" s="106" t="n"/>
       <c r="I37" s="106" t="n"/>
       <c r="J37" s="106" t="n"/>
     </row>
-    <row r="38" ht="28" customHeight="1" s="132">
+    <row r="38" ht="42" customHeight="1" s="132">
       <c r="A38" s="29" t="n"/>
       <c r="B38" s="30" t="inlineStr">
         <is>
@@ -3639,12 +3630,12 @@
       </c>
       <c r="C38" s="32" t="inlineStr">
         <is>
-          <t>From the Hash</t>
+          <t>Dagger Three</t>
         </is>
       </c>
       <c r="D38" s="94" t="inlineStr">
         <is>
-          <t>SHOT -20%</t>
+          <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
         </is>
       </c>
       <c r="E38" s="33" t="inlineStr">
@@ -3653,14 +3644,14 @@
         </is>
       </c>
       <c r="F38" s="80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="105" t="n"/>
       <c r="H38" s="106" t="n"/>
       <c r="I38" s="106" t="n"/>
       <c r="J38" s="106" t="n"/>
     </row>
-    <row r="39" ht="42" customHeight="1" s="132">
+    <row r="39" ht="28" customHeight="1" s="132">
       <c r="A39" s="29" t="n"/>
       <c r="B39" s="30" t="inlineStr">
         <is>
@@ -3669,28 +3660,28 @@
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>From the Logo</t>
-        </is>
-      </c>
-      <c r="D39" s="91" t="inlineStr">
-        <is>
-          <t>SHOT -30%</t>
+          <t>Fadeaway</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>SHOT -10%. Draw 1 card</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball. +1 Point on make</t>
+          <t>Shoot the ball.</t>
         </is>
       </c>
       <c r="F39" s="74" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G39" s="112" t="n"/>
       <c r="H39" s="106" t="n"/>
       <c r="I39" s="106" t="n"/>
       <c r="J39" s="106" t="n"/>
     </row>
-    <row r="40" ht="57" customHeight="1" s="132" thickBot="1">
+    <row r="40" ht="28" customHeight="1" s="132">
       <c r="A40" s="29" t="n"/>
       <c r="B40" s="30" t="inlineStr">
         <is>
@@ -3699,12 +3690,12 @@
       </c>
       <c r="C40" s="32" t="inlineStr">
         <is>
-          <t>Full-Court Heave</t>
-        </is>
-      </c>
-      <c r="D40" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 10%</t>
+          <t>From the Hash</t>
+        </is>
+      </c>
+      <c r="D40" s="94" t="inlineStr">
+        <is>
+          <t>SHOT -20%</t>
         </is>
       </c>
       <c r="E40" s="33" t="inlineStr">
@@ -3720,7 +3711,7 @@
       <c r="I40" s="106" t="n"/>
       <c r="J40" s="106" t="n"/>
     </row>
-    <row r="41" ht="20" customHeight="1" s="132">
+    <row r="41" ht="42" customHeight="1" s="132">
       <c r="A41" s="29" t="n"/>
       <c r="B41" s="30" t="inlineStr">
         <is>
@@ -3729,17 +3720,17 @@
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>Putback Tip</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10%</t>
+          <t>From the Logo</t>
+        </is>
+      </c>
+      <c r="D41" s="91" t="inlineStr">
+        <is>
+          <t>SHOT -30%</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball. After a missed shot: SHOT = 100%</t>
+          <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
       <c r="F41" s="74" t="n">
@@ -3750,7 +3741,7 @@
       <c r="I41" s="106" t="n"/>
       <c r="J41" s="106" t="n"/>
     </row>
-    <row r="42" ht="28" customHeight="1" s="132">
+    <row r="42" ht="57" customHeight="1" s="132">
       <c r="A42" s="29" t="n"/>
       <c r="B42" s="30" t="inlineStr">
         <is>
@@ -3759,28 +3750,28 @@
       </c>
       <c r="C42" s="32" t="inlineStr">
         <is>
-          <t>Skyhook</t>
+          <t>Full-Court Heave</t>
         </is>
       </c>
       <c r="D42" s="33" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
-        </is>
-      </c>
-      <c r="E42" s="94" t="inlineStr">
-        <is>
-          <t>Shoot the ball. Shot is unaffected by Clamps</t>
+          <t>SHOT = 10%</t>
+        </is>
+      </c>
+      <c r="E42" s="33" t="inlineStr">
+        <is>
+          <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
       <c r="F42" s="80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" s="105" t="n"/>
       <c r="H42" s="106" t="n"/>
       <c r="I42" s="106" t="n"/>
       <c r="J42" s="106" t="n"/>
     </row>
-    <row r="43" ht="28" customHeight="1" s="132">
+    <row r="43" ht="20" customHeight="1" s="132">
       <c r="A43" s="29" t="n"/>
       <c r="B43" s="30" t="inlineStr">
         <is>
@@ -3789,201 +3780,201 @@
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>Slam Dunk</t>
+          <t>Putback Tip</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%. SHOT = 100% if SHOT &gt;= 70%</t>
+          <t>SHOT +10%</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball</t>
+          <t>Shoot the ball. After a missed shot: SHOT = 100%</t>
         </is>
       </c>
       <c r="F43" s="74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="112" t="n"/>
       <c r="H43" s="106" t="n"/>
       <c r="I43" s="106" t="n"/>
       <c r="J43" s="106" t="n"/>
     </row>
-    <row r="44" ht="42" customHeight="1" s="132">
-      <c r="A44" s="52" t="n"/>
-      <c r="B44" s="53" t="inlineStr">
+    <row r="44" ht="28" customHeight="1" s="132">
+      <c r="A44" s="29" t="n"/>
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C44" s="69" t="inlineStr">
-        <is>
-          <t>Turnaround Three</t>
-        </is>
-      </c>
-      <c r="D44" s="70" t="inlineStr">
-        <is>
-          <t>Discard any number of cards. SHOT +10% for each</t>
-        </is>
-      </c>
-      <c r="E44" s="70" t="inlineStr">
-        <is>
-          <t>Shoot the ball. +1 Point on make</t>
-        </is>
-      </c>
-      <c r="F44" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="129" t="inlineStr">
-        <is>
-          <t>Only 1 in deck</t>
-        </is>
-      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>Skyhook</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E44" s="94" t="inlineStr">
+        <is>
+          <t>Shoot the ball. Shot is unaffected by Clamps</t>
+        </is>
+      </c>
+      <c r="F44" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" s="105" t="n"/>
       <c r="H44" s="106" t="n"/>
       <c r="I44" s="106" t="n"/>
       <c r="J44" s="106" t="n"/>
     </row>
-    <row r="45" ht="42" customHeight="1" s="132">
-      <c r="A45" s="61" t="n"/>
-      <c r="B45" s="62" t="inlineStr">
+    <row r="45" ht="28" customHeight="1" s="132">
+      <c r="A45" s="29" t="n"/>
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C45" s="66" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Slam Dunk</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10%. SHOT = 100% if SHOT &gt;= 70%</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Shoot the ball</t>
+        </is>
+      </c>
+      <c r="F45" s="74" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" s="112" t="n"/>
+      <c r="H45" s="106" t="n"/>
+      <c r="I45" s="106" t="n"/>
+      <c r="J45" s="106" t="n"/>
+    </row>
+    <row r="46" ht="42" customHeight="1" s="132">
+      <c r="A46" s="52" t="n"/>
+      <c r="B46" s="53" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C46" s="69" t="inlineStr">
+        <is>
+          <t>Turnaround Three</t>
+        </is>
+      </c>
+      <c r="D46" s="70" t="inlineStr">
+        <is>
+          <t>Discard any number of cards. SHOT +10% for each</t>
+        </is>
+      </c>
+      <c r="E46" s="70" t="inlineStr">
+        <is>
+          <t>Shoot the ball. +1 Point on make</t>
+        </is>
+      </c>
+      <c r="F46" s="84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="129" t="inlineStr">
+        <is>
+          <t>Only 1 in deck</t>
+        </is>
+      </c>
+      <c r="H46" s="106" t="n"/>
+      <c r="I46" s="106" t="n"/>
+      <c r="J46" s="106" t="n"/>
+    </row>
+    <row r="47" ht="42" customHeight="1" s="132">
+      <c r="A47" s="61" t="n"/>
+      <c r="B47" s="62" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C47" s="66" t="inlineStr">
         <is>
           <t>Euro Step</t>
         </is>
       </c>
-      <c r="D45" s="67" t="inlineStr">
+      <c r="D47" s="67" t="inlineStr">
         <is>
           <t>Flip a coin until you get Tails. For each Heads, SHOT +5% and Draw 1 card</t>
         </is>
       </c>
-      <c r="E45" s="68" t="n"/>
-      <c r="F45" s="85" t="n">
+      <c r="E47" s="68" t="n"/>
+      <c r="F47" s="85" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="122" t="n"/>
-      <c r="H45" s="104" t="n"/>
-      <c r="I45" s="104" t="n"/>
-      <c r="J45" s="104" t="n"/>
-    </row>
-    <row r="46" ht="29" customHeight="1" s="132" thickBot="1">
-      <c r="A46" s="61" t="n"/>
-      <c r="B46" s="62" t="inlineStr">
+      <c r="G47" s="122" t="n"/>
+      <c r="H47" s="104" t="n"/>
+      <c r="I47" s="104" t="n"/>
+      <c r="J47" s="104" t="n"/>
+    </row>
+    <row r="48" ht="29" customHeight="1" s="132">
+      <c r="A48" s="61" t="n"/>
+      <c r="B48" s="62" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C46" s="66" t="inlineStr">
+      <c r="C48" s="66" t="inlineStr">
         <is>
           <t>Wide-Open Three</t>
         </is>
       </c>
-      <c r="D46" s="67" t="inlineStr">
+      <c r="D48" s="67" t="inlineStr">
         <is>
           <t>Select any number of other players. SHOT +10% for each</t>
         </is>
       </c>
-      <c r="E46" s="68" t="inlineStr">
+      <c r="E48" s="68" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make. Selected players receive +1 AST on a make</t>
         </is>
       </c>
-      <c r="F46" s="85" t="n">
+      <c r="F48" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="G46" s="122" t="inlineStr">
+      <c r="G48" s="122" t="inlineStr">
         <is>
           <t>Selecting none rolls off current SHOT and is still a three</t>
         </is>
       </c>
-      <c r="H46" s="104" t="n"/>
-      <c r="I46" s="104" t="n"/>
-      <c r="J46" s="104" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1" s="132">
-      <c r="A47" s="58" t="inlineStr">
+      <c r="H48" s="104" t="n"/>
+      <c r="I48" s="104" t="n"/>
+      <c r="J48" s="104" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1" s="132">
+      <c r="A49" s="58" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B47" s="59">
-        <f>COUNTIF($B$5:$B$123,"Clamp")</f>
+      <c r="B49" s="59">
+        <f>COUNTIF($B$5:$B$131,"Clamp")</f>
         <v/>
       </c>
-      <c r="C47" s="60" t="n"/>
-      <c r="D47" s="60" t="n"/>
-      <c r="E47" s="60" t="n"/>
-      <c r="F47" s="86" t="n"/>
-      <c r="G47" s="109" t="n"/>
-      <c r="H47" s="110" t="n"/>
-      <c r="I47" s="110" t="n"/>
-      <c r="J47" s="110" t="n"/>
-    </row>
-    <row r="48" ht="56" customHeight="1" s="132">
-      <c r="A48" s="29" t="n"/>
-      <c r="B48" s="30" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C48" s="31" t="inlineStr">
-        <is>
-          <t>Contest</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Next player SHOT -25% if they shoot</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G48" s="130" t="inlineStr">
-        <is>
-          <t>1 def</t>
-        </is>
-      </c>
-      <c r="H48" s="102" t="n"/>
-      <c r="I48" s="102" t="n"/>
-      <c r="J48" s="102" t="n"/>
-    </row>
-    <row r="49" ht="47" customHeight="1" s="132">
-      <c r="A49" s="29" t="n"/>
-      <c r="B49" s="30" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>Double-Team</t>
-        </is>
-      </c>
-      <c r="D49" s="33" t="inlineStr">
-        <is>
-          <t>Next Player cannot play 2 random cards from hand.</t>
-        </is>
-      </c>
-      <c r="E49" s="34" t="n"/>
-      <c r="F49" s="75" t="n">
-        <v>4</v>
-      </c>
-      <c r="G49" s="125" t="inlineStr">
-        <is>
-          <t>2 def</t>
-        </is>
-      </c>
-      <c r="H49" s="102" t="n"/>
-      <c r="I49" s="102" t="n"/>
-      <c r="J49" s="102" t="n"/>
-    </row>
-    <row r="50" ht="54" customHeight="1" s="132">
+      <c r="C49" s="60" t="n"/>
+      <c r="D49" s="60" t="n"/>
+      <c r="E49" s="60" t="n"/>
+      <c r="F49" s="86" t="n"/>
+      <c r="G49" s="109" t="n"/>
+      <c r="H49" s="110" t="n"/>
+      <c r="I49" s="110" t="n"/>
+      <c r="J49" s="110" t="n"/>
+    </row>
+    <row r="50" ht="56" customHeight="1" s="132">
       <c r="A50" s="29" t="n"/>
       <c r="B50" s="30" t="inlineStr">
         <is>
@@ -3992,17 +3983,17 @@
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
-          <t>Full-Court Press</t>
+          <t>Contest</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Next player discards 2 cards at the start of their turn</t>
+          <t>Next player SHOT -25% if they shoot</t>
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
       <c r="F50" s="76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G50" s="130" t="inlineStr">
         <is>
@@ -4013,7 +4004,7 @@
       <c r="I50" s="102" t="n"/>
       <c r="J50" s="102" t="n"/>
     </row>
-    <row r="51" ht="28" customHeight="1" s="132">
+    <row r="51" ht="47" customHeight="1" s="132">
       <c r="A51" s="29" t="n"/>
       <c r="B51" s="30" t="inlineStr">
         <is>
@@ -4022,171 +4013,183 @@
       </c>
       <c r="C51" s="32" t="inlineStr">
         <is>
-          <t>Trap</t>
-        </is>
-      </c>
-      <c r="D51" s="94" t="inlineStr">
-        <is>
-          <t>Next player can only play Pass cards during their turn</t>
+          <t>Double-Team</t>
+        </is>
+      </c>
+      <c r="D51" s="33" t="inlineStr">
+        <is>
+          <t>Next Player cannot play 2 random cards from hand.</t>
         </is>
       </c>
       <c r="E51" s="34" t="n"/>
       <c r="F51" s="75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" s="125" t="inlineStr">
         <is>
-          <t>They can still shoot as another option; 3 def</t>
+          <t>2 def</t>
         </is>
       </c>
       <c r="H51" s="102" t="n"/>
       <c r="I51" s="102" t="n"/>
       <c r="J51" s="102" t="n"/>
     </row>
-    <row r="52" ht="28" customHeight="1" s="132">
-      <c r="A52" s="61" t="n"/>
-      <c r="B52" s="62" t="inlineStr">
+    <row r="52" ht="54" customHeight="1" s="132">
+      <c r="A52" s="29" t="n"/>
+      <c r="B52" s="30" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C52" s="66" t="inlineStr">
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>Full-Court Press</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Next player discards 2 cards at the start of their turn</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="130" t="inlineStr">
+        <is>
+          <t>1 def</t>
+        </is>
+      </c>
+      <c r="H52" s="102" t="n"/>
+      <c r="I52" s="102" t="n"/>
+      <c r="J52" s="102" t="n"/>
+    </row>
+    <row r="53" ht="28" customHeight="1" s="132">
+      <c r="A53" s="29" t="n"/>
+      <c r="B53" s="30" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>Trap</t>
+        </is>
+      </c>
+      <c r="D53" s="94" t="inlineStr">
+        <is>
+          <t>Next player can only play Pass cards during their turn</t>
+        </is>
+      </c>
+      <c r="E53" s="34" t="n"/>
+      <c r="F53" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" s="125" t="inlineStr">
+        <is>
+          <t>They can still shoot as another option; 3 def</t>
+        </is>
+      </c>
+      <c r="H53" s="102" t="n"/>
+      <c r="I53" s="102" t="n"/>
+      <c r="J53" s="102" t="n"/>
+    </row>
+    <row r="54" ht="28" customHeight="1" s="132">
+      <c r="A54" s="61" t="n"/>
+      <c r="B54" s="62" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C54" s="66" t="inlineStr">
         <is>
           <t>Triple-Team</t>
         </is>
       </c>
-      <c r="D52" s="67" t="inlineStr">
+      <c r="D54" s="67" t="inlineStr">
         <is>
           <t>Next player cannot play 3 random cards from hand.</t>
         </is>
       </c>
-      <c r="E52" s="68" t="n"/>
-      <c r="F52" s="85" t="n">
+      <c r="E54" s="68" t="n"/>
+      <c r="F54" s="85" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="135" t="inlineStr">
+      <c r="G54" s="135" t="inlineStr">
         <is>
           <t>3 def</t>
         </is>
       </c>
-      <c r="H52" s="117" t="n"/>
-      <c r="I52" s="117" t="n"/>
-      <c r="J52" s="117" t="n"/>
-    </row>
-    <row r="53" ht="28" customHeight="1" s="132">
-      <c r="A53" s="58" t="inlineStr">
+      <c r="H54" s="117" t="n"/>
+      <c r="I54" s="117" t="n"/>
+      <c r="J54" s="117" t="n"/>
+    </row>
+    <row r="55" ht="28" customHeight="1" s="132">
+      <c r="A55" s="58" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="B53" s="59">
-        <f>COUNTIF($B$5:$B$123,"Whistle")</f>
+      <c r="B55" s="59">
+        <f>COUNTIF($B$5:$B$131,"Whistle")</f>
         <v/>
       </c>
-      <c r="C53" s="60" t="n"/>
-      <c r="D53" s="60" t="n"/>
-      <c r="E53" s="60" t="n"/>
-      <c r="F53" s="86" t="n"/>
-      <c r="G53" s="109" t="n"/>
-      <c r="H53" s="110" t="n"/>
-      <c r="I53" s="110" t="n"/>
-      <c r="J53" s="110" t="n"/>
-    </row>
-    <row r="54" ht="42" customHeight="1" s="132">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="C55" s="60" t="n"/>
+      <c r="D55" s="60" t="n"/>
+      <c r="E55" s="60" t="n"/>
+      <c r="F55" s="86" t="n"/>
+      <c r="G55" s="109" t="n"/>
+      <c r="H55" s="110" t="n"/>
+      <c r="I55" s="110" t="n"/>
+      <c r="J55" s="110" t="n"/>
+    </row>
+    <row r="56" ht="42" customHeight="1" s="132">
+      <c r="A56" s="29" t="inlineStr">
         <is>
           <t>All whistles are limited to 1</t>
         </is>
       </c>
-      <c r="B54" s="30" t="inlineStr">
+      <c r="B56" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C54" s="31" t="inlineStr">
+      <c r="C56" s="31" t="inlineStr">
         <is>
           <t>Back Court Violation</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="138" t="n"/>
-      <c r="G54" s="101" t="inlineStr">
-        <is>
-          <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
-        </is>
-      </c>
-      <c r="H54" s="102" t="n"/>
-      <c r="I54" s="102" t="n"/>
-      <c r="J54" s="102" t="n"/>
-    </row>
-    <row r="55" ht="40" customHeight="1" s="132">
-      <c r="A55" s="29" t="n"/>
-      <c r="B55" s="30" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C55" s="90" t="inlineStr">
-        <is>
-          <t>Blocking Foul</t>
-        </is>
-      </c>
-      <c r="D55" s="93" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
-        </is>
-      </c>
-      <c r="E55" s="34" t="n"/>
-      <c r="F55" s="138" t="n"/>
-      <c r="G55" s="107" t="n"/>
-      <c r="H55" s="102" t="n"/>
-      <c r="I55" s="102" t="n"/>
-      <c r="J55" s="102" t="n"/>
-    </row>
-    <row r="56" ht="30" customHeight="1" s="132">
-      <c r="A56" s="29" t="n"/>
-      <c r="B56" s="30" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C56" s="31" t="inlineStr">
-        <is>
-          <t>Charge</t>
-        </is>
-      </c>
-      <c r="D56" s="92" t="inlineStr">
-        <is>
-          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
         </is>
       </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="138" t="n"/>
-      <c r="G56" s="101" t="n"/>
+      <c r="G56" s="101" t="inlineStr">
+        <is>
+          <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
+        </is>
+      </c>
       <c r="H56" s="102" t="n"/>
       <c r="I56" s="102" t="n"/>
       <c r="J56" s="102" t="n"/>
     </row>
-    <row r="57" ht="56" customHeight="1" s="132">
+    <row r="57" ht="40" customHeight="1" s="132">
       <c r="A57" s="29" t="n"/>
       <c r="B57" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C57" s="32" t="inlineStr">
-        <is>
-          <t>Cleared to Play</t>
-        </is>
-      </c>
-      <c r="D57" s="33" t="inlineStr">
-        <is>
-          <t>Injury Card Played: Cancel card.</t>
+      <c r="C57" s="90" t="inlineStr">
+        <is>
+          <t>Blocking Foul</t>
+        </is>
+      </c>
+      <c r="D57" s="93" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
         </is>
       </c>
       <c r="E57" s="34" t="n"/>
@@ -4196,7 +4199,7 @@
       <c r="I57" s="102" t="n"/>
       <c r="J57" s="102" t="n"/>
     </row>
-    <row r="58" ht="42" customHeight="1" s="132">
+    <row r="58" ht="30" customHeight="1" s="132">
       <c r="A58" s="29" t="n"/>
       <c r="B58" s="30" t="inlineStr">
         <is>
@@ -4205,53 +4208,41 @@
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>Coach’s Challenge</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Any Whistle Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>Pull a Timeout from the discards, if one is there, and take it</t>
-        </is>
-      </c>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="D58" s="92" t="inlineStr">
+        <is>
+          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="n"/>
       <c r="F58" s="138" t="n"/>
       <c r="G58" s="101" t="n"/>
       <c r="H58" s="102" t="n"/>
       <c r="I58" s="102" t="n"/>
       <c r="J58" s="102" t="n"/>
     </row>
-    <row r="59" ht="42" customHeight="1" s="132">
+    <row r="59" ht="56" customHeight="1" s="132">
       <c r="A59" s="29" t="n"/>
       <c r="B59" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C59" s="90" t="inlineStr">
-        <is>
-          <t>Delay-of-Game Warning</t>
-        </is>
-      </c>
-      <c r="D59" s="94" t="inlineStr">
-        <is>
-          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
-        </is>
-      </c>
-      <c r="E59" s="33" t="inlineStr">
-        <is>
-          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
-        </is>
-      </c>
-      <c r="F59" s="139" t="n"/>
-      <c r="G59" s="113" t="inlineStr">
-        <is>
-          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
-        </is>
-      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>Cleared to Play</t>
+        </is>
+      </c>
+      <c r="D59" s="33" t="inlineStr">
+        <is>
+          <t>Injury Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E59" s="34" t="n"/>
+      <c r="F59" s="138" t="n"/>
+      <c r="G59" s="107" t="n"/>
       <c r="H59" s="102" t="n"/>
       <c r="I59" s="102" t="n"/>
       <c r="J59" s="102" t="n"/>
@@ -4265,26 +4256,26 @@
       </c>
       <c r="C60" s="31" t="inlineStr">
         <is>
-          <t>Double Dribble</t>
+          <t>Coach’s Challenge</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="n"/>
+          <t>Any Whistle Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Pull a Timeout from the discards, if one is there, and take it</t>
+        </is>
+      </c>
       <c r="F60" s="138" t="n"/>
-      <c r="G60" s="101" t="inlineStr">
-        <is>
-          <t>The dribbling player inbounds. The round is NOT incremented.</t>
-        </is>
-      </c>
+      <c r="G60" s="101" t="n"/>
       <c r="H60" s="102" t="n"/>
       <c r="I60" s="102" t="n"/>
       <c r="J60" s="102" t="n"/>
     </row>
-    <row r="61" ht="28" customHeight="1" s="132">
+    <row r="61" ht="42" customHeight="1" s="132">
       <c r="A61" s="29" t="n"/>
       <c r="B61" s="30" t="inlineStr">
         <is>
@@ -4293,17 +4284,25 @@
       </c>
       <c r="C61" s="90" t="inlineStr">
         <is>
-          <t>Flagrant Foul</t>
+          <t>Delay-of-Game Warning</t>
         </is>
       </c>
       <c r="D61" s="94" t="inlineStr">
         <is>
-          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E61" s="34" t="n"/>
-      <c r="F61" s="138" t="n"/>
-      <c r="G61" s="107" t="n"/>
+          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
+        </is>
+      </c>
+      <c r="E61" s="33" t="inlineStr">
+        <is>
+          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
+        </is>
+      </c>
+      <c r="F61" s="139" t="n"/>
+      <c r="G61" s="113" t="inlineStr">
+        <is>
+          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
+        </is>
+      </c>
       <c r="H61" s="102" t="n"/>
       <c r="I61" s="102" t="n"/>
       <c r="J61" s="102" t="n"/>
@@ -4315,38 +4314,42 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C62" s="90" t="inlineStr">
-        <is>
-          <t>Flagrant Foul II</t>
-        </is>
-      </c>
-      <c r="D62" s="91" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
+      <c r="C62" s="31" t="inlineStr">
+        <is>
+          <t>Double Dribble</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
         </is>
       </c>
       <c r="E62" s="7" t="n"/>
       <c r="F62" s="138" t="n"/>
-      <c r="G62" s="101" t="n"/>
+      <c r="G62" s="101" t="inlineStr">
+        <is>
+          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+        </is>
+      </c>
       <c r="H62" s="102" t="n"/>
       <c r="I62" s="102" t="n"/>
       <c r="J62" s="102" t="n"/>
     </row>
-    <row r="63" ht="29" customHeight="1" s="132" thickBot="1">
+    <row r="63" ht="28" customHeight="1" s="132">
       <c r="A63" s="29" t="n"/>
       <c r="B63" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C63" s="32" t="inlineStr">
-        <is>
-          <t>Goaltending</t>
-        </is>
-      </c>
-      <c r="D63" s="33" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
+      <c r="C63" s="90" t="inlineStr">
+        <is>
+          <t>Flagrant Foul</t>
+        </is>
+      </c>
+      <c r="D63" s="94" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
         </is>
       </c>
       <c r="E63" s="34" t="n"/>
@@ -4356,21 +4359,21 @@
       <c r="I63" s="102" t="n"/>
       <c r="J63" s="102" t="n"/>
     </row>
-    <row r="64" ht="20" customHeight="1" s="132">
+    <row r="64" ht="42" customHeight="1" s="132">
       <c r="A64" s="29" t="n"/>
       <c r="B64" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C64" s="31" t="inlineStr">
-        <is>
-          <t>Inadvertent Whistle</t>
+      <c r="C64" s="90" t="inlineStr">
+        <is>
+          <t>Flagrant Foul II</t>
         </is>
       </c>
       <c r="D64" s="91" t="inlineStr">
         <is>
-          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
+          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
@@ -4380,7 +4383,7 @@
       <c r="I64" s="102" t="n"/>
       <c r="J64" s="102" t="n"/>
     </row>
-    <row r="65" ht="28" customHeight="1" s="132">
+    <row r="65" ht="29" customHeight="1" s="132">
       <c r="A65" s="29" t="n"/>
       <c r="B65" s="30" t="inlineStr">
         <is>
@@ -4389,12 +4392,12 @@
       </c>
       <c r="C65" s="32" t="inlineStr">
         <is>
-          <t>Official Review</t>
-        </is>
-      </c>
-      <c r="D65" s="94" t="inlineStr">
-        <is>
-          <t>Intangible Played: Discard all Intangibles from player.</t>
+          <t>Goaltending</t>
+        </is>
+      </c>
+      <c r="D65" s="33" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
         </is>
       </c>
       <c r="E65" s="34" t="n"/>
@@ -4404,7 +4407,7 @@
       <c r="I65" s="102" t="n"/>
       <c r="J65" s="102" t="n"/>
     </row>
-    <row r="66" ht="28" customHeight="1" s="132">
+    <row r="66" ht="20" customHeight="1" s="132">
       <c r="A66" s="29" t="n"/>
       <c r="B66" s="30" t="inlineStr">
         <is>
@@ -4413,26 +4416,22 @@
       </c>
       <c r="C66" s="31" t="inlineStr">
         <is>
-          <t>Shot Clock Violation</t>
+          <t>Inadvertent Whistle</t>
         </is>
       </c>
       <c r="D66" s="91" t="inlineStr">
         <is>
-          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
+          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
         </is>
       </c>
       <c r="E66" s="7" t="n"/>
       <c r="F66" s="138" t="n"/>
-      <c r="G66" s="101" t="inlineStr">
-        <is>
-          <t>This inbound does NOT increment the round.</t>
-        </is>
-      </c>
+      <c r="G66" s="101" t="n"/>
       <c r="H66" s="102" t="n"/>
       <c r="I66" s="102" t="n"/>
       <c r="J66" s="102" t="n"/>
     </row>
-    <row r="67" ht="14" customHeight="1" s="132">
+    <row r="67" ht="28" customHeight="1" s="132">
       <c r="A67" s="29" t="n"/>
       <c r="B67" s="30" t="inlineStr">
         <is>
@@ -4441,12 +4440,12 @@
       </c>
       <c r="C67" s="32" t="inlineStr">
         <is>
-          <t>Technical Foul</t>
+          <t>Official Review</t>
         </is>
       </c>
       <c r="D67" s="94" t="inlineStr">
         <is>
-          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
+          <t>Intangible Played: Discard all Intangibles from player.</t>
         </is>
       </c>
       <c r="E67" s="34" t="n"/>
@@ -4456,7 +4455,7 @@
       <c r="I67" s="102" t="n"/>
       <c r="J67" s="102" t="n"/>
     </row>
-    <row r="68" ht="14" customHeight="1" s="132">
+    <row r="68" ht="28" customHeight="1" s="132">
       <c r="A68" s="29" t="n"/>
       <c r="B68" s="30" t="inlineStr">
         <is>
@@ -4465,147 +4464,143 @@
       </c>
       <c r="C68" s="31" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>Shot Clock Violation</t>
         </is>
       </c>
       <c r="D68" s="91" t="inlineStr">
         <is>
-          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
         </is>
       </c>
       <c r="E68" s="7" t="n"/>
       <c r="F68" s="138" t="n"/>
-      <c r="G68" s="101" t="n"/>
+      <c r="G68" s="101" t="inlineStr">
+        <is>
+          <t>This inbound does NOT increment the round.</t>
+        </is>
+      </c>
       <c r="H68" s="102" t="n"/>
       <c r="I68" s="102" t="n"/>
       <c r="J68" s="102" t="n"/>
     </row>
     <row r="69" ht="14" customHeight="1" s="132">
-      <c r="A69" s="61" t="n"/>
-      <c r="B69" s="62" t="inlineStr">
+      <c r="A69" s="29" t="n"/>
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C69" s="63" t="inlineStr">
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>Technical Foul</t>
+        </is>
+      </c>
+      <c r="D69" s="94" t="inlineStr">
+        <is>
+          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E69" s="34" t="n"/>
+      <c r="F69" s="138" t="n"/>
+      <c r="G69" s="107" t="n"/>
+      <c r="H69" s="102" t="n"/>
+      <c r="I69" s="102" t="n"/>
+      <c r="J69" s="102" t="n"/>
+    </row>
+    <row r="70" ht="14" customHeight="1" s="132">
+      <c r="A70" s="29" t="n"/>
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D70" s="91" t="inlineStr">
+        <is>
+          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="138" t="n"/>
+      <c r="G70" s="101" t="n"/>
+      <c r="H70" s="102" t="n"/>
+      <c r="I70" s="102" t="n"/>
+      <c r="J70" s="102" t="n"/>
+    </row>
+    <row r="71" ht="14" customHeight="1" s="132">
+      <c r="A71" s="61" t="n"/>
+      <c r="B71" s="62" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C71" s="63" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="D69" s="64" t="inlineStr">
+      <c r="D71" s="64" t="inlineStr">
         <is>
           <t>Move card played: Cancel card. TOV +1</t>
         </is>
       </c>
-      <c r="E69" s="65" t="n"/>
-      <c r="F69" s="140" t="n"/>
-      <c r="G69" s="116" t="n"/>
-      <c r="H69" s="117" t="n"/>
-      <c r="I69" s="117" t="n"/>
-      <c r="J69" s="117" t="n"/>
-    </row>
-    <row r="70" ht="28" customHeight="1" s="132">
-      <c r="A70" s="61" t="n"/>
-      <c r="B70" s="62" t="inlineStr">
+      <c r="E71" s="65" t="n"/>
+      <c r="F71" s="140" t="n"/>
+      <c r="G71" s="116" t="n"/>
+      <c r="H71" s="117" t="n"/>
+      <c r="I71" s="117" t="n"/>
+      <c r="J71" s="117" t="n"/>
+    </row>
+    <row r="72" ht="28" customHeight="1" s="132">
+      <c r="A72" s="61" t="n"/>
+      <c r="B72" s="62" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C70" s="63" t="inlineStr">
+      <c r="C72" s="63" t="inlineStr">
         <is>
           <t>Clear Path Foul</t>
         </is>
       </c>
-      <c r="D70" s="64" t="inlineStr">
+      <c r="D72" s="64" t="inlineStr">
         <is>
           <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
         </is>
       </c>
-      <c r="E70" s="65" t="n"/>
-      <c r="F70" s="140" t="n"/>
-      <c r="G70" s="116" t="inlineStr">
+      <c r="E72" s="65" t="n"/>
+      <c r="F72" s="140" t="n"/>
+      <c r="G72" s="116" t="inlineStr">
         <is>
           <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
         </is>
       </c>
-      <c r="H70" s="117" t="n"/>
-      <c r="I70" s="117" t="n"/>
-      <c r="J70" s="117" t="n"/>
-    </row>
-    <row r="71" ht="28" customHeight="1" s="132">
-      <c r="A71" s="58" t="inlineStr">
+      <c r="H72" s="117" t="n"/>
+      <c r="I72" s="117" t="n"/>
+      <c r="J72" s="117" t="n"/>
+    </row>
+    <row r="73" ht="28" customHeight="1" s="132">
+      <c r="A73" s="58" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B71" s="59">
-        <f>COUNTIF($B$5:$B$123,"Game Break")</f>
+      <c r="B73" s="59">
+        <f>COUNTIF($B$5:$B$131,"Game Break")</f>
         <v/>
       </c>
-      <c r="C71" s="60" t="n"/>
-      <c r="D71" s="60" t="n"/>
-      <c r="E71" s="60" t="n"/>
-      <c r="F71" s="86" t="n"/>
-      <c r="G71" s="109" t="n"/>
-      <c r="H71" s="110" t="n"/>
-      <c r="I71" s="110" t="n"/>
-      <c r="J71" s="110" t="n"/>
-    </row>
-    <row r="72" ht="28" customHeight="1" s="132">
-      <c r="A72" s="29" t="n"/>
-      <c r="B72" s="30" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>2-Minute Warning</t>
-        </is>
-      </c>
-      <c r="D72" s="33" t="inlineStr">
-        <is>
-          <t>All players discard down to 2 or fewer cards</t>
-        </is>
-      </c>
-      <c r="E72" s="34" t="n"/>
-      <c r="F72" s="75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G72" s="107" t="n"/>
-      <c r="H72" s="102" t="n"/>
-      <c r="I72" s="102" t="n"/>
-      <c r="J72" s="102" t="n"/>
-    </row>
-    <row r="73" ht="42" customHeight="1" s="132">
-      <c r="A73" s="29" t="n"/>
-      <c r="B73" s="30" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C73" s="31" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G73" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
-      <c r="H73" s="102" t="n"/>
-      <c r="I73" s="102" t="n"/>
-      <c r="J73" s="102" t="n"/>
+      <c r="C73" s="60" t="n"/>
+      <c r="D73" s="60" t="n"/>
+      <c r="E73" s="60" t="n"/>
+      <c r="F73" s="86" t="n"/>
+      <c r="G73" s="109" t="n"/>
+      <c r="H73" s="110" t="n"/>
+      <c r="I73" s="110" t="n"/>
+      <c r="J73" s="110" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1" s="132">
       <c r="A74" s="29" t="n"/>
@@ -4616,24 +4611,24 @@
       </c>
       <c r="C74" s="32" t="inlineStr">
         <is>
-          <t>Crowd Noise</t>
+          <t>2-Minute Warning</t>
         </is>
       </c>
       <c r="D74" s="33" t="inlineStr">
         <is>
-          <t>Discard 1 card.</t>
+          <t>All players discard down to 2 or fewer cards</t>
         </is>
       </c>
       <c r="E74" s="34" t="n"/>
       <c r="F74" s="75" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G74" s="107" t="n"/>
       <c r="H74" s="102" t="n"/>
       <c r="I74" s="102" t="n"/>
       <c r="J74" s="102" t="n"/>
     </row>
-    <row r="75" ht="28" customHeight="1" s="132">
+    <row r="75" ht="42" customHeight="1" s="132">
       <c r="A75" s="29" t="n"/>
       <c r="B75" s="30" t="inlineStr">
         <is>
@@ -4642,43 +4637,47 @@
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>Designed Play</t>
+          <t>Benched</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Draw up to a hand of 5</t>
+          <t>Immediately give ball to any other player.</t>
         </is>
       </c>
       <c r="E75" s="7" t="n"/>
       <c r="F75" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G75" s="101" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="G75" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H75" s="102" t="n"/>
       <c r="I75" s="102" t="n"/>
       <c r="J75" s="102" t="n"/>
     </row>
-    <row r="76" ht="20" customHeight="1" s="132">
+    <row r="76" ht="28" customHeight="1" s="132">
       <c r="A76" s="29" t="n"/>
       <c r="B76" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C76" s="90" t="inlineStr">
-        <is>
-          <t>Foul</t>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>Take 1 FT</t>
+          <t>Discard 1 card.</t>
         </is>
       </c>
       <c r="E76" s="34" t="n"/>
       <c r="F76" s="75" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G76" s="107" t="n"/>
       <c r="H76" s="102" t="n"/>
@@ -4694,17 +4693,17 @@
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>MVP Vote</t>
+          <t>Designed Play</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Draw 3 cards up to a hand of 7</t>
+          <t>Draw up to a hand of 5</t>
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
       <c r="F77" s="76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G77" s="101" t="n"/>
       <c r="H77" s="102" t="n"/>
@@ -4718,26 +4717,26 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>Off Night</t>
+      <c r="C78" s="90" t="inlineStr">
+        <is>
+          <t>Foul</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>SHOT -20% this possession</t>
+          <t>Take 1 FT</t>
         </is>
       </c>
       <c r="E78" s="34" t="n"/>
       <c r="F78" s="75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G78" s="107" t="n"/>
       <c r="H78" s="102" t="n"/>
       <c r="I78" s="102" t="n"/>
       <c r="J78" s="102" t="n"/>
     </row>
-    <row r="79" ht="42" customHeight="1" s="132">
+    <row r="79" ht="28" customHeight="1" s="132">
       <c r="A79" s="29" t="n"/>
       <c r="B79" s="30" t="inlineStr">
         <is>
@@ -4746,28 +4745,24 @@
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
-          <t>Swallowed Whistle</t>
+          <t>MVP Vote</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F79" s="74" t="n">
-        <v>5</v>
+          <t>Draw 3 cards up to a hand of 7</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="76" t="n">
+        <v>1</v>
       </c>
       <c r="G79" s="101" t="n"/>
       <c r="H79" s="102" t="n"/>
       <c r="I79" s="102" t="n"/>
       <c r="J79" s="102" t="n"/>
     </row>
-    <row r="80" ht="28" customHeight="1" s="132">
+    <row r="80" ht="20" customHeight="1" s="132">
       <c r="A80" s="29" t="n"/>
       <c r="B80" s="30" t="inlineStr">
         <is>
@@ -4776,26 +4771,24 @@
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
-          <t>Rock Fight</t>
+          <t>Off Night</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>Players cannot shoot when SHOT is 50% or higher</t>
-        </is>
-      </c>
-      <c r="E80" s="33" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F80" s="80" t="n"/>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E80" s="34" t="n"/>
+      <c r="F80" s="75" t="n">
+        <v>3</v>
+      </c>
       <c r="G80" s="107" t="n"/>
       <c r="H80" s="102" t="n"/>
       <c r="I80" s="102" t="n"/>
       <c r="J80" s="102" t="n"/>
     </row>
-    <row r="81" ht="56" customHeight="1" s="132">
+    <row r="81" ht="42" customHeight="1" s="132">
       <c r="A81" s="29" t="n"/>
       <c r="B81" s="30" t="inlineStr">
         <is>
@@ -4804,82 +4797,84 @@
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
-          <t>Traded Mid-Game</t>
+          <t>Swallowed Whistle</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Swap positions with random other player</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="n"/>
-      <c r="F81" s="76" t="n"/>
-      <c r="G81" s="111" t="inlineStr">
-        <is>
-          <t>Applies to rest of game</t>
-        </is>
-      </c>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F81" s="74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G81" s="101" t="n"/>
       <c r="H81" s="102" t="n"/>
       <c r="I81" s="102" t="n"/>
       <c r="J81" s="102" t="n"/>
     </row>
-    <row r="82" ht="42" customHeight="1" s="132">
+    <row r="82" ht="28" customHeight="1" s="132">
       <c r="A82" s="29" t="n"/>
       <c r="B82" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C82" s="134" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D82" s="91" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G82" s="111" t="n"/>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D82" s="33" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is 50% or higher</t>
+        </is>
+      </c>
+      <c r="E82" s="33" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F82" s="80" t="n"/>
+      <c r="G82" s="107" t="n"/>
       <c r="H82" s="102" t="n"/>
       <c r="I82" s="102" t="n"/>
       <c r="J82" s="102" t="n"/>
     </row>
-    <row r="83" ht="42" customHeight="1" s="132">
+    <row r="83" ht="56" customHeight="1" s="132">
       <c r="A83" s="29" t="n"/>
       <c r="B83" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C83" s="134" t="inlineStr">
-        <is>
-          <t>All-Swissh Selection</t>
-        </is>
-      </c>
-      <c r="D83" s="91" t="inlineStr">
-        <is>
-          <t>Draw 3 cards after your next make</t>
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Swap positions with random other player</t>
         </is>
       </c>
       <c r="E83" s="7" t="n"/>
-      <c r="F83" s="76" t="n">
-        <v>3</v>
-      </c>
+      <c r="F83" s="76" t="n"/>
       <c r="G83" s="111" t="inlineStr">
         <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
+          <t>Applies to rest of game</t>
         </is>
       </c>
       <c r="H83" s="102" t="n"/>
       <c r="I83" s="102" t="n"/>
       <c r="J83" s="102" t="n"/>
     </row>
-    <row r="84" ht="28" customHeight="1" s="132">
+    <row r="84" ht="42" customHeight="1" s="132">
       <c r="A84" s="29" t="n"/>
       <c r="B84" s="30" t="inlineStr">
         <is>
@@ -4888,24 +4883,24 @@
       </c>
       <c r="C84" s="134" t="inlineStr">
         <is>
-          <t>All Star Selection</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D84" s="91" t="inlineStr">
         <is>
-          <t>Draw 2 cards</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
       <c r="F84" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G84" s="111" t="n"/>
       <c r="H84" s="102" t="n"/>
       <c r="I84" s="102" t="n"/>
       <c r="J84" s="102" t="n"/>
     </row>
-    <row r="85" ht="28" customHeight="1" s="132">
+    <row r="85" ht="42" customHeight="1" s="132">
       <c r="A85" s="29" t="n"/>
       <c r="B85" s="30" t="inlineStr">
         <is>
@@ -4914,28 +4909,28 @@
       </c>
       <c r="C85" s="134" t="inlineStr">
         <is>
-          <t>Hit the Bike</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D85" s="91" t="inlineStr">
         <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G85" s="111" t="inlineStr">
         <is>
-          <t>This is not a pass</t>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
         </is>
       </c>
       <c r="H85" s="102" t="n"/>
       <c r="I85" s="102" t="n"/>
       <c r="J85" s="102" t="n"/>
     </row>
-    <row r="86" ht="56" customHeight="1" s="132">
+    <row r="86" ht="28" customHeight="1" s="132">
       <c r="A86" s="29" t="n"/>
       <c r="B86" s="30" t="inlineStr">
         <is>
@@ -4944,12 +4939,12 @@
       </c>
       <c r="C86" s="134" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D86" s="91" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
@@ -4961,7 +4956,7 @@
       <c r="I86" s="102" t="n"/>
       <c r="J86" s="102" t="n"/>
     </row>
-    <row r="87" ht="56" customHeight="1" s="132">
+    <row r="87" ht="28" customHeight="1" s="132">
       <c r="A87" s="29" t="n"/>
       <c r="B87" s="30" t="inlineStr">
         <is>
@@ -4970,28 +4965,28 @@
       </c>
       <c r="C87" s="134" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D87" s="91" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G87" s="111" t="inlineStr">
         <is>
-          <t>Deck ones are shown face down</t>
+          <t>This is not a pass</t>
         </is>
       </c>
       <c r="H87" s="102" t="n"/>
       <c r="I87" s="102" t="n"/>
       <c r="J87" s="102" t="n"/>
     </row>
-    <row r="88" ht="28" customHeight="1" s="132">
+    <row r="88" ht="56" customHeight="1" s="132">
       <c r="A88" s="29" t="n"/>
       <c r="B88" s="30" t="inlineStr">
         <is>
@@ -5000,28 +4995,24 @@
       </c>
       <c r="C88" s="134" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D88" s="91" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G88" s="111" t="inlineStr">
-        <is>
-          <t>This is a bad thing in the NBA</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G88" s="111" t="n"/>
       <c r="H88" s="102" t="n"/>
       <c r="I88" s="102" t="n"/>
       <c r="J88" s="102" t="n"/>
     </row>
-    <row r="89" ht="42" customHeight="1" s="132">
+    <row r="89" ht="56" customHeight="1" s="132">
       <c r="A89" s="29" t="n"/>
       <c r="B89" s="30" t="inlineStr">
         <is>
@@ -5030,21 +5021,21 @@
       </c>
       <c r="C89" s="134" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D89" s="91" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G89" s="111" t="inlineStr">
         <is>
-          <t>The hex travels in the declared direction too</t>
+          <t>Deck ones are shown face down</t>
         </is>
       </c>
       <c r="H89" s="102" t="n"/>
@@ -5060,19 +5051,23 @@
       </c>
       <c r="C90" s="134" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D90" s="91" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G90" s="111" t="n"/>
+      <c r="G90" s="111" t="inlineStr">
+        <is>
+          <t>This is a bad thing in the NBA</t>
+        </is>
+      </c>
       <c r="H90" s="102" t="n"/>
       <c r="I90" s="102" t="n"/>
       <c r="J90" s="102" t="n"/>
@@ -5086,24 +5081,28 @@
       </c>
       <c r="C91" s="134" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D91" s="91" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G91" s="111" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G91" s="111" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H91" s="102" t="n"/>
       <c r="I91" s="102" t="n"/>
       <c r="J91" s="102" t="n"/>
     </row>
-    <row r="92" ht="14" customHeight="1" s="132">
+    <row r="92" ht="28" customHeight="1" s="132">
       <c r="A92" s="29" t="n"/>
       <c r="B92" s="30" t="inlineStr">
         <is>
@@ -5112,12 +5111,12 @@
       </c>
       <c r="C92" s="134" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D92" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
@@ -5129,315 +5128,331 @@
       <c r="I92" s="102" t="n"/>
       <c r="J92" s="102" t="n"/>
     </row>
-    <row r="93" ht="28" customHeight="1" s="132">
-      <c r="A93" s="55" t="inlineStr">
-        <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="B93" s="56">
-        <f>COUNTIF($B$5:$B$123,"Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C93" s="57" t="n"/>
-      <c r="D93" s="57" t="n"/>
-      <c r="E93" s="57" t="n"/>
-      <c r="F93" s="88" t="n"/>
-      <c r="G93" s="108" t="n"/>
+    <row r="93" ht="42" customHeight="1" s="132">
+      <c r="A93" s="29" t="n"/>
+      <c r="B93" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C93" s="134" t="inlineStr">
+        <is>
+          <t>Official Timeout</t>
+        </is>
+      </c>
+      <c r="D93" s="91" t="inlineStr">
+        <is>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" s="111" t="n"/>
       <c r="H93" s="102" t="n"/>
       <c r="I93" s="102" t="n"/>
       <c r="J93" s="102" t="n"/>
     </row>
-    <row r="94" ht="28" customHeight="1" s="132">
+    <row r="94" ht="14" customHeight="1" s="132">
       <c r="A94" s="29" t="n"/>
       <c r="B94" s="30" t="inlineStr">
         <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="C94" s="31" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C94" s="134" t="inlineStr">
+        <is>
+          <t>Team Doctor</t>
         </is>
       </c>
       <c r="D94" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G94" s="101" t="n"/>
+      <c r="G94" s="111" t="n"/>
       <c r="H94" s="102" t="n"/>
       <c r="I94" s="102" t="n"/>
       <c r="J94" s="102" t="n"/>
     </row>
-    <row r="95" ht="28" customHeight="1" s="132">
-      <c r="A95" s="58" t="inlineStr">
-        <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="B95" s="59">
-        <f>COUNTIF($B$5:$B$123,"Devastating Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C95" s="60" t="n"/>
-      <c r="D95" s="60" t="n"/>
-      <c r="E95" s="60" t="n"/>
-      <c r="F95" s="86" t="n"/>
-      <c r="G95" s="109" t="n"/>
-      <c r="H95" s="110" t="n"/>
-      <c r="I95" s="110" t="n"/>
-      <c r="J95" s="110" t="n"/>
-    </row>
-    <row r="96" ht="28" customHeight="1" s="132">
-      <c r="A96" s="50" t="n"/>
-      <c r="B96" s="51" t="inlineStr">
-        <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="C96" s="136" t="inlineStr">
-        <is>
-          <t>Torn Achilles</t>
-        </is>
-      </c>
-      <c r="D96" s="137" t="inlineStr">
-        <is>
-          <t>Hand is locked every turn except 1 card (randomly)</t>
-        </is>
-      </c>
-      <c r="E96" s="54" t="n"/>
-      <c r="F96" s="141" t="n"/>
-      <c r="G96" s="114" t="n"/>
-      <c r="H96" s="115" t="n"/>
-      <c r="I96" s="115" t="n"/>
-      <c r="J96" s="115" t="n"/>
-    </row>
-    <row r="97" ht="42" customHeight="1" s="132">
-      <c r="A97" s="55" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="B97" s="56">
-        <f>COUNTIF($B$5:$B$123,"Intangible")</f>
-        <v/>
-      </c>
-      <c r="C97" s="57" t="n"/>
-      <c r="D97" s="57" t="n"/>
-      <c r="E97" s="57" t="n"/>
-      <c r="F97" s="88" t="n"/>
-      <c r="G97" s="108" t="n"/>
+    <row r="95" ht="14" customHeight="1" s="132">
+      <c r="A95" s="29" t="n"/>
+      <c r="B95" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C95" s="134" t="inlineStr">
+        <is>
+          <t>Altercation</t>
+        </is>
+      </c>
+      <c r="D95" s="91" t="inlineStr">
+        <is>
+          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="n"/>
+      <c r="F95" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" s="111" t="n"/>
+      <c r="H95" s="102" t="n"/>
+      <c r="I95" s="102" t="n"/>
+      <c r="J95" s="102" t="n"/>
+    </row>
+    <row r="96" ht="14" customHeight="1" s="132">
+      <c r="A96" s="29" t="n"/>
+      <c r="B96" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C96" s="134" t="inlineStr">
+        <is>
+          <t>Huge Altercation</t>
+        </is>
+      </c>
+      <c r="D96" s="91" t="inlineStr">
+        <is>
+          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="n"/>
+      <c r="F96" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="111" t="n"/>
+      <c r="H96" s="102" t="n"/>
+      <c r="I96" s="102" t="n"/>
+      <c r="J96" s="102" t="n"/>
+    </row>
+    <row r="97" ht="14" customHeight="1" s="132">
+      <c r="A97" s="29" t="n"/>
+      <c r="B97" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C97" s="134" t="inlineStr">
+        <is>
+          <t>Home Court Advantage</t>
+        </is>
+      </c>
+      <c r="D97" s="91" t="inlineStr">
+        <is>
+          <t>SHOT + 10%</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G97" s="111" t="n"/>
       <c r="H97" s="102" t="n"/>
       <c r="I97" s="102" t="n"/>
       <c r="J97" s="102" t="n"/>
     </row>
-    <row r="98" ht="56" customHeight="1" s="132">
-      <c r="A98" s="96" t="inlineStr">
-        <is>
-          <t>All intangibles are limited to 1</t>
-        </is>
-      </c>
+    <row r="98" ht="14" customHeight="1" s="132">
+      <c r="A98" s="29" t="n"/>
       <c r="B98" s="30" t="inlineStr">
         <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C98" s="31" t="inlineStr">
-        <is>
-          <t>Board-Crasher</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% upon Rebounding your own missed shot</t>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C98" s="134" t="inlineStr">
+        <is>
+          <t>Away Game</t>
+        </is>
+      </c>
+      <c r="D98" s="91" t="inlineStr">
+        <is>
+          <t>SHOT - 10%</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
-      <c r="F98" s="138" t="n"/>
-      <c r="G98" s="101" t="n"/>
+      <c r="F98" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G98" s="111" t="n"/>
       <c r="H98" s="102" t="n"/>
       <c r="I98" s="102" t="n"/>
       <c r="J98" s="102" t="n"/>
     </row>
-    <row r="99" ht="57" customHeight="1" s="132" thickBot="1">
+    <row r="99" ht="14" customHeight="1" s="132">
       <c r="A99" s="29" t="n"/>
       <c r="B99" s="30" t="inlineStr">
         <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C99" s="32" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D99" s="33" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E99" s="34" t="n"/>
-      <c r="F99" s="138" t="n"/>
-      <c r="G99" s="107" t="n"/>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C99" s="134" t="inlineStr">
+        <is>
+          <t>Mic'd Up</t>
+        </is>
+      </c>
+      <c r="D99" s="91" t="inlineStr">
+        <is>
+          <t>SHOT + 10% until passed or shot</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="n"/>
+      <c r="F99" s="76" t="n">
+        <v>7</v>
+      </c>
+      <c r="G99" s="111" t="inlineStr">
+        <is>
+          <t>The boost is the holder's alone and does not travel with a pass</t>
+        </is>
+      </c>
       <c r="H99" s="102" t="n"/>
       <c r="I99" s="102" t="n"/>
       <c r="J99" s="102" t="n"/>
     </row>
-    <row r="100" ht="20" customHeight="1" s="132">
+    <row r="100" ht="14" customHeight="1" s="132">
       <c r="A100" s="29" t="n"/>
       <c r="B100" s="30" t="inlineStr">
         <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C100" s="31" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C100" s="134" t="inlineStr">
+        <is>
+          <t>In The Zone</t>
+        </is>
+      </c>
+      <c r="D100" s="91" t="inlineStr">
+        <is>
+          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
-      <c r="F100" s="138" t="n"/>
-      <c r="G100" s="101" t="n"/>
+      <c r="F100" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" s="111" t="n"/>
       <c r="H100" s="102" t="n"/>
       <c r="I100" s="102" t="n"/>
       <c r="J100" s="102" t="n"/>
     </row>
     <row r="101" ht="28" customHeight="1" s="132">
-      <c r="A101" s="29" t="n"/>
-      <c r="B101" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C101" s="32" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D101" s="33" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
-        </is>
-      </c>
-      <c r="E101" s="34" t="n"/>
-      <c r="F101" s="138" t="n"/>
-      <c r="G101" s="107" t="n"/>
+      <c r="A101" s="55" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="B101" s="56">
+        <f>COUNTIF($B$5:$B$131,"Injury GB")</f>
+        <v/>
+      </c>
+      <c r="C101" s="57" t="n"/>
+      <c r="D101" s="57" t="n"/>
+      <c r="E101" s="57" t="n"/>
+      <c r="F101" s="88" t="n"/>
+      <c r="G101" s="108" t="n"/>
       <c r="H101" s="102" t="n"/>
       <c r="I101" s="102" t="n"/>
       <c r="J101" s="102" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" ht="28" customHeight="1" s="132">
       <c r="A102" s="29" t="n"/>
       <c r="B102" s="30" t="inlineStr">
         <is>
-          <t>Intangible</t>
+          <t>Injury GB</t>
         </is>
       </c>
       <c r="C102" s="31" t="inlineStr">
         <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F102" s="139" t="n"/>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D102" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="n"/>
+      <c r="F102" s="76" t="n">
+        <v>3</v>
+      </c>
       <c r="G102" s="101" t="n"/>
       <c r="H102" s="102" t="n"/>
       <c r="I102" s="102" t="n"/>
       <c r="J102" s="102" t="n"/>
     </row>
-    <row r="103">
-      <c r="A103" s="29" t="n"/>
-      <c r="B103" s="30" t="inlineStr">
+    <row r="103" ht="28" customHeight="1" s="132">
+      <c r="A103" s="58" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="B103" s="59">
+        <f>COUNTIF($B$5:$B$131,"Devastating Injury GB")</f>
+        <v/>
+      </c>
+      <c r="C103" s="60" t="n"/>
+      <c r="D103" s="60" t="n"/>
+      <c r="E103" s="60" t="n"/>
+      <c r="F103" s="86" t="n"/>
+      <c r="G103" s="109" t="n"/>
+      <c r="H103" s="110" t="n"/>
+      <c r="I103" s="110" t="n"/>
+      <c r="J103" s="110" t="n"/>
+    </row>
+    <row r="104" ht="28" customHeight="1" s="132">
+      <c r="A104" s="50" t="n"/>
+      <c r="B104" s="51" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="C104" s="136" t="inlineStr">
+        <is>
+          <t>Torn Achilles</t>
+        </is>
+      </c>
+      <c r="D104" s="137" t="inlineStr">
+        <is>
+          <t>Hand is locked every turn except 1 card (randomly)</t>
+        </is>
+      </c>
+      <c r="E104" s="54" t="n"/>
+      <c r="F104" s="141" t="n"/>
+      <c r="G104" s="114" t="n"/>
+      <c r="H104" s="115" t="n"/>
+      <c r="I104" s="115" t="n"/>
+      <c r="J104" s="115" t="n"/>
+    </row>
+    <row r="105" ht="42" customHeight="1" s="132">
+      <c r="A105" s="55" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C103" s="90" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D103" s="94" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E103" s="34" t="n"/>
-      <c r="F103" s="138" t="n"/>
-      <c r="G103" s="125" t="n"/>
-      <c r="H103" s="102" t="n"/>
-      <c r="I103" s="102" t="n"/>
-      <c r="J103" s="102" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="29" t="n"/>
-      <c r="B104" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C104" s="90" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D104" s="91" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="138" t="n"/>
-      <c r="G104" s="101" t="n"/>
-      <c r="H104" s="102" t="n"/>
-      <c r="I104" s="102" t="n"/>
-      <c r="J104" s="102" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="29" t="n"/>
-      <c r="B105" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C105" s="32" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D105" s="33" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E105" s="34" t="n"/>
-      <c r="F105" s="138" t="n"/>
-      <c r="G105" s="107" t="n"/>
+      <c r="B105" s="56">
+        <f>COUNTIF($B$5:$B$131,"Intangible")</f>
+        <v/>
+      </c>
+      <c r="C105" s="57" t="n"/>
+      <c r="D105" s="57" t="n"/>
+      <c r="E105" s="57" t="n"/>
+      <c r="F105" s="88" t="n"/>
+      <c r="G105" s="108" t="n"/>
       <c r="H105" s="102" t="n"/>
       <c r="I105" s="102" t="n"/>
       <c r="J105" s="102" t="n"/>
     </row>
-    <row r="106">
-      <c r="A106" s="29" t="n"/>
+    <row r="106" ht="56" customHeight="1" s="132">
+      <c r="A106" s="96" t="inlineStr">
+        <is>
+          <t>All intangibles are limited to 1</t>
+        </is>
+      </c>
       <c r="B106" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
@@ -5445,12 +5460,12 @@
       </c>
       <c r="C106" s="31" t="inlineStr">
         <is>
-          <t>Great Conditioning</t>
+          <t>Board-Crasher</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+          <t>SHOT +10% upon Rebounding your own missed shot</t>
         </is>
       </c>
       <c r="E106" s="7" t="n"/>
@@ -5460,7 +5475,7 @@
       <c r="I106" s="102" t="n"/>
       <c r="J106" s="102" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" ht="57" customHeight="1" s="132">
       <c r="A107" s="29" t="n"/>
       <c r="B107" s="30" t="inlineStr">
         <is>
@@ -5469,12 +5484,12 @@
       </c>
       <c r="C107" s="32" t="inlineStr">
         <is>
-          <t>Hot Hand</t>
+          <t>Catch &amp; Shoot Specialist</t>
         </is>
       </c>
       <c r="D107" s="33" t="inlineStr">
         <is>
-          <t>SHOT +20% if you scored last round.</t>
+          <t>Additional SHOT +10% on all received passes</t>
         </is>
       </c>
       <c r="E107" s="34" t="n"/>
@@ -5484,7 +5499,7 @@
       <c r="I107" s="102" t="n"/>
       <c r="J107" s="102" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" ht="20" customHeight="1" s="132">
       <c r="A108" s="29" t="n"/>
       <c r="B108" s="30" t="inlineStr">
         <is>
@@ -5493,12 +5508,12 @@
       </c>
       <c r="C108" s="31" t="inlineStr">
         <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D108" s="91" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
         </is>
       </c>
       <c r="E108" s="7" t="n"/>
@@ -5508,7 +5523,7 @@
       <c r="I108" s="102" t="n"/>
       <c r="J108" s="102" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" ht="28" customHeight="1" s="132">
       <c r="A109" s="29" t="n"/>
       <c r="B109" s="30" t="inlineStr">
         <is>
@@ -5517,21 +5532,17 @@
       </c>
       <c r="C109" s="32" t="inlineStr">
         <is>
-          <t>No Bag</t>
+          <t>Floor General</t>
         </is>
       </c>
       <c r="D109" s="33" t="inlineStr">
         <is>
-          <t>Cannot activate Move cards this round</t>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
         </is>
       </c>
       <c r="E109" s="34" t="n"/>
       <c r="F109" s="138" t="n"/>
-      <c r="G109" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G109" s="107" t="n"/>
       <c r="H109" s="102" t="n"/>
       <c r="I109" s="102" t="n"/>
       <c r="J109" s="102" t="n"/>
@@ -5545,16 +5556,20 @@
       </c>
       <c r="C110" s="31" t="inlineStr">
         <is>
-          <t>Point God</t>
+          <t>Fox-Like First Step</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="138" t="n"/>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F110" s="139" t="n"/>
       <c r="G110" s="101" t="n"/>
       <c r="H110" s="102" t="n"/>
       <c r="I110" s="102" t="n"/>
@@ -5567,23 +5582,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C111" s="32" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D111" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
+      <c r="C111" s="90" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D111" s="94" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
         </is>
       </c>
       <c r="E111" s="34" t="n"/>
       <c r="F111" s="138" t="n"/>
-      <c r="G111" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G111" s="125" t="n"/>
       <c r="H111" s="102" t="n"/>
       <c r="I111" s="102" t="n"/>
       <c r="J111" s="102" t="n"/>
@@ -5595,14 +5606,14 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C112" s="31" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
+      <c r="C112" s="90" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D112" s="91" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
         </is>
       </c>
       <c r="E112" s="7" t="n"/>
@@ -5621,12 +5632,12 @@
       </c>
       <c r="C113" s="32" t="inlineStr">
         <is>
-          <t>Sixth Man</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="D113" s="33" t="inlineStr">
         <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
         </is>
       </c>
       <c r="E113" s="34" t="n"/>
@@ -5645,12 +5656,12 @@
       </c>
       <c r="C114" s="31" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Great Conditioning</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
         </is>
       </c>
       <c r="E114" s="7" t="n"/>
@@ -5669,12 +5680,12 @@
       </c>
       <c r="C115" s="32" t="inlineStr">
         <is>
-          <t>Splash Cousin</t>
+          <t>Hot Hand</t>
         </is>
       </c>
       <c r="D115" s="33" t="inlineStr">
         <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
+          <t>SHOT +20% if you scored last round.</t>
         </is>
       </c>
       <c r="E115" s="34" t="n"/>
@@ -5693,12 +5704,12 @@
       </c>
       <c r="C116" s="31" t="inlineStr">
         <is>
-          <t>Unguardable</t>
+          <t>Like That</t>
         </is>
       </c>
       <c r="D116" s="91" t="inlineStr">
         <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
+          <t>Your SHOT % cannot be reduced</t>
         </is>
       </c>
       <c r="E116" s="7" t="n"/>
@@ -5717,19 +5728,19 @@
       </c>
       <c r="C117" s="32" t="inlineStr">
         <is>
-          <t>Lethal Shooter</t>
+          <t>No Bag</t>
         </is>
       </c>
       <c r="D117" s="33" t="inlineStr">
         <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+          <t>Cannot activate Move cards this round</t>
         </is>
       </c>
       <c r="E117" s="34" t="n"/>
       <c r="F117" s="138" t="n"/>
       <c r="G117" s="113" t="inlineStr">
         <is>
-          <t>Special text: “I understand it now”</t>
+          <t>Bad card to draw</t>
         </is>
       </c>
       <c r="H117" s="102" t="n"/>
@@ -5737,173 +5748,375 @@
       <c r="J117" s="102" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="61" t="n"/>
-      <c r="B118" s="62" t="inlineStr">
+      <c r="A118" s="29" t="n"/>
+      <c r="B118" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C118" s="66" t="inlineStr">
+      <c r="C118" s="31" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="138" t="n"/>
+      <c r="G118" s="101" t="n"/>
+      <c r="H118" s="102" t="n"/>
+      <c r="I118" s="102" t="n"/>
+      <c r="J118" s="102" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="29" t="n"/>
+      <c r="B119" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C119" s="32" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D119" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E119" s="34" t="n"/>
+      <c r="F119" s="138" t="n"/>
+      <c r="G119" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
+      <c r="H119" s="102" t="n"/>
+      <c r="I119" s="102" t="n"/>
+      <c r="J119" s="102" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="29" t="n"/>
+      <c r="B120" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C120" s="31" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="138" t="n"/>
+      <c r="G120" s="101" t="n"/>
+      <c r="H120" s="102" t="n"/>
+      <c r="I120" s="102" t="n"/>
+      <c r="J120" s="102" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="29" t="n"/>
+      <c r="B121" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C121" s="32" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D121" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E121" s="34" t="n"/>
+      <c r="F121" s="138" t="n"/>
+      <c r="G121" s="107" t="n"/>
+      <c r="H121" s="102" t="n"/>
+      <c r="I121" s="102" t="n"/>
+      <c r="J121" s="102" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="29" t="n"/>
+      <c r="B122" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C122" s="31" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="n"/>
+      <c r="F122" s="138" t="n"/>
+      <c r="G122" s="101" t="n"/>
+      <c r="H122" s="102" t="n"/>
+      <c r="I122" s="102" t="n"/>
+      <c r="J122" s="102" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="29" t="n"/>
+      <c r="B123" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C123" s="32" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D123" s="33" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E123" s="34" t="n"/>
+      <c r="F123" s="138" t="n"/>
+      <c r="G123" s="107" t="n"/>
+      <c r="H123" s="102" t="n"/>
+      <c r="I123" s="102" t="n"/>
+      <c r="J123" s="102" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="29" t="n"/>
+      <c r="B124" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C124" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D124" s="91" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="n"/>
+      <c r="F124" s="138" t="n"/>
+      <c r="G124" s="101" t="n"/>
+      <c r="H124" s="102" t="n"/>
+      <c r="I124" s="102" t="n"/>
+      <c r="J124" s="102" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="29" t="n"/>
+      <c r="B125" s="30" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C125" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D125" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E125" s="34" t="n"/>
+      <c r="F125" s="138" t="n"/>
+      <c r="G125" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H125" s="102" t="n"/>
+      <c r="I125" s="102" t="n"/>
+      <c r="J125" s="102" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="61" t="n"/>
+      <c r="B126" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C126" s="66" t="inlineStr">
         <is>
           <t>Ball Pounder</t>
         </is>
       </c>
-      <c r="D118" s="95" t="inlineStr">
+      <c r="D126" s="95" t="inlineStr">
         <is>
           <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
-      <c r="E118" s="68" t="n"/>
-      <c r="F118" s="140" t="n"/>
-      <c r="G118" s="126" t="n"/>
-      <c r="H118" s="117" t="n"/>
-      <c r="I118" s="117" t="n"/>
-      <c r="J118" s="117" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="61" t="n"/>
-      <c r="B119" s="62" t="inlineStr">
+      <c r="E126" s="68" t="n"/>
+      <c r="F126" s="140" t="n"/>
+      <c r="G126" s="126" t="n"/>
+      <c r="H126" s="117" t="n"/>
+      <c r="I126" s="117" t="n"/>
+      <c r="J126" s="117" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="61" t="n"/>
+      <c r="B127" s="62" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C119" s="66" t="inlineStr">
+      <c r="C127" s="66" t="inlineStr">
         <is>
           <t>Unselfish</t>
         </is>
       </c>
-      <c r="D119" s="95" t="inlineStr">
+      <c r="D127" s="95" t="inlineStr">
         <is>
           <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
-      <c r="E119" s="68" t="n"/>
-      <c r="F119" s="140" t="n"/>
-      <c r="G119" s="126" t="n"/>
-      <c r="H119" s="117" t="n"/>
-      <c r="I119" s="117" t="n"/>
-      <c r="J119" s="117" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="61" t="n"/>
-      <c r="B120" s="62" t="inlineStr">
+      <c r="E127" s="68" t="n"/>
+      <c r="F127" s="140" t="n"/>
+      <c r="G127" s="126" t="n"/>
+      <c r="H127" s="117" t="n"/>
+      <c r="I127" s="117" t="n"/>
+      <c r="J127" s="117" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="61" t="n"/>
+      <c r="B128" s="62" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C120" s="66" t="inlineStr">
+      <c r="C128" s="66" t="inlineStr">
         <is>
           <t>Dirty Player</t>
         </is>
       </c>
-      <c r="D120" s="95" t="inlineStr">
+      <c r="D128" s="95" t="inlineStr">
         <is>
           <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
-      <c r="E120" s="68" t="n"/>
-      <c r="F120" s="140" t="n"/>
-      <c r="G120" s="126" t="n"/>
-      <c r="H120" s="117" t="n"/>
-      <c r="I120" s="117" t="n"/>
-      <c r="J120" s="117" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="61" t="n"/>
-      <c r="B121" s="62" t="inlineStr">
+      <c r="E128" s="68" t="n"/>
+      <c r="F128" s="140" t="n"/>
+      <c r="G128" s="126" t="n"/>
+      <c r="H128" s="117" t="n"/>
+      <c r="I128" s="117" t="n"/>
+      <c r="J128" s="117" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="61" t="n"/>
+      <c r="B129" s="62" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C121" s="66" t="inlineStr">
+      <c r="C129" s="66" t="inlineStr">
         <is>
           <t>Villainous Reputation</t>
         </is>
       </c>
-      <c r="D121" s="95" t="inlineStr">
+      <c r="D129" s="95" t="inlineStr">
         <is>
           <t>Discard 1 whenever any Whistle triggers</t>
         </is>
       </c>
-      <c r="E121" s="68" t="n"/>
-      <c r="F121" s="140" t="n"/>
-      <c r="G121" s="126" t="inlineStr">
+      <c r="E129" s="68" t="n"/>
+      <c r="F129" s="140" t="n"/>
+      <c r="G129" s="126" t="inlineStr">
         <is>
           <t>Discarded during play, it attaches to a random player — possibly you again</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="61" t="n"/>
-      <c r="B122" s="62" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="61" t="n"/>
+      <c r="B130" s="62" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C122" s="66" t="inlineStr">
+      <c r="C130" s="66" t="inlineStr">
         <is>
           <t>Free Agent</t>
         </is>
       </c>
-      <c r="D122" s="95" t="inlineStr">
+      <c r="D130" s="95" t="inlineStr">
         <is>
           <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
-      <c r="E122" s="68" t="n"/>
-      <c r="F122" s="140" t="n"/>
-      <c r="G122" s="126" t="inlineStr">
+      <c r="E130" s="68" t="n"/>
+      <c r="F130" s="140" t="n"/>
+      <c r="G130" s="126" t="inlineStr">
         <is>
           <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="61" t="n"/>
-      <c r="B123" s="62" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="61" t="n"/>
+      <c r="B131" s="62" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C123" s="66" t="inlineStr">
+      <c r="C131" s="66" t="inlineStr">
         <is>
           <t>Franchise Player</t>
         </is>
       </c>
-      <c r="D123" s="95" t="inlineStr">
+      <c r="D131" s="95" t="inlineStr">
         <is>
           <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
         </is>
       </c>
-      <c r="E123" s="68" t="n"/>
-      <c r="F123" s="140" t="n"/>
-      <c r="G123" s="126" t="n"/>
-      <c r="H123" s="117" t="n"/>
-      <c r="I123" s="117" t="n"/>
-      <c r="J123" s="117" t="n"/>
+      <c r="E131" s="68" t="n"/>
+      <c r="F131" s="140" t="n"/>
+      <c r="G131" s="126" t="n"/>
+      <c r="H131" s="117" t="n"/>
+      <c r="I131" s="117" t="n"/>
+      <c r="J131" s="117" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="110">
+  <mergeCells count="118">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G119:J119"/>
     <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G119:J119"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
-    <mergeCell ref="G5:J5"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G82:J82"/>
     <mergeCell ref="G57:J57"/>
+    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G121:J121"/>
     <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
@@ -5913,14 +6126,13 @@
     <mergeCell ref="G123:J123"/>
     <mergeCell ref="G110:J110"/>
     <mergeCell ref="G113:J113"/>
-    <mergeCell ref="G91:J91"/>
     <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G94:J94"/>
     <mergeCell ref="G75:J75"/>
+    <mergeCell ref="G44:J44"/>
     <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G44:J44"/>
-    <mergeCell ref="G31:J31"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
@@ -5931,11 +6143,13 @@
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="G23:J23"/>
     <mergeCell ref="G97:J97"/>
+    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="G112:J112"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="G62:J62"/>
+    <mergeCell ref="G127:J127"/>
     <mergeCell ref="G49:J49"/>
     <mergeCell ref="G24:J24"/>
     <mergeCell ref="G33:J33"/>
@@ -5946,15 +6160,17 @@
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G76:J76"/>
     <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G90:J90"/>
     <mergeCell ref="G99:J99"/>
     <mergeCell ref="G60:J60"/>
+    <mergeCell ref="G131:J131"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
+    <mergeCell ref="G126:J126"/>
     <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G101:J101"/>
     <mergeCell ref="G116:J116"/>
     <mergeCell ref="G103:J103"/>
@@ -5963,12 +6179,12 @@
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
-    <mergeCell ref="G87:J87"/>
     <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G80:J80"/>
     <mergeCell ref="G95:J95"/>
-    <mergeCell ref="G80:J80"/>
+    <mergeCell ref="G89:J89"/>
+    <mergeCell ref="G64:J64"/>
     <mergeCell ref="G79:J79"/>
-    <mergeCell ref="G64:J64"/>
     <mergeCell ref="G73:J73"/>
     <mergeCell ref="G51:J51"/>
     <mergeCell ref="G54:J54"/>
@@ -5977,7 +6193,6 @@
     <mergeCell ref="G50:J50"/>
     <mergeCell ref="G106:J106"/>
     <mergeCell ref="G56:J56"/>
-    <mergeCell ref="G14:J14"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
@@ -5989,11 +6204,15 @@
     <mergeCell ref="G107:J107"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G93:J93"/>
     <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G93:J93"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G83:J83"/>
     <mergeCell ref="G92:J92"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G14:J14"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2549,7 +2549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2626,39 +2626,40 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$131,"Pass")</f>
+        <f>COUNTIF($B$5:$B$135,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$131,"Move")+COUNTIF($B$5:$B$131,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$135,"Move")+COUNTIF($B$5:$B$135,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$131,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$135,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$131,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$135,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$131,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$135,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$131,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$135,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$131,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$135,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$131,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$135,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="132">
       <c r="A4" s="123" t="inlineStr">
         <is>
@@ -2702,7 +2703,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$131,"Pass")</f>
+        <f>COUNTIF($B$5:$B$135,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="23" t="n"/>
@@ -2788,7 +2789,9 @@
         </is>
       </c>
       <c r="E8" s="34" t="n"/>
-      <c r="F8" s="75" t="n"/>
+      <c r="F8" s="75" t="n">
+        <v>6</v>
+      </c>
       <c r="G8" s="105" t="n"/>
       <c r="H8" s="106" t="n"/>
       <c r="I8" s="106" t="n"/>
@@ -2812,7 +2815,9 @@
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
-      <c r="F9" s="76" t="n"/>
+      <c r="F9" s="76" t="n">
+        <v>6</v>
+      </c>
       <c r="G9" s="112" t="n"/>
       <c r="H9" s="106" t="n"/>
       <c r="I9" s="106" t="n"/>
@@ -3143,7 +3148,7 @@
         </is>
       </c>
       <c r="B21" s="40">
-        <f>COUNTIF($B$5:$B$131,"Move")+COUNTIF($B$5:$B$131,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$135,"Move")+COUNTIF($B$5:$B$135,"Special Move")</f>
         <v/>
       </c>
       <c r="C21" s="41" t="n"/>
@@ -3543,7 +3548,7 @@
         </is>
       </c>
       <c r="B35" s="43">
-        <f>COUNTIF($B$5:$B$131,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$135,"Special Move")</f>
         <v/>
       </c>
       <c r="C35" s="44" t="n"/>
@@ -3962,7 +3967,7 @@
         </is>
       </c>
       <c r="B49" s="59">
-        <f>COUNTIF($B$5:$B$131,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$135,"Clamp")</f>
         <v/>
       </c>
       <c r="C49" s="60" t="n"/>
@@ -4131,7 +4136,7 @@
         </is>
       </c>
       <c r="B55" s="59">
-        <f>COUNTIF($B$5:$B$131,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$135,"Whistle")</f>
         <v/>
       </c>
       <c r="C55" s="60" t="n"/>
@@ -4584,102 +4589,104 @@
       <c r="J72" s="117" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1" s="132">
-      <c r="A73" s="58" t="inlineStr">
+      <c r="A73" s="61" t="n"/>
+      <c r="B73" s="62" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C73" s="63" t="inlineStr">
+        <is>
+          <t>Play-On</t>
+        </is>
+      </c>
+      <c r="D73" s="64" t="inlineStr">
+        <is>
+          <t>Discard each Game Break drawn and draw again, until a card is not one</t>
+        </is>
+      </c>
+      <c r="E73" s="65" t="n"/>
+      <c r="F73" s="140" t="n"/>
+      <c r="G73" s="116" t="inlineStr">
+        <is>
+          <t>Raised where the Break lands, like Cleared to Play — nobody plays a Break</t>
+        </is>
+      </c>
+      <c r="H73" s="117" t="n"/>
+      <c r="I73" s="117" t="n"/>
+      <c r="J73" s="117" t="n"/>
+    </row>
+    <row r="74" ht="28" customHeight="1" s="132">
+      <c r="A74" s="58" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B73" s="59">
-        <f>COUNTIF($B$5:$B$131,"Game Break")</f>
+      <c r="B74" s="59">
+        <f>COUNTIF($B$5:$B$135,"Game Break")</f>
         <v/>
       </c>
-      <c r="C73" s="60" t="n"/>
-      <c r="D73" s="60" t="n"/>
-      <c r="E73" s="60" t="n"/>
-      <c r="F73" s="86" t="n"/>
-      <c r="G73" s="109" t="n"/>
-      <c r="H73" s="110" t="n"/>
-      <c r="I73" s="110" t="n"/>
-      <c r="J73" s="110" t="n"/>
-    </row>
-    <row r="74" ht="28" customHeight="1" s="132">
-      <c r="A74" s="29" t="n"/>
-      <c r="B74" s="30" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>2-Minute Warning</t>
-        </is>
-      </c>
-      <c r="D74" s="33" t="inlineStr">
-        <is>
-          <t>All players discard down to 2 or fewer cards</t>
-        </is>
-      </c>
-      <c r="E74" s="34" t="n"/>
-      <c r="F74" s="75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G74" s="107" t="n"/>
-      <c r="H74" s="102" t="n"/>
-      <c r="I74" s="102" t="n"/>
-      <c r="J74" s="102" t="n"/>
-    </row>
-    <row r="75" ht="42" customHeight="1" s="132">
+      <c r="C74" s="60" t="n"/>
+      <c r="D74" s="60" t="n"/>
+      <c r="E74" s="60" t="n"/>
+      <c r="F74" s="86" t="n"/>
+      <c r="G74" s="109" t="n"/>
+      <c r="H74" s="110" t="n"/>
+      <c r="I74" s="110" t="n"/>
+      <c r="J74" s="110" t="n"/>
+    </row>
+    <row r="75" ht="28" customHeight="1" s="132">
       <c r="A75" s="29" t="n"/>
       <c r="B75" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C75" s="31" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G75" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
+        </is>
+      </c>
+      <c r="D75" s="33" t="inlineStr">
+        <is>
+          <t>All players discard down to 2 or fewer cards</t>
+        </is>
+      </c>
+      <c r="E75" s="34" t="n"/>
+      <c r="F75" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" s="107" t="n"/>
       <c r="H75" s="102" t="n"/>
       <c r="I75" s="102" t="n"/>
       <c r="J75" s="102" t="n"/>
     </row>
-    <row r="76" ht="28" customHeight="1" s="132">
+    <row r="76" ht="42" customHeight="1" s="132">
       <c r="A76" s="29" t="n"/>
       <c r="B76" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C76" s="32" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D76" s="33" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E76" s="34" t="n"/>
-      <c r="F76" s="75" t="n">
-        <v>14</v>
-      </c>
-      <c r="G76" s="107" t="n"/>
+      <c r="C76" s="31" t="inlineStr">
+        <is>
+          <t>Benched</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Immediately give ball to any other player.</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="n"/>
+      <c r="F76" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G76" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H76" s="102" t="n"/>
       <c r="I76" s="102" t="n"/>
       <c r="J76" s="102" t="n"/>
@@ -4691,211 +4698,213 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C77" s="31" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G77" s="101" t="n"/>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
+        </is>
+      </c>
+      <c r="D77" s="33" t="inlineStr">
+        <is>
+          <t>Discard 1 card.</t>
+        </is>
+      </c>
+      <c r="E77" s="34" t="n"/>
+      <c r="F77" s="75" t="n">
+        <v>14</v>
+      </c>
+      <c r="G77" s="107" t="n"/>
       <c r="H77" s="102" t="n"/>
       <c r="I77" s="102" t="n"/>
       <c r="J77" s="102" t="n"/>
     </row>
-    <row r="78" ht="20" customHeight="1" s="132">
+    <row r="78" ht="28" customHeight="1" s="132">
       <c r="A78" s="29" t="n"/>
       <c r="B78" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C78" s="90" t="inlineStr">
-        <is>
-          <t>Foul</t>
-        </is>
-      </c>
-      <c r="D78" s="33" t="inlineStr">
-        <is>
-          <t>Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E78" s="34" t="n"/>
-      <c r="F78" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G78" s="107" t="n"/>
+      <c r="C78" s="31" t="inlineStr">
+        <is>
+          <t>Designed Play</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Draw up to a hand of 5</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="n"/>
+      <c r="F78" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G78" s="101" t="n"/>
       <c r="H78" s="102" t="n"/>
       <c r="I78" s="102" t="n"/>
       <c r="J78" s="102" t="n"/>
     </row>
-    <row r="79" ht="28" customHeight="1" s="132">
+    <row r="79" ht="20" customHeight="1" s="132">
       <c r="A79" s="29" t="n"/>
       <c r="B79" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C79" s="31" t="inlineStr">
-        <is>
-          <t>MVP Vote</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards up to a hand of 7</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="n"/>
-      <c r="F79" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="101" t="n"/>
+      <c r="C79" s="90" t="inlineStr">
+        <is>
+          <t>Foul</t>
+        </is>
+      </c>
+      <c r="D79" s="33" t="inlineStr">
+        <is>
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E79" s="34" t="n"/>
+      <c r="F79" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" s="107" t="n"/>
       <c r="H79" s="102" t="n"/>
       <c r="I79" s="102" t="n"/>
       <c r="J79" s="102" t="n"/>
     </row>
-    <row r="80" ht="20" customHeight="1" s="132">
+    <row r="80" ht="28" customHeight="1" s="132">
       <c r="A80" s="29" t="n"/>
       <c r="B80" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>Off Night</t>
-        </is>
-      </c>
-      <c r="D80" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this possession</t>
-        </is>
-      </c>
-      <c r="E80" s="34" t="n"/>
-      <c r="F80" s="75" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" s="107" t="n"/>
+      <c r="C80" s="31" t="inlineStr">
+        <is>
+          <t>MVP Vote</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Draw 3 cards up to a hand of 7</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n"/>
+      <c r="F80" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="101" t="n"/>
       <c r="H80" s="102" t="n"/>
       <c r="I80" s="102" t="n"/>
       <c r="J80" s="102" t="n"/>
     </row>
-    <row r="81" ht="42" customHeight="1" s="132">
+    <row r="81" ht="20" customHeight="1" s="132">
       <c r="A81" s="29" t="n"/>
       <c r="B81" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C81" s="31" t="inlineStr">
-        <is>
-          <t>Swallowed Whistle</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F81" s="74" t="n">
-        <v>5</v>
-      </c>
-      <c r="G81" s="101" t="n"/>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D81" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E81" s="34" t="n"/>
+      <c r="F81" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" s="107" t="n"/>
       <c r="H81" s="102" t="n"/>
       <c r="I81" s="102" t="n"/>
       <c r="J81" s="102" t="n"/>
     </row>
-    <row r="82" ht="28" customHeight="1" s="132">
+    <row r="82" ht="42" customHeight="1" s="132">
       <c r="A82" s="29" t="n"/>
       <c r="B82" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
-        </is>
-      </c>
-      <c r="D82" s="33" t="inlineStr">
-        <is>
-          <t>Players cannot shoot when SHOT is 50% or higher</t>
-        </is>
-      </c>
-      <c r="E82" s="33" t="inlineStr">
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>Remains for remainder of round</t>
         </is>
       </c>
-      <c r="F82" s="80" t="n"/>
-      <c r="G82" s="107" t="n"/>
+      <c r="F82" s="74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G82" s="101" t="n"/>
       <c r="H82" s="102" t="n"/>
       <c r="I82" s="102" t="n"/>
       <c r="J82" s="102" t="n"/>
     </row>
-    <row r="83" ht="56" customHeight="1" s="132">
+    <row r="83" ht="28" customHeight="1" s="132">
       <c r="A83" s="29" t="n"/>
       <c r="B83" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C83" s="31" t="inlineStr">
-        <is>
-          <t>Traded Mid-Game</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>Swap positions with random other player</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="n"/>
-      <c r="F83" s="76" t="n"/>
-      <c r="G83" s="111" t="inlineStr">
-        <is>
-          <t>Applies to rest of game</t>
-        </is>
-      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D83" s="33" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is 50% or higher</t>
+        </is>
+      </c>
+      <c r="E83" s="33" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F83" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" s="107" t="n"/>
       <c r="H83" s="102" t="n"/>
       <c r="I83" s="102" t="n"/>
       <c r="J83" s="102" t="n"/>
     </row>
-    <row r="84" ht="42" customHeight="1" s="132">
+    <row r="84" ht="56" customHeight="1" s="132">
       <c r="A84" s="29" t="n"/>
       <c r="B84" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C84" s="134" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D84" s="91" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
+      <c r="C84" s="31" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Swap positions with random other player</t>
         </is>
       </c>
       <c r="E84" s="7" t="n"/>
-      <c r="F84" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G84" s="111" t="n"/>
+      <c r="F84" s="76" t="n"/>
+      <c r="G84" s="111" t="inlineStr">
+        <is>
+          <t>Applies to rest of game</t>
+        </is>
+      </c>
       <c r="H84" s="102" t="n"/>
       <c r="I84" s="102" t="n"/>
       <c r="J84" s="102" t="n"/>
@@ -4909,28 +4918,24 @@
       </c>
       <c r="C85" s="134" t="inlineStr">
         <is>
-          <t>All-Swissh Selection</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D85" s="91" t="inlineStr">
         <is>
-          <t>Draw 3 cards after your next make</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G85" s="111" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G85" s="111" t="n"/>
       <c r="H85" s="102" t="n"/>
       <c r="I85" s="102" t="n"/>
       <c r="J85" s="102" t="n"/>
     </row>
-    <row r="86" ht="28" customHeight="1" s="132">
+    <row r="86" ht="42" customHeight="1" s="132">
       <c r="A86" s="29" t="n"/>
       <c r="B86" s="30" t="inlineStr">
         <is>
@@ -4939,19 +4944,23 @@
       </c>
       <c r="C86" s="134" t="inlineStr">
         <is>
-          <t>All Star Selection</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D86" s="91" t="inlineStr">
         <is>
-          <t>Draw 2 cards</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G86" s="111" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G86" s="111" t="inlineStr">
+        <is>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
+        </is>
+      </c>
       <c r="H86" s="102" t="n"/>
       <c r="I86" s="102" t="n"/>
       <c r="J86" s="102" t="n"/>
@@ -4965,28 +4974,24 @@
       </c>
       <c r="C87" s="134" t="inlineStr">
         <is>
-          <t>Hit the Bike</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D87" s="91" t="inlineStr">
         <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G87" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="G87" s="111" t="n"/>
       <c r="H87" s="102" t="n"/>
       <c r="I87" s="102" t="n"/>
       <c r="J87" s="102" t="n"/>
     </row>
-    <row r="88" ht="56" customHeight="1" s="132">
+    <row r="88" ht="28" customHeight="1" s="132">
       <c r="A88" s="29" t="n"/>
       <c r="B88" s="30" t="inlineStr">
         <is>
@@ -4995,19 +5000,23 @@
       </c>
       <c r="C88" s="134" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D88" s="91" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G88" s="111" t="n"/>
+      <c r="G88" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H88" s="102" t="n"/>
       <c r="I88" s="102" t="n"/>
       <c r="J88" s="102" t="n"/>
@@ -5021,28 +5030,24 @@
       </c>
       <c r="C89" s="134" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D89" s="91" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" s="111" t="inlineStr">
-        <is>
-          <t>Deck ones are shown face down</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G89" s="111" t="n"/>
       <c r="H89" s="102" t="n"/>
       <c r="I89" s="102" t="n"/>
       <c r="J89" s="102" t="n"/>
     </row>
-    <row r="90" ht="28" customHeight="1" s="132">
+    <row r="90" ht="56" customHeight="1" s="132">
       <c r="A90" s="29" t="n"/>
       <c r="B90" s="30" t="inlineStr">
         <is>
@@ -5051,28 +5056,28 @@
       </c>
       <c r="C90" s="134" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D90" s="91" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="111" t="inlineStr">
         <is>
-          <t>This is a bad thing in the NBA</t>
+          <t>Deck ones are shown face down</t>
         </is>
       </c>
       <c r="H90" s="102" t="n"/>
       <c r="I90" s="102" t="n"/>
       <c r="J90" s="102" t="n"/>
     </row>
-    <row r="91" ht="42" customHeight="1" s="132">
+    <row r="91" ht="28" customHeight="1" s="132">
       <c r="A91" s="29" t="n"/>
       <c r="B91" s="30" t="inlineStr">
         <is>
@@ -5081,12 +5086,12 @@
       </c>
       <c r="C91" s="134" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D91" s="91" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
@@ -5095,14 +5100,14 @@
       </c>
       <c r="G91" s="111" t="inlineStr">
         <is>
-          <t>The hex travels in the declared direction too</t>
+          <t>This is a bad thing in the NBA</t>
         </is>
       </c>
       <c r="H91" s="102" t="n"/>
       <c r="I91" s="102" t="n"/>
       <c r="J91" s="102" t="n"/>
     </row>
-    <row r="92" ht="28" customHeight="1" s="132">
+    <row r="92" ht="42" customHeight="1" s="132">
       <c r="A92" s="29" t="n"/>
       <c r="B92" s="30" t="inlineStr">
         <is>
@@ -5111,24 +5116,28 @@
       </c>
       <c r="C92" s="134" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D92" s="91" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G92" s="111" t="n"/>
+      <c r="G92" s="111" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H92" s="102" t="n"/>
       <c r="I92" s="102" t="n"/>
       <c r="J92" s="102" t="n"/>
     </row>
-    <row r="93" ht="42" customHeight="1" s="132">
+    <row r="93" ht="28" customHeight="1" s="132">
       <c r="A93" s="29" t="n"/>
       <c r="B93" s="30" t="inlineStr">
         <is>
@@ -5137,24 +5146,24 @@
       </c>
       <c r="C93" s="134" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D93" s="91" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G93" s="111" t="n"/>
       <c r="H93" s="102" t="n"/>
       <c r="I93" s="102" t="n"/>
       <c r="J93" s="102" t="n"/>
     </row>
-    <row r="94" ht="14" customHeight="1" s="132">
+    <row r="94" ht="42" customHeight="1" s="132">
       <c r="A94" s="29" t="n"/>
       <c r="B94" s="30" t="inlineStr">
         <is>
@@ -5163,17 +5172,17 @@
       </c>
       <c r="C94" s="134" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Official Timeout</t>
         </is>
       </c>
       <c r="D94" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94" s="111" t="n"/>
       <c r="H94" s="102" t="n"/>
@@ -5189,17 +5198,17 @@
       </c>
       <c r="C95" s="134" t="inlineStr">
         <is>
-          <t>Altercation</t>
+          <t>Team Doctor</t>
         </is>
       </c>
       <c r="D95" s="91" t="inlineStr">
         <is>
-          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G95" s="111" t="n"/>
       <c r="H95" s="102" t="n"/>
@@ -5215,17 +5224,17 @@
       </c>
       <c r="C96" s="134" t="inlineStr">
         <is>
-          <t>Huge Altercation</t>
+          <t>Altercation</t>
         </is>
       </c>
       <c r="D96" s="91" t="inlineStr">
         <is>
-          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
+          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" s="111" t="n"/>
       <c r="H96" s="102" t="n"/>
@@ -5241,17 +5250,17 @@
       </c>
       <c r="C97" s="134" t="inlineStr">
         <is>
-          <t>Home Court Advantage</t>
+          <t>Huge Altercation</t>
         </is>
       </c>
       <c r="D97" s="91" t="inlineStr">
         <is>
-          <t>SHOT + 10%</t>
+          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G97" s="111" t="n"/>
       <c r="H97" s="102" t="n"/>
@@ -5267,12 +5276,12 @@
       </c>
       <c r="C98" s="134" t="inlineStr">
         <is>
-          <t>Away Game</t>
+          <t>Home Court Advantage</t>
         </is>
       </c>
       <c r="D98" s="91" t="inlineStr">
         <is>
-          <t>SHOT - 10%</t>
+          <t>SHOT + 10%</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -5293,23 +5302,19 @@
       </c>
       <c r="C99" s="134" t="inlineStr">
         <is>
-          <t>Mic'd Up</t>
+          <t>Away Game</t>
         </is>
       </c>
       <c r="D99" s="91" t="inlineStr">
         <is>
-          <t>SHOT + 10% until passed or shot</t>
+          <t>SHOT - 10%</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="76" t="n">
-        <v>7</v>
-      </c>
-      <c r="G99" s="111" t="inlineStr">
-        <is>
-          <t>The boost is the holder's alone and does not travel with a pass</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G99" s="111" t="n"/>
       <c r="H99" s="102" t="n"/>
       <c r="I99" s="102" t="n"/>
       <c r="J99" s="102" t="n"/>
@@ -5323,302 +5328,308 @@
       </c>
       <c r="C100" s="134" t="inlineStr">
         <is>
-          <t>In The Zone</t>
+          <t>Mic'd Up</t>
         </is>
       </c>
       <c r="D100" s="91" t="inlineStr">
         <is>
-          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+          <t>SHOT + 10% until passed or shot</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G100" s="111" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="G100" s="111" t="inlineStr">
+        <is>
+          <t>The boost is the holder's alone and does not travel with a pass</t>
+        </is>
+      </c>
       <c r="H100" s="102" t="n"/>
       <c r="I100" s="102" t="n"/>
       <c r="J100" s="102" t="n"/>
     </row>
-    <row r="101" ht="28" customHeight="1" s="132">
-      <c r="A101" s="55" t="inlineStr">
-        <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="B101" s="56">
-        <f>COUNTIF($B$5:$B$131,"Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C101" s="57" t="n"/>
-      <c r="D101" s="57" t="n"/>
-      <c r="E101" s="57" t="n"/>
-      <c r="F101" s="88" t="n"/>
-      <c r="G101" s="108" t="n"/>
+    <row r="101" ht="14" customHeight="1" s="132">
+      <c r="A101" s="29" t="n"/>
+      <c r="B101" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C101" s="134" t="inlineStr">
+        <is>
+          <t>In The Zone</t>
+        </is>
+      </c>
+      <c r="D101" s="91" t="inlineStr">
+        <is>
+          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="n"/>
+      <c r="F101" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G101" s="111" t="n"/>
       <c r="H101" s="102" t="n"/>
       <c r="I101" s="102" t="n"/>
       <c r="J101" s="102" t="n"/>
     </row>
-    <row r="102" ht="28" customHeight="1" s="132">
+    <row r="102" ht="14" customHeight="1" s="132">
       <c r="A102" s="29" t="n"/>
       <c r="B102" s="30" t="inlineStr">
         <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="C102" s="31" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C102" s="134" t="inlineStr">
+        <is>
+          <t>Role Player</t>
         </is>
       </c>
       <c r="D102" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+          <t>All other players draw 1 card</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G102" s="101" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="G102" s="111" t="n"/>
       <c r="H102" s="102" t="n"/>
       <c r="I102" s="102" t="n"/>
       <c r="J102" s="102" t="n"/>
     </row>
-    <row r="103" ht="28" customHeight="1" s="132">
-      <c r="A103" s="58" t="inlineStr">
-        <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="B103" s="59">
-        <f>COUNTIF($B$5:$B$131,"Devastating Injury GB")</f>
+    <row r="103" ht="14" customHeight="1" s="132">
+      <c r="A103" s="29" t="n"/>
+      <c r="B103" s="30" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C103" s="134" t="inlineStr">
+        <is>
+          <t>Back-and-Forth Game</t>
+        </is>
+      </c>
+      <c r="D103" s="91" t="inlineStr">
+        <is>
+          <t>Discard the next 3 Game Breaks. Whoever draws one draws again</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="n"/>
+      <c r="F103" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" s="111" t="n"/>
+      <c r="H103" s="102" t="n"/>
+      <c r="I103" s="102" t="n"/>
+      <c r="J103" s="102" t="n"/>
+    </row>
+    <row r="104" ht="28" customHeight="1" s="132">
+      <c r="A104" s="55" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="B104" s="56">
+        <f>COUNTIF($B$5:$B$135,"Injury GB")</f>
         <v/>
       </c>
-      <c r="C103" s="60" t="n"/>
-      <c r="D103" s="60" t="n"/>
-      <c r="E103" s="60" t="n"/>
-      <c r="F103" s="86" t="n"/>
-      <c r="G103" s="109" t="n"/>
-      <c r="H103" s="110" t="n"/>
-      <c r="I103" s="110" t="n"/>
-      <c r="J103" s="110" t="n"/>
-    </row>
-    <row r="104" ht="28" customHeight="1" s="132">
-      <c r="A104" s="50" t="n"/>
-      <c r="B104" s="51" t="inlineStr">
-        <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="C104" s="136" t="inlineStr">
-        <is>
-          <t>Torn Achilles</t>
-        </is>
-      </c>
-      <c r="D104" s="137" t="inlineStr">
-        <is>
-          <t>Hand is locked every turn except 1 card (randomly)</t>
-        </is>
-      </c>
-      <c r="E104" s="54" t="n"/>
-      <c r="F104" s="141" t="n"/>
-      <c r="G104" s="114" t="n"/>
-      <c r="H104" s="115" t="n"/>
-      <c r="I104" s="115" t="n"/>
-      <c r="J104" s="115" t="n"/>
-    </row>
-    <row r="105" ht="42" customHeight="1" s="132">
-      <c r="A105" s="55" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="B105" s="56">
-        <f>COUNTIF($B$5:$B$131,"Intangible")</f>
-        <v/>
-      </c>
-      <c r="C105" s="57" t="n"/>
-      <c r="D105" s="57" t="n"/>
-      <c r="E105" s="57" t="n"/>
-      <c r="F105" s="88" t="n"/>
-      <c r="G105" s="108" t="n"/>
+      <c r="C104" s="57" t="n"/>
+      <c r="D104" s="57" t="n"/>
+      <c r="E104" s="57" t="n"/>
+      <c r="F104" s="88" t="n"/>
+      <c r="G104" s="108" t="n"/>
+      <c r="H104" s="102" t="n"/>
+      <c r="I104" s="102" t="n"/>
+      <c r="J104" s="102" t="n"/>
+    </row>
+    <row r="105" ht="28" customHeight="1" s="132">
+      <c r="A105" s="29" t="n"/>
+      <c r="B105" s="30" t="inlineStr">
+        <is>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="C105" s="31" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D105" s="91" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="n"/>
+      <c r="F105" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" s="101" t="n"/>
       <c r="H105" s="102" t="n"/>
       <c r="I105" s="102" t="n"/>
       <c r="J105" s="102" t="n"/>
     </row>
-    <row r="106" ht="56" customHeight="1" s="132">
-      <c r="A106" s="96" t="inlineStr">
-        <is>
-          <t>All intangibles are limited to 1</t>
-        </is>
-      </c>
-      <c r="B106" s="30" t="inlineStr">
+    <row r="106" ht="28" customHeight="1" s="132">
+      <c r="A106" s="58" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="B106" s="59">
+        <f>COUNTIF($B$5:$B$135,"Devastating Injury GB")</f>
+        <v/>
+      </c>
+      <c r="C106" s="60" t="n"/>
+      <c r="D106" s="60" t="n"/>
+      <c r="E106" s="60" t="n"/>
+      <c r="F106" s="86" t="n"/>
+      <c r="G106" s="109" t="n"/>
+      <c r="H106" s="110" t="n"/>
+      <c r="I106" s="110" t="n"/>
+      <c r="J106" s="110" t="n"/>
+    </row>
+    <row r="107" ht="28" customHeight="1" s="132">
+      <c r="A107" s="50" t="n"/>
+      <c r="B107" s="51" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="C107" s="136" t="inlineStr">
+        <is>
+          <t>Torn Achilles</t>
+        </is>
+      </c>
+      <c r="D107" s="137" t="inlineStr">
+        <is>
+          <t>Hand is locked every turn except 1 card (randomly)</t>
+        </is>
+      </c>
+      <c r="E107" s="54" t="n"/>
+      <c r="F107" s="141" t="n"/>
+      <c r="G107" s="114" t="n"/>
+      <c r="H107" s="115" t="n"/>
+      <c r="I107" s="115" t="n"/>
+      <c r="J107" s="115" t="n"/>
+    </row>
+    <row r="108" ht="42" customHeight="1" s="132">
+      <c r="A108" s="55" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C106" s="31" t="inlineStr">
-        <is>
-          <t>Board-Crasher</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% upon Rebounding your own missed shot</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="n"/>
-      <c r="F106" s="138" t="n"/>
-      <c r="G106" s="101" t="n"/>
-      <c r="H106" s="102" t="n"/>
-      <c r="I106" s="102" t="n"/>
-      <c r="J106" s="102" t="n"/>
-    </row>
-    <row r="107" ht="57" customHeight="1" s="132">
-      <c r="A107" s="29" t="n"/>
-      <c r="B107" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C107" s="32" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D107" s="33" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E107" s="34" t="n"/>
-      <c r="F107" s="138" t="n"/>
-      <c r="G107" s="107" t="n"/>
-      <c r="H107" s="102" t="n"/>
-      <c r="I107" s="102" t="n"/>
-      <c r="J107" s="102" t="n"/>
-    </row>
-    <row r="108" ht="20" customHeight="1" s="132">
-      <c r="A108" s="29" t="n"/>
-      <c r="B108" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C108" s="31" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="n"/>
-      <c r="F108" s="138" t="n"/>
-      <c r="G108" s="101" t="n"/>
+      <c r="B108" s="56">
+        <f>COUNTIF($B$5:$B$135,"Intangible")</f>
+        <v/>
+      </c>
+      <c r="C108" s="57" t="n"/>
+      <c r="D108" s="57" t="n"/>
+      <c r="E108" s="57" t="n"/>
+      <c r="F108" s="88" t="n"/>
+      <c r="G108" s="108" t="n"/>
       <c r="H108" s="102" t="n"/>
       <c r="I108" s="102" t="n"/>
       <c r="J108" s="102" t="n"/>
     </row>
-    <row r="109" ht="28" customHeight="1" s="132">
-      <c r="A109" s="29" t="n"/>
+    <row r="109" ht="56" customHeight="1" s="132">
+      <c r="A109" s="96" t="inlineStr">
+        <is>
+          <t>All intangibles are limited to 1</t>
+        </is>
+      </c>
       <c r="B109" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C109" s="32" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D109" s="33" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
-        </is>
-      </c>
-      <c r="E109" s="34" t="n"/>
+      <c r="C109" s="31" t="inlineStr">
+        <is>
+          <t>Board-Crasher</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% upon Rebounding your own missed shot</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="n"/>
       <c r="F109" s="138" t="n"/>
-      <c r="G109" s="107" t="n"/>
+      <c r="G109" s="101" t="n"/>
       <c r="H109" s="102" t="n"/>
       <c r="I109" s="102" t="n"/>
       <c r="J109" s="102" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" ht="57" customHeight="1" s="132">
       <c r="A110" s="29" t="n"/>
       <c r="B110" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C110" s="31" t="inlineStr">
-        <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F110" s="139" t="n"/>
-      <c r="G110" s="101" t="n"/>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D110" s="33" t="inlineStr">
+        <is>
+          <t>Additional SHOT +10% on all received passes</t>
+        </is>
+      </c>
+      <c r="E110" s="34" t="n"/>
+      <c r="F110" s="138" t="n"/>
+      <c r="G110" s="107" t="n"/>
       <c r="H110" s="102" t="n"/>
       <c r="I110" s="102" t="n"/>
       <c r="J110" s="102" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" ht="20" customHeight="1" s="132">
       <c r="A111" s="29" t="n"/>
       <c r="B111" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C111" s="90" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D111" s="94" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E111" s="34" t="n"/>
+      <c r="C111" s="31" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="n"/>
       <c r="F111" s="138" t="n"/>
-      <c r="G111" s="125" t="n"/>
+      <c r="G111" s="101" t="n"/>
       <c r="H111" s="102" t="n"/>
       <c r="I111" s="102" t="n"/>
       <c r="J111" s="102" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" ht="28" customHeight="1" s="132">
       <c r="A112" s="29" t="n"/>
       <c r="B112" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C112" s="90" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D112" s="91" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="n"/>
+      <c r="C112" s="32" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D112" s="33" t="inlineStr">
+        <is>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
+        </is>
+      </c>
+      <c r="E112" s="34" t="n"/>
       <c r="F112" s="138" t="n"/>
-      <c r="G112" s="101" t="n"/>
+      <c r="G112" s="107" t="n"/>
       <c r="H112" s="102" t="n"/>
       <c r="I112" s="102" t="n"/>
       <c r="J112" s="102" t="n"/>
@@ -5630,19 +5641,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C113" s="32" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D113" s="33" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E113" s="34" t="n"/>
-      <c r="F113" s="138" t="n"/>
-      <c r="G113" s="107" t="n"/>
+      <c r="C113" s="31" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F113" s="139" t="n"/>
+      <c r="G113" s="101" t="n"/>
       <c r="H113" s="102" t="n"/>
       <c r="I113" s="102" t="n"/>
       <c r="J113" s="102" t="n"/>
@@ -5654,19 +5669,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C114" s="31" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="n"/>
+      <c r="C114" s="90" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D114" s="94" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
+        </is>
+      </c>
+      <c r="E114" s="34" t="n"/>
       <c r="F114" s="138" t="n"/>
-      <c r="G114" s="101" t="n"/>
+      <c r="G114" s="125" t="n"/>
       <c r="H114" s="102" t="n"/>
       <c r="I114" s="102" t="n"/>
       <c r="J114" s="102" t="n"/>
@@ -5678,19 +5693,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C115" s="32" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D115" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +20% if you scored last round.</t>
-        </is>
-      </c>
-      <c r="E115" s="34" t="n"/>
+      <c r="C115" s="90" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D115" s="91" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="n"/>
       <c r="F115" s="138" t="n"/>
-      <c r="G115" s="107" t="n"/>
+      <c r="G115" s="101" t="n"/>
       <c r="H115" s="102" t="n"/>
       <c r="I115" s="102" t="n"/>
       <c r="J115" s="102" t="n"/>
@@ -5702,19 +5717,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C116" s="31" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D116" s="91" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="n"/>
+      <c r="C116" s="32" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="D116" s="33" t="inlineStr">
+        <is>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+        </is>
+      </c>
+      <c r="E116" s="34" t="n"/>
       <c r="F116" s="138" t="n"/>
-      <c r="G116" s="101" t="n"/>
+      <c r="G116" s="107" t="n"/>
       <c r="H116" s="102" t="n"/>
       <c r="I116" s="102" t="n"/>
       <c r="J116" s="102" t="n"/>
@@ -5726,23 +5741,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C117" s="32" t="inlineStr">
-        <is>
-          <t>No Bag</t>
-        </is>
-      </c>
-      <c r="D117" s="33" t="inlineStr">
-        <is>
-          <t>Cannot activate Move cards this round</t>
-        </is>
-      </c>
-      <c r="E117" s="34" t="n"/>
+      <c r="C117" s="31" t="inlineStr">
+        <is>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="n"/>
       <c r="F117" s="138" t="n"/>
-      <c r="G117" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G117" s="101" t="n"/>
       <c r="H117" s="102" t="n"/>
       <c r="I117" s="102" t="n"/>
       <c r="J117" s="102" t="n"/>
@@ -5754,19 +5765,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C118" s="31" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="n"/>
+      <c r="C118" s="32" t="inlineStr">
+        <is>
+          <t>Hot Hand</t>
+        </is>
+      </c>
+      <c r="D118" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +20% if you scored last round.</t>
+        </is>
+      </c>
+      <c r="E118" s="34" t="n"/>
       <c r="F118" s="138" t="n"/>
-      <c r="G118" s="101" t="n"/>
+      <c r="G118" s="107" t="n"/>
       <c r="H118" s="102" t="n"/>
       <c r="I118" s="102" t="n"/>
       <c r="J118" s="102" t="n"/>
@@ -5778,23 +5789,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C119" s="32" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D119" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
-        </is>
-      </c>
-      <c r="E119" s="34" t="n"/>
+      <c r="C119" s="31" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D119" s="91" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="n"/>
       <c r="F119" s="138" t="n"/>
-      <c r="G119" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G119" s="101" t="n"/>
       <c r="H119" s="102" t="n"/>
       <c r="I119" s="102" t="n"/>
       <c r="J119" s="102" t="n"/>
@@ -5806,19 +5813,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C120" s="31" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="n"/>
+      <c r="C120" s="32" t="inlineStr">
+        <is>
+          <t>No Bag</t>
+        </is>
+      </c>
+      <c r="D120" s="33" t="inlineStr">
+        <is>
+          <t>Cannot activate Move cards this round</t>
+        </is>
+      </c>
+      <c r="E120" s="34" t="n"/>
       <c r="F120" s="138" t="n"/>
-      <c r="G120" s="101" t="n"/>
+      <c r="G120" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H120" s="102" t="n"/>
       <c r="I120" s="102" t="n"/>
       <c r="J120" s="102" t="n"/>
@@ -5830,19 +5841,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C121" s="32" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D121" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
-        </is>
-      </c>
-      <c r="E121" s="34" t="n"/>
+      <c r="C121" s="31" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="n"/>
       <c r="F121" s="138" t="n"/>
-      <c r="G121" s="107" t="n"/>
+      <c r="G121" s="101" t="n"/>
       <c r="H121" s="102" t="n"/>
       <c r="I121" s="102" t="n"/>
       <c r="J121" s="102" t="n"/>
@@ -5854,19 +5865,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C122" s="31" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="n"/>
+      <c r="C122" s="32" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D122" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E122" s="34" t="n"/>
       <c r="F122" s="138" t="n"/>
-      <c r="G122" s="101" t="n"/>
+      <c r="G122" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H122" s="102" t="n"/>
       <c r="I122" s="102" t="n"/>
       <c r="J122" s="102" t="n"/>
@@ -5878,19 +5893,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C123" s="32" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D123" s="33" t="inlineStr">
-        <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E123" s="34" t="n"/>
+      <c r="C123" s="31" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="n"/>
       <c r="F123" s="138" t="n"/>
-      <c r="G123" s="107" t="n"/>
+      <c r="G123" s="101" t="n"/>
       <c r="H123" s="102" t="n"/>
       <c r="I123" s="102" t="n"/>
       <c r="J123" s="102" t="n"/>
@@ -5902,19 +5917,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C124" s="31" t="inlineStr">
-        <is>
-          <t>Unguardable</t>
-        </is>
-      </c>
-      <c r="D124" s="91" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="n"/>
+      <c r="C124" s="32" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D124" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E124" s="34" t="n"/>
       <c r="F124" s="138" t="n"/>
-      <c r="G124" s="101" t="n"/>
+      <c r="G124" s="107" t="n"/>
       <c r="H124" s="102" t="n"/>
       <c r="I124" s="102" t="n"/>
       <c r="J124" s="102" t="n"/>
@@ -5926,98 +5941,98 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C125" s="32" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D125" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
-        </is>
-      </c>
-      <c r="E125" s="34" t="n"/>
+      <c r="C125" s="31" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="n"/>
       <c r="F125" s="138" t="n"/>
-      <c r="G125" s="113" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G125" s="101" t="n"/>
       <c r="H125" s="102" t="n"/>
       <c r="I125" s="102" t="n"/>
       <c r="J125" s="102" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="61" t="n"/>
-      <c r="B126" s="62" t="inlineStr">
+      <c r="A126" s="29" t="n"/>
+      <c r="B126" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C126" s="66" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D126" s="95" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E126" s="68" t="n"/>
-      <c r="F126" s="140" t="n"/>
-      <c r="G126" s="126" t="n"/>
-      <c r="H126" s="117" t="n"/>
-      <c r="I126" s="117" t="n"/>
-      <c r="J126" s="117" t="n"/>
+      <c r="C126" s="32" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D126" s="33" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E126" s="34" t="n"/>
+      <c r="F126" s="138" t="n"/>
+      <c r="G126" s="107" t="n"/>
+      <c r="H126" s="102" t="n"/>
+      <c r="I126" s="102" t="n"/>
+      <c r="J126" s="102" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="61" t="n"/>
-      <c r="B127" s="62" t="inlineStr">
+      <c r="A127" s="29" t="n"/>
+      <c r="B127" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C127" s="66" t="inlineStr">
-        <is>
-          <t>Unselfish</t>
-        </is>
-      </c>
-      <c r="D127" s="95" t="inlineStr">
-        <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
-        </is>
-      </c>
-      <c r="E127" s="68" t="n"/>
-      <c r="F127" s="140" t="n"/>
-      <c r="G127" s="126" t="n"/>
-      <c r="H127" s="117" t="n"/>
-      <c r="I127" s="117" t="n"/>
-      <c r="J127" s="117" t="n"/>
+      <c r="C127" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D127" s="91" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="n"/>
+      <c r="F127" s="138" t="n"/>
+      <c r="G127" s="101" t="n"/>
+      <c r="H127" s="102" t="n"/>
+      <c r="I127" s="102" t="n"/>
+      <c r="J127" s="102" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="61" t="n"/>
-      <c r="B128" s="62" t="inlineStr">
+      <c r="A128" s="29" t="n"/>
+      <c r="B128" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C128" s="66" t="inlineStr">
-        <is>
-          <t>Dirty Player</t>
-        </is>
-      </c>
-      <c r="D128" s="95" t="inlineStr">
-        <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
-        </is>
-      </c>
-      <c r="E128" s="68" t="n"/>
-      <c r="F128" s="140" t="n"/>
-      <c r="G128" s="126" t="n"/>
-      <c r="H128" s="117" t="n"/>
-      <c r="I128" s="117" t="n"/>
-      <c r="J128" s="117" t="n"/>
+      <c r="C128" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D128" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E128" s="34" t="n"/>
+      <c r="F128" s="138" t="n"/>
+      <c r="G128" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H128" s="102" t="n"/>
+      <c r="I128" s="102" t="n"/>
+      <c r="J128" s="102" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="61" t="n"/>
@@ -6028,21 +6043,20 @@
       </c>
       <c r="C129" s="66" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D129" s="95" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E129" s="68" t="n"/>
       <c r="F129" s="140" t="n"/>
-      <c r="G129" s="126" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="G129" s="126" t="n"/>
+      <c r="H129" s="117" t="n"/>
+      <c r="I129" s="117" t="n"/>
+      <c r="J129" s="117" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="61" t="n"/>
@@ -6053,21 +6067,20 @@
       </c>
       <c r="C130" s="66" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D130" s="95" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E130" s="68" t="n"/>
       <c r="F130" s="140" t="n"/>
-      <c r="G130" s="126" t="inlineStr">
-        <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
-        </is>
-      </c>
+      <c r="G130" s="126" t="n"/>
+      <c r="H130" s="117" t="n"/>
+      <c r="I130" s="117" t="n"/>
+      <c r="J130" s="117" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="61" t="n"/>
@@ -6078,12 +6091,12 @@
       </c>
       <c r="C131" s="66" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D131" s="95" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E131" s="68" t="n"/>
@@ -6093,10 +6106,109 @@
       <c r="I131" s="117" t="n"/>
       <c r="J131" s="117" t="n"/>
     </row>
+    <row r="132">
+      <c r="A132" s="61" t="n"/>
+      <c r="B132" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C132" s="66" t="inlineStr">
+        <is>
+          <t>Villainous Reputation</t>
+        </is>
+      </c>
+      <c r="D132" s="95" t="inlineStr">
+        <is>
+          <t>Discard 1 whenever any Whistle triggers</t>
+        </is>
+      </c>
+      <c r="E132" s="68" t="n"/>
+      <c r="F132" s="140" t="n"/>
+      <c r="G132" s="126" t="inlineStr">
+        <is>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="61" t="n"/>
+      <c r="B133" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C133" s="66" t="inlineStr">
+        <is>
+          <t>Free Agent</t>
+        </is>
+      </c>
+      <c r="D133" s="95" t="inlineStr">
+        <is>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+        </is>
+      </c>
+      <c r="E133" s="68" t="n"/>
+      <c r="F133" s="140" t="n"/>
+      <c r="G133" s="126" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="61" t="n"/>
+      <c r="B134" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C134" s="66" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D134" s="95" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E134" s="68" t="n"/>
+      <c r="F134" s="140" t="n"/>
+      <c r="G134" s="126" t="n"/>
+      <c r="H134" s="117" t="n"/>
+      <c r="I134" s="117" t="n"/>
+      <c r="J134" s="117" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="61" t="n"/>
+      <c r="B135" s="62" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C135" s="66" t="inlineStr">
+        <is>
+          <t>Fundamentalist</t>
+        </is>
+      </c>
+      <c r="D135" s="95" t="inlineStr">
+        <is>
+          <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent</t>
+        </is>
+      </c>
+      <c r="E135" s="68" t="n"/>
+      <c r="F135" s="140" t="n"/>
+      <c r="G135" s="126" t="n"/>
+      <c r="H135" s="117" t="n"/>
+      <c r="I135" s="117" t="n"/>
+      <c r="J135" s="117" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="118">
+  <mergeCells count="122">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
     <mergeCell ref="G119:J119"/>
@@ -6127,16 +6239,17 @@
     <mergeCell ref="G110:J110"/>
     <mergeCell ref="G113:J113"/>
     <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G94:J94"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G84:J84"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
     <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="G61:J61"/>
     <mergeCell ref="G70:J70"/>
@@ -6157,15 +6270,18 @@
     <mergeCell ref="G65:J65"/>
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="G35:J35"/>
+    <mergeCell ref="G129:J129"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G76:J76"/>
     <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G90:J90"/>
     <mergeCell ref="G99:J99"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="G131:J131"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
+    <mergeCell ref="G130:J130"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
     <mergeCell ref="G126:J126"/>
@@ -6182,13 +6298,13 @@
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G80:J80"/>
     <mergeCell ref="G95:J95"/>
-    <mergeCell ref="G89:J89"/>
     <mergeCell ref="G64:J64"/>
     <mergeCell ref="G79:J79"/>
     <mergeCell ref="G73:J73"/>
     <mergeCell ref="G51:J51"/>
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="G63:J63"/>
+    <mergeCell ref="G134:J134"/>
     <mergeCell ref="G41:J41"/>
     <mergeCell ref="G50:J50"/>
     <mergeCell ref="G106:J106"/>
@@ -6209,7 +6325,6 @@
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G83:J83"/>
-    <mergeCell ref="G92:J92"/>
     <mergeCell ref="G124:J124"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="G14:J14"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -176,7 +176,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="58">
     <border>
       <left/>
       <right/>
@@ -829,13 +829,109 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1237,6 +1333,69 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2659,7 +2818,6 @@
       </c>
       <c r="J2" s="19" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="132">
       <c r="A4" s="123" t="inlineStr">
         <is>
@@ -2687,59 +2845,59 @@
           <t>Number in Deck</t>
         </is>
       </c>
-      <c r="G4" s="103" t="inlineStr">
+      <c r="G4" s="142" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="H4" s="104" t="n"/>
-      <c r="I4" s="104" t="n"/>
-      <c r="J4" s="104" t="n"/>
+      <c r="H4" s="143" t="n"/>
+      <c r="I4" s="143" t="n"/>
+      <c r="J4" s="143" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="132">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="144" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="B5" s="22">
-        <f>COUNTIF($B$5:$B$135,"Pass")</f>
+      <c r="B5" s="145">
+        <f>COUNTIF($B$6:$B$135,"Pass")</f>
         <v/>
       </c>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="72" t="n"/>
-      <c r="G5" s="120" t="n"/>
-      <c r="H5" s="121" t="n"/>
-      <c r="I5" s="121" t="n"/>
-      <c r="J5" s="121" t="n"/>
+      <c r="C5" s="146" t="n"/>
+      <c r="D5" s="146" t="n"/>
+      <c r="E5" s="146" t="n"/>
+      <c r="F5" s="147" t="n"/>
+      <c r="G5" s="148" t="n"/>
+      <c r="H5" s="149" t="n"/>
+      <c r="I5" s="149" t="n"/>
+      <c r="J5" s="149" t="n"/>
     </row>
     <row r="6" ht="56" customHeight="1" s="132">
-      <c r="A6" s="24" t="n"/>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="A6" s="29" t="n"/>
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Behind-the-Back</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Pass back to player who passed to you. If ball not received from a player, TOV +1</t>
         </is>
       </c>
-      <c r="E6" s="28" t="n"/>
-      <c r="F6" s="73" t="n">
+      <c r="E6" s="34" t="n"/>
+      <c r="F6" s="75" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="105" t="n"/>
-      <c r="H6" s="106" t="n"/>
-      <c r="I6" s="106" t="n"/>
-      <c r="J6" s="106" t="n"/>
+      <c r="G6" s="107" t="n"/>
+      <c r="H6" s="102" t="n"/>
+      <c r="I6" s="102" t="n"/>
+      <c r="J6" s="102" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1" s="132">
       <c r="A7" s="29" t="n"/>
@@ -2766,10 +2924,10 @@
       <c r="F7" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="112" t="n"/>
-      <c r="H7" s="106" t="n"/>
-      <c r="I7" s="106" t="n"/>
-      <c r="J7" s="106" t="n"/>
+      <c r="G7" s="101" t="n"/>
+      <c r="H7" s="102" t="n"/>
+      <c r="I7" s="102" t="n"/>
+      <c r="J7" s="102" t="n"/>
     </row>
     <row r="8" ht="56" customHeight="1" s="132">
       <c r="A8" s="29" t="n"/>
@@ -2792,10 +2950,10 @@
       <c r="F8" s="75" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="105" t="n"/>
-      <c r="H8" s="106" t="n"/>
-      <c r="I8" s="106" t="n"/>
-      <c r="J8" s="106" t="n"/>
+      <c r="G8" s="107" t="n"/>
+      <c r="H8" s="102" t="n"/>
+      <c r="I8" s="102" t="n"/>
+      <c r="J8" s="102" t="n"/>
     </row>
     <row r="9" ht="56" customHeight="1" s="132">
       <c r="A9" s="29" t="n"/>
@@ -2818,10 +2976,10 @@
       <c r="F9" s="76" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="112" t="n"/>
-      <c r="H9" s="106" t="n"/>
-      <c r="I9" s="106" t="n"/>
-      <c r="J9" s="106" t="n"/>
+      <c r="G9" s="101" t="n"/>
+      <c r="H9" s="102" t="n"/>
+      <c r="I9" s="102" t="n"/>
+      <c r="J9" s="102" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1" s="132">
       <c r="A10" s="29" t="n"/>
@@ -2844,10 +3002,10 @@
       <c r="F10" s="75" t="n">
         <v>20</v>
       </c>
-      <c r="G10" s="105" t="n"/>
-      <c r="H10" s="106" t="n"/>
-      <c r="I10" s="106" t="n"/>
-      <c r="J10" s="106" t="n"/>
+      <c r="G10" s="107" t="n"/>
+      <c r="H10" s="102" t="n"/>
+      <c r="I10" s="102" t="n"/>
+      <c r="J10" s="102" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1" s="132">
       <c r="A11" s="29" t="n"/>
@@ -2870,10 +3028,10 @@
       <c r="F11" s="76" t="n">
         <v>31</v>
       </c>
-      <c r="G11" s="112" t="n"/>
-      <c r="H11" s="106" t="n"/>
-      <c r="I11" s="106" t="n"/>
-      <c r="J11" s="106" t="n"/>
+      <c r="G11" s="101" t="n"/>
+      <c r="H11" s="102" t="n"/>
+      <c r="I11" s="102" t="n"/>
+      <c r="J11" s="102" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1" s="132">
       <c r="A12" s="29" t="n"/>
@@ -2896,10 +3054,10 @@
       <c r="F12" s="75" t="n">
         <v>31</v>
       </c>
-      <c r="G12" s="105" t="n"/>
-      <c r="H12" s="106" t="n"/>
-      <c r="I12" s="106" t="n"/>
-      <c r="J12" s="106" t="n"/>
+      <c r="G12" s="107" t="n"/>
+      <c r="H12" s="102" t="n"/>
+      <c r="I12" s="102" t="n"/>
+      <c r="J12" s="102" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1" s="132">
       <c r="A13" s="29" t="n"/>
@@ -2922,198 +3080,198 @@
       <c r="F13" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="G13" s="112" t="n"/>
-      <c r="H13" s="106" t="n"/>
-      <c r="I13" s="106" t="n"/>
-      <c r="J13" s="106" t="n"/>
+      <c r="G13" s="101" t="n"/>
+      <c r="H13" s="102" t="n"/>
+      <c r="I13" s="102" t="n"/>
+      <c r="J13" s="102" t="n"/>
     </row>
     <row r="14" ht="29" customHeight="1" s="132">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="A14" s="29" t="n"/>
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>Bullet Pass</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Pass to player of choice. SHOT +5%</t>
         </is>
       </c>
-      <c r="E14" s="38" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>New players discards 1 card at random</t>
         </is>
       </c>
-      <c r="F14" s="77" t="n">
+      <c r="F14" s="80" t="n">
         <v>12</v>
       </c>
-      <c r="G14" s="127" t="n"/>
-      <c r="H14" s="104" t="n"/>
-      <c r="I14" s="104" t="n"/>
-      <c r="J14" s="104" t="n"/>
+      <c r="G14" s="107" t="n"/>
+      <c r="H14" s="102" t="n"/>
+      <c r="I14" s="102" t="n"/>
+      <c r="J14" s="102" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="132">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>Alley-Oop</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>SHOT +20%. Pass to player of choice</t>
         </is>
       </c>
-      <c r="E15" s="38" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>Receiving player shoots immediately after drawing for turn</t>
         </is>
       </c>
-      <c r="F15" s="77" t="n">
+      <c r="F15" s="80" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="127" t="n"/>
-      <c r="H15" s="104" t="n"/>
-      <c r="I15" s="104" t="n"/>
-      <c r="J15" s="104" t="n"/>
+      <c r="G15" s="107" t="n"/>
+      <c r="H15" s="102" t="n"/>
+      <c r="I15" s="102" t="n"/>
+      <c r="J15" s="102" t="n"/>
     </row>
     <row r="16" ht="14" customHeight="1" s="132">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="A16" s="29" t="n"/>
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>Hand-Off</t>
         </is>
       </c>
-      <c r="D16" s="38" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>SHOT +5%. Pass to player to Left or Right. Draw 1 card</t>
         </is>
       </c>
-      <c r="E16" s="38" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>If played following a Dribble: draw 1 additional and SHOT +5% more</t>
         </is>
       </c>
-      <c r="F16" s="77" t="n">
+      <c r="F16" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="G16" s="127" t="inlineStr">
+      <c r="G16" s="107" t="inlineStr">
         <is>
           <t>This is the Dribble Hand-Off</t>
         </is>
       </c>
-      <c r="H16" s="104" t="n"/>
-      <c r="I16" s="104" t="n"/>
-      <c r="J16" s="104" t="n"/>
+      <c r="H16" s="102" t="n"/>
+      <c r="I16" s="102" t="n"/>
+      <c r="J16" s="102" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1" s="132">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="36" t="inlineStr">
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>Outlet Pass</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>SHOT +10%. Shot Clock +01. Pass to player of choice</t>
         </is>
       </c>
-      <c r="E17" s="38" t="n"/>
-      <c r="F17" s="77" t="n">
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="127" t="inlineStr">
+      <c r="G17" s="107" t="inlineStr">
         <is>
           <t>The clock increments instead of decrementing — it does not break even</t>
         </is>
       </c>
-      <c r="H17" s="104" t="n"/>
-      <c r="I17" s="104" t="n"/>
-      <c r="J17" s="104" t="n"/>
+      <c r="H17" s="102" t="n"/>
+      <c r="I17" s="102" t="n"/>
+      <c r="J17" s="102" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1" s="132">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="A18" s="29" t="n"/>
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>Kick-Out</t>
         </is>
       </c>
-      <c r="D18" s="38" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>SHOT +10%. Upgraded to 3pt. Pass to player of choice</t>
         </is>
       </c>
-      <c r="E18" s="38" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>Following Drive: draw 1. Following a Dribble Drive: gain 1 AST also</t>
         </is>
       </c>
-      <c r="F18" s="77" t="n">
+      <c r="F18" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="127" t="inlineStr">
+      <c r="G18" s="107" t="inlineStr">
         <is>
           <t>The most it grants is a draw and 1 AST</t>
         </is>
       </c>
-      <c r="H18" s="104" t="n"/>
-      <c r="I18" s="104" t="n"/>
-      <c r="J18" s="104" t="n"/>
+      <c r="H18" s="102" t="n"/>
+      <c r="I18" s="102" t="n"/>
+      <c r="J18" s="102" t="n"/>
     </row>
     <row r="19" ht="56" customHeight="1" s="132">
-      <c r="A19" s="35" t="n"/>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>Right Back</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>SHOT +5%. Pass to player of choice. They immediately pass it back</t>
         </is>
       </c>
-      <c r="E19" s="38" t="n"/>
-      <c r="F19" s="77" t="n">
+      <c r="E19" s="33" t="n"/>
+      <c r="F19" s="80" t="n">
         <v>7</v>
       </c>
-      <c r="G19" s="127" t="inlineStr">
+      <c r="G19" s="107" t="inlineStr">
         <is>
           <t>Results in a draw for each player and SHOT +10% overall. Whatever the trip costs them happens in between</t>
         </is>
       </c>
-      <c r="H19" s="104" t="n"/>
-      <c r="I19" s="104" t="n"/>
-      <c r="J19" s="104" t="n"/>
+      <c r="H19" s="102" t="n"/>
+      <c r="I19" s="102" t="n"/>
+      <c r="J19" s="102" t="n"/>
     </row>
     <row r="20" ht="56" customHeight="1" s="132">
       <c r="A20" s="35" t="n"/>
@@ -3136,55 +3294,55 @@
       <c r="F20" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="G20" s="127" t="n"/>
-      <c r="H20" s="104" t="n"/>
-      <c r="I20" s="104" t="n"/>
-      <c r="J20" s="104" t="n"/>
+      <c r="G20" s="150" t="n"/>
+      <c r="H20" s="151" t="n"/>
+      <c r="I20" s="151" t="n"/>
+      <c r="J20" s="151" t="n"/>
     </row>
     <row r="21" ht="14" customHeight="1" s="132">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="144" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="B21" s="40">
-        <f>COUNTIF($B$5:$B$135,"Move")+COUNTIF($B$5:$B$135,"Special Move")</f>
+      <c r="B21" s="145">
+        <f>COUNTIF($B$22:$B$135,"Move")+COUNTIF($B$22:$B$135,"Special Move")</f>
         <v/>
       </c>
-      <c r="C21" s="41" t="n"/>
-      <c r="D21" s="41" t="n"/>
-      <c r="E21" s="41" t="n"/>
-      <c r="F21" s="78" t="n"/>
-      <c r="G21" s="120" t="n"/>
-      <c r="H21" s="121" t="n"/>
-      <c r="I21" s="121" t="n"/>
-      <c r="J21" s="121" t="n"/>
+      <c r="C21" s="146" t="n"/>
+      <c r="D21" s="146" t="n"/>
+      <c r="E21" s="146" t="n"/>
+      <c r="F21" s="147" t="n"/>
+      <c r="G21" s="148" t="n"/>
+      <c r="H21" s="149" t="n"/>
+      <c r="I21" s="149" t="n"/>
+      <c r="J21" s="149" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1" s="132">
-      <c r="A22" s="45" t="n"/>
-      <c r="B22" s="46" t="inlineStr">
+      <c r="A22" s="29" t="n"/>
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>Dribble</t>
         </is>
       </c>
-      <c r="D22" s="48" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>Draw 1 card. SHOT -10%</t>
         </is>
       </c>
-      <c r="E22" s="49" t="n"/>
-      <c r="F22" s="79" t="n">
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="75" t="n">
         <v>15</v>
       </c>
-      <c r="G22" s="118" t="n"/>
-      <c r="H22" s="119" t="n"/>
-      <c r="I22" s="119" t="n"/>
-      <c r="J22" s="119" t="n"/>
+      <c r="G22" s="107" t="n"/>
+      <c r="H22" s="102" t="n"/>
+      <c r="I22" s="102" t="n"/>
+      <c r="J22" s="102" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1" s="132">
       <c r="A23" s="29" t="n"/>
@@ -3479,18 +3637,18 @@
       <c r="J32" s="102" t="n"/>
     </row>
     <row r="33" ht="14" customHeight="1" s="132">
-      <c r="A33" s="61" t="n"/>
-      <c r="B33" s="62" t="inlineStr">
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C33" s="63" t="inlineStr">
+      <c r="C33" s="32" t="inlineStr">
         <is>
           <t>Triple Threat</t>
         </is>
       </c>
-      <c r="D33" s="64" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>Choose 1:
 Draw 1 card
@@ -3498,99 +3656,99 @@
 SHOT +10%</t>
         </is>
       </c>
-      <c r="E33" s="64" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>Cannot use further Move cards</t>
         </is>
       </c>
-      <c r="F33" s="81" t="n">
+      <c r="F33" s="80" t="n">
         <v>15</v>
       </c>
-      <c r="G33" s="116" t="inlineStr">
+      <c r="G33" s="107" t="inlineStr">
         <is>
           <t>Cannot use further Move cards applies to that possession only.</t>
         </is>
       </c>
-      <c r="H33" s="117" t="n"/>
-      <c r="I33" s="117" t="n"/>
-      <c r="J33" s="117" t="n"/>
+      <c r="H33" s="102" t="n"/>
+      <c r="I33" s="102" t="n"/>
+      <c r="J33" s="102" t="n"/>
     </row>
     <row r="34" ht="14" customHeight="1" s="132">
-      <c r="A34" s="61" t="n"/>
-      <c r="B34" s="62" t="inlineStr">
+      <c r="A34" s="35" t="n"/>
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C34" s="63" t="inlineStr">
+      <c r="C34" s="37" t="inlineStr">
         <is>
           <t>Clear Out</t>
         </is>
       </c>
-      <c r="D34" s="64" t="inlineStr">
+      <c r="D34" s="38" t="inlineStr">
         <is>
           <t>First action only. The next pass to a side goes past you. One that named you is a TOV and ends the round</t>
         </is>
       </c>
-      <c r="E34" s="64" t="n"/>
-      <c r="F34" s="81" t="n">
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="G34" s="116" t="n"/>
-      <c r="H34" s="117" t="n"/>
-      <c r="I34" s="117" t="n"/>
-      <c r="J34" s="117" t="n"/>
+      <c r="G34" s="150" t="n"/>
+      <c r="H34" s="151" t="n"/>
+      <c r="I34" s="151" t="n"/>
+      <c r="J34" s="151" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1" s="132">
-      <c r="A35" s="42" t="inlineStr">
+      <c r="A35" s="144" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="B35" s="43">
-        <f>COUNTIF($B$5:$B$135,"Special Move")</f>
+      <c r="B35" s="145">
+        <f>COUNTIF($B$36:$B$135,"Special Move")</f>
         <v/>
       </c>
-      <c r="C35" s="44" t="n"/>
-      <c r="D35" s="44" t="n"/>
-      <c r="E35" s="44" t="n"/>
-      <c r="F35" s="82" t="n"/>
-      <c r="G35" s="120" t="n"/>
-      <c r="H35" s="121" t="n"/>
-      <c r="I35" s="121" t="n"/>
-      <c r="J35" s="121" t="n"/>
+      <c r="C35" s="146" t="n"/>
+      <c r="D35" s="146" t="n"/>
+      <c r="E35" s="146" t="n"/>
+      <c r="F35" s="147" t="n"/>
+      <c r="G35" s="148" t="n"/>
+      <c r="H35" s="149" t="n"/>
+      <c r="I35" s="149" t="n"/>
+      <c r="J35" s="149" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1" s="132">
-      <c r="A36" s="24" t="n"/>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="A36" s="29" t="n"/>
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="32" t="inlineStr">
         <is>
           <t>Bankshot</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>Flip a coin:
 Heads: SHOT +10%
 Tails: SHOT -10%</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F36" s="83" t="n">
+      <c r="F36" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="G36" s="105" t="n"/>
-      <c r="H36" s="106" t="n"/>
-      <c r="I36" s="106" t="n"/>
-      <c r="J36" s="106" t="n"/>
+      <c r="G36" s="107" t="n"/>
+      <c r="H36" s="102" t="n"/>
+      <c r="I36" s="102" t="n"/>
+      <c r="J36" s="102" t="n"/>
     </row>
     <row r="37" ht="28" customHeight="1" s="132">
       <c r="A37" s="29" t="n"/>
@@ -3617,14 +3775,14 @@
       <c r="F37" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="G37" s="128" t="inlineStr">
+      <c r="G37" s="111" t="inlineStr">
         <is>
           <t>Can only play with Shot Clock at 1</t>
         </is>
       </c>
-      <c r="H37" s="106" t="n"/>
-      <c r="I37" s="106" t="n"/>
-      <c r="J37" s="106" t="n"/>
+      <c r="H37" s="102" t="n"/>
+      <c r="I37" s="102" t="n"/>
+      <c r="J37" s="102" t="n"/>
     </row>
     <row r="38" ht="42" customHeight="1" s="132">
       <c r="A38" s="29" t="n"/>
@@ -3651,10 +3809,10 @@
       <c r="F38" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="G38" s="105" t="n"/>
-      <c r="H38" s="106" t="n"/>
-      <c r="I38" s="106" t="n"/>
-      <c r="J38" s="106" t="n"/>
+      <c r="G38" s="107" t="n"/>
+      <c r="H38" s="102" t="n"/>
+      <c r="I38" s="102" t="n"/>
+      <c r="J38" s="102" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1" s="132">
       <c r="A39" s="29" t="n"/>
@@ -3681,10 +3839,10 @@
       <c r="F39" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="G39" s="112" t="n"/>
-      <c r="H39" s="106" t="n"/>
-      <c r="I39" s="106" t="n"/>
-      <c r="J39" s="106" t="n"/>
+      <c r="G39" s="101" t="n"/>
+      <c r="H39" s="102" t="n"/>
+      <c r="I39" s="102" t="n"/>
+      <c r="J39" s="102" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1" s="132">
       <c r="A40" s="29" t="n"/>
@@ -3711,10 +3869,10 @@
       <c r="F40" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="G40" s="105" t="n"/>
-      <c r="H40" s="106" t="n"/>
-      <c r="I40" s="106" t="n"/>
-      <c r="J40" s="106" t="n"/>
+      <c r="G40" s="107" t="n"/>
+      <c r="H40" s="102" t="n"/>
+      <c r="I40" s="102" t="n"/>
+      <c r="J40" s="102" t="n"/>
     </row>
     <row r="41" ht="42" customHeight="1" s="132">
       <c r="A41" s="29" t="n"/>
@@ -3741,10 +3899,10 @@
       <c r="F41" s="74" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="112" t="n"/>
-      <c r="H41" s="106" t="n"/>
-      <c r="I41" s="106" t="n"/>
-      <c r="J41" s="106" t="n"/>
+      <c r="G41" s="101" t="n"/>
+      <c r="H41" s="102" t="n"/>
+      <c r="I41" s="102" t="n"/>
+      <c r="J41" s="102" t="n"/>
     </row>
     <row r="42" ht="57" customHeight="1" s="132">
       <c r="A42" s="29" t="n"/>
@@ -3771,10 +3929,10 @@
       <c r="F42" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="105" t="n"/>
-      <c r="H42" s="106" t="n"/>
-      <c r="I42" s="106" t="n"/>
-      <c r="J42" s="106" t="n"/>
+      <c r="G42" s="107" t="n"/>
+      <c r="H42" s="102" t="n"/>
+      <c r="I42" s="102" t="n"/>
+      <c r="J42" s="102" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1" s="132">
       <c r="A43" s="29" t="n"/>
@@ -3801,10 +3959,10 @@
       <c r="F43" s="74" t="n">
         <v>3</v>
       </c>
-      <c r="G43" s="112" t="n"/>
-      <c r="H43" s="106" t="n"/>
-      <c r="I43" s="106" t="n"/>
-      <c r="J43" s="106" t="n"/>
+      <c r="G43" s="101" t="n"/>
+      <c r="H43" s="102" t="n"/>
+      <c r="I43" s="102" t="n"/>
+      <c r="J43" s="102" t="n"/>
     </row>
     <row r="44" ht="28" customHeight="1" s="132">
       <c r="A44" s="29" t="n"/>
@@ -3831,10 +3989,10 @@
       <c r="F44" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="105" t="n"/>
-      <c r="H44" s="106" t="n"/>
-      <c r="I44" s="106" t="n"/>
-      <c r="J44" s="106" t="n"/>
+      <c r="G44" s="107" t="n"/>
+      <c r="H44" s="102" t="n"/>
+      <c r="I44" s="102" t="n"/>
+      <c r="J44" s="102" t="n"/>
     </row>
     <row r="45" ht="28" customHeight="1" s="132">
       <c r="A45" s="29" t="n"/>
@@ -3861,123 +4019,123 @@
       <c r="F45" s="74" t="n">
         <v>4</v>
       </c>
-      <c r="G45" s="112" t="n"/>
-      <c r="H45" s="106" t="n"/>
-      <c r="I45" s="106" t="n"/>
-      <c r="J45" s="106" t="n"/>
+      <c r="G45" s="101" t="n"/>
+      <c r="H45" s="102" t="n"/>
+      <c r="I45" s="102" t="n"/>
+      <c r="J45" s="102" t="n"/>
     </row>
     <row r="46" ht="42" customHeight="1" s="132">
-      <c r="A46" s="52" t="n"/>
-      <c r="B46" s="53" t="inlineStr">
+      <c r="A46" s="29" t="n"/>
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C46" s="69" t="inlineStr">
+      <c r="C46" s="32" t="inlineStr">
         <is>
           <t>Turnaround Three</t>
         </is>
       </c>
-      <c r="D46" s="70" t="inlineStr">
+      <c r="D46" s="33" t="inlineStr">
         <is>
           <t>Discard any number of cards. SHOT +10% for each</t>
         </is>
       </c>
-      <c r="E46" s="70" t="inlineStr">
+      <c r="E46" s="33" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F46" s="84" t="n">
+      <c r="F46" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="129" t="inlineStr">
+      <c r="G46" s="113" t="inlineStr">
         <is>
           <t>Only 1 in deck</t>
         </is>
       </c>
-      <c r="H46" s="106" t="n"/>
-      <c r="I46" s="106" t="n"/>
-      <c r="J46" s="106" t="n"/>
+      <c r="H46" s="102" t="n"/>
+      <c r="I46" s="102" t="n"/>
+      <c r="J46" s="102" t="n"/>
     </row>
     <row r="47" ht="42" customHeight="1" s="132">
-      <c r="A47" s="61" t="n"/>
-      <c r="B47" s="62" t="inlineStr">
+      <c r="A47" s="29" t="n"/>
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C47" s="66" t="inlineStr">
+      <c r="C47" s="31" t="inlineStr">
         <is>
           <t>Euro Step</t>
         </is>
       </c>
-      <c r="D47" s="67" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Flip a coin until you get Tails. For each Heads, SHOT +5% and Draw 1 card</t>
         </is>
       </c>
-      <c r="E47" s="68" t="n"/>
-      <c r="F47" s="85" t="n">
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G47" s="122" t="n"/>
-      <c r="H47" s="104" t="n"/>
-      <c r="I47" s="104" t="n"/>
-      <c r="J47" s="104" t="n"/>
+      <c r="G47" s="101" t="n"/>
+      <c r="H47" s="102" t="n"/>
+      <c r="I47" s="102" t="n"/>
+      <c r="J47" s="102" t="n"/>
     </row>
     <row r="48" ht="29" customHeight="1" s="132">
-      <c r="A48" s="61" t="n"/>
-      <c r="B48" s="62" t="inlineStr">
+      <c r="A48" s="35" t="n"/>
+      <c r="B48" s="36" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C48" s="66" t="inlineStr">
+      <c r="C48" s="152" t="inlineStr">
         <is>
           <t>Wide-Open Three</t>
         </is>
       </c>
-      <c r="D48" s="67" t="inlineStr">
+      <c r="D48" s="153" t="inlineStr">
         <is>
           <t>Select any number of other players. SHOT +10% for each</t>
         </is>
       </c>
-      <c r="E48" s="68" t="inlineStr">
+      <c r="E48" s="154" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make. Selected players receive +1 AST on a make</t>
         </is>
       </c>
-      <c r="F48" s="85" t="n">
+      <c r="F48" s="155" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="122" t="inlineStr">
+      <c r="G48" s="156" t="inlineStr">
         <is>
           <t>Selecting none rolls off current SHOT and is still a three</t>
         </is>
       </c>
-      <c r="H48" s="104" t="n"/>
-      <c r="I48" s="104" t="n"/>
-      <c r="J48" s="104" t="n"/>
+      <c r="H48" s="151" t="n"/>
+      <c r="I48" s="151" t="n"/>
+      <c r="J48" s="151" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1" s="132">
-      <c r="A49" s="58" t="inlineStr">
+      <c r="A49" s="144" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B49" s="59">
-        <f>COUNTIF($B$5:$B$135,"Clamp")</f>
+      <c r="B49" s="145">
+        <f>COUNTIF($B$50:$B$135,"Clamp")</f>
         <v/>
       </c>
-      <c r="C49" s="60" t="n"/>
-      <c r="D49" s="60" t="n"/>
-      <c r="E49" s="60" t="n"/>
-      <c r="F49" s="86" t="n"/>
-      <c r="G49" s="109" t="n"/>
-      <c r="H49" s="110" t="n"/>
-      <c r="I49" s="110" t="n"/>
-      <c r="J49" s="110" t="n"/>
+      <c r="C49" s="146" t="n"/>
+      <c r="D49" s="146" t="n"/>
+      <c r="E49" s="146" t="n"/>
+      <c r="F49" s="147" t="n"/>
+      <c r="G49" s="148" t="n"/>
+      <c r="H49" s="149" t="n"/>
+      <c r="I49" s="149" t="n"/>
+      <c r="J49" s="149" t="n"/>
     </row>
     <row r="50" ht="56" customHeight="1" s="132">
       <c r="A50" s="29" t="n"/>
@@ -4100,53 +4258,53 @@
       <c r="J53" s="102" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1" s="132">
-      <c r="A54" s="61" t="n"/>
-      <c r="B54" s="62" t="inlineStr">
+      <c r="A54" s="35" t="n"/>
+      <c r="B54" s="36" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C54" s="66" t="inlineStr">
+      <c r="C54" s="152" t="inlineStr">
         <is>
           <t>Triple-Team</t>
         </is>
       </c>
-      <c r="D54" s="67" t="inlineStr">
+      <c r="D54" s="153" t="inlineStr">
         <is>
           <t>Next player cannot play 3 random cards from hand.</t>
         </is>
       </c>
-      <c r="E54" s="68" t="n"/>
-      <c r="F54" s="85" t="n">
+      <c r="E54" s="154" t="n"/>
+      <c r="F54" s="155" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="135" t="inlineStr">
+      <c r="G54" s="157" t="inlineStr">
         <is>
           <t>3 def</t>
         </is>
       </c>
-      <c r="H54" s="117" t="n"/>
-      <c r="I54" s="117" t="n"/>
-      <c r="J54" s="117" t="n"/>
+      <c r="H54" s="151" t="n"/>
+      <c r="I54" s="151" t="n"/>
+      <c r="J54" s="151" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1" s="132">
-      <c r="A55" s="58" t="inlineStr">
+      <c r="A55" s="144" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="B55" s="59">
-        <f>COUNTIF($B$5:$B$135,"Whistle")</f>
+      <c r="B55" s="145">
+        <f>COUNTIF($B$56:$B$135,"Whistle")</f>
         <v/>
       </c>
-      <c r="C55" s="60" t="n"/>
-      <c r="D55" s="60" t="n"/>
-      <c r="E55" s="60" t="n"/>
-      <c r="F55" s="86" t="n"/>
-      <c r="G55" s="109" t="n"/>
-      <c r="H55" s="110" t="n"/>
-      <c r="I55" s="110" t="n"/>
-      <c r="J55" s="110" t="n"/>
+      <c r="C55" s="146" t="n"/>
+      <c r="D55" s="146" t="n"/>
+      <c r="E55" s="146" t="n"/>
+      <c r="F55" s="147" t="n"/>
+      <c r="G55" s="148" t="n"/>
+      <c r="H55" s="149" t="n"/>
+      <c r="I55" s="149" t="n"/>
+      <c r="J55" s="149" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1" s="132">
       <c r="A56" s="29" t="inlineStr">
@@ -4537,103 +4695,103 @@
       <c r="J70" s="102" t="n"/>
     </row>
     <row r="71" ht="14" customHeight="1" s="132">
-      <c r="A71" s="61" t="n"/>
-      <c r="B71" s="62" t="inlineStr">
+      <c r="A71" s="29" t="n"/>
+      <c r="B71" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C71" s="63" t="inlineStr">
+      <c r="C71" s="32" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="D71" s="64" t="inlineStr">
+      <c r="D71" s="33" t="inlineStr">
         <is>
           <t>Move card played: Cancel card. TOV +1</t>
         </is>
       </c>
-      <c r="E71" s="65" t="n"/>
-      <c r="F71" s="140" t="n"/>
-      <c r="G71" s="116" t="n"/>
-      <c r="H71" s="117" t="n"/>
-      <c r="I71" s="117" t="n"/>
-      <c r="J71" s="117" t="n"/>
+      <c r="E71" s="34" t="n"/>
+      <c r="F71" s="138" t="n"/>
+      <c r="G71" s="107" t="n"/>
+      <c r="H71" s="102" t="n"/>
+      <c r="I71" s="102" t="n"/>
+      <c r="J71" s="102" t="n"/>
     </row>
     <row r="72" ht="28" customHeight="1" s="132">
-      <c r="A72" s="61" t="n"/>
-      <c r="B72" s="62" t="inlineStr">
+      <c r="A72" s="29" t="n"/>
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C72" s="63" t="inlineStr">
+      <c r="C72" s="32" t="inlineStr">
         <is>
           <t>Clear Path Foul</t>
         </is>
       </c>
-      <c r="D72" s="64" t="inlineStr">
+      <c r="D72" s="33" t="inlineStr">
         <is>
           <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
         </is>
       </c>
-      <c r="E72" s="65" t="n"/>
-      <c r="F72" s="140" t="n"/>
-      <c r="G72" s="116" t="inlineStr">
+      <c r="E72" s="34" t="n"/>
+      <c r="F72" s="138" t="n"/>
+      <c r="G72" s="107" t="inlineStr">
         <is>
           <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
         </is>
       </c>
-      <c r="H72" s="117" t="n"/>
-      <c r="I72" s="117" t="n"/>
-      <c r="J72" s="117" t="n"/>
+      <c r="H72" s="102" t="n"/>
+      <c r="I72" s="102" t="n"/>
+      <c r="J72" s="102" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1" s="132">
-      <c r="A73" s="61" t="n"/>
-      <c r="B73" s="62" t="inlineStr">
+      <c r="A73" s="35" t="n"/>
+      <c r="B73" s="36" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C73" s="63" t="inlineStr">
+      <c r="C73" s="37" t="inlineStr">
         <is>
           <t>Play-On</t>
         </is>
       </c>
-      <c r="D73" s="64" t="inlineStr">
+      <c r="D73" s="38" t="inlineStr">
         <is>
           <t>Discard each Game Break drawn and draw again, until a card is not one</t>
         </is>
       </c>
-      <c r="E73" s="65" t="n"/>
-      <c r="F73" s="140" t="n"/>
-      <c r="G73" s="116" t="inlineStr">
+      <c r="E73" s="158" t="n"/>
+      <c r="F73" s="159" t="n"/>
+      <c r="G73" s="150" t="inlineStr">
         <is>
           <t>Raised where the Break lands, like Cleared to Play — nobody plays a Break</t>
         </is>
       </c>
-      <c r="H73" s="117" t="n"/>
-      <c r="I73" s="117" t="n"/>
-      <c r="J73" s="117" t="n"/>
+      <c r="H73" s="151" t="n"/>
+      <c r="I73" s="151" t="n"/>
+      <c r="J73" s="151" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1" s="132">
-      <c r="A74" s="58" t="inlineStr">
+      <c r="A74" s="144" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B74" s="59">
-        <f>COUNTIF($B$5:$B$135,"Game Break")</f>
+      <c r="B74" s="145">
+        <f>COUNTIF($B$75:$B$135,"Game Break")</f>
         <v/>
       </c>
-      <c r="C74" s="60" t="n"/>
-      <c r="D74" s="60" t="n"/>
-      <c r="E74" s="60" t="n"/>
-      <c r="F74" s="86" t="n"/>
-      <c r="G74" s="109" t="n"/>
-      <c r="H74" s="110" t="n"/>
-      <c r="I74" s="110" t="n"/>
-      <c r="J74" s="110" t="n"/>
+      <c r="C74" s="146" t="n"/>
+      <c r="D74" s="146" t="n"/>
+      <c r="E74" s="146" t="n"/>
+      <c r="F74" s="147" t="n"/>
+      <c r="G74" s="148" t="n"/>
+      <c r="H74" s="149" t="n"/>
+      <c r="I74" s="149" t="n"/>
+      <c r="J74" s="149" t="n"/>
     </row>
     <row r="75" ht="28" customHeight="1" s="132">
       <c r="A75" s="29" t="n"/>
@@ -5402,137 +5560,137 @@
       <c r="J102" s="102" t="n"/>
     </row>
     <row r="103" ht="14" customHeight="1" s="132">
-      <c r="A103" s="29" t="n"/>
-      <c r="B103" s="30" t="inlineStr">
+      <c r="A103" s="35" t="n"/>
+      <c r="B103" s="36" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C103" s="134" t="inlineStr">
+      <c r="C103" s="160" t="inlineStr">
         <is>
           <t>Back-and-Forth Game</t>
         </is>
       </c>
-      <c r="D103" s="91" t="inlineStr">
+      <c r="D103" s="161" t="inlineStr">
         <is>
           <t>Discard the next 3 Game Breaks. Whoever draws one draws again</t>
         </is>
       </c>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="76" t="n">
+      <c r="E103" s="154" t="n"/>
+      <c r="F103" s="155" t="n">
         <v>3</v>
       </c>
-      <c r="G103" s="111" t="n"/>
-      <c r="H103" s="102" t="n"/>
-      <c r="I103" s="102" t="n"/>
-      <c r="J103" s="102" t="n"/>
+      <c r="G103" s="162" t="n"/>
+      <c r="H103" s="151" t="n"/>
+      <c r="I103" s="151" t="n"/>
+      <c r="J103" s="151" t="n"/>
     </row>
     <row r="104" ht="28" customHeight="1" s="132">
-      <c r="A104" s="55" t="inlineStr">
+      <c r="A104" s="144" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="B104" s="56">
-        <f>COUNTIF($B$5:$B$135,"Injury GB")</f>
+      <c r="B104" s="145">
+        <f>COUNTIF($B$105:$B$135,"Injury GB")</f>
         <v/>
       </c>
-      <c r="C104" s="57" t="n"/>
-      <c r="D104" s="57" t="n"/>
-      <c r="E104" s="57" t="n"/>
-      <c r="F104" s="88" t="n"/>
-      <c r="G104" s="108" t="n"/>
-      <c r="H104" s="102" t="n"/>
-      <c r="I104" s="102" t="n"/>
-      <c r="J104" s="102" t="n"/>
+      <c r="C104" s="146" t="n"/>
+      <c r="D104" s="146" t="n"/>
+      <c r="E104" s="146" t="n"/>
+      <c r="F104" s="147" t="n"/>
+      <c r="G104" s="148" t="n"/>
+      <c r="H104" s="149" t="n"/>
+      <c r="I104" s="149" t="n"/>
+      <c r="J104" s="149" t="n"/>
     </row>
     <row r="105" ht="28" customHeight="1" s="132">
-      <c r="A105" s="29" t="n"/>
-      <c r="B105" s="30" t="inlineStr">
+      <c r="A105" s="35" t="n"/>
+      <c r="B105" s="36" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="C105" s="31" t="inlineStr">
+      <c r="C105" s="152" t="inlineStr">
         <is>
           <t>Bone Bruise</t>
         </is>
       </c>
-      <c r="D105" s="91" t="inlineStr">
+      <c r="D105" s="161" t="inlineStr">
         <is>
           <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
         </is>
       </c>
-      <c r="E105" s="7" t="n"/>
-      <c r="F105" s="76" t="n">
+      <c r="E105" s="154" t="n"/>
+      <c r="F105" s="155" t="n">
         <v>3</v>
       </c>
-      <c r="G105" s="101" t="n"/>
-      <c r="H105" s="102" t="n"/>
-      <c r="I105" s="102" t="n"/>
-      <c r="J105" s="102" t="n"/>
+      <c r="G105" s="156" t="n"/>
+      <c r="H105" s="151" t="n"/>
+      <c r="I105" s="151" t="n"/>
+      <c r="J105" s="151" t="n"/>
     </row>
     <row r="106" ht="28" customHeight="1" s="132">
-      <c r="A106" s="58" t="inlineStr">
+      <c r="A106" s="144" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="B106" s="59">
-        <f>COUNTIF($B$5:$B$135,"Devastating Injury GB")</f>
+      <c r="B106" s="145">
+        <f>COUNTIF($B$107:$B$135,"Devastating Injury GB")</f>
         <v/>
       </c>
-      <c r="C106" s="60" t="n"/>
-      <c r="D106" s="60" t="n"/>
-      <c r="E106" s="60" t="n"/>
-      <c r="F106" s="86" t="n"/>
-      <c r="G106" s="109" t="n"/>
-      <c r="H106" s="110" t="n"/>
-      <c r="I106" s="110" t="n"/>
-      <c r="J106" s="110" t="n"/>
+      <c r="C106" s="146" t="n"/>
+      <c r="D106" s="146" t="n"/>
+      <c r="E106" s="146" t="n"/>
+      <c r="F106" s="147" t="n"/>
+      <c r="G106" s="148" t="n"/>
+      <c r="H106" s="149" t="n"/>
+      <c r="I106" s="149" t="n"/>
+      <c r="J106" s="149" t="n"/>
     </row>
     <row r="107" ht="28" customHeight="1" s="132">
-      <c r="A107" s="50" t="n"/>
-      <c r="B107" s="51" t="inlineStr">
+      <c r="A107" s="35" t="n"/>
+      <c r="B107" s="36" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="C107" s="136" t="inlineStr">
+      <c r="C107" s="163" t="inlineStr">
         <is>
           <t>Torn Achilles</t>
         </is>
       </c>
-      <c r="D107" s="137" t="inlineStr">
+      <c r="D107" s="164" t="inlineStr">
         <is>
           <t>Hand is locked every turn except 1 card (randomly)</t>
         </is>
       </c>
-      <c r="E107" s="54" t="n"/>
-      <c r="F107" s="141" t="n"/>
-      <c r="G107" s="114" t="n"/>
-      <c r="H107" s="115" t="n"/>
-      <c r="I107" s="115" t="n"/>
-      <c r="J107" s="115" t="n"/>
+      <c r="E107" s="154" t="n"/>
+      <c r="F107" s="159" t="n"/>
+      <c r="G107" s="156" t="n"/>
+      <c r="H107" s="151" t="n"/>
+      <c r="I107" s="151" t="n"/>
+      <c r="J107" s="151" t="n"/>
     </row>
     <row r="108" ht="42" customHeight="1" s="132">
-      <c r="A108" s="55" t="inlineStr">
+      <c r="A108" s="144" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B108" s="56">
-        <f>COUNTIF($B$5:$B$135,"Intangible")</f>
+      <c r="B108" s="145">
+        <f>COUNTIF($B$109:$B$135,"Intangible")</f>
         <v/>
       </c>
-      <c r="C108" s="57" t="n"/>
-      <c r="D108" s="57" t="n"/>
-      <c r="E108" s="57" t="n"/>
-      <c r="F108" s="88" t="n"/>
-      <c r="G108" s="108" t="n"/>
-      <c r="H108" s="102" t="n"/>
-      <c r="I108" s="102" t="n"/>
-      <c r="J108" s="102" t="n"/>
+      <c r="C108" s="146" t="n"/>
+      <c r="D108" s="146" t="n"/>
+      <c r="E108" s="146" t="n"/>
+      <c r="F108" s="147" t="n"/>
+      <c r="G108" s="148" t="n"/>
+      <c r="H108" s="149" t="n"/>
+      <c r="I108" s="149" t="n"/>
+      <c r="J108" s="149" t="n"/>
     </row>
     <row r="109" ht="56" customHeight="1" s="132">
       <c r="A109" s="96" t="inlineStr">
@@ -6035,174 +6193,180 @@
       <c r="J128" s="102" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="61" t="n"/>
-      <c r="B129" s="62" t="inlineStr">
+      <c r="A129" s="29" t="n"/>
+      <c r="B129" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C129" s="66" t="inlineStr">
+      <c r="C129" s="31" t="inlineStr">
         <is>
           <t>Ball Pounder</t>
         </is>
       </c>
-      <c r="D129" s="95" t="inlineStr">
+      <c r="D129" s="91" t="inlineStr">
         <is>
           <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
-      <c r="E129" s="68" t="n"/>
-      <c r="F129" s="140" t="n"/>
-      <c r="G129" s="126" t="n"/>
-      <c r="H129" s="117" t="n"/>
-      <c r="I129" s="117" t="n"/>
-      <c r="J129" s="117" t="n"/>
+      <c r="E129" s="7" t="n"/>
+      <c r="F129" s="138" t="n"/>
+      <c r="G129" s="101" t="n"/>
+      <c r="H129" s="102" t="n"/>
+      <c r="I129" s="102" t="n"/>
+      <c r="J129" s="102" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="61" t="n"/>
-      <c r="B130" s="62" t="inlineStr">
+      <c r="A130" s="29" t="n"/>
+      <c r="B130" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C130" s="66" t="inlineStr">
+      <c r="C130" s="31" t="inlineStr">
         <is>
           <t>Unselfish</t>
         </is>
       </c>
-      <c r="D130" s="95" t="inlineStr">
+      <c r="D130" s="91" t="inlineStr">
         <is>
           <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
-      <c r="E130" s="68" t="n"/>
-      <c r="F130" s="140" t="n"/>
-      <c r="G130" s="126" t="n"/>
-      <c r="H130" s="117" t="n"/>
-      <c r="I130" s="117" t="n"/>
-      <c r="J130" s="117" t="n"/>
+      <c r="E130" s="7" t="n"/>
+      <c r="F130" s="138" t="n"/>
+      <c r="G130" s="101" t="n"/>
+      <c r="H130" s="102" t="n"/>
+      <c r="I130" s="102" t="n"/>
+      <c r="J130" s="102" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="61" t="n"/>
-      <c r="B131" s="62" t="inlineStr">
+      <c r="A131" s="29" t="n"/>
+      <c r="B131" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C131" s="66" t="inlineStr">
+      <c r="C131" s="31" t="inlineStr">
         <is>
           <t>Dirty Player</t>
         </is>
       </c>
-      <c r="D131" s="95" t="inlineStr">
+      <c r="D131" s="91" t="inlineStr">
         <is>
           <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
-      <c r="E131" s="68" t="n"/>
-      <c r="F131" s="140" t="n"/>
-      <c r="G131" s="126" t="n"/>
-      <c r="H131" s="117" t="n"/>
-      <c r="I131" s="117" t="n"/>
-      <c r="J131" s="117" t="n"/>
+      <c r="E131" s="7" t="n"/>
+      <c r="F131" s="138" t="n"/>
+      <c r="G131" s="101" t="n"/>
+      <c r="H131" s="102" t="n"/>
+      <c r="I131" s="102" t="n"/>
+      <c r="J131" s="102" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="61" t="n"/>
-      <c r="B132" s="62" t="inlineStr">
+      <c r="A132" s="29" t="n"/>
+      <c r="B132" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C132" s="66" t="inlineStr">
+      <c r="C132" s="31" t="inlineStr">
         <is>
           <t>Villainous Reputation</t>
         </is>
       </c>
-      <c r="D132" s="95" t="inlineStr">
+      <c r="D132" s="91" t="inlineStr">
         <is>
           <t>Discard 1 whenever any Whistle triggers</t>
         </is>
       </c>
-      <c r="E132" s="68" t="n"/>
-      <c r="F132" s="140" t="n"/>
-      <c r="G132" s="126" t="inlineStr">
+      <c r="E132" s="7" t="n"/>
+      <c r="F132" s="138" t="n"/>
+      <c r="G132" s="101" t="inlineStr">
         <is>
           <t>Discarded during play, it attaches to a random player — possibly you again</t>
         </is>
       </c>
+      <c r="H132" s="102" t="n"/>
+      <c r="I132" s="102" t="n"/>
+      <c r="J132" s="102" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="61" t="n"/>
-      <c r="B133" s="62" t="inlineStr">
+      <c r="A133" s="29" t="n"/>
+      <c r="B133" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C133" s="66" t="inlineStr">
+      <c r="C133" s="31" t="inlineStr">
         <is>
           <t>Free Agent</t>
         </is>
       </c>
-      <c r="D133" s="95" t="inlineStr">
+      <c r="D133" s="91" t="inlineStr">
         <is>
           <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
-      <c r="E133" s="68" t="n"/>
-      <c r="F133" s="140" t="n"/>
-      <c r="G133" s="126" t="inlineStr">
+      <c r="E133" s="7" t="n"/>
+      <c r="F133" s="138" t="n"/>
+      <c r="G133" s="101" t="inlineStr">
         <is>
           <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
         </is>
       </c>
+      <c r="H133" s="102" t="n"/>
+      <c r="I133" s="102" t="n"/>
+      <c r="J133" s="102" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="61" t="n"/>
-      <c r="B134" s="62" t="inlineStr">
+      <c r="A134" s="29" t="n"/>
+      <c r="B134" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C134" s="66" t="inlineStr">
+      <c r="C134" s="31" t="inlineStr">
         <is>
           <t>Franchise Player</t>
         </is>
       </c>
-      <c r="D134" s="95" t="inlineStr">
+      <c r="D134" s="91" t="inlineStr">
         <is>
           <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
         </is>
       </c>
-      <c r="E134" s="68" t="n"/>
-      <c r="F134" s="140" t="n"/>
-      <c r="G134" s="126" t="n"/>
-      <c r="H134" s="117" t="n"/>
-      <c r="I134" s="117" t="n"/>
-      <c r="J134" s="117" t="n"/>
+      <c r="E134" s="7" t="n"/>
+      <c r="F134" s="138" t="n"/>
+      <c r="G134" s="101" t="n"/>
+      <c r="H134" s="102" t="n"/>
+      <c r="I134" s="102" t="n"/>
+      <c r="J134" s="102" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="61" t="n"/>
-      <c r="B135" s="62" t="inlineStr">
+      <c r="A135" s="35" t="n"/>
+      <c r="B135" s="36" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C135" s="66" t="inlineStr">
+      <c r="C135" s="152" t="inlineStr">
         <is>
           <t>Fundamentalist</t>
         </is>
       </c>
-      <c r="D135" s="95" t="inlineStr">
+      <c r="D135" s="161" t="inlineStr">
         <is>
           <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent</t>
         </is>
       </c>
-      <c r="E135" s="68" t="n"/>
-      <c r="F135" s="140" t="n"/>
-      <c r="G135" s="126" t="n"/>
-      <c r="H135" s="117" t="n"/>
-      <c r="I135" s="117" t="n"/>
-      <c r="J135" s="117" t="n"/>
+      <c r="E135" s="154" t="n"/>
+      <c r="F135" s="159" t="n"/>
+      <c r="G135" s="156" t="n"/>
+      <c r="H135" s="151" t="n"/>
+      <c r="I135" s="151" t="n"/>
+      <c r="J135" s="151" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="122">

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2708,7 +2708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2785,35 +2785,35 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$135,"Pass")</f>
+        <f>COUNTIF($B$5:$B$136,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$135,"Move")+COUNTIF($B$5:$B$135,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$136,"Move")+COUNTIF($B$5:$B$136,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$135,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$136,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$135,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$136,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$135,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$136,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$135,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$136,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$135,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$136,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$135,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$136,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="19" t="n"/>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="B5" s="145">
-        <f>COUNTIF($B$6:$B$135,"Pass")</f>
+        <f>COUNTIF($B$6:$B$136,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="146" t="n"/>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="B21" s="145">
-        <f>COUNTIF($B$22:$B$135,"Move")+COUNTIF($B$22:$B$135,"Special Move")</f>
+        <f>COUNTIF($B$22:$B$136,"Move")+COUNTIF($B$22:$B$136,"Special Move")</f>
         <v/>
       </c>
       <c r="C21" s="146" t="n"/>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="B35" s="145">
-        <f>COUNTIF($B$36:$B$135,"Special Move")</f>
+        <f>COUNTIF($B$36:$B$136,"Special Move")</f>
         <v/>
       </c>
       <c r="C35" s="146" t="n"/>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="B49" s="145">
-        <f>COUNTIF($B$50:$B$135,"Clamp")</f>
+        <f>COUNTIF($B$50:$B$136,"Clamp")</f>
         <v/>
       </c>
       <c r="C49" s="146" t="n"/>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="B55" s="145">
-        <f>COUNTIF($B$56:$B$135,"Whistle")</f>
+        <f>COUNTIF($B$56:$B$136,"Whistle")</f>
         <v/>
       </c>
       <c r="C55" s="146" t="n"/>
@@ -4747,130 +4747,128 @@
       <c r="J72" s="102" t="n"/>
     </row>
     <row r="73" ht="28" customHeight="1" s="132">
-      <c r="A73" s="35" t="n"/>
-      <c r="B73" s="36" t="inlineStr">
+      <c r="A73" s="29" t="n"/>
+      <c r="B73" s="30" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C73" s="37" t="inlineStr">
+      <c r="C73" s="32" t="inlineStr">
         <is>
           <t>Play-On</t>
         </is>
       </c>
-      <c r="D73" s="38" t="inlineStr">
+      <c r="D73" s="33" t="inlineStr">
         <is>
           <t>Discard each Game Break drawn and draw again, until a card is not one</t>
         </is>
       </c>
-      <c r="E73" s="158" t="n"/>
-      <c r="F73" s="159" t="n"/>
-      <c r="G73" s="150" t="inlineStr">
+      <c r="E73" s="34" t="n"/>
+      <c r="F73" s="138" t="n"/>
+      <c r="G73" s="107" t="inlineStr">
         <is>
           <t>Raised where the Break lands, like Cleared to Play — nobody plays a Break</t>
         </is>
       </c>
-      <c r="H73" s="151" t="n"/>
-      <c r="I73" s="151" t="n"/>
-      <c r="J73" s="151" t="n"/>
+      <c r="H73" s="102" t="n"/>
+      <c r="I73" s="102" t="n"/>
+      <c r="J73" s="102" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1" s="132">
-      <c r="A74" s="144" t="inlineStr">
+      <c r="A74" s="35" t="n"/>
+      <c r="B74" s="36" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C74" s="37" t="inlineStr">
+        <is>
+          <t>Crew Chief Review</t>
+        </is>
+      </c>
+      <c r="D74" s="38" t="inlineStr">
+        <is>
+          <t>Cancel a pass. The ball comes to you</t>
+        </is>
+      </c>
+      <c r="E74" s="158" t="n"/>
+      <c r="F74" s="159" t="n"/>
+      <c r="G74" s="150" t="n"/>
+      <c r="H74" s="151" t="n"/>
+      <c r="I74" s="151" t="n"/>
+      <c r="J74" s="151" t="n"/>
+    </row>
+    <row r="75" ht="28" customHeight="1" s="132">
+      <c r="A75" s="144" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B74" s="145">
-        <f>COUNTIF($B$75:$B$135,"Game Break")</f>
+      <c r="B75" s="145">
+        <f>COUNTIF($B$76:$B$136,"Game Break")</f>
         <v/>
       </c>
-      <c r="C74" s="146" t="n"/>
-      <c r="D74" s="146" t="n"/>
-      <c r="E74" s="146" t="n"/>
-      <c r="F74" s="147" t="n"/>
-      <c r="G74" s="148" t="n"/>
-      <c r="H74" s="149" t="n"/>
-      <c r="I74" s="149" t="n"/>
-      <c r="J74" s="149" t="n"/>
-    </row>
-    <row r="75" ht="28" customHeight="1" s="132">
-      <c r="A75" s="29" t="n"/>
-      <c r="B75" s="30" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C75" s="32" t="inlineStr">
-        <is>
-          <t>2-Minute Warning</t>
-        </is>
-      </c>
-      <c r="D75" s="33" t="inlineStr">
-        <is>
-          <t>All players discard down to 2 or fewer cards</t>
-        </is>
-      </c>
-      <c r="E75" s="34" t="n"/>
-      <c r="F75" s="75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" s="107" t="n"/>
-      <c r="H75" s="102" t="n"/>
-      <c r="I75" s="102" t="n"/>
-      <c r="J75" s="102" t="n"/>
-    </row>
-    <row r="76" ht="42" customHeight="1" s="132">
+      <c r="C75" s="146" t="n"/>
+      <c r="D75" s="146" t="n"/>
+      <c r="E75" s="146" t="n"/>
+      <c r="F75" s="147" t="n"/>
+      <c r="G75" s="148" t="n"/>
+      <c r="H75" s="149" t="n"/>
+      <c r="I75" s="149" t="n"/>
+      <c r="J75" s="149" t="n"/>
+    </row>
+    <row r="76" ht="28" customHeight="1" s="132">
       <c r="A76" s="29" t="n"/>
       <c r="B76" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C76" s="31" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G76" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
+        </is>
+      </c>
+      <c r="D76" s="33" t="inlineStr">
+        <is>
+          <t>All players discard down to 2 or fewer cards</t>
+        </is>
+      </c>
+      <c r="E76" s="34" t="n"/>
+      <c r="F76" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="107" t="n"/>
       <c r="H76" s="102" t="n"/>
       <c r="I76" s="102" t="n"/>
       <c r="J76" s="102" t="n"/>
     </row>
-    <row r="77" ht="28" customHeight="1" s="132">
+    <row r="77" ht="42" customHeight="1" s="132">
       <c r="A77" s="29" t="n"/>
       <c r="B77" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D77" s="33" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E77" s="34" t="n"/>
-      <c r="F77" s="75" t="n">
-        <v>14</v>
-      </c>
-      <c r="G77" s="107" t="n"/>
+      <c r="C77" s="31" t="inlineStr">
+        <is>
+          <t>Benched</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Immediately give ball to any other player.</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H77" s="102" t="n"/>
       <c r="I77" s="102" t="n"/>
       <c r="J77" s="102" t="n"/>
@@ -4882,213 +4880,213 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C78" s="31" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="n"/>
-      <c r="F78" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G78" s="101" t="n"/>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
+        </is>
+      </c>
+      <c r="D78" s="33" t="inlineStr">
+        <is>
+          <t>Discard 1 card.</t>
+        </is>
+      </c>
+      <c r="E78" s="34" t="n"/>
+      <c r="F78" s="75" t="n">
+        <v>14</v>
+      </c>
+      <c r="G78" s="107" t="n"/>
       <c r="H78" s="102" t="n"/>
       <c r="I78" s="102" t="n"/>
       <c r="J78" s="102" t="n"/>
     </row>
-    <row r="79" ht="20" customHeight="1" s="132">
+    <row r="79" ht="28" customHeight="1" s="132">
       <c r="A79" s="29" t="n"/>
       <c r="B79" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C79" s="90" t="inlineStr">
-        <is>
-          <t>Foul</t>
-        </is>
-      </c>
-      <c r="D79" s="33" t="inlineStr">
-        <is>
-          <t>Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E79" s="34" t="n"/>
-      <c r="F79" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G79" s="107" t="n"/>
+      <c r="C79" s="31" t="inlineStr">
+        <is>
+          <t>Designed Play</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Draw up to a hand of 5</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="G79" s="101" t="n"/>
       <c r="H79" s="102" t="n"/>
       <c r="I79" s="102" t="n"/>
       <c r="J79" s="102" t="n"/>
     </row>
-    <row r="80" ht="28" customHeight="1" s="132">
+    <row r="80" ht="20" customHeight="1" s="132">
       <c r="A80" s="29" t="n"/>
       <c r="B80" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C80" s="31" t="inlineStr">
-        <is>
-          <t>MVP Vote</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards up to a hand of 7</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="n"/>
-      <c r="F80" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="101" t="n"/>
+      <c r="C80" s="90" t="inlineStr">
+        <is>
+          <t>Foul</t>
+        </is>
+      </c>
+      <c r="D80" s="33" t="inlineStr">
+        <is>
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E80" s="34" t="n"/>
+      <c r="F80" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" s="107" t="n"/>
       <c r="H80" s="102" t="n"/>
       <c r="I80" s="102" t="n"/>
       <c r="J80" s="102" t="n"/>
     </row>
-    <row r="81" ht="20" customHeight="1" s="132">
+    <row r="81" ht="28" customHeight="1" s="132">
       <c r="A81" s="29" t="n"/>
       <c r="B81" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>Off Night</t>
-        </is>
-      </c>
-      <c r="D81" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this possession</t>
-        </is>
-      </c>
-      <c r="E81" s="34" t="n"/>
-      <c r="F81" s="75" t="n">
-        <v>3</v>
-      </c>
-      <c r="G81" s="107" t="n"/>
+      <c r="C81" s="31" t="inlineStr">
+        <is>
+          <t>MVP Vote</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Draw 3 cards up to a hand of 7</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="101" t="n"/>
       <c r="H81" s="102" t="n"/>
       <c r="I81" s="102" t="n"/>
       <c r="J81" s="102" t="n"/>
     </row>
-    <row r="82" ht="42" customHeight="1" s="132">
+    <row r="82" ht="20" customHeight="1" s="132">
       <c r="A82" s="29" t="n"/>
       <c r="B82" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C82" s="31" t="inlineStr">
-        <is>
-          <t>Swallowed Whistle</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F82" s="74" t="n">
-        <v>5</v>
-      </c>
-      <c r="G82" s="101" t="n"/>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D82" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E82" s="34" t="n"/>
+      <c r="F82" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" s="107" t="n"/>
       <c r="H82" s="102" t="n"/>
       <c r="I82" s="102" t="n"/>
       <c r="J82" s="102" t="n"/>
     </row>
-    <row r="83" ht="28" customHeight="1" s="132">
+    <row r="83" ht="42" customHeight="1" s="132">
       <c r="A83" s="29" t="n"/>
       <c r="B83" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C83" s="32" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
-        </is>
-      </c>
-      <c r="D83" s="33" t="inlineStr">
-        <is>
-          <t>Players cannot shoot when SHOT is 50% or higher</t>
-        </is>
-      </c>
-      <c r="E83" s="33" t="inlineStr">
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>Remains for remainder of round</t>
         </is>
       </c>
-      <c r="F83" s="80" t="n">
-        <v>4</v>
-      </c>
-      <c r="G83" s="107" t="n"/>
+      <c r="F83" s="74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" s="101" t="n"/>
       <c r="H83" s="102" t="n"/>
       <c r="I83" s="102" t="n"/>
       <c r="J83" s="102" t="n"/>
     </row>
-    <row r="84" ht="56" customHeight="1" s="132">
+    <row r="84" ht="28" customHeight="1" s="132">
       <c r="A84" s="29" t="n"/>
       <c r="B84" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C84" s="31" t="inlineStr">
-        <is>
-          <t>Traded Mid-Game</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>Swap positions with random other player</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="n"/>
-      <c r="F84" s="76" t="n"/>
-      <c r="G84" s="111" t="inlineStr">
-        <is>
-          <t>Applies to rest of game</t>
-        </is>
-      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D84" s="33" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is 50% or higher</t>
+        </is>
+      </c>
+      <c r="E84" s="33" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F84" s="80" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" s="107" t="n"/>
       <c r="H84" s="102" t="n"/>
       <c r="I84" s="102" t="n"/>
       <c r="J84" s="102" t="n"/>
     </row>
-    <row r="85" ht="42" customHeight="1" s="132">
+    <row r="85" ht="56" customHeight="1" s="132">
       <c r="A85" s="29" t="n"/>
       <c r="B85" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C85" s="134" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D85" s="91" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
+      <c r="C85" s="31" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Swap positions with random other player</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
-      <c r="F85" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G85" s="111" t="n"/>
+      <c r="F85" s="76" t="n"/>
+      <c r="G85" s="111" t="inlineStr">
+        <is>
+          <t>Applies to rest of game</t>
+        </is>
+      </c>
       <c r="H85" s="102" t="n"/>
       <c r="I85" s="102" t="n"/>
       <c r="J85" s="102" t="n"/>
@@ -5102,28 +5100,24 @@
       </c>
       <c r="C86" s="134" t="inlineStr">
         <is>
-          <t>All-Swissh Selection</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D86" s="91" t="inlineStr">
         <is>
-          <t>Draw 3 cards after your next make</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
       <c r="F86" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G86" s="111" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G86" s="111" t="n"/>
       <c r="H86" s="102" t="n"/>
       <c r="I86" s="102" t="n"/>
       <c r="J86" s="102" t="n"/>
     </row>
-    <row r="87" ht="28" customHeight="1" s="132">
+    <row r="87" ht="42" customHeight="1" s="132">
       <c r="A87" s="29" t="n"/>
       <c r="B87" s="30" t="inlineStr">
         <is>
@@ -5132,19 +5126,23 @@
       </c>
       <c r="C87" s="134" t="inlineStr">
         <is>
-          <t>All Star Selection</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D87" s="91" t="inlineStr">
         <is>
-          <t>Draw 2 cards</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G87" s="111" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G87" s="111" t="inlineStr">
+        <is>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
+        </is>
+      </c>
       <c r="H87" s="102" t="n"/>
       <c r="I87" s="102" t="n"/>
       <c r="J87" s="102" t="n"/>
@@ -5158,28 +5156,24 @@
       </c>
       <c r="C88" s="134" t="inlineStr">
         <is>
-          <t>Hit the Bike</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D88" s="91" t="inlineStr">
         <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G88" s="111" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="G88" s="111" t="n"/>
       <c r="H88" s="102" t="n"/>
       <c r="I88" s="102" t="n"/>
       <c r="J88" s="102" t="n"/>
     </row>
-    <row r="89" ht="56" customHeight="1" s="132">
+    <row r="89" ht="28" customHeight="1" s="132">
       <c r="A89" s="29" t="n"/>
       <c r="B89" s="30" t="inlineStr">
         <is>
@@ -5188,19 +5182,23 @@
       </c>
       <c r="C89" s="134" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D89" s="91" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="G89" s="111" t="n"/>
+      <c r="G89" s="111" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H89" s="102" t="n"/>
       <c r="I89" s="102" t="n"/>
       <c r="J89" s="102" t="n"/>
@@ -5214,28 +5212,24 @@
       </c>
       <c r="C90" s="134" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D90" s="91" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G90" s="111" t="inlineStr">
-        <is>
-          <t>Deck ones are shown face down</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G90" s="111" t="n"/>
       <c r="H90" s="102" t="n"/>
       <c r="I90" s="102" t="n"/>
       <c r="J90" s="102" t="n"/>
     </row>
-    <row r="91" ht="28" customHeight="1" s="132">
+    <row r="91" ht="56" customHeight="1" s="132">
       <c r="A91" s="29" t="n"/>
       <c r="B91" s="30" t="inlineStr">
         <is>
@@ -5244,28 +5238,28 @@
       </c>
       <c r="C91" s="134" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D91" s="91" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G91" s="111" t="inlineStr">
         <is>
-          <t>This is a bad thing in the NBA</t>
+          <t>Deck ones are shown face down</t>
         </is>
       </c>
       <c r="H91" s="102" t="n"/>
       <c r="I91" s="102" t="n"/>
       <c r="J91" s="102" t="n"/>
     </row>
-    <row r="92" ht="42" customHeight="1" s="132">
+    <row r="92" ht="28" customHeight="1" s="132">
       <c r="A92" s="29" t="n"/>
       <c r="B92" s="30" t="inlineStr">
         <is>
@@ -5274,12 +5268,12 @@
       </c>
       <c r="C92" s="134" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D92" s="91" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
@@ -5288,14 +5282,14 @@
       </c>
       <c r="G92" s="111" t="inlineStr">
         <is>
-          <t>The hex travels in the declared direction too</t>
+          <t>This is a bad thing in the NBA</t>
         </is>
       </c>
       <c r="H92" s="102" t="n"/>
       <c r="I92" s="102" t="n"/>
       <c r="J92" s="102" t="n"/>
     </row>
-    <row r="93" ht="28" customHeight="1" s="132">
+    <row r="93" ht="42" customHeight="1" s="132">
       <c r="A93" s="29" t="n"/>
       <c r="B93" s="30" t="inlineStr">
         <is>
@@ -5304,24 +5298,28 @@
       </c>
       <c r="C93" s="134" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D93" s="91" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G93" s="111" t="n"/>
+      <c r="G93" s="111" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H93" s="102" t="n"/>
       <c r="I93" s="102" t="n"/>
       <c r="J93" s="102" t="n"/>
     </row>
-    <row r="94" ht="42" customHeight="1" s="132">
+    <row r="94" ht="28" customHeight="1" s="132">
       <c r="A94" s="29" t="n"/>
       <c r="B94" s="30" t="inlineStr">
         <is>
@@ -5330,24 +5328,24 @@
       </c>
       <c r="C94" s="134" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D94" s="91" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G94" s="111" t="n"/>
       <c r="H94" s="102" t="n"/>
       <c r="I94" s="102" t="n"/>
       <c r="J94" s="102" t="n"/>
     </row>
-    <row r="95" ht="14" customHeight="1" s="132">
+    <row r="95" ht="42" customHeight="1" s="132">
       <c r="A95" s="29" t="n"/>
       <c r="B95" s="30" t="inlineStr">
         <is>
@@ -5356,17 +5354,17 @@
       </c>
       <c r="C95" s="134" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Official Timeout</t>
         </is>
       </c>
       <c r="D95" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G95" s="111" t="n"/>
       <c r="H95" s="102" t="n"/>
@@ -5382,17 +5380,17 @@
       </c>
       <c r="C96" s="134" t="inlineStr">
         <is>
-          <t>Altercation</t>
+          <t>Team Doctor</t>
         </is>
       </c>
       <c r="D96" s="91" t="inlineStr">
         <is>
-          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G96" s="111" t="n"/>
       <c r="H96" s="102" t="n"/>
@@ -5408,17 +5406,17 @@
       </c>
       <c r="C97" s="134" t="inlineStr">
         <is>
-          <t>Huge Altercation</t>
+          <t>Altercation</t>
         </is>
       </c>
       <c r="D97" s="91" t="inlineStr">
         <is>
-          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
+          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G97" s="111" t="n"/>
       <c r="H97" s="102" t="n"/>
@@ -5434,17 +5432,17 @@
       </c>
       <c r="C98" s="134" t="inlineStr">
         <is>
-          <t>Home Court Advantage</t>
+          <t>Huge Altercation</t>
         </is>
       </c>
       <c r="D98" s="91" t="inlineStr">
         <is>
-          <t>SHOT + 10%</t>
+          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G98" s="111" t="n"/>
       <c r="H98" s="102" t="n"/>
@@ -5460,12 +5458,12 @@
       </c>
       <c r="C99" s="134" t="inlineStr">
         <is>
-          <t>Away Game</t>
+          <t>Home Court Advantage</t>
         </is>
       </c>
       <c r="D99" s="91" t="inlineStr">
         <is>
-          <t>SHOT - 10%</t>
+          <t>SHOT + 10%</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -5486,23 +5484,19 @@
       </c>
       <c r="C100" s="134" t="inlineStr">
         <is>
-          <t>Mic'd Up</t>
+          <t>Away Game</t>
         </is>
       </c>
       <c r="D100" s="91" t="inlineStr">
         <is>
-          <t>SHOT + 10% until passed or shot</t>
+          <t>SHOT - 10%</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="76" t="n">
-        <v>7</v>
-      </c>
-      <c r="G100" s="111" t="inlineStr">
-        <is>
-          <t>The boost is the holder's alone and does not travel with a pass</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G100" s="111" t="n"/>
       <c r="H100" s="102" t="n"/>
       <c r="I100" s="102" t="n"/>
       <c r="J100" s="102" t="n"/>
@@ -5516,19 +5510,23 @@
       </c>
       <c r="C101" s="134" t="inlineStr">
         <is>
-          <t>In The Zone</t>
+          <t>Mic'd Up</t>
         </is>
       </c>
       <c r="D101" s="91" t="inlineStr">
         <is>
-          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+          <t>SHOT + 10% until passed or shot</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G101" s="111" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="G101" s="111" t="inlineStr">
+        <is>
+          <t>The boost is the holder's alone and does not travel with a pass</t>
+        </is>
+      </c>
       <c r="H101" s="102" t="n"/>
       <c r="I101" s="102" t="n"/>
       <c r="J101" s="102" t="n"/>
@@ -5542,12 +5540,12 @@
       </c>
       <c r="C102" s="134" t="inlineStr">
         <is>
-          <t>Role Player</t>
+          <t>In The Zone</t>
         </is>
       </c>
       <c r="D102" s="91" t="inlineStr">
         <is>
-          <t>All other players draw 1 card</t>
+          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -5560,262 +5558,260 @@
       <c r="J102" s="102" t="n"/>
     </row>
     <row r="103" ht="14" customHeight="1" s="132">
-      <c r="A103" s="35" t="n"/>
-      <c r="B103" s="36" t="inlineStr">
+      <c r="A103" s="29" t="n"/>
+      <c r="B103" s="30" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C103" s="160" t="inlineStr">
+      <c r="C103" s="134" t="inlineStr">
+        <is>
+          <t>Role Player</t>
+        </is>
+      </c>
+      <c r="D103" s="91" t="inlineStr">
+        <is>
+          <t>All other players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="n"/>
+      <c r="F103" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="G103" s="111" t="n"/>
+      <c r="H103" s="102" t="n"/>
+      <c r="I103" s="102" t="n"/>
+      <c r="J103" s="102" t="n"/>
+    </row>
+    <row r="104" ht="14" customHeight="1" s="132">
+      <c r="A104" s="35" t="n"/>
+      <c r="B104" s="36" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C104" s="160" t="inlineStr">
         <is>
           <t>Back-and-Forth Game</t>
         </is>
       </c>
-      <c r="D103" s="161" t="inlineStr">
+      <c r="D104" s="161" t="inlineStr">
         <is>
           <t>Discard the next 3 Game Breaks. Whoever draws one draws again</t>
         </is>
       </c>
-      <c r="E103" s="154" t="n"/>
-      <c r="F103" s="155" t="n">
+      <c r="E104" s="154" t="n"/>
+      <c r="F104" s="155" t="n">
         <v>3</v>
       </c>
-      <c r="G103" s="162" t="n"/>
-      <c r="H103" s="151" t="n"/>
-      <c r="I103" s="151" t="n"/>
-      <c r="J103" s="151" t="n"/>
-    </row>
-    <row r="104" ht="28" customHeight="1" s="132">
-      <c r="A104" s="144" t="inlineStr">
+      <c r="G104" s="162" t="n"/>
+      <c r="H104" s="151" t="n"/>
+      <c r="I104" s="151" t="n"/>
+      <c r="J104" s="151" t="n"/>
+    </row>
+    <row r="105" ht="28" customHeight="1" s="132">
+      <c r="A105" s="144" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="B104" s="145">
-        <f>COUNTIF($B$105:$B$135,"Injury GB")</f>
+      <c r="B105" s="145">
+        <f>COUNTIF($B$106:$B$136,"Injury GB")</f>
         <v/>
       </c>
-      <c r="C104" s="146" t="n"/>
-      <c r="D104" s="146" t="n"/>
-      <c r="E104" s="146" t="n"/>
-      <c r="F104" s="147" t="n"/>
-      <c r="G104" s="148" t="n"/>
-      <c r="H104" s="149" t="n"/>
-      <c r="I104" s="149" t="n"/>
-      <c r="J104" s="149" t="n"/>
-    </row>
-    <row r="105" ht="28" customHeight="1" s="132">
-      <c r="A105" s="35" t="n"/>
-      <c r="B105" s="36" t="inlineStr">
+      <c r="C105" s="146" t="n"/>
+      <c r="D105" s="146" t="n"/>
+      <c r="E105" s="146" t="n"/>
+      <c r="F105" s="147" t="n"/>
+      <c r="G105" s="148" t="n"/>
+      <c r="H105" s="149" t="n"/>
+      <c r="I105" s="149" t="n"/>
+      <c r="J105" s="149" t="n"/>
+    </row>
+    <row r="106" ht="28" customHeight="1" s="132">
+      <c r="A106" s="35" t="n"/>
+      <c r="B106" s="36" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="C105" s="152" t="inlineStr">
+      <c r="C106" s="152" t="inlineStr">
         <is>
           <t>Bone Bruise</t>
         </is>
       </c>
-      <c r="D105" s="161" t="inlineStr">
+      <c r="D106" s="161" t="inlineStr">
         <is>
           <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
         </is>
       </c>
-      <c r="E105" s="154" t="n"/>
-      <c r="F105" s="155" t="n">
+      <c r="E106" s="154" t="n"/>
+      <c r="F106" s="155" t="n">
         <v>3</v>
       </c>
-      <c r="G105" s="156" t="n"/>
-      <c r="H105" s="151" t="n"/>
-      <c r="I105" s="151" t="n"/>
-      <c r="J105" s="151" t="n"/>
-    </row>
-    <row r="106" ht="28" customHeight="1" s="132">
-      <c r="A106" s="144" t="inlineStr">
+      <c r="G106" s="156" t="n"/>
+      <c r="H106" s="151" t="n"/>
+      <c r="I106" s="151" t="n"/>
+      <c r="J106" s="151" t="n"/>
+    </row>
+    <row r="107" ht="28" customHeight="1" s="132">
+      <c r="A107" s="144" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="B106" s="145">
-        <f>COUNTIF($B$107:$B$135,"Devastating Injury GB")</f>
+      <c r="B107" s="145">
+        <f>COUNTIF($B$108:$B$136,"Devastating Injury GB")</f>
         <v/>
       </c>
-      <c r="C106" s="146" t="n"/>
-      <c r="D106" s="146" t="n"/>
-      <c r="E106" s="146" t="n"/>
-      <c r="F106" s="147" t="n"/>
-      <c r="G106" s="148" t="n"/>
-      <c r="H106" s="149" t="n"/>
-      <c r="I106" s="149" t="n"/>
-      <c r="J106" s="149" t="n"/>
-    </row>
-    <row r="107" ht="28" customHeight="1" s="132">
-      <c r="A107" s="35" t="n"/>
-      <c r="B107" s="36" t="inlineStr">
+      <c r="C107" s="146" t="n"/>
+      <c r="D107" s="146" t="n"/>
+      <c r="E107" s="146" t="n"/>
+      <c r="F107" s="147" t="n"/>
+      <c r="G107" s="148" t="n"/>
+      <c r="H107" s="149" t="n"/>
+      <c r="I107" s="149" t="n"/>
+      <c r="J107" s="149" t="n"/>
+    </row>
+    <row r="108" ht="28" customHeight="1" s="132">
+      <c r="A108" s="35" t="n"/>
+      <c r="B108" s="36" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="C107" s="163" t="inlineStr">
+      <c r="C108" s="163" t="inlineStr">
         <is>
           <t>Torn Achilles</t>
         </is>
       </c>
-      <c r="D107" s="164" t="inlineStr">
+      <c r="D108" s="164" t="inlineStr">
         <is>
           <t>Hand is locked every turn except 1 card (randomly)</t>
         </is>
       </c>
-      <c r="E107" s="154" t="n"/>
-      <c r="F107" s="159" t="n"/>
-      <c r="G107" s="156" t="n"/>
-      <c r="H107" s="151" t="n"/>
-      <c r="I107" s="151" t="n"/>
-      <c r="J107" s="151" t="n"/>
-    </row>
-    <row r="108" ht="42" customHeight="1" s="132">
-      <c r="A108" s="144" t="inlineStr">
+      <c r="E108" s="154" t="n"/>
+      <c r="F108" s="159" t="n"/>
+      <c r="G108" s="156" t="n"/>
+      <c r="H108" s="151" t="n"/>
+      <c r="I108" s="151" t="n"/>
+      <c r="J108" s="151" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1" s="132">
+      <c r="A109" s="144" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B108" s="145">
-        <f>COUNTIF($B$109:$B$135,"Intangible")</f>
+      <c r="B109" s="145">
+        <f>COUNTIF($B$110:$B$136,"Intangible")</f>
         <v/>
       </c>
-      <c r="C108" s="146" t="n"/>
-      <c r="D108" s="146" t="n"/>
-      <c r="E108" s="146" t="n"/>
-      <c r="F108" s="147" t="n"/>
-      <c r="G108" s="148" t="n"/>
-      <c r="H108" s="149" t="n"/>
-      <c r="I108" s="149" t="n"/>
-      <c r="J108" s="149" t="n"/>
-    </row>
-    <row r="109" ht="56" customHeight="1" s="132">
-      <c r="A109" s="96" t="inlineStr">
+      <c r="C109" s="146" t="n"/>
+      <c r="D109" s="146" t="n"/>
+      <c r="E109" s="146" t="n"/>
+      <c r="F109" s="147" t="n"/>
+      <c r="G109" s="148" t="n"/>
+      <c r="H109" s="149" t="n"/>
+      <c r="I109" s="149" t="n"/>
+      <c r="J109" s="149" t="n"/>
+    </row>
+    <row r="110" ht="56" customHeight="1" s="132">
+      <c r="A110" s="96" t="inlineStr">
         <is>
           <t>All intangibles are limited to 1</t>
         </is>
       </c>
-      <c r="B109" s="30" t="inlineStr">
+      <c r="B110" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C109" s="31" t="inlineStr">
+      <c r="C110" s="31" t="inlineStr">
         <is>
           <t>Board-Crasher</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>SHOT +10% upon Rebounding your own missed shot</t>
         </is>
       </c>
-      <c r="E109" s="7" t="n"/>
-      <c r="F109" s="138" t="n"/>
-      <c r="G109" s="101" t="n"/>
-      <c r="H109" s="102" t="n"/>
-      <c r="I109" s="102" t="n"/>
-      <c r="J109" s="102" t="n"/>
-    </row>
-    <row r="110" ht="57" customHeight="1" s="132">
-      <c r="A110" s="29" t="n"/>
-      <c r="B110" s="30" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C110" s="32" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D110" s="33" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E110" s="34" t="n"/>
+      <c r="E110" s="7" t="n"/>
       <c r="F110" s="138" t="n"/>
-      <c r="G110" s="107" t="n"/>
+      <c r="G110" s="101" t="n"/>
       <c r="H110" s="102" t="n"/>
       <c r="I110" s="102" t="n"/>
       <c r="J110" s="102" t="n"/>
     </row>
-    <row r="111" ht="20" customHeight="1" s="132">
+    <row r="111" ht="57" customHeight="1" s="132">
       <c r="A111" s="29" t="n"/>
       <c r="B111" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C111" s="31" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="n"/>
+      <c r="C111" s="32" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D111" s="33" t="inlineStr">
+        <is>
+          <t>Additional SHOT +10% on all received passes</t>
+        </is>
+      </c>
+      <c r="E111" s="34" t="n"/>
       <c r="F111" s="138" t="n"/>
-      <c r="G111" s="101" t="n"/>
+      <c r="G111" s="107" t="n"/>
       <c r="H111" s="102" t="n"/>
       <c r="I111" s="102" t="n"/>
       <c r="J111" s="102" t="n"/>
     </row>
-    <row r="112" ht="28" customHeight="1" s="132">
+    <row r="112" ht="20" customHeight="1" s="132">
       <c r="A112" s="29" t="n"/>
       <c r="B112" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C112" s="32" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D112" s="33" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
-        </is>
-      </c>
-      <c r="E112" s="34" t="n"/>
+      <c r="C112" s="31" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="n"/>
       <c r="F112" s="138" t="n"/>
-      <c r="G112" s="107" t="n"/>
+      <c r="G112" s="101" t="n"/>
       <c r="H112" s="102" t="n"/>
       <c r="I112" s="102" t="n"/>
       <c r="J112" s="102" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" ht="28" customHeight="1" s="132">
       <c r="A113" s="29" t="n"/>
       <c r="B113" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C113" s="31" t="inlineStr">
-        <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F113" s="139" t="n"/>
-      <c r="G113" s="101" t="n"/>
+      <c r="C113" s="32" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D113" s="33" t="inlineStr">
+        <is>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
+        </is>
+      </c>
+      <c r="E113" s="34" t="n"/>
+      <c r="F113" s="138" t="n"/>
+      <c r="G113" s="107" t="n"/>
       <c r="H113" s="102" t="n"/>
       <c r="I113" s="102" t="n"/>
       <c r="J113" s="102" t="n"/>
@@ -5827,19 +5823,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C114" s="90" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D114" s="94" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E114" s="34" t="n"/>
-      <c r="F114" s="138" t="n"/>
-      <c r="G114" s="125" t="n"/>
+      <c r="C114" s="31" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F114" s="139" t="n"/>
+      <c r="G114" s="101" t="n"/>
       <c r="H114" s="102" t="n"/>
       <c r="I114" s="102" t="n"/>
       <c r="J114" s="102" t="n"/>
@@ -5853,17 +5853,17 @@
       </c>
       <c r="C115" s="90" t="inlineStr">
         <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D115" s="91" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="n"/>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D115" s="94" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
+        </is>
+      </c>
+      <c r="E115" s="34" t="n"/>
       <c r="F115" s="138" t="n"/>
-      <c r="G115" s="101" t="n"/>
+      <c r="G115" s="125" t="n"/>
       <c r="H115" s="102" t="n"/>
       <c r="I115" s="102" t="n"/>
       <c r="J115" s="102" t="n"/>
@@ -5875,19 +5875,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C116" s="32" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D116" s="33" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E116" s="34" t="n"/>
+      <c r="C116" s="90" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D116" s="91" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="n"/>
       <c r="F116" s="138" t="n"/>
-      <c r="G116" s="107" t="n"/>
+      <c r="G116" s="101" t="n"/>
       <c r="H116" s="102" t="n"/>
       <c r="I116" s="102" t="n"/>
       <c r="J116" s="102" t="n"/>
@@ -5899,19 +5899,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C117" s="31" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="n"/>
+      <c r="C117" s="32" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="D117" s="33" t="inlineStr">
+        <is>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+        </is>
+      </c>
+      <c r="E117" s="34" t="n"/>
       <c r="F117" s="138" t="n"/>
-      <c r="G117" s="101" t="n"/>
+      <c r="G117" s="107" t="n"/>
       <c r="H117" s="102" t="n"/>
       <c r="I117" s="102" t="n"/>
       <c r="J117" s="102" t="n"/>
@@ -5923,19 +5923,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C118" s="32" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D118" s="33" t="inlineStr">
-        <is>
-          <t>SHOT +20% if you scored last round.</t>
-        </is>
-      </c>
-      <c r="E118" s="34" t="n"/>
+      <c r="C118" s="31" t="inlineStr">
+        <is>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="n"/>
       <c r="F118" s="138" t="n"/>
-      <c r="G118" s="107" t="n"/>
+      <c r="G118" s="101" t="n"/>
       <c r="H118" s="102" t="n"/>
       <c r="I118" s="102" t="n"/>
       <c r="J118" s="102" t="n"/>
@@ -5947,19 +5947,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C119" s="31" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D119" s="91" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="n"/>
+      <c r="C119" s="32" t="inlineStr">
+        <is>
+          <t>Hot Hand</t>
+        </is>
+      </c>
+      <c r="D119" s="33" t="inlineStr">
+        <is>
+          <t>SHOT +20% if you scored last round.</t>
+        </is>
+      </c>
+      <c r="E119" s="34" t="n"/>
       <c r="F119" s="138" t="n"/>
-      <c r="G119" s="101" t="n"/>
+      <c r="G119" s="107" t="n"/>
       <c r="H119" s="102" t="n"/>
       <c r="I119" s="102" t="n"/>
       <c r="J119" s="102" t="n"/>
@@ -5971,23 +5971,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C120" s="32" t="inlineStr">
-        <is>
-          <t>No Bag</t>
-        </is>
-      </c>
-      <c r="D120" s="33" t="inlineStr">
-        <is>
-          <t>Cannot activate Move cards this round</t>
-        </is>
-      </c>
-      <c r="E120" s="34" t="n"/>
+      <c r="C120" s="31" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D120" s="91" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="n"/>
       <c r="F120" s="138" t="n"/>
-      <c r="G120" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G120" s="101" t="n"/>
       <c r="H120" s="102" t="n"/>
       <c r="I120" s="102" t="n"/>
       <c r="J120" s="102" t="n"/>
@@ -5999,19 +5995,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C121" s="31" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="n"/>
+      <c r="C121" s="32" t="inlineStr">
+        <is>
+          <t>No Bag</t>
+        </is>
+      </c>
+      <c r="D121" s="33" t="inlineStr">
+        <is>
+          <t>Cannot activate Move cards this round</t>
+        </is>
+      </c>
+      <c r="E121" s="34" t="n"/>
       <c r="F121" s="138" t="n"/>
-      <c r="G121" s="101" t="n"/>
+      <c r="G121" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H121" s="102" t="n"/>
       <c r="I121" s="102" t="n"/>
       <c r="J121" s="102" t="n"/>
@@ -6023,23 +6023,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C122" s="32" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D122" s="33" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
-        </is>
-      </c>
-      <c r="E122" s="34" t="n"/>
+      <c r="C122" s="31" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="n"/>
       <c r="F122" s="138" t="n"/>
-      <c r="G122" s="113" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G122" s="101" t="n"/>
       <c r="H122" s="102" t="n"/>
       <c r="I122" s="102" t="n"/>
       <c r="J122" s="102" t="n"/>
@@ -6051,19 +6047,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C123" s="31" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="n"/>
+      <c r="C123" s="32" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D123" s="33" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E123" s="34" t="n"/>
       <c r="F123" s="138" t="n"/>
-      <c r="G123" s="101" t="n"/>
+      <c r="G123" s="113" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H123" s="102" t="n"/>
       <c r="I123" s="102" t="n"/>
       <c r="J123" s="102" t="n"/>
@@ -6075,19 +6075,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C124" s="32" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D124" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
-        </is>
-      </c>
-      <c r="E124" s="34" t="n"/>
+      <c r="C124" s="31" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="n"/>
       <c r="F124" s="138" t="n"/>
-      <c r="G124" s="107" t="n"/>
+      <c r="G124" s="101" t="n"/>
       <c r="H124" s="102" t="n"/>
       <c r="I124" s="102" t="n"/>
       <c r="J124" s="102" t="n"/>
@@ -6099,19 +6099,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C125" s="31" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="n"/>
+      <c r="C125" s="32" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D125" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E125" s="34" t="n"/>
       <c r="F125" s="138" t="n"/>
-      <c r="G125" s="101" t="n"/>
+      <c r="G125" s="107" t="n"/>
       <c r="H125" s="102" t="n"/>
       <c r="I125" s="102" t="n"/>
       <c r="J125" s="102" t="n"/>
@@ -6123,19 +6123,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C126" s="32" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D126" s="33" t="inlineStr">
-        <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E126" s="34" t="n"/>
+      <c r="C126" s="31" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="n"/>
       <c r="F126" s="138" t="n"/>
-      <c r="G126" s="107" t="n"/>
+      <c r="G126" s="101" t="n"/>
       <c r="H126" s="102" t="n"/>
       <c r="I126" s="102" t="n"/>
       <c r="J126" s="102" t="n"/>
@@ -6147,19 +6147,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C127" s="31" t="inlineStr">
-        <is>
-          <t>Unguardable</t>
-        </is>
-      </c>
-      <c r="D127" s="91" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="n"/>
+      <c r="C127" s="32" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D127" s="33" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E127" s="34" t="n"/>
       <c r="F127" s="138" t="n"/>
-      <c r="G127" s="101" t="n"/>
+      <c r="G127" s="107" t="n"/>
       <c r="H127" s="102" t="n"/>
       <c r="I127" s="102" t="n"/>
       <c r="J127" s="102" t="n"/>
@@ -6171,23 +6171,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C128" s="32" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D128" s="33" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
-        </is>
-      </c>
-      <c r="E128" s="34" t="n"/>
+      <c r="C128" s="31" t="inlineStr">
+        <is>
+          <t>Unguardable</t>
+        </is>
+      </c>
+      <c r="D128" s="91" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="n"/>
       <c r="F128" s="138" t="n"/>
-      <c r="G128" s="113" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G128" s="101" t="n"/>
       <c r="H128" s="102" t="n"/>
       <c r="I128" s="102" t="n"/>
       <c r="J128" s="102" t="n"/>
@@ -6199,19 +6195,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C129" s="31" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D129" s="91" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="n"/>
+      <c r="C129" s="32" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D129" s="33" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E129" s="34" t="n"/>
       <c r="F129" s="138" t="n"/>
-      <c r="G129" s="101" t="n"/>
+      <c r="G129" s="113" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
       <c r="H129" s="102" t="n"/>
       <c r="I129" s="102" t="n"/>
       <c r="J129" s="102" t="n"/>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="C130" s="31" t="inlineStr">
         <is>
-          <t>Unselfish</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D130" s="91" t="inlineStr">
         <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E130" s="7" t="n"/>
@@ -6249,12 +6249,12 @@
       </c>
       <c r="C131" s="31" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D131" s="91" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E131" s="7" t="n"/>
@@ -6273,21 +6273,17 @@
       </c>
       <c r="C132" s="31" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D132" s="91" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E132" s="7" t="n"/>
       <c r="F132" s="138" t="n"/>
-      <c r="G132" s="101" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="G132" s="101" t="n"/>
       <c r="H132" s="102" t="n"/>
       <c r="I132" s="102" t="n"/>
       <c r="J132" s="102" t="n"/>
@@ -6301,19 +6297,19 @@
       </c>
       <c r="C133" s="31" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Villainous Reputation</t>
         </is>
       </c>
       <c r="D133" s="91" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>Discard 1 whenever any Whistle triggers</t>
         </is>
       </c>
       <c r="E133" s="7" t="n"/>
       <c r="F133" s="138" t="n"/>
       <c r="G133" s="101" t="inlineStr">
         <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
         </is>
       </c>
       <c r="H133" s="102" t="n"/>
@@ -6329,71 +6325,101 @@
       </c>
       <c r="C134" s="31" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Free Agent</t>
         </is>
       </c>
       <c r="D134" s="91" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="138" t="n"/>
-      <c r="G134" s="101" t="n"/>
+      <c r="G134" s="101" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+        </is>
+      </c>
       <c r="H134" s="102" t="n"/>
       <c r="I134" s="102" t="n"/>
       <c r="J134" s="102" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="35" t="n"/>
-      <c r="B135" s="36" t="inlineStr">
+      <c r="A135" s="29" t="n"/>
+      <c r="B135" s="30" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C135" s="152" t="inlineStr">
+      <c r="C135" s="31" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D135" s="91" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="n"/>
+      <c r="F135" s="138" t="n"/>
+      <c r="G135" s="101" t="n"/>
+      <c r="H135" s="102" t="n"/>
+      <c r="I135" s="102" t="n"/>
+      <c r="J135" s="102" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="35" t="n"/>
+      <c r="B136" s="36" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C136" s="152" t="inlineStr">
         <is>
           <t>Fundamentalist</t>
         </is>
       </c>
-      <c r="D135" s="161" t="inlineStr">
+      <c r="D136" s="161" t="inlineStr">
         <is>
           <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent</t>
         </is>
       </c>
-      <c r="E135" s="154" t="n"/>
-      <c r="F135" s="159" t="n"/>
-      <c r="G135" s="156" t="n"/>
-      <c r="H135" s="151" t="n"/>
-      <c r="I135" s="151" t="n"/>
-      <c r="J135" s="151" t="n"/>
+      <c r="E136" s="154" t="n"/>
+      <c r="F136" s="159" t="n"/>
+      <c r="G136" s="156" t="n"/>
+      <c r="H136" s="151" t="n"/>
+      <c r="I136" s="151" t="n"/>
+      <c r="J136" s="151" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="122">
+  <mergeCells count="123">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
-    <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G135:J135"/>
+    <mergeCell ref="G32:J32"/>
     <mergeCell ref="G119:J119"/>
-    <mergeCell ref="G32:J32"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G136:J136"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G82:J82"/>
     <mergeCell ref="G57:J57"/>
-    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
+    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G34:J34"/>
     <mergeCell ref="G121:J121"/>
-    <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="G108:J108"/>
@@ -6401,8 +6427,10 @@
     <mergeCell ref="G114:J114"/>
     <mergeCell ref="G123:J123"/>
     <mergeCell ref="G110:J110"/>
+    <mergeCell ref="G20:J20"/>
     <mergeCell ref="G113:J113"/>
-    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G91:J91"/>
+    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G94:J94"/>
     <mergeCell ref="G75:J75"/>
@@ -6413,16 +6441,15 @@
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
     <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="G61:J61"/>
     <mergeCell ref="G70:J70"/>
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="G23:J23"/>
     <mergeCell ref="G97:J97"/>
-    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G38:J38"/>
+    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G112:J112"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="G62:J62"/>
@@ -6438,19 +6465,20 @@
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G76:J76"/>
     <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G90:J90"/>
     <mergeCell ref="G99:J99"/>
     <mergeCell ref="G60:J60"/>
+    <mergeCell ref="G9:J9"/>
     <mergeCell ref="G131:J131"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G59:J59"/>
+    <mergeCell ref="G124:J124"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G130:J130"/>
+    <mergeCell ref="G59:J59"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
     <mergeCell ref="G126:J126"/>
+    <mergeCell ref="G132:J132"/>
+    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G101:J101"/>
     <mergeCell ref="G116:J116"/>
     <mergeCell ref="G103:J103"/>
@@ -6459,39 +6487,36 @@
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
+    <mergeCell ref="G87:J87"/>
     <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G95:J95"/>
     <mergeCell ref="G80:J80"/>
-    <mergeCell ref="G95:J95"/>
+    <mergeCell ref="G79:J79"/>
     <mergeCell ref="G64:J64"/>
-    <mergeCell ref="G79:J79"/>
     <mergeCell ref="G73:J73"/>
     <mergeCell ref="G51:J51"/>
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="G63:J63"/>
-    <mergeCell ref="G134:J134"/>
     <mergeCell ref="G41:J41"/>
     <mergeCell ref="G50:J50"/>
     <mergeCell ref="G106:J106"/>
     <mergeCell ref="G56:J56"/>
+    <mergeCell ref="G14:J14"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="G120:J120"/>
+    <mergeCell ref="G98:J98"/>
+    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G27:J27"/>
-    <mergeCell ref="G98:J98"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G93:J93"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G83:J83"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G14:J14"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -6173,7 +6173,7 @@
       </c>
       <c r="C128" s="31" t="inlineStr">
         <is>
-          <t>Unguardable</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="D128" s="91" t="inlineStr">
@@ -6396,30 +6396,29 @@
   <mergeCells count="123">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
-    <mergeCell ref="G135:J135"/>
+    <mergeCell ref="G119:J119"/>
     <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G119:J119"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
-    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G71:J71"/>
     <mergeCell ref="G136:J136"/>
-    <mergeCell ref="G71:J71"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G82:J82"/>
     <mergeCell ref="G57:J57"/>
+    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
-    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G121:J121"/>
     <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G121:J121"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="G108:J108"/>
@@ -6447,9 +6446,9 @@
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="G23:J23"/>
     <mergeCell ref="G97:J97"/>
+    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G38:J38"/>
-    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G112:J112"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="G62:J62"/>
@@ -6469,16 +6468,15 @@
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G131:J131"/>
-    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G130:J130"/>
-    <mergeCell ref="G59:J59"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
     <mergeCell ref="G126:J126"/>
     <mergeCell ref="G132:J132"/>
+    <mergeCell ref="G39:J39"/>
     <mergeCell ref="G122:J122"/>
-    <mergeCell ref="G39:J39"/>
     <mergeCell ref="G101:J101"/>
     <mergeCell ref="G116:J116"/>
     <mergeCell ref="G103:J103"/>
@@ -6489,10 +6487,10 @@
     <mergeCell ref="G118:J118"/>
     <mergeCell ref="G87:J87"/>
     <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G80:J80"/>
     <mergeCell ref="G95:J95"/>
-    <mergeCell ref="G80:J80"/>
+    <mergeCell ref="G64:J64"/>
     <mergeCell ref="G79:J79"/>
-    <mergeCell ref="G64:J64"/>
     <mergeCell ref="G73:J73"/>
     <mergeCell ref="G51:J51"/>
     <mergeCell ref="G54:J54"/>
@@ -6501,22 +6499,24 @@
     <mergeCell ref="G50:J50"/>
     <mergeCell ref="G106:J106"/>
     <mergeCell ref="G56:J56"/>
-    <mergeCell ref="G14:J14"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="G120:J120"/>
+    <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
-    <mergeCell ref="G107:J107"/>
-    <mergeCell ref="G27:J27"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
+    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G83:J83"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G14:J14"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -3455,7 +3455,11 @@
       <c r="F26" s="80" t="n">
         <v>15</v>
       </c>
-      <c r="G26" s="107" t="n"/>
+      <c r="G26" s="107" t="inlineStr">
+        <is>
+          <t>isDribble = true</t>
+        </is>
+      </c>
       <c r="H26" s="102" t="n"/>
       <c r="I26" s="102" t="n"/>
       <c r="J26" s="102" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -3691,14 +3691,18 @@
       </c>
       <c r="D34" s="38" t="inlineStr">
         <is>
-          <t>First action only. The next pass to a side goes past you. One that named you is a TOV and ends the round</t>
+          <t>First action only. Step aside: the ball, and any Clamps on you, carry on to the next player</t>
         </is>
       </c>
       <c r="E34" s="38" t="n"/>
       <c r="F34" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="G34" s="150" t="n"/>
+      <c r="G34" s="150" t="inlineStr">
+        <is>
+          <t>Not a pass — the credit stays with whoever threw it. Only playable off a Left or Right pass, since there has to be a direction to carry on in</t>
+        </is>
+      </c>
       <c r="H34" s="151" t="n"/>
       <c r="I34" s="151" t="n"/>
       <c r="J34" s="151" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D34" s="38" t="inlineStr">
         <is>
-          <t>First action only. Step aside: the ball, and any Clamps on you, carry on to the next player</t>
+          <t>Offered as the ball reaches you: step aside and it carries on to the next player, Clamps and all</t>
         </is>
       </c>
       <c r="E34" s="38" t="n"/>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="G34" s="150" t="inlineStr">
         <is>
-          <t>Not a pass — the credit stays with whoever threw it. Only playable off a Left or Right pass, since there has to be a direction to carry on in</t>
+          <t>Asked before the Clamps land, so a man who steps out is not there for them either. Not a pass — the credit stays with whoever threw it. Only offered off a Left or Right pass</t>
         </is>
       </c>
       <c r="H34" s="151" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8540" yWindow="1900" windowWidth="21600" windowHeight="18980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4220" yWindow="660" windowWidth="25920" windowHeight="18980" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Card Types" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cards" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Helvetica Neue"/>
       <color indexed="8"/>
@@ -126,8 +126,22 @@
       <color indexed="8"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="18"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -172,11 +186,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -279,51 +299,6 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="medium">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
         <color indexed="11"/>
       </right>
       <top style="thin">
@@ -353,293 +328,6 @@
       <left style="thin">
         <color indexed="10"/>
       </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="medium">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="11"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="11"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="10"/>
@@ -657,102 +345,6 @@
       </top>
       <bottom style="thin">
         <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -780,53 +372,6 @@
       <bottom style="thin">
         <color indexed="10"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -919,8 +464,37 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -931,7 +505,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -995,407 +569,190 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="15" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="17" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2522,20 +1879,20 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col width="26.5" customWidth="1" style="132" min="1" max="1"/>
-    <col width="41.83203125" customWidth="1" style="132" min="2" max="2"/>
-    <col width="38.1640625" customWidth="1" style="132" min="3" max="3"/>
-    <col width="16.33203125" customWidth="1" style="132" min="4" max="7"/>
+    <col width="26.5" customWidth="1" style="85" min="1" max="1"/>
+    <col width="41.83203125" customWidth="1" style="85" min="2" max="2"/>
+    <col width="38.1640625" customWidth="1" style="85" min="3" max="3"/>
+    <col width="16.33203125" customWidth="1" style="85" min="4" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="132">
-      <c r="A1" s="131" t="inlineStr">
+    <row r="1" ht="27.75" customHeight="1" s="85">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Card Types</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20.25" customHeight="1" s="132">
+    <row r="2" ht="20.25" customHeight="1" s="85">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Types</t>
@@ -2550,7 +1907,7 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
     </row>
-    <row r="3" ht="32.25" customHeight="1" s="132">
+    <row r="3" ht="32.25" customHeight="1" s="85">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Special Move</t>
@@ -2565,7 +1922,7 @@
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1" s="132">
+    <row r="4" ht="20" customHeight="1" s="85">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Clamp</t>
@@ -2580,7 +1937,7 @@
       <c r="D4" s="7" t="n"/>
       <c r="E4" s="7" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="132">
+    <row r="5" ht="20" customHeight="1" s="85">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Move</t>
@@ -2595,7 +1952,7 @@
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
     </row>
-    <row r="6" ht="56" customHeight="1" s="132">
+    <row r="6" ht="56" customHeight="1" s="85">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
@@ -2610,7 +1967,7 @@
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
     </row>
-    <row r="7" ht="32" customHeight="1" s="132">
+    <row r="7" ht="32" customHeight="1" s="85">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Whistle</t>
@@ -2625,7 +1982,7 @@
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
     </row>
-    <row r="8" ht="44" customHeight="1" s="132">
+    <row r="8" ht="44" customHeight="1" s="85">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Intangible</t>
@@ -2640,7 +1997,7 @@
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
     </row>
-    <row r="9" ht="20" customHeight="1" s="132">
+    <row r="9" ht="20" customHeight="1" s="85">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Game Break</t>
@@ -2655,7 +2012,7 @@
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
     </row>
-    <row r="10" ht="32" customHeight="1" s="132">
+    <row r="10" ht="32" customHeight="1" s="85">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Injury Game Break</t>
@@ -2670,7 +2027,7 @@
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
     </row>
-    <row r="11" ht="32" customHeight="1" s="132">
+    <row r="11" ht="32" customHeight="1" s="85">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Devastating Injury Game Break</t>
@@ -2716,21 +2073,21 @@
     <col width="15.1640625" customWidth="1" style="8" min="3" max="3"/>
     <col width="20.83203125" customWidth="1" style="8" min="4" max="4"/>
     <col width="20.1640625" customWidth="1" style="8" min="5" max="5"/>
-    <col width="15" customWidth="1" style="132" min="6" max="6"/>
+    <col width="15" customWidth="1" style="85" min="6" max="6"/>
     <col width="20.1640625" customWidth="1" style="8" min="7" max="7"/>
     <col width="14.6640625" customWidth="1" style="8" min="8" max="9"/>
-    <col width="48.5" customWidth="1" style="132" min="10" max="10"/>
-    <col width="19.1640625" customWidth="1" style="132" min="11" max="11"/>
-    <col width="13" customWidth="1" style="132" min="12" max="12"/>
-    <col width="16.33203125" customWidth="1" style="132" min="13" max="13"/>
-    <col width="84.6640625" customWidth="1" style="132" min="14" max="14"/>
-    <col width="30.83203125" customWidth="1" style="132" min="15" max="15"/>
-    <col width="16.33203125" customWidth="1" style="132" min="16" max="16"/>
-    <col width="30.83203125" customWidth="1" style="132" min="17" max="17"/>
-    <col width="16.33203125" customWidth="1" style="132" min="18" max="19"/>
+    <col width="48.5" customWidth="1" style="85" min="10" max="10"/>
+    <col width="19.1640625" customWidth="1" style="85" min="11" max="11"/>
+    <col width="13" customWidth="1" style="85" min="12" max="12"/>
+    <col width="16.33203125" customWidth="1" style="85" min="13" max="13"/>
+    <col width="84.6640625" customWidth="1" style="85" min="14" max="14"/>
+    <col width="30.83203125" customWidth="1" style="85" min="15" max="15"/>
+    <col width="16.33203125" customWidth="1" style="85" min="16" max="16"/>
+    <col width="30.83203125" customWidth="1" style="85" min="17" max="17"/>
+    <col width="16.33203125" customWidth="1" style="85" min="18" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.75" customHeight="1" s="132">
+    <row r="1" ht="26.75" customHeight="1" s="85">
       <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Card Types</t>
@@ -2776,9 +2133,13 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="J1" s="11" t="n"/>
-    </row>
-    <row r="2" ht="29.75" customHeight="1" s="132">
+      <c r="J1" s="86" t="inlineStr">
+        <is>
+          <t>TOTAL UNIQUE CARDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="29.75" customHeight="1" s="85">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Totals</t>
@@ -2801,7 +2162,7 @@
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$136,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$136,"Game Break")&amp;" ("&amp;(COUNTIF($B$5:$B$136,"Game Break")+G2+H2)&amp;")"</f>
         <v/>
       </c>
       <c r="G2" s="18">
@@ -2816,15 +2177,18 @@
         <f>COUNTIF($B$5:$B$136,"Intangible")</f>
         <v/>
       </c>
-      <c r="J2" s="19" t="n"/>
-    </row>
-    <row r="4" ht="20.75" customHeight="1" s="132">
-      <c r="A4" s="123" t="inlineStr">
+      <c r="J2" s="87">
+        <f>SUM(B2:E2)+COUNTIF($B$5:$B$136,"Game Break")+SUM(G2:I2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="20.75" customHeight="1" s="85">
+      <c r="A4" s="81" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="124" t="n"/>
+      <c r="B4" s="82" t="n"/>
       <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Name</t>
@@ -2845,68 +2209,68 @@
           <t>Number in Deck</t>
         </is>
       </c>
-      <c r="G4" s="142" t="inlineStr">
+      <c r="G4" s="68" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="H4" s="143" t="n"/>
-      <c r="I4" s="143" t="n"/>
-      <c r="J4" s="143" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1" s="132">
-      <c r="A5" s="144" t="inlineStr">
+      <c r="H4" s="69" t="n"/>
+      <c r="I4" s="69" t="n"/>
+      <c r="J4" s="69" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="85">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="B5" s="145">
+      <c r="B5" s="53">
         <f>COUNTIF($B$6:$B$136,"Pass")</f>
         <v/>
       </c>
-      <c r="C5" s="146" t="n"/>
-      <c r="D5" s="146" t="n"/>
-      <c r="E5" s="146" t="n"/>
-      <c r="F5" s="147" t="n"/>
-      <c r="G5" s="148" t="n"/>
-      <c r="H5" s="149" t="n"/>
-      <c r="I5" s="149" t="n"/>
-      <c r="J5" s="149" t="n"/>
-    </row>
-    <row r="6" ht="56" customHeight="1" s="132">
-      <c r="A6" s="29" t="n"/>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="55" t="n"/>
+      <c r="G5" s="66" t="n"/>
+      <c r="H5" s="67" t="n"/>
+      <c r="I5" s="67" t="n"/>
+      <c r="J5" s="67" t="n"/>
+    </row>
+    <row r="6" ht="56" customHeight="1" s="85">
+      <c r="A6" s="21" t="n"/>
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Behind-the-Back</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Pass back to player who passed to you. If ball not received from a player, TOV +1</t>
         </is>
       </c>
-      <c r="E6" s="34" t="n"/>
-      <c r="F6" s="75" t="n">
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="107" t="n"/>
-      <c r="H6" s="102" t="n"/>
-      <c r="I6" s="102" t="n"/>
-      <c r="J6" s="102" t="n"/>
-    </row>
-    <row r="7" ht="28" customHeight="1" s="132">
-      <c r="A7" s="29" t="n"/>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="G6" s="72" t="n"/>
+      <c r="H6" s="71" t="n"/>
+      <c r="I6" s="71" t="n"/>
+      <c r="J6" s="71" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1" s="85">
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Dime</t>
         </is>
@@ -2921,48 +2285,48 @@
           <t>If new player scores that turn: AST +1</t>
         </is>
       </c>
-      <c r="F7" s="74" t="n">
+      <c r="F7" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="101" t="n"/>
-      <c r="H7" s="102" t="n"/>
-      <c r="I7" s="102" t="n"/>
-      <c r="J7" s="102" t="n"/>
-    </row>
-    <row r="8" ht="56" customHeight="1" s="132">
-      <c r="A8" s="29" t="n"/>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="G7" s="70" t="n"/>
+      <c r="H7" s="71" t="n"/>
+      <c r="I7" s="71" t="n"/>
+      <c r="J7" s="71" t="n"/>
+    </row>
+    <row r="8" ht="56" customHeight="1" s="85">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Lob</t>
         </is>
       </c>
-      <c r="D8" s="94" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>SHOT +10%. Pass to player of choice. They must attempt a shot as their first action.</t>
         </is>
       </c>
-      <c r="E8" s="34" t="n"/>
-      <c r="F8" s="75" t="n">
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="107" t="n"/>
-      <c r="H8" s="102" t="n"/>
-      <c r="I8" s="102" t="n"/>
-      <c r="J8" s="102" t="n"/>
-    </row>
-    <row r="9" ht="56" customHeight="1" s="132">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="G8" s="72" t="n"/>
+      <c r="H8" s="71" t="n"/>
+      <c r="I8" s="71" t="n"/>
+      <c r="J8" s="71" t="n"/>
+    </row>
+    <row r="9" ht="56" customHeight="1" s="85">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Nutmeg</t>
         </is>
@@ -2973,48 +2337,48 @@
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
-      <c r="F9" s="76" t="n">
+      <c r="F9" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="101" t="n"/>
-      <c r="H9" s="102" t="n"/>
-      <c r="I9" s="102" t="n"/>
-      <c r="J9" s="102" t="n"/>
-    </row>
-    <row r="10" ht="14" customHeight="1" s="132">
-      <c r="A10" s="29" t="n"/>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="G9" s="70" t="n"/>
+      <c r="H9" s="71" t="n"/>
+      <c r="I9" s="71" t="n"/>
+      <c r="J9" s="71" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1" s="85">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>Skip Pass</t>
         </is>
       </c>
-      <c r="D10" s="33" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Pass Across. SHOT +5%</t>
         </is>
       </c>
-      <c r="E10" s="34" t="n"/>
-      <c r="F10" s="75" t="n">
-        <v>20</v>
-      </c>
-      <c r="G10" s="107" t="n"/>
-      <c r="H10" s="102" t="n"/>
-      <c r="I10" s="102" t="n"/>
-      <c r="J10" s="102" t="n"/>
-    </row>
-    <row r="11" ht="14" customHeight="1" s="132">
-      <c r="A11" s="29" t="n"/>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="G10" s="72" t="n"/>
+      <c r="H10" s="71" t="n"/>
+      <c r="I10" s="71" t="n"/>
+      <c r="J10" s="71" t="n"/>
+    </row>
+    <row r="11" ht="14" customHeight="1" s="85">
+      <c r="A11" s="21" t="n"/>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>Swing Left</t>
         </is>
@@ -3025,48 +2389,48 @@
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
-      <c r="F11" s="76" t="n">
-        <v>31</v>
-      </c>
-      <c r="G11" s="101" t="n"/>
-      <c r="H11" s="102" t="n"/>
-      <c r="I11" s="102" t="n"/>
-      <c r="J11" s="102" t="n"/>
-    </row>
-    <row r="12" ht="14" customHeight="1" s="132">
-      <c r="A12" s="29" t="n"/>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="F11" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="G11" s="70" t="n"/>
+      <c r="H11" s="71" t="n"/>
+      <c r="I11" s="71" t="n"/>
+      <c r="J11" s="71" t="n"/>
+    </row>
+    <row r="12" ht="14" customHeight="1" s="85">
+      <c r="A12" s="21" t="n"/>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>Swing Right</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Pass Right. SHOT +5%</t>
         </is>
       </c>
-      <c r="E12" s="34" t="n"/>
-      <c r="F12" s="75" t="n">
-        <v>31</v>
-      </c>
-      <c r="G12" s="107" t="n"/>
-      <c r="H12" s="102" t="n"/>
-      <c r="I12" s="102" t="n"/>
-      <c r="J12" s="102" t="n"/>
-    </row>
-    <row r="13" ht="28" customHeight="1" s="132">
-      <c r="A13" s="29" t="n"/>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="G12" s="72" t="n"/>
+      <c r="H12" s="71" t="n"/>
+      <c r="I12" s="71" t="n"/>
+      <c r="J12" s="71" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1" s="85">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>No-Look</t>
         </is>
@@ -3077,281 +2441,281 @@
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
-      <c r="F13" s="76" t="n">
+      <c r="F13" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="G13" s="101" t="n"/>
-      <c r="H13" s="102" t="n"/>
-      <c r="I13" s="102" t="n"/>
-      <c r="J13" s="102" t="n"/>
-    </row>
-    <row r="14" ht="29" customHeight="1" s="132">
-      <c r="A14" s="29" t="n"/>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="G13" s="70" t="n"/>
+      <c r="H13" s="71" t="n"/>
+      <c r="I13" s="71" t="n"/>
+      <c r="J13" s="71" t="n"/>
+    </row>
+    <row r="14" ht="29" customHeight="1" s="85">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Bullet Pass</t>
         </is>
       </c>
-      <c r="D14" s="33" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Pass to player of choice. SHOT +5%</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>New players discards 1 card at random</t>
         </is>
       </c>
-      <c r="F14" s="80" t="n">
+      <c r="F14" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="G14" s="107" t="n"/>
-      <c r="H14" s="102" t="n"/>
-      <c r="I14" s="102" t="n"/>
-      <c r="J14" s="102" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" s="132">
-      <c r="A15" s="29" t="n"/>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="G14" s="72" t="n"/>
+      <c r="H14" s="71" t="n"/>
+      <c r="I14" s="71" t="n"/>
+      <c r="J14" s="71" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" s="85">
+      <c r="A15" s="21" t="n"/>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Alley-Oop</t>
         </is>
       </c>
-      <c r="D15" s="33" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>SHOT +20%. Pass to player of choice</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Receiving player shoots immediately after drawing for turn</t>
         </is>
       </c>
-      <c r="F15" s="80" t="n">
+      <c r="F15" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="107" t="n"/>
-      <c r="H15" s="102" t="n"/>
-      <c r="I15" s="102" t="n"/>
-      <c r="J15" s="102" t="n"/>
-    </row>
-    <row r="16" ht="14" customHeight="1" s="132">
-      <c r="A16" s="29" t="n"/>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="G15" s="72" t="n"/>
+      <c r="H15" s="71" t="n"/>
+      <c r="I15" s="71" t="n"/>
+      <c r="J15" s="71" t="n"/>
+    </row>
+    <row r="16" ht="14" customHeight="1" s="85">
+      <c r="A16" s="21" t="n"/>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>Hand-Off</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>SHOT +5%. Pass to player to Left or Right. Draw 1 card</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>If played following a Dribble: draw 1 additional and SHOT +5% more</t>
         </is>
       </c>
-      <c r="F16" s="80" t="n">
+      <c r="F16" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="G16" s="107" t="inlineStr">
+      <c r="G16" s="72" t="inlineStr">
         <is>
           <t>This is the Dribble Hand-Off</t>
         </is>
       </c>
-      <c r="H16" s="102" t="n"/>
-      <c r="I16" s="102" t="n"/>
-      <c r="J16" s="102" t="n"/>
-    </row>
-    <row r="17" ht="28" customHeight="1" s="132">
-      <c r="A17" s="29" t="n"/>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="H16" s="71" t="n"/>
+      <c r="I16" s="71" t="n"/>
+      <c r="J16" s="71" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" s="85">
+      <c r="A17" s="21" t="n"/>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Outlet Pass</t>
         </is>
       </c>
-      <c r="D17" s="33" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>SHOT +10%. Shot Clock +01. Pass to player of choice</t>
         </is>
       </c>
-      <c r="E17" s="33" t="n"/>
-      <c r="F17" s="80" t="n">
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="107" t="inlineStr">
+      <c r="G17" s="72" t="inlineStr">
         <is>
           <t>The clock increments instead of decrementing — it does not break even</t>
         </is>
       </c>
-      <c r="H17" s="102" t="n"/>
-      <c r="I17" s="102" t="n"/>
-      <c r="J17" s="102" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1" s="132">
-      <c r="A18" s="29" t="n"/>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="H17" s="71" t="n"/>
+      <c r="I17" s="71" t="n"/>
+      <c r="J17" s="71" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" s="85">
+      <c r="A18" s="21" t="n"/>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Kick-Out</t>
         </is>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>SHOT +10%. Upgraded to 3pt. Pass to player of choice</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Following Drive: draw 1. Following a Dribble Drive: gain 1 AST also</t>
         </is>
       </c>
-      <c r="F18" s="80" t="n">
+      <c r="F18" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="107" t="inlineStr">
+      <c r="G18" s="72" t="inlineStr">
         <is>
           <t>The most it grants is a draw and 1 AST</t>
         </is>
       </c>
-      <c r="H18" s="102" t="n"/>
-      <c r="I18" s="102" t="n"/>
-      <c r="J18" s="102" t="n"/>
-    </row>
-    <row r="19" ht="56" customHeight="1" s="132">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="H18" s="71" t="n"/>
+      <c r="I18" s="71" t="n"/>
+      <c r="J18" s="71" t="n"/>
+    </row>
+    <row r="19" ht="56" customHeight="1" s="85">
+      <c r="A19" s="21" t="n"/>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Right Back</t>
         </is>
       </c>
-      <c r="D19" s="33" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>SHOT +5%. Pass to player of choice. They immediately pass it back</t>
         </is>
       </c>
-      <c r="E19" s="33" t="n"/>
-      <c r="F19" s="80" t="n">
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="G19" s="107" t="inlineStr">
+      <c r="G19" s="72" t="inlineStr">
         <is>
           <t>Results in a draw for each player and SHOT +10% overall. Whatever the trip costs them happens in between</t>
         </is>
       </c>
-      <c r="H19" s="102" t="n"/>
-      <c r="I19" s="102" t="n"/>
-      <c r="J19" s="102" t="n"/>
-    </row>
-    <row r="20" ht="56" customHeight="1" s="132">
-      <c r="A20" s="35" t="n"/>
-      <c r="B20" s="36" t="inlineStr">
+      <c r="H19" s="71" t="n"/>
+      <c r="I19" s="71" t="n"/>
+      <c r="J19" s="71" t="n"/>
+    </row>
+    <row r="20" ht="56" customHeight="1" s="85">
+      <c r="A20" s="27" t="n"/>
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C20" s="37" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Touch Pass</t>
         </is>
       </c>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>SHOT +5%. Pass to player of choice. If played as first action, draw 2 cards</t>
         </is>
       </c>
-      <c r="E20" s="38" t="n"/>
-      <c r="F20" s="77" t="n">
+      <c r="E20" s="30" t="n"/>
+      <c r="F20" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="G20" s="150" t="n"/>
-      <c r="H20" s="151" t="n"/>
-      <c r="I20" s="151" t="n"/>
-      <c r="J20" s="151" t="n"/>
-    </row>
-    <row r="21" ht="14" customHeight="1" s="132">
-      <c r="A21" s="144" t="inlineStr">
+      <c r="G20" s="78" t="n"/>
+      <c r="H20" s="76" t="n"/>
+      <c r="I20" s="76" t="n"/>
+      <c r="J20" s="76" t="n"/>
+    </row>
+    <row r="21" ht="14" customHeight="1" s="85">
+      <c r="A21" s="52" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="B21" s="145">
+      <c r="B21" s="53">
         <f>COUNTIF($B$22:$B$136,"Move")+COUNTIF($B$22:$B$136,"Special Move")</f>
         <v/>
       </c>
-      <c r="C21" s="146" t="n"/>
-      <c r="D21" s="146" t="n"/>
-      <c r="E21" s="146" t="n"/>
-      <c r="F21" s="147" t="n"/>
-      <c r="G21" s="148" t="n"/>
-      <c r="H21" s="149" t="n"/>
-      <c r="I21" s="149" t="n"/>
-      <c r="J21" s="149" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1" s="132">
-      <c r="A22" s="29" t="n"/>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="54" t="n"/>
+      <c r="E21" s="54" t="n"/>
+      <c r="F21" s="55" t="n"/>
+      <c r="G21" s="66" t="n"/>
+      <c r="H21" s="67" t="n"/>
+      <c r="I21" s="67" t="n"/>
+      <c r="J21" s="67" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1" s="85">
+      <c r="A22" s="21" t="n"/>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Dribble</t>
         </is>
       </c>
-      <c r="D22" s="33" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Draw 1 card. SHOT -10%</t>
         </is>
       </c>
-      <c r="E22" s="34" t="n"/>
-      <c r="F22" s="75" t="n">
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="G22" s="107" t="n"/>
-      <c r="H22" s="102" t="n"/>
-      <c r="I22" s="102" t="n"/>
-      <c r="J22" s="102" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1" s="132">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="G22" s="72" t="n"/>
+      <c r="H22" s="71" t="n"/>
+      <c r="I22" s="71" t="n"/>
+      <c r="J22" s="71" t="n"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" s="85">
+      <c r="A23" s="21" t="n"/>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Drive</t>
         </is>
@@ -3366,112 +2730,112 @@
           <t>Following Dribble: SHOT +10%</t>
         </is>
       </c>
-      <c r="F23" s="74" t="n">
+      <c r="F23" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="G23" s="101" t="n"/>
-      <c r="H23" s="102" t="n"/>
-      <c r="I23" s="102" t="n"/>
-      <c r="J23" s="102" t="n"/>
-    </row>
-    <row r="24" ht="28" customHeight="1" s="132">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="G23" s="70" t="n"/>
+      <c r="H23" s="71" t="n"/>
+      <c r="I23" s="71" t="n"/>
+      <c r="J23" s="71" t="n"/>
+    </row>
+    <row r="24" ht="28" customHeight="1" s="85">
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>Ankle Breaker</t>
         </is>
       </c>
-      <c r="D24" s="33" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>Target player discards 1 card. SHOT +10%</t>
         </is>
       </c>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="75" t="n">
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="G24" s="107" t="n"/>
-      <c r="H24" s="102" t="n"/>
-      <c r="I24" s="102" t="n"/>
-      <c r="J24" s="102" t="n"/>
-    </row>
-    <row r="25" ht="28" customHeight="1" s="132">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="G24" s="72" t="n"/>
+      <c r="H24" s="71" t="n"/>
+      <c r="I24" s="71" t="n"/>
+      <c r="J24" s="71" t="n"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" s="85">
+      <c r="A25" s="21" t="n"/>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C25" s="90" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>Flop</t>
         </is>
       </c>
-      <c r="D25" s="91" t="inlineStr">
+      <c r="D25" s="38" t="inlineStr">
         <is>
           <t>Cancel Clamps. Take 1 FT for each. If no Clamps on you, TOV +1</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="76" t="n">
+      <c r="F25" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="130" t="inlineStr">
+      <c r="G25" s="80" t="inlineStr">
         <is>
           <t>Take 1 FT attempt for each Clamp on you and cancel it. If no Clamps on you, TOV +1</t>
         </is>
       </c>
-      <c r="H25" s="102" t="n"/>
-      <c r="I25" s="102" t="n"/>
-      <c r="J25" s="102" t="n"/>
-    </row>
-    <row r="26" ht="28" customHeight="1" s="132">
-      <c r="A26" s="29" t="n"/>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="H25" s="71" t="n"/>
+      <c r="I25" s="71" t="n"/>
+      <c r="J25" s="71" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" s="85">
+      <c r="A26" s="21" t="n"/>
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>Hesi</t>
         </is>
       </c>
-      <c r="D26" s="33" t="inlineStr">
+      <c r="D26" s="25" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E26" s="33" t="inlineStr">
+      <c r="E26" s="25" t="inlineStr">
         <is>
           <t>Shot Clock -1</t>
         </is>
       </c>
-      <c r="F26" s="80" t="n">
+      <c r="F26" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="G26" s="107" t="inlineStr">
+      <c r="G26" s="72" t="inlineStr">
         <is>
           <t>isDribble = true</t>
         </is>
       </c>
-      <c r="H26" s="102" t="n"/>
-      <c r="I26" s="102" t="n"/>
-      <c r="J26" s="102" t="n"/>
-    </row>
-    <row r="27" ht="14" customHeight="1" s="132">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="H26" s="71" t="n"/>
+      <c r="I26" s="71" t="n"/>
+      <c r="J26" s="71" t="n"/>
+    </row>
+    <row r="27" ht="14" customHeight="1" s="85">
+      <c r="A27" s="21" t="n"/>
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>Pump Fake</t>
         </is>
@@ -3486,134 +2850,134 @@
           <t>Cancel all Clamps on you</t>
         </is>
       </c>
-      <c r="F27" s="74" t="n">
+      <c r="F27" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="G27" s="101" t="n"/>
-      <c r="H27" s="102" t="n"/>
-      <c r="I27" s="102" t="n"/>
-      <c r="J27" s="102" t="n"/>
-    </row>
-    <row r="28" ht="71" customHeight="1" s="132">
-      <c r="A28" s="29" t="n"/>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="G27" s="70" t="n"/>
+      <c r="H27" s="71" t="n"/>
+      <c r="I27" s="71" t="n"/>
+      <c r="J27" s="71" t="n"/>
+    </row>
+    <row r="28" ht="71" customHeight="1" s="85">
+      <c r="A28" s="21" t="n"/>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C28" s="32" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>Rhythm Dribble</t>
         </is>
       </c>
-      <c r="D28" s="33" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>Draw 1 card. SHOT +10%. Shot Clock -1</t>
         </is>
       </c>
-      <c r="E28" s="34" t="n"/>
-      <c r="F28" s="75" t="n">
+      <c r="E28" s="26" t="n"/>
+      <c r="F28" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="G28" s="107" t="n"/>
-      <c r="H28" s="102" t="n"/>
-      <c r="I28" s="102" t="n"/>
-      <c r="J28" s="102" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1" s="132">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="G28" s="72" t="n"/>
+      <c r="H28" s="71" t="n"/>
+      <c r="I28" s="71" t="n"/>
+      <c r="J28" s="71" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="85">
+      <c r="A29" s="21" t="n"/>
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C29" s="133" t="inlineStr">
+      <c r="C29" s="48" t="inlineStr">
         <is>
           <t>Pound Dribble</t>
         </is>
       </c>
-      <c r="D29" s="94" t="inlineStr">
+      <c r="D29" s="41" t="inlineStr">
         <is>
           <t>Draw 2 cards then Discard 1. SHOT +10% Shot Clock -1</t>
         </is>
       </c>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="75" t="n">
+      <c r="E29" s="26" t="n"/>
+      <c r="F29" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="G29" s="107" t="n"/>
-      <c r="H29" s="102" t="n"/>
-      <c r="I29" s="102" t="n"/>
-      <c r="J29" s="102" t="n"/>
-    </row>
-    <row r="30" ht="42" customHeight="1" s="132">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="G29" s="72" t="n"/>
+      <c r="H29" s="71" t="n"/>
+      <c r="I29" s="71" t="n"/>
+      <c r="J29" s="71" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1" s="85">
+      <c r="A30" s="21" t="n"/>
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C30" s="133" t="inlineStr">
+      <c r="C30" s="48" t="inlineStr">
         <is>
           <t>Spin Move</t>
         </is>
       </c>
-      <c r="D30" s="94" t="inlineStr">
+      <c r="D30" s="41" t="inlineStr">
         <is>
           <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +10% for each</t>
         </is>
       </c>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="75" t="n">
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="G30" s="125" t="inlineStr">
+      <c r="G30" s="77" t="inlineStr">
         <is>
           <t>isDribble = true</t>
         </is>
       </c>
-      <c r="H30" s="102" t="n"/>
-      <c r="I30" s="102" t="n"/>
-      <c r="J30" s="102" t="n"/>
-    </row>
-    <row r="31" ht="14" customHeight="1" s="132">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="H30" s="71" t="n"/>
+      <c r="I30" s="71" t="n"/>
+      <c r="J30" s="71" t="n"/>
+    </row>
+    <row r="31" ht="14" customHeight="1" s="85">
+      <c r="A31" s="21" t="n"/>
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C31" s="133" t="inlineStr">
+      <c r="C31" s="48" t="inlineStr">
         <is>
           <t>Crossover</t>
         </is>
       </c>
-      <c r="D31" s="94" t="inlineStr">
+      <c r="D31" s="41" t="inlineStr">
         <is>
           <t>Draw 1 Card. SHOT +10%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
         </is>
       </c>
-      <c r="E31" s="34" t="n"/>
-      <c r="F31" s="75" t="n">
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="125" t="inlineStr">
+      <c r="G31" s="77" t="inlineStr">
         <is>
           <t>isDribble = true</t>
         </is>
       </c>
-      <c r="H31" s="102" t="n"/>
-      <c r="I31" s="102" t="n"/>
-      <c r="J31" s="102" t="n"/>
-    </row>
-    <row r="32" ht="28" customHeight="1" s="132">
-      <c r="A32" s="29" t="n"/>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="H31" s="71" t="n"/>
+      <c r="I31" s="71" t="n"/>
+      <c r="J31" s="71" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1" s="85">
+      <c r="A32" s="21" t="n"/>
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>Stepback</t>
         </is>
@@ -3628,31 +2992,31 @@
           <t>Discard 1: SHOT +10%</t>
         </is>
       </c>
-      <c r="F32" s="74" t="n">
+      <c r="F32" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="G32" s="101" t="inlineStr">
+      <c r="G32" s="70" t="inlineStr">
         <is>
           <t>The discard is an optional prompt.</t>
         </is>
       </c>
-      <c r="H32" s="102" t="n"/>
-      <c r="I32" s="102" t="n"/>
-      <c r="J32" s="102" t="n"/>
-    </row>
-    <row r="33" ht="14" customHeight="1" s="132">
-      <c r="A33" s="29" t="n"/>
-      <c r="B33" s="30" t="inlineStr">
+      <c r="H32" s="71" t="n"/>
+      <c r="I32" s="71" t="n"/>
+      <c r="J32" s="71" t="n"/>
+    </row>
+    <row r="33" ht="14" customHeight="1" s="85">
+      <c r="A33" s="21" t="n"/>
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>Triple Threat</t>
         </is>
       </c>
-      <c r="D33" s="33" t="inlineStr">
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>Choose 1:
 Draw 1 card
@@ -3660,112 +3024,112 @@
 SHOT +10%</t>
         </is>
       </c>
-      <c r="E33" s="33" t="inlineStr">
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>Cannot use further Move cards</t>
         </is>
       </c>
-      <c r="F33" s="80" t="n">
+      <c r="F33" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="G33" s="107" t="inlineStr">
+      <c r="G33" s="72" t="inlineStr">
         <is>
           <t>Cannot use further Move cards applies to that possession only.</t>
         </is>
       </c>
-      <c r="H33" s="102" t="n"/>
-      <c r="I33" s="102" t="n"/>
-      <c r="J33" s="102" t="n"/>
-    </row>
-    <row r="34" ht="14" customHeight="1" s="132">
-      <c r="A34" s="35" t="n"/>
-      <c r="B34" s="36" t="inlineStr">
+      <c r="H33" s="71" t="n"/>
+      <c r="I33" s="71" t="n"/>
+      <c r="J33" s="71" t="n"/>
+    </row>
+    <row r="34" ht="14" customHeight="1" s="85">
+      <c r="A34" s="27" t="n"/>
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>Clear Out</t>
         </is>
       </c>
-      <c r="D34" s="38" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>Offered as the ball reaches you: step aside and it carries on to the next player, Clamps and all</t>
         </is>
       </c>
-      <c r="E34" s="38" t="n"/>
-      <c r="F34" s="77" t="n">
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="G34" s="150" t="inlineStr">
+      <c r="G34" s="78" t="inlineStr">
         <is>
           <t>Asked before the Clamps land, so a man who steps out is not there for them either. Not a pass — the credit stays with whoever threw it. Only offered off a Left or Right pass</t>
         </is>
       </c>
-      <c r="H34" s="151" t="n"/>
-      <c r="I34" s="151" t="n"/>
-      <c r="J34" s="151" t="n"/>
-    </row>
-    <row r="35" ht="28" customHeight="1" s="132">
-      <c r="A35" s="144" t="inlineStr">
+      <c r="H34" s="76" t="n"/>
+      <c r="I34" s="76" t="n"/>
+      <c r="J34" s="76" t="n"/>
+    </row>
+    <row r="35" ht="28" customHeight="1" s="85">
+      <c r="A35" s="52" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="B35" s="145">
+      <c r="B35" s="53">
         <f>COUNTIF($B$36:$B$136,"Special Move")</f>
         <v/>
       </c>
-      <c r="C35" s="146" t="n"/>
-      <c r="D35" s="146" t="n"/>
-      <c r="E35" s="146" t="n"/>
-      <c r="F35" s="147" t="n"/>
-      <c r="G35" s="148" t="n"/>
-      <c r="H35" s="149" t="n"/>
-      <c r="I35" s="149" t="n"/>
-      <c r="J35" s="149" t="n"/>
-    </row>
-    <row r="36" ht="28" customHeight="1" s="132">
-      <c r="A36" s="29" t="n"/>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="C35" s="54" t="n"/>
+      <c r="D35" s="54" t="n"/>
+      <c r="E35" s="54" t="n"/>
+      <c r="F35" s="55" t="n"/>
+      <c r="G35" s="66" t="n"/>
+      <c r="H35" s="67" t="n"/>
+      <c r="I35" s="67" t="n"/>
+      <c r="J35" s="67" t="n"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" s="85">
+      <c r="A36" s="21" t="n"/>
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C36" s="32" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>Bankshot</t>
         </is>
       </c>
-      <c r="D36" s="33" t="inlineStr">
+      <c r="D36" s="25" t="inlineStr">
         <is>
           <t>Flip a coin:
 Heads: SHOT +10%
 Tails: SHOT -10%</t>
         </is>
       </c>
-      <c r="E36" s="33" t="inlineStr">
+      <c r="E36" s="25" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F36" s="80" t="n">
+      <c r="F36" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G36" s="107" t="n"/>
-      <c r="H36" s="102" t="n"/>
-      <c r="I36" s="102" t="n"/>
-      <c r="J36" s="102" t="n"/>
-    </row>
-    <row r="37" ht="28" customHeight="1" s="132">
-      <c r="A37" s="29" t="n"/>
-      <c r="B37" s="30" t="inlineStr">
+      <c r="G36" s="72" t="n"/>
+      <c r="H36" s="71" t="n"/>
+      <c r="I36" s="71" t="n"/>
+      <c r="J36" s="71" t="n"/>
+    </row>
+    <row r="37" ht="28" customHeight="1" s="85">
+      <c r="A37" s="21" t="n"/>
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C37" s="31" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>Buzzer Beater</t>
         </is>
@@ -3780,56 +3144,56 @@
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F37" s="74" t="n">
+      <c r="F37" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="G37" s="111" t="inlineStr">
+      <c r="G37" s="74" t="inlineStr">
         <is>
           <t>Can only play with Shot Clock at 1</t>
         </is>
       </c>
-      <c r="H37" s="102" t="n"/>
-      <c r="I37" s="102" t="n"/>
-      <c r="J37" s="102" t="n"/>
-    </row>
-    <row r="38" ht="42" customHeight="1" s="132">
-      <c r="A38" s="29" t="n"/>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="H37" s="71" t="n"/>
+      <c r="I37" s="71" t="n"/>
+      <c r="J37" s="71" t="n"/>
+    </row>
+    <row r="38" ht="42" customHeight="1" s="85">
+      <c r="A38" s="21" t="n"/>
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>Dagger Three</t>
         </is>
       </c>
-      <c r="D38" s="94" t="inlineStr">
+      <c r="D38" s="41" t="inlineStr">
         <is>
           <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
         </is>
       </c>
-      <c r="E38" s="33" t="inlineStr">
+      <c r="E38" s="25" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F38" s="80" t="n">
+      <c r="F38" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G38" s="107" t="n"/>
-      <c r="H38" s="102" t="n"/>
-      <c r="I38" s="102" t="n"/>
-      <c r="J38" s="102" t="n"/>
-    </row>
-    <row r="39" ht="28" customHeight="1" s="132">
-      <c r="A39" s="29" t="n"/>
-      <c r="B39" s="30" t="inlineStr">
+      <c r="G38" s="72" t="n"/>
+      <c r="H38" s="71" t="n"/>
+      <c r="I38" s="71" t="n"/>
+      <c r="J38" s="71" t="n"/>
+    </row>
+    <row r="39" ht="28" customHeight="1" s="85">
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C39" s="31" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>Fadeaway</t>
         </is>
@@ -3844,57 +3208,57 @@
           <t>Shoot the ball.</t>
         </is>
       </c>
-      <c r="F39" s="74" t="n">
+      <c r="F39" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="G39" s="101" t="n"/>
-      <c r="H39" s="102" t="n"/>
-      <c r="I39" s="102" t="n"/>
-      <c r="J39" s="102" t="n"/>
-    </row>
-    <row r="40" ht="28" customHeight="1" s="132">
-      <c r="A40" s="29" t="n"/>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="G39" s="70" t="n"/>
+      <c r="H39" s="71" t="n"/>
+      <c r="I39" s="71" t="n"/>
+      <c r="J39" s="71" t="n"/>
+    </row>
+    <row r="40" ht="28" customHeight="1" s="85">
+      <c r="A40" s="21" t="n"/>
+      <c r="B40" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C40" s="32" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>From the Hash</t>
         </is>
       </c>
-      <c r="D40" s="94" t="inlineStr">
+      <c r="D40" s="41" t="inlineStr">
         <is>
           <t>SHOT -20%</t>
         </is>
       </c>
-      <c r="E40" s="33" t="inlineStr">
+      <c r="E40" s="25" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F40" s="80" t="n">
+      <c r="F40" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G40" s="107" t="n"/>
-      <c r="H40" s="102" t="n"/>
-      <c r="I40" s="102" t="n"/>
-      <c r="J40" s="102" t="n"/>
-    </row>
-    <row r="41" ht="42" customHeight="1" s="132">
-      <c r="A41" s="29" t="n"/>
-      <c r="B41" s="30" t="inlineStr">
+      <c r="G40" s="72" t="n"/>
+      <c r="H40" s="71" t="n"/>
+      <c r="I40" s="71" t="n"/>
+      <c r="J40" s="71" t="n"/>
+    </row>
+    <row r="41" ht="42" customHeight="1" s="85">
+      <c r="A41" s="21" t="n"/>
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C41" s="31" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>From the Logo</t>
         </is>
       </c>
-      <c r="D41" s="91" t="inlineStr">
+      <c r="D41" s="38" t="inlineStr">
         <is>
           <t>SHOT -30%</t>
         </is>
@@ -3904,52 +3268,52 @@
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F41" s="74" t="n">
+      <c r="F41" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="G41" s="101" t="n"/>
-      <c r="H41" s="102" t="n"/>
-      <c r="I41" s="102" t="n"/>
-      <c r="J41" s="102" t="n"/>
-    </row>
-    <row r="42" ht="57" customHeight="1" s="132">
-      <c r="A42" s="29" t="n"/>
-      <c r="B42" s="30" t="inlineStr">
+      <c r="G41" s="70" t="n"/>
+      <c r="H41" s="71" t="n"/>
+      <c r="I41" s="71" t="n"/>
+      <c r="J41" s="71" t="n"/>
+    </row>
+    <row r="42" ht="57" customHeight="1" s="85">
+      <c r="A42" s="21" t="n"/>
+      <c r="B42" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C42" s="32" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>Full-Court Heave</t>
         </is>
       </c>
-      <c r="D42" s="33" t="inlineStr">
+      <c r="D42" s="25" t="inlineStr">
         <is>
           <t>SHOT = 10%</t>
         </is>
       </c>
-      <c r="E42" s="33" t="inlineStr">
+      <c r="E42" s="25" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F42" s="80" t="n">
+      <c r="F42" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="107" t="n"/>
-      <c r="H42" s="102" t="n"/>
-      <c r="I42" s="102" t="n"/>
-      <c r="J42" s="102" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1" s="132">
-      <c r="A43" s="29" t="n"/>
-      <c r="B43" s="30" t="inlineStr">
+      <c r="G42" s="72" t="n"/>
+      <c r="H42" s="71" t="n"/>
+      <c r="I42" s="71" t="n"/>
+      <c r="J42" s="71" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1" s="85">
+      <c r="A43" s="21" t="n"/>
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C43" s="31" t="inlineStr">
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>Putback Tip</t>
         </is>
@@ -3964,52 +3328,52 @@
           <t>Shoot the ball. After a missed shot: SHOT = 100%</t>
         </is>
       </c>
-      <c r="F43" s="74" t="n">
+      <c r="F43" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="G43" s="101" t="n"/>
-      <c r="H43" s="102" t="n"/>
-      <c r="I43" s="102" t="n"/>
-      <c r="J43" s="102" t="n"/>
-    </row>
-    <row r="44" ht="28" customHeight="1" s="132">
-      <c r="A44" s="29" t="n"/>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="G43" s="70" t="n"/>
+      <c r="H43" s="71" t="n"/>
+      <c r="I43" s="71" t="n"/>
+      <c r="J43" s="71" t="n"/>
+    </row>
+    <row r="44" ht="28" customHeight="1" s="85">
+      <c r="A44" s="21" t="n"/>
+      <c r="B44" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C44" s="32" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>Skyhook</t>
         </is>
       </c>
-      <c r="D44" s="33" t="inlineStr">
+      <c r="D44" s="25" t="inlineStr">
         <is>
           <t>SHOT +10%</t>
         </is>
       </c>
-      <c r="E44" s="94" t="inlineStr">
+      <c r="E44" s="41" t="inlineStr">
         <is>
           <t>Shoot the ball. Shot is unaffected by Clamps</t>
         </is>
       </c>
-      <c r="F44" s="80" t="n">
+      <c r="F44" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="107" t="n"/>
-      <c r="H44" s="102" t="n"/>
-      <c r="I44" s="102" t="n"/>
-      <c r="J44" s="102" t="n"/>
-    </row>
-    <row r="45" ht="28" customHeight="1" s="132">
-      <c r="A45" s="29" t="n"/>
-      <c r="B45" s="30" t="inlineStr">
+      <c r="G44" s="72" t="n"/>
+      <c r="H44" s="71" t="n"/>
+      <c r="I44" s="71" t="n"/>
+      <c r="J44" s="71" t="n"/>
+    </row>
+    <row r="45" ht="28" customHeight="1" s="85">
+      <c r="A45" s="21" t="n"/>
+      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C45" s="31" t="inlineStr">
+      <c r="C45" s="23" t="inlineStr">
         <is>
           <t>Slam Dunk</t>
         </is>
@@ -4024,56 +3388,56 @@
           <t>Shoot the ball</t>
         </is>
       </c>
-      <c r="F45" s="74" t="n">
+      <c r="F45" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="G45" s="101" t="n"/>
-      <c r="H45" s="102" t="n"/>
-      <c r="I45" s="102" t="n"/>
-      <c r="J45" s="102" t="n"/>
-    </row>
-    <row r="46" ht="42" customHeight="1" s="132">
-      <c r="A46" s="29" t="n"/>
-      <c r="B46" s="30" t="inlineStr">
+      <c r="G45" s="70" t="n"/>
+      <c r="H45" s="71" t="n"/>
+      <c r="I45" s="71" t="n"/>
+      <c r="J45" s="71" t="n"/>
+    </row>
+    <row r="46" ht="42" customHeight="1" s="85">
+      <c r="A46" s="21" t="n"/>
+      <c r="B46" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C46" s="32" t="inlineStr">
+      <c r="C46" s="24" t="inlineStr">
         <is>
           <t>Turnaround Three</t>
         </is>
       </c>
-      <c r="D46" s="33" t="inlineStr">
+      <c r="D46" s="25" t="inlineStr">
         <is>
           <t>Discard any number of cards. SHOT +10% for each</t>
         </is>
       </c>
-      <c r="E46" s="33" t="inlineStr">
+      <c r="E46" s="25" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make</t>
         </is>
       </c>
-      <c r="F46" s="80" t="n">
+      <c r="F46" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="113" t="inlineStr">
+      <c r="G46" s="73" t="inlineStr">
         <is>
           <t>Only 1 in deck</t>
         </is>
       </c>
-      <c r="H46" s="102" t="n"/>
-      <c r="I46" s="102" t="n"/>
-      <c r="J46" s="102" t="n"/>
-    </row>
-    <row r="47" ht="42" customHeight="1" s="132">
-      <c r="A47" s="29" t="n"/>
-      <c r="B47" s="30" t="inlineStr">
+      <c r="H46" s="71" t="n"/>
+      <c r="I46" s="71" t="n"/>
+      <c r="J46" s="71" t="n"/>
+    </row>
+    <row r="47" ht="42" customHeight="1" s="85">
+      <c r="A47" s="21" t="n"/>
+      <c r="B47" s="22" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C47" s="31" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>Euro Step</t>
         </is>
@@ -4084,75 +3448,75 @@
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
-      <c r="F47" s="76" t="n">
+      <c r="F47" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="G47" s="101" t="n"/>
-      <c r="H47" s="102" t="n"/>
-      <c r="I47" s="102" t="n"/>
-      <c r="J47" s="102" t="n"/>
-    </row>
-    <row r="48" ht="29" customHeight="1" s="132">
-      <c r="A48" s="35" t="n"/>
-      <c r="B48" s="36" t="inlineStr">
+      <c r="G47" s="70" t="n"/>
+      <c r="H47" s="71" t="n"/>
+      <c r="I47" s="71" t="n"/>
+      <c r="J47" s="71" t="n"/>
+    </row>
+    <row r="48" ht="29" customHeight="1" s="85">
+      <c r="A48" s="27" t="n"/>
+      <c r="B48" s="28" t="inlineStr">
         <is>
           <t>Special Move</t>
         </is>
       </c>
-      <c r="C48" s="152" t="inlineStr">
+      <c r="C48" s="56" t="inlineStr">
         <is>
           <t>Wide-Open Three</t>
         </is>
       </c>
-      <c r="D48" s="153" t="inlineStr">
+      <c r="D48" s="57" t="inlineStr">
         <is>
           <t>Select any number of other players. SHOT +10% for each</t>
         </is>
       </c>
-      <c r="E48" s="154" t="inlineStr">
+      <c r="E48" s="58" t="inlineStr">
         <is>
           <t>Shoot the ball. +1 Point on make. Selected players receive +1 AST on a make</t>
         </is>
       </c>
-      <c r="F48" s="155" t="n">
+      <c r="F48" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="156" t="inlineStr">
+      <c r="G48" s="75" t="inlineStr">
         <is>
           <t>Selecting none rolls off current SHOT and is still a three</t>
         </is>
       </c>
-      <c r="H48" s="151" t="n"/>
-      <c r="I48" s="151" t="n"/>
-      <c r="J48" s="151" t="n"/>
-    </row>
-    <row r="49" ht="20" customHeight="1" s="132">
-      <c r="A49" s="144" t="inlineStr">
+      <c r="H48" s="76" t="n"/>
+      <c r="I48" s="76" t="n"/>
+      <c r="J48" s="76" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1" s="85">
+      <c r="A49" s="52" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B49" s="145">
+      <c r="B49" s="53">
         <f>COUNTIF($B$50:$B$136,"Clamp")</f>
         <v/>
       </c>
-      <c r="C49" s="146" t="n"/>
-      <c r="D49" s="146" t="n"/>
-      <c r="E49" s="146" t="n"/>
-      <c r="F49" s="147" t="n"/>
-      <c r="G49" s="148" t="n"/>
-      <c r="H49" s="149" t="n"/>
-      <c r="I49" s="149" t="n"/>
-      <c r="J49" s="149" t="n"/>
-    </row>
-    <row r="50" ht="56" customHeight="1" s="132">
-      <c r="A50" s="29" t="n"/>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="C49" s="54" t="n"/>
+      <c r="D49" s="54" t="n"/>
+      <c r="E49" s="54" t="n"/>
+      <c r="F49" s="55" t="n"/>
+      <c r="G49" s="66" t="n"/>
+      <c r="H49" s="67" t="n"/>
+      <c r="I49" s="67" t="n"/>
+      <c r="J49" s="67" t="n"/>
+    </row>
+    <row r="50" ht="56" customHeight="1" s="85">
+      <c r="A50" s="21" t="n"/>
+      <c r="B50" s="22" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C50" s="31" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>Contest</t>
         </is>
@@ -4163,56 +3527,56 @@
         </is>
       </c>
       <c r="E50" s="7" t="n"/>
-      <c r="F50" s="76" t="n">
+      <c r="F50" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="G50" s="130" t="inlineStr">
+      <c r="G50" s="80" t="inlineStr">
         <is>
           <t>1 def</t>
         </is>
       </c>
-      <c r="H50" s="102" t="n"/>
-      <c r="I50" s="102" t="n"/>
-      <c r="J50" s="102" t="n"/>
-    </row>
-    <row r="51" ht="47" customHeight="1" s="132">
-      <c r="A51" s="29" t="n"/>
-      <c r="B51" s="30" t="inlineStr">
+      <c r="H50" s="71" t="n"/>
+      <c r="I50" s="71" t="n"/>
+      <c r="J50" s="71" t="n"/>
+    </row>
+    <row r="51" ht="47" customHeight="1" s="85">
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="22" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C51" s="32" t="inlineStr">
+      <c r="C51" s="24" t="inlineStr">
         <is>
           <t>Double-Team</t>
         </is>
       </c>
-      <c r="D51" s="33" t="inlineStr">
+      <c r="D51" s="25" t="inlineStr">
         <is>
           <t>Next Player cannot play 2 random cards from hand.</t>
         </is>
       </c>
-      <c r="E51" s="34" t="n"/>
-      <c r="F51" s="75" t="n">
+      <c r="E51" s="26" t="n"/>
+      <c r="F51" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="G51" s="125" t="inlineStr">
+      <c r="G51" s="77" t="inlineStr">
         <is>
           <t>2 def</t>
         </is>
       </c>
-      <c r="H51" s="102" t="n"/>
-      <c r="I51" s="102" t="n"/>
-      <c r="J51" s="102" t="n"/>
-    </row>
-    <row r="52" ht="54" customHeight="1" s="132">
-      <c r="A52" s="29" t="n"/>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="H51" s="71" t="n"/>
+      <c r="I51" s="71" t="n"/>
+      <c r="J51" s="71" t="n"/>
+    </row>
+    <row r="52" ht="54" customHeight="1" s="85">
+      <c r="A52" s="21" t="n"/>
+      <c r="B52" s="22" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C52" s="31" t="inlineStr">
+      <c r="C52" s="23" t="inlineStr">
         <is>
           <t>Full-Court Press</t>
         </is>
@@ -4223,109 +3587,109 @@
         </is>
       </c>
       <c r="E52" s="7" t="n"/>
-      <c r="F52" s="76" t="n">
+      <c r="F52" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G52" s="130" t="inlineStr">
+      <c r="G52" s="80" t="inlineStr">
         <is>
           <t>1 def</t>
         </is>
       </c>
-      <c r="H52" s="102" t="n"/>
-      <c r="I52" s="102" t="n"/>
-      <c r="J52" s="102" t="n"/>
-    </row>
-    <row r="53" ht="28" customHeight="1" s="132">
-      <c r="A53" s="29" t="n"/>
-      <c r="B53" s="30" t="inlineStr">
+      <c r="H52" s="71" t="n"/>
+      <c r="I52" s="71" t="n"/>
+      <c r="J52" s="71" t="n"/>
+    </row>
+    <row r="53" ht="28" customHeight="1" s="85">
+      <c r="A53" s="21" t="n"/>
+      <c r="B53" s="22" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C53" s="32" t="inlineStr">
+      <c r="C53" s="24" t="inlineStr">
         <is>
           <t>Trap</t>
         </is>
       </c>
-      <c r="D53" s="94" t="inlineStr">
+      <c r="D53" s="41" t="inlineStr">
         <is>
           <t>Next player can only play Pass cards during their turn</t>
         </is>
       </c>
-      <c r="E53" s="34" t="n"/>
-      <c r="F53" s="75" t="n">
+      <c r="E53" s="26" t="n"/>
+      <c r="F53" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="G53" s="125" t="inlineStr">
+      <c r="G53" s="77" t="inlineStr">
         <is>
           <t>They can still shoot as another option; 3 def</t>
         </is>
       </c>
-      <c r="H53" s="102" t="n"/>
-      <c r="I53" s="102" t="n"/>
-      <c r="J53" s="102" t="n"/>
-    </row>
-    <row r="54" ht="28" customHeight="1" s="132">
-      <c r="A54" s="35" t="n"/>
-      <c r="B54" s="36" t="inlineStr">
+      <c r="H53" s="71" t="n"/>
+      <c r="I53" s="71" t="n"/>
+      <c r="J53" s="71" t="n"/>
+    </row>
+    <row r="54" ht="28" customHeight="1" s="85">
+      <c r="A54" s="27" t="n"/>
+      <c r="B54" s="28" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C54" s="152" t="inlineStr">
+      <c r="C54" s="56" t="inlineStr">
         <is>
           <t>Triple-Team</t>
         </is>
       </c>
-      <c r="D54" s="153" t="inlineStr">
+      <c r="D54" s="57" t="inlineStr">
         <is>
           <t>Next player cannot play 3 random cards from hand.</t>
         </is>
       </c>
-      <c r="E54" s="154" t="n"/>
-      <c r="F54" s="155" t="n">
+      <c r="E54" s="58" t="n"/>
+      <c r="F54" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="157" t="inlineStr">
+      <c r="G54" s="83" t="inlineStr">
         <is>
           <t>3 def</t>
         </is>
       </c>
-      <c r="H54" s="151" t="n"/>
-      <c r="I54" s="151" t="n"/>
-      <c r="J54" s="151" t="n"/>
-    </row>
-    <row r="55" ht="28" customHeight="1" s="132">
-      <c r="A55" s="144" t="inlineStr">
+      <c r="H54" s="76" t="n"/>
+      <c r="I54" s="76" t="n"/>
+      <c r="J54" s="76" t="n"/>
+    </row>
+    <row r="55" ht="28" customHeight="1" s="85">
+      <c r="A55" s="52" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="B55" s="145">
+      <c r="B55" s="53">
         <f>COUNTIF($B$56:$B$136,"Whistle")</f>
         <v/>
       </c>
-      <c r="C55" s="146" t="n"/>
-      <c r="D55" s="146" t="n"/>
-      <c r="E55" s="146" t="n"/>
-      <c r="F55" s="147" t="n"/>
-      <c r="G55" s="148" t="n"/>
-      <c r="H55" s="149" t="n"/>
-      <c r="I55" s="149" t="n"/>
-      <c r="J55" s="149" t="n"/>
-    </row>
-    <row r="56" ht="42" customHeight="1" s="132">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="C55" s="54" t="n"/>
+      <c r="D55" s="54" t="n"/>
+      <c r="E55" s="54" t="n"/>
+      <c r="F55" s="55" t="n"/>
+      <c r="G55" s="66" t="n"/>
+      <c r="H55" s="67" t="n"/>
+      <c r="I55" s="67" t="n"/>
+      <c r="J55" s="67" t="n"/>
+    </row>
+    <row r="56" ht="42" customHeight="1" s="85">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>All whistles are limited to 1</t>
         </is>
       </c>
-      <c r="B56" s="30" t="inlineStr">
+      <c r="B56" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C56" s="31" t="inlineStr">
+      <c r="C56" s="23" t="inlineStr">
         <is>
           <t>Back Court Violation</t>
         </is>
@@ -4336,96 +3700,96 @@
         </is>
       </c>
       <c r="E56" s="7" t="n"/>
-      <c r="F56" s="138" t="n"/>
-      <c r="G56" s="101" t="inlineStr">
+      <c r="F56" s="50" t="n"/>
+      <c r="G56" s="70" t="inlineStr">
         <is>
           <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
         </is>
       </c>
-      <c r="H56" s="102" t="n"/>
-      <c r="I56" s="102" t="n"/>
-      <c r="J56" s="102" t="n"/>
-    </row>
-    <row r="57" ht="40" customHeight="1" s="132">
-      <c r="A57" s="29" t="n"/>
-      <c r="B57" s="30" t="inlineStr">
+      <c r="H56" s="71" t="n"/>
+      <c r="I56" s="71" t="n"/>
+      <c r="J56" s="71" t="n"/>
+    </row>
+    <row r="57" ht="40" customHeight="1" s="85">
+      <c r="A57" s="21" t="n"/>
+      <c r="B57" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C57" s="90" t="inlineStr">
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>Blocking Foul</t>
         </is>
       </c>
-      <c r="D57" s="93" t="inlineStr">
+      <c r="D57" s="40" t="inlineStr">
         <is>
           <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
         </is>
       </c>
-      <c r="E57" s="34" t="n"/>
-      <c r="F57" s="138" t="n"/>
-      <c r="G57" s="107" t="n"/>
-      <c r="H57" s="102" t="n"/>
-      <c r="I57" s="102" t="n"/>
-      <c r="J57" s="102" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1" s="132">
-      <c r="A58" s="29" t="n"/>
-      <c r="B58" s="30" t="inlineStr">
+      <c r="E57" s="26" t="n"/>
+      <c r="F57" s="50" t="n"/>
+      <c r="G57" s="72" t="n"/>
+      <c r="H57" s="71" t="n"/>
+      <c r="I57" s="71" t="n"/>
+      <c r="J57" s="71" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1" s="85">
+      <c r="A58" s="21" t="n"/>
+      <c r="B58" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C58" s="31" t="inlineStr">
+      <c r="C58" s="23" t="inlineStr">
         <is>
           <t>Charge</t>
         </is>
       </c>
-      <c r="D58" s="92" t="inlineStr">
+      <c r="D58" s="39" t="inlineStr">
         <is>
           <t>Shot Attempt: Cancel. Shooter Inbounds</t>
         </is>
       </c>
       <c r="E58" s="7" t="n"/>
-      <c r="F58" s="138" t="n"/>
-      <c r="G58" s="101" t="n"/>
-      <c r="H58" s="102" t="n"/>
-      <c r="I58" s="102" t="n"/>
-      <c r="J58" s="102" t="n"/>
-    </row>
-    <row r="59" ht="56" customHeight="1" s="132">
-      <c r="A59" s="29" t="n"/>
-      <c r="B59" s="30" t="inlineStr">
+      <c r="F58" s="50" t="n"/>
+      <c r="G58" s="70" t="n"/>
+      <c r="H58" s="71" t="n"/>
+      <c r="I58" s="71" t="n"/>
+      <c r="J58" s="71" t="n"/>
+    </row>
+    <row r="59" ht="56" customHeight="1" s="85">
+      <c r="A59" s="21" t="n"/>
+      <c r="B59" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C59" s="32" t="inlineStr">
+      <c r="C59" s="24" t="inlineStr">
         <is>
           <t>Cleared to Play</t>
         </is>
       </c>
-      <c r="D59" s="33" t="inlineStr">
+      <c r="D59" s="25" t="inlineStr">
         <is>
           <t>Injury Card Played: Cancel card.</t>
         </is>
       </c>
-      <c r="E59" s="34" t="n"/>
-      <c r="F59" s="138" t="n"/>
-      <c r="G59" s="107" t="n"/>
-      <c r="H59" s="102" t="n"/>
-      <c r="I59" s="102" t="n"/>
-      <c r="J59" s="102" t="n"/>
-    </row>
-    <row r="60" ht="42" customHeight="1" s="132">
-      <c r="A60" s="29" t="n"/>
-      <c r="B60" s="30" t="inlineStr">
+      <c r="E59" s="26" t="n"/>
+      <c r="F59" s="50" t="n"/>
+      <c r="G59" s="72" t="n"/>
+      <c r="H59" s="71" t="n"/>
+      <c r="I59" s="71" t="n"/>
+      <c r="J59" s="71" t="n"/>
+    </row>
+    <row r="60" ht="42" customHeight="1" s="85">
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C60" s="31" t="inlineStr">
+      <c r="C60" s="23" t="inlineStr">
         <is>
           <t>Coach’s Challenge</t>
         </is>
@@ -4440,52 +3804,52 @@
           <t>Pull a Timeout from the discards, if one is there, and take it</t>
         </is>
       </c>
-      <c r="F60" s="138" t="n"/>
-      <c r="G60" s="101" t="n"/>
-      <c r="H60" s="102" t="n"/>
-      <c r="I60" s="102" t="n"/>
-      <c r="J60" s="102" t="n"/>
-    </row>
-    <row r="61" ht="42" customHeight="1" s="132">
-      <c r="A61" s="29" t="n"/>
-      <c r="B61" s="30" t="inlineStr">
+      <c r="F60" s="50" t="n"/>
+      <c r="G60" s="70" t="n"/>
+      <c r="H60" s="71" t="n"/>
+      <c r="I60" s="71" t="n"/>
+      <c r="J60" s="71" t="n"/>
+    </row>
+    <row r="61" ht="42" customHeight="1" s="85">
+      <c r="A61" s="21" t="n"/>
+      <c r="B61" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C61" s="90" t="inlineStr">
+      <c r="C61" s="37" t="inlineStr">
         <is>
           <t>Delay-of-Game Warning</t>
         </is>
       </c>
-      <c r="D61" s="94" t="inlineStr">
+      <c r="D61" s="41" t="inlineStr">
         <is>
           <t>Lower Shot Clock with a card: Cancel that card's effects</t>
         </is>
       </c>
-      <c r="E61" s="33" t="inlineStr">
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
         </is>
       </c>
-      <c r="F61" s="139" t="n"/>
-      <c r="G61" s="113" t="inlineStr">
+      <c r="F61" s="51" t="n"/>
+      <c r="G61" s="73" t="inlineStr">
         <is>
           <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
         </is>
       </c>
-      <c r="H61" s="102" t="n"/>
-      <c r="I61" s="102" t="n"/>
-      <c r="J61" s="102" t="n"/>
-    </row>
-    <row r="62" ht="42" customHeight="1" s="132">
-      <c r="A62" s="29" t="n"/>
-      <c r="B62" s="30" t="inlineStr">
+      <c r="H61" s="71" t="n"/>
+      <c r="I61" s="71" t="n"/>
+      <c r="J61" s="71" t="n"/>
+    </row>
+    <row r="62" ht="42" customHeight="1" s="85">
+      <c r="A62" s="21" t="n"/>
+      <c r="B62" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C62" s="31" t="inlineStr">
+      <c r="C62" s="23" t="inlineStr">
         <is>
           <t>Double Dribble</t>
         </is>
@@ -4496,369 +3860,369 @@
         </is>
       </c>
       <c r="E62" s="7" t="n"/>
-      <c r="F62" s="138" t="n"/>
-      <c r="G62" s="101" t="inlineStr">
+      <c r="F62" s="50" t="n"/>
+      <c r="G62" s="70" t="inlineStr">
         <is>
           <t>The dribbling player inbounds. The round is NOT incremented.</t>
         </is>
       </c>
-      <c r="H62" s="102" t="n"/>
-      <c r="I62" s="102" t="n"/>
-      <c r="J62" s="102" t="n"/>
-    </row>
-    <row r="63" ht="28" customHeight="1" s="132">
-      <c r="A63" s="29" t="n"/>
-      <c r="B63" s="30" t="inlineStr">
+      <c r="H62" s="71" t="n"/>
+      <c r="I62" s="71" t="n"/>
+      <c r="J62" s="71" t="n"/>
+    </row>
+    <row r="63" ht="28" customHeight="1" s="85">
+      <c r="A63" s="21" t="n"/>
+      <c r="B63" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C63" s="90" t="inlineStr">
+      <c r="C63" s="37" t="inlineStr">
         <is>
           <t>Flagrant Foul</t>
         </is>
       </c>
-      <c r="D63" s="94" t="inlineStr">
+      <c r="D63" s="41" t="inlineStr">
         <is>
           <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
         </is>
       </c>
-      <c r="E63" s="34" t="n"/>
-      <c r="F63" s="138" t="n"/>
-      <c r="G63" s="107" t="n"/>
-      <c r="H63" s="102" t="n"/>
-      <c r="I63" s="102" t="n"/>
-      <c r="J63" s="102" t="n"/>
-    </row>
-    <row r="64" ht="42" customHeight="1" s="132">
-      <c r="A64" s="29" t="n"/>
-      <c r="B64" s="30" t="inlineStr">
+      <c r="E63" s="26" t="n"/>
+      <c r="F63" s="50" t="n"/>
+      <c r="G63" s="72" t="n"/>
+      <c r="H63" s="71" t="n"/>
+      <c r="I63" s="71" t="n"/>
+      <c r="J63" s="71" t="n"/>
+    </row>
+    <row r="64" ht="42" customHeight="1" s="85">
+      <c r="A64" s="21" t="n"/>
+      <c r="B64" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C64" s="90" t="inlineStr">
+      <c r="C64" s="37" t="inlineStr">
         <is>
           <t>Flagrant Foul II</t>
         </is>
       </c>
-      <c r="D64" s="91" t="inlineStr">
+      <c r="D64" s="38" t="inlineStr">
         <is>
           <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
         </is>
       </c>
       <c r="E64" s="7" t="n"/>
-      <c r="F64" s="138" t="n"/>
-      <c r="G64" s="101" t="n"/>
-      <c r="H64" s="102" t="n"/>
-      <c r="I64" s="102" t="n"/>
-      <c r="J64" s="102" t="n"/>
-    </row>
-    <row r="65" ht="29" customHeight="1" s="132">
-      <c r="A65" s="29" t="n"/>
-      <c r="B65" s="30" t="inlineStr">
+      <c r="F64" s="50" t="n"/>
+      <c r="G64" s="70" t="n"/>
+      <c r="H64" s="71" t="n"/>
+      <c r="I64" s="71" t="n"/>
+      <c r="J64" s="71" t="n"/>
+    </row>
+    <row r="65" ht="29" customHeight="1" s="85">
+      <c r="A65" s="21" t="n"/>
+      <c r="B65" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C65" s="32" t="inlineStr">
+      <c r="C65" s="24" t="inlineStr">
         <is>
           <t>Goaltending</t>
         </is>
       </c>
-      <c r="D65" s="33" t="inlineStr">
+      <c r="D65" s="25" t="inlineStr">
         <is>
           <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
         </is>
       </c>
-      <c r="E65" s="34" t="n"/>
-      <c r="F65" s="138" t="n"/>
-      <c r="G65" s="107" t="n"/>
-      <c r="H65" s="102" t="n"/>
-      <c r="I65" s="102" t="n"/>
-      <c r="J65" s="102" t="n"/>
-    </row>
-    <row r="66" ht="20" customHeight="1" s="132">
-      <c r="A66" s="29" t="n"/>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="E65" s="26" t="n"/>
+      <c r="F65" s="50" t="n"/>
+      <c r="G65" s="72" t="n"/>
+      <c r="H65" s="71" t="n"/>
+      <c r="I65" s="71" t="n"/>
+      <c r="J65" s="71" t="n"/>
+    </row>
+    <row r="66" ht="20" customHeight="1" s="85">
+      <c r="A66" s="21" t="n"/>
+      <c r="B66" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C66" s="31" t="inlineStr">
+      <c r="C66" s="23" t="inlineStr">
         <is>
           <t>Inadvertent Whistle</t>
         </is>
       </c>
-      <c r="D66" s="91" t="inlineStr">
+      <c r="D66" s="38" t="inlineStr">
         <is>
           <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
         </is>
       </c>
       <c r="E66" s="7" t="n"/>
-      <c r="F66" s="138" t="n"/>
-      <c r="G66" s="101" t="n"/>
-      <c r="H66" s="102" t="n"/>
-      <c r="I66" s="102" t="n"/>
-      <c r="J66" s="102" t="n"/>
-    </row>
-    <row r="67" ht="28" customHeight="1" s="132">
-      <c r="A67" s="29" t="n"/>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="F66" s="50" t="n"/>
+      <c r="G66" s="70" t="n"/>
+      <c r="H66" s="71" t="n"/>
+      <c r="I66" s="71" t="n"/>
+      <c r="J66" s="71" t="n"/>
+    </row>
+    <row r="67" ht="28" customHeight="1" s="85">
+      <c r="A67" s="21" t="n"/>
+      <c r="B67" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C67" s="32" t="inlineStr">
+      <c r="C67" s="24" t="inlineStr">
         <is>
           <t>Official Review</t>
         </is>
       </c>
-      <c r="D67" s="94" t="inlineStr">
+      <c r="D67" s="41" t="inlineStr">
         <is>
           <t>Intangible Played: Discard all Intangibles from player.</t>
         </is>
       </c>
-      <c r="E67" s="34" t="n"/>
-      <c r="F67" s="138" t="n"/>
-      <c r="G67" s="107" t="n"/>
-      <c r="H67" s="102" t="n"/>
-      <c r="I67" s="102" t="n"/>
-      <c r="J67" s="102" t="n"/>
-    </row>
-    <row r="68" ht="28" customHeight="1" s="132">
-      <c r="A68" s="29" t="n"/>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="E67" s="26" t="n"/>
+      <c r="F67" s="50" t="n"/>
+      <c r="G67" s="72" t="n"/>
+      <c r="H67" s="71" t="n"/>
+      <c r="I67" s="71" t="n"/>
+      <c r="J67" s="71" t="n"/>
+    </row>
+    <row r="68" ht="28" customHeight="1" s="85">
+      <c r="A68" s="21" t="n"/>
+      <c r="B68" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C68" s="31" t="inlineStr">
+      <c r="C68" s="23" t="inlineStr">
         <is>
           <t>Shot Clock Violation</t>
         </is>
       </c>
-      <c r="D68" s="91" t="inlineStr">
+      <c r="D68" s="38" t="inlineStr">
         <is>
           <t>Shot Clock is changed: TOV +1. Ball OOB</t>
         </is>
       </c>
       <c r="E68" s="7" t="n"/>
-      <c r="F68" s="138" t="n"/>
-      <c r="G68" s="101" t="inlineStr">
+      <c r="F68" s="50" t="n"/>
+      <c r="G68" s="70" t="inlineStr">
         <is>
           <t>This inbound does NOT increment the round.</t>
         </is>
       </c>
-      <c r="H68" s="102" t="n"/>
-      <c r="I68" s="102" t="n"/>
-      <c r="J68" s="102" t="n"/>
-    </row>
-    <row r="69" ht="14" customHeight="1" s="132">
-      <c r="A69" s="29" t="n"/>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="H68" s="71" t="n"/>
+      <c r="I68" s="71" t="n"/>
+      <c r="J68" s="71" t="n"/>
+    </row>
+    <row r="69" ht="14" customHeight="1" s="85">
+      <c r="A69" s="21" t="n"/>
+      <c r="B69" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C69" s="32" t="inlineStr">
+      <c r="C69" s="24" t="inlineStr">
         <is>
           <t>Technical Foul</t>
         </is>
       </c>
-      <c r="D69" s="94" t="inlineStr">
+      <c r="D69" s="41" t="inlineStr">
         <is>
           <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
         </is>
       </c>
-      <c r="E69" s="34" t="n"/>
-      <c r="F69" s="138" t="n"/>
-      <c r="G69" s="107" t="n"/>
-      <c r="H69" s="102" t="n"/>
-      <c r="I69" s="102" t="n"/>
-      <c r="J69" s="102" t="n"/>
-    </row>
-    <row r="70" ht="14" customHeight="1" s="132">
-      <c r="A70" s="29" t="n"/>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="E69" s="26" t="n"/>
+      <c r="F69" s="50" t="n"/>
+      <c r="G69" s="72" t="n"/>
+      <c r="H69" s="71" t="n"/>
+      <c r="I69" s="71" t="n"/>
+      <c r="J69" s="71" t="n"/>
+    </row>
+    <row r="70" ht="14" customHeight="1" s="85">
+      <c r="A70" s="21" t="n"/>
+      <c r="B70" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C70" s="31" t="inlineStr">
+      <c r="C70" s="23" t="inlineStr">
         <is>
           <t>Timeout</t>
         </is>
       </c>
-      <c r="D70" s="91" t="inlineStr">
+      <c r="D70" s="38" t="inlineStr">
         <is>
           <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
         </is>
       </c>
       <c r="E70" s="7" t="n"/>
-      <c r="F70" s="138" t="n"/>
-      <c r="G70" s="101" t="n"/>
-      <c r="H70" s="102" t="n"/>
-      <c r="I70" s="102" t="n"/>
-      <c r="J70" s="102" t="n"/>
-    </row>
-    <row r="71" ht="14" customHeight="1" s="132">
-      <c r="A71" s="29" t="n"/>
-      <c r="B71" s="30" t="inlineStr">
+      <c r="F70" s="50" t="n"/>
+      <c r="G70" s="70" t="n"/>
+      <c r="H70" s="71" t="n"/>
+      <c r="I70" s="71" t="n"/>
+      <c r="J70" s="71" t="n"/>
+    </row>
+    <row r="71" ht="14" customHeight="1" s="85">
+      <c r="A71" s="21" t="n"/>
+      <c r="B71" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C71" s="32" t="inlineStr">
+      <c r="C71" s="24" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="D71" s="33" t="inlineStr">
+      <c r="D71" s="25" t="inlineStr">
         <is>
           <t>Move card played: Cancel card. TOV +1</t>
         </is>
       </c>
-      <c r="E71" s="34" t="n"/>
-      <c r="F71" s="138" t="n"/>
-      <c r="G71" s="107" t="n"/>
-      <c r="H71" s="102" t="n"/>
-      <c r="I71" s="102" t="n"/>
-      <c r="J71" s="102" t="n"/>
-    </row>
-    <row r="72" ht="28" customHeight="1" s="132">
-      <c r="A72" s="29" t="n"/>
-      <c r="B72" s="30" t="inlineStr">
+      <c r="E71" s="26" t="n"/>
+      <c r="F71" s="50" t="n"/>
+      <c r="G71" s="72" t="n"/>
+      <c r="H71" s="71" t="n"/>
+      <c r="I71" s="71" t="n"/>
+      <c r="J71" s="71" t="n"/>
+    </row>
+    <row r="72" ht="28" customHeight="1" s="85">
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C72" s="32" t="inlineStr">
+      <c r="C72" s="24" t="inlineStr">
         <is>
           <t>Clear Path Foul</t>
         </is>
       </c>
-      <c r="D72" s="33" t="inlineStr">
+      <c r="D72" s="25" t="inlineStr">
         <is>
           <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
         </is>
       </c>
-      <c r="E72" s="34" t="n"/>
-      <c r="F72" s="138" t="n"/>
-      <c r="G72" s="107" t="inlineStr">
+      <c r="E72" s="26" t="n"/>
+      <c r="F72" s="50" t="n"/>
+      <c r="G72" s="72" t="inlineStr">
         <is>
           <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
         </is>
       </c>
-      <c r="H72" s="102" t="n"/>
-      <c r="I72" s="102" t="n"/>
-      <c r="J72" s="102" t="n"/>
-    </row>
-    <row r="73" ht="28" customHeight="1" s="132">
-      <c r="A73" s="29" t="n"/>
-      <c r="B73" s="30" t="inlineStr">
+      <c r="H72" s="71" t="n"/>
+      <c r="I72" s="71" t="n"/>
+      <c r="J72" s="71" t="n"/>
+    </row>
+    <row r="73" ht="28" customHeight="1" s="85">
+      <c r="A73" s="21" t="n"/>
+      <c r="B73" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C73" s="32" t="inlineStr">
+      <c r="C73" s="24" t="inlineStr">
         <is>
           <t>Play-On</t>
         </is>
       </c>
-      <c r="D73" s="33" t="inlineStr">
+      <c r="D73" s="25" t="inlineStr">
         <is>
           <t>Discard each Game Break drawn and draw again, until a card is not one</t>
         </is>
       </c>
-      <c r="E73" s="34" t="n"/>
-      <c r="F73" s="138" t="n"/>
-      <c r="G73" s="107" t="inlineStr">
+      <c r="E73" s="26" t="n"/>
+      <c r="F73" s="50" t="n"/>
+      <c r="G73" s="72" t="inlineStr">
         <is>
           <t>Raised where the Break lands, like Cleared to Play — nobody plays a Break</t>
         </is>
       </c>
-      <c r="H73" s="102" t="n"/>
-      <c r="I73" s="102" t="n"/>
-      <c r="J73" s="102" t="n"/>
-    </row>
-    <row r="74" ht="28" customHeight="1" s="132">
-      <c r="A74" s="35" t="n"/>
-      <c r="B74" s="36" t="inlineStr">
+      <c r="H73" s="71" t="n"/>
+      <c r="I73" s="71" t="n"/>
+      <c r="J73" s="71" t="n"/>
+    </row>
+    <row r="74" ht="28" customHeight="1" s="85">
+      <c r="A74" s="27" t="n"/>
+      <c r="B74" s="28" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C74" s="37" t="inlineStr">
+      <c r="C74" s="29" t="inlineStr">
         <is>
           <t>Crew Chief Review</t>
         </is>
       </c>
-      <c r="D74" s="38" t="inlineStr">
+      <c r="D74" s="30" t="inlineStr">
         <is>
           <t>Cancel a pass. The ball comes to you</t>
         </is>
       </c>
-      <c r="E74" s="158" t="n"/>
-      <c r="F74" s="159" t="n"/>
-      <c r="G74" s="150" t="n"/>
-      <c r="H74" s="151" t="n"/>
-      <c r="I74" s="151" t="n"/>
-      <c r="J74" s="151" t="n"/>
-    </row>
-    <row r="75" ht="28" customHeight="1" s="132">
-      <c r="A75" s="144" t="inlineStr">
+      <c r="E74" s="60" t="n"/>
+      <c r="F74" s="61" t="n"/>
+      <c r="G74" s="78" t="n"/>
+      <c r="H74" s="76" t="n"/>
+      <c r="I74" s="76" t="n"/>
+      <c r="J74" s="76" t="n"/>
+    </row>
+    <row r="75" ht="28" customHeight="1" s="85">
+      <c r="A75" s="52" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B75" s="145">
+      <c r="B75" s="53">
         <f>COUNTIF($B$76:$B$136,"Game Break")</f>
         <v/>
       </c>
-      <c r="C75" s="146" t="n"/>
-      <c r="D75" s="146" t="n"/>
-      <c r="E75" s="146" t="n"/>
-      <c r="F75" s="147" t="n"/>
-      <c r="G75" s="148" t="n"/>
-      <c r="H75" s="149" t="n"/>
-      <c r="I75" s="149" t="n"/>
-      <c r="J75" s="149" t="n"/>
-    </row>
-    <row r="76" ht="28" customHeight="1" s="132">
-      <c r="A76" s="29" t="n"/>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="C75" s="54" t="n"/>
+      <c r="D75" s="54" t="n"/>
+      <c r="E75" s="54" t="n"/>
+      <c r="F75" s="55" t="n"/>
+      <c r="G75" s="66" t="n"/>
+      <c r="H75" s="67" t="n"/>
+      <c r="I75" s="67" t="n"/>
+      <c r="J75" s="67" t="n"/>
+    </row>
+    <row r="76" ht="28" customHeight="1" s="85">
+      <c r="A76" s="21" t="n"/>
+      <c r="B76" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C76" s="32" t="inlineStr">
+      <c r="C76" s="24" t="inlineStr">
         <is>
           <t>2-Minute Warning</t>
         </is>
       </c>
-      <c r="D76" s="33" t="inlineStr">
+      <c r="D76" s="25" t="inlineStr">
         <is>
           <t>All players discard down to 2 or fewer cards</t>
         </is>
       </c>
-      <c r="E76" s="34" t="n"/>
-      <c r="F76" s="75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G76" s="107" t="n"/>
-      <c r="H76" s="102" t="n"/>
-      <c r="I76" s="102" t="n"/>
-      <c r="J76" s="102" t="n"/>
-    </row>
-    <row r="77" ht="42" customHeight="1" s="132">
-      <c r="A77" s="29" t="n"/>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="E76" s="26" t="n"/>
+      <c r="F76" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" s="72" t="n"/>
+      <c r="H76" s="71" t="n"/>
+      <c r="I76" s="71" t="n"/>
+      <c r="J76" s="71" t="n"/>
+    </row>
+    <row r="77" ht="42" customHeight="1" s="85">
+      <c r="A77" s="21" t="n"/>
+      <c r="B77" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C77" s="31" t="inlineStr">
+      <c r="C77" s="23" t="inlineStr">
         <is>
           <t>Benched</t>
         </is>
@@ -4869,52 +4233,52 @@
         </is>
       </c>
       <c r="E77" s="7" t="n"/>
-      <c r="F77" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G77" s="111" t="inlineStr">
+      <c r="F77" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="74" t="inlineStr">
         <is>
           <t>This is not a pass</t>
         </is>
       </c>
-      <c r="H77" s="102" t="n"/>
-      <c r="I77" s="102" t="n"/>
-      <c r="J77" s="102" t="n"/>
-    </row>
-    <row r="78" ht="28" customHeight="1" s="132">
-      <c r="A78" s="29" t="n"/>
-      <c r="B78" s="30" t="inlineStr">
+      <c r="H77" s="71" t="n"/>
+      <c r="I77" s="71" t="n"/>
+      <c r="J77" s="71" t="n"/>
+    </row>
+    <row r="78" ht="28" customHeight="1" s="85">
+      <c r="A78" s="21" t="n"/>
+      <c r="B78" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C78" s="32" t="inlineStr">
+      <c r="C78" s="24" t="inlineStr">
         <is>
           <t>Crowd Noise</t>
         </is>
       </c>
-      <c r="D78" s="33" t="inlineStr">
+      <c r="D78" s="25" t="inlineStr">
         <is>
           <t>Discard 1 card.</t>
         </is>
       </c>
-      <c r="E78" s="34" t="n"/>
-      <c r="F78" s="75" t="n">
-        <v>14</v>
-      </c>
-      <c r="G78" s="107" t="n"/>
-      <c r="H78" s="102" t="n"/>
-      <c r="I78" s="102" t="n"/>
-      <c r="J78" s="102" t="n"/>
-    </row>
-    <row r="79" ht="28" customHeight="1" s="132">
-      <c r="A79" s="29" t="n"/>
-      <c r="B79" s="30" t="inlineStr">
+      <c r="E78" s="26" t="n"/>
+      <c r="F78" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" s="72" t="n"/>
+      <c r="H78" s="71" t="n"/>
+      <c r="I78" s="71" t="n"/>
+      <c r="J78" s="71" t="n"/>
+    </row>
+    <row r="79" ht="28" customHeight="1" s="85">
+      <c r="A79" s="21" t="n"/>
+      <c r="B79" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C79" s="31" t="inlineStr">
+      <c r="C79" s="23" t="inlineStr">
         <is>
           <t>Designed Play</t>
         </is>
@@ -4925,48 +4289,48 @@
         </is>
       </c>
       <c r="E79" s="7" t="n"/>
-      <c r="F79" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="G79" s="101" t="n"/>
-      <c r="H79" s="102" t="n"/>
-      <c r="I79" s="102" t="n"/>
-      <c r="J79" s="102" t="n"/>
-    </row>
-    <row r="80" ht="20" customHeight="1" s="132">
-      <c r="A80" s="29" t="n"/>
-      <c r="B80" s="30" t="inlineStr">
+      <c r="F79" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="70" t="n"/>
+      <c r="H79" s="71" t="n"/>
+      <c r="I79" s="71" t="n"/>
+      <c r="J79" s="71" t="n"/>
+    </row>
+    <row r="80" ht="20" customHeight="1" s="85">
+      <c r="A80" s="21" t="n"/>
+      <c r="B80" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C80" s="90" t="inlineStr">
+      <c r="C80" s="37" t="inlineStr">
         <is>
           <t>Foul</t>
         </is>
       </c>
-      <c r="D80" s="33" t="inlineStr">
+      <c r="D80" s="25" t="inlineStr">
         <is>
           <t>Take 1 FT</t>
         </is>
       </c>
-      <c r="E80" s="34" t="n"/>
-      <c r="F80" s="75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G80" s="107" t="n"/>
-      <c r="H80" s="102" t="n"/>
-      <c r="I80" s="102" t="n"/>
-      <c r="J80" s="102" t="n"/>
-    </row>
-    <row r="81" ht="28" customHeight="1" s="132">
-      <c r="A81" s="29" t="n"/>
-      <c r="B81" s="30" t="inlineStr">
+      <c r="E80" s="26" t="n"/>
+      <c r="F80" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" s="72" t="n"/>
+      <c r="H80" s="71" t="n"/>
+      <c r="I80" s="71" t="n"/>
+      <c r="J80" s="71" t="n"/>
+    </row>
+    <row r="81" ht="28" customHeight="1" s="85">
+      <c r="A81" s="21" t="n"/>
+      <c r="B81" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C81" s="31" t="inlineStr">
+      <c r="C81" s="23" t="inlineStr">
         <is>
           <t>MVP Vote</t>
         </is>
@@ -4977,48 +4341,48 @@
         </is>
       </c>
       <c r="E81" s="7" t="n"/>
-      <c r="F81" s="76" t="n">
+      <c r="F81" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="101" t="n"/>
-      <c r="H81" s="102" t="n"/>
-      <c r="I81" s="102" t="n"/>
-      <c r="J81" s="102" t="n"/>
-    </row>
-    <row r="82" ht="20" customHeight="1" s="132">
-      <c r="A82" s="29" t="n"/>
-      <c r="B82" s="30" t="inlineStr">
+      <c r="G81" s="70" t="n"/>
+      <c r="H81" s="71" t="n"/>
+      <c r="I81" s="71" t="n"/>
+      <c r="J81" s="71" t="n"/>
+    </row>
+    <row r="82" ht="20" customHeight="1" s="85">
+      <c r="A82" s="21" t="n"/>
+      <c r="B82" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C82" s="32" t="inlineStr">
+      <c r="C82" s="24" t="inlineStr">
         <is>
           <t>Off Night</t>
         </is>
       </c>
-      <c r="D82" s="33" t="inlineStr">
+      <c r="D82" s="25" t="inlineStr">
         <is>
           <t>SHOT -20% this possession</t>
         </is>
       </c>
-      <c r="E82" s="34" t="n"/>
-      <c r="F82" s="75" t="n">
+      <c r="E82" s="26" t="n"/>
+      <c r="F82" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G82" s="107" t="n"/>
-      <c r="H82" s="102" t="n"/>
-      <c r="I82" s="102" t="n"/>
-      <c r="J82" s="102" t="n"/>
-    </row>
-    <row r="83" ht="42" customHeight="1" s="132">
-      <c r="A83" s="29" t="n"/>
-      <c r="B83" s="30" t="inlineStr">
+      <c r="G82" s="72" t="n"/>
+      <c r="H82" s="71" t="n"/>
+      <c r="I82" s="71" t="n"/>
+      <c r="J82" s="71" t="n"/>
+    </row>
+    <row r="83" ht="42" customHeight="1" s="85">
+      <c r="A83" s="21" t="n"/>
+      <c r="B83" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C83" s="31" t="inlineStr">
+      <c r="C83" s="23" t="inlineStr">
         <is>
           <t>Swallowed Whistle</t>
         </is>
@@ -5033,52 +4397,52 @@
           <t>Remains for remainder of round</t>
         </is>
       </c>
-      <c r="F83" s="74" t="n">
-        <v>5</v>
-      </c>
-      <c r="G83" s="101" t="n"/>
-      <c r="H83" s="102" t="n"/>
-      <c r="I83" s="102" t="n"/>
-      <c r="J83" s="102" t="n"/>
-    </row>
-    <row r="84" ht="28" customHeight="1" s="132">
-      <c r="A84" s="29" t="n"/>
-      <c r="B84" s="30" t="inlineStr">
+      <c r="F83" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" s="70" t="n"/>
+      <c r="H83" s="71" t="n"/>
+      <c r="I83" s="71" t="n"/>
+      <c r="J83" s="71" t="n"/>
+    </row>
+    <row r="84" ht="28" customHeight="1" s="85">
+      <c r="A84" s="21" t="n"/>
+      <c r="B84" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C84" s="32" t="inlineStr">
+      <c r="C84" s="24" t="inlineStr">
         <is>
           <t>Rock Fight</t>
         </is>
       </c>
-      <c r="D84" s="33" t="inlineStr">
+      <c r="D84" s="25" t="inlineStr">
         <is>
           <t>Players cannot shoot when SHOT is 50% or higher</t>
         </is>
       </c>
-      <c r="E84" s="33" t="inlineStr">
+      <c r="E84" s="25" t="inlineStr">
         <is>
           <t>Remains for remainder of round</t>
         </is>
       </c>
-      <c r="F84" s="80" t="n">
-        <v>4</v>
-      </c>
-      <c r="G84" s="107" t="n"/>
-      <c r="H84" s="102" t="n"/>
-      <c r="I84" s="102" t="n"/>
-      <c r="J84" s="102" t="n"/>
-    </row>
-    <row r="85" ht="56" customHeight="1" s="132">
-      <c r="A85" s="29" t="n"/>
-      <c r="B85" s="30" t="inlineStr">
+      <c r="F84" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="72" t="n"/>
+      <c r="H84" s="71" t="n"/>
+      <c r="I84" s="71" t="n"/>
+      <c r="J84" s="71" t="n"/>
+    </row>
+    <row r="85" ht="56" customHeight="1" s="85">
+      <c r="A85" s="21" t="n"/>
+      <c r="B85" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C85" s="31" t="inlineStr">
+      <c r="C85" s="23" t="inlineStr">
         <is>
           <t>Traded Mid-Game</t>
         </is>
@@ -5089,653 +4453,653 @@
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
-      <c r="F85" s="76" t="n"/>
-      <c r="G85" s="111" t="inlineStr">
+      <c r="F85" s="34" t="n"/>
+      <c r="G85" s="74" t="inlineStr">
         <is>
           <t>Applies to rest of game</t>
         </is>
       </c>
-      <c r="H85" s="102" t="n"/>
-      <c r="I85" s="102" t="n"/>
-      <c r="J85" s="102" t="n"/>
-    </row>
-    <row r="86" ht="42" customHeight="1" s="132">
-      <c r="A86" s="29" t="n"/>
-      <c r="B86" s="30" t="inlineStr">
+      <c r="H85" s="71" t="n"/>
+      <c r="I85" s="71" t="n"/>
+      <c r="J85" s="71" t="n"/>
+    </row>
+    <row r="86" ht="42" customHeight="1" s="85">
+      <c r="A86" s="21" t="n"/>
+      <c r="B86" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C86" s="134" t="inlineStr">
+      <c r="C86" s="49" t="inlineStr">
         <is>
           <t>Salary Cap Increase</t>
         </is>
       </c>
-      <c r="D86" s="91" t="inlineStr">
+      <c r="D86" s="38" t="inlineStr">
         <is>
           <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E86" s="7" t="n"/>
-      <c r="F86" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G86" s="111" t="n"/>
-      <c r="H86" s="102" t="n"/>
-      <c r="I86" s="102" t="n"/>
-      <c r="J86" s="102" t="n"/>
-    </row>
-    <row r="87" ht="42" customHeight="1" s="132">
-      <c r="A87" s="29" t="n"/>
-      <c r="B87" s="30" t="inlineStr">
+      <c r="F86" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" s="74" t="n"/>
+      <c r="H86" s="71" t="n"/>
+      <c r="I86" s="71" t="n"/>
+      <c r="J86" s="71" t="n"/>
+    </row>
+    <row r="87" ht="42" customHeight="1" s="85">
+      <c r="A87" s="21" t="n"/>
+      <c r="B87" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C87" s="134" t="inlineStr">
+      <c r="C87" s="49" t="inlineStr">
         <is>
           <t>All-Swissh Selection</t>
         </is>
       </c>
-      <c r="D87" s="91" t="inlineStr">
+      <c r="D87" s="38" t="inlineStr">
         <is>
           <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
-      <c r="F87" s="76" t="n">
+      <c r="F87" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G87" s="111" t="inlineStr">
+      <c r="G87" s="74" t="inlineStr">
         <is>
           <t>Arms an icon in the HUD tracking the pending draws</t>
         </is>
       </c>
-      <c r="H87" s="102" t="n"/>
-      <c r="I87" s="102" t="n"/>
-      <c r="J87" s="102" t="n"/>
-    </row>
-    <row r="88" ht="28" customHeight="1" s="132">
-      <c r="A88" s="29" t="n"/>
-      <c r="B88" s="30" t="inlineStr">
+      <c r="H87" s="71" t="n"/>
+      <c r="I87" s="71" t="n"/>
+      <c r="J87" s="71" t="n"/>
+    </row>
+    <row r="88" ht="28" customHeight="1" s="85">
+      <c r="A88" s="21" t="n"/>
+      <c r="B88" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C88" s="134" t="inlineStr">
+      <c r="C88" s="49" t="inlineStr">
         <is>
           <t>All Star Selection</t>
         </is>
       </c>
-      <c r="D88" s="91" t="inlineStr">
+      <c r="D88" s="38" t="inlineStr">
         <is>
           <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
-      <c r="F88" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G88" s="111" t="n"/>
-      <c r="H88" s="102" t="n"/>
-      <c r="I88" s="102" t="n"/>
-      <c r="J88" s="102" t="n"/>
-    </row>
-    <row r="89" ht="28" customHeight="1" s="132">
-      <c r="A89" s="29" t="n"/>
-      <c r="B89" s="30" t="inlineStr">
+      <c r="F88" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G88" s="74" t="n"/>
+      <c r="H88" s="71" t="n"/>
+      <c r="I88" s="71" t="n"/>
+      <c r="J88" s="71" t="n"/>
+    </row>
+    <row r="89" ht="28" customHeight="1" s="85">
+      <c r="A89" s="21" t="n"/>
+      <c r="B89" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C89" s="134" t="inlineStr">
+      <c r="C89" s="49" t="inlineStr">
         <is>
           <t>Hit the Bike</t>
         </is>
       </c>
-      <c r="D89" s="91" t="inlineStr">
+      <c r="D89" s="38" t="inlineStr">
         <is>
           <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G89" s="111" t="inlineStr">
+      <c r="F89" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" s="74" t="inlineStr">
         <is>
           <t>This is not a pass</t>
         </is>
       </c>
-      <c r="H89" s="102" t="n"/>
-      <c r="I89" s="102" t="n"/>
-      <c r="J89" s="102" t="n"/>
-    </row>
-    <row r="90" ht="56" customHeight="1" s="132">
-      <c r="A90" s="29" t="n"/>
-      <c r="B90" s="30" t="inlineStr">
+      <c r="H89" s="71" t="n"/>
+      <c r="I89" s="71" t="n"/>
+      <c r="J89" s="71" t="n"/>
+    </row>
+    <row r="90" ht="56" customHeight="1" s="85">
+      <c r="A90" s="21" t="n"/>
+      <c r="B90" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C90" s="134" t="inlineStr">
+      <c r="C90" s="49" t="inlineStr">
         <is>
           <t>Ice Wrap</t>
         </is>
       </c>
-      <c r="D90" s="91" t="inlineStr">
+      <c r="D90" s="38" t="inlineStr">
         <is>
           <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G90" s="111" t="n"/>
-      <c r="H90" s="102" t="n"/>
-      <c r="I90" s="102" t="n"/>
-      <c r="J90" s="102" t="n"/>
-    </row>
-    <row r="91" ht="56" customHeight="1" s="132">
-      <c r="A91" s="29" t="n"/>
-      <c r="B91" s="30" t="inlineStr">
+      <c r="F90" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G90" s="74" t="n"/>
+      <c r="H90" s="71" t="n"/>
+      <c r="I90" s="71" t="n"/>
+      <c r="J90" s="71" t="n"/>
+    </row>
+    <row r="91" ht="56" customHeight="1" s="85">
+      <c r="A91" s="21" t="n"/>
+      <c r="B91" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C91" s="134" t="inlineStr">
+      <c r="C91" s="49" t="inlineStr">
         <is>
           <t>Wet Spot</t>
         </is>
       </c>
-      <c r="D91" s="91" t="inlineStr">
+      <c r="D91" s="38" t="inlineStr">
         <is>
           <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G91" s="111" t="inlineStr">
+      <c r="F91" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G91" s="74" t="inlineStr">
         <is>
           <t>Deck ones are shown face down</t>
         </is>
       </c>
-      <c r="H91" s="102" t="n"/>
-      <c r="I91" s="102" t="n"/>
-      <c r="J91" s="102" t="n"/>
-    </row>
-    <row r="92" ht="28" customHeight="1" s="132">
-      <c r="A92" s="29" t="n"/>
-      <c r="B92" s="30" t="inlineStr">
+      <c r="H91" s="71" t="n"/>
+      <c r="I91" s="71" t="n"/>
+      <c r="J91" s="71" t="n"/>
+    </row>
+    <row r="92" ht="28" customHeight="1" s="85">
+      <c r="A92" s="21" t="n"/>
+      <c r="B92" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C92" s="134" t="inlineStr">
+      <c r="C92" s="49" t="inlineStr">
         <is>
           <t>Fresh Ball</t>
         </is>
       </c>
-      <c r="D92" s="91" t="inlineStr">
+      <c r="D92" s="38" t="inlineStr">
         <is>
           <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="76" t="n">
+      <c r="F92" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G92" s="111" t="inlineStr">
+      <c r="G92" s="74" t="inlineStr">
         <is>
           <t>This is a bad thing in the NBA</t>
         </is>
       </c>
-      <c r="H92" s="102" t="n"/>
-      <c r="I92" s="102" t="n"/>
-      <c r="J92" s="102" t="n"/>
-    </row>
-    <row r="93" ht="42" customHeight="1" s="132">
-      <c r="A93" s="29" t="n"/>
-      <c r="B93" s="30" t="inlineStr">
+      <c r="H92" s="71" t="n"/>
+      <c r="I92" s="71" t="n"/>
+      <c r="J92" s="71" t="n"/>
+    </row>
+    <row r="93" ht="42" customHeight="1" s="85">
+      <c r="A93" s="21" t="n"/>
+      <c r="B93" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C93" s="134" t="inlineStr">
+      <c r="C93" s="49" t="inlineStr">
         <is>
           <t>Trade Deadline</t>
         </is>
       </c>
-      <c r="D93" s="91" t="inlineStr">
+      <c r="D93" s="38" t="inlineStr">
         <is>
           <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="76" t="n">
+      <c r="F93" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G93" s="111" t="inlineStr">
+      <c r="G93" s="74" t="inlineStr">
         <is>
           <t>The hex travels in the declared direction too</t>
         </is>
       </c>
-      <c r="H93" s="102" t="n"/>
-      <c r="I93" s="102" t="n"/>
-      <c r="J93" s="102" t="n"/>
-    </row>
-    <row r="94" ht="28" customHeight="1" s="132">
-      <c r="A94" s="29" t="n"/>
-      <c r="B94" s="30" t="inlineStr">
+      <c r="H93" s="71" t="n"/>
+      <c r="I93" s="71" t="n"/>
+      <c r="J93" s="71" t="n"/>
+    </row>
+    <row r="94" ht="28" customHeight="1" s="85">
+      <c r="A94" s="21" t="n"/>
+      <c r="B94" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C94" s="134" t="inlineStr">
+      <c r="C94" s="49" t="inlineStr">
         <is>
           <t>Floor Cleanup</t>
         </is>
       </c>
-      <c r="D94" s="91" t="inlineStr">
+      <c r="D94" s="38" t="inlineStr">
         <is>
           <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
-      <c r="F94" s="76" t="n">
+      <c r="F94" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G94" s="111" t="n"/>
-      <c r="H94" s="102" t="n"/>
-      <c r="I94" s="102" t="n"/>
-      <c r="J94" s="102" t="n"/>
-    </row>
-    <row r="95" ht="42" customHeight="1" s="132">
-      <c r="A95" s="29" t="n"/>
-      <c r="B95" s="30" t="inlineStr">
+      <c r="G94" s="74" t="n"/>
+      <c r="H94" s="71" t="n"/>
+      <c r="I94" s="71" t="n"/>
+      <c r="J94" s="71" t="n"/>
+    </row>
+    <row r="95" ht="42" customHeight="1" s="85">
+      <c r="A95" s="21" t="n"/>
+      <c r="B95" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C95" s="134" t="inlineStr">
+      <c r="C95" s="49" t="inlineStr">
         <is>
           <t>Official Timeout</t>
         </is>
       </c>
-      <c r="D95" s="91" t="inlineStr">
+      <c r="D95" s="38" t="inlineStr">
         <is>
           <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G95" s="111" t="n"/>
-      <c r="H95" s="102" t="n"/>
-      <c r="I95" s="102" t="n"/>
-      <c r="J95" s="102" t="n"/>
-    </row>
-    <row r="96" ht="14" customHeight="1" s="132">
-      <c r="A96" s="29" t="n"/>
-      <c r="B96" s="30" t="inlineStr">
+      <c r="F95" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" s="74" t="n"/>
+      <c r="H95" s="71" t="n"/>
+      <c r="I95" s="71" t="n"/>
+      <c r="J95" s="71" t="n"/>
+    </row>
+    <row r="96" ht="14" customHeight="1" s="85">
+      <c r="A96" s="21" t="n"/>
+      <c r="B96" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C96" s="134" t="inlineStr">
+      <c r="C96" s="49" t="inlineStr">
         <is>
           <t>Team Doctor</t>
         </is>
       </c>
-      <c r="D96" s="91" t="inlineStr">
+      <c r="D96" s="38" t="inlineStr">
         <is>
           <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
-      <c r="F96" s="76" t="n">
+      <c r="F96" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G96" s="111" t="n"/>
-      <c r="H96" s="102" t="n"/>
-      <c r="I96" s="102" t="n"/>
-      <c r="J96" s="102" t="n"/>
-    </row>
-    <row r="97" ht="14" customHeight="1" s="132">
-      <c r="A97" s="29" t="n"/>
-      <c r="B97" s="30" t="inlineStr">
+      <c r="G96" s="74" t="n"/>
+      <c r="H96" s="71" t="n"/>
+      <c r="I96" s="71" t="n"/>
+      <c r="J96" s="71" t="n"/>
+    </row>
+    <row r="97" ht="14" customHeight="1" s="85">
+      <c r="A97" s="21" t="n"/>
+      <c r="B97" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C97" s="134" t="inlineStr">
+      <c r="C97" s="49" t="inlineStr">
         <is>
           <t>Altercation</t>
         </is>
       </c>
-      <c r="D97" s="91" t="inlineStr">
+      <c r="D97" s="38" t="inlineStr">
         <is>
           <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
-      <c r="F97" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G97" s="111" t="n"/>
-      <c r="H97" s="102" t="n"/>
-      <c r="I97" s="102" t="n"/>
-      <c r="J97" s="102" t="n"/>
-    </row>
-    <row r="98" ht="14" customHeight="1" s="132">
-      <c r="A98" s="29" t="n"/>
-      <c r="B98" s="30" t="inlineStr">
+      <c r="F97" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G97" s="74" t="n"/>
+      <c r="H97" s="71" t="n"/>
+      <c r="I97" s="71" t="n"/>
+      <c r="J97" s="71" t="n"/>
+    </row>
+    <row r="98" ht="14" customHeight="1" s="85">
+      <c r="A98" s="21" t="n"/>
+      <c r="B98" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C98" s="134" t="inlineStr">
+      <c r="C98" s="49" t="inlineStr">
         <is>
           <t>Huge Altercation</t>
         </is>
       </c>
-      <c r="D98" s="91" t="inlineStr">
+      <c r="D98" s="38" t="inlineStr">
         <is>
           <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
-      <c r="F98" s="76" t="n">
+      <c r="F98" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="G98" s="111" t="n"/>
-      <c r="H98" s="102" t="n"/>
-      <c r="I98" s="102" t="n"/>
-      <c r="J98" s="102" t="n"/>
-    </row>
-    <row r="99" ht="14" customHeight="1" s="132">
-      <c r="A99" s="29" t="n"/>
-      <c r="B99" s="30" t="inlineStr">
+      <c r="G98" s="74" t="n"/>
+      <c r="H98" s="71" t="n"/>
+      <c r="I98" s="71" t="n"/>
+      <c r="J98" s="71" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1" s="85">
+      <c r="A99" s="21" t="n"/>
+      <c r="B99" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C99" s="134" t="inlineStr">
+      <c r="C99" s="49" t="inlineStr">
         <is>
           <t>Home Court Advantage</t>
         </is>
       </c>
-      <c r="D99" s="91" t="inlineStr">
+      <c r="D99" s="38" t="inlineStr">
         <is>
           <t>SHOT + 10%</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G99" s="111" t="n"/>
-      <c r="H99" s="102" t="n"/>
-      <c r="I99" s="102" t="n"/>
-      <c r="J99" s="102" t="n"/>
-    </row>
-    <row r="100" ht="14" customHeight="1" s="132">
-      <c r="A100" s="29" t="n"/>
-      <c r="B100" s="30" t="inlineStr">
+      <c r="F99" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G99" s="74" t="n"/>
+      <c r="H99" s="71" t="n"/>
+      <c r="I99" s="71" t="n"/>
+      <c r="J99" s="71" t="n"/>
+    </row>
+    <row r="100" ht="14" customHeight="1" s="85">
+      <c r="A100" s="21" t="n"/>
+      <c r="B100" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C100" s="134" t="inlineStr">
+      <c r="C100" s="49" t="inlineStr">
         <is>
           <t>Away Game</t>
         </is>
       </c>
-      <c r="D100" s="91" t="inlineStr">
+      <c r="D100" s="38" t="inlineStr">
         <is>
           <t>SHOT - 10%</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
-      <c r="F100" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G100" s="111" t="n"/>
-      <c r="H100" s="102" t="n"/>
-      <c r="I100" s="102" t="n"/>
-      <c r="J100" s="102" t="n"/>
-    </row>
-    <row r="101" ht="14" customHeight="1" s="132">
-      <c r="A101" s="29" t="n"/>
-      <c r="B101" s="30" t="inlineStr">
+      <c r="F100" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" s="74" t="n"/>
+      <c r="H100" s="71" t="n"/>
+      <c r="I100" s="71" t="n"/>
+      <c r="J100" s="71" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1" s="85">
+      <c r="A101" s="21" t="n"/>
+      <c r="B101" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C101" s="134" t="inlineStr">
+      <c r="C101" s="49" t="inlineStr">
         <is>
           <t>Mic'd Up</t>
         </is>
       </c>
-      <c r="D101" s="91" t="inlineStr">
+      <c r="D101" s="38" t="inlineStr">
         <is>
           <t>SHOT + 10% until passed or shot</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
-      <c r="F101" s="76" t="n">
-        <v>7</v>
-      </c>
-      <c r="G101" s="111" t="inlineStr">
+      <c r="F101" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G101" s="74" t="inlineStr">
         <is>
           <t>The boost is the holder's alone and does not travel with a pass</t>
         </is>
       </c>
-      <c r="H101" s="102" t="n"/>
-      <c r="I101" s="102" t="n"/>
-      <c r="J101" s="102" t="n"/>
-    </row>
-    <row r="102" ht="14" customHeight="1" s="132">
-      <c r="A102" s="29" t="n"/>
-      <c r="B102" s="30" t="inlineStr">
+      <c r="H101" s="71" t="n"/>
+      <c r="I101" s="71" t="n"/>
+      <c r="J101" s="71" t="n"/>
+    </row>
+    <row r="102" ht="14" customHeight="1" s="85">
+      <c r="A102" s="21" t="n"/>
+      <c r="B102" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C102" s="134" t="inlineStr">
+      <c r="C102" s="49" t="inlineStr">
         <is>
           <t>In The Zone</t>
         </is>
       </c>
-      <c r="D102" s="91" t="inlineStr">
+      <c r="D102" s="38" t="inlineStr">
         <is>
           <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
-      <c r="F102" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G102" s="111" t="n"/>
-      <c r="H102" s="102" t="n"/>
-      <c r="I102" s="102" t="n"/>
-      <c r="J102" s="102" t="n"/>
-    </row>
-    <row r="103" ht="14" customHeight="1" s="132">
-      <c r="A103" s="29" t="n"/>
-      <c r="B103" s="30" t="inlineStr">
+      <c r="F102" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G102" s="74" t="n"/>
+      <c r="H102" s="71" t="n"/>
+      <c r="I102" s="71" t="n"/>
+      <c r="J102" s="71" t="n"/>
+    </row>
+    <row r="103" ht="14" customHeight="1" s="85">
+      <c r="A103" s="21" t="n"/>
+      <c r="B103" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C103" s="134" t="inlineStr">
+      <c r="C103" s="49" t="inlineStr">
         <is>
           <t>Role Player</t>
         </is>
       </c>
-      <c r="D103" s="91" t="inlineStr">
+      <c r="D103" s="38" t="inlineStr">
         <is>
           <t>All other players draw 1 card</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="G103" s="111" t="n"/>
-      <c r="H103" s="102" t="n"/>
-      <c r="I103" s="102" t="n"/>
-      <c r="J103" s="102" t="n"/>
-    </row>
-    <row r="104" ht="14" customHeight="1" s="132">
-      <c r="A104" s="35" t="n"/>
-      <c r="B104" s="36" t="inlineStr">
+      <c r="F103" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G103" s="74" t="n"/>
+      <c r="H103" s="71" t="n"/>
+      <c r="I103" s="71" t="n"/>
+      <c r="J103" s="71" t="n"/>
+    </row>
+    <row r="104" ht="14" customHeight="1" s="85">
+      <c r="A104" s="27" t="n"/>
+      <c r="B104" s="28" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C104" s="160" t="inlineStr">
+      <c r="C104" s="62" t="inlineStr">
         <is>
           <t>Back-and-Forth Game</t>
         </is>
       </c>
-      <c r="D104" s="161" t="inlineStr">
+      <c r="D104" s="63" t="inlineStr">
         <is>
           <t>Discard the next 3 Game Breaks. Whoever draws one draws again</t>
         </is>
       </c>
-      <c r="E104" s="154" t="n"/>
-      <c r="F104" s="155" t="n">
+      <c r="E104" s="58" t="n"/>
+      <c r="F104" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="G104" s="162" t="n"/>
-      <c r="H104" s="151" t="n"/>
-      <c r="I104" s="151" t="n"/>
-      <c r="J104" s="151" t="n"/>
-    </row>
-    <row r="105" ht="28" customHeight="1" s="132">
-      <c r="A105" s="144" t="inlineStr">
+      <c r="G104" s="79" t="n"/>
+      <c r="H104" s="76" t="n"/>
+      <c r="I104" s="76" t="n"/>
+      <c r="J104" s="76" t="n"/>
+    </row>
+    <row r="105" ht="28" customHeight="1" s="85">
+      <c r="A105" s="52" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="B105" s="145">
+      <c r="B105" s="53">
         <f>COUNTIF($B$106:$B$136,"Injury GB")</f>
         <v/>
       </c>
-      <c r="C105" s="146" t="n"/>
-      <c r="D105" s="146" t="n"/>
-      <c r="E105" s="146" t="n"/>
-      <c r="F105" s="147" t="n"/>
-      <c r="G105" s="148" t="n"/>
-      <c r="H105" s="149" t="n"/>
-      <c r="I105" s="149" t="n"/>
-      <c r="J105" s="149" t="n"/>
-    </row>
-    <row r="106" ht="28" customHeight="1" s="132">
-      <c r="A106" s="35" t="n"/>
-      <c r="B106" s="36" t="inlineStr">
+      <c r="C105" s="54" t="n"/>
+      <c r="D105" s="54" t="n"/>
+      <c r="E105" s="54" t="n"/>
+      <c r="F105" s="55" t="n"/>
+      <c r="G105" s="66" t="n"/>
+      <c r="H105" s="67" t="n"/>
+      <c r="I105" s="67" t="n"/>
+      <c r="J105" s="67" t="n"/>
+    </row>
+    <row r="106" ht="28" customHeight="1" s="85">
+      <c r="A106" s="27" t="n"/>
+      <c r="B106" s="28" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="C106" s="152" t="inlineStr">
+      <c r="C106" s="56" t="inlineStr">
         <is>
           <t>Bone Bruise</t>
         </is>
       </c>
-      <c r="D106" s="161" t="inlineStr">
+      <c r="D106" s="63" t="inlineStr">
         <is>
           <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
         </is>
       </c>
-      <c r="E106" s="154" t="n"/>
-      <c r="F106" s="155" t="n">
+      <c r="E106" s="58" t="n"/>
+      <c r="F106" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="G106" s="156" t="n"/>
-      <c r="H106" s="151" t="n"/>
-      <c r="I106" s="151" t="n"/>
-      <c r="J106" s="151" t="n"/>
-    </row>
-    <row r="107" ht="28" customHeight="1" s="132">
-      <c r="A107" s="144" t="inlineStr">
+      <c r="G106" s="75" t="n"/>
+      <c r="H106" s="76" t="n"/>
+      <c r="I106" s="76" t="n"/>
+      <c r="J106" s="76" t="n"/>
+    </row>
+    <row r="107" ht="28" customHeight="1" s="85">
+      <c r="A107" s="52" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="B107" s="145">
+      <c r="B107" s="53">
         <f>COUNTIF($B$108:$B$136,"Devastating Injury GB")</f>
         <v/>
       </c>
-      <c r="C107" s="146" t="n"/>
-      <c r="D107" s="146" t="n"/>
-      <c r="E107" s="146" t="n"/>
-      <c r="F107" s="147" t="n"/>
-      <c r="G107" s="148" t="n"/>
-      <c r="H107" s="149" t="n"/>
-      <c r="I107" s="149" t="n"/>
-      <c r="J107" s="149" t="n"/>
-    </row>
-    <row r="108" ht="28" customHeight="1" s="132">
-      <c r="A108" s="35" t="n"/>
-      <c r="B108" s="36" t="inlineStr">
+      <c r="C107" s="54" t="n"/>
+      <c r="D107" s="54" t="n"/>
+      <c r="E107" s="54" t="n"/>
+      <c r="F107" s="55" t="n"/>
+      <c r="G107" s="66" t="n"/>
+      <c r="H107" s="67" t="n"/>
+      <c r="I107" s="67" t="n"/>
+      <c r="J107" s="67" t="n"/>
+    </row>
+    <row r="108" ht="28" customHeight="1" s="85">
+      <c r="A108" s="27" t="n"/>
+      <c r="B108" s="28" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="C108" s="163" t="inlineStr">
+      <c r="C108" s="64" t="inlineStr">
         <is>
           <t>Torn Achilles</t>
         </is>
       </c>
-      <c r="D108" s="164" t="inlineStr">
+      <c r="D108" s="65" t="inlineStr">
         <is>
           <t>Hand is locked every turn except 1 card (randomly)</t>
         </is>
       </c>
-      <c r="E108" s="154" t="n"/>
-      <c r="F108" s="159" t="n"/>
-      <c r="G108" s="156" t="n"/>
-      <c r="H108" s="151" t="n"/>
-      <c r="I108" s="151" t="n"/>
-      <c r="J108" s="151" t="n"/>
-    </row>
-    <row r="109" ht="42" customHeight="1" s="132">
-      <c r="A109" s="144" t="inlineStr">
+      <c r="E108" s="58" t="n"/>
+      <c r="F108" s="61" t="n"/>
+      <c r="G108" s="75" t="n"/>
+      <c r="H108" s="76" t="n"/>
+      <c r="I108" s="76" t="n"/>
+      <c r="J108" s="76" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1" s="85">
+      <c r="A109" s="52" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B109" s="145">
+      <c r="B109" s="53">
         <f>COUNTIF($B$110:$B$136,"Intangible")</f>
         <v/>
       </c>
-      <c r="C109" s="146" t="n"/>
-      <c r="D109" s="146" t="n"/>
-      <c r="E109" s="146" t="n"/>
-      <c r="F109" s="147" t="n"/>
-      <c r="G109" s="148" t="n"/>
-      <c r="H109" s="149" t="n"/>
-      <c r="I109" s="149" t="n"/>
-      <c r="J109" s="149" t="n"/>
-    </row>
-    <row r="110" ht="56" customHeight="1" s="132">
-      <c r="A110" s="96" t="inlineStr">
+      <c r="C109" s="54" t="n"/>
+      <c r="D109" s="54" t="n"/>
+      <c r="E109" s="54" t="n"/>
+      <c r="F109" s="55" t="n"/>
+      <c r="G109" s="66" t="n"/>
+      <c r="H109" s="67" t="n"/>
+      <c r="I109" s="67" t="n"/>
+      <c r="J109" s="67" t="n"/>
+    </row>
+    <row r="110" ht="56" customHeight="1" s="85">
+      <c r="A110" s="42" t="inlineStr">
         <is>
           <t>All intangibles are limited to 1</t>
         </is>
       </c>
-      <c r="B110" s="30" t="inlineStr">
+      <c r="B110" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C110" s="31" t="inlineStr">
+      <c r="C110" s="23" t="inlineStr">
         <is>
           <t>Board-Crasher</t>
         </is>
@@ -5746,44 +5110,44 @@
         </is>
       </c>
       <c r="E110" s="7" t="n"/>
-      <c r="F110" s="138" t="n"/>
-      <c r="G110" s="101" t="n"/>
-      <c r="H110" s="102" t="n"/>
-      <c r="I110" s="102" t="n"/>
-      <c r="J110" s="102" t="n"/>
-    </row>
-    <row r="111" ht="57" customHeight="1" s="132">
-      <c r="A111" s="29" t="n"/>
-      <c r="B111" s="30" t="inlineStr">
+      <c r="F110" s="50" t="n"/>
+      <c r="G110" s="70" t="n"/>
+      <c r="H110" s="71" t="n"/>
+      <c r="I110" s="71" t="n"/>
+      <c r="J110" s="71" t="n"/>
+    </row>
+    <row r="111" ht="57" customHeight="1" s="85">
+      <c r="A111" s="21" t="n"/>
+      <c r="B111" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C111" s="32" t="inlineStr">
+      <c r="C111" s="24" t="inlineStr">
         <is>
           <t>Catch &amp; Shoot Specialist</t>
         </is>
       </c>
-      <c r="D111" s="33" t="inlineStr">
+      <c r="D111" s="25" t="inlineStr">
         <is>
           <t>Additional SHOT +10% on all received passes</t>
         </is>
       </c>
-      <c r="E111" s="34" t="n"/>
-      <c r="F111" s="138" t="n"/>
-      <c r="G111" s="107" t="n"/>
-      <c r="H111" s="102" t="n"/>
-      <c r="I111" s="102" t="n"/>
-      <c r="J111" s="102" t="n"/>
-    </row>
-    <row r="112" ht="20" customHeight="1" s="132">
-      <c r="A112" s="29" t="n"/>
-      <c r="B112" s="30" t="inlineStr">
+      <c r="E111" s="26" t="n"/>
+      <c r="F111" s="50" t="n"/>
+      <c r="G111" s="72" t="n"/>
+      <c r="H111" s="71" t="n"/>
+      <c r="I111" s="71" t="n"/>
+      <c r="J111" s="71" t="n"/>
+    </row>
+    <row r="112" ht="20" customHeight="1" s="85">
+      <c r="A112" s="21" t="n"/>
+      <c r="B112" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C112" s="31" t="inlineStr">
+      <c r="C112" s="23" t="inlineStr">
         <is>
           <t>Clutch Gene</t>
         </is>
@@ -5794,44 +5158,44 @@
         </is>
       </c>
       <c r="E112" s="7" t="n"/>
-      <c r="F112" s="138" t="n"/>
-      <c r="G112" s="101" t="n"/>
-      <c r="H112" s="102" t="n"/>
-      <c r="I112" s="102" t="n"/>
-      <c r="J112" s="102" t="n"/>
-    </row>
-    <row r="113" ht="28" customHeight="1" s="132">
-      <c r="A113" s="29" t="n"/>
-      <c r="B113" s="30" t="inlineStr">
+      <c r="F112" s="50" t="n"/>
+      <c r="G112" s="70" t="n"/>
+      <c r="H112" s="71" t="n"/>
+      <c r="I112" s="71" t="n"/>
+      <c r="J112" s="71" t="n"/>
+    </row>
+    <row r="113" ht="28" customHeight="1" s="85">
+      <c r="A113" s="21" t="n"/>
+      <c r="B113" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C113" s="32" t="inlineStr">
+      <c r="C113" s="24" t="inlineStr">
         <is>
           <t>Floor General</t>
         </is>
       </c>
-      <c r="D113" s="33" t="inlineStr">
+      <c r="D113" s="25" t="inlineStr">
         <is>
           <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
         </is>
       </c>
-      <c r="E113" s="34" t="n"/>
-      <c r="F113" s="138" t="n"/>
-      <c r="G113" s="107" t="n"/>
-      <c r="H113" s="102" t="n"/>
-      <c r="I113" s="102" t="n"/>
-      <c r="J113" s="102" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="29" t="n"/>
-      <c r="B114" s="30" t="inlineStr">
+      <c r="E113" s="26" t="n"/>
+      <c r="F113" s="50" t="n"/>
+      <c r="G113" s="72" t="n"/>
+      <c r="H113" s="71" t="n"/>
+      <c r="I113" s="71" t="n"/>
+      <c r="J113" s="71" t="n"/>
+    </row>
+    <row r="114" ht="42" customHeight="1" s="85">
+      <c r="A114" s="21" t="n"/>
+      <c r="B114" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C114" s="31" t="inlineStr">
+      <c r="C114" s="23" t="inlineStr">
         <is>
           <t>Fox-Like First Step</t>
         </is>
@@ -5846,92 +5210,92 @@
           <t>Your Move cards are unaffected by opponents</t>
         </is>
       </c>
-      <c r="F114" s="139" t="n"/>
-      <c r="G114" s="101" t="n"/>
-      <c r="H114" s="102" t="n"/>
-      <c r="I114" s="102" t="n"/>
-      <c r="J114" s="102" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="29" t="n"/>
-      <c r="B115" s="30" t="inlineStr">
+      <c r="F114" s="51" t="n"/>
+      <c r="G114" s="70" t="n"/>
+      <c r="H114" s="71" t="n"/>
+      <c r="I114" s="71" t="n"/>
+      <c r="J114" s="71" t="n"/>
+    </row>
+    <row r="115" ht="28" customHeight="1" s="85">
+      <c r="A115" s="21" t="n"/>
+      <c r="B115" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C115" s="90" t="inlineStr">
+      <c r="C115" s="37" t="inlineStr">
         <is>
           <t>Freethrow Merchant</t>
         </is>
       </c>
-      <c r="D115" s="94" t="inlineStr">
+      <c r="D115" s="41" t="inlineStr">
         <is>
           <t>All Clamps on you grant 1 FT instead</t>
         </is>
       </c>
-      <c r="E115" s="34" t="n"/>
-      <c r="F115" s="138" t="n"/>
-      <c r="G115" s="125" t="n"/>
-      <c r="H115" s="102" t="n"/>
-      <c r="I115" s="102" t="n"/>
-      <c r="J115" s="102" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="29" t="n"/>
-      <c r="B116" s="30" t="inlineStr">
+      <c r="E115" s="26" t="n"/>
+      <c r="F115" s="50" t="n"/>
+      <c r="G115" s="77" t="n"/>
+      <c r="H115" s="71" t="n"/>
+      <c r="I115" s="71" t="n"/>
+      <c r="J115" s="71" t="n"/>
+    </row>
+    <row r="116" ht="28" customHeight="1" s="85">
+      <c r="A116" s="21" t="n"/>
+      <c r="B116" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C116" s="90" t="inlineStr">
+      <c r="C116" s="37" t="inlineStr">
         <is>
           <t>Generational Whistle</t>
         </is>
       </c>
-      <c r="D116" s="91" t="inlineStr">
+      <c r="D116" s="38" t="inlineStr">
         <is>
           <t>Take 1 additional FT</t>
         </is>
       </c>
       <c r="E116" s="7" t="n"/>
-      <c r="F116" s="138" t="n"/>
-      <c r="G116" s="101" t="n"/>
-      <c r="H116" s="102" t="n"/>
-      <c r="I116" s="102" t="n"/>
-      <c r="J116" s="102" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="29" t="n"/>
-      <c r="B117" s="30" t="inlineStr">
+      <c r="F116" s="50" t="n"/>
+      <c r="G116" s="70" t="n"/>
+      <c r="H116" s="71" t="n"/>
+      <c r="I116" s="71" t="n"/>
+      <c r="J116" s="71" t="n"/>
+    </row>
+    <row r="117" ht="56" customHeight="1" s="85">
+      <c r="A117" s="21" t="n"/>
+      <c r="B117" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C117" s="32" t="inlineStr">
+      <c r="C117" s="24" t="inlineStr">
         <is>
           <t>Gravity</t>
         </is>
       </c>
-      <c r="D117" s="33" t="inlineStr">
+      <c r="D117" s="25" t="inlineStr">
         <is>
           <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
         </is>
       </c>
-      <c r="E117" s="34" t="n"/>
-      <c r="F117" s="138" t="n"/>
-      <c r="G117" s="107" t="n"/>
-      <c r="H117" s="102" t="n"/>
-      <c r="I117" s="102" t="n"/>
-      <c r="J117" s="102" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="29" t="n"/>
-      <c r="B118" s="30" t="inlineStr">
+      <c r="E117" s="26" t="n"/>
+      <c r="F117" s="50" t="n"/>
+      <c r="G117" s="72" t="n"/>
+      <c r="H117" s="71" t="n"/>
+      <c r="I117" s="71" t="n"/>
+      <c r="J117" s="71" t="n"/>
+    </row>
+    <row r="118" ht="56" customHeight="1" s="85">
+      <c r="A118" s="21" t="n"/>
+      <c r="B118" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C118" s="31" t="inlineStr">
+      <c r="C118" s="23" t="inlineStr">
         <is>
           <t>Great Conditioning</t>
         </is>
@@ -5942,96 +5306,96 @@
         </is>
       </c>
       <c r="E118" s="7" t="n"/>
-      <c r="F118" s="138" t="n"/>
-      <c r="G118" s="101" t="n"/>
-      <c r="H118" s="102" t="n"/>
-      <c r="I118" s="102" t="n"/>
-      <c r="J118" s="102" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="29" t="n"/>
-      <c r="B119" s="30" t="inlineStr">
+      <c r="F118" s="50" t="n"/>
+      <c r="G118" s="70" t="n"/>
+      <c r="H118" s="71" t="n"/>
+      <c r="I118" s="71" t="n"/>
+      <c r="J118" s="71" t="n"/>
+    </row>
+    <row r="119" ht="28" customHeight="1" s="85">
+      <c r="A119" s="21" t="n"/>
+      <c r="B119" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C119" s="32" t="inlineStr">
+      <c r="C119" s="24" t="inlineStr">
         <is>
           <t>Hot Hand</t>
         </is>
       </c>
-      <c r="D119" s="33" t="inlineStr">
+      <c r="D119" s="25" t="inlineStr">
         <is>
           <t>SHOT +20% if you scored last round.</t>
         </is>
       </c>
-      <c r="E119" s="34" t="n"/>
-      <c r="F119" s="138" t="n"/>
-      <c r="G119" s="107" t="n"/>
-      <c r="H119" s="102" t="n"/>
-      <c r="I119" s="102" t="n"/>
-      <c r="J119" s="102" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="29" t="n"/>
-      <c r="B120" s="30" t="inlineStr">
+      <c r="E119" s="26" t="n"/>
+      <c r="F119" s="50" t="n"/>
+      <c r="G119" s="72" t="n"/>
+      <c r="H119" s="71" t="n"/>
+      <c r="I119" s="71" t="n"/>
+      <c r="J119" s="71" t="n"/>
+    </row>
+    <row r="120" ht="28" customHeight="1" s="85">
+      <c r="A120" s="21" t="n"/>
+      <c r="B120" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C120" s="31" t="inlineStr">
+      <c r="C120" s="23" t="inlineStr">
         <is>
           <t>Like That</t>
         </is>
       </c>
-      <c r="D120" s="91" t="inlineStr">
+      <c r="D120" s="38" t="inlineStr">
         <is>
           <t>Your SHOT % cannot be reduced</t>
         </is>
       </c>
       <c r="E120" s="7" t="n"/>
-      <c r="F120" s="138" t="n"/>
-      <c r="G120" s="101" t="n"/>
-      <c r="H120" s="102" t="n"/>
-      <c r="I120" s="102" t="n"/>
-      <c r="J120" s="102" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="29" t="n"/>
-      <c r="B121" s="30" t="inlineStr">
+      <c r="F120" s="50" t="n"/>
+      <c r="G120" s="70" t="n"/>
+      <c r="H120" s="71" t="n"/>
+      <c r="I120" s="71" t="n"/>
+      <c r="J120" s="71" t="n"/>
+    </row>
+    <row r="121" ht="28" customHeight="1" s="85">
+      <c r="A121" s="21" t="n"/>
+      <c r="B121" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C121" s="32" t="inlineStr">
+      <c r="C121" s="24" t="inlineStr">
         <is>
           <t>No Bag</t>
         </is>
       </c>
-      <c r="D121" s="33" t="inlineStr">
+      <c r="D121" s="25" t="inlineStr">
         <is>
           <t>Cannot activate Move cards this round</t>
         </is>
       </c>
-      <c r="E121" s="34" t="n"/>
-      <c r="F121" s="138" t="n"/>
-      <c r="G121" s="113" t="inlineStr">
+      <c r="E121" s="26" t="n"/>
+      <c r="F121" s="50" t="n"/>
+      <c r="G121" s="73" t="inlineStr">
         <is>
           <t>Bad card to draw</t>
         </is>
       </c>
-      <c r="H121" s="102" t="n"/>
-      <c r="I121" s="102" t="n"/>
-      <c r="J121" s="102" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="29" t="n"/>
-      <c r="B122" s="30" t="inlineStr">
+      <c r="H121" s="71" t="n"/>
+      <c r="I121" s="71" t="n"/>
+      <c r="J121" s="71" t="n"/>
+    </row>
+    <row r="122" ht="28" customHeight="1" s="85">
+      <c r="A122" s="21" t="n"/>
+      <c r="B122" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C122" s="31" t="inlineStr">
+      <c r="C122" s="23" t="inlineStr">
         <is>
           <t>Point God</t>
         </is>
@@ -6042,48 +5406,48 @@
         </is>
       </c>
       <c r="E122" s="7" t="n"/>
-      <c r="F122" s="138" t="n"/>
-      <c r="G122" s="101" t="n"/>
-      <c r="H122" s="102" t="n"/>
-      <c r="I122" s="102" t="n"/>
-      <c r="J122" s="102" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="29" t="n"/>
-      <c r="B123" s="30" t="inlineStr">
+      <c r="F122" s="50" t="n"/>
+      <c r="G122" s="70" t="n"/>
+      <c r="H122" s="71" t="n"/>
+      <c r="I122" s="71" t="n"/>
+      <c r="J122" s="71" t="n"/>
+    </row>
+    <row r="123" ht="14" customHeight="1" s="85">
+      <c r="A123" s="21" t="n"/>
+      <c r="B123" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C123" s="32" t="inlineStr">
+      <c r="C123" s="24" t="inlineStr">
         <is>
           <t>Shooting Slump</t>
         </is>
       </c>
-      <c r="D123" s="33" t="inlineStr">
+      <c r="D123" s="25" t="inlineStr">
         <is>
           <t>SHOT -20% this round</t>
         </is>
       </c>
-      <c r="E123" s="34" t="n"/>
-      <c r="F123" s="138" t="n"/>
-      <c r="G123" s="113" t="inlineStr">
+      <c r="E123" s="26" t="n"/>
+      <c r="F123" s="50" t="n"/>
+      <c r="G123" s="73" t="inlineStr">
         <is>
           <t>Bad card to draw</t>
         </is>
       </c>
-      <c r="H123" s="102" t="n"/>
-      <c r="I123" s="102" t="n"/>
-      <c r="J123" s="102" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="29" t="n"/>
-      <c r="B124" s="30" t="inlineStr">
+      <c r="H123" s="71" t="n"/>
+      <c r="I123" s="71" t="n"/>
+      <c r="J123" s="71" t="n"/>
+    </row>
+    <row r="124" ht="28" customHeight="1" s="85">
+      <c r="A124" s="21" t="n"/>
+      <c r="B124" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C124" s="31" t="inlineStr">
+      <c r="C124" s="23" t="inlineStr">
         <is>
           <t>Shot Creator</t>
         </is>
@@ -6094,44 +5458,44 @@
         </is>
       </c>
       <c r="E124" s="7" t="n"/>
-      <c r="F124" s="138" t="n"/>
-      <c r="G124" s="101" t="n"/>
-      <c r="H124" s="102" t="n"/>
-      <c r="I124" s="102" t="n"/>
-      <c r="J124" s="102" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="29" t="n"/>
-      <c r="B125" s="30" t="inlineStr">
+      <c r="F124" s="50" t="n"/>
+      <c r="G124" s="70" t="n"/>
+      <c r="H124" s="71" t="n"/>
+      <c r="I124" s="71" t="n"/>
+      <c r="J124" s="71" t="n"/>
+    </row>
+    <row r="125" ht="28" customHeight="1" s="85">
+      <c r="A125" s="21" t="n"/>
+      <c r="B125" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C125" s="32" t="inlineStr">
+      <c r="C125" s="24" t="inlineStr">
         <is>
           <t>Sixth Man</t>
         </is>
       </c>
-      <c r="D125" s="33" t="inlineStr">
+      <c r="D125" s="25" t="inlineStr">
         <is>
           <t>SHOT = 100% if taking 6th shot of the round</t>
         </is>
       </c>
-      <c r="E125" s="34" t="n"/>
-      <c r="F125" s="138" t="n"/>
-      <c r="G125" s="107" t="n"/>
-      <c r="H125" s="102" t="n"/>
-      <c r="I125" s="102" t="n"/>
-      <c r="J125" s="102" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="29" t="n"/>
-      <c r="B126" s="30" t="inlineStr">
+      <c r="E125" s="26" t="n"/>
+      <c r="F125" s="50" t="n"/>
+      <c r="G125" s="72" t="n"/>
+      <c r="H125" s="71" t="n"/>
+      <c r="I125" s="71" t="n"/>
+      <c r="J125" s="71" t="n"/>
+    </row>
+    <row r="126" ht="28" customHeight="1" s="85">
+      <c r="A126" s="21" t="n"/>
+      <c r="B126" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C126" s="31" t="inlineStr">
+      <c r="C126" s="23" t="inlineStr">
         <is>
           <t>Sniper</t>
         </is>
@@ -6142,263 +5506,263 @@
         </is>
       </c>
       <c r="E126" s="7" t="n"/>
-      <c r="F126" s="138" t="n"/>
-      <c r="G126" s="101" t="n"/>
-      <c r="H126" s="102" t="n"/>
-      <c r="I126" s="102" t="n"/>
-      <c r="J126" s="102" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="29" t="n"/>
-      <c r="B127" s="30" t="inlineStr">
+      <c r="F126" s="50" t="n"/>
+      <c r="G126" s="70" t="n"/>
+      <c r="H126" s="71" t="n"/>
+      <c r="I126" s="71" t="n"/>
+      <c r="J126" s="71" t="n"/>
+    </row>
+    <row r="127" ht="28" customHeight="1" s="85">
+      <c r="A127" s="21" t="n"/>
+      <c r="B127" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C127" s="32" t="inlineStr">
+      <c r="C127" s="24" t="inlineStr">
         <is>
           <t>Splash Cousin</t>
         </is>
       </c>
-      <c r="D127" s="33" t="inlineStr">
+      <c r="D127" s="25" t="inlineStr">
         <is>
           <t>All Three-Point Line Shots: SHOT = 100%</t>
         </is>
       </c>
-      <c r="E127" s="34" t="n"/>
-      <c r="F127" s="138" t="n"/>
-      <c r="G127" s="107" t="n"/>
-      <c r="H127" s="102" t="n"/>
-      <c r="I127" s="102" t="n"/>
-      <c r="J127" s="102" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="29" t="n"/>
-      <c r="B128" s="30" t="inlineStr">
+      <c r="E127" s="26" t="n"/>
+      <c r="F127" s="50" t="n"/>
+      <c r="G127" s="72" t="n"/>
+      <c r="H127" s="71" t="n"/>
+      <c r="I127" s="71" t="n"/>
+      <c r="J127" s="71" t="n"/>
+    </row>
+    <row r="128" ht="28" customHeight="1" s="85">
+      <c r="A128" s="21" t="n"/>
+      <c r="B128" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C128" s="31" t="inlineStr">
+      <c r="C128" s="23" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="D128" s="91" t="inlineStr">
+      <c r="D128" s="38" t="inlineStr">
         <is>
           <t>All Clamps on you have no effect on SHOT %</t>
         </is>
       </c>
       <c r="E128" s="7" t="n"/>
-      <c r="F128" s="138" t="n"/>
-      <c r="G128" s="101" t="n"/>
-      <c r="H128" s="102" t="n"/>
-      <c r="I128" s="102" t="n"/>
-      <c r="J128" s="102" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="29" t="n"/>
-      <c r="B129" s="30" t="inlineStr">
+      <c r="F128" s="50" t="n"/>
+      <c r="G128" s="70" t="n"/>
+      <c r="H128" s="71" t="n"/>
+      <c r="I128" s="71" t="n"/>
+      <c r="J128" s="71" t="n"/>
+    </row>
+    <row r="129" ht="56" customHeight="1" s="85">
+      <c r="A129" s="21" t="n"/>
+      <c r="B129" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C129" s="32" t="inlineStr">
+      <c r="C129" s="24" t="inlineStr">
         <is>
           <t>Lethal Shooter</t>
         </is>
       </c>
-      <c r="D129" s="33" t="inlineStr">
+      <c r="D129" s="25" t="inlineStr">
         <is>
           <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
         </is>
       </c>
-      <c r="E129" s="34" t="n"/>
-      <c r="F129" s="138" t="n"/>
-      <c r="G129" s="113" t="inlineStr">
+      <c r="E129" s="26" t="n"/>
+      <c r="F129" s="50" t="n"/>
+      <c r="G129" s="73" t="inlineStr">
         <is>
           <t>Special text: “I understand it now”</t>
         </is>
       </c>
-      <c r="H129" s="102" t="n"/>
-      <c r="I129" s="102" t="n"/>
-      <c r="J129" s="102" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="29" t="n"/>
-      <c r="B130" s="30" t="inlineStr">
+      <c r="H129" s="71" t="n"/>
+      <c r="I129" s="71" t="n"/>
+      <c r="J129" s="71" t="n"/>
+    </row>
+    <row r="130" ht="56" customHeight="1" s="85">
+      <c r="A130" s="21" t="n"/>
+      <c r="B130" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C130" s="31" t="inlineStr">
+      <c r="C130" s="23" t="inlineStr">
         <is>
           <t>Ball Pounder</t>
         </is>
       </c>
-      <c r="D130" s="91" t="inlineStr">
+      <c r="D130" s="38" t="inlineStr">
         <is>
           <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E130" s="7" t="n"/>
-      <c r="F130" s="138" t="n"/>
-      <c r="G130" s="101" t="n"/>
-      <c r="H130" s="102" t="n"/>
-      <c r="I130" s="102" t="n"/>
-      <c r="J130" s="102" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="29" t="n"/>
-      <c r="B131" s="30" t="inlineStr">
+      <c r="F130" s="50" t="n"/>
+      <c r="G130" s="70" t="n"/>
+      <c r="H130" s="71" t="n"/>
+      <c r="I130" s="71" t="n"/>
+      <c r="J130" s="71" t="n"/>
+    </row>
+    <row r="131" ht="56" customHeight="1" s="85">
+      <c r="A131" s="21" t="n"/>
+      <c r="B131" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C131" s="31" t="inlineStr">
+      <c r="C131" s="23" t="inlineStr">
         <is>
           <t>Unselfish</t>
         </is>
       </c>
-      <c r="D131" s="91" t="inlineStr">
+      <c r="D131" s="38" t="inlineStr">
         <is>
           <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E131" s="7" t="n"/>
-      <c r="F131" s="138" t="n"/>
-      <c r="G131" s="101" t="n"/>
-      <c r="H131" s="102" t="n"/>
-      <c r="I131" s="102" t="n"/>
-      <c r="J131" s="102" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="29" t="n"/>
-      <c r="B132" s="30" t="inlineStr">
+      <c r="F131" s="50" t="n"/>
+      <c r="G131" s="70" t="n"/>
+      <c r="H131" s="71" t="n"/>
+      <c r="I131" s="71" t="n"/>
+      <c r="J131" s="71" t="n"/>
+    </row>
+    <row r="132" ht="56" customHeight="1" s="85">
+      <c r="A132" s="21" t="n"/>
+      <c r="B132" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C132" s="31" t="inlineStr">
+      <c r="C132" s="23" t="inlineStr">
         <is>
           <t>Dirty Player</t>
         </is>
       </c>
-      <c r="D132" s="91" t="inlineStr">
+      <c r="D132" s="38" t="inlineStr">
         <is>
           <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E132" s="7" t="n"/>
-      <c r="F132" s="138" t="n"/>
-      <c r="G132" s="101" t="n"/>
-      <c r="H132" s="102" t="n"/>
-      <c r="I132" s="102" t="n"/>
-      <c r="J132" s="102" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="29" t="n"/>
-      <c r="B133" s="30" t="inlineStr">
+      <c r="F132" s="50" t="n"/>
+      <c r="G132" s="70" t="n"/>
+      <c r="H132" s="71" t="n"/>
+      <c r="I132" s="71" t="n"/>
+      <c r="J132" s="71" t="n"/>
+    </row>
+    <row r="133" ht="56" customHeight="1" s="85">
+      <c r="A133" s="21" t="n"/>
+      <c r="B133" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C133" s="31" t="inlineStr">
+      <c r="C133" s="23" t="inlineStr">
         <is>
           <t>Villainous Reputation</t>
         </is>
       </c>
-      <c r="D133" s="91" t="inlineStr">
+      <c r="D133" s="38" t="inlineStr">
         <is>
           <t>Discard 1 whenever any Whistle triggers</t>
         </is>
       </c>
       <c r="E133" s="7" t="n"/>
-      <c r="F133" s="138" t="n"/>
-      <c r="G133" s="101" t="inlineStr">
+      <c r="F133" s="50" t="n"/>
+      <c r="G133" s="70" t="inlineStr">
         <is>
           <t>Discarded during play, it attaches to a random player — possibly you again</t>
         </is>
       </c>
-      <c r="H133" s="102" t="n"/>
-      <c r="I133" s="102" t="n"/>
-      <c r="J133" s="102" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="29" t="n"/>
-      <c r="B134" s="30" t="inlineStr">
+      <c r="H133" s="71" t="n"/>
+      <c r="I133" s="71" t="n"/>
+      <c r="J133" s="71" t="n"/>
+    </row>
+    <row r="134" ht="126" customHeight="1" s="85">
+      <c r="A134" s="21" t="n"/>
+      <c r="B134" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C134" s="31" t="inlineStr">
+      <c r="C134" s="23" t="inlineStr">
         <is>
           <t>Free Agent</t>
         </is>
       </c>
-      <c r="D134" s="91" t="inlineStr">
+      <c r="D134" s="38" t="inlineStr">
         <is>
           <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
       <c r="E134" s="7" t="n"/>
-      <c r="F134" s="138" t="n"/>
-      <c r="G134" s="101" t="inlineStr">
+      <c r="F134" s="50" t="n"/>
+      <c r="G134" s="70" t="inlineStr">
         <is>
           <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
         </is>
       </c>
-      <c r="H134" s="102" t="n"/>
-      <c r="I134" s="102" t="n"/>
-      <c r="J134" s="102" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="29" t="n"/>
-      <c r="B135" s="30" t="inlineStr">
+      <c r="H134" s="71" t="n"/>
+      <c r="I134" s="71" t="n"/>
+      <c r="J134" s="71" t="n"/>
+    </row>
+    <row r="135" ht="70" customHeight="1" s="85">
+      <c r="A135" s="21" t="n"/>
+      <c r="B135" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C135" s="31" t="inlineStr">
+      <c r="C135" s="23" t="inlineStr">
         <is>
           <t>Franchise Player</t>
         </is>
       </c>
-      <c r="D135" s="91" t="inlineStr">
+      <c r="D135" s="38" t="inlineStr">
         <is>
           <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
         </is>
       </c>
       <c r="E135" s="7" t="n"/>
-      <c r="F135" s="138" t="n"/>
-      <c r="G135" s="101" t="n"/>
-      <c r="H135" s="102" t="n"/>
-      <c r="I135" s="102" t="n"/>
-      <c r="J135" s="102" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="35" t="n"/>
-      <c r="B136" s="36" t="inlineStr">
+      <c r="F135" s="50" t="n"/>
+      <c r="G135" s="70" t="n"/>
+      <c r="H135" s="71" t="n"/>
+      <c r="I135" s="71" t="n"/>
+      <c r="J135" s="71" t="n"/>
+    </row>
+    <row r="136" ht="56" customHeight="1" s="85">
+      <c r="A136" s="27" t="n"/>
+      <c r="B136" s="28" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C136" s="152" t="inlineStr">
+      <c r="C136" s="56" t="inlineStr">
         <is>
           <t>Fundamentalist</t>
         </is>
       </c>
-      <c r="D136" s="161" t="inlineStr">
+      <c r="D136" s="63" t="inlineStr">
         <is>
           <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent</t>
         </is>
       </c>
-      <c r="E136" s="154" t="n"/>
-      <c r="F136" s="159" t="n"/>
-      <c r="G136" s="156" t="n"/>
-      <c r="H136" s="151" t="n"/>
-      <c r="I136" s="151" t="n"/>
-      <c r="J136" s="151" t="n"/>
+      <c r="E136" s="58" t="n"/>
+      <c r="F136" s="61" t="n"/>
+      <c r="G136" s="75" t="n"/>
+      <c r="H136" s="76" t="n"/>
+      <c r="I136" s="76" t="n"/>
+      <c r="J136" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="123">
@@ -6474,8 +5838,8 @@
     <mergeCell ref="G25:J25"/>
     <mergeCell ref="G99:J99"/>
     <mergeCell ref="G60:J60"/>
+    <mergeCell ref="G131:J131"/>
     <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G131:J131"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G130:J130"/>
@@ -6510,8 +5874,8 @@
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
+    <mergeCell ref="G27:J27"/>
     <mergeCell ref="G120:J120"/>
-    <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2065,7 +2065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2146,39 +2146,39 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$136,"Pass")</f>
+        <f>COUNTIF($B$5:$B$137,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$136,"Move")+COUNTIF($B$5:$B$136,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$137,"Move")+COUNTIF($B$5:$B$137,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$136,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$137,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$136,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$137,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$136,"Game Break")&amp;" ("&amp;(COUNTIF($B$5:$B$136,"Game Break")+G2+H2)&amp;")"</f>
+        <f>COUNTIF($B$5:$B$137,"Game Break")&amp;" ("&amp;(COUNTIF($B$5:$B$137,"Game Break")+G2+H2)&amp;")"</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$136,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$137,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$136,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$137,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$136,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$137,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="87">
-        <f>SUM(B2:E2)+COUNTIF($B$5:$B$136,"Game Break")+SUM(G2:I2)</f>
+        <f>SUM(B2:E2)+COUNTIF($B$5:$B$137,"Game Break")+SUM(G2:I2)</f>
         <v/>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="B5" s="53">
-        <f>COUNTIF($B$6:$B$136,"Pass")</f>
+        <f>COUNTIF($B$6:$B$137,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="54" t="n"/>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" s="70" t="n"/>
       <c r="H11" s="71" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="33" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" s="72" t="n"/>
       <c r="H12" s="71" t="n"/>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="B21" s="53">
-        <f>COUNTIF($B$22:$B$136,"Move")+COUNTIF($B$22:$B$136,"Special Move")</f>
+        <f>COUNTIF($B$22:$B$137,"Move")+COUNTIF($B$22:$B$137,"Special Move")</f>
         <v/>
       </c>
       <c r="C21" s="54" t="n"/>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="B35" s="53">
-        <f>COUNTIF($B$36:$B$136,"Special Move")</f>
+        <f>COUNTIF($B$36:$B$137,"Special Move")</f>
         <v/>
       </c>
       <c r="C35" s="54" t="n"/>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="B49" s="53">
-        <f>COUNTIF($B$50:$B$136,"Clamp")</f>
+        <f>COUNTIF($B$50:$B$137,"Clamp")</f>
         <v/>
       </c>
       <c r="C49" s="54" t="n"/>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="B55" s="53">
-        <f>COUNTIF($B$56:$B$136,"Whistle")</f>
+        <f>COUNTIF($B$56:$B$137,"Whistle")</f>
         <v/>
       </c>
       <c r="C55" s="54" t="n"/>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B75" s="53">
-        <f>COUNTIF($B$76:$B$136,"Game Break")</f>
+        <f>COUNTIF($B$76:$B$137,"Game Break")</f>
         <v/>
       </c>
       <c r="C75" s="54" t="n"/>
@@ -4449,16 +4449,14 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Swap positions with random other player</t>
+          <t>Swap hands with a random other player</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
-      <c r="F85" s="34" t="n"/>
-      <c r="G85" s="74" t="inlineStr">
-        <is>
-          <t>Applies to rest of game</t>
-        </is>
-      </c>
+      <c r="F85" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="74" t="n"/>
       <c r="H85" s="71" t="n"/>
       <c r="I85" s="71" t="n"/>
       <c r="J85" s="71" t="n"/>
@@ -4988,7 +4986,7 @@
         </is>
       </c>
       <c r="B105" s="53">
-        <f>COUNTIF($B$106:$B$136,"Injury GB")</f>
+        <f>COUNTIF($B$106:$B$137,"Injury GB")</f>
         <v/>
       </c>
       <c r="C105" s="54" t="n"/>
@@ -5033,7 +5031,7 @@
         </is>
       </c>
       <c r="B107" s="53">
-        <f>COUNTIF($B$108:$B$136,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$108:$B$137,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="C107" s="54" t="n"/>
@@ -5076,7 +5074,7 @@
         </is>
       </c>
       <c r="B109" s="53">
-        <f>COUNTIF($B$110:$B$136,"Intangible")</f>
+        <f>COUNTIF($B$110:$B$137,"Intangible")</f>
         <v/>
       </c>
       <c r="C109" s="54" t="n"/>
@@ -5165,28 +5163,21 @@
       <c r="J112" s="71" t="n"/>
     </row>
     <row r="113" ht="28" customHeight="1" s="85">
-      <c r="A113" s="21" t="n"/>
-      <c r="B113" s="22" t="inlineStr">
+      <c r="B113" s="0" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C113" s="24" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D113" s="25" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest</t>
-        </is>
-      </c>
-      <c r="E113" s="26" t="n"/>
-      <c r="F113" s="50" t="n"/>
-      <c r="G113" s="72" t="n"/>
-      <c r="H113" s="71" t="n"/>
-      <c r="I113" s="71" t="n"/>
-      <c r="J113" s="71" t="n"/>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>Roswell Reach</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="inlineStr">
+        <is>
+          <t>All your Rebound bids of 1 or more count as 1 higher</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="42" customHeight="1" s="85">
       <c r="A114" s="21" t="n"/>
@@ -5195,23 +5186,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C114" s="23" t="inlineStr">
-        <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F114" s="51" t="n"/>
-      <c r="G114" s="70" t="n"/>
+      <c r="C114" s="24" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D114" s="25" t="inlineStr">
+        <is>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
+        </is>
+      </c>
+      <c r="E114" s="26" t="n"/>
+      <c r="F114" s="50" t="n"/>
+      <c r="G114" s="72" t="n"/>
       <c r="H114" s="71" t="n"/>
       <c r="I114" s="71" t="n"/>
       <c r="J114" s="71" t="n"/>
@@ -5223,19 +5210,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C115" s="37" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D115" s="41" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E115" s="26" t="n"/>
-      <c r="F115" s="50" t="n"/>
-      <c r="G115" s="77" t="n"/>
+      <c r="C115" s="23" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F115" s="51" t="n"/>
+      <c r="G115" s="70" t="n"/>
       <c r="H115" s="71" t="n"/>
       <c r="I115" s="71" t="n"/>
       <c r="J115" s="71" t="n"/>
@@ -5249,17 +5240,17 @@
       </c>
       <c r="C116" s="37" t="inlineStr">
         <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D116" s="38" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="n"/>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D116" s="41" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
+        </is>
+      </c>
+      <c r="E116" s="26" t="n"/>
       <c r="F116" s="50" t="n"/>
-      <c r="G116" s="70" t="n"/>
+      <c r="G116" s="77" t="n"/>
       <c r="H116" s="71" t="n"/>
       <c r="I116" s="71" t="n"/>
       <c r="J116" s="71" t="n"/>
@@ -5271,19 +5262,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C117" s="24" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D117" s="25" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E117" s="26" t="n"/>
+      <c r="C117" s="37" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D117" s="38" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="n"/>
       <c r="F117" s="50" t="n"/>
-      <c r="G117" s="72" t="n"/>
+      <c r="G117" s="70" t="n"/>
       <c r="H117" s="71" t="n"/>
       <c r="I117" s="71" t="n"/>
       <c r="J117" s="71" t="n"/>
@@ -5295,19 +5286,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C118" s="23" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="n"/>
+      <c r="C118" s="24" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="D118" s="25" t="inlineStr">
+        <is>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+        </is>
+      </c>
+      <c r="E118" s="26" t="n"/>
       <c r="F118" s="50" t="n"/>
-      <c r="G118" s="70" t="n"/>
+      <c r="G118" s="72" t="n"/>
       <c r="H118" s="71" t="n"/>
       <c r="I118" s="71" t="n"/>
       <c r="J118" s="71" t="n"/>
@@ -5319,19 +5310,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C119" s="24" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D119" s="25" t="inlineStr">
-        <is>
-          <t>SHOT +20% if you scored last round.</t>
-        </is>
-      </c>
-      <c r="E119" s="26" t="n"/>
+      <c r="C119" s="23" t="inlineStr">
+        <is>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="n"/>
       <c r="F119" s="50" t="n"/>
-      <c r="G119" s="72" t="n"/>
+      <c r="G119" s="70" t="n"/>
       <c r="H119" s="71" t="n"/>
       <c r="I119" s="71" t="n"/>
       <c r="J119" s="71" t="n"/>
@@ -5343,19 +5334,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C120" s="23" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D120" s="38" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="n"/>
+      <c r="C120" s="24" t="inlineStr">
+        <is>
+          <t>Hot Hand</t>
+        </is>
+      </c>
+      <c r="D120" s="25" t="inlineStr">
+        <is>
+          <t>SHOT +20% if you scored last round.</t>
+        </is>
+      </c>
+      <c r="E120" s="26" t="n"/>
       <c r="F120" s="50" t="n"/>
-      <c r="G120" s="70" t="n"/>
+      <c r="G120" s="72" t="n"/>
       <c r="H120" s="71" t="n"/>
       <c r="I120" s="71" t="n"/>
       <c r="J120" s="71" t="n"/>
@@ -5367,23 +5358,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C121" s="24" t="inlineStr">
-        <is>
-          <t>No Bag</t>
-        </is>
-      </c>
-      <c r="D121" s="25" t="inlineStr">
-        <is>
-          <t>Cannot activate Move cards this round</t>
-        </is>
-      </c>
-      <c r="E121" s="26" t="n"/>
+      <c r="C121" s="23" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D121" s="38" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="n"/>
       <c r="F121" s="50" t="n"/>
-      <c r="G121" s="73" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G121" s="70" t="n"/>
       <c r="H121" s="71" t="n"/>
       <c r="I121" s="71" t="n"/>
       <c r="J121" s="71" t="n"/>
@@ -5395,19 +5382,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C122" s="23" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="n"/>
+      <c r="C122" s="24" t="inlineStr">
+        <is>
+          <t>No Bag</t>
+        </is>
+      </c>
+      <c r="D122" s="25" t="inlineStr">
+        <is>
+          <t>Cannot activate Move cards this round</t>
+        </is>
+      </c>
+      <c r="E122" s="26" t="n"/>
       <c r="F122" s="50" t="n"/>
-      <c r="G122" s="70" t="n"/>
+      <c r="G122" s="73" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H122" s="71" t="n"/>
       <c r="I122" s="71" t="n"/>
       <c r="J122" s="71" t="n"/>
@@ -5419,23 +5410,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C123" s="24" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D123" s="25" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
-        </is>
-      </c>
-      <c r="E123" s="26" t="n"/>
+      <c r="C123" s="23" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="n"/>
       <c r="F123" s="50" t="n"/>
-      <c r="G123" s="73" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G123" s="70" t="n"/>
       <c r="H123" s="71" t="n"/>
       <c r="I123" s="71" t="n"/>
       <c r="J123" s="71" t="n"/>
@@ -5447,19 +5434,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C124" s="23" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="n"/>
+      <c r="C124" s="24" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D124" s="25" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E124" s="26" t="n"/>
       <c r="F124" s="50" t="n"/>
-      <c r="G124" s="70" t="n"/>
+      <c r="G124" s="73" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H124" s="71" t="n"/>
       <c r="I124" s="71" t="n"/>
       <c r="J124" s="71" t="n"/>
@@ -5471,19 +5462,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C125" s="24" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D125" s="25" t="inlineStr">
-        <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
-        </is>
-      </c>
-      <c r="E125" s="26" t="n"/>
+      <c r="C125" s="23" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="n"/>
       <c r="F125" s="50" t="n"/>
-      <c r="G125" s="72" t="n"/>
+      <c r="G125" s="70" t="n"/>
       <c r="H125" s="71" t="n"/>
       <c r="I125" s="71" t="n"/>
       <c r="J125" s="71" t="n"/>
@@ -5495,19 +5486,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C126" s="23" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="n"/>
+      <c r="C126" s="24" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D126" s="25" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E126" s="26" t="n"/>
       <c r="F126" s="50" t="n"/>
-      <c r="G126" s="70" t="n"/>
+      <c r="G126" s="72" t="n"/>
       <c r="H126" s="71" t="n"/>
       <c r="I126" s="71" t="n"/>
       <c r="J126" s="71" t="n"/>
@@ -5519,19 +5510,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C127" s="24" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D127" s="25" t="inlineStr">
-        <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E127" s="26" t="n"/>
+      <c r="C127" s="23" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="n"/>
       <c r="F127" s="50" t="n"/>
-      <c r="G127" s="72" t="n"/>
+      <c r="G127" s="70" t="n"/>
       <c r="H127" s="71" t="n"/>
       <c r="I127" s="71" t="n"/>
       <c r="J127" s="71" t="n"/>
@@ -5543,19 +5534,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C128" s="23" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D128" s="38" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="n"/>
+      <c r="C128" s="24" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D128" s="25" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E128" s="26" t="n"/>
       <c r="F128" s="50" t="n"/>
-      <c r="G128" s="70" t="n"/>
+      <c r="G128" s="72" t="n"/>
       <c r="H128" s="71" t="n"/>
       <c r="I128" s="71" t="n"/>
       <c r="J128" s="71" t="n"/>
@@ -5567,23 +5558,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C129" s="24" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D129" s="25" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
-        </is>
-      </c>
-      <c r="E129" s="26" t="n"/>
+      <c r="C129" s="23" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D129" s="38" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="n"/>
       <c r="F129" s="50" t="n"/>
-      <c r="G129" s="73" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G129" s="70" t="n"/>
       <c r="H129" s="71" t="n"/>
       <c r="I129" s="71" t="n"/>
       <c r="J129" s="71" t="n"/>
@@ -5595,19 +5582,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C130" s="23" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D130" s="38" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="n"/>
+      <c r="C130" s="24" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D130" s="25" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E130" s="26" t="n"/>
       <c r="F130" s="50" t="n"/>
-      <c r="G130" s="70" t="n"/>
+      <c r="G130" s="73" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
       <c r="H130" s="71" t="n"/>
       <c r="I130" s="71" t="n"/>
       <c r="J130" s="71" t="n"/>
@@ -5621,12 +5612,12 @@
       </c>
       <c r="C131" s="23" t="inlineStr">
         <is>
-          <t>Unselfish</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D131" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E131" s="7" t="n"/>
@@ -5645,12 +5636,12 @@
       </c>
       <c r="C132" s="23" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D132" s="38" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E132" s="7" t="n"/>
@@ -5669,21 +5660,17 @@
       </c>
       <c r="C133" s="23" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D133" s="38" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E133" s="7" t="n"/>
       <c r="F133" s="50" t="n"/>
-      <c r="G133" s="70" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="G133" s="70" t="n"/>
       <c r="H133" s="71" t="n"/>
       <c r="I133" s="71" t="n"/>
       <c r="J133" s="71" t="n"/>
@@ -5697,19 +5684,19 @@
       </c>
       <c r="C134" s="23" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Villainous Reputation</t>
         </is>
       </c>
       <c r="D134" s="38" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>Discard 1 whenever any Whistle triggers</t>
         </is>
       </c>
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="50" t="n"/>
       <c r="G134" s="70" t="inlineStr">
         <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
         </is>
       </c>
       <c r="H134" s="71" t="n"/>
@@ -5725,44 +5712,72 @@
       </c>
       <c r="C135" s="23" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Free Agent</t>
         </is>
       </c>
       <c r="D135" s="38" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
       <c r="E135" s="7" t="n"/>
       <c r="F135" s="50" t="n"/>
-      <c r="G135" s="70" t="n"/>
+      <c r="G135" s="70" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+        </is>
+      </c>
       <c r="H135" s="71" t="n"/>
       <c r="I135" s="71" t="n"/>
       <c r="J135" s="71" t="n"/>
     </row>
     <row r="136" ht="56" customHeight="1" s="85">
-      <c r="A136" s="27" t="n"/>
-      <c r="B136" s="28" t="inlineStr">
+      <c r="A136" s="21" t="n"/>
+      <c r="B136" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C136" s="56" t="inlineStr">
+      <c r="C136" s="23" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D136" s="38" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="n"/>
+      <c r="F136" s="50" t="n"/>
+      <c r="G136" s="70" t="n"/>
+      <c r="H136" s="71" t="n"/>
+      <c r="I136" s="71" t="n"/>
+      <c r="J136" s="71" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="27" t="n"/>
+      <c r="B137" s="28" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C137" s="56" t="inlineStr">
         <is>
           <t>Fundamentalist</t>
         </is>
       </c>
-      <c r="D136" s="63" t="inlineStr">
+      <c r="D137" s="63" t="inlineStr">
         <is>
           <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent</t>
         </is>
       </c>
-      <c r="E136" s="58" t="n"/>
-      <c r="F136" s="61" t="n"/>
-      <c r="G136" s="75" t="n"/>
-      <c r="H136" s="76" t="n"/>
-      <c r="I136" s="76" t="n"/>
-      <c r="J136" s="76" t="n"/>
+      <c r="E137" s="58" t="n"/>
+      <c r="F137" s="61" t="n"/>
+      <c r="G137" s="75" t="n"/>
+      <c r="H137" s="76" t="n"/>
+      <c r="I137" s="76" t="n"/>
+      <c r="J137" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="123">

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2065,7 +2065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2146,39 +2146,39 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$137,"Pass")</f>
+        <f>COUNTIF($B$5:$B$140,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$137,"Move")+COUNTIF($B$5:$B$137,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$140,"Move")+COUNTIF($B$5:$B$140,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$137,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$140,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$137,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$140,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$137,"Game Break")&amp;" ("&amp;(COUNTIF($B$5:$B$137,"Game Break")+G2+H2)&amp;")"</f>
+        <f>COUNTIF($B$5:$B$140,"Game Break")&amp;" ("&amp;(COUNTIF($B$5:$B$140,"Game Break")+G2+H2)&amp;")"</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$137,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$140,"Injury GB")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$137,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$140,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$137,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$140,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="87">
-        <f>SUM(B2:E2)+COUNTIF($B$5:$B$137,"Game Break")+SUM(G2:I2)</f>
+        <f>SUM(B2:E2)+COUNTIF($B$5:$B$140,"Game Break")+SUM(G2:I2)</f>
         <v/>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="B5" s="53">
-        <f>COUNTIF($B$6:$B$137,"Pass")</f>
+        <f>COUNTIF($B$6:$B$140,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="54" t="n"/>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F7" s="32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G7" s="70" t="n"/>
       <c r="H7" s="71" t="n"/>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="72" t="n"/>
       <c r="H10" s="71" t="n"/>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="70" t="n"/>
       <c r="H11" s="71" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="33" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" s="72" t="n"/>
       <c r="H12" s="71" t="n"/>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G13" s="70" t="n"/>
       <c r="H13" s="71" t="n"/>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="F14" s="36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14" s="72" t="n"/>
       <c r="H14" s="71" t="n"/>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="F16" s="36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G16" s="72" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="B21" s="53">
-        <f>COUNTIF($B$22:$B$137,"Move")+COUNTIF($B$22:$B$137,"Special Move")</f>
+        <f>COUNTIF($B$22:$B$140,"Move")+COUNTIF($B$22:$B$140,"Special Move")</f>
         <v/>
       </c>
       <c r="C21" s="54" t="n"/>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="F23" s="32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G23" s="70" t="n"/>
       <c r="H23" s="71" t="n"/>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="F26" s="36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G26" s="72" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="B35" s="53">
-        <f>COUNTIF($B$36:$B$137,"Special Move")</f>
+        <f>COUNTIF($B$36:$B$140,"Special Move")</f>
         <v/>
       </c>
       <c r="C35" s="54" t="n"/>
@@ -3491,113 +3491,98 @@
       <c r="J48" s="76" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1" s="85">
-      <c r="A49" s="52" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>2-Hand Jam</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>SHOT +10%. Shoot the ball. Another +10% straight off your own board</t>
+        </is>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>Always the reverse dunk</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="56" customHeight="1" s="85">
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>Give-and-Go Dunk</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>Clean look only — no Clamps on you and nothing has gone off this possession. SHOT +30%. Shoot the ball</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>Any of the three dunks</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="47" customHeight="1" s="85">
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>Tomahawk</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>SHOT +15% at 50% or better, −15% under it. Shoot the ball</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>Always the one-hand dunk</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="54" customHeight="1" s="85">
+      <c r="A52" s="52" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B49" s="53">
-        <f>COUNTIF($B$50:$B$137,"Clamp")</f>
+      <c r="B52" s="53">
+        <f>COUNTIF($B$50:$B$140,"Clamp")</f>
         <v/>
       </c>
-      <c r="C49" s="54" t="n"/>
-      <c r="D49" s="54" t="n"/>
-      <c r="E49" s="54" t="n"/>
-      <c r="F49" s="55" t="n"/>
-      <c r="G49" s="66" t="n"/>
-      <c r="H49" s="67" t="n"/>
-      <c r="I49" s="67" t="n"/>
-      <c r="J49" s="67" t="n"/>
-    </row>
-    <row r="50" ht="56" customHeight="1" s="85">
-      <c r="A50" s="21" t="n"/>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="inlineStr">
-        <is>
-          <t>Contest</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Next player SHOT -25% if they shoot</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="G50" s="80" t="inlineStr">
-        <is>
-          <t>1 def</t>
-        </is>
-      </c>
-      <c r="H50" s="71" t="n"/>
-      <c r="I50" s="71" t="n"/>
-      <c r="J50" s="71" t="n"/>
-    </row>
-    <row r="51" ht="47" customHeight="1" s="85">
-      <c r="A51" s="21" t="n"/>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>Double-Team</t>
-        </is>
-      </c>
-      <c r="D51" s="25" t="inlineStr">
-        <is>
-          <t>Next Player cannot play 2 random cards from hand.</t>
-        </is>
-      </c>
-      <c r="E51" s="26" t="n"/>
-      <c r="F51" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="G51" s="77" t="inlineStr">
-        <is>
-          <t>2 def</t>
-        </is>
-      </c>
-      <c r="H51" s="71" t="n"/>
-      <c r="I51" s="71" t="n"/>
-      <c r="J51" s="71" t="n"/>
-    </row>
-    <row r="52" ht="54" customHeight="1" s="85">
-      <c r="A52" s="21" t="n"/>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C52" s="23" t="inlineStr">
-        <is>
-          <t>Full-Court Press</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Next player discards 2 cards at the start of their turn</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="n"/>
-      <c r="F52" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="80" t="inlineStr">
-        <is>
-          <t>1 def</t>
-        </is>
-      </c>
-      <c r="H52" s="71" t="n"/>
-      <c r="I52" s="71" t="n"/>
-      <c r="J52" s="71" t="n"/>
+      <c r="C52" s="54" t="n"/>
+      <c r="D52" s="54" t="n"/>
+      <c r="E52" s="54" t="n"/>
+      <c r="F52" s="55" t="n"/>
+      <c r="G52" s="66" t="n"/>
+      <c r="H52" s="67" t="n"/>
+      <c r="I52" s="67" t="n"/>
+      <c r="J52" s="67" t="n"/>
     </row>
     <row r="53" ht="28" customHeight="1" s="85">
       <c r="A53" s="21" t="n"/>
@@ -3606,23 +3591,23 @@
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>Trap</t>
-        </is>
-      </c>
-      <c r="D53" s="41" t="inlineStr">
-        <is>
-          <t>Next player can only play Pass cards during their turn</t>
-        </is>
-      </c>
-      <c r="E53" s="26" t="n"/>
-      <c r="F53" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="G53" s="77" t="inlineStr">
-        <is>
-          <t>They can still shoot as another option; 3 def</t>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>Contest</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Next player SHOT -25% if they shoot</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" s="80" t="inlineStr">
+        <is>
+          <t>1 def</t>
         </is>
       </c>
       <c r="H53" s="71" t="n"/>
@@ -3630,80 +3615,89 @@
       <c r="J53" s="71" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1" s="85">
-      <c r="A54" s="27" t="n"/>
-      <c r="B54" s="28" t="inlineStr">
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="22" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C54" s="56" t="inlineStr">
-        <is>
-          <t>Triple-Team</t>
-        </is>
-      </c>
-      <c r="D54" s="57" t="inlineStr">
-        <is>
-          <t>Next player cannot play 3 random cards from hand.</t>
-        </is>
-      </c>
-      <c r="E54" s="58" t="n"/>
-      <c r="F54" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" s="83" t="inlineStr">
-        <is>
-          <t>3 def</t>
-        </is>
-      </c>
-      <c r="H54" s="76" t="n"/>
-      <c r="I54" s="76" t="n"/>
-      <c r="J54" s="76" t="n"/>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>Double-Team</t>
+        </is>
+      </c>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>Next Player cannot play 2 random cards from hand.</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="n"/>
+      <c r="F54" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" s="77" t="inlineStr">
+        <is>
+          <t>2 def</t>
+        </is>
+      </c>
+      <c r="H54" s="71" t="n"/>
+      <c r="I54" s="71" t="n"/>
+      <c r="J54" s="71" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1" s="85">
-      <c r="A55" s="52" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="B55" s="53">
-        <f>COUNTIF($B$56:$B$137,"Whistle")</f>
-        <v/>
-      </c>
-      <c r="C55" s="54" t="n"/>
-      <c r="D55" s="54" t="n"/>
-      <c r="E55" s="54" t="n"/>
-      <c r="F55" s="55" t="n"/>
-      <c r="G55" s="66" t="n"/>
-      <c r="H55" s="67" t="n"/>
-      <c r="I55" s="67" t="n"/>
-      <c r="J55" s="67" t="n"/>
+      <c r="A55" s="21" t="n"/>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>Full-Court Press</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Next player discards 2 cards at the start of their turn</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="80" t="inlineStr">
+        <is>
+          <t>1 def</t>
+        </is>
+      </c>
+      <c r="H55" s="71" t="n"/>
+      <c r="I55" s="71" t="n"/>
+      <c r="J55" s="71" t="n"/>
     </row>
     <row r="56" ht="42" customHeight="1" s="85">
-      <c r="A56" s="21" t="inlineStr">
-        <is>
-          <t>All whistles are limited to 1</t>
-        </is>
-      </c>
+      <c r="A56" s="21" t="n"/>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C56" s="23" t="inlineStr">
-        <is>
-          <t>Back Court Violation</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="50" t="n"/>
-      <c r="G56" s="70" t="inlineStr">
-        <is>
-          <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>Trap</t>
+        </is>
+      </c>
+      <c r="D56" s="41" t="inlineStr">
+        <is>
+          <t>Next player can only play Pass cards during their turn</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="n"/>
+      <c r="F56" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" s="77" t="inlineStr">
+        <is>
+          <t>They can still shoot as another option; 3 def</t>
         </is>
       </c>
       <c r="H56" s="71" t="n"/>
@@ -3711,73 +3705,82 @@
       <c r="J56" s="71" t="n"/>
     </row>
     <row r="57" ht="40" customHeight="1" s="85">
-      <c r="A57" s="21" t="n"/>
-      <c r="B57" s="22" t="inlineStr">
+      <c r="A57" s="27" t="n"/>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C57" s="56" t="inlineStr">
+        <is>
+          <t>Triple-Team</t>
+        </is>
+      </c>
+      <c r="D57" s="57" t="inlineStr">
+        <is>
+          <t>Next player cannot play 3 random cards from hand.</t>
+        </is>
+      </c>
+      <c r="E57" s="58" t="n"/>
+      <c r="F57" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" s="83" t="inlineStr">
+        <is>
+          <t>3 def</t>
+        </is>
+      </c>
+      <c r="H57" s="76" t="n"/>
+      <c r="I57" s="76" t="n"/>
+      <c r="J57" s="76" t="n"/>
+    </row>
+    <row r="58" ht="30" customHeight="1" s="85">
+      <c r="A58" s="52" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C57" s="37" t="inlineStr">
-        <is>
-          <t>Blocking Foul</t>
-        </is>
-      </c>
-      <c r="D57" s="40" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
-        </is>
-      </c>
-      <c r="E57" s="26" t="n"/>
-      <c r="F57" s="50" t="n"/>
-      <c r="G57" s="72" t="n"/>
-      <c r="H57" s="71" t="n"/>
-      <c r="I57" s="71" t="n"/>
-      <c r="J57" s="71" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1" s="85">
-      <c r="A58" s="21" t="n"/>
-      <c r="B58" s="22" t="inlineStr">
+      <c r="B58" s="53">
+        <f>COUNTIF($B$56:$B$140,"Whistle")</f>
+        <v/>
+      </c>
+      <c r="C58" s="54" t="n"/>
+      <c r="D58" s="54" t="n"/>
+      <c r="E58" s="54" t="n"/>
+      <c r="F58" s="55" t="n"/>
+      <c r="G58" s="66" t="n"/>
+      <c r="H58" s="67" t="n"/>
+      <c r="I58" s="67" t="n"/>
+      <c r="J58" s="67" t="n"/>
+    </row>
+    <row r="59" ht="56" customHeight="1" s="85">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>All whistles are limited to 1</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C58" s="23" t="inlineStr">
-        <is>
-          <t>Charge</t>
-        </is>
-      </c>
-      <c r="D58" s="39" t="inlineStr">
-        <is>
-          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="n"/>
-      <c r="F58" s="50" t="n"/>
-      <c r="G58" s="70" t="n"/>
-      <c r="H58" s="71" t="n"/>
-      <c r="I58" s="71" t="n"/>
-      <c r="J58" s="71" t="n"/>
-    </row>
-    <row r="59" ht="56" customHeight="1" s="85">
-      <c r="A59" s="21" t="n"/>
-      <c r="B59" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C59" s="24" t="inlineStr">
-        <is>
-          <t>Cleared to Play</t>
-        </is>
-      </c>
-      <c r="D59" s="25" t="inlineStr">
-        <is>
-          <t>Injury Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E59" s="26" t="n"/>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>Back Court Violation</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="n"/>
       <c r="F59" s="50" t="n"/>
-      <c r="G59" s="72" t="n"/>
+      <c r="G59" s="70" t="inlineStr">
+        <is>
+          <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
+        </is>
+      </c>
       <c r="H59" s="71" t="n"/>
       <c r="I59" s="71" t="n"/>
       <c r="J59" s="71" t="n"/>
@@ -3789,23 +3792,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C60" s="23" t="inlineStr">
-        <is>
-          <t>Coach’s Challenge</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Any Whistle Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Pull a Timeout from the discards, if one is there, and take it</t>
-        </is>
-      </c>
+      <c r="C60" s="37" t="inlineStr">
+        <is>
+          <t>Blocking Foul</t>
+        </is>
+      </c>
+      <c r="D60" s="40" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="n"/>
       <c r="F60" s="50" t="n"/>
-      <c r="G60" s="70" t="n"/>
+      <c r="G60" s="72" t="n"/>
       <c r="H60" s="71" t="n"/>
       <c r="I60" s="71" t="n"/>
       <c r="J60" s="71" t="n"/>
@@ -3817,27 +3816,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C61" s="37" t="inlineStr">
-        <is>
-          <t>Delay-of-Game Warning</t>
-        </is>
-      </c>
-      <c r="D61" s="41" t="inlineStr">
-        <is>
-          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="inlineStr">
-        <is>
-          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
-        </is>
-      </c>
-      <c r="F61" s="51" t="n"/>
-      <c r="G61" s="73" t="inlineStr">
-        <is>
-          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
-        </is>
-      </c>
+      <c r="C61" s="23" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="D61" s="39" t="inlineStr">
+        <is>
+          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="50" t="n"/>
+      <c r="G61" s="70" t="n"/>
       <c r="H61" s="71" t="n"/>
       <c r="I61" s="71" t="n"/>
       <c r="J61" s="71" t="n"/>
@@ -3849,23 +3840,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C62" s="23" t="inlineStr">
-        <is>
-          <t>Double Dribble</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="n"/>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>Cleared to Play</t>
+        </is>
+      </c>
+      <c r="D62" s="25" t="inlineStr">
+        <is>
+          <t>Injury Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="n"/>
       <c r="F62" s="50" t="n"/>
-      <c r="G62" s="70" t="inlineStr">
-        <is>
-          <t>The dribbling player inbounds. The round is NOT incremented.</t>
-        </is>
-      </c>
+      <c r="G62" s="72" t="n"/>
       <c r="H62" s="71" t="n"/>
       <c r="I62" s="71" t="n"/>
       <c r="J62" s="71" t="n"/>
@@ -3877,19 +3864,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C63" s="37" t="inlineStr">
-        <is>
-          <t>Flagrant Foul</t>
-        </is>
-      </c>
-      <c r="D63" s="41" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E63" s="26" t="n"/>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>Coach’s Challenge</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Any Whistle Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pull a Timeout from the discards, if one is there, and take it</t>
+        </is>
+      </c>
       <c r="F63" s="50" t="n"/>
-      <c r="G63" s="72" t="n"/>
+      <c r="G63" s="70" t="n"/>
       <c r="H63" s="71" t="n"/>
       <c r="I63" s="71" t="n"/>
       <c r="J63" s="71" t="n"/>
@@ -3903,17 +3894,25 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>Flagrant Foul II</t>
-        </is>
-      </c>
-      <c r="D64" s="38" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="50" t="n"/>
-      <c r="G64" s="70" t="n"/>
+          <t>Delay-of-Game Warning</t>
+        </is>
+      </c>
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
+        </is>
+      </c>
+      <c r="E64" s="25" t="inlineStr">
+        <is>
+          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
+        </is>
+      </c>
+      <c r="F64" s="51" t="n"/>
+      <c r="G64" s="73" t="inlineStr">
+        <is>
+          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
+        </is>
+      </c>
       <c r="H64" s="71" t="n"/>
       <c r="I64" s="71" t="n"/>
       <c r="J64" s="71" t="n"/>
@@ -3925,19 +3924,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C65" s="24" t="inlineStr">
-        <is>
-          <t>Goaltending</t>
-        </is>
-      </c>
-      <c r="D65" s="25" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
-        </is>
-      </c>
-      <c r="E65" s="26" t="n"/>
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>Double Dribble</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="n"/>
       <c r="F65" s="50" t="n"/>
-      <c r="G65" s="72" t="n"/>
+      <c r="G65" s="70" t="inlineStr">
+        <is>
+          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+        </is>
+      </c>
       <c r="H65" s="71" t="n"/>
       <c r="I65" s="71" t="n"/>
       <c r="J65" s="71" t="n"/>
@@ -3949,19 +3952,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C66" s="23" t="inlineStr">
-        <is>
-          <t>Inadvertent Whistle</t>
-        </is>
-      </c>
-      <c r="D66" s="38" t="inlineStr">
-        <is>
-          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="n"/>
+      <c r="C66" s="37" t="inlineStr">
+        <is>
+          <t>Flagrant Foul</t>
+        </is>
+      </c>
+      <c r="D66" s="41" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="n"/>
       <c r="F66" s="50" t="n"/>
-      <c r="G66" s="70" t="n"/>
+      <c r="G66" s="72" t="n"/>
       <c r="H66" s="71" t="n"/>
       <c r="I66" s="71" t="n"/>
       <c r="J66" s="71" t="n"/>
@@ -3973,19 +3976,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C67" s="24" t="inlineStr">
-        <is>
-          <t>Official Review</t>
-        </is>
-      </c>
-      <c r="D67" s="41" t="inlineStr">
-        <is>
-          <t>Intangible Played: Discard all Intangibles from player.</t>
-        </is>
-      </c>
-      <c r="E67" s="26" t="n"/>
+      <c r="C67" s="37" t="inlineStr">
+        <is>
+          <t>Flagrant Foul II</t>
+        </is>
+      </c>
+      <c r="D67" s="38" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="n"/>
       <c r="F67" s="50" t="n"/>
-      <c r="G67" s="72" t="n"/>
+      <c r="G67" s="70" t="n"/>
       <c r="H67" s="71" t="n"/>
       <c r="I67" s="71" t="n"/>
       <c r="J67" s="71" t="n"/>
@@ -3997,23 +4000,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C68" s="23" t="inlineStr">
-        <is>
-          <t>Shot Clock Violation</t>
-        </is>
-      </c>
-      <c r="D68" s="38" t="inlineStr">
-        <is>
-          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="n"/>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>Goaltending</t>
+        </is>
+      </c>
+      <c r="D68" s="25" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="n"/>
       <c r="F68" s="50" t="n"/>
-      <c r="G68" s="70" t="inlineStr">
-        <is>
-          <t>This inbound does NOT increment the round.</t>
-        </is>
-      </c>
+      <c r="G68" s="72" t="n"/>
       <c r="H68" s="71" t="n"/>
       <c r="I68" s="71" t="n"/>
       <c r="J68" s="71" t="n"/>
@@ -4025,19 +4024,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C69" s="24" t="inlineStr">
-        <is>
-          <t>Technical Foul</t>
-        </is>
-      </c>
-      <c r="D69" s="41" t="inlineStr">
-        <is>
-          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E69" s="26" t="n"/>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>Inadvertent Whistle</t>
+        </is>
+      </c>
+      <c r="D69" s="38" t="inlineStr">
+        <is>
+          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="n"/>
       <c r="F69" s="50" t="n"/>
-      <c r="G69" s="72" t="n"/>
+      <c r="G69" s="70" t="n"/>
       <c r="H69" s="71" t="n"/>
       <c r="I69" s="71" t="n"/>
       <c r="J69" s="71" t="n"/>
@@ -4049,19 +4048,19 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C70" s="23" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
-      <c r="D70" s="38" t="inlineStr">
-        <is>
-          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="n"/>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>Official Review</t>
+        </is>
+      </c>
+      <c r="D70" s="41" t="inlineStr">
+        <is>
+          <t>Intangible Played: Discard all Intangibles from player.</t>
+        </is>
+      </c>
+      <c r="E70" s="26" t="n"/>
       <c r="F70" s="50" t="n"/>
-      <c r="G70" s="70" t="n"/>
+      <c r="G70" s="72" t="n"/>
       <c r="H70" s="71" t="n"/>
       <c r="I70" s="71" t="n"/>
       <c r="J70" s="71" t="n"/>
@@ -4073,19 +4072,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C71" s="24" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D71" s="25" t="inlineStr">
-        <is>
-          <t>Move card played: Cancel card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E71" s="26" t="n"/>
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>Shot Clock Violation</t>
+        </is>
+      </c>
+      <c r="D71" s="38" t="inlineStr">
+        <is>
+          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="n"/>
       <c r="F71" s="50" t="n"/>
-      <c r="G71" s="72" t="n"/>
+      <c r="G71" s="70" t="inlineStr">
+        <is>
+          <t>This inbound does NOT increment the round.</t>
+        </is>
+      </c>
       <c r="H71" s="71" t="n"/>
       <c r="I71" s="71" t="n"/>
       <c r="J71" s="71" t="n"/>
@@ -4099,21 +4102,17 @@
       </c>
       <c r="C72" s="24" t="inlineStr">
         <is>
-          <t>Clear Path Foul</t>
-        </is>
-      </c>
-      <c r="D72" s="25" t="inlineStr">
-        <is>
-          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
+          <t>Technical Foul</t>
+        </is>
+      </c>
+      <c r="D72" s="41" t="inlineStr">
+        <is>
+          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
         </is>
       </c>
       <c r="E72" s="26" t="n"/>
       <c r="F72" s="50" t="n"/>
-      <c r="G72" s="72" t="inlineStr">
-        <is>
-          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
-        </is>
-      </c>
+      <c r="G72" s="72" t="n"/>
       <c r="H72" s="71" t="n"/>
       <c r="I72" s="71" t="n"/>
       <c r="J72" s="71" t="n"/>
@@ -4125,151 +4124,145 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C73" s="24" t="inlineStr">
-        <is>
-          <t>Play-On</t>
-        </is>
-      </c>
-      <c r="D73" s="25" t="inlineStr">
-        <is>
-          <t>Discard each Game Break drawn and draw again, until a card is not one</t>
-        </is>
-      </c>
-      <c r="E73" s="26" t="n"/>
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D73" s="38" t="inlineStr">
+        <is>
+          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="n"/>
       <c r="F73" s="50" t="n"/>
-      <c r="G73" s="72" t="inlineStr">
-        <is>
-          <t>Raised where the Break lands, like Cleared to Play — nobody plays a Break</t>
-        </is>
-      </c>
+      <c r="G73" s="70" t="n"/>
       <c r="H73" s="71" t="n"/>
       <c r="I73" s="71" t="n"/>
       <c r="J73" s="71" t="n"/>
     </row>
     <row r="74" ht="28" customHeight="1" s="85">
-      <c r="A74" s="27" t="n"/>
-      <c r="B74" s="28" t="inlineStr">
+      <c r="A74" s="21" t="n"/>
+      <c r="B74" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C74" s="29" t="inlineStr">
-        <is>
-          <t>Crew Chief Review</t>
-        </is>
-      </c>
-      <c r="D74" s="30" t="inlineStr">
-        <is>
-          <t>Cancel a pass. The ball comes to you</t>
-        </is>
-      </c>
-      <c r="E74" s="60" t="n"/>
-      <c r="F74" s="61" t="n"/>
-      <c r="G74" s="78" t="n"/>
-      <c r="H74" s="76" t="n"/>
-      <c r="I74" s="76" t="n"/>
-      <c r="J74" s="76" t="n"/>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D74" s="25" t="inlineStr">
+        <is>
+          <t>Move card played: Cancel card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E74" s="26" t="n"/>
+      <c r="F74" s="50" t="n"/>
+      <c r="G74" s="72" t="n"/>
+      <c r="H74" s="71" t="n"/>
+      <c r="I74" s="71" t="n"/>
+      <c r="J74" s="71" t="n"/>
     </row>
     <row r="75" ht="28" customHeight="1" s="85">
-      <c r="A75" s="52" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="B75" s="53">
-        <f>COUNTIF($B$76:$B$137,"Game Break")</f>
-        <v/>
-      </c>
-      <c r="C75" s="54" t="n"/>
-      <c r="D75" s="54" t="n"/>
-      <c r="E75" s="54" t="n"/>
-      <c r="F75" s="55" t="n"/>
-      <c r="G75" s="66" t="n"/>
-      <c r="H75" s="67" t="n"/>
-      <c r="I75" s="67" t="n"/>
-      <c r="J75" s="67" t="n"/>
+      <c r="A75" s="21" t="n"/>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>Clear Path Foul</t>
+        </is>
+      </c>
+      <c r="D75" s="25" t="inlineStr">
+        <is>
+          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E75" s="26" t="n"/>
+      <c r="F75" s="50" t="n"/>
+      <c r="G75" s="72" t="inlineStr">
+        <is>
+          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
+        </is>
+      </c>
+      <c r="H75" s="71" t="n"/>
+      <c r="I75" s="71" t="n"/>
+      <c r="J75" s="71" t="n"/>
     </row>
     <row r="76" ht="28" customHeight="1" s="85">
       <c r="A76" s="21" t="n"/>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>2-Minute Warning</t>
+          <t>Play-On</t>
         </is>
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>All players discard down to 2 or fewer cards</t>
+          <t>Discard each Game Break drawn and draw again, until a card is not one</t>
         </is>
       </c>
       <c r="E76" s="26" t="n"/>
-      <c r="F76" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G76" s="72" t="n"/>
+      <c r="F76" s="50" t="n"/>
+      <c r="G76" s="72" t="inlineStr">
+        <is>
+          <t>Raised where the Break lands, like Cleared to Play — nobody plays a Break</t>
+        </is>
+      </c>
       <c r="H76" s="71" t="n"/>
       <c r="I76" s="71" t="n"/>
       <c r="J76" s="71" t="n"/>
     </row>
     <row r="77" ht="42" customHeight="1" s="85">
-      <c r="A77" s="21" t="n"/>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="A77" s="27" t="n"/>
+      <c r="B77" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>Crew Chief Review</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>Cancel a pass. The ball comes to you</t>
+        </is>
+      </c>
+      <c r="E77" s="60" t="n"/>
+      <c r="F77" s="61" t="n"/>
+      <c r="G77" s="78" t="n"/>
+      <c r="H77" s="76" t="n"/>
+      <c r="I77" s="76" t="n"/>
+      <c r="J77" s="76" t="n"/>
+    </row>
+    <row r="78" ht="28" customHeight="1" s="85">
+      <c r="A78" s="52" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C77" s="23" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" s="74" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
-      <c r="H77" s="71" t="n"/>
-      <c r="I77" s="71" t="n"/>
-      <c r="J77" s="71" t="n"/>
-    </row>
-    <row r="78" ht="28" customHeight="1" s="85">
-      <c r="A78" s="21" t="n"/>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C78" s="24" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D78" s="25" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E78" s="26" t="n"/>
-      <c r="F78" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G78" s="72" t="n"/>
-      <c r="H78" s="71" t="n"/>
-      <c r="I78" s="71" t="n"/>
-      <c r="J78" s="71" t="n"/>
+      <c r="B78" s="53">
+        <f>COUNTIF($B$76:$B$140,"Game Break")</f>
+        <v/>
+      </c>
+      <c r="C78" s="54" t="n"/>
+      <c r="D78" s="54" t="n"/>
+      <c r="E78" s="54" t="n"/>
+      <c r="F78" s="55" t="n"/>
+      <c r="G78" s="66" t="n"/>
+      <c r="H78" s="67" t="n"/>
+      <c r="I78" s="67" t="n"/>
+      <c r="J78" s="67" t="n"/>
     </row>
     <row r="79" ht="28" customHeight="1" s="85">
       <c r="A79" s="21" t="n"/>
@@ -4278,21 +4271,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C79" s="23" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="n"/>
-      <c r="F79" s="34" t="n">
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
+        </is>
+      </c>
+      <c r="D79" s="25" t="inlineStr">
+        <is>
+          <t>All players discard down to 2 or fewer cards</t>
+        </is>
+      </c>
+      <c r="E79" s="26" t="n"/>
+      <c r="F79" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G79" s="70" t="n"/>
+      <c r="G79" s="72" t="n"/>
       <c r="H79" s="71" t="n"/>
       <c r="I79" s="71" t="n"/>
       <c r="J79" s="71" t="n"/>
@@ -4304,21 +4297,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C80" s="37" t="inlineStr">
-        <is>
-          <t>Foul</t>
-        </is>
-      </c>
-      <c r="D80" s="25" t="inlineStr">
-        <is>
-          <t>Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E80" s="26" t="n"/>
-      <c r="F80" s="33" t="n">
+      <c r="C80" s="23" t="inlineStr">
+        <is>
+          <t>Benched</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Immediately give ball to any other player.</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n"/>
+      <c r="F80" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G80" s="72" t="n"/>
+      <c r="G80" s="74" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H80" s="71" t="n"/>
       <c r="I80" s="71" t="n"/>
       <c r="J80" s="71" t="n"/>
@@ -4330,21 +4327,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C81" s="23" t="inlineStr">
-        <is>
-          <t>MVP Vote</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards up to a hand of 7</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="n"/>
-      <c r="F81" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="70" t="n"/>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
+        </is>
+      </c>
+      <c r="D81" s="25" t="inlineStr">
+        <is>
+          <t>Discard 1 card.</t>
+        </is>
+      </c>
+      <c r="E81" s="26" t="n"/>
+      <c r="F81" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" s="72" t="n"/>
       <c r="H81" s="71" t="n"/>
       <c r="I81" s="71" t="n"/>
       <c r="J81" s="71" t="n"/>
@@ -4356,21 +4353,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C82" s="24" t="inlineStr">
-        <is>
-          <t>Off Night</t>
-        </is>
-      </c>
-      <c r="D82" s="25" t="inlineStr">
-        <is>
-          <t>SHOT -20% this possession</t>
-        </is>
-      </c>
-      <c r="E82" s="26" t="n"/>
-      <c r="F82" s="33" t="n">
+      <c r="C82" s="23" t="inlineStr">
+        <is>
+          <t>Designed Play</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Draw up to a hand of 5</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="n"/>
+      <c r="F82" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G82" s="72" t="n"/>
+      <c r="G82" s="70" t="n"/>
       <c r="H82" s="71" t="n"/>
       <c r="I82" s="71" t="n"/>
       <c r="J82" s="71" t="n"/>
@@ -4382,25 +4379,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C83" s="23" t="inlineStr">
-        <is>
-          <t>Swallowed Whistle</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F83" s="32" t="n">
+      <c r="C83" s="37" t="inlineStr">
+        <is>
+          <t>Foul</t>
+        </is>
+      </c>
+      <c r="D83" s="25" t="inlineStr">
+        <is>
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E83" s="26" t="n"/>
+      <c r="F83" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G83" s="70" t="n"/>
+      <c r="G83" s="72" t="n"/>
       <c r="H83" s="71" t="n"/>
       <c r="I83" s="71" t="n"/>
       <c r="J83" s="71" t="n"/>
@@ -4412,25 +4405,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C84" s="24" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
-        </is>
-      </c>
-      <c r="D84" s="25" t="inlineStr">
-        <is>
-          <t>Players cannot shoot when SHOT is 50% or higher</t>
-        </is>
-      </c>
-      <c r="E84" s="25" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F84" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G84" s="72" t="n"/>
+      <c r="C84" s="23" t="inlineStr">
+        <is>
+          <t>MVP Vote</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Draw 3 cards up to a hand of 7</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="n"/>
+      <c r="F84" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="70" t="n"/>
       <c r="H84" s="71" t="n"/>
       <c r="I84" s="71" t="n"/>
       <c r="J84" s="71" t="n"/>
@@ -4442,21 +4431,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C85" s="23" t="inlineStr">
-        <is>
-          <t>Traded Mid-Game</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>Swap hands with a random other player</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="n"/>
-      <c r="F85" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="74" t="n"/>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D85" s="25" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E85" s="26" t="n"/>
+      <c r="F85" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" s="72" t="n"/>
       <c r="H85" s="71" t="n"/>
       <c r="I85" s="71" t="n"/>
       <c r="J85" s="71" t="n"/>
@@ -4468,21 +4457,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C86" s="49" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D86" s="38" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="34" t="n">
+      <c r="C86" s="23" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F86" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="G86" s="74" t="n"/>
+      <c r="G86" s="70" t="n"/>
       <c r="H86" s="71" t="n"/>
       <c r="I86" s="71" t="n"/>
       <c r="J86" s="71" t="n"/>
@@ -4494,25 +4487,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C87" s="49" t="inlineStr">
-        <is>
-          <t>All-Swissh Selection</t>
-        </is>
-      </c>
-      <c r="D87" s="38" t="inlineStr">
-        <is>
-          <t>Draw 3 cards after your next make</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="n"/>
-      <c r="F87" s="34" t="n">
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D87" s="25" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is 50% or higher</t>
+        </is>
+      </c>
+      <c r="E87" s="25" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F87" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G87" s="74" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+      <c r="G87" s="72" t="n"/>
       <c r="H87" s="71" t="n"/>
       <c r="I87" s="71" t="n"/>
       <c r="J87" s="71" t="n"/>
@@ -4524,19 +4517,19 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C88" s="49" t="inlineStr">
-        <is>
-          <t>All Star Selection</t>
-        </is>
-      </c>
-      <c r="D88" s="38" t="inlineStr">
-        <is>
-          <t>Draw 2 cards</t>
+      <c r="C88" s="23" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Swap hands with a random other player</t>
         </is>
       </c>
       <c r="E88" s="7" t="n"/>
       <c r="F88" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G88" s="74" t="n"/>
       <c r="H88" s="71" t="n"/>
@@ -4552,23 +4545,19 @@
       </c>
       <c r="C89" s="49" t="inlineStr">
         <is>
-          <t>Hit the Bike</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D89" s="38" t="inlineStr">
         <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G89" s="74" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="G89" s="74" t="n"/>
       <c r="H89" s="71" t="n"/>
       <c r="I89" s="71" t="n"/>
       <c r="J89" s="71" t="n"/>
@@ -4582,19 +4571,23 @@
       </c>
       <c r="C90" s="49" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D90" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G90" s="74" t="n"/>
+      <c r="G90" s="74" t="inlineStr">
+        <is>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
+        </is>
+      </c>
       <c r="H90" s="71" t="n"/>
       <c r="I90" s="71" t="n"/>
       <c r="J90" s="71" t="n"/>
@@ -4608,23 +4601,19 @@
       </c>
       <c r="C91" s="49" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D91" s="38" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G91" s="74" t="inlineStr">
-        <is>
-          <t>Deck ones are shown face down</t>
-        </is>
-      </c>
+      <c r="G91" s="74" t="n"/>
       <c r="H91" s="71" t="n"/>
       <c r="I91" s="71" t="n"/>
       <c r="J91" s="71" t="n"/>
@@ -4638,12 +4627,12 @@
       </c>
       <c r="C92" s="49" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D92" s="38" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
@@ -4652,7 +4641,7 @@
       </c>
       <c r="G92" s="74" t="inlineStr">
         <is>
-          <t>This is a bad thing in the NBA</t>
+          <t>This is not a pass</t>
         </is>
       </c>
       <c r="H92" s="71" t="n"/>
@@ -4668,23 +4657,19 @@
       </c>
       <c r="C93" s="49" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D93" s="38" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G93" s="74" t="inlineStr">
-        <is>
-          <t>The hex travels in the declared direction too</t>
-        </is>
-      </c>
+      <c r="G93" s="74" t="n"/>
       <c r="H93" s="71" t="n"/>
       <c r="I93" s="71" t="n"/>
       <c r="J93" s="71" t="n"/>
@@ -4698,19 +4683,23 @@
       </c>
       <c r="C94" s="49" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D94" s="38" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G94" s="74" t="n"/>
+      <c r="G94" s="74" t="inlineStr">
+        <is>
+          <t>Deck ones are shown face down</t>
+        </is>
+      </c>
       <c r="H94" s="71" t="n"/>
       <c r="I94" s="71" t="n"/>
       <c r="J94" s="71" t="n"/>
@@ -4724,19 +4713,23 @@
       </c>
       <c r="C95" s="49" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D95" s="38" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G95" s="74" t="n"/>
+      <c r="G95" s="74" t="inlineStr">
+        <is>
+          <t>This is a bad thing in the NBA</t>
+        </is>
+      </c>
       <c r="H95" s="71" t="n"/>
       <c r="I95" s="71" t="n"/>
       <c r="J95" s="71" t="n"/>
@@ -4750,19 +4743,23 @@
       </c>
       <c r="C96" s="49" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D96" s="38" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G96" s="74" t="n"/>
+      <c r="G96" s="74" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H96" s="71" t="n"/>
       <c r="I96" s="71" t="n"/>
       <c r="J96" s="71" t="n"/>
@@ -4776,12 +4773,12 @@
       </c>
       <c r="C97" s="49" t="inlineStr">
         <is>
-          <t>Altercation</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D97" s="38" t="inlineStr">
         <is>
-          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -4802,17 +4799,17 @@
       </c>
       <c r="C98" s="49" t="inlineStr">
         <is>
-          <t>Huge Altercation</t>
+          <t>Official Timeout</t>
         </is>
       </c>
       <c r="D98" s="38" t="inlineStr">
         <is>
-          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G98" s="74" t="n"/>
       <c r="H98" s="71" t="n"/>
@@ -4828,12 +4825,12 @@
       </c>
       <c r="C99" s="49" t="inlineStr">
         <is>
-          <t>Home Court Advantage</t>
+          <t>Team Doctor</t>
         </is>
       </c>
       <c r="D99" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 10%</t>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -4854,12 +4851,12 @@
       </c>
       <c r="C100" s="49" t="inlineStr">
         <is>
-          <t>Away Game</t>
+          <t>Altercation</t>
         </is>
       </c>
       <c r="D100" s="38" t="inlineStr">
         <is>
-          <t>SHOT - 10%</t>
+          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -4880,23 +4877,19 @@
       </c>
       <c r="C101" s="49" t="inlineStr">
         <is>
-          <t>Mic'd Up</t>
+          <t>Huge Altercation</t>
         </is>
       </c>
       <c r="D101" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 10% until passed or shot</t>
+          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G101" s="74" t="inlineStr">
-        <is>
-          <t>The boost is the holder's alone and does not travel with a pass</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G101" s="74" t="n"/>
       <c r="H101" s="71" t="n"/>
       <c r="I101" s="71" t="n"/>
       <c r="J101" s="71" t="n"/>
@@ -4910,12 +4903,12 @@
       </c>
       <c r="C102" s="49" t="inlineStr">
         <is>
-          <t>In The Zone</t>
+          <t>Home Court Advantage</t>
         </is>
       </c>
       <c r="D102" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+          <t>SHOT + 10%</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -4936,12 +4929,12 @@
       </c>
       <c r="C103" s="49" t="inlineStr">
         <is>
-          <t>Role Player</t>
+          <t>Away Game</t>
         </is>
       </c>
       <c r="D103" s="38" t="inlineStr">
         <is>
-          <t>All other players draw 1 card</t>
+          <t>SHOT - 10%</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -4954,230 +4947,247 @@
       <c r="J103" s="71" t="n"/>
     </row>
     <row r="104" ht="14" customHeight="1" s="85">
-      <c r="A104" s="27" t="n"/>
-      <c r="B104" s="28" t="inlineStr">
+      <c r="A104" s="21" t="n"/>
+      <c r="B104" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C104" s="62" t="inlineStr">
+      <c r="C104" s="49" t="inlineStr">
+        <is>
+          <t>Mic'd Up</t>
+        </is>
+      </c>
+      <c r="D104" s="38" t="inlineStr">
+        <is>
+          <t>SHOT + 10% until passed or shot</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="n"/>
+      <c r="F104" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" s="74" t="inlineStr">
+        <is>
+          <t>The boost is the holder's alone and does not travel with a pass</t>
+        </is>
+      </c>
+      <c r="H104" s="71" t="n"/>
+      <c r="I104" s="71" t="n"/>
+      <c r="J104" s="71" t="n"/>
+    </row>
+    <row r="105" ht="28" customHeight="1" s="85">
+      <c r="A105" s="21" t="n"/>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C105" s="49" t="inlineStr">
+        <is>
+          <t>In The Zone</t>
+        </is>
+      </c>
+      <c r="D105" s="38" t="inlineStr">
+        <is>
+          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="n"/>
+      <c r="F105" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G105" s="74" t="n"/>
+      <c r="H105" s="71" t="n"/>
+      <c r="I105" s="71" t="n"/>
+      <c r="J105" s="71" t="n"/>
+    </row>
+    <row r="106" ht="28" customHeight="1" s="85">
+      <c r="A106" s="21" t="n"/>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C106" s="49" t="inlineStr">
+        <is>
+          <t>Role Player</t>
+        </is>
+      </c>
+      <c r="D106" s="38" t="inlineStr">
+        <is>
+          <t>All other players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="n"/>
+      <c r="F106" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" s="74" t="n"/>
+      <c r="H106" s="71" t="n"/>
+      <c r="I106" s="71" t="n"/>
+      <c r="J106" s="71" t="n"/>
+    </row>
+    <row r="107" ht="28" customHeight="1" s="85">
+      <c r="A107" s="27" t="n"/>
+      <c r="B107" s="28" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C107" s="62" t="inlineStr">
         <is>
           <t>Back-and-Forth Game</t>
         </is>
       </c>
-      <c r="D104" s="63" t="inlineStr">
+      <c r="D107" s="63" t="inlineStr">
         <is>
           <t>Discard the next 3 Game Breaks. Whoever draws one draws again</t>
         </is>
       </c>
-      <c r="E104" s="58" t="n"/>
-      <c r="F104" s="59" t="n">
+      <c r="E107" s="58" t="n"/>
+      <c r="F107" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="G104" s="79" t="n"/>
-      <c r="H104" s="76" t="n"/>
-      <c r="I104" s="76" t="n"/>
-      <c r="J104" s="76" t="n"/>
-    </row>
-    <row r="105" ht="28" customHeight="1" s="85">
-      <c r="A105" s="52" t="inlineStr">
+      <c r="G107" s="79" t="n"/>
+      <c r="H107" s="76" t="n"/>
+      <c r="I107" s="76" t="n"/>
+      <c r="J107" s="76" t="n"/>
+    </row>
+    <row r="108" ht="28" customHeight="1" s="85">
+      <c r="A108" s="52" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="B105" s="53">
-        <f>COUNTIF($B$106:$B$137,"Injury GB")</f>
+      <c r="B108" s="53">
+        <f>COUNTIF($B$106:$B$140,"Injury GB")</f>
         <v/>
       </c>
-      <c r="C105" s="54" t="n"/>
-      <c r="D105" s="54" t="n"/>
-      <c r="E105" s="54" t="n"/>
-      <c r="F105" s="55" t="n"/>
-      <c r="G105" s="66" t="n"/>
-      <c r="H105" s="67" t="n"/>
-      <c r="I105" s="67" t="n"/>
-      <c r="J105" s="67" t="n"/>
-    </row>
-    <row r="106" ht="28" customHeight="1" s="85">
-      <c r="A106" s="27" t="n"/>
-      <c r="B106" s="28" t="inlineStr">
+      <c r="C108" s="54" t="n"/>
+      <c r="D108" s="54" t="n"/>
+      <c r="E108" s="54" t="n"/>
+      <c r="F108" s="55" t="n"/>
+      <c r="G108" s="66" t="n"/>
+      <c r="H108" s="67" t="n"/>
+      <c r="I108" s="67" t="n"/>
+      <c r="J108" s="67" t="n"/>
+    </row>
+    <row r="109" ht="42" customHeight="1" s="85">
+      <c r="A109" s="27" t="n"/>
+      <c r="B109" s="28" t="inlineStr">
         <is>
           <t>Injury GB</t>
         </is>
       </c>
-      <c r="C106" s="56" t="inlineStr">
+      <c r="C109" s="56" t="inlineStr">
         <is>
           <t>Bone Bruise</t>
         </is>
       </c>
-      <c r="D106" s="63" t="inlineStr">
+      <c r="D109" s="63" t="inlineStr">
         <is>
           <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
         </is>
       </c>
-      <c r="E106" s="58" t="n"/>
-      <c r="F106" s="59" t="n">
+      <c r="E109" s="58" t="n"/>
+      <c r="F109" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="G106" s="75" t="n"/>
-      <c r="H106" s="76" t="n"/>
-      <c r="I106" s="76" t="n"/>
-      <c r="J106" s="76" t="n"/>
-    </row>
-    <row r="107" ht="28" customHeight="1" s="85">
-      <c r="A107" s="52" t="inlineStr">
+      <c r="G109" s="75" t="n"/>
+      <c r="H109" s="76" t="n"/>
+      <c r="I109" s="76" t="n"/>
+      <c r="J109" s="76" t="n"/>
+    </row>
+    <row r="110" ht="56" customHeight="1" s="85">
+      <c r="A110" s="52" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="B107" s="53">
-        <f>COUNTIF($B$108:$B$137,"Devastating Injury GB")</f>
+      <c r="B110" s="53">
+        <f>COUNTIF($B$108:$B$140,"Devastating Injury GB")</f>
         <v/>
       </c>
-      <c r="C107" s="54" t="n"/>
-      <c r="D107" s="54" t="n"/>
-      <c r="E107" s="54" t="n"/>
-      <c r="F107" s="55" t="n"/>
-      <c r="G107" s="66" t="n"/>
-      <c r="H107" s="67" t="n"/>
-      <c r="I107" s="67" t="n"/>
-      <c r="J107" s="67" t="n"/>
-    </row>
-    <row r="108" ht="28" customHeight="1" s="85">
-      <c r="A108" s="27" t="n"/>
-      <c r="B108" s="28" t="inlineStr">
+      <c r="C110" s="54" t="n"/>
+      <c r="D110" s="54" t="n"/>
+      <c r="E110" s="54" t="n"/>
+      <c r="F110" s="55" t="n"/>
+      <c r="G110" s="66" t="n"/>
+      <c r="H110" s="67" t="n"/>
+      <c r="I110" s="67" t="n"/>
+      <c r="J110" s="67" t="n"/>
+    </row>
+    <row r="111" ht="57" customHeight="1" s="85">
+      <c r="A111" s="27" t="n"/>
+      <c r="B111" s="28" t="inlineStr">
         <is>
           <t>Devastating Injury GB</t>
         </is>
       </c>
-      <c r="C108" s="64" t="inlineStr">
+      <c r="C111" s="64" t="inlineStr">
         <is>
           <t>Torn Achilles</t>
         </is>
       </c>
-      <c r="D108" s="65" t="inlineStr">
+      <c r="D111" s="65" t="inlineStr">
         <is>
           <t>Hand is locked every turn except 1 card (randomly)</t>
         </is>
       </c>
-      <c r="E108" s="58" t="n"/>
-      <c r="F108" s="61" t="n"/>
-      <c r="G108" s="75" t="n"/>
-      <c r="H108" s="76" t="n"/>
-      <c r="I108" s="76" t="n"/>
-      <c r="J108" s="76" t="n"/>
-    </row>
-    <row r="109" ht="42" customHeight="1" s="85">
-      <c r="A109" s="52" t="inlineStr">
+      <c r="E111" s="58" t="n"/>
+      <c r="F111" s="61" t="n"/>
+      <c r="G111" s="75" t="n"/>
+      <c r="H111" s="76" t="n"/>
+      <c r="I111" s="76" t="n"/>
+      <c r="J111" s="76" t="n"/>
+    </row>
+    <row r="112" ht="20" customHeight="1" s="85">
+      <c r="A112" s="52" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B109" s="53">
-        <f>COUNTIF($B$110:$B$137,"Intangible")</f>
+      <c r="B112" s="53">
+        <f>COUNTIF($B$110:$B$140,"Intangible")</f>
         <v/>
       </c>
-      <c r="C109" s="54" t="n"/>
-      <c r="D109" s="54" t="n"/>
-      <c r="E109" s="54" t="n"/>
-      <c r="F109" s="55" t="n"/>
-      <c r="G109" s="66" t="n"/>
-      <c r="H109" s="67" t="n"/>
-      <c r="I109" s="67" t="n"/>
-      <c r="J109" s="67" t="n"/>
-    </row>
-    <row r="110" ht="56" customHeight="1" s="85">
-      <c r="A110" s="42" t="inlineStr">
+      <c r="C112" s="54" t="n"/>
+      <c r="D112" s="54" t="n"/>
+      <c r="E112" s="54" t="n"/>
+      <c r="F112" s="55" t="n"/>
+      <c r="G112" s="66" t="n"/>
+      <c r="H112" s="67" t="n"/>
+      <c r="I112" s="67" t="n"/>
+      <c r="J112" s="67" t="n"/>
+    </row>
+    <row r="113" ht="28" customHeight="1" s="85">
+      <c r="A113" s="42" t="inlineStr">
         <is>
           <t>All intangibles are limited to 1</t>
         </is>
       </c>
-      <c r="B110" s="22" t="inlineStr">
+      <c r="B113" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C110" s="23" t="inlineStr">
+      <c r="C113" s="23" t="inlineStr">
         <is>
           <t>Board-Crasher</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>SHOT +10% upon Rebounding your own missed shot</t>
         </is>
       </c>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="50" t="n"/>
-      <c r="G110" s="70" t="n"/>
-      <c r="H110" s="71" t="n"/>
-      <c r="I110" s="71" t="n"/>
-      <c r="J110" s="71" t="n"/>
-    </row>
-    <row r="111" ht="57" customHeight="1" s="85">
-      <c r="A111" s="21" t="n"/>
-      <c r="B111" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C111" s="24" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D111" s="25" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E111" s="26" t="n"/>
-      <c r="F111" s="50" t="n"/>
-      <c r="G111" s="72" t="n"/>
-      <c r="H111" s="71" t="n"/>
-      <c r="I111" s="71" t="n"/>
-      <c r="J111" s="71" t="n"/>
-    </row>
-    <row r="112" ht="20" customHeight="1" s="85">
-      <c r="A112" s="21" t="n"/>
-      <c r="B112" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C112" s="23" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
-        </is>
-      </c>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="50" t="n"/>
-      <c r="G112" s="70" t="n"/>
-      <c r="H112" s="71" t="n"/>
-      <c r="I112" s="71" t="n"/>
-      <c r="J112" s="71" t="n"/>
-    </row>
-    <row r="113" ht="28" customHeight="1" s="85">
-      <c r="B113" s="0" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C113" s="0" t="inlineStr">
-        <is>
-          <t>Roswell Reach</t>
-        </is>
-      </c>
-      <c r="D113" s="0" t="inlineStr">
-        <is>
-          <t>All your Rebound bids of 1 or more count as 1 higher</t>
-        </is>
-      </c>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="50" t="n"/>
+      <c r="G113" s="70" t="n"/>
+      <c r="H113" s="71" t="n"/>
+      <c r="I113" s="71" t="n"/>
+      <c r="J113" s="71" t="n"/>
     </row>
     <row r="114" ht="42" customHeight="1" s="85">
       <c r="A114" s="21" t="n"/>
@@ -5188,12 +5198,12 @@
       </c>
       <c r="C114" s="24" t="inlineStr">
         <is>
-          <t>Floor General</t>
+          <t>Catch &amp; Shoot Specialist</t>
         </is>
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
+          <t>Additional SHOT +10% on all received passes</t>
         </is>
       </c>
       <c r="E114" s="26" t="n"/>
@@ -5212,48 +5222,37 @@
       </c>
       <c r="C115" s="23" t="inlineStr">
         <is>
-          <t>Fox-Like First Step</t>
+          <t>Clutch Gene</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F115" s="51" t="n"/>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="50" t="n"/>
       <c r="G115" s="70" t="n"/>
       <c r="H115" s="71" t="n"/>
       <c r="I115" s="71" t="n"/>
       <c r="J115" s="71" t="n"/>
     </row>
     <row r="116" ht="28" customHeight="1" s="85">
-      <c r="A116" s="21" t="n"/>
-      <c r="B116" s="22" t="inlineStr">
+      <c r="B116" s="0" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C116" s="37" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D116" s="41" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E116" s="26" t="n"/>
-      <c r="F116" s="50" t="n"/>
-      <c r="G116" s="77" t="n"/>
-      <c r="H116" s="71" t="n"/>
-      <c r="I116" s="71" t="n"/>
-      <c r="J116" s="71" t="n"/>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>Roswell Reach</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="inlineStr">
+        <is>
+          <t>All your Rebound bids of 1 or more count as 1 higher</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="56" customHeight="1" s="85">
       <c r="A117" s="21" t="n"/>
@@ -5262,19 +5261,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C117" s="37" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D117" s="38" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="n"/>
+      <c r="C117" s="24" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D117" s="25" t="inlineStr">
+        <is>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
+        </is>
+      </c>
+      <c r="E117" s="26" t="n"/>
       <c r="F117" s="50" t="n"/>
-      <c r="G117" s="70" t="n"/>
+      <c r="G117" s="72" t="n"/>
       <c r="H117" s="71" t="n"/>
       <c r="I117" s="71" t="n"/>
       <c r="J117" s="71" t="n"/>
@@ -5286,19 +5285,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C118" s="24" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D118" s="25" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E118" s="26" t="n"/>
-      <c r="F118" s="50" t="n"/>
-      <c r="G118" s="72" t="n"/>
+      <c r="C118" s="23" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F118" s="51" t="n"/>
+      <c r="G118" s="70" t="n"/>
       <c r="H118" s="71" t="n"/>
       <c r="I118" s="71" t="n"/>
       <c r="J118" s="71" t="n"/>
@@ -5310,19 +5313,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C119" s="23" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="n"/>
+      <c r="C119" s="37" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D119" s="41" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
+        </is>
+      </c>
+      <c r="E119" s="26" t="n"/>
       <c r="F119" s="50" t="n"/>
-      <c r="G119" s="70" t="n"/>
+      <c r="G119" s="77" t="n"/>
       <c r="H119" s="71" t="n"/>
       <c r="I119" s="71" t="n"/>
       <c r="J119" s="71" t="n"/>
@@ -5334,19 +5337,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C120" s="24" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D120" s="25" t="inlineStr">
-        <is>
-          <t>SHOT +20% if you scored last round.</t>
-        </is>
-      </c>
-      <c r="E120" s="26" t="n"/>
+      <c r="C120" s="37" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D120" s="38" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="n"/>
       <c r="F120" s="50" t="n"/>
-      <c r="G120" s="72" t="n"/>
+      <c r="G120" s="70" t="n"/>
       <c r="H120" s="71" t="n"/>
       <c r="I120" s="71" t="n"/>
       <c r="J120" s="71" t="n"/>
@@ -5358,19 +5361,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C121" s="23" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D121" s="38" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="n"/>
+      <c r="C121" s="24" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="D121" s="25" t="inlineStr">
+        <is>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+        </is>
+      </c>
+      <c r="E121" s="26" t="n"/>
       <c r="F121" s="50" t="n"/>
-      <c r="G121" s="70" t="n"/>
+      <c r="G121" s="72" t="n"/>
       <c r="H121" s="71" t="n"/>
       <c r="I121" s="71" t="n"/>
       <c r="J121" s="71" t="n"/>
@@ -5382,23 +5385,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C122" s="24" t="inlineStr">
-        <is>
-          <t>No Bag</t>
-        </is>
-      </c>
-      <c r="D122" s="25" t="inlineStr">
-        <is>
-          <t>Cannot activate Move cards this round</t>
-        </is>
-      </c>
-      <c r="E122" s="26" t="n"/>
+      <c r="C122" s="23" t="inlineStr">
+        <is>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="n"/>
       <c r="F122" s="50" t="n"/>
-      <c r="G122" s="73" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G122" s="70" t="n"/>
       <c r="H122" s="71" t="n"/>
       <c r="I122" s="71" t="n"/>
       <c r="J122" s="71" t="n"/>
@@ -5410,19 +5409,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C123" s="23" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="n"/>
+      <c r="C123" s="24" t="inlineStr">
+        <is>
+          <t>Hot Hand</t>
+        </is>
+      </c>
+      <c r="D123" s="25" t="inlineStr">
+        <is>
+          <t>SHOT +20% if you scored last round.</t>
+        </is>
+      </c>
+      <c r="E123" s="26" t="n"/>
       <c r="F123" s="50" t="n"/>
-      <c r="G123" s="70" t="n"/>
+      <c r="G123" s="72" t="n"/>
       <c r="H123" s="71" t="n"/>
       <c r="I123" s="71" t="n"/>
       <c r="J123" s="71" t="n"/>
@@ -5434,23 +5433,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C124" s="24" t="inlineStr">
-        <is>
-          <t>Shooting Slump</t>
-        </is>
-      </c>
-      <c r="D124" s="25" t="inlineStr">
-        <is>
-          <t>SHOT -20% this round</t>
-        </is>
-      </c>
-      <c r="E124" s="26" t="n"/>
+      <c r="C124" s="23" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D124" s="38" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="n"/>
       <c r="F124" s="50" t="n"/>
-      <c r="G124" s="73" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G124" s="70" t="n"/>
       <c r="H124" s="71" t="n"/>
       <c r="I124" s="71" t="n"/>
       <c r="J124" s="71" t="n"/>
@@ -5462,19 +5457,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C125" s="23" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="n"/>
+      <c r="C125" s="24" t="inlineStr">
+        <is>
+          <t>No Bag</t>
+        </is>
+      </c>
+      <c r="D125" s="25" t="inlineStr">
+        <is>
+          <t>Cannot activate Move cards this round</t>
+        </is>
+      </c>
+      <c r="E125" s="26" t="n"/>
       <c r="F125" s="50" t="n"/>
-      <c r="G125" s="70" t="n"/>
+      <c r="G125" s="73" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H125" s="71" t="n"/>
       <c r="I125" s="71" t="n"/>
       <c r="J125" s="71" t="n"/>
@@ -5486,19 +5485,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C126" s="24" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D126" s="25" t="inlineStr">
-        <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
-        </is>
-      </c>
-      <c r="E126" s="26" t="n"/>
+      <c r="C126" s="23" t="inlineStr">
+        <is>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="n"/>
       <c r="F126" s="50" t="n"/>
-      <c r="G126" s="72" t="n"/>
+      <c r="G126" s="70" t="n"/>
       <c r="H126" s="71" t="n"/>
       <c r="I126" s="71" t="n"/>
       <c r="J126" s="71" t="n"/>
@@ -5510,19 +5509,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C127" s="23" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="n"/>
+      <c r="C127" s="24" t="inlineStr">
+        <is>
+          <t>Shooting Slump</t>
+        </is>
+      </c>
+      <c r="D127" s="25" t="inlineStr">
+        <is>
+          <t>SHOT -20% this round</t>
+        </is>
+      </c>
+      <c r="E127" s="26" t="n"/>
       <c r="F127" s="50" t="n"/>
-      <c r="G127" s="70" t="n"/>
+      <c r="G127" s="73" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H127" s="71" t="n"/>
       <c r="I127" s="71" t="n"/>
       <c r="J127" s="71" t="n"/>
@@ -5534,19 +5537,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C128" s="24" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D128" s="25" t="inlineStr">
-        <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
-        </is>
-      </c>
-      <c r="E128" s="26" t="n"/>
+      <c r="C128" s="23" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="n"/>
       <c r="F128" s="50" t="n"/>
-      <c r="G128" s="72" t="n"/>
+      <c r="G128" s="70" t="n"/>
       <c r="H128" s="71" t="n"/>
       <c r="I128" s="71" t="n"/>
       <c r="J128" s="71" t="n"/>
@@ -5558,19 +5561,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C129" s="23" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D129" s="38" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="n"/>
+      <c r="C129" s="24" t="inlineStr">
+        <is>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D129" s="25" t="inlineStr">
+        <is>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
+        </is>
+      </c>
+      <c r="E129" s="26" t="n"/>
       <c r="F129" s="50" t="n"/>
-      <c r="G129" s="70" t="n"/>
+      <c r="G129" s="72" t="n"/>
       <c r="H129" s="71" t="n"/>
       <c r="I129" s="71" t="n"/>
       <c r="J129" s="71" t="n"/>
@@ -5582,23 +5585,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C130" s="24" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D130" s="25" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
-        </is>
-      </c>
-      <c r="E130" s="26" t="n"/>
+      <c r="C130" s="23" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="n"/>
       <c r="F130" s="50" t="n"/>
-      <c r="G130" s="73" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G130" s="70" t="n"/>
       <c r="H130" s="71" t="n"/>
       <c r="I130" s="71" t="n"/>
       <c r="J130" s="71" t="n"/>
@@ -5610,19 +5609,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C131" s="23" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D131" s="38" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="n"/>
+      <c r="C131" s="24" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D131" s="25" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E131" s="26" t="n"/>
       <c r="F131" s="50" t="n"/>
-      <c r="G131" s="70" t="n"/>
+      <c r="G131" s="72" t="n"/>
       <c r="H131" s="71" t="n"/>
       <c r="I131" s="71" t="n"/>
       <c r="J131" s="71" t="n"/>
@@ -5636,12 +5635,12 @@
       </c>
       <c r="C132" s="23" t="inlineStr">
         <is>
-          <t>Unselfish</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="D132" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
+          <t>All Clamps on you have no effect on SHOT %</t>
         </is>
       </c>
       <c r="E132" s="7" t="n"/>
@@ -5658,19 +5657,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C133" s="23" t="inlineStr">
-        <is>
-          <t>Dirty Player</t>
-        </is>
-      </c>
-      <c r="D133" s="38" t="inlineStr">
-        <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="n"/>
+      <c r="C133" s="24" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D133" s="25" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E133" s="26" t="n"/>
       <c r="F133" s="50" t="n"/>
-      <c r="G133" s="70" t="n"/>
+      <c r="G133" s="73" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
       <c r="H133" s="71" t="n"/>
       <c r="I133" s="71" t="n"/>
       <c r="J133" s="71" t="n"/>
@@ -5684,21 +5687,17 @@
       </c>
       <c r="C134" s="23" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D134" s="38" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="50" t="n"/>
-      <c r="G134" s="70" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="G134" s="70" t="n"/>
       <c r="H134" s="71" t="n"/>
       <c r="I134" s="71" t="n"/>
       <c r="J134" s="71" t="n"/>
@@ -5712,21 +5711,17 @@
       </c>
       <c r="C135" s="23" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D135" s="38" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E135" s="7" t="n"/>
       <c r="F135" s="50" t="n"/>
-      <c r="G135" s="70" t="inlineStr">
-        <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
-        </is>
-      </c>
+      <c r="G135" s="70" t="n"/>
       <c r="H135" s="71" t="n"/>
       <c r="I135" s="71" t="n"/>
       <c r="J135" s="71" t="n"/>
@@ -5740,12 +5735,12 @@
       </c>
       <c r="C136" s="23" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D136" s="38" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E136" s="7" t="n"/>
@@ -5756,28 +5751,108 @@
       <c r="J136" s="71" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="27" t="n"/>
-      <c r="B137" s="28" t="inlineStr">
+      <c r="A137" s="21" t="n"/>
+      <c r="B137" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C137" s="56" t="inlineStr">
+      <c r="C137" s="23" t="inlineStr">
+        <is>
+          <t>Villainous Reputation</t>
+        </is>
+      </c>
+      <c r="D137" s="38" t="inlineStr">
+        <is>
+          <t>Discard 1 whenever any Whistle triggers</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="n"/>
+      <c r="F137" s="50" t="n"/>
+      <c r="G137" s="70" t="inlineStr">
+        <is>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
+        </is>
+      </c>
+      <c r="H137" s="71" t="n"/>
+      <c r="I137" s="71" t="n"/>
+      <c r="J137" s="71" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="21" t="n"/>
+      <c r="B138" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C138" s="23" t="inlineStr">
+        <is>
+          <t>Free Agent</t>
+        </is>
+      </c>
+      <c r="D138" s="38" t="inlineStr">
+        <is>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="n"/>
+      <c r="F138" s="50" t="n"/>
+      <c r="G138" s="70" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+        </is>
+      </c>
+      <c r="H138" s="71" t="n"/>
+      <c r="I138" s="71" t="n"/>
+      <c r="J138" s="71" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="21" t="n"/>
+      <c r="B139" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C139" s="23" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D139" s="38" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="n"/>
+      <c r="F139" s="50" t="n"/>
+      <c r="G139" s="70" t="n"/>
+      <c r="H139" s="71" t="n"/>
+      <c r="I139" s="71" t="n"/>
+      <c r="J139" s="71" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="27" t="n"/>
+      <c r="B140" s="28" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C140" s="56" t="inlineStr">
         <is>
           <t>Fundamentalist</t>
         </is>
       </c>
-      <c r="D137" s="63" t="inlineStr">
+      <c r="D140" s="63" t="inlineStr">
         <is>
           <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent</t>
         </is>
       </c>
-      <c r="E137" s="58" t="n"/>
-      <c r="F137" s="61" t="n"/>
-      <c r="G137" s="75" t="n"/>
-      <c r="H137" s="76" t="n"/>
-      <c r="I137" s="76" t="n"/>
-      <c r="J137" s="76" t="n"/>
+      <c r="E140" s="58" t="n"/>
+      <c r="F140" s="61" t="n"/>
+      <c r="G140" s="75" t="n"/>
+      <c r="H140" s="76" t="n"/>
+      <c r="I140" s="76" t="n"/>
+      <c r="J140" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="123">

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2701,7 +2701,7 @@
       </c>
       <c r="E22" s="26" t="n"/>
       <c r="F22" s="33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="72" t="n"/>
       <c r="H22" s="71" t="n"/>
@@ -5799,7 +5799,7 @@
       <c r="F138" s="50" t="n"/>
       <c r="G138" s="70" t="inlineStr">
         <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid</t>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
         </is>
       </c>
       <c r="H138" s="71" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>Players cannot shoot when SHOT is 50% or higher</t>
+          <t>Players cannot shoot when SHOT is above 50%</t>
         </is>
       </c>
       <c r="E87" s="25" t="inlineStr">

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2065,7 +2065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="B5" s="53">
-        <f>COUNTIF($B$6:$B$140,"Pass")</f>
+        <f>COUNTIF($B$6:$B$143,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="54" t="n"/>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="B21" s="53">
-        <f>COUNTIF($B$22:$B$140,"Move")+COUNTIF($B$22:$B$140,"Special Move")</f>
+        <f>COUNTIF($B$22:$B$143,"Move")+COUNTIF($B$22:$B$143,"Special Move")</f>
         <v/>
       </c>
       <c r="C21" s="54" t="n"/>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="B35" s="53">
-        <f>COUNTIF($B$36:$B$140,"Special Move")</f>
+        <f>COUNTIF($B$36:$B$143,"Special Move")</f>
         <v/>
       </c>
       <c r="C35" s="54" t="n"/>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="B52" s="53">
-        <f>COUNTIF($B$50:$B$140,"Clamp")</f>
+        <f>COUNTIF($B$53:$B$143,"Clamp")</f>
         <v/>
       </c>
       <c r="C52" s="54" t="n"/>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="B58" s="53">
-        <f>COUNTIF($B$56:$B$140,"Whistle")</f>
+        <f>COUNTIF($B$59:$B$143,"Whistle")</f>
         <v/>
       </c>
       <c r="C58" s="54" t="n"/>
@@ -4246,49 +4246,47 @@
       <c r="J77" s="76" t="n"/>
     </row>
     <row r="78" ht="28" customHeight="1" s="85">
-      <c r="A78" s="52" t="inlineStr">
+      <c r="A78" s="27" t="n"/>
+      <c r="B78" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>Discontinued Dribble</t>
+        </is>
+      </c>
+      <c r="D78" s="30" t="inlineStr">
+        <is>
+          <t>Card Drawn: That player's possession ends immediately. They inbound</t>
+        </is>
+      </c>
+      <c r="E78" s="60" t="n"/>
+      <c r="F78" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="78" t="n"/>
+      <c r="H78" s="76" t="n"/>
+    </row>
+    <row r="79" ht="28" customHeight="1" s="85">
+      <c r="A79" s="52" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="B78" s="53">
-        <f>COUNTIF($B$76:$B$140,"Game Break")</f>
+      <c r="B79" s="53">
+        <f>COUNTIF($B$80:$B$143,"Game Break")</f>
         <v/>
       </c>
-      <c r="C78" s="54" t="n"/>
-      <c r="D78" s="54" t="n"/>
-      <c r="E78" s="54" t="n"/>
-      <c r="F78" s="55" t="n"/>
-      <c r="G78" s="66" t="n"/>
-      <c r="H78" s="67" t="n"/>
-      <c r="I78" s="67" t="n"/>
-      <c r="J78" s="67" t="n"/>
-    </row>
-    <row r="79" ht="28" customHeight="1" s="85">
-      <c r="A79" s="21" t="n"/>
-      <c r="B79" s="22" t="inlineStr">
-        <is>
-          <t>Game Break</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="inlineStr">
-        <is>
-          <t>2-Minute Warning</t>
-        </is>
-      </c>
-      <c r="D79" s="25" t="inlineStr">
-        <is>
-          <t>All players discard down to 2 or fewer cards</t>
-        </is>
-      </c>
-      <c r="E79" s="26" t="n"/>
-      <c r="F79" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" s="72" t="n"/>
-      <c r="H79" s="71" t="n"/>
-      <c r="I79" s="71" t="n"/>
-      <c r="J79" s="71" t="n"/>
+      <c r="C79" s="54" t="n"/>
+      <c r="D79" s="54" t="n"/>
+      <c r="E79" s="54" t="n"/>
+      <c r="F79" s="55" t="n"/>
+      <c r="G79" s="66" t="n"/>
+      <c r="H79" s="67" t="n"/>
+      <c r="I79" s="67" t="n"/>
+      <c r="J79" s="67" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1" s="85">
       <c r="A80" s="21" t="n"/>
@@ -4297,25 +4295,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C80" s="23" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="n"/>
-      <c r="F80" s="34" t="n">
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
+        </is>
+      </c>
+      <c r="D80" s="25" t="inlineStr">
+        <is>
+          <t>All players discard down to 2 or fewer cards</t>
+        </is>
+      </c>
+      <c r="E80" s="26" t="n"/>
+      <c r="F80" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G80" s="74" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="G80" s="72" t="n"/>
       <c r="H80" s="71" t="n"/>
       <c r="I80" s="71" t="n"/>
       <c r="J80" s="71" t="n"/>
@@ -4327,21 +4321,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C81" s="24" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D81" s="25" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E81" s="26" t="n"/>
-      <c r="F81" s="33" t="n">
+      <c r="C81" s="23" t="inlineStr">
+        <is>
+          <t>Benched</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Immediately give ball to any other player.</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G81" s="72" t="n"/>
+      <c r="G81" s="74" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H81" s="71" t="n"/>
       <c r="I81" s="71" t="n"/>
       <c r="J81" s="71" t="n"/>
@@ -4353,21 +4351,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C82" s="23" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="34" t="n">
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
+        </is>
+      </c>
+      <c r="D82" s="25" t="inlineStr">
+        <is>
+          <t>Discard 1 card.</t>
+        </is>
+      </c>
+      <c r="E82" s="26" t="n"/>
+      <c r="F82" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G82" s="70" t="n"/>
+      <c r="G82" s="72" t="n"/>
       <c r="H82" s="71" t="n"/>
       <c r="I82" s="71" t="n"/>
       <c r="J82" s="71" t="n"/>
@@ -4379,21 +4377,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C83" s="37" t="inlineStr">
-        <is>
-          <t>Foul</t>
-        </is>
-      </c>
-      <c r="D83" s="25" t="inlineStr">
-        <is>
-          <t>Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E83" s="26" t="n"/>
-      <c r="F83" s="33" t="n">
+      <c r="C83" s="23" t="inlineStr">
+        <is>
+          <t>Designed Play</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Draw up to a hand of 5</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="n"/>
+      <c r="F83" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G83" s="72" t="n"/>
+      <c r="G83" s="70" t="n"/>
       <c r="H83" s="71" t="n"/>
       <c r="I83" s="71" t="n"/>
       <c r="J83" s="71" t="n"/>
@@ -4405,21 +4403,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C84" s="23" t="inlineStr">
-        <is>
-          <t>MVP Vote</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards up to a hand of 7</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="n"/>
-      <c r="F84" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="70" t="n"/>
+      <c r="C84" s="37" t="inlineStr">
+        <is>
+          <t>Foul</t>
+        </is>
+      </c>
+      <c r="D84" s="25" t="inlineStr">
+        <is>
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E84" s="26" t="n"/>
+      <c r="F84" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="72" t="n"/>
       <c r="H84" s="71" t="n"/>
       <c r="I84" s="71" t="n"/>
       <c r="J84" s="71" t="n"/>
@@ -4431,21 +4429,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C85" s="24" t="inlineStr">
-        <is>
-          <t>Off Night</t>
-        </is>
-      </c>
-      <c r="D85" s="25" t="inlineStr">
-        <is>
-          <t>SHOT -20% this possession</t>
-        </is>
-      </c>
-      <c r="E85" s="26" t="n"/>
-      <c r="F85" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G85" s="72" t="n"/>
+      <c r="C85" s="23" t="inlineStr">
+        <is>
+          <t>MVP Vote</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Draw 3 cards up to a hand of 7</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="70" t="n"/>
       <c r="H85" s="71" t="n"/>
       <c r="I85" s="71" t="n"/>
       <c r="J85" s="71" t="n"/>
@@ -4457,25 +4455,21 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C86" s="23" t="inlineStr">
-        <is>
-          <t>Swallowed Whistle</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F86" s="32" t="n">
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D86" s="25" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E86" s="26" t="n"/>
+      <c r="F86" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G86" s="70" t="n"/>
+      <c r="G86" s="72" t="n"/>
       <c r="H86" s="71" t="n"/>
       <c r="I86" s="71" t="n"/>
       <c r="J86" s="71" t="n"/>
@@ -4487,25 +4481,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C87" s="24" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
-        </is>
-      </c>
-      <c r="D87" s="25" t="inlineStr">
-        <is>
-          <t>Players cannot shoot when SHOT is above 50%</t>
-        </is>
-      </c>
-      <c r="E87" s="25" t="inlineStr">
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>Remains for remainder of round</t>
         </is>
       </c>
-      <c r="F87" s="36" t="n">
+      <c r="F87" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="G87" s="72" t="n"/>
+      <c r="G87" s="70" t="n"/>
       <c r="H87" s="71" t="n"/>
       <c r="I87" s="71" t="n"/>
       <c r="J87" s="71" t="n"/>
@@ -4517,21 +4511,25 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C88" s="23" t="inlineStr">
-        <is>
-          <t>Traded Mid-Game</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>Swap hands with a random other player</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="74" t="n"/>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D88" s="25" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is above 50%</t>
+        </is>
+      </c>
+      <c r="E88" s="25" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F88" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G88" s="72" t="n"/>
       <c r="H88" s="71" t="n"/>
       <c r="I88" s="71" t="n"/>
       <c r="J88" s="71" t="n"/>
@@ -4543,19 +4541,19 @@
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C89" s="49" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D89" s="38" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
+      <c r="C89" s="23" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Swap hands with a random other player</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G89" s="74" t="n"/>
       <c r="H89" s="71" t="n"/>
@@ -4571,23 +4569,19 @@
       </c>
       <c r="C90" s="49" t="inlineStr">
         <is>
-          <t>All-Swissh Selection</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D90" s="38" t="inlineStr">
         <is>
-          <t>Draw 3 cards after your next make</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G90" s="74" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+      <c r="G90" s="74" t="n"/>
       <c r="H90" s="71" t="n"/>
       <c r="I90" s="71" t="n"/>
       <c r="J90" s="71" t="n"/>
@@ -4601,19 +4595,23 @@
       </c>
       <c r="C91" s="49" t="inlineStr">
         <is>
-          <t>All Star Selection</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D91" s="38" t="inlineStr">
         <is>
-          <t>Draw 2 cards</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G91" s="74" t="n"/>
+      <c r="G91" s="74" t="inlineStr">
+        <is>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
+        </is>
+      </c>
       <c r="H91" s="71" t="n"/>
       <c r="I91" s="71" t="n"/>
       <c r="J91" s="71" t="n"/>
@@ -4627,23 +4625,19 @@
       </c>
       <c r="C92" s="49" t="inlineStr">
         <is>
-          <t>Hit the Bike</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D92" s="38" t="inlineStr">
         <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G92" s="74" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="G92" s="74" t="n"/>
       <c r="H92" s="71" t="n"/>
       <c r="I92" s="71" t="n"/>
       <c r="J92" s="71" t="n"/>
@@ -4657,19 +4651,23 @@
       </c>
       <c r="C93" s="49" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D93" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G93" s="74" t="n"/>
+      <c r="G93" s="74" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H93" s="71" t="n"/>
       <c r="I93" s="71" t="n"/>
       <c r="J93" s="71" t="n"/>
@@ -4683,23 +4681,19 @@
       </c>
       <c r="C94" s="49" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D94" s="38" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G94" s="74" t="inlineStr">
-        <is>
-          <t>Deck ones are shown face down</t>
-        </is>
-      </c>
+      <c r="G94" s="74" t="n"/>
       <c r="H94" s="71" t="n"/>
       <c r="I94" s="71" t="n"/>
       <c r="J94" s="71" t="n"/>
@@ -4713,12 +4707,12 @@
       </c>
       <c r="C95" s="49" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D95" s="38" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
@@ -4727,7 +4721,7 @@
       </c>
       <c r="G95" s="74" t="inlineStr">
         <is>
-          <t>This is a bad thing in the NBA</t>
+          <t>Deck ones are shown face down</t>
         </is>
       </c>
       <c r="H95" s="71" t="n"/>
@@ -4743,12 +4737,12 @@
       </c>
       <c r="C96" s="49" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D96" s="38" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -4757,7 +4751,7 @@
       </c>
       <c r="G96" s="74" t="inlineStr">
         <is>
-          <t>The hex travels in the declared direction too</t>
+          <t>This is a bad thing in the NBA</t>
         </is>
       </c>
       <c r="H96" s="71" t="n"/>
@@ -4773,19 +4767,23 @@
       </c>
       <c r="C97" s="49" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D97" s="38" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G97" s="74" t="n"/>
+      <c r="G97" s="74" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H97" s="71" t="n"/>
       <c r="I97" s="71" t="n"/>
       <c r="J97" s="71" t="n"/>
@@ -4799,12 +4797,12 @@
       </c>
       <c r="C98" s="49" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D98" s="38" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -4825,12 +4823,12 @@
       </c>
       <c r="C99" s="49" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Official Timeout</t>
         </is>
       </c>
       <c r="D99" s="38" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -4851,12 +4849,12 @@
       </c>
       <c r="C100" s="49" t="inlineStr">
         <is>
-          <t>Altercation</t>
+          <t>Team Doctor</t>
         </is>
       </c>
       <c r="D100" s="38" t="inlineStr">
         <is>
-          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
@@ -4877,17 +4875,17 @@
       </c>
       <c r="C101" s="49" t="inlineStr">
         <is>
-          <t>Huge Altercation</t>
+          <t>Altercation</t>
         </is>
       </c>
       <c r="D101" s="38" t="inlineStr">
         <is>
-          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
+          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G101" s="74" t="n"/>
       <c r="H101" s="71" t="n"/>
@@ -4903,17 +4901,17 @@
       </c>
       <c r="C102" s="49" t="inlineStr">
         <is>
-          <t>Home Court Advantage</t>
+          <t>Huge Altercation</t>
         </is>
       </c>
       <c r="D102" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 10%</t>
+          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G102" s="74" t="n"/>
       <c r="H102" s="71" t="n"/>
@@ -4929,12 +4927,12 @@
       </c>
       <c r="C103" s="49" t="inlineStr">
         <is>
-          <t>Away Game</t>
+          <t>Home Court Advantage</t>
         </is>
       </c>
       <c r="D103" s="38" t="inlineStr">
         <is>
-          <t>SHOT - 10%</t>
+          <t>SHOT + 10%</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -4955,23 +4953,19 @@
       </c>
       <c r="C104" s="49" t="inlineStr">
         <is>
-          <t>Mic'd Up</t>
+          <t>Away Game</t>
         </is>
       </c>
       <c r="D104" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 10% until passed or shot</t>
+          <t>SHOT - 10%</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G104" s="74" t="inlineStr">
-        <is>
-          <t>The boost is the holder's alone and does not travel with a pass</t>
-        </is>
-      </c>
+      <c r="G104" s="74" t="n"/>
       <c r="H104" s="71" t="n"/>
       <c r="I104" s="71" t="n"/>
       <c r="J104" s="71" t="n"/>
@@ -4985,19 +4979,23 @@
       </c>
       <c r="C105" s="49" t="inlineStr">
         <is>
-          <t>In The Zone</t>
+          <t>Mic'd Up</t>
         </is>
       </c>
       <c r="D105" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+          <t>SHOT + 10% until passed or shot</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G105" s="74" t="n"/>
+      <c r="G105" s="74" t="inlineStr">
+        <is>
+          <t>The boost is the holder's alone and does not travel with a pass</t>
+        </is>
+      </c>
       <c r="H105" s="71" t="n"/>
       <c r="I105" s="71" t="n"/>
       <c r="J105" s="71" t="n"/>
@@ -5011,12 +5009,12 @@
       </c>
       <c r="C106" s="49" t="inlineStr">
         <is>
-          <t>Role Player</t>
+          <t>In The Zone</t>
         </is>
       </c>
       <c r="D106" s="38" t="inlineStr">
         <is>
-          <t>All other players draw 1 card</t>
+          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
         </is>
       </c>
       <c r="E106" s="7" t="n"/>
@@ -5029,84 +5027,89 @@
       <c r="J106" s="71" t="n"/>
     </row>
     <row r="107" ht="28" customHeight="1" s="85">
-      <c r="A107" s="27" t="n"/>
-      <c r="B107" s="28" t="inlineStr">
+      <c r="A107" s="21" t="n"/>
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>Game Break</t>
         </is>
       </c>
-      <c r="C107" s="62" t="inlineStr">
+      <c r="C107" s="49" t="inlineStr">
+        <is>
+          <t>Role Player</t>
+        </is>
+      </c>
+      <c r="D107" s="38" t="inlineStr">
+        <is>
+          <t>All other players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G107" s="74" t="n"/>
+      <c r="H107" s="71" t="n"/>
+      <c r="I107" s="71" t="n"/>
+      <c r="J107" s="71" t="n"/>
+    </row>
+    <row r="108" ht="28" customHeight="1" s="85">
+      <c r="A108" s="27" t="n"/>
+      <c r="B108" s="28" t="inlineStr">
+        <is>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C108" s="62" t="inlineStr">
         <is>
           <t>Back-and-Forth Game</t>
         </is>
       </c>
-      <c r="D107" s="63" t="inlineStr">
+      <c r="D108" s="63" t="inlineStr">
         <is>
           <t>Discard the next 3 Game Breaks. Whoever draws one draws again</t>
         </is>
       </c>
-      <c r="E107" s="58" t="n"/>
-      <c r="F107" s="59" t="n">
+      <c r="E108" s="58" t="n"/>
+      <c r="F108" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="G107" s="79" t="n"/>
-      <c r="H107" s="76" t="n"/>
-      <c r="I107" s="76" t="n"/>
-      <c r="J107" s="76" t="n"/>
-    </row>
-    <row r="108" ht="28" customHeight="1" s="85">
-      <c r="A108" s="52" t="inlineStr">
-        <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="B108" s="53">
-        <f>COUNTIF($B$106:$B$140,"Injury GB")</f>
-        <v/>
-      </c>
-      <c r="C108" s="54" t="n"/>
-      <c r="D108" s="54" t="n"/>
-      <c r="E108" s="54" t="n"/>
-      <c r="F108" s="55" t="n"/>
-      <c r="G108" s="66" t="n"/>
-      <c r="H108" s="67" t="n"/>
-      <c r="I108" s="67" t="n"/>
-      <c r="J108" s="67" t="n"/>
+      <c r="G108" s="79" t="n"/>
+      <c r="H108" s="76" t="n"/>
+      <c r="I108" s="76" t="n"/>
+      <c r="J108" s="76" t="n"/>
     </row>
     <row r="109" ht="42" customHeight="1" s="85">
       <c r="A109" s="27" t="n"/>
       <c r="B109" s="28" t="inlineStr">
         <is>
-          <t>Injury GB</t>
-        </is>
-      </c>
-      <c r="C109" s="56" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
+          <t>Game Break</t>
+        </is>
+      </c>
+      <c r="C109" s="62" t="inlineStr">
+        <is>
+          <t>Off the Backboard</t>
         </is>
       </c>
       <c r="D109" s="63" t="inlineStr">
         <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+          <t>Your next missed shot rebounds itself</t>
         </is>
       </c>
       <c r="E109" s="58" t="n"/>
       <c r="F109" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="G109" s="75" t="n"/>
+      <c r="G109" s="79" t="n"/>
       <c r="H109" s="76" t="n"/>
-      <c r="I109" s="76" t="n"/>
-      <c r="J109" s="76" t="n"/>
     </row>
     <row r="110" ht="56" customHeight="1" s="85">
       <c r="A110" s="52" t="inlineStr">
         <is>
-          <t>Devastating Injury GB</t>
+          <t>Injury GB</t>
         </is>
       </c>
       <c r="B110" s="53">
-        <f>COUNTIF($B$108:$B$140,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$111:$B$143,"Injury GB")</f>
         <v/>
       </c>
       <c r="C110" s="54" t="n"/>
@@ -5122,21 +5125,23 @@
       <c r="A111" s="27" t="n"/>
       <c r="B111" s="28" t="inlineStr">
         <is>
-          <t>Devastating Injury GB</t>
-        </is>
-      </c>
-      <c r="C111" s="64" t="inlineStr">
-        <is>
-          <t>Torn Achilles</t>
-        </is>
-      </c>
-      <c r="D111" s="65" t="inlineStr">
-        <is>
-          <t>Hand is locked every turn except 1 card (randomly)</t>
+          <t>Injury GB</t>
+        </is>
+      </c>
+      <c r="C111" s="56" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D111" s="63" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
         </is>
       </c>
       <c r="E111" s="58" t="n"/>
-      <c r="F111" s="61" t="n"/>
+      <c r="F111" s="59" t="n">
+        <v>3</v>
+      </c>
       <c r="G111" s="75" t="n"/>
       <c r="H111" s="76" t="n"/>
       <c r="I111" s="76" t="n"/>
@@ -5145,11 +5150,11 @@
     <row r="112" ht="20" customHeight="1" s="85">
       <c r="A112" s="52" t="inlineStr">
         <is>
-          <t>Intangible</t>
+          <t>Devastating Injury GB</t>
         </is>
       </c>
       <c r="B112" s="53">
-        <f>COUNTIF($B$110:$B$140,"Intangible")</f>
+        <f>COUNTIF($B$113:$B$143,"Devastating Injury GB")</f>
         <v/>
       </c>
       <c r="C112" s="54" t="n"/>
@@ -5162,72 +5167,67 @@
       <c r="J112" s="67" t="n"/>
     </row>
     <row r="113" ht="28" customHeight="1" s="85">
-      <c r="A113" s="42" t="inlineStr">
+      <c r="A113" s="27" t="n"/>
+      <c r="B113" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury GB</t>
+        </is>
+      </c>
+      <c r="C113" s="64" t="inlineStr">
+        <is>
+          <t>Torn Achilles</t>
+        </is>
+      </c>
+      <c r="D113" s="65" t="inlineStr">
+        <is>
+          <t>Hand is locked every turn except 1 card (randomly)</t>
+        </is>
+      </c>
+      <c r="E113" s="58" t="n"/>
+      <c r="F113" s="61" t="n"/>
+      <c r="G113" s="75" t="n"/>
+      <c r="H113" s="76" t="n"/>
+      <c r="I113" s="76" t="n"/>
+      <c r="J113" s="76" t="n"/>
+    </row>
+    <row r="114" ht="42" customHeight="1" s="85">
+      <c r="A114" s="52" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="B114" s="53">
+        <f>COUNTIF($B$115:$B$143,"Intangible")</f>
+        <v/>
+      </c>
+      <c r="C114" s="54" t="n"/>
+      <c r="D114" s="54" t="n"/>
+      <c r="E114" s="54" t="n"/>
+      <c r="F114" s="55" t="n"/>
+      <c r="G114" s="66" t="n"/>
+      <c r="H114" s="67" t="n"/>
+      <c r="I114" s="67" t="n"/>
+      <c r="J114" s="67" t="n"/>
+    </row>
+    <row r="115" ht="28" customHeight="1" s="85">
+      <c r="A115" s="42" t="inlineStr">
         <is>
           <t>All intangibles are limited to 1</t>
         </is>
       </c>
-      <c r="B113" s="22" t="inlineStr">
+      <c r="B115" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C113" s="23" t="inlineStr">
+      <c r="C115" s="23" t="inlineStr">
         <is>
           <t>Board-Crasher</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>SHOT +10% upon Rebounding your own missed shot</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="n"/>
-      <c r="F113" s="50" t="n"/>
-      <c r="G113" s="70" t="n"/>
-      <c r="H113" s="71" t="n"/>
-      <c r="I113" s="71" t="n"/>
-      <c r="J113" s="71" t="n"/>
-    </row>
-    <row r="114" ht="42" customHeight="1" s="85">
-      <c r="A114" s="21" t="n"/>
-      <c r="B114" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C114" s="24" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D114" s="25" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E114" s="26" t="n"/>
-      <c r="F114" s="50" t="n"/>
-      <c r="G114" s="72" t="n"/>
-      <c r="H114" s="71" t="n"/>
-      <c r="I114" s="71" t="n"/>
-      <c r="J114" s="71" t="n"/>
-    </row>
-    <row r="115" ht="28" customHeight="1" s="85">
-      <c r="A115" s="21" t="n"/>
-      <c r="B115" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C115" s="23" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
         </is>
       </c>
       <c r="E115" s="7" t="n"/>
@@ -5238,21 +5238,28 @@
       <c r="J115" s="71" t="n"/>
     </row>
     <row r="116" ht="28" customHeight="1" s="85">
-      <c r="B116" s="0" t="inlineStr">
+      <c r="A116" s="21" t="n"/>
+      <c r="B116" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C116" s="0" t="inlineStr">
-        <is>
-          <t>Roswell Reach</t>
-        </is>
-      </c>
-      <c r="D116" s="0" t="inlineStr">
-        <is>
-          <t>All your Rebound bids of 1 or more count as 1 higher</t>
-        </is>
-      </c>
+      <c r="C116" s="24" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D116" s="25" t="inlineStr">
+        <is>
+          <t>Additional SHOT +10% on all received passes</t>
+        </is>
+      </c>
+      <c r="E116" s="26" t="n"/>
+      <c r="F116" s="50" t="n"/>
+      <c r="G116" s="72" t="n"/>
+      <c r="H116" s="71" t="n"/>
+      <c r="I116" s="71" t="n"/>
+      <c r="J116" s="71" t="n"/>
     </row>
     <row r="117" ht="56" customHeight="1" s="85">
       <c r="A117" s="21" t="n"/>
@@ -5261,50 +5268,39 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C117" s="24" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D117" s="25" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
-        </is>
-      </c>
-      <c r="E117" s="26" t="n"/>
+      <c r="C117" s="23" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="n"/>
       <c r="F117" s="50" t="n"/>
-      <c r="G117" s="72" t="n"/>
+      <c r="G117" s="70" t="n"/>
       <c r="H117" s="71" t="n"/>
       <c r="I117" s="71" t="n"/>
       <c r="J117" s="71" t="n"/>
     </row>
     <row r="118" ht="56" customHeight="1" s="85">
-      <c r="A118" s="21" t="n"/>
-      <c r="B118" s="22" t="inlineStr">
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C118" s="23" t="inlineStr">
-        <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F118" s="51" t="n"/>
-      <c r="G118" s="70" t="n"/>
-      <c r="H118" s="71" t="n"/>
-      <c r="I118" s="71" t="n"/>
-      <c r="J118" s="71" t="n"/>
+      <c r="C118" s="0" t="inlineStr">
+        <is>
+          <t>Roswell Reach</t>
+        </is>
+      </c>
+      <c r="D118" s="0" t="inlineStr">
+        <is>
+          <t>All your Rebound bids of 1 or more count as 1 higher</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="28" customHeight="1" s="85">
       <c r="A119" s="21" t="n"/>
@@ -5313,19 +5309,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C119" s="37" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D119" s="41" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
+      <c r="C119" s="24" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D119" s="25" t="inlineStr">
+        <is>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
         </is>
       </c>
       <c r="E119" s="26" t="n"/>
       <c r="F119" s="50" t="n"/>
-      <c r="G119" s="77" t="n"/>
+      <c r="G119" s="72" t="n"/>
       <c r="H119" s="71" t="n"/>
       <c r="I119" s="71" t="n"/>
       <c r="J119" s="71" t="n"/>
@@ -5337,18 +5333,22 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C120" s="37" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D120" s="38" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="n"/>
-      <c r="F120" s="50" t="n"/>
+      <c r="C120" s="23" t="inlineStr">
+        <is>
+          <t>Fox-Like First Step</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F120" s="51" t="n"/>
       <c r="G120" s="70" t="n"/>
       <c r="H120" s="71" t="n"/>
       <c r="I120" s="71" t="n"/>
@@ -5361,19 +5361,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C121" s="24" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D121" s="25" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+      <c r="C121" s="37" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D121" s="41" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
         </is>
       </c>
       <c r="E121" s="26" t="n"/>
       <c r="F121" s="50" t="n"/>
-      <c r="G121" s="72" t="n"/>
+      <c r="G121" s="77" t="n"/>
       <c r="H121" s="71" t="n"/>
       <c r="I121" s="71" t="n"/>
       <c r="J121" s="71" t="n"/>
@@ -5385,14 +5385,14 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C122" s="23" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+      <c r="C122" s="37" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D122" s="38" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
         </is>
       </c>
       <c r="E122" s="7" t="n"/>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="C123" s="24" t="inlineStr">
         <is>
-          <t>Hot Hand</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>SHOT +20% if you scored last round.</t>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
         </is>
       </c>
       <c r="E123" s="26" t="n"/>
@@ -5435,12 +5435,12 @@
       </c>
       <c r="C124" s="23" t="inlineStr">
         <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D124" s="38" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
         </is>
       </c>
       <c r="E124" s="7" t="n"/>
@@ -5459,21 +5459,17 @@
       </c>
       <c r="C125" s="24" t="inlineStr">
         <is>
-          <t>No Bag</t>
+          <t>Hot Hand</t>
         </is>
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>Cannot activate Move cards this round</t>
+          <t>SHOT +20% if you scored last round.</t>
         </is>
       </c>
       <c r="E125" s="26" t="n"/>
       <c r="F125" s="50" t="n"/>
-      <c r="G125" s="73" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G125" s="72" t="n"/>
       <c r="H125" s="71" t="n"/>
       <c r="I125" s="71" t="n"/>
       <c r="J125" s="71" t="n"/>
@@ -5487,12 +5483,12 @@
       </c>
       <c r="C126" s="23" t="inlineStr">
         <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D126" s="38" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
         </is>
       </c>
       <c r="E126" s="7" t="n"/>
@@ -5511,12 +5507,12 @@
       </c>
       <c r="C127" s="24" t="inlineStr">
         <is>
-          <t>Shooting Slump</t>
+          <t>No Bag</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>SHOT -20% this round</t>
+          <t>Cannot activate Move cards this round</t>
         </is>
       </c>
       <c r="E127" s="26" t="n"/>
@@ -5539,12 +5535,12 @@
       </c>
       <c r="C128" s="23" t="inlineStr">
         <is>
-          <t>Shot Creator</t>
+          <t>Point God</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Draw 1 additional card after every draw effect</t>
+          <t>Draw 1 card following each of your passes</t>
         </is>
       </c>
       <c r="E128" s="7" t="n"/>
@@ -5563,17 +5559,21 @@
       </c>
       <c r="C129" s="24" t="inlineStr">
         <is>
-          <t>Sixth Man</t>
+          <t>Shooting Slump</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
+          <t>SHOT -20% this round</t>
         </is>
       </c>
       <c r="E129" s="26" t="n"/>
       <c r="F129" s="50" t="n"/>
-      <c r="G129" s="72" t="n"/>
+      <c r="G129" s="73" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H129" s="71" t="n"/>
       <c r="I129" s="71" t="n"/>
       <c r="J129" s="71" t="n"/>
@@ -5587,12 +5587,12 @@
       </c>
       <c r="C130" s="23" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Shot Creator</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
+          <t>Draw 1 additional card after every draw effect</t>
         </is>
       </c>
       <c r="E130" s="7" t="n"/>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="C131" s="24" t="inlineStr">
         <is>
-          <t>Splash Cousin</t>
+          <t>Sixth Man</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
+          <t>SHOT = 100% if taking 6th shot of the round</t>
         </is>
       </c>
       <c r="E131" s="26" t="n"/>
@@ -5635,12 +5635,12 @@
       </c>
       <c r="C132" s="23" t="inlineStr">
         <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D132" s="38" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +10% on all Three-Point Line Shots</t>
         </is>
       </c>
       <c r="E132" s="7" t="n"/>
@@ -5659,21 +5659,17 @@
       </c>
       <c r="C133" s="24" t="inlineStr">
         <is>
-          <t>Lethal Shooter</t>
+          <t>Splash Cousin</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
         </is>
       </c>
       <c r="E133" s="26" t="n"/>
       <c r="F133" s="50" t="n"/>
-      <c r="G133" s="73" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G133" s="72" t="n"/>
       <c r="H133" s="71" t="n"/>
       <c r="I133" s="71" t="n"/>
       <c r="J133" s="71" t="n"/>
@@ -5687,12 +5683,12 @@
       </c>
       <c r="C134" s="23" t="inlineStr">
         <is>
-          <t>Ball Pounder</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="D134" s="38" t="inlineStr">
         <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
+          <t>All Clamps on you have no effect on SHOT %</t>
         </is>
       </c>
       <c r="E134" s="7" t="n"/>
@@ -5709,19 +5705,23 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C135" s="23" t="inlineStr">
-        <is>
-          <t>Unselfish</t>
-        </is>
-      </c>
-      <c r="D135" s="38" t="inlineStr">
-        <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="n"/>
+      <c r="C135" s="24" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D135" s="25" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E135" s="26" t="n"/>
       <c r="F135" s="50" t="n"/>
-      <c r="G135" s="70" t="n"/>
+      <c r="G135" s="73" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
       <c r="H135" s="71" t="n"/>
       <c r="I135" s="71" t="n"/>
       <c r="J135" s="71" t="n"/>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="C136" s="23" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D136" s="38" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E136" s="7" t="n"/>
@@ -5759,21 +5759,17 @@
       </c>
       <c r="C137" s="23" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D137" s="38" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E137" s="7" t="n"/>
       <c r="F137" s="50" t="n"/>
-      <c r="G137" s="70" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
-        </is>
-      </c>
+      <c r="G137" s="70" t="n"/>
       <c r="H137" s="71" t="n"/>
       <c r="I137" s="71" t="n"/>
       <c r="J137" s="71" t="n"/>
@@ -5787,21 +5783,17 @@
       </c>
       <c r="C138" s="23" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D138" s="38" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
         </is>
       </c>
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="50" t="n"/>
-      <c r="G138" s="70" t="inlineStr">
-        <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
-        </is>
-      </c>
+      <c r="G138" s="70" t="n"/>
       <c r="H138" s="71" t="n"/>
       <c r="I138" s="71" t="n"/>
       <c r="J138" s="71" t="n"/>
@@ -5815,44 +5807,124 @@
       </c>
       <c r="C139" s="23" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Villainous Reputation</t>
         </is>
       </c>
       <c r="D139" s="38" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Discard 1 whenever any Whistle triggers</t>
         </is>
       </c>
       <c r="E139" s="7" t="n"/>
       <c r="F139" s="50" t="n"/>
-      <c r="G139" s="70" t="n"/>
+      <c r="G139" s="70" t="inlineStr">
+        <is>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
+        </is>
+      </c>
       <c r="H139" s="71" t="n"/>
       <c r="I139" s="71" t="n"/>
       <c r="J139" s="71" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="27" t="n"/>
-      <c r="B140" s="28" t="inlineStr">
+      <c r="A140" s="21" t="n"/>
+      <c r="B140" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C140" s="56" t="inlineStr">
+      <c r="C140" s="23" t="inlineStr">
+        <is>
+          <t>Free Agent</t>
+        </is>
+      </c>
+      <c r="D140" s="38" t="inlineStr">
+        <is>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="n"/>
+      <c r="F140" s="50" t="n"/>
+      <c r="G140" s="70" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
+        </is>
+      </c>
+      <c r="H140" s="71" t="n"/>
+      <c r="I140" s="71" t="n"/>
+      <c r="J140" s="71" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="21" t="n"/>
+      <c r="B141" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C141" s="23" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D141" s="38" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="n"/>
+      <c r="F141" s="50" t="n"/>
+      <c r="G141" s="70" t="n"/>
+      <c r="H141" s="71" t="n"/>
+      <c r="I141" s="71" t="n"/>
+      <c r="J141" s="71" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="27" t="n"/>
+      <c r="B142" s="28" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C142" s="56" t="inlineStr">
         <is>
           <t>Fundamentalist</t>
         </is>
       </c>
-      <c r="D140" s="63" t="inlineStr">
+      <c r="D142" s="63" t="inlineStr">
         <is>
           <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent</t>
         </is>
       </c>
-      <c r="E140" s="58" t="n"/>
-      <c r="F140" s="61" t="n"/>
-      <c r="G140" s="75" t="n"/>
-      <c r="H140" s="76" t="n"/>
-      <c r="I140" s="76" t="n"/>
-      <c r="J140" s="76" t="n"/>
+      <c r="E142" s="58" t="n"/>
+      <c r="F142" s="61" t="n"/>
+      <c r="G142" s="75" t="n"/>
+      <c r="H142" s="76" t="n"/>
+      <c r="I142" s="76" t="n"/>
+      <c r="J142" s="76" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="27" t="n"/>
+      <c r="B143" s="28" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C143" s="56" t="inlineStr">
+        <is>
+          <t>Moves At Own Pace</t>
+        </is>
+      </c>
+      <c r="D143" s="63" t="inlineStr">
+        <is>
+          <t>Cannot be called for Traveling or Shot Clock violations</t>
+        </is>
+      </c>
+      <c r="E143" s="58" t="n"/>
+      <c r="F143" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="75" t="n"/>
+      <c r="H143" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="123">

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2182,6 +2182,7 @@
         <v/>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="85">
       <c r="A4" s="81" t="inlineStr">
         <is>
@@ -2333,7 +2334,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Pass Left or Right. Move 1 card from new player to next player in same direction. SHOT +5%</t>
+          <t>Pass Left or Right. Move 1 card from new player to next player in same direction. SHOT +10%</t>
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
@@ -2359,7 +2360,7 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Pass Across. SHOT +5%</t>
+          <t>Pass Across. SHOT +10%</t>
         </is>
       </c>
       <c r="E10" s="26" t="n"/>
@@ -2385,7 +2386,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Pass Left. SHOT +5%</t>
+          <t>Pass Left. SHOT +10%</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -2411,7 +2412,7 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Pass Right. SHOT +5%</t>
+          <t>Pass Right. SHOT +10%</t>
         </is>
       </c>
       <c r="E12" s="26" t="n"/>
@@ -2437,7 +2438,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Pass to random other player. SHOT +5%</t>
+          <t>Pass to random other player. SHOT +10%</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -2463,7 +2464,7 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>Pass to player of choice. SHOT +5%</t>
+          <t>Pass to player of choice. SHOT +10%</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -2523,7 +2524,7 @@
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>SHOT +5%. Pass to player to Left or Right. Draw 1 card</t>
+          <t>SHOT +10%. Pass to player to Left or Right. Draw 1 card</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -2621,7 +2622,7 @@
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>SHOT +5%. Pass to player of choice. They immediately pass it back</t>
+          <t>SHOT +10%. Pass to player of choice. They immediately pass it back</t>
         </is>
       </c>
       <c r="E19" s="25" t="n"/>
@@ -2651,7 +2652,7 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>SHOT +5%. Pass to player of choice. If played as first action, draw 2 cards</t>
+          <t>SHOT +10%. Pass to player of choice. If played as first action, draw 2 cards</t>
         </is>
       </c>
       <c r="E20" s="30" t="n"/>
@@ -4268,6 +4269,8 @@
       </c>
       <c r="G78" s="78" t="n"/>
       <c r="H78" s="76" t="n"/>
+      <c r="I78" s="76" t="n"/>
+      <c r="J78" s="76" t="n"/>
     </row>
     <row r="79" ht="28" customHeight="1" s="85">
       <c r="A79" s="52" t="inlineStr">
@@ -5101,6 +5104,8 @@
       </c>
       <c r="G109" s="79" t="n"/>
       <c r="H109" s="76" t="n"/>
+      <c r="I109" s="76" t="n"/>
+      <c r="J109" s="76" t="n"/>
     </row>
     <row r="110" ht="56" customHeight="1" s="85">
       <c r="A110" s="52" t="inlineStr">

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Pass back to player who passed to you. If ball not received from a player, TOV +1</t>
+          <t>Pass back to player who passed to you. Gains what that pass gained. If ball not received from a player, TOV +1</t>
         </is>
       </c>
       <c r="E6" s="26" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Pass to player of choice. SHOT +10%</t>
+          <t>Pass to player of choice. SHOT +20%</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D8" s="41" t="inlineStr">
         <is>
-          <t>SHOT +10%. Pass to player of choice. They must attempt a shot as their first action.</t>
+          <t>SHOT +20%. Pass to player of choice. They must attempt a shot as their first action.</t>
         </is>
       </c>
       <c r="E8" s="26" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Pass Left or Right. Move 1 card from new player to next player in same direction. SHOT +10%</t>
+          <t>Pass Left or Right. Move 1 card from new player to next player in same direction. SHOT +20%</t>
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Pass to random other player. SHOT +10%</t>
+          <t>Pass to random other player. SHOT +20%</t>
         </is>
       </c>
       <c r="E13" s="7" t="n"/>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>Pass to player of choice. SHOT +10%</t>
+          <t>Pass to player of choice. SHOT +20%</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>SHOT +20%. Pass to player of choice</t>
+          <t>SHOT +30%. Pass to player of choice</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>SHOT +10%. Pass to player to Left or Right. Draw 1 card</t>
+          <t>SHOT +20%. Pass to player to Left or Right. Draw 1 card</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>If played following a Dribble: draw 1 additional and SHOT +5% more</t>
+          <t>If played following a Dribble: draw 1 additional and SHOT +10% more</t>
         </is>
       </c>
       <c r="F16" s="36" t="n">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>SHOT +10%. Shot Clock +01. Pass to player of choice</t>
+          <t>SHOT +20%. Shot Clock +01. Pass to player of choice</t>
         </is>
       </c>
       <c r="E17" s="25" t="n"/>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>SHOT +10%. Upgraded to 3pt. Pass to player of choice</t>
+          <t>SHOT +20%. Upgraded to 3pt. Pass to player of choice</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>SHOT +10%. Pass to player of choice. They immediately pass it back</t>
+          <t>SHOT +15%. Pass to player of choice. They immediately pass it back</t>
         </is>
       </c>
       <c r="E19" s="25" t="n"/>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>SHOT +10%. Pass to player of choice. If played as first action, draw 2 cards</t>
+          <t>SHOT +20%. Pass to player of choice. If played as first action, draw 2 cards</t>
         </is>
       </c>
       <c r="E20" s="30" t="n"/>
@@ -2723,12 +2723,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
+          <t>SHOT +20%</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Following Dribble: SHOT +10%</t>
+          <t>Following Dribble: SHOT +20%</t>
         </is>
       </c>
       <c r="F23" s="32" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>Target player discards 1 card. SHOT +10%</t>
+          <t>Target player discards 1 card. SHOT +20%</t>
         </is>
       </c>
       <c r="E24" s="26" t="n"/>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>Hesi</t>
+          <t>Hesitation Dribble</t>
         </is>
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
+          <t>SHOT +20%</t>
         </is>
       </c>
       <c r="E26" s="25" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
+          <t>SHOT +20%</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>Draw 1 card. SHOT +10%. Shot Clock -1</t>
+          <t>Draw 1 card. SHOT +20%. Shot Clock -1</t>
         </is>
       </c>
       <c r="E28" s="26" t="n"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="D29" s="41" t="inlineStr">
         <is>
-          <t>Draw 2 cards then Discard 1. SHOT +10% Shot Clock -1</t>
+          <t>Draw 2 cards then Discard 1. SHOT +20% Shot Clock -1</t>
         </is>
       </c>
       <c r="E29" s="26" t="n"/>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D30" s="41" t="inlineStr">
         <is>
-          <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +10% for each</t>
+          <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +20% for each</t>
         </is>
       </c>
       <c r="E30" s="26" t="n"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D31" s="41" t="inlineStr">
         <is>
-          <t>Draw 1 Card. SHOT +10%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
+          <t>Draw 1 Card. SHOT +20%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
         </is>
       </c>
       <c r="E31" s="26" t="n"/>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
+          <t>SHOT +20%</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Discard 1: SHOT +10%</t>
+          <t>Discard 1: SHOT +20%</t>
         </is>
       </c>
       <c r="F32" s="32" t="n">
@@ -3021,8 +3021,8 @@
         <is>
           <t>Choose 1:
 Draw 1 card
-Pass to player of choice (SHOT +5%)
-SHOT +10%</t>
+Pass to player of choice (SHOT +20%)
+SHOT +20%</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>SHOT = 10%</t>
+          <t>SHOT = 25%</t>
         </is>
       </c>
       <c r="E42" s="25" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
+          <t>SHOT +20%</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="D44" s="25" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
+          <t>SHOT +25%</t>
         </is>
       </c>
       <c r="E44" s="41" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%. SHOT = 100% if SHOT &gt;= 70%</t>
+          <t>SHOT +20%. SHOT = 100% if SHOT &gt;= 75%</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Flip a coin until you get Tails. For each Heads, SHOT +5% and Draw 1 card</t>
+          <t>Flip a coin until you get 2 Tails. For each Heads, SHOT +5% and Draw 1 card</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>SHOT +10%. Shoot the ball. Another +10% straight off your own board</t>
+          <t>SHOT +20%. Shoot the ball. Another +10% straight off your own board</t>
         </is>
       </c>
       <c r="F49" s="0" t="n">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D103" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 10%</t>
+          <t>SHOT + 25%</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>SHOT +20% if you scored last round.</t>
+          <t>SHOT +25% if you scored last round.</t>
         </is>
       </c>
       <c r="E125" s="26" t="n"/>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>SHOT = 100% if taking 6th shot of the round</t>
+          <t>SHOT +60% on any six: cards in hand, Shot Clock, shot of the round, or score</t>
         </is>
       </c>
       <c r="E131" s="26" t="n"/>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10% on all Three-Point Line Shots</t>
+          <t>SHOT +25% on all Three-Point Line Shots</t>
         </is>
       </c>
       <c r="E132" s="7" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -1876,7 +1876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col width="26.5" customWidth="1" style="85" min="1" max="1"/>
@@ -2041,6 +2041,30 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1" s="85">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>The floor. Persistent, global and replaceable: one is always out, Cardwood until somebody plays over it. One per player per possession</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" s="85">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>The ball. An overlay on a Regulation Ball, which is no card at all. Persistent, global and replaceable, and never stacks. One per player per possession</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2065,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J143"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2182,7 +2206,6 @@
         <v/>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="85">
       <c r="A4" s="81" t="inlineStr">
         <is>
@@ -5907,7 +5930,7 @@
       <c r="I142" s="76" t="n"/>
       <c r="J142" s="76" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" s="85">
       <c r="A143" s="27" t="n"/>
       <c r="B143" s="28" t="inlineStr">
         <is>
@@ -5931,8 +5954,55 @@
       <c r="G143" s="75" t="n"/>
       <c r="H143" s="76" t="n"/>
     </row>
+    <row r="144" ht="42" customHeight="1" s="85">
+      <c r="A144" s="52" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="B144" s="53">
+        <f>COUNTIF($B$145:$B$145,"Varena")</f>
+        <v/>
+      </c>
+      <c r="C144" s="54" t="n"/>
+      <c r="D144" s="54" t="n"/>
+      <c r="E144" s="54" t="n"/>
+      <c r="F144" s="55" t="n"/>
+      <c r="G144" s="66" t="n"/>
+      <c r="H144" s="67" t="n"/>
+      <c r="I144" s="67" t="n"/>
+      <c r="J144" s="67" t="n"/>
+    </row>
+    <row r="145" s="85">
+      <c r="A145" s="27" t="n"/>
+      <c r="B145" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C145" s="56" t="inlineStr">
+        <is>
+          <t>Cardwood</t>
+        </is>
+      </c>
+      <c r="D145" s="63" t="inlineStr">
+        <is>
+          <t>The default floor</t>
+        </is>
+      </c>
+      <c r="E145" s="58" t="n"/>
+      <c r="F145" s="61" t="n"/>
+      <c r="G145" s="75" t="inlineStr">
+        <is>
+          <t>Not in the deck. The floor every game opens on, and what the slot reads as when nobody has played a Varena over it</t>
+        </is>
+      </c>
+      <c r="H145" s="76" t="n"/>
+      <c r="I145" s="76" t="n"/>
+      <c r="J145" s="76" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="123">
+  <mergeCells count="124">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G135:J135"/>
@@ -5948,6 +6018,7 @@
     <mergeCell ref="G96:J96"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G136:J136"/>
+    <mergeCell ref="G145:J145"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G82:J82"/>
     <mergeCell ref="G57:J57"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -5987,14 +5987,16 @@
       </c>
       <c r="D145" s="63" t="inlineStr">
         <is>
-          <t>The default floor</t>
+          <t>Changes the court back to basic</t>
         </is>
       </c>
       <c r="E145" s="58" t="n"/>
-      <c r="F145" s="61" t="n"/>
+      <c r="F145" s="61" t="n">
+        <v>10</v>
+      </c>
       <c r="G145" s="75" t="inlineStr">
         <is>
-          <t>Not in the deck. The floor every game opens on, and what the slot reads as when nobody has played a Varena over it</t>
+          <t>Also the floor every game opens on, before anybody plays a Varena over it</t>
         </is>
       </c>
       <c r="H145" s="76" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Play these immediately when dealt. One-off effects</t>
+          <t>Retired — out of the deck, replaced by Varenas and Variaballs. Only the Injuries below are still dealt</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -4298,11 +4298,11 @@
     <row r="79" ht="28" customHeight="1" s="85">
       <c r="A79" s="52" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Breaks</t>
         </is>
       </c>
       <c r="B79" s="53">
-        <f>COUNTIF($B$80:$B$143,"Game Break")</f>
+        <f>COUNTIF($B$80:$B$109,"Retired Game Break")</f>
         <v/>
       </c>
       <c r="C79" s="54" t="n"/>
@@ -4318,7 +4318,7 @@
       <c r="A80" s="21" t="n"/>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="E80" s="26" t="n"/>
       <c r="F80" s="33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G80" s="72" t="n"/>
       <c r="H80" s="71" t="n"/>
@@ -4344,7 +4344,7 @@
       <c r="A81" s="21" t="n"/>
       <c r="B81" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C81" s="23" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="E81" s="7" t="n"/>
       <c r="F81" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G81" s="74" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
       <c r="A82" s="21" t="n"/>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C82" s="24" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="E82" s="26" t="n"/>
       <c r="F82" s="33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G82" s="72" t="n"/>
       <c r="H82" s="71" t="n"/>
@@ -4400,7 +4400,7 @@
       <c r="A83" s="21" t="n"/>
       <c r="B83" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C83" s="23" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="E83" s="7" t="n"/>
       <c r="F83" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G83" s="70" t="n"/>
       <c r="H83" s="71" t="n"/>
@@ -4426,7 +4426,7 @@
       <c r="A84" s="21" t="n"/>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C84" s="37" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E84" s="26" t="n"/>
       <c r="F84" s="33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G84" s="72" t="n"/>
       <c r="H84" s="71" t="n"/>
@@ -4452,7 +4452,7 @@
       <c r="A85" s="21" t="n"/>
       <c r="B85" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C85" s="23" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="70" t="n"/>
       <c r="H85" s="71" t="n"/>
@@ -4478,7 +4478,7 @@
       <c r="A86" s="21" t="n"/>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="E86" s="26" t="n"/>
       <c r="F86" s="33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G86" s="72" t="n"/>
       <c r="H86" s="71" t="n"/>
@@ -4504,7 +4504,7 @@
       <c r="A87" s="21" t="n"/>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C87" s="23" t="inlineStr">
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="F87" s="32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G87" s="70" t="n"/>
       <c r="H87" s="71" t="n"/>
@@ -4534,7 +4534,7 @@
       <c r="A88" s="21" t="n"/>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C88" s="24" t="inlineStr">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="F88" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G88" s="72" t="n"/>
       <c r="H88" s="71" t="n"/>
@@ -4564,7 +4564,7 @@
       <c r="A89" s="21" t="n"/>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C89" s="23" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" s="74" t="n"/>
       <c r="H89" s="71" t="n"/>
@@ -4590,7 +4590,7 @@
       <c r="A90" s="21" t="n"/>
       <c r="B90" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C90" s="49" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="E90" s="7" t="n"/>
       <c r="F90" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G90" s="74" t="n"/>
       <c r="H90" s="71" t="n"/>
@@ -4616,7 +4616,7 @@
       <c r="A91" s="21" t="n"/>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C91" s="49" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="E91" s="7" t="n"/>
       <c r="F91" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G91" s="74" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
       <c r="A92" s="21" t="n"/>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C92" s="49" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="E92" s="7" t="n"/>
       <c r="F92" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G92" s="74" t="n"/>
       <c r="H92" s="71" t="n"/>
@@ -4672,7 +4672,7 @@
       <c r="A93" s="21" t="n"/>
       <c r="B93" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C93" s="49" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G93" s="74" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
       <c r="A94" s="21" t="n"/>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C94" s="49" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="E94" s="7" t="n"/>
       <c r="F94" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G94" s="74" t="n"/>
       <c r="H94" s="71" t="n"/>
@@ -4728,7 +4728,7 @@
       <c r="A95" s="21" t="n"/>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C95" s="49" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G95" s="74" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
       <c r="A96" s="21" t="n"/>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C96" s="49" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G96" s="74" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
       <c r="A97" s="21" t="n"/>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C97" s="49" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="E97" s="7" t="n"/>
       <c r="F97" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G97" s="74" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
       <c r="A98" s="21" t="n"/>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C98" s="49" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G98" s="74" t="n"/>
       <c r="H98" s="71" t="n"/>
@@ -4844,7 +4844,7 @@
       <c r="A99" s="21" t="n"/>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C99" s="49" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G99" s="74" t="n"/>
       <c r="H99" s="71" t="n"/>
@@ -4870,7 +4870,7 @@
       <c r="A100" s="21" t="n"/>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C100" s="49" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G100" s="74" t="n"/>
       <c r="H100" s="71" t="n"/>
@@ -4896,7 +4896,7 @@
       <c r="A101" s="21" t="n"/>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C101" s="49" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G101" s="74" t="n"/>
       <c r="H101" s="71" t="n"/>
@@ -4922,7 +4922,7 @@
       <c r="A102" s="21" t="n"/>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C102" s="49" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="74" t="n"/>
       <c r="H102" s="71" t="n"/>
@@ -4948,7 +4948,7 @@
       <c r="A103" s="21" t="n"/>
       <c r="B103" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C103" s="49" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E103" s="7" t="n"/>
       <c r="F103" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G103" s="74" t="n"/>
       <c r="H103" s="71" t="n"/>
@@ -4974,7 +4974,7 @@
       <c r="A104" s="21" t="n"/>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C104" s="49" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="E104" s="7" t="n"/>
       <c r="F104" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G104" s="74" t="n"/>
       <c r="H104" s="71" t="n"/>
@@ -5000,7 +5000,7 @@
       <c r="A105" s="21" t="n"/>
       <c r="B105" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C105" s="49" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G105" s="74" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
       <c r="A106" s="21" t="n"/>
       <c r="B106" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C106" s="49" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G106" s="74" t="n"/>
       <c r="H106" s="71" t="n"/>
@@ -5056,7 +5056,7 @@
       <c r="A107" s="21" t="n"/>
       <c r="B107" s="22" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C107" s="49" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E107" s="7" t="n"/>
       <c r="F107" s="34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G107" s="74" t="n"/>
       <c r="H107" s="71" t="n"/>
@@ -5082,7 +5082,7 @@
       <c r="A108" s="27" t="n"/>
       <c r="B108" s="28" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C108" s="62" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="E108" s="58" t="n"/>
       <c r="F108" s="59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G108" s="79" t="n"/>
       <c r="H108" s="76" t="n"/>
@@ -5108,7 +5108,7 @@
       <c r="A109" s="27" t="n"/>
       <c r="B109" s="28" t="inlineStr">
         <is>
-          <t>Game Break</t>
+          <t>Retired Game Break</t>
         </is>
       </c>
       <c r="C109" s="62" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="E109" s="58" t="n"/>
       <c r="F109" s="59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G109" s="79" t="n"/>
       <c r="H109" s="76" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Retired — out of the deck, replaced by Varenas and Variaballs. Only the Injuries below are still dealt</t>
+          <t>Retired — out of the deck, replaced by Varenas and Variaballs</t>
         </is>
       </c>
       <c r="C9" s="7" t="n"/>
@@ -2015,7 +2015,7 @@
     <row r="10" ht="32" customHeight="1" s="85">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Injury Game Break</t>
+          <t>Injury</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -2030,12 +2030,12 @@
     <row r="11" ht="32" customHeight="1" s="85">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Devastating Injury Game Break</t>
+          <t>Devastating Injury</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same as above but also have effects that linger through the rounds </t>
+          <t>A sub-type of Injury. Same as above but also have effects that linger through the rounds</t>
         </is>
       </c>
       <c r="C11" s="7" t="n"/>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="G1" s="11" t="inlineStr">
         <is>
-          <t>Injury GB</t>
+          <t>Injury</t>
         </is>
       </c>
       <c r="H1" s="11" t="inlineStr">
         <is>
-          <t>Devastating Injury GB</t>
+          <t>Devastating Injury</t>
         </is>
       </c>
       <c r="I1" s="11" t="inlineStr">
@@ -2186,15 +2186,15 @@
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$140,"Game Break")&amp;" ("&amp;(COUNTIF($B$5:$B$140,"Game Break")+G2+H2)&amp;")"</f>
+        <f>COUNTIF($B$5:$B$140,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$140,"Injury GB")</f>
+        <f>COUNTIF($B$5:$B$140,"Injury")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$140,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$5:$B$140,"Devastating Injury")</f>
         <v/>
       </c>
       <c r="I2" s="17">
@@ -5133,11 +5133,11 @@
     <row r="110" ht="56" customHeight="1" s="85">
       <c r="A110" s="52" t="inlineStr">
         <is>
-          <t>Injury GB</t>
+          <t>Injury</t>
         </is>
       </c>
       <c r="B110" s="53">
-        <f>COUNTIF($B$111:$B$143,"Injury GB")</f>
+        <f>COUNTIF($B$111:$B$143,"Injury")</f>
         <v/>
       </c>
       <c r="C110" s="54" t="n"/>
@@ -5153,7 +5153,7 @@
       <c r="A111" s="27" t="n"/>
       <c r="B111" s="28" t="inlineStr">
         <is>
-          <t>Injury GB</t>
+          <t>Injury</t>
         </is>
       </c>
       <c r="C111" s="56" t="inlineStr">
@@ -5178,11 +5178,11 @@
     <row r="112" ht="20" customHeight="1" s="85">
       <c r="A112" s="52" t="inlineStr">
         <is>
-          <t>Devastating Injury GB</t>
+          <t>Devastating Injury</t>
         </is>
       </c>
       <c r="B112" s="53">
-        <f>COUNTIF($B$113:$B$143,"Devastating Injury GB")</f>
+        <f>COUNTIF($B$113:$B$143,"Devastating Injury")</f>
         <v/>
       </c>
       <c r="C112" s="54" t="n"/>
@@ -5198,7 +5198,7 @@
       <c r="A113" s="27" t="n"/>
       <c r="B113" s="28" t="inlineStr">
         <is>
-          <t>Devastating Injury GB</t>
+          <t>Devastating Injury</t>
         </is>
       </c>
       <c r="C113" s="64" t="inlineStr">

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -5992,7 +5992,7 @@
       </c>
       <c r="E145" s="58" t="n"/>
       <c r="F145" s="61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G145" s="75" t="inlineStr">
         <is>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2336,7 +2336,7 @@
       </c>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" s="72" t="n"/>
       <c r="H8" s="71" t="n"/>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="70" t="n"/>
       <c r="H9" s="71" t="n"/>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G10" s="72" t="n"/>
       <c r="H10" s="71" t="n"/>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G11" s="70" t="n"/>
       <c r="H11" s="71" t="n"/>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="33" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G12" s="72" t="n"/>
       <c r="H12" s="71" t="n"/>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G13" s="70" t="n"/>
       <c r="H13" s="71" t="n"/>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="F14" s="36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G14" s="72" t="n"/>
       <c r="H14" s="71" t="n"/>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="F16" s="36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" s="72" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E17" s="25" t="n"/>
       <c r="F17" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G17" s="72" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="F18" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="72" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="E19" s="25" t="n"/>
       <c r="F19" s="36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G19" s="72" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E22" s="26" t="n"/>
       <c r="F22" s="33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="72" t="n"/>
       <c r="H22" s="71" t="n"/>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="F23" s="32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G23" s="70" t="n"/>
       <c r="H23" s="71" t="n"/>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G24" s="72" t="n"/>
       <c r="H24" s="71" t="n"/>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="F26" s="36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G26" s="72" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="F27" s="32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G27" s="70" t="n"/>
       <c r="H27" s="71" t="n"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="E30" s="26" t="n"/>
       <c r="F30" s="33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G30" s="77" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="F32" s="32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G32" s="70" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="F33" s="36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G33" s="72" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E34" s="30" t="n"/>
       <c r="F34" s="35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G34" s="78" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="F36" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="72" t="n"/>
       <c r="H36" s="71" t="n"/>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="F37" s="32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G37" s="74" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="F38" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" s="72" t="n"/>
       <c r="H38" s="71" t="n"/>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="F40" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G40" s="72" t="n"/>
       <c r="H40" s="71" t="n"/>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="F41" s="32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G41" s="70" t="n"/>
       <c r="H41" s="71" t="n"/>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="F42" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G42" s="72" t="n"/>
       <c r="H42" s="71" t="n"/>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F43" s="32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G43" s="70" t="n"/>
       <c r="H43" s="71" t="n"/>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="F44" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G44" s="72" t="n"/>
       <c r="H44" s="71" t="n"/>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="F45" s="32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G45" s="70" t="n"/>
       <c r="H45" s="71" t="n"/>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="F48" s="59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G48" s="75" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E54" s="26" t="n"/>
       <c r="F54" s="33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G54" s="77" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="E55" s="7" t="n"/>
       <c r="F55" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G55" s="80" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="E57" s="58" t="n"/>
       <c r="F57" s="59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G57" s="83" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="E111" s="58" t="n"/>
       <c r="F111" s="59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G111" s="75" t="n"/>
       <c r="H111" s="76" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2089,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J145"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2170,42 +2170,43 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$140,"Pass")</f>
+        <f>COUNTIF($B$5:$B$144,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$140,"Move")+COUNTIF($B$5:$B$140,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$144,"Move")+COUNTIF($B$5:$B$144,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$140,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$144,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$140,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$144,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$140,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$144,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$140,"Injury")</f>
+        <f>COUNTIF($B$5:$B$144,"Injury")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$140,"Devastating Injury")</f>
+        <f>COUNTIF($B$5:$B$144,"Devastating Injury")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$140,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$144,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="87">
-        <f>SUM(B2:E2)+COUNTIF($B$5:$B$140,"Game Break")+SUM(G2:I2)</f>
+        <f>SUM(B2:E2)+COUNTIF($B$5:$B$144,"Game Break")+SUM(G2:I2)</f>
         <v/>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="85">
       <c r="A4" s="81" t="inlineStr">
         <is>
@@ -2249,7 +2250,7 @@
         </is>
       </c>
       <c r="B5" s="53">
-        <f>COUNTIF($B$6:$B$143,"Pass")</f>
+        <f>COUNTIF($B$6:$B$147,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="54" t="n"/>
@@ -2611,20 +2612,16 @@
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>SHOT +20%. Upgraded to 3pt. Pass to player of choice</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>Following Drive: draw 1. Following a Dribble Drive: gain 1 AST also</t>
-        </is>
-      </c>
+          <t>SHOT +10%. Draw 2 Cards. Move all your Clamps to Receiver, and they immediately attempt a three</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n"/>
       <c r="F18" s="36" t="n">
         <v>5</v>
       </c>
       <c r="G18" s="72" t="inlineStr">
         <is>
-          <t>The most it grants is a draw and 1 AST</t>
+          <t>They attempt the three after their draw</t>
         </is>
       </c>
       <c r="H18" s="71" t="n"/>
@@ -2694,7 +2691,7 @@
         </is>
       </c>
       <c r="B21" s="53">
-        <f>COUNTIF($B$22:$B$143,"Move")+COUNTIF($B$22:$B$143,"Special Move")</f>
+        <f>COUNTIF($B$22:$B$147,"Move")+COUNTIF($B$22:$B$147,"Special Move")</f>
         <v/>
       </c>
       <c r="C21" s="54" t="n"/>
@@ -3102,7 +3099,7 @@
         </is>
       </c>
       <c r="B35" s="53">
-        <f>COUNTIF($B$36:$B$143,"Special Move")</f>
+        <f>COUNTIF($B$36:$B$147,"Special Move")</f>
         <v/>
       </c>
       <c r="C35" s="54" t="n"/>
@@ -3199,7 +3196,7 @@
       </c>
       <c r="E38" s="25" t="inlineStr">
         <is>
-          <t>Shoot the ball. +1 Point on make</t>
+          <t>Shoot the ball</t>
         </is>
       </c>
       <c r="F38" s="36" t="n">
@@ -3259,11 +3256,11 @@
       </c>
       <c r="E40" s="25" t="inlineStr">
         <is>
-          <t>Shoot the ball. +1 Point on make</t>
+          <t>Shoot the ball</t>
         </is>
       </c>
       <c r="F40" s="36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" s="72" t="n"/>
       <c r="H40" s="71" t="n"/>
@@ -3289,11 +3286,11 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball. +1 Point on make</t>
+          <t>Shoot the ball</t>
         </is>
       </c>
       <c r="F41" s="32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G41" s="70" t="n"/>
       <c r="H41" s="71" t="n"/>
@@ -3319,11 +3316,11 @@
       </c>
       <c r="E42" s="25" t="inlineStr">
         <is>
-          <t>Shoot the ball. +1 Point on make</t>
+          <t>Shoot the ball</t>
         </is>
       </c>
       <c r="F42" s="36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G42" s="72" t="n"/>
       <c r="H42" s="71" t="n"/>
@@ -3439,7 +3436,7 @@
       </c>
       <c r="E46" s="25" t="inlineStr">
         <is>
-          <t>Shoot the ball. +1 Point on make</t>
+          <t>Shoot the ball</t>
         </is>
       </c>
       <c r="F46" s="36" t="n">
@@ -3499,7 +3496,7 @@
       </c>
       <c r="E48" s="58" t="inlineStr">
         <is>
-          <t>Shoot the ball. +1 Point on make. Selected players receive +1 AST on a make</t>
+          <t>Shoot the ball. Selected players receive +1 AST on a make</t>
         </is>
       </c>
       <c r="F48" s="59" t="n">
@@ -3589,54 +3586,50 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="54" customHeight="1" s="85">
-      <c r="A52" s="52" t="inlineStr">
+    <row r="52" ht="47" customHeight="1" s="85">
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>Special Move</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>Three-Ball</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>SHOT -10%</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Shoot the ball</t>
+        </is>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" s="0" t="n"/>
+    </row>
+    <row r="53" ht="54" customHeight="1" s="85">
+      <c r="A53" s="52" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="B52" s="53">
-        <f>COUNTIF($B$53:$B$143,"Clamp")</f>
+      <c r="B53" s="53">
+        <f>COUNTIF($B$54:$B$147,"Clamp")</f>
         <v/>
       </c>
-      <c r="C52" s="54" t="n"/>
-      <c r="D52" s="54" t="n"/>
-      <c r="E52" s="54" t="n"/>
-      <c r="F52" s="55" t="n"/>
-      <c r="G52" s="66" t="n"/>
-      <c r="H52" s="67" t="n"/>
-      <c r="I52" s="67" t="n"/>
-      <c r="J52" s="67" t="n"/>
-    </row>
-    <row r="53" ht="28" customHeight="1" s="85">
-      <c r="A53" s="21" t="n"/>
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t>Clamp</t>
-        </is>
-      </c>
-      <c r="C53" s="23" t="inlineStr">
-        <is>
-          <t>Contest</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Next player SHOT -25% if they shoot</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="G53" s="80" t="inlineStr">
-        <is>
-          <t>1 def</t>
-        </is>
-      </c>
-      <c r="H53" s="71" t="n"/>
-      <c r="I53" s="71" t="n"/>
-      <c r="J53" s="71" t="n"/>
+      <c r="C53" s="54" t="n"/>
+      <c r="D53" s="54" t="n"/>
+      <c r="E53" s="54" t="n"/>
+      <c r="F53" s="55" t="n"/>
+      <c r="G53" s="66" t="n"/>
+      <c r="H53" s="67" t="n"/>
+      <c r="I53" s="67" t="n"/>
+      <c r="J53" s="67" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1" s="85">
       <c r="A54" s="21" t="n"/>
@@ -3645,23 +3638,23 @@
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>Double-Team</t>
-        </is>
-      </c>
-      <c r="D54" s="25" t="inlineStr">
-        <is>
-          <t>Next Player cannot play 2 random cards from hand.</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="n"/>
-      <c r="F54" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="G54" s="77" t="inlineStr">
-        <is>
-          <t>2 def</t>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>Contest</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Next player SHOT -25% if they shoot</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G54" s="80" t="inlineStr">
+        <is>
+          <t>1 def</t>
         </is>
       </c>
       <c r="H54" s="71" t="n"/>
@@ -3675,236 +3668,252 @@
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
-        <is>
-          <t>Full-Court Press</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Next player discards 2 cards at the start of their turn</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="34" t="n">
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>Double-Team</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>Next Player cannot play 2 random cards from hand.</t>
+        </is>
+      </c>
+      <c r="E55" s="26" t="n"/>
+      <c r="F55" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="G55" s="80" t="inlineStr">
-        <is>
-          <t>1 def</t>
+      <c r="G55" s="77" t="inlineStr">
+        <is>
+          <t>2 def</t>
         </is>
       </c>
       <c r="H55" s="71" t="n"/>
       <c r="I55" s="71" t="n"/>
       <c r="J55" s="71" t="n"/>
     </row>
-    <row r="56" ht="42" customHeight="1" s="85">
+    <row r="56" ht="28" customHeight="1" s="85">
       <c r="A56" s="21" t="n"/>
       <c r="B56" s="22" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
-        <is>
-          <t>Trap</t>
-        </is>
-      </c>
-      <c r="D56" s="41" t="inlineStr">
-        <is>
-          <t>Next player can only play Pass cards during their turn</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="n"/>
-      <c r="F56" s="33" t="n">
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>Full-Court Press</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Next player discards 2 cards at the start of their turn</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="G56" s="77" t="inlineStr">
-        <is>
-          <t>They can still shoot as another option; 3 def</t>
+      <c r="G56" s="80" t="inlineStr">
+        <is>
+          <t>1 def</t>
         </is>
       </c>
       <c r="H56" s="71" t="n"/>
       <c r="I56" s="71" t="n"/>
       <c r="J56" s="71" t="n"/>
     </row>
-    <row r="57" ht="40" customHeight="1" s="85">
-      <c r="A57" s="27" t="n"/>
-      <c r="B57" s="28" t="inlineStr">
+    <row r="57" ht="42" customHeight="1" s="85">
+      <c r="A57" s="21" t="n"/>
+      <c r="B57" s="22" t="inlineStr">
         <is>
           <t>Clamp</t>
         </is>
       </c>
-      <c r="C57" s="56" t="inlineStr">
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>Trap</t>
+        </is>
+      </c>
+      <c r="D57" s="41" t="inlineStr">
+        <is>
+          <t>Next player can only play Pass cards during their turn</t>
+        </is>
+      </c>
+      <c r="E57" s="26" t="n"/>
+      <c r="F57" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" s="77" t="inlineStr">
+        <is>
+          <t>They can still shoot as another option; 3 def</t>
+        </is>
+      </c>
+      <c r="H57" s="71" t="n"/>
+      <c r="I57" s="71" t="n"/>
+      <c r="J57" s="71" t="n"/>
+    </row>
+    <row r="58" ht="40" customHeight="1" s="85">
+      <c r="A58" s="27" t="n"/>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C58" s="56" t="inlineStr">
         <is>
           <t>Triple-Team</t>
         </is>
       </c>
-      <c r="D57" s="57" t="inlineStr">
+      <c r="D58" s="57" t="inlineStr">
         <is>
           <t>Next player cannot play 3 random cards from hand.</t>
         </is>
       </c>
-      <c r="E57" s="58" t="n"/>
-      <c r="F57" s="59" t="n">
+      <c r="E58" s="58" t="n"/>
+      <c r="F58" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="G57" s="83" t="inlineStr">
+      <c r="G58" s="83" t="inlineStr">
         <is>
           <t>3 def</t>
         </is>
       </c>
-      <c r="H57" s="76" t="n"/>
-      <c r="I57" s="76" t="n"/>
-      <c r="J57" s="76" t="n"/>
-    </row>
-    <row r="58" ht="30" customHeight="1" s="85">
-      <c r="A58" s="52" t="inlineStr">
+      <c r="H58" s="76" t="n"/>
+      <c r="I58" s="76" t="n"/>
+      <c r="J58" s="76" t="n"/>
+    </row>
+    <row r="59" ht="40" customHeight="1" s="85">
+      <c r="A59" s="27" t="n"/>
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C59" s="56" t="inlineStr">
+        <is>
+          <t>Close-Out</t>
+        </is>
+      </c>
+      <c r="D59" s="57" t="inlineStr">
+        <is>
+          <t>Player cannot attempt a three-pointer</t>
+        </is>
+      </c>
+      <c r="E59" s="58" t="n"/>
+      <c r="F59" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" s="83" t="inlineStr">
+        <is>
+          <t>[NOT IN THE GAME YET]</t>
+        </is>
+      </c>
+      <c r="H59" s="76" t="n"/>
+      <c r="I59" s="76" t="n"/>
+      <c r="J59" s="76" t="n"/>
+    </row>
+    <row r="60" ht="40" customHeight="1" s="85">
+      <c r="A60" s="27" t="n"/>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C60" s="56" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="D60" s="57" t="inlineStr">
+        <is>
+          <t>Cannot Shoot. If player has no playable Pass cards, TOV +1; Round ends</t>
+        </is>
+      </c>
+      <c r="E60" s="58" t="n"/>
+      <c r="F60" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="83" t="inlineStr">
+        <is>
+          <t>[NOT IN THE GAME YET]</t>
+        </is>
+      </c>
+      <c r="H60" s="76" t="n"/>
+      <c r="I60" s="76" t="n"/>
+      <c r="J60" s="76" t="n"/>
+    </row>
+    <row r="61" ht="40" customHeight="1" s="85">
+      <c r="A61" s="27" t="n"/>
+      <c r="B61" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C61" s="56" t="inlineStr">
+        <is>
+          <t>Man-To-Man</t>
+        </is>
+      </c>
+      <c r="D61" s="57" t="inlineStr">
+        <is>
+          <t>SHOT - 10% each time a card is played</t>
+        </is>
+      </c>
+      <c r="E61" s="58" t="n"/>
+      <c r="F61" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G61" s="83" t="n"/>
+      <c r="H61" s="76" t="n"/>
+      <c r="I61" s="76" t="n"/>
+      <c r="J61" s="76" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1" s="85">
+      <c r="A62" s="52" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="B58" s="53">
-        <f>COUNTIF($B$59:$B$143,"Whistle")</f>
+      <c r="B62" s="53">
+        <f>COUNTIF($B$63:$B$147,"Whistle")</f>
         <v/>
       </c>
-      <c r="C58" s="54" t="n"/>
-      <c r="D58" s="54" t="n"/>
-      <c r="E58" s="54" t="n"/>
-      <c r="F58" s="55" t="n"/>
-      <c r="G58" s="66" t="n"/>
-      <c r="H58" s="67" t="n"/>
-      <c r="I58" s="67" t="n"/>
-      <c r="J58" s="67" t="n"/>
-    </row>
-    <row r="59" ht="56" customHeight="1" s="85">
-      <c r="A59" s="21" t="inlineStr">
+      <c r="C62" s="54" t="n"/>
+      <c r="D62" s="54" t="n"/>
+      <c r="E62" s="54" t="n"/>
+      <c r="F62" s="55" t="n"/>
+      <c r="G62" s="66" t="n"/>
+      <c r="H62" s="67" t="n"/>
+      <c r="I62" s="67" t="n"/>
+      <c r="J62" s="67" t="n"/>
+    </row>
+    <row r="63" ht="56" customHeight="1" s="85">
+      <c r="A63" s="21" t="inlineStr">
         <is>
           <t>All whistles are limited to 1</t>
         </is>
       </c>
-      <c r="B59" s="22" t="inlineStr">
+      <c r="B63" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C59" s="23" t="inlineStr">
+      <c r="C63" s="23" t="inlineStr">
         <is>
           <t>Back Court Violation</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
         </is>
       </c>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="50" t="n"/>
-      <c r="G59" s="70" t="inlineStr">
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="50" t="n"/>
+      <c r="G63" s="70" t="inlineStr">
         <is>
           <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
         </is>
       </c>
-      <c r="H59" s="71" t="n"/>
-      <c r="I59" s="71" t="n"/>
-      <c r="J59" s="71" t="n"/>
-    </row>
-    <row r="60" ht="42" customHeight="1" s="85">
-      <c r="A60" s="21" t="n"/>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C60" s="37" t="inlineStr">
-        <is>
-          <t>Blocking Foul</t>
-        </is>
-      </c>
-      <c r="D60" s="40" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
-        </is>
-      </c>
-      <c r="E60" s="26" t="n"/>
-      <c r="F60" s="50" t="n"/>
-      <c r="G60" s="72" t="n"/>
-      <c r="H60" s="71" t="n"/>
-      <c r="I60" s="71" t="n"/>
-      <c r="J60" s="71" t="n"/>
-    </row>
-    <row r="61" ht="42" customHeight="1" s="85">
-      <c r="A61" s="21" t="n"/>
-      <c r="B61" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C61" s="23" t="inlineStr">
-        <is>
-          <t>Charge</t>
-        </is>
-      </c>
-      <c r="D61" s="39" t="inlineStr">
-        <is>
-          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="50" t="n"/>
-      <c r="G61" s="70" t="n"/>
-      <c r="H61" s="71" t="n"/>
-      <c r="I61" s="71" t="n"/>
-      <c r="J61" s="71" t="n"/>
-    </row>
-    <row r="62" ht="42" customHeight="1" s="85">
-      <c r="A62" s="21" t="n"/>
-      <c r="B62" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C62" s="24" t="inlineStr">
-        <is>
-          <t>Cleared to Play</t>
-        </is>
-      </c>
-      <c r="D62" s="25" t="inlineStr">
-        <is>
-          <t>Injury Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="n"/>
-      <c r="F62" s="50" t="n"/>
-      <c r="G62" s="72" t="n"/>
-      <c r="H62" s="71" t="n"/>
-      <c r="I62" s="71" t="n"/>
-      <c r="J62" s="71" t="n"/>
-    </row>
-    <row r="63" ht="28" customHeight="1" s="85">
-      <c r="A63" s="21" t="n"/>
-      <c r="B63" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C63" s="23" t="inlineStr">
-        <is>
-          <t>Coach’s Challenge</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Any Whistle Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Pull a Timeout from the discards, if one is there, and take it</t>
-        </is>
-      </c>
-      <c r="F63" s="50" t="n"/>
-      <c r="G63" s="70" t="n"/>
       <c r="H63" s="71" t="n"/>
       <c r="I63" s="71" t="n"/>
       <c r="J63" s="71" t="n"/>
@@ -3918,30 +3927,22 @@
       </c>
       <c r="C64" s="37" t="inlineStr">
         <is>
-          <t>Delay-of-Game Warning</t>
-        </is>
-      </c>
-      <c r="D64" s="41" t="inlineStr">
-        <is>
-          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
-        </is>
-      </c>
-      <c r="E64" s="25" t="inlineStr">
-        <is>
-          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
-        </is>
-      </c>
-      <c r="F64" s="51" t="n"/>
-      <c r="G64" s="73" t="inlineStr">
-        <is>
-          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
-        </is>
-      </c>
+          <t>Blocking Foul</t>
+        </is>
+      </c>
+      <c r="D64" s="40" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="n"/>
+      <c r="F64" s="50" t="n"/>
+      <c r="G64" s="72" t="n"/>
       <c r="H64" s="71" t="n"/>
       <c r="I64" s="71" t="n"/>
       <c r="J64" s="71" t="n"/>
     </row>
-    <row r="65" ht="29" customHeight="1" s="85">
+    <row r="65" ht="42" customHeight="1" s="85">
       <c r="A65" s="21" t="n"/>
       <c r="B65" s="22" t="inlineStr">
         <is>
@@ -3950,40 +3951,36 @@
       </c>
       <c r="C65" s="23" t="inlineStr">
         <is>
-          <t>Double Dribble</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="D65" s="39" t="inlineStr">
+        <is>
+          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
         </is>
       </c>
       <c r="E65" s="7" t="n"/>
       <c r="F65" s="50" t="n"/>
-      <c r="G65" s="70" t="inlineStr">
-        <is>
-          <t>The dribbling player inbounds. The round is NOT incremented.</t>
-        </is>
-      </c>
+      <c r="G65" s="70" t="n"/>
       <c r="H65" s="71" t="n"/>
       <c r="I65" s="71" t="n"/>
       <c r="J65" s="71" t="n"/>
     </row>
-    <row r="66" ht="20" customHeight="1" s="85">
+    <row r="66" ht="42" customHeight="1" s="85">
       <c r="A66" s="21" t="n"/>
       <c r="B66" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C66" s="37" t="inlineStr">
-        <is>
-          <t>Flagrant Foul</t>
-        </is>
-      </c>
-      <c r="D66" s="41" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>Cleared to Play</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>Injury Card Played: Cancel card.</t>
         </is>
       </c>
       <c r="E66" s="26" t="n"/>
@@ -4000,48 +3997,60 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C67" s="37" t="inlineStr">
-        <is>
-          <t>Flagrant Foul II</t>
-        </is>
-      </c>
-      <c r="D67" s="38" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="n"/>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>Coach’s Challenge</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Any Whistle Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Pull a Timeout from the discards, if one is there, and take it</t>
+        </is>
+      </c>
       <c r="F67" s="50" t="n"/>
       <c r="G67" s="70" t="n"/>
       <c r="H67" s="71" t="n"/>
       <c r="I67" s="71" t="n"/>
       <c r="J67" s="71" t="n"/>
     </row>
-    <row r="68" ht="28" customHeight="1" s="85">
+    <row r="68" ht="42" customHeight="1" s="85">
       <c r="A68" s="21" t="n"/>
       <c r="B68" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C68" s="24" t="inlineStr">
-        <is>
-          <t>Goaltending</t>
-        </is>
-      </c>
-      <c r="D68" s="25" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
-        </is>
-      </c>
-      <c r="E68" s="26" t="n"/>
-      <c r="F68" s="50" t="n"/>
-      <c r="G68" s="72" t="n"/>
+      <c r="C68" s="37" t="inlineStr">
+        <is>
+          <t>Delay-of-Game Warning</t>
+        </is>
+      </c>
+      <c r="D68" s="41" t="inlineStr">
+        <is>
+          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
+        </is>
+      </c>
+      <c r="E68" s="25" t="inlineStr">
+        <is>
+          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
+        </is>
+      </c>
+      <c r="F68" s="51" t="n"/>
+      <c r="G68" s="73" t="inlineStr">
+        <is>
+          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
+        </is>
+      </c>
       <c r="H68" s="71" t="n"/>
       <c r="I68" s="71" t="n"/>
       <c r="J68" s="71" t="n"/>
     </row>
-    <row r="69" ht="14" customHeight="1" s="85">
+    <row r="69" ht="29" customHeight="1" s="85">
       <c r="A69" s="21" t="n"/>
       <c r="B69" s="22" t="inlineStr">
         <is>
@@ -4050,36 +4059,40 @@
       </c>
       <c r="C69" s="23" t="inlineStr">
         <is>
-          <t>Inadvertent Whistle</t>
-        </is>
-      </c>
-      <c r="D69" s="38" t="inlineStr">
-        <is>
-          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
+          <t>Double Dribble</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
         </is>
       </c>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="50" t="n"/>
-      <c r="G69" s="70" t="n"/>
+      <c r="G69" s="70" t="inlineStr">
+        <is>
+          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+        </is>
+      </c>
       <c r="H69" s="71" t="n"/>
       <c r="I69" s="71" t="n"/>
       <c r="J69" s="71" t="n"/>
     </row>
-    <row r="70" ht="14" customHeight="1" s="85">
+    <row r="70" ht="20" customHeight="1" s="85">
       <c r="A70" s="21" t="n"/>
       <c r="B70" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C70" s="24" t="inlineStr">
-        <is>
-          <t>Official Review</t>
+      <c r="C70" s="37" t="inlineStr">
+        <is>
+          <t>Flagrant Foul</t>
         </is>
       </c>
       <c r="D70" s="41" t="inlineStr">
         <is>
-          <t>Intangible Played: Discard all Intangibles from player.</t>
+          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
         </is>
       </c>
       <c r="E70" s="26" t="n"/>
@@ -4089,30 +4102,26 @@
       <c r="I70" s="71" t="n"/>
       <c r="J70" s="71" t="n"/>
     </row>
-    <row r="71" ht="14" customHeight="1" s="85">
+    <row r="71" ht="28" customHeight="1" s="85">
       <c r="A71" s="21" t="n"/>
       <c r="B71" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C71" s="23" t="inlineStr">
-        <is>
-          <t>Shot Clock Violation</t>
+      <c r="C71" s="37" t="inlineStr">
+        <is>
+          <t>Flagrant Foul II</t>
         </is>
       </c>
       <c r="D71" s="38" t="inlineStr">
         <is>
-          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
+          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
         </is>
       </c>
       <c r="E71" s="7" t="n"/>
       <c r="F71" s="50" t="n"/>
-      <c r="G71" s="70" t="inlineStr">
-        <is>
-          <t>This inbound does NOT increment the round.</t>
-        </is>
-      </c>
+      <c r="G71" s="70" t="n"/>
       <c r="H71" s="71" t="n"/>
       <c r="I71" s="71" t="n"/>
       <c r="J71" s="71" t="n"/>
@@ -4126,12 +4135,12 @@
       </c>
       <c r="C72" s="24" t="inlineStr">
         <is>
-          <t>Technical Foul</t>
-        </is>
-      </c>
-      <c r="D72" s="41" t="inlineStr">
-        <is>
-          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
+          <t>Goaltending</t>
+        </is>
+      </c>
+      <c r="D72" s="25" t="inlineStr">
+        <is>
+          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
         </is>
       </c>
       <c r="E72" s="26" t="n"/>
@@ -4141,7 +4150,7 @@
       <c r="I72" s="71" t="n"/>
       <c r="J72" s="71" t="n"/>
     </row>
-    <row r="73" ht="28" customHeight="1" s="85">
+    <row r="73" ht="14" customHeight="1" s="85">
       <c r="A73" s="21" t="n"/>
       <c r="B73" s="22" t="inlineStr">
         <is>
@@ -4150,12 +4159,12 @@
       </c>
       <c r="C73" s="23" t="inlineStr">
         <is>
-          <t>Timeout</t>
+          <t>Inadvertent Whistle</t>
         </is>
       </c>
       <c r="D73" s="38" t="inlineStr">
         <is>
-          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
         </is>
       </c>
       <c r="E73" s="7" t="n"/>
@@ -4165,7 +4174,7 @@
       <c r="I73" s="71" t="n"/>
       <c r="J73" s="71" t="n"/>
     </row>
-    <row r="74" ht="28" customHeight="1" s="85">
+    <row r="74" ht="14" customHeight="1" s="85">
       <c r="A74" s="21" t="n"/>
       <c r="B74" s="22" t="inlineStr">
         <is>
@@ -4174,12 +4183,12 @@
       </c>
       <c r="C74" s="24" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D74" s="25" t="inlineStr">
-        <is>
-          <t>Move card played: Cancel card. TOV +1</t>
+          <t>Official Review</t>
+        </is>
+      </c>
+      <c r="D74" s="41" t="inlineStr">
+        <is>
+          <t>Intangible Played: Discard all Intangibles from player.</t>
         </is>
       </c>
       <c r="E74" s="26" t="n"/>
@@ -4189,28 +4198,28 @@
       <c r="I74" s="71" t="n"/>
       <c r="J74" s="71" t="n"/>
     </row>
-    <row r="75" ht="28" customHeight="1" s="85">
+    <row r="75" ht="14" customHeight="1" s="85">
       <c r="A75" s="21" t="n"/>
       <c r="B75" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C75" s="24" t="inlineStr">
-        <is>
-          <t>Clear Path Foul</t>
-        </is>
-      </c>
-      <c r="D75" s="25" t="inlineStr">
-        <is>
-          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E75" s="26" t="n"/>
+      <c r="C75" s="23" t="inlineStr">
+        <is>
+          <t>Shot Clock Violation</t>
+        </is>
+      </c>
+      <c r="D75" s="38" t="inlineStr">
+        <is>
+          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="n"/>
       <c r="F75" s="50" t="n"/>
-      <c r="G75" s="72" t="inlineStr">
-        <is>
-          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
+      <c r="G75" s="70" t="inlineStr">
+        <is>
+          <t>This inbound does NOT increment the round.</t>
         </is>
       </c>
       <c r="H75" s="71" t="n"/>
@@ -4226,217 +4235,209 @@
       </c>
       <c r="C76" s="24" t="inlineStr">
         <is>
-          <t>Play-On</t>
-        </is>
-      </c>
-      <c r="D76" s="25" t="inlineStr">
-        <is>
-          <t>Discard each Game Break drawn and draw again, until a card is not one</t>
+          <t>Technical Foul</t>
+        </is>
+      </c>
+      <c r="D76" s="41" t="inlineStr">
+        <is>
+          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
         </is>
       </c>
       <c r="E76" s="26" t="n"/>
       <c r="F76" s="50" t="n"/>
-      <c r="G76" s="72" t="inlineStr">
-        <is>
-          <t>Raised where the Break lands, like Cleared to Play — nobody plays a Break</t>
-        </is>
-      </c>
+      <c r="G76" s="72" t="n"/>
       <c r="H76" s="71" t="n"/>
       <c r="I76" s="71" t="n"/>
       <c r="J76" s="71" t="n"/>
     </row>
-    <row r="77" ht="42" customHeight="1" s="85">
-      <c r="A77" s="27" t="n"/>
-      <c r="B77" s="28" t="inlineStr">
+    <row r="77" ht="28" customHeight="1" s="85">
+      <c r="A77" s="21" t="n"/>
+      <c r="B77" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>Crew Chief Review</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>Cancel a pass. The ball comes to you</t>
-        </is>
-      </c>
-      <c r="E77" s="60" t="n"/>
-      <c r="F77" s="61" t="n"/>
-      <c r="G77" s="78" t="n"/>
-      <c r="H77" s="76" t="n"/>
-      <c r="I77" s="76" t="n"/>
-      <c r="J77" s="76" t="n"/>
+      <c r="C77" s="23" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D77" s="38" t="inlineStr">
+        <is>
+          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="50" t="n"/>
+      <c r="G77" s="70" t="n"/>
+      <c r="H77" s="71" t="n"/>
+      <c r="I77" s="71" t="n"/>
+      <c r="J77" s="71" t="n"/>
     </row>
     <row r="78" ht="28" customHeight="1" s="85">
-      <c r="A78" s="27" t="n"/>
-      <c r="B78" s="28" t="inlineStr">
+      <c r="A78" s="21" t="n"/>
+      <c r="B78" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>Discontinued Dribble</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>Card Drawn: That player's possession ends immediately. They inbound</t>
-        </is>
-      </c>
-      <c r="E78" s="60" t="n"/>
-      <c r="F78" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="78" t="n"/>
-      <c r="H78" s="76" t="n"/>
-      <c r="I78" s="76" t="n"/>
-      <c r="J78" s="76" t="n"/>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D78" s="25" t="inlineStr">
+        <is>
+          <t>Move card played: Cancel card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E78" s="26" t="n"/>
+      <c r="F78" s="50" t="n"/>
+      <c r="G78" s="72" t="n"/>
+      <c r="H78" s="71" t="n"/>
+      <c r="I78" s="71" t="n"/>
+      <c r="J78" s="71" t="n"/>
     </row>
     <row r="79" ht="28" customHeight="1" s="85">
-      <c r="A79" s="52" t="inlineStr">
-        <is>
-          <t>Retired Game Breaks</t>
-        </is>
-      </c>
-      <c r="B79" s="53">
-        <f>COUNTIF($B$80:$B$109,"Retired Game Break")</f>
-        <v/>
-      </c>
-      <c r="C79" s="54" t="n"/>
-      <c r="D79" s="54" t="n"/>
-      <c r="E79" s="54" t="n"/>
-      <c r="F79" s="55" t="n"/>
-      <c r="G79" s="66" t="n"/>
-      <c r="H79" s="67" t="n"/>
-      <c r="I79" s="67" t="n"/>
-      <c r="J79" s="67" t="n"/>
-    </row>
-    <row r="80" ht="20" customHeight="1" s="85">
+      <c r="A79" s="21" t="n"/>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>Clear Path Foul</t>
+        </is>
+      </c>
+      <c r="D79" s="25" t="inlineStr">
+        <is>
+          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E79" s="26" t="n"/>
+      <c r="F79" s="50" t="n"/>
+      <c r="G79" s="72" t="inlineStr">
+        <is>
+          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
+        </is>
+      </c>
+      <c r="H79" s="71" t="n"/>
+      <c r="I79" s="71" t="n"/>
+      <c r="J79" s="71" t="n"/>
+    </row>
+    <row r="80" ht="28" customHeight="1" s="85">
       <c r="A80" s="21" t="n"/>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>Retired Game Break</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="C80" s="24" t="inlineStr">
         <is>
-          <t>2-Minute Warning</t>
+          <t>Play-On</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>All players discard down to 2 or fewer cards</t>
+          <t>Discard each Game Break drawn and draw again, until a card is not one</t>
         </is>
       </c>
       <c r="E80" s="26" t="n"/>
-      <c r="F80" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="72" t="n"/>
+      <c r="F80" s="50" t="n"/>
+      <c r="G80" s="72" t="inlineStr">
+        <is>
+          <t>Raised where the Break lands, like Cleared to Play — nobody plays a Break</t>
+        </is>
+      </c>
       <c r="H80" s="71" t="n"/>
       <c r="I80" s="71" t="n"/>
       <c r="J80" s="71" t="n"/>
     </row>
-    <row r="81" ht="28" customHeight="1" s="85">
-      <c r="A81" s="21" t="n"/>
-      <c r="B81" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C81" s="23" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="n"/>
-      <c r="F81" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="74" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
-      <c r="H81" s="71" t="n"/>
-      <c r="I81" s="71" t="n"/>
-      <c r="J81" s="71" t="n"/>
-    </row>
-    <row r="82" ht="20" customHeight="1" s="85">
-      <c r="A82" s="21" t="n"/>
-      <c r="B82" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C82" s="24" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D82" s="25" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E82" s="26" t="n"/>
-      <c r="F82" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="72" t="n"/>
-      <c r="H82" s="71" t="n"/>
-      <c r="I82" s="71" t="n"/>
-      <c r="J82" s="71" t="n"/>
-    </row>
-    <row r="83" ht="42" customHeight="1" s="85">
-      <c r="A83" s="21" t="n"/>
-      <c r="B83" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C83" s="23" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="n"/>
-      <c r="F83" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="70" t="n"/>
-      <c r="H83" s="71" t="n"/>
-      <c r="I83" s="71" t="n"/>
-      <c r="J83" s="71" t="n"/>
-    </row>
-    <row r="84" ht="28" customHeight="1" s="85">
+    <row r="81" ht="42" customHeight="1" s="85">
+      <c r="A81" s="27" t="n"/>
+      <c r="B81" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C81" s="29" t="inlineStr">
+        <is>
+          <t>Crew Chief Review</t>
+        </is>
+      </c>
+      <c r="D81" s="30" t="inlineStr">
+        <is>
+          <t>Cancel a pass. The ball comes to you</t>
+        </is>
+      </c>
+      <c r="E81" s="60" t="n"/>
+      <c r="F81" s="61" t="n"/>
+      <c r="G81" s="78" t="n"/>
+      <c r="H81" s="76" t="n"/>
+      <c r="I81" s="76" t="n"/>
+      <c r="J81" s="76" t="n"/>
+    </row>
+    <row r="82" ht="28" customHeight="1" s="85">
+      <c r="A82" s="27" t="n"/>
+      <c r="B82" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>Discontinued Dribble</t>
+        </is>
+      </c>
+      <c r="D82" s="30" t="inlineStr">
+        <is>
+          <t>Card Drawn: That player's possession ends immediately. They inbound</t>
+        </is>
+      </c>
+      <c r="E82" s="60" t="n"/>
+      <c r="F82" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="78" t="n"/>
+      <c r="H82" s="76" t="n"/>
+      <c r="I82" s="76" t="n"/>
+      <c r="J82" s="76" t="n"/>
+    </row>
+    <row r="83" ht="28" customHeight="1" s="85">
+      <c r="A83" s="52" t="inlineStr">
+        <is>
+          <t>Retired Game Breaks</t>
+        </is>
+      </c>
+      <c r="B83" s="53">
+        <f>COUNTIF($B$84:$B$113,"Retired Game Break")</f>
+        <v/>
+      </c>
+      <c r="C83" s="54" t="n"/>
+      <c r="D83" s="54" t="n"/>
+      <c r="E83" s="54" t="n"/>
+      <c r="F83" s="55" t="n"/>
+      <c r="G83" s="66" t="n"/>
+      <c r="H83" s="67" t="n"/>
+      <c r="I83" s="67" t="n"/>
+      <c r="J83" s="67" t="n"/>
+    </row>
+    <row r="84" ht="20" customHeight="1" s="85">
       <c r="A84" s="21" t="n"/>
       <c r="B84" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C84" s="37" t="inlineStr">
-        <is>
-          <t>Foul</t>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
         </is>
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>Take 1 FT</t>
+          <t>All players discard down to 2 or fewer cards</t>
         </is>
       </c>
       <c r="E84" s="26" t="n"/>
@@ -4448,7 +4449,7 @@
       <c r="I84" s="71" t="n"/>
       <c r="J84" s="71" t="n"/>
     </row>
-    <row r="85" ht="56" customHeight="1" s="85">
+    <row r="85" ht="28" customHeight="1" s="85">
       <c r="A85" s="21" t="n"/>
       <c r="B85" s="22" t="inlineStr">
         <is>
@@ -4457,24 +4458,28 @@
       </c>
       <c r="C85" s="23" t="inlineStr">
         <is>
-          <t>MVP Vote</t>
+          <t>Benched</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Draw 3 cards up to a hand of 7</t>
+          <t>Immediately give ball to any other player.</t>
         </is>
       </c>
       <c r="E85" s="7" t="n"/>
       <c r="F85" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G85" s="70" t="n"/>
+      <c r="G85" s="74" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H85" s="71" t="n"/>
       <c r="I85" s="71" t="n"/>
       <c r="J85" s="71" t="n"/>
     </row>
-    <row r="86" ht="42" customHeight="1" s="85">
+    <row r="86" ht="20" customHeight="1" s="85">
       <c r="A86" s="21" t="n"/>
       <c r="B86" s="22" t="inlineStr">
         <is>
@@ -4483,12 +4488,12 @@
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>Off Night</t>
+          <t>Crowd Noise</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>SHOT -20% this possession</t>
+          <t>Discard 1 card.</t>
         </is>
       </c>
       <c r="E86" s="26" t="n"/>
@@ -4509,20 +4514,16 @@
       </c>
       <c r="C87" s="23" t="inlineStr">
         <is>
-          <t>Swallowed Whistle</t>
+          <t>Designed Play</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F87" s="32" t="n">
+          <t>Draw up to a hand of 5</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G87" s="70" t="n"/>
@@ -4537,22 +4538,18 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C88" s="24" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
+      <c r="C88" s="37" t="inlineStr">
+        <is>
+          <t>Foul</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>Players cannot shoot when SHOT is above 50%</t>
-        </is>
-      </c>
-      <c r="E88" s="25" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F88" s="36" t="n">
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E88" s="26" t="n"/>
+      <c r="F88" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="72" t="n"/>
@@ -4560,7 +4557,7 @@
       <c r="I88" s="71" t="n"/>
       <c r="J88" s="71" t="n"/>
     </row>
-    <row r="89" ht="28" customHeight="1" s="85">
+    <row r="89" ht="56" customHeight="1" s="85">
       <c r="A89" s="21" t="n"/>
       <c r="B89" s="22" t="inlineStr">
         <is>
@@ -4569,75 +4566,75 @@
       </c>
       <c r="C89" s="23" t="inlineStr">
         <is>
-          <t>Traded Mid-Game</t>
+          <t>MVP Vote</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Swap hands with a random other player</t>
+          <t>Draw 3 cards up to a hand of 7</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
       <c r="F89" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G89" s="74" t="n"/>
+      <c r="G89" s="70" t="n"/>
       <c r="H89" s="71" t="n"/>
       <c r="I89" s="71" t="n"/>
       <c r="J89" s="71" t="n"/>
     </row>
-    <row r="90" ht="56" customHeight="1" s="85">
+    <row r="90" ht="42" customHeight="1" s="85">
       <c r="A90" s="21" t="n"/>
       <c r="B90" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C90" s="49" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D90" s="38" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="n"/>
-      <c r="F90" s="34" t="n">
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D90" s="25" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E90" s="26" t="n"/>
+      <c r="F90" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G90" s="74" t="n"/>
+      <c r="G90" s="72" t="n"/>
       <c r="H90" s="71" t="n"/>
       <c r="I90" s="71" t="n"/>
       <c r="J90" s="71" t="n"/>
     </row>
-    <row r="91" ht="56" customHeight="1" s="85">
+    <row r="91" ht="42" customHeight="1" s="85">
       <c r="A91" s="21" t="n"/>
       <c r="B91" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C91" s="49" t="inlineStr">
-        <is>
-          <t>All-Swissh Selection</t>
-        </is>
-      </c>
-      <c r="D91" s="38" t="inlineStr">
-        <is>
-          <t>Draw 3 cards after your next make</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="34" t="n">
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F91" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G91" s="74" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+      <c r="G91" s="70" t="n"/>
       <c r="H91" s="71" t="n"/>
       <c r="I91" s="71" t="n"/>
       <c r="J91" s="71" t="n"/>
@@ -4649,56 +4646,56 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C92" s="49" t="inlineStr">
-        <is>
-          <t>All Star Selection</t>
-        </is>
-      </c>
-      <c r="D92" s="38" t="inlineStr">
-        <is>
-          <t>Draw 2 cards</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="n"/>
-      <c r="F92" s="34" t="n">
+      <c r="C92" s="24" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D92" s="25" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is above 50%</t>
+        </is>
+      </c>
+      <c r="E92" s="25" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F92" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G92" s="74" t="n"/>
+      <c r="G92" s="72" t="n"/>
       <c r="H92" s="71" t="n"/>
       <c r="I92" s="71" t="n"/>
       <c r="J92" s="71" t="n"/>
     </row>
-    <row r="93" ht="42" customHeight="1" s="85">
+    <row r="93" ht="28" customHeight="1" s="85">
       <c r="A93" s="21" t="n"/>
       <c r="B93" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C93" s="49" t="inlineStr">
-        <is>
-          <t>Hit the Bike</t>
-        </is>
-      </c>
-      <c r="D93" s="38" t="inlineStr">
-        <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+      <c r="C93" s="23" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Swap hands with a random other player</t>
         </is>
       </c>
       <c r="E93" s="7" t="n"/>
       <c r="F93" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G93" s="74" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="G93" s="74" t="n"/>
       <c r="H93" s="71" t="n"/>
       <c r="I93" s="71" t="n"/>
       <c r="J93" s="71" t="n"/>
     </row>
-    <row r="94" ht="28" customHeight="1" s="85">
+    <row r="94" ht="56" customHeight="1" s="85">
       <c r="A94" s="21" t="n"/>
       <c r="B94" s="22" t="inlineStr">
         <is>
@@ -4707,12 +4704,12 @@
       </c>
       <c r="C94" s="49" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D94" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E94" s="7" t="n"/>
@@ -4724,7 +4721,7 @@
       <c r="I94" s="71" t="n"/>
       <c r="J94" s="71" t="n"/>
     </row>
-    <row r="95" ht="42" customHeight="1" s="85">
+    <row r="95" ht="56" customHeight="1" s="85">
       <c r="A95" s="21" t="n"/>
       <c r="B95" s="22" t="inlineStr">
         <is>
@@ -4733,12 +4730,12 @@
       </c>
       <c r="C95" s="49" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D95" s="38" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
@@ -4747,14 +4744,14 @@
       </c>
       <c r="G95" s="74" t="inlineStr">
         <is>
-          <t>Deck ones are shown face down</t>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
         </is>
       </c>
       <c r="H95" s="71" t="n"/>
       <c r="I95" s="71" t="n"/>
       <c r="J95" s="71" t="n"/>
     </row>
-    <row r="96" ht="14" customHeight="1" s="85">
+    <row r="96" ht="28" customHeight="1" s="85">
       <c r="A96" s="21" t="n"/>
       <c r="B96" s="22" t="inlineStr">
         <is>
@@ -4763,28 +4760,24 @@
       </c>
       <c r="C96" s="49" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D96" s="38" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="74" t="inlineStr">
-        <is>
-          <t>This is a bad thing in the NBA</t>
-        </is>
-      </c>
+      <c r="G96" s="74" t="n"/>
       <c r="H96" s="71" t="n"/>
       <c r="I96" s="71" t="n"/>
       <c r="J96" s="71" t="n"/>
     </row>
-    <row r="97" ht="14" customHeight="1" s="85">
+    <row r="97" ht="42" customHeight="1" s="85">
       <c r="A97" s="21" t="n"/>
       <c r="B97" s="22" t="inlineStr">
         <is>
@@ -4793,12 +4786,12 @@
       </c>
       <c r="C97" s="49" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D97" s="38" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -4807,14 +4800,14 @@
       </c>
       <c r="G97" s="74" t="inlineStr">
         <is>
-          <t>The hex travels in the declared direction too</t>
+          <t>This is not a pass</t>
         </is>
       </c>
       <c r="H97" s="71" t="n"/>
       <c r="I97" s="71" t="n"/>
       <c r="J97" s="71" t="n"/>
     </row>
-    <row r="98" ht="14" customHeight="1" s="85">
+    <row r="98" ht="28" customHeight="1" s="85">
       <c r="A98" s="21" t="n"/>
       <c r="B98" s="22" t="inlineStr">
         <is>
@@ -4823,12 +4816,12 @@
       </c>
       <c r="C98" s="49" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D98" s="38" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -4840,7 +4833,7 @@
       <c r="I98" s="71" t="n"/>
       <c r="J98" s="71" t="n"/>
     </row>
-    <row r="99" ht="14" customHeight="1" s="85">
+    <row r="99" ht="42" customHeight="1" s="85">
       <c r="A99" s="21" t="n"/>
       <c r="B99" s="22" t="inlineStr">
         <is>
@@ -4849,19 +4842,23 @@
       </c>
       <c r="C99" s="49" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D99" s="38" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
       <c r="F99" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G99" s="74" t="n"/>
+      <c r="G99" s="74" t="inlineStr">
+        <is>
+          <t>Deck ones are shown face down</t>
+        </is>
+      </c>
       <c r="H99" s="71" t="n"/>
       <c r="I99" s="71" t="n"/>
       <c r="J99" s="71" t="n"/>
@@ -4875,19 +4872,23 @@
       </c>
       <c r="C100" s="49" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D100" s="38" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="74" t="n"/>
+      <c r="G100" s="74" t="inlineStr">
+        <is>
+          <t>This is a bad thing in the NBA</t>
+        </is>
+      </c>
       <c r="H100" s="71" t="n"/>
       <c r="I100" s="71" t="n"/>
       <c r="J100" s="71" t="n"/>
@@ -4901,19 +4902,23 @@
       </c>
       <c r="C101" s="49" t="inlineStr">
         <is>
-          <t>Altercation</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D101" s="38" t="inlineStr">
         <is>
-          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
       <c r="F101" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G101" s="74" t="n"/>
+      <c r="G101" s="74" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H101" s="71" t="n"/>
       <c r="I101" s="71" t="n"/>
       <c r="J101" s="71" t="n"/>
@@ -4927,12 +4932,12 @@
       </c>
       <c r="C102" s="49" t="inlineStr">
         <is>
-          <t>Huge Altercation</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D102" s="38" t="inlineStr">
         <is>
-          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
@@ -4953,12 +4958,12 @@
       </c>
       <c r="C103" s="49" t="inlineStr">
         <is>
-          <t>Home Court Advantage</t>
+          <t>Official Timeout</t>
         </is>
       </c>
       <c r="D103" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 25%</t>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
@@ -4979,12 +4984,12 @@
       </c>
       <c r="C104" s="49" t="inlineStr">
         <is>
-          <t>Away Game</t>
+          <t>Team Doctor</t>
         </is>
       </c>
       <c r="D104" s="38" t="inlineStr">
         <is>
-          <t>SHOT - 10%</t>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -4996,7 +5001,7 @@
       <c r="I104" s="71" t="n"/>
       <c r="J104" s="71" t="n"/>
     </row>
-    <row r="105" ht="28" customHeight="1" s="85">
+    <row r="105" ht="14" customHeight="1" s="85">
       <c r="A105" s="21" t="n"/>
       <c r="B105" s="22" t="inlineStr">
         <is>
@@ -5005,28 +5010,24 @@
       </c>
       <c r="C105" s="49" t="inlineStr">
         <is>
-          <t>Mic'd Up</t>
+          <t>Altercation</t>
         </is>
       </c>
       <c r="D105" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 10% until passed or shot</t>
+          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
       <c r="F105" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="74" t="inlineStr">
-        <is>
-          <t>The boost is the holder's alone and does not travel with a pass</t>
-        </is>
-      </c>
+      <c r="G105" s="74" t="n"/>
       <c r="H105" s="71" t="n"/>
       <c r="I105" s="71" t="n"/>
       <c r="J105" s="71" t="n"/>
     </row>
-    <row r="106" ht="28" customHeight="1" s="85">
+    <row r="106" ht="14" customHeight="1" s="85">
       <c r="A106" s="21" t="n"/>
       <c r="B106" s="22" t="inlineStr">
         <is>
@@ -5035,12 +5036,12 @@
       </c>
       <c r="C106" s="49" t="inlineStr">
         <is>
-          <t>In The Zone</t>
+          <t>Huge Altercation</t>
         </is>
       </c>
       <c r="D106" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
         </is>
       </c>
       <c r="E106" s="7" t="n"/>
@@ -5052,7 +5053,7 @@
       <c r="I106" s="71" t="n"/>
       <c r="J106" s="71" t="n"/>
     </row>
-    <row r="107" ht="28" customHeight="1" s="85">
+    <row r="107" ht="14" customHeight="1" s="85">
       <c r="A107" s="21" t="n"/>
       <c r="B107" s="22" t="inlineStr">
         <is>
@@ -5061,12 +5062,12 @@
       </c>
       <c r="C107" s="49" t="inlineStr">
         <is>
-          <t>Role Player</t>
+          <t>Home Court Advantage</t>
         </is>
       </c>
       <c r="D107" s="38" t="inlineStr">
         <is>
-          <t>All other players draw 1 card</t>
+          <t>SHOT + 25%</t>
         </is>
       </c>
       <c r="E107" s="7" t="n"/>
@@ -5078,154 +5079,174 @@
       <c r="I107" s="71" t="n"/>
       <c r="J107" s="71" t="n"/>
     </row>
-    <row r="108" ht="28" customHeight="1" s="85">
-      <c r="A108" s="27" t="n"/>
-      <c r="B108" s="28" t="inlineStr">
+    <row r="108" ht="14" customHeight="1" s="85">
+      <c r="A108" s="21" t="n"/>
+      <c r="B108" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C108" s="62" t="inlineStr">
+      <c r="C108" s="49" t="inlineStr">
+        <is>
+          <t>Away Game</t>
+        </is>
+      </c>
+      <c r="D108" s="38" t="inlineStr">
+        <is>
+          <t>SHOT - 10%</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="n"/>
+      <c r="F108" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="74" t="n"/>
+      <c r="H108" s="71" t="n"/>
+      <c r="I108" s="71" t="n"/>
+      <c r="J108" s="71" t="n"/>
+    </row>
+    <row r="109" ht="28" customHeight="1" s="85">
+      <c r="A109" s="21" t="n"/>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C109" s="49" t="inlineStr">
+        <is>
+          <t>Mic'd Up</t>
+        </is>
+      </c>
+      <c r="D109" s="38" t="inlineStr">
+        <is>
+          <t>SHOT + 10% until passed or shot</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="n"/>
+      <c r="F109" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="74" t="inlineStr">
+        <is>
+          <t>The boost is the holder's alone and does not travel with a pass</t>
+        </is>
+      </c>
+      <c r="H109" s="71" t="n"/>
+      <c r="I109" s="71" t="n"/>
+      <c r="J109" s="71" t="n"/>
+    </row>
+    <row r="110" ht="28" customHeight="1" s="85">
+      <c r="A110" s="21" t="n"/>
+      <c r="B110" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C110" s="49" t="inlineStr">
+        <is>
+          <t>In The Zone</t>
+        </is>
+      </c>
+      <c r="D110" s="38" t="inlineStr">
+        <is>
+          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="n"/>
+      <c r="F110" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="74" t="n"/>
+      <c r="H110" s="71" t="n"/>
+      <c r="I110" s="71" t="n"/>
+      <c r="J110" s="71" t="n"/>
+    </row>
+    <row r="111" ht="28" customHeight="1" s="85">
+      <c r="A111" s="21" t="n"/>
+      <c r="B111" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C111" s="49" t="inlineStr">
+        <is>
+          <t>Role Player</t>
+        </is>
+      </c>
+      <c r="D111" s="38" t="inlineStr">
+        <is>
+          <t>All other players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="n"/>
+      <c r="F111" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="74" t="n"/>
+      <c r="H111" s="71" t="n"/>
+      <c r="I111" s="71" t="n"/>
+      <c r="J111" s="71" t="n"/>
+    </row>
+    <row r="112" ht="28" customHeight="1" s="85">
+      <c r="A112" s="27" t="n"/>
+      <c r="B112" s="28" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C112" s="62" t="inlineStr">
         <is>
           <t>Back-and-Forth Game</t>
         </is>
       </c>
-      <c r="D108" s="63" t="inlineStr">
+      <c r="D112" s="63" t="inlineStr">
         <is>
           <t>Discard the next 3 Game Breaks. Whoever draws one draws again</t>
         </is>
       </c>
-      <c r="E108" s="58" t="n"/>
-      <c r="F108" s="59" t="n">
+      <c r="E112" s="58" t="n"/>
+      <c r="F112" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="79" t="n"/>
-      <c r="H108" s="76" t="n"/>
-      <c r="I108" s="76" t="n"/>
-      <c r="J108" s="76" t="n"/>
-    </row>
-    <row r="109" ht="42" customHeight="1" s="85">
-      <c r="A109" s="27" t="n"/>
-      <c r="B109" s="28" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C109" s="62" t="inlineStr">
-        <is>
-          <t>Off the Backboard</t>
-        </is>
-      </c>
-      <c r="D109" s="63" t="inlineStr">
-        <is>
-          <t>Your next missed shot rebounds itself</t>
-        </is>
-      </c>
-      <c r="E109" s="58" t="n"/>
-      <c r="F109" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="79" t="n"/>
-      <c r="H109" s="76" t="n"/>
-      <c r="I109" s="76" t="n"/>
-      <c r="J109" s="76" t="n"/>
-    </row>
-    <row r="110" ht="56" customHeight="1" s="85">
-      <c r="A110" s="52" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="B110" s="53">
-        <f>COUNTIF($B$111:$B$143,"Injury")</f>
-        <v/>
-      </c>
-      <c r="C110" s="54" t="n"/>
-      <c r="D110" s="54" t="n"/>
-      <c r="E110" s="54" t="n"/>
-      <c r="F110" s="55" t="n"/>
-      <c r="G110" s="66" t="n"/>
-      <c r="H110" s="67" t="n"/>
-      <c r="I110" s="67" t="n"/>
-      <c r="J110" s="67" t="n"/>
-    </row>
-    <row r="111" ht="57" customHeight="1" s="85">
-      <c r="A111" s="27" t="n"/>
-      <c r="B111" s="28" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="C111" s="56" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
-        </is>
-      </c>
-      <c r="D111" s="63" t="inlineStr">
-        <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
-        </is>
-      </c>
-      <c r="E111" s="58" t="n"/>
-      <c r="F111" s="59" t="n">
-        <v>5</v>
-      </c>
-      <c r="G111" s="75" t="n"/>
-      <c r="H111" s="76" t="n"/>
-      <c r="I111" s="76" t="n"/>
-      <c r="J111" s="76" t="n"/>
-    </row>
-    <row r="112" ht="20" customHeight="1" s="85">
-      <c r="A112" s="52" t="inlineStr">
-        <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="B112" s="53">
-        <f>COUNTIF($B$113:$B$143,"Devastating Injury")</f>
-        <v/>
-      </c>
-      <c r="C112" s="54" t="n"/>
-      <c r="D112" s="54" t="n"/>
-      <c r="E112" s="54" t="n"/>
-      <c r="F112" s="55" t="n"/>
-      <c r="G112" s="66" t="n"/>
-      <c r="H112" s="67" t="n"/>
-      <c r="I112" s="67" t="n"/>
-      <c r="J112" s="67" t="n"/>
-    </row>
-    <row r="113" ht="28" customHeight="1" s="85">
+      <c r="G112" s="79" t="n"/>
+      <c r="H112" s="76" t="n"/>
+      <c r="I112" s="76" t="n"/>
+      <c r="J112" s="76" t="n"/>
+    </row>
+    <row r="113" ht="42" customHeight="1" s="85">
       <c r="A113" s="27" t="n"/>
       <c r="B113" s="28" t="inlineStr">
         <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="C113" s="64" t="inlineStr">
-        <is>
-          <t>Torn Achilles</t>
-        </is>
-      </c>
-      <c r="D113" s="65" t="inlineStr">
-        <is>
-          <t>Hand is locked every turn except 1 card (randomly)</t>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C113" s="62" t="inlineStr">
+        <is>
+          <t>Off the Backboard</t>
+        </is>
+      </c>
+      <c r="D113" s="63" t="inlineStr">
+        <is>
+          <t>Your next missed shot rebounds itself</t>
         </is>
       </c>
       <c r="E113" s="58" t="n"/>
-      <c r="F113" s="61" t="n"/>
-      <c r="G113" s="75" t="n"/>
+      <c r="F113" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="79" t="n"/>
       <c r="H113" s="76" t="n"/>
       <c r="I113" s="76" t="n"/>
       <c r="J113" s="76" t="n"/>
     </row>
-    <row r="114" ht="42" customHeight="1" s="85">
+    <row r="114" ht="56" customHeight="1" s="85">
       <c r="A114" s="52" t="inlineStr">
         <is>
-          <t>Intangible</t>
+          <t>Injury</t>
         </is>
       </c>
       <c r="B114" s="53">
-        <f>COUNTIF($B$115:$B$143,"Intangible")</f>
+        <f>COUNTIF($B$115:$B$147,"Injury")</f>
         <v/>
       </c>
       <c r="C114" s="54" t="n"/>
@@ -5237,119 +5258,118 @@
       <c r="I114" s="67" t="n"/>
       <c r="J114" s="67" t="n"/>
     </row>
-    <row r="115" ht="28" customHeight="1" s="85">
-      <c r="A115" s="42" t="inlineStr">
+    <row r="115" ht="57" customHeight="1" s="85">
+      <c r="A115" s="27" t="n"/>
+      <c r="B115" s="28" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C115" s="56" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D115" s="63" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+        </is>
+      </c>
+      <c r="E115" s="58" t="n"/>
+      <c r="F115" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G115" s="75" t="n"/>
+      <c r="H115" s="76" t="n"/>
+      <c r="I115" s="76" t="n"/>
+      <c r="J115" s="76" t="n"/>
+    </row>
+    <row r="116" ht="20" customHeight="1" s="85">
+      <c r="A116" s="52" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="B116" s="53">
+        <f>COUNTIF($B$117:$B$147,"Devastating Injury")</f>
+        <v/>
+      </c>
+      <c r="C116" s="54" t="n"/>
+      <c r="D116" s="54" t="n"/>
+      <c r="E116" s="54" t="n"/>
+      <c r="F116" s="55" t="n"/>
+      <c r="G116" s="66" t="n"/>
+      <c r="H116" s="67" t="n"/>
+      <c r="I116" s="67" t="n"/>
+      <c r="J116" s="67" t="n"/>
+    </row>
+    <row r="117" ht="28" customHeight="1" s="85">
+      <c r="A117" s="27" t="n"/>
+      <c r="B117" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C117" s="64" t="inlineStr">
+        <is>
+          <t>Torn Achilles</t>
+        </is>
+      </c>
+      <c r="D117" s="65" t="inlineStr">
+        <is>
+          <t>Hand is locked every turn except 1 card (randomly)</t>
+        </is>
+      </c>
+      <c r="E117" s="58" t="n"/>
+      <c r="F117" s="61" t="n"/>
+      <c r="G117" s="75" t="n"/>
+      <c r="H117" s="76" t="n"/>
+      <c r="I117" s="76" t="n"/>
+      <c r="J117" s="76" t="n"/>
+    </row>
+    <row r="118" ht="42" customHeight="1" s="85">
+      <c r="A118" s="52" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="B118" s="53">
+        <f>COUNTIF($B$119:$B$147,"Intangible")</f>
+        <v/>
+      </c>
+      <c r="C118" s="54" t="n"/>
+      <c r="D118" s="54" t="n"/>
+      <c r="E118" s="54" t="n"/>
+      <c r="F118" s="55" t="n"/>
+      <c r="G118" s="66" t="n"/>
+      <c r="H118" s="67" t="n"/>
+      <c r="I118" s="67" t="n"/>
+      <c r="J118" s="67" t="n"/>
+    </row>
+    <row r="119" ht="28" customHeight="1" s="85">
+      <c r="A119" s="42" t="inlineStr">
         <is>
           <t>All intangibles are limited to 1</t>
         </is>
       </c>
-      <c r="B115" s="22" t="inlineStr">
+      <c r="B119" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C115" s="23" t="inlineStr">
+      <c r="C119" s="23" t="inlineStr">
         <is>
           <t>Board-Crasher</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>SHOT +10% upon Rebounding your own missed shot</t>
         </is>
       </c>
-      <c r="E115" s="7" t="n"/>
-      <c r="F115" s="50" t="n"/>
-      <c r="G115" s="70" t="n"/>
-      <c r="H115" s="71" t="n"/>
-      <c r="I115" s="71" t="n"/>
-      <c r="J115" s="71" t="n"/>
-    </row>
-    <row r="116" ht="28" customHeight="1" s="85">
-      <c r="A116" s="21" t="n"/>
-      <c r="B116" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C116" s="24" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D116" s="25" t="inlineStr">
-        <is>
-          <t>Additional SHOT +10% on all received passes</t>
-        </is>
-      </c>
-      <c r="E116" s="26" t="n"/>
-      <c r="F116" s="50" t="n"/>
-      <c r="G116" s="72" t="n"/>
-      <c r="H116" s="71" t="n"/>
-      <c r="I116" s="71" t="n"/>
-      <c r="J116" s="71" t="n"/>
-    </row>
-    <row r="117" ht="56" customHeight="1" s="85">
-      <c r="A117" s="21" t="n"/>
-      <c r="B117" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C117" s="23" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="50" t="n"/>
-      <c r="G117" s="70" t="n"/>
-      <c r="H117" s="71" t="n"/>
-      <c r="I117" s="71" t="n"/>
-      <c r="J117" s="71" t="n"/>
-    </row>
-    <row r="118" ht="56" customHeight="1" s="85">
-      <c r="B118" s="0" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C118" s="0" t="inlineStr">
-        <is>
-          <t>Roswell Reach</t>
-        </is>
-      </c>
-      <c r="D118" s="0" t="inlineStr">
-        <is>
-          <t>All your Rebound bids of 1 or more count as 1 higher</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="28" customHeight="1" s="85">
-      <c r="A119" s="21" t="n"/>
-      <c r="B119" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C119" s="24" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D119" s="25" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
-        </is>
-      </c>
-      <c r="E119" s="26" t="n"/>
+      <c r="E119" s="7" t="n"/>
       <c r="F119" s="50" t="n"/>
-      <c r="G119" s="72" t="n"/>
+      <c r="G119" s="70" t="n"/>
       <c r="H119" s="71" t="n"/>
       <c r="I119" s="71" t="n"/>
       <c r="J119" s="71" t="n"/>
@@ -5361,76 +5381,65 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C120" s="23" t="inlineStr">
-        <is>
-          <t>Fox-Like First Step</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
-      <c r="F120" s="51" t="n"/>
-      <c r="G120" s="70" t="n"/>
+      <c r="C120" s="24" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D120" s="25" t="inlineStr">
+        <is>
+          <t>Additional SHOT +10% on all received passes</t>
+        </is>
+      </c>
+      <c r="E120" s="26" t="n"/>
+      <c r="F120" s="50" t="n"/>
+      <c r="G120" s="72" t="n"/>
       <c r="H120" s="71" t="n"/>
       <c r="I120" s="71" t="n"/>
       <c r="J120" s="71" t="n"/>
     </row>
-    <row r="121" ht="28" customHeight="1" s="85">
+    <row r="121" ht="56" customHeight="1" s="85">
       <c r="A121" s="21" t="n"/>
       <c r="B121" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C121" s="37" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D121" s="41" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E121" s="26" t="n"/>
+      <c r="C121" s="23" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="n"/>
       <c r="F121" s="50" t="n"/>
-      <c r="G121" s="77" t="n"/>
+      <c r="G121" s="70" t="n"/>
       <c r="H121" s="71" t="n"/>
       <c r="I121" s="71" t="n"/>
       <c r="J121" s="71" t="n"/>
     </row>
-    <row r="122" ht="28" customHeight="1" s="85">
-      <c r="A122" s="21" t="n"/>
-      <c r="B122" s="22" t="inlineStr">
+    <row r="122" ht="56" customHeight="1" s="85">
+      <c r="B122" s="0" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C122" s="37" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D122" s="38" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="n"/>
-      <c r="F122" s="50" t="n"/>
-      <c r="G122" s="70" t="n"/>
-      <c r="H122" s="71" t="n"/>
-      <c r="I122" s="71" t="n"/>
-      <c r="J122" s="71" t="n"/>
-    </row>
-    <row r="123" ht="14" customHeight="1" s="85">
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>Roswell Reach</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t>All your Rebound bids of 1 or more count as 1 higher</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="28" customHeight="1" s="85">
       <c r="A123" s="21" t="n"/>
       <c r="B123" s="22" t="inlineStr">
         <is>
@@ -5439,12 +5448,12 @@
       </c>
       <c r="C123" s="24" t="inlineStr">
         <is>
-          <t>Gravity</t>
+          <t>Floor General</t>
         </is>
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
         </is>
       </c>
       <c r="E123" s="26" t="n"/>
@@ -5463,16 +5472,20 @@
       </c>
       <c r="C124" s="23" t="inlineStr">
         <is>
-          <t>Great Conditioning</t>
+          <t>Fox-Like First Step</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="n"/>
-      <c r="F124" s="50" t="n"/>
+          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>Your Move cards are unaffected by opponents</t>
+        </is>
+      </c>
+      <c r="F124" s="51" t="n"/>
       <c r="G124" s="70" t="n"/>
       <c r="H124" s="71" t="n"/>
       <c r="I124" s="71" t="n"/>
@@ -5485,19 +5498,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C125" s="24" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D125" s="25" t="inlineStr">
-        <is>
-          <t>SHOT +25% if you scored last round.</t>
+      <c r="C125" s="37" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D125" s="41" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
         </is>
       </c>
       <c r="E125" s="26" t="n"/>
       <c r="F125" s="50" t="n"/>
-      <c r="G125" s="72" t="n"/>
+      <c r="G125" s="77" t="n"/>
       <c r="H125" s="71" t="n"/>
       <c r="I125" s="71" t="n"/>
       <c r="J125" s="71" t="n"/>
@@ -5509,14 +5522,14 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C126" s="23" t="inlineStr">
-        <is>
-          <t>Like That</t>
+      <c r="C126" s="37" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
         </is>
       </c>
       <c r="D126" s="38" t="inlineStr">
         <is>
-          <t>Your SHOT % cannot be reduced</t>
+          <t>Take 1 additional FT</t>
         </is>
       </c>
       <c r="E126" s="7" t="n"/>
@@ -5526,7 +5539,7 @@
       <c r="I126" s="71" t="n"/>
       <c r="J126" s="71" t="n"/>
     </row>
-    <row r="127" ht="28" customHeight="1" s="85">
+    <row r="127" ht="14" customHeight="1" s="85">
       <c r="A127" s="21" t="n"/>
       <c r="B127" s="22" t="inlineStr">
         <is>
@@ -5535,21 +5548,17 @@
       </c>
       <c r="C127" s="24" t="inlineStr">
         <is>
-          <t>No Bag</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>Cannot activate Move cards this round</t>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
         </is>
       </c>
       <c r="E127" s="26" t="n"/>
       <c r="F127" s="50" t="n"/>
-      <c r="G127" s="73" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G127" s="72" t="n"/>
       <c r="H127" s="71" t="n"/>
       <c r="I127" s="71" t="n"/>
       <c r="J127" s="71" t="n"/>
@@ -5563,12 +5572,12 @@
       </c>
       <c r="C128" s="23" t="inlineStr">
         <is>
-          <t>Point God</t>
+          <t>Great Conditioning</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Draw 1 card following each of your passes</t>
+          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
         </is>
       </c>
       <c r="E128" s="7" t="n"/>
@@ -5578,7 +5587,7 @@
       <c r="I128" s="71" t="n"/>
       <c r="J128" s="71" t="n"/>
     </row>
-    <row r="129" ht="56" customHeight="1" s="85">
+    <row r="129" ht="28" customHeight="1" s="85">
       <c r="A129" s="21" t="n"/>
       <c r="B129" s="22" t="inlineStr">
         <is>
@@ -5587,26 +5596,22 @@
       </c>
       <c r="C129" s="24" t="inlineStr">
         <is>
-          <t>Shooting Slump</t>
+          <t>Hot Hand</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>SHOT -20% this round</t>
+          <t>SHOT +25% if you scored last round.</t>
         </is>
       </c>
       <c r="E129" s="26" t="n"/>
       <c r="F129" s="50" t="n"/>
-      <c r="G129" s="73" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G129" s="72" t="n"/>
       <c r="H129" s="71" t="n"/>
       <c r="I129" s="71" t="n"/>
       <c r="J129" s="71" t="n"/>
     </row>
-    <row r="130" ht="56" customHeight="1" s="85">
+    <row r="130" ht="28" customHeight="1" s="85">
       <c r="A130" s="21" t="n"/>
       <c r="B130" s="22" t="inlineStr">
         <is>
@@ -5615,12 +5620,12 @@
       </c>
       <c r="C130" s="23" t="inlineStr">
         <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D130" s="38" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
         </is>
       </c>
       <c r="E130" s="7" t="n"/>
@@ -5630,7 +5635,7 @@
       <c r="I130" s="71" t="n"/>
       <c r="J130" s="71" t="n"/>
     </row>
-    <row r="131" ht="56" customHeight="1" s="85">
+    <row r="131" ht="28" customHeight="1" s="85">
       <c r="A131" s="21" t="n"/>
       <c r="B131" s="22" t="inlineStr">
         <is>
@@ -5639,22 +5644,26 @@
       </c>
       <c r="C131" s="24" t="inlineStr">
         <is>
-          <t>Sixth Man</t>
+          <t>No Bag</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>SHOT +60% on any six: cards in hand, Shot Clock, shot of the round, or score</t>
+          <t>Cannot activate Move cards this round</t>
         </is>
       </c>
       <c r="E131" s="26" t="n"/>
       <c r="F131" s="50" t="n"/>
-      <c r="G131" s="72" t="n"/>
+      <c r="G131" s="73" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H131" s="71" t="n"/>
       <c r="I131" s="71" t="n"/>
       <c r="J131" s="71" t="n"/>
     </row>
-    <row r="132" ht="56" customHeight="1" s="85">
+    <row r="132" ht="28" customHeight="1" s="85">
       <c r="A132" s="21" t="n"/>
       <c r="B132" s="22" t="inlineStr">
         <is>
@@ -5663,12 +5672,12 @@
       </c>
       <c r="C132" s="23" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Point God</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>SHOT +25% on all Three-Point Line Shots</t>
+          <t>Draw 1 card following each of your passes</t>
         </is>
       </c>
       <c r="E132" s="7" t="n"/>
@@ -5687,22 +5696,26 @@
       </c>
       <c r="C133" s="24" t="inlineStr">
         <is>
-          <t>Splash Cousin</t>
+          <t>Shooting Slump</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
+          <t>SHOT -20% this round</t>
         </is>
       </c>
       <c r="E133" s="26" t="n"/>
       <c r="F133" s="50" t="n"/>
-      <c r="G133" s="72" t="n"/>
+      <c r="G133" s="73" t="inlineStr">
+        <is>
+          <t>Bad card to draw</t>
+        </is>
+      </c>
       <c r="H133" s="71" t="n"/>
       <c r="I133" s="71" t="n"/>
       <c r="J133" s="71" t="n"/>
     </row>
-    <row r="134" ht="126" customHeight="1" s="85">
+    <row r="134" ht="56" customHeight="1" s="85">
       <c r="A134" s="21" t="n"/>
       <c r="B134" s="22" t="inlineStr">
         <is>
@@ -5711,12 +5724,12 @@
       </c>
       <c r="C134" s="23" t="inlineStr">
         <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D134" s="38" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
         </is>
       </c>
       <c r="E134" s="7" t="n"/>
@@ -5726,7 +5739,7 @@
       <c r="I134" s="71" t="n"/>
       <c r="J134" s="71" t="n"/>
     </row>
-    <row r="135" ht="70" customHeight="1" s="85">
+    <row r="135" ht="56" customHeight="1" s="85">
       <c r="A135" s="21" t="n"/>
       <c r="B135" s="22" t="inlineStr">
         <is>
@@ -5735,21 +5748,17 @@
       </c>
       <c r="C135" s="24" t="inlineStr">
         <is>
-          <t>Lethal Shooter</t>
+          <t>Sixth Man</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+          <t>SHOT +60% on any six: cards in hand, Shot Clock, shot of the round, or score</t>
         </is>
       </c>
       <c r="E135" s="26" t="n"/>
       <c r="F135" s="50" t="n"/>
-      <c r="G135" s="73" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G135" s="72" t="n"/>
       <c r="H135" s="71" t="n"/>
       <c r="I135" s="71" t="n"/>
       <c r="J135" s="71" t="n"/>
@@ -5763,12 +5772,12 @@
       </c>
       <c r="C136" s="23" t="inlineStr">
         <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D136" s="38" t="inlineStr">
-        <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>SHOT +25% on all Three-Point Line Shots</t>
         </is>
       </c>
       <c r="E136" s="7" t="n"/>
@@ -5778,31 +5787,31 @@
       <c r="I136" s="71" t="n"/>
       <c r="J136" s="71" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" ht="56" customHeight="1" s="85">
       <c r="A137" s="21" t="n"/>
       <c r="B137" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C137" s="23" t="inlineStr">
-        <is>
-          <t>Unselfish</t>
-        </is>
-      </c>
-      <c r="D137" s="38" t="inlineStr">
-        <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="n"/>
+      <c r="C137" s="24" t="inlineStr">
+        <is>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D137" s="25" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
+        </is>
+      </c>
+      <c r="E137" s="26" t="n"/>
       <c r="F137" s="50" t="n"/>
-      <c r="G137" s="70" t="n"/>
+      <c r="G137" s="72" t="n"/>
       <c r="H137" s="71" t="n"/>
       <c r="I137" s="71" t="n"/>
       <c r="J137" s="71" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" ht="126" customHeight="1" s="85">
       <c r="A138" s="21" t="n"/>
       <c r="B138" s="22" t="inlineStr">
         <is>
@@ -5811,12 +5820,12 @@
       </c>
       <c r="C138" s="23" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="D138" s="38" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+          <t>All Clamps on you have no effect on SHOT %</t>
         </is>
       </c>
       <c r="E138" s="7" t="n"/>
@@ -5826,35 +5835,35 @@
       <c r="I138" s="71" t="n"/>
       <c r="J138" s="71" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" ht="70" customHeight="1" s="85">
       <c r="A139" s="21" t="n"/>
       <c r="B139" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C139" s="23" t="inlineStr">
-        <is>
-          <t>Villainous Reputation</t>
-        </is>
-      </c>
-      <c r="D139" s="38" t="inlineStr">
-        <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="n"/>
+      <c r="C139" s="24" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D139" s="25" t="inlineStr">
+        <is>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+        </is>
+      </c>
+      <c r="E139" s="26" t="n"/>
       <c r="F139" s="50" t="n"/>
-      <c r="G139" s="70" t="inlineStr">
-        <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
+      <c r="G139" s="73" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
         </is>
       </c>
       <c r="H139" s="71" t="n"/>
       <c r="I139" s="71" t="n"/>
       <c r="J139" s="71" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" ht="56" customHeight="1" s="85">
       <c r="A140" s="21" t="n"/>
       <c r="B140" s="22" t="inlineStr">
         <is>
@@ -5863,26 +5872,22 @@
       </c>
       <c r="C140" s="23" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D140" s="38" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
         </is>
       </c>
       <c r="E140" s="7" t="n"/>
       <c r="F140" s="50" t="n"/>
-      <c r="G140" s="70" t="inlineStr">
-        <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
-        </is>
-      </c>
+      <c r="G140" s="70" t="n"/>
       <c r="H140" s="71" t="n"/>
       <c r="I140" s="71" t="n"/>
       <c r="J140" s="71" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" s="85">
       <c r="A141" s="21" t="n"/>
       <c r="B141" s="22" t="inlineStr">
         <is>
@@ -5891,12 +5896,12 @@
       </c>
       <c r="C141" s="23" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Unselfish</t>
         </is>
       </c>
       <c r="D141" s="38" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
         </is>
       </c>
       <c r="E141" s="7" t="n"/>
@@ -5906,229 +5911,337 @@
       <c r="I141" s="71" t="n"/>
       <c r="J141" s="71" t="n"/>
     </row>
-    <row r="142">
-      <c r="A142" s="27" t="n"/>
-      <c r="B142" s="28" t="inlineStr">
+    <row r="142" s="85">
+      <c r="A142" s="21" t="n"/>
+      <c r="B142" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C142" s="56" t="inlineStr">
+      <c r="C142" s="23" t="inlineStr">
+        <is>
+          <t>Dirty Player</t>
+        </is>
+      </c>
+      <c r="D142" s="38" t="inlineStr">
+        <is>
+          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="n"/>
+      <c r="F142" s="50" t="n"/>
+      <c r="G142" s="70" t="n"/>
+      <c r="H142" s="71" t="n"/>
+      <c r="I142" s="71" t="n"/>
+      <c r="J142" s="71" t="n"/>
+    </row>
+    <row r="143" s="85">
+      <c r="A143" s="21" t="n"/>
+      <c r="B143" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C143" s="23" t="inlineStr">
+        <is>
+          <t>Villainous Reputation</t>
+        </is>
+      </c>
+      <c r="D143" s="38" t="inlineStr">
+        <is>
+          <t>Discard 1 whenever any Whistle triggers</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="n"/>
+      <c r="F143" s="50" t="n"/>
+      <c r="G143" s="70" t="inlineStr">
+        <is>
+          <t>Discarded during play, it attaches to a random player — possibly you again</t>
+        </is>
+      </c>
+      <c r="H143" s="71" t="n"/>
+      <c r="I143" s="71" t="n"/>
+      <c r="J143" s="71" t="n"/>
+    </row>
+    <row r="144" s="85">
+      <c r="A144" s="21" t="n"/>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C144" s="23" t="inlineStr">
+        <is>
+          <t>Free Agent</t>
+        </is>
+      </c>
+      <c r="D144" s="38" t="inlineStr">
+        <is>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="n"/>
+      <c r="F144" s="50" t="n"/>
+      <c r="G144" s="70" t="inlineStr">
+        <is>
+          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
+        </is>
+      </c>
+      <c r="H144" s="71" t="n"/>
+      <c r="I144" s="71" t="n"/>
+      <c r="J144" s="71" t="n"/>
+    </row>
+    <row r="145" s="85">
+      <c r="A145" s="21" t="n"/>
+      <c r="B145" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C145" s="23" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D145" s="38" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="n"/>
+      <c r="F145" s="50" t="n"/>
+      <c r="G145" s="70" t="n"/>
+      <c r="H145" s="71" t="n"/>
+      <c r="I145" s="71" t="n"/>
+      <c r="J145" s="71" t="n"/>
+    </row>
+    <row r="146" s="85">
+      <c r="A146" s="27" t="n"/>
+      <c r="B146" s="28" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C146" s="56" t="inlineStr">
         <is>
           <t>Fundamentalist</t>
         </is>
       </c>
-      <c r="D142" s="63" t="inlineStr">
+      <c r="D146" s="63" t="inlineStr">
         <is>
           <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent</t>
         </is>
       </c>
-      <c r="E142" s="58" t="n"/>
-      <c r="F142" s="61" t="n"/>
-      <c r="G142" s="75" t="n"/>
-      <c r="H142" s="76" t="n"/>
-      <c r="I142" s="76" t="n"/>
-      <c r="J142" s="76" t="n"/>
-    </row>
-    <row r="143" s="85">
-      <c r="A143" s="27" t="n"/>
-      <c r="B143" s="28" t="inlineStr">
+      <c r="E146" s="58" t="n"/>
+      <c r="F146" s="61" t="n"/>
+      <c r="G146" s="75" t="n"/>
+      <c r="H146" s="76" t="n"/>
+      <c r="I146" s="76" t="n"/>
+      <c r="J146" s="76" t="n"/>
+    </row>
+    <row r="147" s="85">
+      <c r="A147" s="27" t="n"/>
+      <c r="B147" s="28" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C143" s="56" t="inlineStr">
+      <c r="C147" s="56" t="inlineStr">
         <is>
           <t>Moves At Own Pace</t>
         </is>
       </c>
-      <c r="D143" s="63" t="inlineStr">
+      <c r="D147" s="63" t="inlineStr">
         <is>
           <t>Cannot be called for Traveling or Shot Clock violations</t>
         </is>
       </c>
-      <c r="E143" s="58" t="n"/>
-      <c r="F143" s="61" t="n">
+      <c r="E147" s="58" t="n"/>
+      <c r="F147" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="G143" s="75" t="n"/>
-      <c r="H143" s="76" t="n"/>
-    </row>
-    <row r="144" ht="42" customHeight="1" s="85">
-      <c r="A144" s="52" t="inlineStr">
+      <c r="G147" s="75" t="n"/>
+      <c r="H147" s="76" t="n"/>
+    </row>
+    <row r="148" ht="42" customHeight="1" s="85">
+      <c r="A148" s="52" t="inlineStr">
         <is>
           <t>Varena</t>
         </is>
       </c>
-      <c r="B144" s="53">
-        <f>COUNTIF($B$145:$B$145,"Varena")</f>
+      <c r="B148" s="53">
+        <f>COUNTIF($B$149:$B$149,"Varena")</f>
         <v/>
       </c>
-      <c r="C144" s="54" t="n"/>
-      <c r="D144" s="54" t="n"/>
-      <c r="E144" s="54" t="n"/>
-      <c r="F144" s="55" t="n"/>
-      <c r="G144" s="66" t="n"/>
-      <c r="H144" s="67" t="n"/>
-      <c r="I144" s="67" t="n"/>
-      <c r="J144" s="67" t="n"/>
-    </row>
-    <row r="145" s="85">
-      <c r="A145" s="27" t="n"/>
-      <c r="B145" s="28" t="inlineStr">
+      <c r="C148" s="54" t="n"/>
+      <c r="D148" s="54" t="n"/>
+      <c r="E148" s="54" t="n"/>
+      <c r="F148" s="55" t="n"/>
+      <c r="G148" s="66" t="n"/>
+      <c r="H148" s="67" t="n"/>
+      <c r="I148" s="67" t="n"/>
+      <c r="J148" s="67" t="n"/>
+    </row>
+    <row r="149" s="85">
+      <c r="A149" s="27" t="n"/>
+      <c r="B149" s="28" t="inlineStr">
         <is>
           <t>Varena</t>
         </is>
       </c>
-      <c r="C145" s="56" t="inlineStr">
+      <c r="C149" s="56" t="inlineStr">
         <is>
           <t>Cardwood</t>
         </is>
       </c>
-      <c r="D145" s="63" t="inlineStr">
+      <c r="D149" s="63" t="inlineStr">
         <is>
           <t>Changes the court back to basic</t>
         </is>
       </c>
-      <c r="E145" s="58" t="n"/>
-      <c r="F145" s="61" t="n">
+      <c r="E149" s="58" t="n"/>
+      <c r="F149" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="G145" s="75" t="inlineStr">
+      <c r="G149" s="75" t="inlineStr">
         <is>
           <t>Also the floor every game opens on, before anybody plays a Varena over it</t>
         </is>
       </c>
-      <c r="H145" s="76" t="n"/>
-      <c r="I145" s="76" t="n"/>
-      <c r="J145" s="76" t="n"/>
+      <c r="H149" s="76" t="n"/>
+      <c r="I149" s="76" t="n"/>
+      <c r="J149" s="76" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="124">
+  <mergeCells count="128">
+    <mergeCell ref="G88:J88"/>
+    <mergeCell ref="G26:J26"/>
     <mergeCell ref="G55:J55"/>
+    <mergeCell ref="G35:J35"/>
     <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G129:J129"/>
+    <mergeCell ref="G109:J109"/>
     <mergeCell ref="G135:J135"/>
-    <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G76:J76"/>
+    <mergeCell ref="G25:J25"/>
     <mergeCell ref="G119:J119"/>
     <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G99:J99"/>
     <mergeCell ref="G46:J46"/>
+    <mergeCell ref="G60:J60"/>
     <mergeCell ref="G40:J40"/>
+    <mergeCell ref="G9:J9"/>
     <mergeCell ref="G111:J111"/>
+    <mergeCell ref="G131:J131"/>
+    <mergeCell ref="G140:J140"/>
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
-    <mergeCell ref="G96:J96"/>
+    <mergeCell ref="G59:J59"/>
+    <mergeCell ref="G115:J115"/>
+    <mergeCell ref="G130:J130"/>
+    <mergeCell ref="G11:J11"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G136:J136"/>
-    <mergeCell ref="G145:J145"/>
+    <mergeCell ref="G117:J117"/>
+    <mergeCell ref="G126:J126"/>
+    <mergeCell ref="G132:J132"/>
     <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G82:J82"/>
-    <mergeCell ref="G57:J57"/>
+    <mergeCell ref="G101:J101"/>
+    <mergeCell ref="G116:J116"/>
+    <mergeCell ref="G103:J103"/>
+    <mergeCell ref="G37:J37"/>
     <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G57:J57"/>
+    <mergeCell ref="G13:J13"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G78:J78"/>
+    <mergeCell ref="G118:J118"/>
+    <mergeCell ref="G87:J87"/>
     <mergeCell ref="G121:J121"/>
     <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
+    <mergeCell ref="G139:J139"/>
+    <mergeCell ref="G15:J15"/>
     <mergeCell ref="G108:J108"/>
+    <mergeCell ref="G80:J80"/>
     <mergeCell ref="G58:J58"/>
     <mergeCell ref="G114:J114"/>
+    <mergeCell ref="G95:J95"/>
+    <mergeCell ref="G89:J89"/>
     <mergeCell ref="G123:J123"/>
     <mergeCell ref="G110:J110"/>
+    <mergeCell ref="G79:J79"/>
+    <mergeCell ref="G64:J64"/>
+    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="G51:J51"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="G113:J113"/>
     <mergeCell ref="G91:J91"/>
     <mergeCell ref="G85:J85"/>
+    <mergeCell ref="G54:J54"/>
     <mergeCell ref="G100:J100"/>
-    <mergeCell ref="G94:J94"/>
+    <mergeCell ref="G63:J63"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G134:J134"/>
+    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G106:J106"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G149:J149"/>
+    <mergeCell ref="G56:J56"/>
     <mergeCell ref="G102:J102"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G105:J105"/>
+    <mergeCell ref="G43:J43"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
+    <mergeCell ref="G52:J52"/>
     <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G86:J86"/>
+    <mergeCell ref="G120:J120"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="G98:J98"/>
     <mergeCell ref="G67:J67"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="G42:J42"/>
     <mergeCell ref="G61:J61"/>
+    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G70:J70"/>
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G97:J97"/>
+    <mergeCell ref="G17:J17"/>
     <mergeCell ref="G125:J125"/>
+    <mergeCell ref="G38:J38"/>
     <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G38:J38"/>
     <mergeCell ref="G112:J112"/>
-    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G28:J28"/>
     <mergeCell ref="G62:J62"/>
+    <mergeCell ref="G6:J6"/>
     <mergeCell ref="G127:J127"/>
+    <mergeCell ref="G69:J69"/>
     <mergeCell ref="G49:J49"/>
+    <mergeCell ref="G83:J83"/>
     <mergeCell ref="G24:J24"/>
     <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G124:J124"/>
     <mergeCell ref="G104:J104"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G133:J133"/>
     <mergeCell ref="G65:J65"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="G129:J129"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G76:J76"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G99:J99"/>
-    <mergeCell ref="G60:J60"/>
-    <mergeCell ref="G131:J131"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G59:J59"/>
-    <mergeCell ref="G115:J115"/>
-    <mergeCell ref="G130:J130"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G117:J117"/>
-    <mergeCell ref="G126:J126"/>
-    <mergeCell ref="G132:J132"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G122:J122"/>
-    <mergeCell ref="G101:J101"/>
-    <mergeCell ref="G116:J116"/>
-    <mergeCell ref="G103:J103"/>
-    <mergeCell ref="G37:J37"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G78:J78"/>
-    <mergeCell ref="G118:J118"/>
-    <mergeCell ref="G87:J87"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G80:J80"/>
-    <mergeCell ref="G95:J95"/>
-    <mergeCell ref="G64:J64"/>
-    <mergeCell ref="G79:J79"/>
-    <mergeCell ref="G73:J73"/>
-    <mergeCell ref="G51:J51"/>
-    <mergeCell ref="G54:J54"/>
-    <mergeCell ref="G63:J63"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="G50:J50"/>
-    <mergeCell ref="G106:J106"/>
-    <mergeCell ref="G56:J56"/>
-    <mergeCell ref="G105:J105"/>
-    <mergeCell ref="G43:J43"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="G120:J120"/>
-    <mergeCell ref="G98:J98"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G107:J107"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G69:J69"/>
-    <mergeCell ref="G83:J83"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G45:J45"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -3602,7 +3602,7 @@
           <t>SHOT -10%</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="G59" s="83" t="inlineStr">
         <is>
-          <t>[NOT IN THE GAME YET]</t>
+          <t>A Kick-Out to them is not shot — it becomes a normal pass</t>
         </is>
       </c>
       <c r="H59" s="76" t="n"/>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G60" s="83" t="inlineStr">
         <is>
-          <t>[NOT IN THE GAME YET]</t>
+          <t>Checked any time during the possession</t>
         </is>
       </c>
       <c r="H60" s="76" t="n"/>
@@ -6114,133 +6114,133 @@
     </row>
   </sheetData>
   <mergeCells count="128">
-    <mergeCell ref="G88:J88"/>
-    <mergeCell ref="G26:J26"/>
     <mergeCell ref="G55:J55"/>
-    <mergeCell ref="G35:J35"/>
     <mergeCell ref="G4:J4"/>
-    <mergeCell ref="G129:J129"/>
+    <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
-    <mergeCell ref="G135:J135"/>
     <mergeCell ref="G47:J47"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G76:J76"/>
-    <mergeCell ref="G25:J25"/>
     <mergeCell ref="G119:J119"/>
     <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G99:J99"/>
     <mergeCell ref="G46:J46"/>
-    <mergeCell ref="G60:J60"/>
     <mergeCell ref="G40:J40"/>
-    <mergeCell ref="G9:J9"/>
     <mergeCell ref="G111:J111"/>
-    <mergeCell ref="G131:J131"/>
-    <mergeCell ref="G140:J140"/>
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
-    <mergeCell ref="G59:J59"/>
-    <mergeCell ref="G115:J115"/>
-    <mergeCell ref="G130:J130"/>
-    <mergeCell ref="G11:J11"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G136:J136"/>
-    <mergeCell ref="G117:J117"/>
-    <mergeCell ref="G126:J126"/>
-    <mergeCell ref="G132:J132"/>
     <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G82:J82"/>
-    <mergeCell ref="G101:J101"/>
-    <mergeCell ref="G116:J116"/>
-    <mergeCell ref="G103:J103"/>
-    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="G57:J57"/>
     <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G57:J57"/>
-    <mergeCell ref="G13:J13"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
-    <mergeCell ref="G78:J78"/>
-    <mergeCell ref="G118:J118"/>
-    <mergeCell ref="G87:J87"/>
     <mergeCell ref="G121:J121"/>
     <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="G139:J139"/>
-    <mergeCell ref="G15:J15"/>
     <mergeCell ref="G108:J108"/>
-    <mergeCell ref="G80:J80"/>
     <mergeCell ref="G58:J58"/>
     <mergeCell ref="G114:J114"/>
-    <mergeCell ref="G95:J95"/>
-    <mergeCell ref="G89:J89"/>
     <mergeCell ref="G123:J123"/>
     <mergeCell ref="G110:J110"/>
-    <mergeCell ref="G79:J79"/>
-    <mergeCell ref="G64:J64"/>
-    <mergeCell ref="G73:J73"/>
-    <mergeCell ref="G51:J51"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="G113:J113"/>
     <mergeCell ref="G91:J91"/>
     <mergeCell ref="G85:J85"/>
+    <mergeCell ref="G100:J100"/>
+    <mergeCell ref="G75:J75"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G149:J149"/>
+    <mergeCell ref="G102:J102"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G77:J77"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G86:J86"/>
+    <mergeCell ref="G67:J67"/>
+    <mergeCell ref="G61:J61"/>
+    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G125:J125"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G112:J112"/>
+    <mergeCell ref="G62:J62"/>
+    <mergeCell ref="G127:J127"/>
+    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G104:J104"/>
+    <mergeCell ref="G65:J65"/>
+    <mergeCell ref="G88:J88"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="G129:J129"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G76:J76"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G99:J99"/>
+    <mergeCell ref="G60:J60"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G131:J131"/>
+    <mergeCell ref="G140:J140"/>
+    <mergeCell ref="G59:J59"/>
+    <mergeCell ref="G115:J115"/>
+    <mergeCell ref="G130:J130"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G117:J117"/>
+    <mergeCell ref="G126:J126"/>
+    <mergeCell ref="G132:J132"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G122:J122"/>
+    <mergeCell ref="G101:J101"/>
+    <mergeCell ref="G116:J116"/>
+    <mergeCell ref="G103:J103"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G78:J78"/>
+    <mergeCell ref="G118:J118"/>
+    <mergeCell ref="G87:J87"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G80:J80"/>
+    <mergeCell ref="G95:J95"/>
+    <mergeCell ref="G89:J89"/>
+    <mergeCell ref="G64:J64"/>
+    <mergeCell ref="G79:J79"/>
+    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="G51:J51"/>
     <mergeCell ref="G54:J54"/>
-    <mergeCell ref="G100:J100"/>
     <mergeCell ref="G63:J63"/>
     <mergeCell ref="G41:J41"/>
     <mergeCell ref="G134:J134"/>
     <mergeCell ref="G50:J50"/>
     <mergeCell ref="G106:J106"/>
-    <mergeCell ref="G75:J75"/>
-    <mergeCell ref="G44:J44"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G84:J84"/>
-    <mergeCell ref="G149:J149"/>
     <mergeCell ref="G56:J56"/>
-    <mergeCell ref="G102:J102"/>
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="G77:J77"/>
     <mergeCell ref="G52:J52"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G120:J120"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
-    <mergeCell ref="G67:J67"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G61:J61"/>
     <mergeCell ref="G107:J107"/>
-    <mergeCell ref="G70:J70"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="G23:J23"/>
     <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G125:J125"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G112:J112"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G62:J62"/>
     <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G127:J127"/>
     <mergeCell ref="G69:J69"/>
-    <mergeCell ref="G49:J49"/>
     <mergeCell ref="G83:J83"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G33:J33"/>
     <mergeCell ref="G124:J124"/>
-    <mergeCell ref="G104:J104"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="G133:J133"/>
-    <mergeCell ref="G65:J65"/>
     <mergeCell ref="G45:J45"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2089,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="B5" s="53">
-        <f>COUNTIF($B$6:$B$147,"Pass")</f>
+        <f>COUNTIF($B$6:$B$148,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="54" t="n"/>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="B21" s="53">
-        <f>COUNTIF($B$22:$B$147,"Move")+COUNTIF($B$22:$B$147,"Special Move")</f>
+        <f>COUNTIF($B$22:$B$148,"Move")+COUNTIF($B$22:$B$148,"Special Move")</f>
         <v/>
       </c>
       <c r="C21" s="54" t="n"/>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="B35" s="53">
-        <f>COUNTIF($B$36:$B$147,"Special Move")</f>
+        <f>COUNTIF($B$36:$B$148,"Special Move")</f>
         <v/>
       </c>
       <c r="C35" s="54" t="n"/>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="B53" s="53">
-        <f>COUNTIF($B$54:$B$147,"Clamp")</f>
+        <f>COUNTIF($B$54:$B$148,"Clamp")</f>
         <v/>
       </c>
       <c r="C53" s="54" t="n"/>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="B62" s="53">
-        <f>COUNTIF($B$63:$B$147,"Whistle")</f>
+        <f>COUNTIF($B$63:$B$148,"Whistle")</f>
         <v/>
       </c>
       <c r="C62" s="54" t="n"/>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="B114" s="53">
-        <f>COUNTIF($B$115:$B$147,"Injury")</f>
+        <f>COUNTIF($B$115:$B$148,"Injury")</f>
         <v/>
       </c>
       <c r="C114" s="54" t="n"/>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="B116" s="53">
-        <f>COUNTIF($B$117:$B$147,"Devastating Injury")</f>
+        <f>COUNTIF($B$117:$B$148,"Devastating Injury")</f>
         <v/>
       </c>
       <c r="C116" s="54" t="n"/>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="B118" s="53">
-        <f>COUNTIF($B$119:$B$147,"Intangible")</f>
+        <f>COUNTIF($B$119:$B$148,"Intangible")</f>
         <v/>
       </c>
       <c r="C118" s="54" t="n"/>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>Additional SHOT +10% on all received passes</t>
+          <t>SHOT +25% on received passes, if shooting is your first action</t>
         </is>
       </c>
       <c r="E120" s="26" t="n"/>
@@ -5472,19 +5472,15 @@
       </c>
       <c r="C124" s="23" t="inlineStr">
         <is>
-          <t>Fox-Like First Step</t>
+          <t>Southpaw Shooter</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>All Move cards that reduce SHOT increase it by that amount instead.</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>Your Move cards are unaffected by opponents</t>
-        </is>
-      </c>
+          <t>SHOT gains and losses are reversed</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="n"/>
       <c r="F124" s="51" t="n"/>
       <c r="G124" s="70" t="n"/>
       <c r="H124" s="71" t="n"/>
@@ -5577,12 +5573,16 @@
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Immediately discard all Injury Game Breaks you draw and draw a new card for each</t>
+          <t>Immediately discard all Injuries you draw and draw a new card for each</t>
         </is>
       </c>
       <c r="E128" s="7" t="n"/>
       <c r="F128" s="50" t="n"/>
-      <c r="G128" s="70" t="n"/>
+      <c r="G128" s="70" t="inlineStr">
+        <is>
+          <t>Also discards any Injuries you already have (not on the card)</t>
+        </is>
+      </c>
       <c r="H128" s="71" t="n"/>
       <c r="I128" s="71" t="n"/>
       <c r="J128" s="71" t="n"/>
@@ -5630,7 +5630,11 @@
       </c>
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="50" t="n"/>
-      <c r="G130" s="70" t="n"/>
+      <c r="G130" s="70" t="inlineStr">
+        <is>
+          <t>Variaball effects still lower SHOT: the ball is altered, not the player (not on the card)</t>
+        </is>
+      </c>
       <c r="H130" s="71" t="n"/>
       <c r="I130" s="71" t="n"/>
       <c r="J130" s="71" t="n"/>
@@ -5644,21 +5648,17 @@
       </c>
       <c r="C131" s="24" t="inlineStr">
         <is>
-          <t>No Bag</t>
+          <t>Park Shark</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>Cannot activate Move cards this round</t>
+          <t>SHOT +25% on every shot. Cannot use Move or Special Move cards, or shoot threes</t>
         </is>
       </c>
       <c r="E131" s="26" t="n"/>
       <c r="F131" s="50" t="n"/>
-      <c r="G131" s="73" t="inlineStr">
-        <is>
-          <t>Bad card to draw</t>
-        </is>
-      </c>
+      <c r="G131" s="73" t="n"/>
       <c r="H131" s="71" t="n"/>
       <c r="I131" s="71" t="n"/>
       <c r="J131" s="71" t="n"/>
@@ -5696,19 +5696,19 @@
       </c>
       <c r="C133" s="24" t="inlineStr">
         <is>
-          <t>Shooting Slump</t>
+          <t>Shot Creator</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>SHOT -20% this round</t>
+          <t>Draw 1 additional card after every draw effect</t>
         </is>
       </c>
       <c r="E133" s="26" t="n"/>
       <c r="F133" s="50" t="n"/>
       <c r="G133" s="73" t="inlineStr">
         <is>
-          <t>Bad card to draw</t>
+          <t>Triggers once per act of drawing: a Draw 2 still gives only 1 extra</t>
         </is>
       </c>
       <c r="H133" s="71" t="n"/>
@@ -5724,17 +5724,21 @@
       </c>
       <c r="C134" s="23" t="inlineStr">
         <is>
-          <t>Shot Creator</t>
+          <t>Sixth Man</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Draw 1 additional card after every draw effect</t>
+          <t>SHOT = 60% on any six: cards in hand, Shot Clock, shot of the round, or score</t>
         </is>
       </c>
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="50" t="n"/>
-      <c r="G134" s="70" t="n"/>
+      <c r="G134" s="70" t="inlineStr">
+        <is>
+          <t>A second SHOOT (60%) button beside Shoot, shown only on a six. Ignore it when SHOT is already higher</t>
+        </is>
+      </c>
       <c r="H134" s="71" t="n"/>
       <c r="I134" s="71" t="n"/>
       <c r="J134" s="71" t="n"/>
@@ -5748,12 +5752,12 @@
       </c>
       <c r="C135" s="24" t="inlineStr">
         <is>
-          <t>Sixth Man</t>
+          <t>Sniper</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>SHOT +60% on any six: cards in hand, Shot Clock, shot of the round, or score</t>
+          <t>SHOT +25% on all Three-Point Line Shots</t>
         </is>
       </c>
       <c r="E135" s="26" t="n"/>
@@ -5772,12 +5776,12 @@
       </c>
       <c r="C136" s="23" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Splash Cousin</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>SHOT +25% on all Three-Point Line Shots</t>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
         </is>
       </c>
       <c r="E136" s="7" t="n"/>
@@ -5796,12 +5800,12 @@
       </c>
       <c r="C137" s="24" t="inlineStr">
         <is>
-          <t>Splash Cousin</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
+          <t>All Clamps on you have no effect on SHOT %</t>
         </is>
       </c>
       <c r="E137" s="26" t="n"/>
@@ -5820,17 +5824,21 @@
       </c>
       <c r="C138" s="23" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Lethal Shooter</t>
         </is>
       </c>
       <c r="D138" s="38" t="inlineStr">
         <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
         </is>
       </c>
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="50" t="n"/>
-      <c r="G138" s="70" t="n"/>
+      <c r="G138" s="70" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
       <c r="H138" s="71" t="n"/>
       <c r="I138" s="71" t="n"/>
       <c r="J138" s="71" t="n"/>
@@ -5844,21 +5852,17 @@
       </c>
       <c r="C139" s="24" t="inlineStr">
         <is>
-          <t>Lethal Shooter</t>
+          <t>Ball Pounder</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+          <t>Every Dribble draws 1 card but gives SHOT -10% and Shot Clock - 01</t>
         </is>
       </c>
       <c r="E139" s="26" t="n"/>
       <c r="F139" s="50" t="n"/>
-      <c r="G139" s="73" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G139" s="73" t="n"/>
       <c r="H139" s="71" t="n"/>
       <c r="I139" s="71" t="n"/>
       <c r="J139" s="71" t="n"/>
@@ -5872,12 +5876,12 @@
       </c>
       <c r="C140" s="23" t="inlineStr">
         <is>
-          <t>Ball Pounder</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D140" s="38" t="inlineStr">
         <is>
-          <t>All Dribble cards you play draw an additional card but lower SHOT by an additional 10%</t>
+          <t>When sending Clamps, the clamped player discards 1 for each of your Clamps if they have any Injuries. Discard 1 whenever a Whistle triggers</t>
         </is>
       </c>
       <c r="E140" s="7" t="n"/>
@@ -5896,17 +5900,21 @@
       </c>
       <c r="C141" s="23" t="inlineStr">
         <is>
-          <t>Unselfish</t>
+          <t>Free Agent</t>
         </is>
       </c>
       <c r="D141" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card and increase next SHOT +5% whenever you positively affect another player</t>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
       <c r="E141" s="7" t="n"/>
       <c r="F141" s="50" t="n"/>
-      <c r="G141" s="70" t="n"/>
+      <c r="G141" s="70" t="inlineStr">
+        <is>
+          <t>Low priority to bring back. The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
+        </is>
+      </c>
       <c r="H141" s="71" t="n"/>
       <c r="I141" s="71" t="n"/>
       <c r="J141" s="71" t="n"/>
@@ -5920,12 +5928,12 @@
       </c>
       <c r="C142" s="23" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Franchise Player</t>
         </is>
       </c>
       <c r="D142" s="38" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 if they have any Injuries</t>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
         </is>
       </c>
       <c r="E142" s="7" t="n"/>
@@ -5944,19 +5952,19 @@
       </c>
       <c r="C143" s="23" t="inlineStr">
         <is>
-          <t>Villainous Reputation</t>
+          <t>Fundamentalist</t>
         </is>
       </c>
       <c r="D143" s="38" t="inlineStr">
         <is>
-          <t>Discard 1 whenever any Whistle triggers</t>
+          <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent. Discards the current ball</t>
         </is>
       </c>
       <c r="E143" s="7" t="n"/>
       <c r="F143" s="50" t="n"/>
       <c r="G143" s="70" t="inlineStr">
         <is>
-          <t>Discarded during play, it attaches to a random player — possibly you again</t>
+          <t>The ball is discarded once, on activation</t>
         </is>
       </c>
       <c r="H143" s="71" t="n"/>
@@ -5972,21 +5980,19 @@
       </c>
       <c r="C144" s="23" t="inlineStr">
         <is>
-          <t>Free Agent</t>
+          <t>Moves At Own Pace</t>
         </is>
       </c>
       <c r="D144" s="38" t="inlineStr">
         <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>Cannot be called for Traveling or Shot Clock violations</t>
         </is>
       </c>
       <c r="E144" s="7" t="n"/>
-      <c r="F144" s="50" t="n"/>
-      <c r="G144" s="70" t="inlineStr">
-        <is>
-          <t>The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
-        </is>
-      </c>
+      <c r="F144" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="70" t="n"/>
       <c r="H144" s="71" t="n"/>
       <c r="I144" s="71" t="n"/>
       <c r="J144" s="71" t="n"/>
@@ -6000,12 +6006,12 @@
       </c>
       <c r="C145" s="23" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Equalizer</t>
         </is>
       </c>
       <c r="D145" s="38" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Any 'SHOT =' shot you take becomes 100%</t>
         </is>
       </c>
       <c r="E145" s="7" t="n"/>
@@ -6024,17 +6030,21 @@
       </c>
       <c r="C146" s="56" t="inlineStr">
         <is>
-          <t>Fundamentalist</t>
+          <t>Varsitile</t>
         </is>
       </c>
       <c r="D146" s="63" t="inlineStr">
         <is>
-          <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent</t>
+          <t>You can play more than 1 Varena and Variaball per turn. Once per possession, you can exchange the Varena and/or ball for one in the Discards</t>
         </is>
       </c>
       <c r="E146" s="58" t="n"/>
       <c r="F146" s="61" t="n"/>
-      <c r="G146" s="75" t="n"/>
+      <c r="G146" s="75" t="inlineStr">
+        <is>
+          <t>One use can exchange both. Not in the deck until Variaballs are</t>
+        </is>
+      </c>
       <c r="H146" s="76" t="n"/>
       <c r="I146" s="76" t="n"/>
       <c r="J146" s="76" t="n"/>
@@ -6048,79 +6058,108 @@
       </c>
       <c r="C147" s="56" t="inlineStr">
         <is>
-          <t>Moves At Own Pace</t>
+          <t>Brawl Handler</t>
         </is>
       </c>
       <c r="D147" s="63" t="inlineStr">
         <is>
-          <t>Cannot be called for Traveling or Shot Clock violations</t>
+          <t>Remove all your Clamps when you change the ball</t>
         </is>
       </c>
       <c r="E147" s="58" t="n"/>
-      <c r="F147" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" s="75" t="n"/>
+      <c r="F147" s="61" t="n"/>
+      <c r="G147" s="75" t="inlineStr">
+        <is>
+          <t>Not in the deck until Variaballs are</t>
+        </is>
+      </c>
       <c r="H147" s="76" t="n"/>
     </row>
-    <row r="148" ht="42" customHeight="1" s="85">
-      <c r="A148" s="52" t="inlineStr">
+    <row r="148" s="85">
+      <c r="A148" s="27" t="n"/>
+      <c r="B148" s="28" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C148" s="56" t="inlineStr">
+        <is>
+          <t>Baller</t>
+        </is>
+      </c>
+      <c r="D148" s="63" t="inlineStr">
+        <is>
+          <t>Draw 1 card each time you change the ball</t>
+        </is>
+      </c>
+      <c r="E148" s="58" t="n"/>
+      <c r="F148" s="61" t="n"/>
+      <c r="G148" s="75" t="inlineStr">
+        <is>
+          <t>Not in the deck until Variaballs are</t>
+        </is>
+      </c>
+      <c r="H148" s="76" t="n"/>
+    </row>
+    <row r="149" ht="42" customHeight="1" s="85">
+      <c r="A149" s="52" t="inlineStr">
         <is>
           <t>Varena</t>
         </is>
       </c>
-      <c r="B148" s="53">
-        <f>COUNTIF($B$149:$B$149,"Varena")</f>
+      <c r="B149" s="53">
+        <f>COUNTIF($B$150:$B$150,"Varena")</f>
         <v/>
       </c>
-      <c r="C148" s="54" t="n"/>
-      <c r="D148" s="54" t="n"/>
-      <c r="E148" s="54" t="n"/>
-      <c r="F148" s="55" t="n"/>
-      <c r="G148" s="66" t="n"/>
-      <c r="H148" s="67" t="n"/>
-      <c r="I148" s="67" t="n"/>
-      <c r="J148" s="67" t="n"/>
-    </row>
-    <row r="149" s="85">
-      <c r="A149" s="27" t="n"/>
-      <c r="B149" s="28" t="inlineStr">
+      <c r="C149" s="54" t="n"/>
+      <c r="D149" s="54" t="n"/>
+      <c r="E149" s="54" t="n"/>
+      <c r="F149" s="55" t="n"/>
+      <c r="G149" s="66" t="n"/>
+      <c r="H149" s="67" t="n"/>
+      <c r="I149" s="67" t="n"/>
+      <c r="J149" s="67" t="n"/>
+    </row>
+    <row r="150" s="85">
+      <c r="A150" s="27" t="n"/>
+      <c r="B150" s="28" t="inlineStr">
         <is>
           <t>Varena</t>
         </is>
       </c>
-      <c r="C149" s="56" t="inlineStr">
+      <c r="C150" s="56" t="inlineStr">
         <is>
           <t>Cardwood</t>
         </is>
       </c>
-      <c r="D149" s="63" t="inlineStr">
+      <c r="D150" s="63" t="inlineStr">
         <is>
           <t>Changes the court back to basic</t>
         </is>
       </c>
-      <c r="E149" s="58" t="n"/>
-      <c r="F149" s="61" t="n">
+      <c r="E150" s="58" t="n"/>
+      <c r="F150" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="G149" s="75" t="inlineStr">
+      <c r="G150" s="75" t="inlineStr">
         <is>
           <t>Also the floor every game opens on, before anybody plays a Varena over it</t>
         </is>
       </c>
-      <c r="H149" s="76" t="n"/>
-      <c r="I149" s="76" t="n"/>
-      <c r="J149" s="76" t="n"/>
+      <c r="H150" s="76" t="n"/>
+      <c r="I150" s="76" t="n"/>
+      <c r="J150" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="128">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G109:J109"/>
     <mergeCell ref="G135:J135"/>
-    <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G32:J32"/>
     <mergeCell ref="G119:J119"/>
-    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G150:J150"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
@@ -6131,13 +6170,13 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G82:J82"/>
     <mergeCell ref="G57:J57"/>
-    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
+    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G34:J34"/>
     <mergeCell ref="G121:J121"/>
-    <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="G139:J139"/>
@@ -6155,7 +6194,6 @@
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="G84:J84"/>
-    <mergeCell ref="G149:J149"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
@@ -6166,9 +6204,9 @@
     <mergeCell ref="G70:J70"/>
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G112:J112"/>
     <mergeCell ref="G62:J62"/>
     <mergeCell ref="G127:J127"/>
@@ -6188,16 +6226,17 @@
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G131:J131"/>
+    <mergeCell ref="G124:J124"/>
     <mergeCell ref="G140:J140"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G130:J130"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
+    <mergeCell ref="G39:J39"/>
     <mergeCell ref="G126:J126"/>
+    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G132:J132"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G101:J101"/>
     <mergeCell ref="G116:J116"/>
     <mergeCell ref="G103:J103"/>
@@ -6207,6 +6246,7 @@
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
     <mergeCell ref="G87:J87"/>
+    <mergeCell ref="G133:J133"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G80:J80"/>
     <mergeCell ref="G95:J95"/>
@@ -6226,9 +6266,9 @@
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
-    <mergeCell ref="G120:J120"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="G98:J98"/>
+    <mergeCell ref="G120:J120"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
     <mergeCell ref="G107:J107"/>
@@ -6238,9 +6278,7 @@
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G83:J83"/>
-    <mergeCell ref="G124:J124"/>
     <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G133:J133"/>
     <mergeCell ref="G45:J45"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2206,7 +2206,6 @@
         <v/>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="85">
       <c r="A4" s="81" t="inlineStr">
         <is>
@@ -2672,10 +2671,14 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>SHOT +20%. Pass to player of choice. If played as first action, draw 2 cards</t>
-        </is>
-      </c>
-      <c r="E20" s="30" t="n"/>
+          <t>SHOT +20%. Pass to player of choice</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>If played as first action, draw 2 cards</t>
+        </is>
+      </c>
       <c r="F20" s="35" t="n">
         <v>5</v>
       </c>
@@ -2945,10 +2948,14 @@
       </c>
       <c r="D30" s="41" t="inlineStr">
         <is>
-          <t>SHOT + 10%. If being Clamped, discard all Clamps and gain additional SHOT +20% for each</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="n"/>
+          <t>SHOT + 10%</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>If being Clamped, discard all Clamps and gain additional SHOT +20% for each</t>
+        </is>
+      </c>
       <c r="F30" s="33" t="n">
         <v>5</v>
       </c>
@@ -2975,10 +2982,14 @@
       </c>
       <c r="D31" s="41" t="inlineStr">
         <is>
-          <t>Draw 1 Card. SHOT +20%. If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
-        </is>
-      </c>
-      <c r="E31" s="26" t="n"/>
+          <t>Draw 1 Card. SHOT +20%</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
+        </is>
+      </c>
       <c r="F31" s="33" t="n">
         <v>5</v>
       </c>
@@ -3401,12 +3412,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>SHOT +20%. SHOT = 100% if SHOT &gt;= 75%</t>
+          <t>SHOT +20%</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball</t>
+          <t>Shoot the ball. SHOT = 100% if SHOT &gt;= 75%</t>
         </is>
       </c>
       <c r="F45" s="32" t="n">
@@ -3524,7 +3535,12 @@
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>SHOT +20%. Shoot the ball. Another +10% straight off your own board</t>
+          <t>SHOT +20%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Shoot the ball. Another +10% straight off your own board</t>
         </is>
       </c>
       <c r="F49" s="0" t="n">
@@ -3549,7 +3565,12 @@
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
-          <t>Clean look only — no Clamps on you and nothing has gone off this possession. SHOT +30%. Shoot the ball</t>
+          <t>Clean look only — no Clamps on you and nothing has gone off this possession. SHOT +30%</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Shoot the ball</t>
         </is>
       </c>
       <c r="F50" s="0" t="n">
@@ -3574,7 +3595,12 @@
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>SHOT +15% at 50% or better, −15% under it. Shoot the ball</t>
+          <t>SHOT +15% at 50% or better, −15% under it</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Shoot the ball</t>
         </is>
       </c>
       <c r="F51" s="0" t="n">
@@ -6154,12 +6180,12 @@
   <mergeCells count="128">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
-    <mergeCell ref="G135:J135"/>
     <mergeCell ref="G47:J47"/>
-    <mergeCell ref="G32:J32"/>
     <mergeCell ref="G119:J119"/>
     <mergeCell ref="G150:J150"/>
+    <mergeCell ref="G32:J32"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
@@ -6170,13 +6196,13 @@
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="G82:J82"/>
     <mergeCell ref="G57:J57"/>
+    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
-    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G121:J121"/>
     <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G121:J121"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="G139:J139"/>
@@ -6204,9 +6230,9 @@
     <mergeCell ref="G70:J70"/>
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G112:J112"/>
     <mergeCell ref="G62:J62"/>
     <mergeCell ref="G127:J127"/>
@@ -6226,17 +6252,16 @@
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="G131:J131"/>
-    <mergeCell ref="G124:J124"/>
     <mergeCell ref="G140:J140"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G130:J130"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
+    <mergeCell ref="G126:J126"/>
     <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G126:J126"/>
+    <mergeCell ref="G132:J132"/>
     <mergeCell ref="G122:J122"/>
-    <mergeCell ref="G132:J132"/>
     <mergeCell ref="G101:J101"/>
     <mergeCell ref="G116:J116"/>
     <mergeCell ref="G103:J103"/>
@@ -6246,7 +6271,6 @@
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
     <mergeCell ref="G87:J87"/>
-    <mergeCell ref="G133:J133"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G80:J80"/>
     <mergeCell ref="G95:J95"/>
@@ -6267,8 +6291,8 @@
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="G27:J27"/>
+    <mergeCell ref="G120:J120"/>
     <mergeCell ref="G98:J98"/>
-    <mergeCell ref="G120:J120"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
     <mergeCell ref="G107:J107"/>
@@ -6278,7 +6302,9 @@
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G83:J83"/>
+    <mergeCell ref="G124:J124"/>
     <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G133:J133"/>
     <mergeCell ref="G45:J45"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2089,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J150"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2170,42 +2170,43 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$144,"Pass")</f>
+        <f>COUNTIF($B$5:$B$146,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$144,"Move")+COUNTIF($B$5:$B$144,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$146,"Move")+COUNTIF($B$5:$B$146,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$144,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$146,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$144,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$146,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$144,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$146,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$144,"Injury")</f>
+        <f>COUNTIF($B$5:$B$146,"Injury")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$144,"Devastating Injury")</f>
+        <f>COUNTIF($B$5:$B$146,"Devastating Injury")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$144,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$146,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="87">
-        <f>SUM(B2:E2)+COUNTIF($B$5:$B$144,"Game Break")+SUM(G2:I2)</f>
+        <f>SUM(B2:E2)+COUNTIF($B$5:$B$146,"Game Break")+SUM(G2:I2)</f>
         <v/>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="85">
       <c r="A4" s="81" t="inlineStr">
         <is>
@@ -2249,7 +2250,7 @@
         </is>
       </c>
       <c r="B5" s="53">
-        <f>COUNTIF($B$6:$B$148,"Pass")</f>
+        <f>COUNTIF($B$6:$B$150,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="54" t="n"/>
@@ -2694,7 +2695,7 @@
         </is>
       </c>
       <c r="B21" s="53">
-        <f>COUNTIF($B$22:$B$148,"Move")+COUNTIF($B$22:$B$148,"Special Move")</f>
+        <f>COUNTIF($B$22:$B$150,"Move")+COUNTIF($B$22:$B$150,"Special Move")</f>
         <v/>
       </c>
       <c r="C21" s="54" t="n"/>
@@ -3110,7 +3111,7 @@
         </is>
       </c>
       <c r="B35" s="53">
-        <f>COUNTIF($B$36:$B$148,"Special Move")</f>
+        <f>COUNTIF($B$36:$B$150,"Special Move")</f>
         <v/>
       </c>
       <c r="C35" s="54" t="n"/>
@@ -3538,7 +3539,7 @@
           <t>SHOT +20%</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>Shoot the ball. Another +10% straight off your own board</t>
         </is>
@@ -3568,7 +3569,7 @@
           <t>Clean look only — no Clamps on you and nothing has gone off this possession. SHOT +30%</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
@@ -3598,7 +3599,7 @@
           <t>SHOT +15% at 50% or better, −15% under it</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>Shoot the ball</t>
         </is>
@@ -3645,7 +3646,7 @@
         </is>
       </c>
       <c r="B53" s="53">
-        <f>COUNTIF($B$54:$B$148,"Clamp")</f>
+        <f>COUNTIF($B$54:$B$150,"Clamp")</f>
         <v/>
       </c>
       <c r="C53" s="54" t="n"/>
@@ -3900,7 +3901,7 @@
         </is>
       </c>
       <c r="B62" s="53">
-        <f>COUNTIF($B$63:$B$148,"Whistle")</f>
+        <f>COUNTIF($B$63:$B$150,"Whistle")</f>
         <v/>
       </c>
       <c r="C62" s="54" t="n"/>
@@ -4431,79 +4432,79 @@
       <c r="J82" s="76" t="n"/>
     </row>
     <row r="83" ht="28" customHeight="1" s="85">
-      <c r="A83" s="52" t="inlineStr">
+      <c r="A83" s="27" t="n"/>
+      <c r="B83" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C83" s="29" t="inlineStr">
+        <is>
+          <t>Tile Tampering</t>
+        </is>
+      </c>
+      <c r="D83" s="30" t="inlineStr">
+        <is>
+          <t>Varena Played: Cancel card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E83" s="60" t="n"/>
+      <c r="F83" s="61" t="n"/>
+      <c r="G83" s="78" t="inlineStr">
+        <is>
+          <t>The Varena's player inbounds (side-out)</t>
+        </is>
+      </c>
+      <c r="H83" s="76" t="n"/>
+      <c r="I83" s="76" t="n"/>
+      <c r="J83" s="76" t="n"/>
+    </row>
+    <row r="84" ht="28" customHeight="1" s="85">
+      <c r="A84" s="27" t="n"/>
+      <c r="B84" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C84" s="29" t="inlineStr">
+        <is>
+          <t>Over-Varing Evidence</t>
+        </is>
+      </c>
+      <c r="D84" s="30" t="inlineStr">
+        <is>
+          <t>Variaball Played: Cancel card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E84" s="60" t="n"/>
+      <c r="F84" s="61" t="n"/>
+      <c r="G84" s="78" t="inlineStr">
+        <is>
+          <t>The Variaball's player inbounds (side-out)</t>
+        </is>
+      </c>
+      <c r="H84" s="76" t="n"/>
+      <c r="I84" s="76" t="n"/>
+      <c r="J84" s="76" t="n"/>
+    </row>
+    <row r="85" ht="28" customHeight="1" s="85">
+      <c r="A85" s="52" t="inlineStr">
         <is>
           <t>Retired Game Breaks</t>
         </is>
       </c>
-      <c r="B83" s="53">
-        <f>COUNTIF($B$84:$B$113,"Retired Game Break")</f>
+      <c r="B85" s="53">
+        <f>COUNTIF($B$86:$B$115,"Retired Game Break")</f>
         <v/>
       </c>
-      <c r="C83" s="54" t="n"/>
-      <c r="D83" s="54" t="n"/>
-      <c r="E83" s="54" t="n"/>
-      <c r="F83" s="55" t="n"/>
-      <c r="G83" s="66" t="n"/>
-      <c r="H83" s="67" t="n"/>
-      <c r="I83" s="67" t="n"/>
-      <c r="J83" s="67" t="n"/>
-    </row>
-    <row r="84" ht="20" customHeight="1" s="85">
-      <c r="A84" s="21" t="n"/>
-      <c r="B84" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C84" s="24" t="inlineStr">
-        <is>
-          <t>2-Minute Warning</t>
-        </is>
-      </c>
-      <c r="D84" s="25" t="inlineStr">
-        <is>
-          <t>All players discard down to 2 or fewer cards</t>
-        </is>
-      </c>
-      <c r="E84" s="26" t="n"/>
-      <c r="F84" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="72" t="n"/>
-      <c r="H84" s="71" t="n"/>
-      <c r="I84" s="71" t="n"/>
-      <c r="J84" s="71" t="n"/>
-    </row>
-    <row r="85" ht="28" customHeight="1" s="85">
-      <c r="A85" s="21" t="n"/>
-      <c r="B85" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C85" s="23" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="n"/>
-      <c r="F85" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="74" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
-      <c r="H85" s="71" t="n"/>
-      <c r="I85" s="71" t="n"/>
-      <c r="J85" s="71" t="n"/>
+      <c r="C85" s="54" t="n"/>
+      <c r="D85" s="54" t="n"/>
+      <c r="E85" s="54" t="n"/>
+      <c r="F85" s="55" t="n"/>
+      <c r="G85" s="66" t="n"/>
+      <c r="H85" s="67" t="n"/>
+      <c r="I85" s="67" t="n"/>
+      <c r="J85" s="67" t="n"/>
     </row>
     <row r="86" ht="20" customHeight="1" s="85">
       <c r="A86" s="21" t="n"/>
@@ -4514,12 +4515,12 @@
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>Crowd Noise</t>
+          <t>2-Minute Warning</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>Discard 1 card.</t>
+          <t>All players discard down to 2 or fewer cards</t>
         </is>
       </c>
       <c r="E86" s="26" t="n"/>
@@ -4531,7 +4532,7 @@
       <c r="I86" s="71" t="n"/>
       <c r="J86" s="71" t="n"/>
     </row>
-    <row r="87" ht="42" customHeight="1" s="85">
+    <row r="87" ht="28" customHeight="1" s="85">
       <c r="A87" s="21" t="n"/>
       <c r="B87" s="22" t="inlineStr">
         <is>
@@ -4540,38 +4541,42 @@
       </c>
       <c r="C87" s="23" t="inlineStr">
         <is>
-          <t>Designed Play</t>
+          <t>Benched</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Draw up to a hand of 5</t>
+          <t>Immediately give ball to any other player.</t>
         </is>
       </c>
       <c r="E87" s="7" t="n"/>
       <c r="F87" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="70" t="n"/>
+      <c r="G87" s="74" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H87" s="71" t="n"/>
       <c r="I87" s="71" t="n"/>
       <c r="J87" s="71" t="n"/>
     </row>
-    <row r="88" ht="28" customHeight="1" s="85">
+    <row r="88" ht="20" customHeight="1" s="85">
       <c r="A88" s="21" t="n"/>
       <c r="B88" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C88" s="37" t="inlineStr">
-        <is>
-          <t>Foul</t>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
         </is>
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>Take 1 FT</t>
+          <t>Discard 1 card.</t>
         </is>
       </c>
       <c r="E88" s="26" t="n"/>
@@ -4583,7 +4588,7 @@
       <c r="I88" s="71" t="n"/>
       <c r="J88" s="71" t="n"/>
     </row>
-    <row r="89" ht="56" customHeight="1" s="85">
+    <row r="89" ht="42" customHeight="1" s="85">
       <c r="A89" s="21" t="n"/>
       <c r="B89" s="22" t="inlineStr">
         <is>
@@ -4592,12 +4597,12 @@
       </c>
       <c r="C89" s="23" t="inlineStr">
         <is>
-          <t>MVP Vote</t>
+          <t>Designed Play</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Draw 3 cards up to a hand of 7</t>
+          <t>Draw up to a hand of 5</t>
         </is>
       </c>
       <c r="E89" s="7" t="n"/>
@@ -4609,21 +4614,21 @@
       <c r="I89" s="71" t="n"/>
       <c r="J89" s="71" t="n"/>
     </row>
-    <row r="90" ht="42" customHeight="1" s="85">
+    <row r="90" ht="28" customHeight="1" s="85">
       <c r="A90" s="21" t="n"/>
       <c r="B90" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C90" s="24" t="inlineStr">
-        <is>
-          <t>Off Night</t>
+      <c r="C90" s="37" t="inlineStr">
+        <is>
+          <t>Foul</t>
         </is>
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>SHOT -20% this possession</t>
+          <t>Take 1 FT</t>
         </is>
       </c>
       <c r="E90" s="26" t="n"/>
@@ -4635,7 +4640,7 @@
       <c r="I90" s="71" t="n"/>
       <c r="J90" s="71" t="n"/>
     </row>
-    <row r="91" ht="42" customHeight="1" s="85">
+    <row r="91" ht="56" customHeight="1" s="85">
       <c r="A91" s="21" t="n"/>
       <c r="B91" s="22" t="inlineStr">
         <is>
@@ -4644,20 +4649,16 @@
       </c>
       <c r="C91" s="23" t="inlineStr">
         <is>
-          <t>Swallowed Whistle</t>
+          <t>MVP Vote</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F91" s="32" t="n">
+          <t>Draw 3 cards up to a hand of 7</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="n"/>
+      <c r="F91" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="70" t="n"/>
@@ -4665,7 +4666,7 @@
       <c r="I91" s="71" t="n"/>
       <c r="J91" s="71" t="n"/>
     </row>
-    <row r="92" ht="28" customHeight="1" s="85">
+    <row r="92" ht="42" customHeight="1" s="85">
       <c r="A92" s="21" t="n"/>
       <c r="B92" s="22" t="inlineStr">
         <is>
@@ -4674,20 +4675,16 @@
       </c>
       <c r="C92" s="24" t="inlineStr">
         <is>
-          <t>Rock Fight</t>
+          <t>Off Night</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>Players cannot shoot when SHOT is above 50%</t>
-        </is>
-      </c>
-      <c r="E92" s="25" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F92" s="36" t="n">
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E92" s="26" t="n"/>
+      <c r="F92" s="33" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="72" t="n"/>
@@ -4695,7 +4692,7 @@
       <c r="I92" s="71" t="n"/>
       <c r="J92" s="71" t="n"/>
     </row>
-    <row r="93" ht="28" customHeight="1" s="85">
+    <row r="93" ht="42" customHeight="1" s="85">
       <c r="A93" s="21" t="n"/>
       <c r="B93" s="22" t="inlineStr">
         <is>
@@ -4704,80 +4701,84 @@
       </c>
       <c r="C93" s="23" t="inlineStr">
         <is>
-          <t>Traded Mid-Game</t>
+          <t>Swallowed Whistle</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Swap hands with a random other player</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="n"/>
-      <c r="F93" s="34" t="n">
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F93" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G93" s="74" t="n"/>
+      <c r="G93" s="70" t="n"/>
       <c r="H93" s="71" t="n"/>
       <c r="I93" s="71" t="n"/>
       <c r="J93" s="71" t="n"/>
     </row>
-    <row r="94" ht="56" customHeight="1" s="85">
+    <row r="94" ht="28" customHeight="1" s="85">
       <c r="A94" s="21" t="n"/>
       <c r="B94" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C94" s="49" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D94" s="38" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="n"/>
-      <c r="F94" s="34" t="n">
+      <c r="C94" s="24" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D94" s="25" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is above 50%</t>
+        </is>
+      </c>
+      <c r="E94" s="25" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F94" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G94" s="74" t="n"/>
+      <c r="G94" s="72" t="n"/>
       <c r="H94" s="71" t="n"/>
       <c r="I94" s="71" t="n"/>
       <c r="J94" s="71" t="n"/>
     </row>
-    <row r="95" ht="56" customHeight="1" s="85">
+    <row r="95" ht="28" customHeight="1" s="85">
       <c r="A95" s="21" t="n"/>
       <c r="B95" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C95" s="49" t="inlineStr">
-        <is>
-          <t>All-Swissh Selection</t>
-        </is>
-      </c>
-      <c r="D95" s="38" t="inlineStr">
-        <is>
-          <t>Draw 3 cards after your next make</t>
+      <c r="C95" s="23" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Swap hands with a random other player</t>
         </is>
       </c>
       <c r="E95" s="7" t="n"/>
       <c r="F95" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G95" s="74" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+      <c r="G95" s="74" t="n"/>
       <c r="H95" s="71" t="n"/>
       <c r="I95" s="71" t="n"/>
       <c r="J95" s="71" t="n"/>
     </row>
-    <row r="96" ht="28" customHeight="1" s="85">
+    <row r="96" ht="56" customHeight="1" s="85">
       <c r="A96" s="21" t="n"/>
       <c r="B96" s="22" t="inlineStr">
         <is>
@@ -4786,12 +4787,12 @@
       </c>
       <c r="C96" s="49" t="inlineStr">
         <is>
-          <t>All Star Selection</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D96" s="38" t="inlineStr">
         <is>
-          <t>Draw 2 cards</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
@@ -4803,7 +4804,7 @@
       <c r="I96" s="71" t="n"/>
       <c r="J96" s="71" t="n"/>
     </row>
-    <row r="97" ht="42" customHeight="1" s="85">
+    <row r="97" ht="56" customHeight="1" s="85">
       <c r="A97" s="21" t="n"/>
       <c r="B97" s="22" t="inlineStr">
         <is>
@@ -4812,12 +4813,12 @@
       </c>
       <c r="C97" s="49" t="inlineStr">
         <is>
-          <t>Hit the Bike</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D97" s="38" t="inlineStr">
         <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E97" s="7" t="n"/>
@@ -4826,7 +4827,7 @@
       </c>
       <c r="G97" s="74" t="inlineStr">
         <is>
-          <t>This is not a pass</t>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
         </is>
       </c>
       <c r="H97" s="71" t="n"/>
@@ -4842,12 +4843,12 @@
       </c>
       <c r="C98" s="49" t="inlineStr">
         <is>
-          <t>Ice Wrap</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D98" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
@@ -4868,12 +4869,12 @@
       </c>
       <c r="C99" s="49" t="inlineStr">
         <is>
-          <t>Wet Spot</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D99" s="38" t="inlineStr">
         <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E99" s="7" t="n"/>
@@ -4882,14 +4883,14 @@
       </c>
       <c r="G99" s="74" t="inlineStr">
         <is>
-          <t>Deck ones are shown face down</t>
+          <t>This is not a pass</t>
         </is>
       </c>
       <c r="H99" s="71" t="n"/>
       <c r="I99" s="71" t="n"/>
       <c r="J99" s="71" t="n"/>
     </row>
-    <row r="100" ht="14" customHeight="1" s="85">
+    <row r="100" ht="28" customHeight="1" s="85">
       <c r="A100" s="21" t="n"/>
       <c r="B100" s="22" t="inlineStr">
         <is>
@@ -4898,28 +4899,24 @@
       </c>
       <c r="C100" s="49" t="inlineStr">
         <is>
-          <t>Fresh Ball</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D100" s="38" t="inlineStr">
         <is>
-          <t>Next player does not draw at the start of their possession</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="74" t="inlineStr">
-        <is>
-          <t>This is a bad thing in the NBA</t>
-        </is>
-      </c>
+      <c r="G100" s="74" t="n"/>
       <c r="H100" s="71" t="n"/>
       <c r="I100" s="71" t="n"/>
       <c r="J100" s="71" t="n"/>
     </row>
-    <row r="101" ht="14" customHeight="1" s="85">
+    <row r="101" ht="42" customHeight="1" s="85">
       <c r="A101" s="21" t="n"/>
       <c r="B101" s="22" t="inlineStr">
         <is>
@@ -4928,12 +4925,12 @@
       </c>
       <c r="C101" s="49" t="inlineStr">
         <is>
-          <t>Trade Deadline</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D101" s="38" t="inlineStr">
         <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E101" s="7" t="n"/>
@@ -4942,7 +4939,7 @@
       </c>
       <c r="G101" s="74" t="inlineStr">
         <is>
-          <t>The hex travels in the declared direction too</t>
+          <t>Deck ones are shown face down</t>
         </is>
       </c>
       <c r="H101" s="71" t="n"/>
@@ -4958,19 +4955,23 @@
       </c>
       <c r="C102" s="49" t="inlineStr">
         <is>
-          <t>Floor Cleanup</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D102" s="38" t="inlineStr">
         <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E102" s="7" t="n"/>
       <c r="F102" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="74" t="n"/>
+      <c r="G102" s="74" t="inlineStr">
+        <is>
+          <t>This is a bad thing in the NBA</t>
+        </is>
+      </c>
       <c r="H102" s="71" t="n"/>
       <c r="I102" s="71" t="n"/>
       <c r="J102" s="71" t="n"/>
@@ -4984,19 +4985,23 @@
       </c>
       <c r="C103" s="49" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D103" s="38" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E103" s="7" t="n"/>
       <c r="F103" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="74" t="n"/>
+      <c r="G103" s="74" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H103" s="71" t="n"/>
       <c r="I103" s="71" t="n"/>
       <c r="J103" s="71" t="n"/>
@@ -5010,12 +5015,12 @@
       </c>
       <c r="C104" s="49" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D104" s="38" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -5036,12 +5041,12 @@
       </c>
       <c r="C105" s="49" t="inlineStr">
         <is>
-          <t>Altercation</t>
+          <t>Official Timeout</t>
         </is>
       </c>
       <c r="D105" s="38" t="inlineStr">
         <is>
-          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -5062,12 +5067,12 @@
       </c>
       <c r="C106" s="49" t="inlineStr">
         <is>
-          <t>Huge Altercation</t>
+          <t>Team Doctor</t>
         </is>
       </c>
       <c r="D106" s="38" t="inlineStr">
         <is>
-          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
         </is>
       </c>
       <c r="E106" s="7" t="n"/>
@@ -5088,12 +5093,12 @@
       </c>
       <c r="C107" s="49" t="inlineStr">
         <is>
-          <t>Home Court Advantage</t>
+          <t>Altercation</t>
         </is>
       </c>
       <c r="D107" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 25%</t>
+          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
         </is>
       </c>
       <c r="E107" s="7" t="n"/>
@@ -5114,12 +5119,12 @@
       </c>
       <c r="C108" s="49" t="inlineStr">
         <is>
-          <t>Away Game</t>
+          <t>Huge Altercation</t>
         </is>
       </c>
       <c r="D108" s="38" t="inlineStr">
         <is>
-          <t>SHOT - 10%</t>
+          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
         </is>
       </c>
       <c r="E108" s="7" t="n"/>
@@ -5131,7 +5136,7 @@
       <c r="I108" s="71" t="n"/>
       <c r="J108" s="71" t="n"/>
     </row>
-    <row r="109" ht="28" customHeight="1" s="85">
+    <row r="109" ht="14" customHeight="1" s="85">
       <c r="A109" s="21" t="n"/>
       <c r="B109" s="22" t="inlineStr">
         <is>
@@ -5140,28 +5145,24 @@
       </c>
       <c r="C109" s="49" t="inlineStr">
         <is>
-          <t>Mic'd Up</t>
+          <t>Home Court Advantage</t>
         </is>
       </c>
       <c r="D109" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 10% until passed or shot</t>
+          <t>SHOT + 25%</t>
         </is>
       </c>
       <c r="E109" s="7" t="n"/>
       <c r="F109" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="74" t="inlineStr">
-        <is>
-          <t>The boost is the holder's alone and does not travel with a pass</t>
-        </is>
-      </c>
+      <c r="G109" s="74" t="n"/>
       <c r="H109" s="71" t="n"/>
       <c r="I109" s="71" t="n"/>
       <c r="J109" s="71" t="n"/>
     </row>
-    <row r="110" ht="28" customHeight="1" s="85">
+    <row r="110" ht="14" customHeight="1" s="85">
       <c r="A110" s="21" t="n"/>
       <c r="B110" s="22" t="inlineStr">
         <is>
@@ -5170,12 +5171,12 @@
       </c>
       <c r="C110" s="49" t="inlineStr">
         <is>
-          <t>In The Zone</t>
+          <t>Away Game</t>
         </is>
       </c>
       <c r="D110" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+          <t>SHOT - 10%</t>
         </is>
       </c>
       <c r="E110" s="7" t="n"/>
@@ -5196,128 +5197,139 @@
       </c>
       <c r="C111" s="49" t="inlineStr">
         <is>
-          <t>Role Player</t>
+          <t>Mic'd Up</t>
         </is>
       </c>
       <c r="D111" s="38" t="inlineStr">
         <is>
-          <t>All other players draw 1 card</t>
+          <t>SHOT + 10% until passed or shot</t>
         </is>
       </c>
       <c r="E111" s="7" t="n"/>
       <c r="F111" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G111" s="74" t="n"/>
+      <c r="G111" s="74" t="inlineStr">
+        <is>
+          <t>The boost is the holder's alone and does not travel with a pass</t>
+        </is>
+      </c>
       <c r="H111" s="71" t="n"/>
       <c r="I111" s="71" t="n"/>
       <c r="J111" s="71" t="n"/>
     </row>
     <row r="112" ht="28" customHeight="1" s="85">
-      <c r="A112" s="27" t="n"/>
-      <c r="B112" s="28" t="inlineStr">
+      <c r="A112" s="21" t="n"/>
+      <c r="B112" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C112" s="62" t="inlineStr">
+      <c r="C112" s="49" t="inlineStr">
+        <is>
+          <t>In The Zone</t>
+        </is>
+      </c>
+      <c r="D112" s="38" t="inlineStr">
+        <is>
+          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="n"/>
+      <c r="F112" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="74" t="n"/>
+      <c r="H112" s="71" t="n"/>
+      <c r="I112" s="71" t="n"/>
+      <c r="J112" s="71" t="n"/>
+    </row>
+    <row r="113" ht="28" customHeight="1" s="85">
+      <c r="A113" s="21" t="n"/>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C113" s="49" t="inlineStr">
+        <is>
+          <t>Role Player</t>
+        </is>
+      </c>
+      <c r="D113" s="38" t="inlineStr">
+        <is>
+          <t>All other players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="n"/>
+      <c r="F113" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="74" t="n"/>
+      <c r="H113" s="71" t="n"/>
+      <c r="I113" s="71" t="n"/>
+      <c r="J113" s="71" t="n"/>
+    </row>
+    <row r="114" ht="28" customHeight="1" s="85">
+      <c r="A114" s="27" t="n"/>
+      <c r="B114" s="28" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C114" s="62" t="inlineStr">
         <is>
           <t>Back-and-Forth Game</t>
         </is>
       </c>
-      <c r="D112" s="63" t="inlineStr">
+      <c r="D114" s="63" t="inlineStr">
         <is>
           <t>Discard the next 3 Game Breaks. Whoever draws one draws again</t>
         </is>
       </c>
-      <c r="E112" s="58" t="n"/>
-      <c r="F112" s="59" t="n">
+      <c r="E114" s="58" t="n"/>
+      <c r="F114" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="G112" s="79" t="n"/>
-      <c r="H112" s="76" t="n"/>
-      <c r="I112" s="76" t="n"/>
-      <c r="J112" s="76" t="n"/>
-    </row>
-    <row r="113" ht="42" customHeight="1" s="85">
-      <c r="A113" s="27" t="n"/>
-      <c r="B113" s="28" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C113" s="62" t="inlineStr">
-        <is>
-          <t>Off the Backboard</t>
-        </is>
-      </c>
-      <c r="D113" s="63" t="inlineStr">
-        <is>
-          <t>Your next missed shot rebounds itself</t>
-        </is>
-      </c>
-      <c r="E113" s="58" t="n"/>
-      <c r="F113" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="79" t="n"/>
-      <c r="H113" s="76" t="n"/>
-      <c r="I113" s="76" t="n"/>
-      <c r="J113" s="76" t="n"/>
-    </row>
-    <row r="114" ht="56" customHeight="1" s="85">
-      <c r="A114" s="52" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="B114" s="53">
-        <f>COUNTIF($B$115:$B$148,"Injury")</f>
-        <v/>
-      </c>
-      <c r="C114" s="54" t="n"/>
-      <c r="D114" s="54" t="n"/>
-      <c r="E114" s="54" t="n"/>
-      <c r="F114" s="55" t="n"/>
-      <c r="G114" s="66" t="n"/>
-      <c r="H114" s="67" t="n"/>
-      <c r="I114" s="67" t="n"/>
-      <c r="J114" s="67" t="n"/>
-    </row>
-    <row r="115" ht="57" customHeight="1" s="85">
+      <c r="G114" s="79" t="n"/>
+      <c r="H114" s="76" t="n"/>
+      <c r="I114" s="76" t="n"/>
+      <c r="J114" s="76" t="n"/>
+    </row>
+    <row r="115" ht="42" customHeight="1" s="85">
       <c r="A115" s="27" t="n"/>
       <c r="B115" s="28" t="inlineStr">
         <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="C115" s="56" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C115" s="62" t="inlineStr">
+        <is>
+          <t>Off the Backboard</t>
         </is>
       </c>
       <c r="D115" s="63" t="inlineStr">
         <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+          <t>Your next missed shot rebounds itself</t>
         </is>
       </c>
       <c r="E115" s="58" t="n"/>
       <c r="F115" s="59" t="n">
-        <v>5</v>
-      </c>
-      <c r="G115" s="75" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G115" s="79" t="n"/>
       <c r="H115" s="76" t="n"/>
       <c r="I115" s="76" t="n"/>
       <c r="J115" s="76" t="n"/>
     </row>
-    <row r="116" ht="20" customHeight="1" s="85">
+    <row r="116" ht="56" customHeight="1" s="85">
       <c r="A116" s="52" t="inlineStr">
         <is>
-          <t>Devastating Injury</t>
+          <t>Injury</t>
         </is>
       </c>
       <c r="B116" s="53">
-        <f>COUNTIF($B$117:$B$148,"Devastating Injury")</f>
+        <f>COUNTIF($B$117:$B$150,"Injury")</f>
         <v/>
       </c>
       <c r="C116" s="54" t="n"/>
@@ -5329,38 +5341,40 @@
       <c r="I116" s="67" t="n"/>
       <c r="J116" s="67" t="n"/>
     </row>
-    <row r="117" ht="28" customHeight="1" s="85">
+    <row r="117" ht="57" customHeight="1" s="85">
       <c r="A117" s="27" t="n"/>
       <c r="B117" s="28" t="inlineStr">
         <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="C117" s="64" t="inlineStr">
-        <is>
-          <t>Torn Achilles</t>
-        </is>
-      </c>
-      <c r="D117" s="65" t="inlineStr">
-        <is>
-          <t>Hand is locked every turn except 1 card (randomly)</t>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C117" s="56" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D117" s="63" t="inlineStr">
+        <is>
+          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
         </is>
       </c>
       <c r="E117" s="58" t="n"/>
-      <c r="F117" s="61" t="n"/>
+      <c r="F117" s="59" t="n">
+        <v>5</v>
+      </c>
       <c r="G117" s="75" t="n"/>
       <c r="H117" s="76" t="n"/>
       <c r="I117" s="76" t="n"/>
       <c r="J117" s="76" t="n"/>
     </row>
-    <row r="118" ht="42" customHeight="1" s="85">
+    <row r="118" ht="20" customHeight="1" s="85">
       <c r="A118" s="52" t="inlineStr">
         <is>
-          <t>Intangible</t>
+          <t>Devastating Injury</t>
         </is>
       </c>
       <c r="B118" s="53">
-        <f>COUNTIF($B$119:$B$148,"Intangible")</f>
+        <f>COUNTIF($B$119:$B$150,"Devastating Injury")</f>
         <v/>
       </c>
       <c r="C118" s="54" t="n"/>
@@ -5373,72 +5387,67 @@
       <c r="J118" s="67" t="n"/>
     </row>
     <row r="119" ht="28" customHeight="1" s="85">
-      <c r="A119" s="42" t="inlineStr">
+      <c r="A119" s="27" t="n"/>
+      <c r="B119" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C119" s="64" t="inlineStr">
+        <is>
+          <t>Torn Achilles</t>
+        </is>
+      </c>
+      <c r="D119" s="65" t="inlineStr">
+        <is>
+          <t>Hand is locked every turn except 1 card (randomly)</t>
+        </is>
+      </c>
+      <c r="E119" s="58" t="n"/>
+      <c r="F119" s="61" t="n"/>
+      <c r="G119" s="75" t="n"/>
+      <c r="H119" s="76" t="n"/>
+      <c r="I119" s="76" t="n"/>
+      <c r="J119" s="76" t="n"/>
+    </row>
+    <row r="120" ht="42" customHeight="1" s="85">
+      <c r="A120" s="52" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="B120" s="53">
+        <f>COUNTIF($B$121:$B$150,"Intangible")</f>
+        <v/>
+      </c>
+      <c r="C120" s="54" t="n"/>
+      <c r="D120" s="54" t="n"/>
+      <c r="E120" s="54" t="n"/>
+      <c r="F120" s="55" t="n"/>
+      <c r="G120" s="66" t="n"/>
+      <c r="H120" s="67" t="n"/>
+      <c r="I120" s="67" t="n"/>
+      <c r="J120" s="67" t="n"/>
+    </row>
+    <row r="121" ht="28" customHeight="1" s="85">
+      <c r="A121" s="42" t="inlineStr">
         <is>
           <t>All intangibles are limited to 1</t>
         </is>
       </c>
-      <c r="B119" s="22" t="inlineStr">
+      <c r="B121" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C119" s="23" t="inlineStr">
+      <c r="C121" s="23" t="inlineStr">
         <is>
           <t>Board-Crasher</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D121" s="6" t="inlineStr">
         <is>
           <t>SHOT +10% upon Rebounding your own missed shot</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="n"/>
-      <c r="F119" s="50" t="n"/>
-      <c r="G119" s="70" t="n"/>
-      <c r="H119" s="71" t="n"/>
-      <c r="I119" s="71" t="n"/>
-      <c r="J119" s="71" t="n"/>
-    </row>
-    <row r="120" ht="28" customHeight="1" s="85">
-      <c r="A120" s="21" t="n"/>
-      <c r="B120" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C120" s="24" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D120" s="25" t="inlineStr">
-        <is>
-          <t>SHOT +25% on received passes, if shooting is your first action</t>
-        </is>
-      </c>
-      <c r="E120" s="26" t="n"/>
-      <c r="F120" s="50" t="n"/>
-      <c r="G120" s="72" t="n"/>
-      <c r="H120" s="71" t="n"/>
-      <c r="I120" s="71" t="n"/>
-      <c r="J120" s="71" t="n"/>
-    </row>
-    <row r="121" ht="56" customHeight="1" s="85">
-      <c r="A121" s="21" t="n"/>
-      <c r="B121" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C121" s="23" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
         </is>
       </c>
       <c r="E121" s="7" t="n"/>
@@ -5448,70 +5457,70 @@
       <c r="I121" s="71" t="n"/>
       <c r="J121" s="71" t="n"/>
     </row>
-    <row r="122" ht="56" customHeight="1" s="85">
-      <c r="B122" s="0" t="inlineStr">
+    <row r="122" ht="28" customHeight="1" s="85">
+      <c r="A122" s="21" t="n"/>
+      <c r="B122" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C122" s="0" t="inlineStr">
-        <is>
-          <t>Roswell Reach</t>
-        </is>
-      </c>
-      <c r="D122" s="0" t="inlineStr">
-        <is>
-          <t>All your Rebound bids of 1 or more count as 1 higher</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="28" customHeight="1" s="85">
+      <c r="C122" s="24" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D122" s="25" t="inlineStr">
+        <is>
+          <t>SHOT +25% on received passes, if shooting is your first action</t>
+        </is>
+      </c>
+      <c r="E122" s="26" t="n"/>
+      <c r="F122" s="50" t="n"/>
+      <c r="G122" s="72" t="n"/>
+      <c r="H122" s="71" t="n"/>
+      <c r="I122" s="71" t="n"/>
+      <c r="J122" s="71" t="n"/>
+    </row>
+    <row r="123" ht="56" customHeight="1" s="85">
       <c r="A123" s="21" t="n"/>
       <c r="B123" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C123" s="24" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D123" s="25" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
-        </is>
-      </c>
-      <c r="E123" s="26" t="n"/>
+      <c r="C123" s="23" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="n"/>
       <c r="F123" s="50" t="n"/>
-      <c r="G123" s="72" t="n"/>
+      <c r="G123" s="70" t="n"/>
       <c r="H123" s="71" t="n"/>
       <c r="I123" s="71" t="n"/>
       <c r="J123" s="71" t="n"/>
     </row>
-    <row r="124" ht="28" customHeight="1" s="85">
-      <c r="A124" s="21" t="n"/>
-      <c r="B124" s="22" t="inlineStr">
+    <row r="124" ht="56" customHeight="1" s="85">
+      <c r="B124" s="0" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C124" s="23" t="inlineStr">
-        <is>
-          <t>Southpaw Shooter</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>SHOT gains and losses are reversed</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="n"/>
-      <c r="F124" s="51" t="n"/>
-      <c r="G124" s="70" t="n"/>
-      <c r="H124" s="71" t="n"/>
-      <c r="I124" s="71" t="n"/>
-      <c r="J124" s="71" t="n"/>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>Roswell Reach</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="inlineStr">
+        <is>
+          <t>All your Rebound bids of 1 or more count as 1 higher</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="28" customHeight="1" s="85">
       <c r="A125" s="21" t="n"/>
@@ -5520,19 +5529,19 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C125" s="37" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D125" s="41" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
+      <c r="C125" s="24" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D125" s="25" t="inlineStr">
+        <is>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
         </is>
       </c>
       <c r="E125" s="26" t="n"/>
       <c r="F125" s="50" t="n"/>
-      <c r="G125" s="77" t="n"/>
+      <c r="G125" s="72" t="n"/>
       <c r="H125" s="71" t="n"/>
       <c r="I125" s="71" t="n"/>
       <c r="J125" s="71" t="n"/>
@@ -5544,43 +5553,43 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C126" s="37" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D126" s="38" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="n"/>
-      <c r="F126" s="50" t="n"/>
+      <c r="C126" s="23" t="inlineStr">
+        <is>
+          <t>Southpaw Shooter</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>SHOT gains and losses are reversed</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="n"/>
+      <c r="F126" s="51" t="n"/>
       <c r="G126" s="70" t="n"/>
       <c r="H126" s="71" t="n"/>
       <c r="I126" s="71" t="n"/>
       <c r="J126" s="71" t="n"/>
     </row>
-    <row r="127" ht="14" customHeight="1" s="85">
+    <row r="127" ht="28" customHeight="1" s="85">
       <c r="A127" s="21" t="n"/>
       <c r="B127" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C127" s="24" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D127" s="25" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
+      <c r="C127" s="37" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D127" s="41" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
         </is>
       </c>
       <c r="E127" s="26" t="n"/>
       <c r="F127" s="50" t="n"/>
-      <c r="G127" s="72" t="n"/>
+      <c r="G127" s="77" t="n"/>
       <c r="H127" s="71" t="n"/>
       <c r="I127" s="71" t="n"/>
       <c r="J127" s="71" t="n"/>
@@ -5592,28 +5601,24 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C128" s="23" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injuries you draw and draw a new card for each</t>
+      <c r="C128" s="37" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D128" s="38" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
         </is>
       </c>
       <c r="E128" s="7" t="n"/>
       <c r="F128" s="50" t="n"/>
-      <c r="G128" s="70" t="inlineStr">
-        <is>
-          <t>Also discards any Injuries you already have (not on the card)</t>
-        </is>
-      </c>
+      <c r="G128" s="70" t="n"/>
       <c r="H128" s="71" t="n"/>
       <c r="I128" s="71" t="n"/>
       <c r="J128" s="71" t="n"/>
     </row>
-    <row r="129" ht="28" customHeight="1" s="85">
+    <row r="129" ht="14" customHeight="1" s="85">
       <c r="A129" s="21" t="n"/>
       <c r="B129" s="22" t="inlineStr">
         <is>
@@ -5622,12 +5627,12 @@
       </c>
       <c r="C129" s="24" t="inlineStr">
         <is>
-          <t>Hot Hand</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>SHOT +25% if you scored last round.</t>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
         </is>
       </c>
       <c r="E129" s="26" t="n"/>
@@ -5646,19 +5651,19 @@
       </c>
       <c r="C130" s="23" t="inlineStr">
         <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D130" s="38" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>Immediately discard all Injuries you draw and draw a new card for each</t>
         </is>
       </c>
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="50" t="n"/>
       <c r="G130" s="70" t="inlineStr">
         <is>
-          <t>Variaball effects still lower SHOT: the ball is altered, not the player (not on the card)</t>
+          <t>Also discards any Injuries you already have (not on the card)</t>
         </is>
       </c>
       <c r="H130" s="71" t="n"/>
@@ -5674,17 +5679,17 @@
       </c>
       <c r="C131" s="24" t="inlineStr">
         <is>
-          <t>Park Shark</t>
+          <t>Hot Hand</t>
         </is>
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>SHOT +25% on every shot. Cannot use Move or Special Move cards, or shoot threes</t>
+          <t>SHOT +25% if you scored last round.</t>
         </is>
       </c>
       <c r="E131" s="26" t="n"/>
       <c r="F131" s="50" t="n"/>
-      <c r="G131" s="73" t="n"/>
+      <c r="G131" s="72" t="n"/>
       <c r="H131" s="71" t="n"/>
       <c r="I131" s="71" t="n"/>
       <c r="J131" s="71" t="n"/>
@@ -5698,22 +5703,26 @@
       </c>
       <c r="C132" s="23" t="inlineStr">
         <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D132" s="38" t="inlineStr">
+        <is>
+          <t>Your SHOT % cannot be reduced</t>
         </is>
       </c>
       <c r="E132" s="7" t="n"/>
       <c r="F132" s="50" t="n"/>
-      <c r="G132" s="70" t="n"/>
+      <c r="G132" s="70" t="inlineStr">
+        <is>
+          <t>Variaball effects still lower SHOT: the ball is altered, not the player (not on the card)</t>
+        </is>
+      </c>
       <c r="H132" s="71" t="n"/>
       <c r="I132" s="71" t="n"/>
       <c r="J132" s="71" t="n"/>
     </row>
-    <row r="133" ht="56" customHeight="1" s="85">
+    <row r="133" ht="28" customHeight="1" s="85">
       <c r="A133" s="21" t="n"/>
       <c r="B133" s="22" t="inlineStr">
         <is>
@@ -5722,26 +5731,22 @@
       </c>
       <c r="C133" s="24" t="inlineStr">
         <is>
-          <t>Shot Creator</t>
+          <t>Park Shark</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>Draw 1 additional card after every draw effect</t>
+          <t>SHOT +25% on every shot. Cannot use Move or Special Move cards, or shoot threes</t>
         </is>
       </c>
       <c r="E133" s="26" t="n"/>
       <c r="F133" s="50" t="n"/>
-      <c r="G133" s="73" t="inlineStr">
-        <is>
-          <t>Triggers once per act of drawing: a Draw 2 still gives only 1 extra</t>
-        </is>
-      </c>
+      <c r="G133" s="73" t="n"/>
       <c r="H133" s="71" t="n"/>
       <c r="I133" s="71" t="n"/>
       <c r="J133" s="71" t="n"/>
     </row>
-    <row r="134" ht="56" customHeight="1" s="85">
+    <row r="134" ht="28" customHeight="1" s="85">
       <c r="A134" s="21" t="n"/>
       <c r="B134" s="22" t="inlineStr">
         <is>
@@ -5750,21 +5755,17 @@
       </c>
       <c r="C134" s="23" t="inlineStr">
         <is>
-          <t>Sixth Man</t>
+          <t>Point God</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>SHOT = 60% on any six: cards in hand, Shot Clock, shot of the round, or score</t>
+          <t>Draw 1 card following each of your passes</t>
         </is>
       </c>
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="50" t="n"/>
-      <c r="G134" s="70" t="inlineStr">
-        <is>
-          <t>A second SHOOT (60%) button beside Shoot, shown only on a six. Ignore it when SHOT is already higher</t>
-        </is>
-      </c>
+      <c r="G134" s="70" t="n"/>
       <c r="H134" s="71" t="n"/>
       <c r="I134" s="71" t="n"/>
       <c r="J134" s="71" t="n"/>
@@ -5778,17 +5779,21 @@
       </c>
       <c r="C135" s="24" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Shot Creator</t>
         </is>
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>SHOT +25% on all Three-Point Line Shots</t>
+          <t>Draw 1 additional card after every draw effect</t>
         </is>
       </c>
       <c r="E135" s="26" t="n"/>
       <c r="F135" s="50" t="n"/>
-      <c r="G135" s="72" t="n"/>
+      <c r="G135" s="73" t="inlineStr">
+        <is>
+          <t>Triggers once per act of drawing: a Draw 2 still gives only 1 extra</t>
+        </is>
+      </c>
       <c r="H135" s="71" t="n"/>
       <c r="I135" s="71" t="n"/>
       <c r="J135" s="71" t="n"/>
@@ -5802,17 +5807,21 @@
       </c>
       <c r="C136" s="23" t="inlineStr">
         <is>
-          <t>Splash Cousin</t>
+          <t>Sixth Man</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
+          <t>SHOT = 60% on any six: cards in hand, Shot Clock, shot of the round, or score</t>
         </is>
       </c>
       <c r="E136" s="7" t="n"/>
       <c r="F136" s="50" t="n"/>
-      <c r="G136" s="70" t="n"/>
+      <c r="G136" s="70" t="inlineStr">
+        <is>
+          <t>A second SHOOT (60%) button beside Shoot, shown only on a six. Ignore it when SHOT is already higher</t>
+        </is>
+      </c>
       <c r="H136" s="71" t="n"/>
       <c r="I136" s="71" t="n"/>
       <c r="J136" s="71" t="n"/>
@@ -5826,12 +5835,12 @@
       </c>
       <c r="C137" s="24" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Sniper</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
+          <t>SHOT +25% on all Three-Point Line Shots</t>
         </is>
       </c>
       <c r="E137" s="26" t="n"/>
@@ -5841,7 +5850,7 @@
       <c r="I137" s="71" t="n"/>
       <c r="J137" s="71" t="n"/>
     </row>
-    <row r="138" ht="126" customHeight="1" s="85">
+    <row r="138" ht="56" customHeight="1" s="85">
       <c r="A138" s="21" t="n"/>
       <c r="B138" s="22" t="inlineStr">
         <is>
@@ -5850,26 +5859,22 @@
       </c>
       <c r="C138" s="23" t="inlineStr">
         <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D138" s="38" t="inlineStr">
-        <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>All Three-Point Line Shots: SHOT = 100%</t>
         </is>
       </c>
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="50" t="n"/>
-      <c r="G138" s="70" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="G138" s="70" t="n"/>
       <c r="H138" s="71" t="n"/>
       <c r="I138" s="71" t="n"/>
       <c r="J138" s="71" t="n"/>
     </row>
-    <row r="139" ht="70" customHeight="1" s="85">
+    <row r="139" ht="56" customHeight="1" s="85">
       <c r="A139" s="21" t="n"/>
       <c r="B139" s="22" t="inlineStr">
         <is>
@@ -5878,22 +5883,22 @@
       </c>
       <c r="C139" s="24" t="inlineStr">
         <is>
-          <t>Ball Pounder</t>
+          <t>Competitive</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>Every Dribble draws 1 card but gives SHOT -10% and Shot Clock - 01</t>
+          <t>All Clamps on you have no effect on SHOT %</t>
         </is>
       </c>
       <c r="E139" s="26" t="n"/>
       <c r="F139" s="50" t="n"/>
-      <c r="G139" s="73" t="n"/>
+      <c r="G139" s="72" t="n"/>
       <c r="H139" s="71" t="n"/>
       <c r="I139" s="71" t="n"/>
       <c r="J139" s="71" t="n"/>
     </row>
-    <row r="140" ht="56" customHeight="1" s="85">
+    <row r="140" ht="126" customHeight="1" s="85">
       <c r="A140" s="21" t="n"/>
       <c r="B140" s="22" t="inlineStr">
         <is>
@@ -5902,50 +5907,50 @@
       </c>
       <c r="C140" s="23" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
+          <t>Lethal Shooter</t>
         </is>
       </c>
       <c r="D140" s="38" t="inlineStr">
         <is>
-          <t>When sending Clamps, the clamped player discards 1 for each of your Clamps if they have any Injuries. Discard 1 whenever a Whistle triggers</t>
+          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
         </is>
       </c>
       <c r="E140" s="7" t="n"/>
       <c r="F140" s="50" t="n"/>
-      <c r="G140" s="70" t="n"/>
+      <c r="G140" s="70" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
       <c r="H140" s="71" t="n"/>
       <c r="I140" s="71" t="n"/>
       <c r="J140" s="71" t="n"/>
     </row>
-    <row r="141" s="85">
+    <row r="141" ht="70" customHeight="1" s="85">
       <c r="A141" s="21" t="n"/>
       <c r="B141" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C141" s="23" t="inlineStr">
-        <is>
-          <t>Free Agent</t>
-        </is>
-      </c>
-      <c r="D141" s="38" t="inlineStr">
-        <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="n"/>
+      <c r="C141" s="24" t="inlineStr">
+        <is>
+          <t>Ball Pounder</t>
+        </is>
+      </c>
+      <c r="D141" s="25" t="inlineStr">
+        <is>
+          <t>Every Dribble draws 1 card but gives SHOT -10% and Shot Clock - 01</t>
+        </is>
+      </c>
+      <c r="E141" s="26" t="n"/>
       <c r="F141" s="50" t="n"/>
-      <c r="G141" s="70" t="inlineStr">
-        <is>
-          <t>Low priority to bring back. The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
-        </is>
-      </c>
+      <c r="G141" s="73" t="n"/>
       <c r="H141" s="71" t="n"/>
       <c r="I141" s="71" t="n"/>
       <c r="J141" s="71" t="n"/>
     </row>
-    <row r="142" s="85">
+    <row r="142" ht="56" customHeight="1" s="85">
       <c r="A142" s="21" t="n"/>
       <c r="B142" s="22" t="inlineStr">
         <is>
@@ -5954,12 +5959,12 @@
       </c>
       <c r="C142" s="23" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
+          <t>Dirty Player</t>
         </is>
       </c>
       <c r="D142" s="38" t="inlineStr">
         <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>When sending Clamps, the clamped player discards 1 for each of your Clamps if they have any Injuries. Discard 1 whenever a Whistle triggers</t>
         </is>
       </c>
       <c r="E142" s="7" t="n"/>
@@ -5978,19 +5983,19 @@
       </c>
       <c r="C143" s="23" t="inlineStr">
         <is>
-          <t>Fundamentalist</t>
+          <t>Free Agent</t>
         </is>
       </c>
       <c r="D143" s="38" t="inlineStr">
         <is>
-          <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent. Discards the current ball</t>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
         </is>
       </c>
       <c r="E143" s="7" t="n"/>
       <c r="F143" s="50" t="n"/>
       <c r="G143" s="70" t="inlineStr">
         <is>
-          <t>The ball is discarded once, on activation</t>
+          <t>Low priority to bring back. The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
         </is>
       </c>
       <c r="H143" s="71" t="n"/>
@@ -6006,18 +6011,16 @@
       </c>
       <c r="C144" s="23" t="inlineStr">
         <is>
-          <t>Moves At Own Pace</t>
+          <t>Franchise Player</t>
         </is>
       </c>
       <c r="D144" s="38" t="inlineStr">
         <is>
-          <t>Cannot be called for Traveling or Shot Clock violations</t>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
         </is>
       </c>
       <c r="E144" s="7" t="n"/>
-      <c r="F144" s="50" t="n">
-        <v>1</v>
-      </c>
+      <c r="F144" s="50" t="n"/>
       <c r="G144" s="70" t="n"/>
       <c r="H144" s="71" t="n"/>
       <c r="I144" s="71" t="n"/>
@@ -6032,74 +6035,74 @@
       </c>
       <c r="C145" s="23" t="inlineStr">
         <is>
-          <t>Equalizer</t>
+          <t>Fundamentalist</t>
         </is>
       </c>
       <c r="D145" s="38" t="inlineStr">
         <is>
-          <t>Any 'SHOT =' shot you take becomes 100%</t>
+          <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent. Discards the current ball</t>
         </is>
       </c>
       <c r="E145" s="7" t="n"/>
       <c r="F145" s="50" t="n"/>
-      <c r="G145" s="70" t="n"/>
+      <c r="G145" s="70" t="inlineStr">
+        <is>
+          <t>The ball is discarded once, on activation</t>
+        </is>
+      </c>
       <c r="H145" s="71" t="n"/>
       <c r="I145" s="71" t="n"/>
       <c r="J145" s="71" t="n"/>
     </row>
     <row r="146" s="85">
-      <c r="A146" s="27" t="n"/>
-      <c r="B146" s="28" t="inlineStr">
+      <c r="A146" s="21" t="n"/>
+      <c r="B146" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C146" s="56" t="inlineStr">
-        <is>
-          <t>Varsitile</t>
-        </is>
-      </c>
-      <c r="D146" s="63" t="inlineStr">
-        <is>
-          <t>You can play more than 1 Varena and Variaball per turn. Once per possession, you can exchange the Varena and/or ball for one in the Discards</t>
-        </is>
-      </c>
-      <c r="E146" s="58" t="n"/>
-      <c r="F146" s="61" t="n"/>
-      <c r="G146" s="75" t="inlineStr">
-        <is>
-          <t>One use can exchange both. Not in the deck until Variaballs are</t>
-        </is>
-      </c>
-      <c r="H146" s="76" t="n"/>
-      <c r="I146" s="76" t="n"/>
-      <c r="J146" s="76" t="n"/>
+      <c r="C146" s="23" t="inlineStr">
+        <is>
+          <t>Moves At Own Pace</t>
+        </is>
+      </c>
+      <c r="D146" s="38" t="inlineStr">
+        <is>
+          <t>Cannot be called for Traveling or Shot Clock violations</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="n"/>
+      <c r="F146" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="70" t="n"/>
+      <c r="H146" s="71" t="n"/>
+      <c r="I146" s="71" t="n"/>
+      <c r="J146" s="71" t="n"/>
     </row>
     <row r="147" s="85">
-      <c r="A147" s="27" t="n"/>
-      <c r="B147" s="28" t="inlineStr">
+      <c r="A147" s="21" t="n"/>
+      <c r="B147" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C147" s="56" t="inlineStr">
-        <is>
-          <t>Brawl Handler</t>
-        </is>
-      </c>
-      <c r="D147" s="63" t="inlineStr">
-        <is>
-          <t>Remove all your Clamps when you change the ball</t>
-        </is>
-      </c>
-      <c r="E147" s="58" t="n"/>
-      <c r="F147" s="61" t="n"/>
-      <c r="G147" s="75" t="inlineStr">
-        <is>
-          <t>Not in the deck until Variaballs are</t>
-        </is>
-      </c>
-      <c r="H147" s="76" t="n"/>
+      <c r="C147" s="23" t="inlineStr">
+        <is>
+          <t>Equalizer</t>
+        </is>
+      </c>
+      <c r="D147" s="38" t="inlineStr">
+        <is>
+          <t>Any 'SHOT =' shot you take becomes 100%</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="n"/>
+      <c r="F147" s="50" t="n"/>
+      <c r="G147" s="70" t="n"/>
+      <c r="H147" s="71" t="n"/>
+      <c r="I147" s="71" t="n"/>
+      <c r="J147" s="71" t="n"/>
     </row>
     <row r="148" s="85">
       <c r="A148" s="27" t="n"/>
@@ -6110,202 +6113,1582 @@
       </c>
       <c r="C148" s="56" t="inlineStr">
         <is>
-          <t>Baller</t>
+          <t>Varsitile</t>
         </is>
       </c>
       <c r="D148" s="63" t="inlineStr">
         <is>
-          <t>Draw 1 card each time you change the ball</t>
+          <t>You can play more than 1 Varena and Variaball per turn. Once per possession, you can exchange the Varena and/or ball for one in the Discards</t>
         </is>
       </c>
       <c r="E148" s="58" t="n"/>
       <c r="F148" s="61" t="n"/>
       <c r="G148" s="75" t="inlineStr">
         <is>
-          <t>Not in the deck until Variaballs are</t>
+          <t>One use can exchange both</t>
         </is>
       </c>
       <c r="H148" s="76" t="n"/>
-    </row>
-    <row r="149" ht="42" customHeight="1" s="85">
-      <c r="A149" s="52" t="inlineStr">
-        <is>
-          <t>Varena</t>
-        </is>
-      </c>
-      <c r="B149" s="53">
-        <f>COUNTIF($B$150:$B$150,"Varena")</f>
-        <v/>
-      </c>
-      <c r="C149" s="54" t="n"/>
-      <c r="D149" s="54" t="n"/>
-      <c r="E149" s="54" t="n"/>
-      <c r="F149" s="55" t="n"/>
-      <c r="G149" s="66" t="n"/>
-      <c r="H149" s="67" t="n"/>
-      <c r="I149" s="67" t="n"/>
-      <c r="J149" s="67" t="n"/>
+      <c r="I148" s="76" t="n"/>
+      <c r="J148" s="76" t="n"/>
+    </row>
+    <row r="149" s="85">
+      <c r="A149" s="27" t="n"/>
+      <c r="B149" s="28" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C149" s="56" t="inlineStr">
+        <is>
+          <t>Brawl Handler</t>
+        </is>
+      </c>
+      <c r="D149" s="63" t="inlineStr">
+        <is>
+          <t>Remove all your Clamps when you change the ball</t>
+        </is>
+      </c>
+      <c r="E149" s="58" t="n"/>
+      <c r="F149" s="61" t="n"/>
+      <c r="G149" s="75" t="n"/>
+      <c r="H149" s="76" t="n"/>
     </row>
     <row r="150" s="85">
       <c r="A150" s="27" t="n"/>
       <c r="B150" s="28" t="inlineStr">
         <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C150" s="56" t="inlineStr">
+        <is>
+          <t>Baller</t>
+        </is>
+      </c>
+      <c r="D150" s="63" t="inlineStr">
+        <is>
+          <t>Draw 1 card each time you change the ball</t>
+        </is>
+      </c>
+      <c r="E150" s="58" t="n"/>
+      <c r="F150" s="61" t="n"/>
+      <c r="G150" s="75" t="n"/>
+      <c r="H150" s="76" t="n"/>
+    </row>
+    <row r="151" ht="42" customHeight="1" s="85">
+      <c r="A151" s="52" t="inlineStr">
+        <is>
           <t>Varena</t>
         </is>
       </c>
-      <c r="C150" s="56" t="inlineStr">
+      <c r="B151" s="53">
+        <f>COUNTIF($B$152:$B$180,"Varena")</f>
+        <v/>
+      </c>
+      <c r="C151" s="54" t="n"/>
+      <c r="D151" s="54" t="n"/>
+      <c r="E151" s="54" t="n"/>
+      <c r="F151" s="55" t="n"/>
+      <c r="G151" s="66" t="n"/>
+      <c r="H151" s="67" t="n"/>
+      <c r="I151" s="67" t="n"/>
+      <c r="J151" s="67" t="n"/>
+    </row>
+    <row r="152" s="85">
+      <c r="A152" s="27" t="n"/>
+      <c r="B152" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C152" s="56" t="inlineStr">
         <is>
           <t>Cardwood</t>
         </is>
       </c>
-      <c r="D150" s="63" t="inlineStr">
+      <c r="D152" s="63" t="inlineStr">
         <is>
           <t>Changes the court back to basic</t>
         </is>
       </c>
-      <c r="E150" s="58" t="n"/>
-      <c r="F150" s="61" t="n">
+      <c r="E152" s="58" t="n"/>
+      <c r="F152" s="61" t="n">
         <v>5</v>
       </c>
-      <c r="G150" s="75" t="inlineStr">
+      <c r="G152" s="75" t="inlineStr">
         <is>
           <t>Also the floor every game opens on, before anybody plays a Varena over it</t>
         </is>
       </c>
-      <c r="H150" s="76" t="n"/>
-      <c r="I150" s="76" t="n"/>
-      <c r="J150" s="76" t="n"/>
+      <c r="H152" s="76" t="n"/>
+      <c r="I152" s="76" t="n"/>
+      <c r="J152" s="76" t="n"/>
+    </row>
+    <row r="153" s="85">
+      <c r="A153" s="27" t="n"/>
+      <c r="B153" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C153" s="56" t="inlineStr">
+        <is>
+          <t>Prime Parquet</t>
+        </is>
+      </c>
+      <c r="D153" s="63" t="inlineStr">
+        <is>
+          <t>SHOT +10% on every shot</t>
+        </is>
+      </c>
+      <c r="E153" s="58" t="n"/>
+      <c r="F153" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G153" s="75" t="n"/>
+      <c r="H153" s="76" t="n"/>
+      <c r="I153" s="76" t="n"/>
+      <c r="J153" s="76" t="n"/>
+    </row>
+    <row r="154" s="85">
+      <c r="A154" s="27" t="n"/>
+      <c r="B154" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C154" s="56" t="inlineStr">
+        <is>
+          <t>Lacktop</t>
+        </is>
+      </c>
+      <c r="D154" s="63" t="inlineStr">
+        <is>
+          <t>SHOT -10% on every shot</t>
+        </is>
+      </c>
+      <c r="E154" s="58" t="n"/>
+      <c r="F154" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G154" s="75" t="n"/>
+      <c r="H154" s="76" t="n"/>
+      <c r="I154" s="76" t="n"/>
+      <c r="J154" s="76" t="n"/>
+    </row>
+    <row r="155" s="85">
+      <c r="A155" s="27" t="n"/>
+      <c r="B155" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C155" s="56" t="inlineStr">
+        <is>
+          <t>Smacktop</t>
+        </is>
+      </c>
+      <c r="D155" s="63" t="inlineStr">
+        <is>
+          <t>Clear All Whistles. Whistles Cannot Be Played. All Clamps are enhanced</t>
+        </is>
+      </c>
+      <c r="E155" s="58" t="n"/>
+      <c r="F155" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G155" s="75" t="inlineStr">
+        <is>
+          <t>Enhanced: +10% more reduction, one more card discarded, one more card locked</t>
+        </is>
+      </c>
+      <c r="H155" s="76" t="n"/>
+      <c r="I155" s="76" t="n"/>
+      <c r="J155" s="76" t="n"/>
+    </row>
+    <row r="156" s="85">
+      <c r="A156" s="27" t="n"/>
+      <c r="B156" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C156" s="56" t="inlineStr">
+        <is>
+          <t>Boarder Court</t>
+        </is>
+      </c>
+      <c r="D156" s="63" t="inlineStr">
+        <is>
+          <t>Off your own miss, your Rebound bid counts as one card more</t>
+        </is>
+      </c>
+      <c r="E156" s="58" t="n"/>
+      <c r="F156" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="75" t="inlineStr">
+        <is>
+          <t>Still needs a bid of at least one</t>
+        </is>
+      </c>
+      <c r="H156" s="76" t="n"/>
+      <c r="I156" s="76" t="n"/>
+      <c r="J156" s="76" t="n"/>
+    </row>
+    <row r="157" s="85">
+      <c r="A157" s="27" t="n"/>
+      <c r="B157" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C157" s="56" t="inlineStr">
+        <is>
+          <t>Dim Dome</t>
+        </is>
+      </c>
+      <c r="D157" s="63" t="inlineStr">
+        <is>
+          <t>SHOT is hidden from everyone but the ball holder</t>
+        </is>
+      </c>
+      <c r="E157" s="58" t="n"/>
+      <c r="F157" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="75" t="inlineStr">
+        <is>
+          <t>On a table, flip the % device face down</t>
+        </is>
+      </c>
+      <c r="H157" s="76" t="n"/>
+      <c r="I157" s="76" t="n"/>
+      <c r="J157" s="76" t="n"/>
+    </row>
+    <row r="158" s="85">
+      <c r="A158" s="27" t="n"/>
+      <c r="B158" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C158" s="56" t="inlineStr">
+        <is>
+          <t>Tri-hard Tiling</t>
+        </is>
+      </c>
+      <c r="D158" s="63" t="inlineStr">
+        <is>
+          <t>Hand limit 3</t>
+        </is>
+      </c>
+      <c r="E158" s="58" t="n"/>
+      <c r="F158" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G158" s="75" t="inlineStr">
+        <is>
+          <t>Hands over 3 are cut to 3 when it lands (owner picks). A draw into a hand of 3 is discarded</t>
+        </is>
+      </c>
+      <c r="H158" s="76" t="n"/>
+      <c r="I158" s="76" t="n"/>
+      <c r="J158" s="76" t="n"/>
+    </row>
+    <row r="159" s="85">
+      <c r="A159" s="27" t="n"/>
+      <c r="B159" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C159" s="56" t="inlineStr">
+        <is>
+          <t>Policeum</t>
+        </is>
+      </c>
+      <c r="D159" s="63" t="inlineStr">
+        <is>
+          <t>Referees do not leave once triggered</t>
+        </is>
+      </c>
+      <c r="E159" s="58" t="n"/>
+      <c r="F159" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G159" s="75" t="inlineStr">
+        <is>
+          <t>A called referee stays until the floor changes. The 3-ref cap bounds it</t>
+        </is>
+      </c>
+      <c r="H159" s="76" t="n"/>
+      <c r="I159" s="76" t="n"/>
+      <c r="J159" s="76" t="n"/>
+    </row>
+    <row r="160" s="85">
+      <c r="A160" s="27" t="n"/>
+      <c r="B160" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C160" s="56" t="inlineStr">
+        <is>
+          <t>Kiddie Court</t>
+        </is>
+      </c>
+      <c r="D160" s="63" t="inlineStr">
+        <is>
+          <t>No threes. Every make counts 2. SHOT +10%, and dunks +10% more</t>
+        </is>
+      </c>
+      <c r="E160" s="58" t="n"/>
+      <c r="F160" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G160" s="75" t="inlineStr">
+        <is>
+          <t>Shuts off every card that makes a three (Kick-Out)</t>
+        </is>
+      </c>
+      <c r="H160" s="76" t="n"/>
+      <c r="I160" s="76" t="n"/>
+      <c r="J160" s="76" t="n"/>
+    </row>
+    <row r="161" s="85">
+      <c r="A161" s="27" t="n"/>
+      <c r="B161" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C161" s="56" t="inlineStr">
+        <is>
+          <t>Recharging Resin</t>
+        </is>
+      </c>
+      <c r="D161" s="63" t="inlineStr">
+        <is>
+          <t>Everyone refills to a hand of 5 at the start of their possession</t>
+        </is>
+      </c>
+      <c r="E161" s="58" t="n"/>
+      <c r="F161" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G161" s="75" t="inlineStr">
+        <is>
+          <t>After the draw for turn</t>
+        </is>
+      </c>
+      <c r="H161" s="76" t="n"/>
+      <c r="I161" s="76" t="n"/>
+      <c r="J161" s="76" t="n"/>
+    </row>
+    <row r="162" s="85">
+      <c r="A162" s="27" t="n"/>
+      <c r="B162" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C162" s="56" t="inlineStr">
+        <is>
+          <t>Contact Court</t>
+        </is>
+      </c>
+      <c r="D162" s="63" t="inlineStr">
+        <is>
+          <t>Being clamped: take 1 FT. The Clamp still lands</t>
+        </is>
+      </c>
+      <c r="E162" s="58" t="n"/>
+      <c r="F162" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G162" s="75" t="inlineStr">
+        <is>
+          <t>One free throw however many Clamps land</t>
+        </is>
+      </c>
+      <c r="H162" s="76" t="n"/>
+      <c r="I162" s="76" t="n"/>
+      <c r="J162" s="76" t="n"/>
+    </row>
+    <row r="163" s="85">
+      <c r="A163" s="27" t="n"/>
+      <c r="B163" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C163" s="56" t="inlineStr">
+        <is>
+          <t>MVPiquia</t>
+        </is>
+      </c>
+      <c r="D163" s="63" t="inlineStr">
+        <is>
+          <t>The highest scorer refills to 5 at the start of their possession</t>
+        </is>
+      </c>
+      <c r="E163" s="58" t="n"/>
+      <c r="F163" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="75" t="inlineStr">
+        <is>
+          <t>A tie for the lead counts</t>
+        </is>
+      </c>
+      <c r="H163" s="76" t="n"/>
+      <c r="I163" s="76" t="n"/>
+      <c r="J163" s="76" t="n"/>
+    </row>
+    <row r="164" s="85">
+      <c r="A164" s="27" t="n"/>
+      <c r="B164" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C164" s="56" t="inlineStr">
+        <is>
+          <t>Polypaypylene</t>
+        </is>
+      </c>
+      <c r="D164" s="63" t="inlineStr">
+        <is>
+          <t>Making a shot: Draw 3</t>
+        </is>
+      </c>
+      <c r="E164" s="58" t="n"/>
+      <c r="F164" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="75" t="n"/>
+      <c r="H164" s="76" t="n"/>
+      <c r="I164" s="76" t="n"/>
+      <c r="J164" s="76" t="n"/>
+    </row>
+    <row r="165" s="85">
+      <c r="A165" s="27" t="n"/>
+      <c r="B165" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C165" s="56" t="inlineStr">
+        <is>
+          <t>Recoverena</t>
+        </is>
+      </c>
+      <c r="D165" s="63" t="inlineStr">
+        <is>
+          <t>Discard all Injuries. A new Injury is discarded, and that player draws 1</t>
+        </is>
+      </c>
+      <c r="E165" s="58" t="n"/>
+      <c r="F165" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G165" s="75" t="inlineStr">
+        <is>
+          <t>Every player's Injuries go when it lands</t>
+        </is>
+      </c>
+      <c r="H165" s="76" t="n"/>
+      <c r="I165" s="76" t="n"/>
+      <c r="J165" s="76" t="n"/>
+    </row>
+    <row r="166" s="85">
+      <c r="A166" s="27" t="n"/>
+      <c r="B166" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C166" s="56" t="inlineStr">
+        <is>
+          <t>Carousel Court</t>
+        </is>
+      </c>
+      <c r="D166" s="63" t="inlineStr">
+        <is>
+          <t>Declare left or right. Every possession, hands move one seat that way</t>
+        </is>
+      </c>
+      <c r="E166" s="58" t="n"/>
+      <c r="F166" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="75" t="inlineStr">
+        <is>
+          <t>Declared by whoever plays it</t>
+        </is>
+      </c>
+      <c r="H166" s="76" t="n"/>
+      <c r="I166" s="76" t="n"/>
+      <c r="J166" s="76" t="n"/>
+    </row>
+    <row r="167" s="85">
+      <c r="A167" s="27" t="n"/>
+      <c r="B167" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C167" s="56" t="inlineStr">
+        <is>
+          <t>Traderous Tarmac</t>
+        </is>
+      </c>
+      <c r="D167" s="63" t="inlineStr">
+        <is>
+          <t>During your turn, hand off any number of the Clamps on you to other players</t>
+        </is>
+      </c>
+      <c r="E167" s="58" t="n"/>
+      <c r="F167" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="75" t="inlineStr">
+        <is>
+          <t>The player assigns each Clamp: all to one player, one each, or any split</t>
+        </is>
+      </c>
+      <c r="H167" s="76" t="n"/>
+      <c r="I167" s="76" t="n"/>
+      <c r="J167" s="76" t="n"/>
+    </row>
+    <row r="168" s="85">
+      <c r="A168" s="27" t="n"/>
+      <c r="B168" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C168" s="56" t="inlineStr">
+        <is>
+          <t>Clearcoat Court</t>
+        </is>
+      </c>
+      <c r="D168" s="63" t="inlineStr">
+        <is>
+          <t>Every possession: clear all referees, Clamps, Injuries and Intangibles</t>
+        </is>
+      </c>
+      <c r="E168" s="58" t="n"/>
+      <c r="F168" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G168" s="75" t="inlineStr">
+        <is>
+          <t>Standing Clamps only; Clamps still in the air land after the wipe</t>
+        </is>
+      </c>
+      <c r="H168" s="76" t="n"/>
+      <c r="I168" s="76" t="n"/>
+      <c r="J168" s="76" t="n"/>
+    </row>
+    <row r="169" s="85">
+      <c r="A169" s="27" t="n"/>
+      <c r="B169" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C169" s="56" t="inlineStr">
+        <is>
+          <t>Malice Palace</t>
+        </is>
+      </c>
+      <c r="D169" s="63" t="inlineStr">
+        <is>
+          <t>At the start of your possession, before your draw: discard your hand</t>
+        </is>
+      </c>
+      <c r="E169" s="58" t="n"/>
+      <c r="F169" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="75" t="n"/>
+      <c r="H169" s="76" t="n"/>
+      <c r="I169" s="76" t="n"/>
+      <c r="J169" s="76" t="n"/>
+    </row>
+    <row r="170" s="85">
+      <c r="A170" s="27" t="n"/>
+      <c r="B170" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C170" s="56" t="inlineStr">
+        <is>
+          <t>Turnstile Tile</t>
+        </is>
+      </c>
+      <c r="D170" s="63" t="inlineStr">
+        <is>
+          <t>SHOT +25% and -25%, alternating each possession</t>
+        </is>
+      </c>
+      <c r="E170" s="58" t="n"/>
+      <c r="F170" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G170" s="75" t="inlineStr">
+        <is>
+          <t>+25% the possession it lands</t>
+        </is>
+      </c>
+      <c r="H170" s="76" t="n"/>
+      <c r="I170" s="76" t="n"/>
+      <c r="J170" s="76" t="n"/>
+    </row>
+    <row r="171" s="85">
+      <c r="A171" s="27" t="n"/>
+      <c r="B171" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C171" s="56" t="inlineStr">
+        <is>
+          <t>Roleplayer Polymer</t>
+        </is>
+      </c>
+      <c r="D171" s="63" t="inlineStr">
+        <is>
+          <t>Every possession, everyone but the turn player draws 1</t>
+        </is>
+      </c>
+      <c r="E171" s="58" t="n"/>
+      <c r="F171" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G171" s="75" t="n"/>
+      <c r="H171" s="76" t="n"/>
+      <c r="I171" s="76" t="n"/>
+      <c r="J171" s="76" t="n"/>
+    </row>
+    <row r="172" s="85">
+      <c r="A172" s="27" t="n"/>
+      <c r="B172" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C172" s="56" t="inlineStr">
+        <is>
+          <t>Variaball Vinyl</t>
+        </is>
+      </c>
+      <c r="D172" s="63" t="inlineStr">
+        <is>
+          <t>The draw for turn goes to a random player each possession</t>
+        </is>
+      </c>
+      <c r="E172" s="58" t="n"/>
+      <c r="F172" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="75" t="inlineStr">
+        <is>
+          <t>Can be the turn player</t>
+        </is>
+      </c>
+      <c r="H172" s="76" t="n"/>
+      <c r="I172" s="76" t="n"/>
+      <c r="J172" s="76" t="n"/>
+    </row>
+    <row r="173" s="85">
+      <c r="A173" s="27" t="n"/>
+      <c r="B173" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C173" s="56" t="inlineStr">
+        <is>
+          <t>Gravi-Gym</t>
+        </is>
+      </c>
+      <c r="D173" s="63" t="inlineStr">
+        <is>
+          <t>SHOT -10%. No dunks</t>
+        </is>
+      </c>
+      <c r="E173" s="58" t="n"/>
+      <c r="F173" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G173" s="75" t="inlineStr">
+        <is>
+          <t>Cards that dunk cannot be played</t>
+        </is>
+      </c>
+      <c r="H173" s="76" t="n"/>
+      <c r="I173" s="76" t="n"/>
+      <c r="J173" s="76" t="n"/>
+    </row>
+    <row r="174" s="85">
+      <c r="A174" s="27" t="n"/>
+      <c r="B174" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C174" s="56" t="inlineStr">
+        <is>
+          <t>Vintage Varnish</t>
+        </is>
+      </c>
+      <c r="D174" s="63" t="inlineStr">
+        <is>
+          <t>Shot Clock 14. No threes. No Variaballs. 1 Intangible per player</t>
+        </is>
+      </c>
+      <c r="E174" s="58" t="n"/>
+      <c r="F174" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G174" s="75" t="inlineStr">
+        <is>
+          <t>Discards the ball in play when it lands</t>
+        </is>
+      </c>
+      <c r="H174" s="76" t="n"/>
+      <c r="I174" s="76" t="n"/>
+      <c r="J174" s="76" t="n"/>
+    </row>
+    <row r="175" s="85">
+      <c r="A175" s="27" t="n"/>
+      <c r="B175" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C175" s="56" t="inlineStr">
+        <is>
+          <t>S.O.S — Sell-Out Stadium</t>
+        </is>
+      </c>
+      <c r="D175" s="63" t="inlineStr">
+        <is>
+          <t>A three can be shot as a two at double SHOT</t>
+        </is>
+      </c>
+      <c r="E175" s="58" t="n"/>
+      <c r="F175" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G175" s="75" t="inlineStr">
+        <is>
+          <t>Keeps every other printed effect</t>
+        </is>
+      </c>
+      <c r="H175" s="76" t="n"/>
+      <c r="I175" s="76" t="n"/>
+      <c r="J175" s="76" t="n"/>
+    </row>
+    <row r="176" s="85">
+      <c r="A176" s="27" t="n"/>
+      <c r="B176" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C176" s="56" t="inlineStr">
+        <is>
+          <t>Grayvstone</t>
+        </is>
+      </c>
+      <c r="D176" s="63" t="inlineStr">
+        <is>
+          <t>Each possession, the ball becomes the last Variaball in the discards</t>
+        </is>
+      </c>
+      <c r="E176" s="58" t="n"/>
+      <c r="F176" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="75" t="inlineStr">
+        <is>
+          <t>With none there, nothing happens</t>
+        </is>
+      </c>
+      <c r="H176" s="76" t="n"/>
+      <c r="I176" s="76" t="n"/>
+      <c r="J176" s="76" t="n"/>
+    </row>
+    <row r="177" s="85">
+      <c r="A177" s="27" t="n"/>
+      <c r="B177" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C177" s="56" t="inlineStr">
+        <is>
+          <t>Con-crete</t>
+        </is>
+      </c>
+      <c r="D177" s="63" t="inlineStr">
+        <is>
+          <t>Move cards: SHOT -10%</t>
+        </is>
+      </c>
+      <c r="E177" s="58" t="n"/>
+      <c r="F177" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G177" s="75" t="n"/>
+      <c r="H177" s="76" t="n"/>
+      <c r="I177" s="76" t="n"/>
+      <c r="J177" s="76" t="n"/>
+    </row>
+    <row r="178" s="85">
+      <c r="A178" s="27" t="n"/>
+      <c r="B178" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C178" s="56" t="inlineStr">
+        <is>
+          <t>Spazzphalt</t>
+        </is>
+      </c>
+      <c r="D178" s="63" t="inlineStr">
+        <is>
+          <t>SHOT = a random 0–100%, in steps of 5</t>
+        </is>
+      </c>
+      <c r="E178" s="58" t="n"/>
+      <c r="F178" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G178" s="75" t="inlineStr">
+        <is>
+          <t>Rolled fresh for every shot</t>
+        </is>
+      </c>
+      <c r="H178" s="76" t="n"/>
+      <c r="I178" s="76" t="n"/>
+      <c r="J178" s="76" t="n"/>
+    </row>
+    <row r="179" s="85">
+      <c r="A179" s="27" t="n"/>
+      <c r="B179" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C179" s="56" t="inlineStr">
+        <is>
+          <t>Frostbite Finish</t>
+        </is>
+      </c>
+      <c r="D179" s="63" t="inlineStr">
+        <is>
+          <t>Playing a Move costs discarding 1 other card</t>
+        </is>
+      </c>
+      <c r="E179" s="58" t="n"/>
+      <c r="F179" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" s="75" t="inlineStr">
+        <is>
+          <t>The owner picks the card. A Move that is your whole hand can't be played</t>
+        </is>
+      </c>
+      <c r="H179" s="76" t="n"/>
+      <c r="I179" s="76" t="n"/>
+      <c r="J179" s="76" t="n"/>
+    </row>
+    <row r="180" s="85">
+      <c r="A180" s="27" t="n"/>
+      <c r="B180" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C180" s="56" t="inlineStr">
+        <is>
+          <t>Tick-Tock Tile</t>
+        </is>
+      </c>
+      <c r="D180" s="63" t="inlineStr">
+        <is>
+          <t>Playing any card also ticks the Shot Clock</t>
+        </is>
+      </c>
+      <c r="E180" s="58" t="n"/>
+      <c r="F180" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G180" s="75" t="inlineStr">
+        <is>
+          <t>The tick is paid after the card resolves, so a shot at 01 still goes up</t>
+        </is>
+      </c>
+      <c r="H180" s="76" t="n"/>
+      <c r="I180" s="76" t="n"/>
+      <c r="J180" s="76" t="n"/>
+    </row>
+    <row r="181" ht="42" customHeight="1" s="85">
+      <c r="A181" s="52" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="B181" s="53">
+        <f>COUNTIF($B$182:$B$197,"Variaball")</f>
+        <v/>
+      </c>
+      <c r="C181" s="54" t="n"/>
+      <c r="D181" s="54" t="n"/>
+      <c r="E181" s="54" t="n"/>
+      <c r="F181" s="55" t="n"/>
+      <c r="G181" s="66" t="n"/>
+      <c r="H181" s="67" t="n"/>
+      <c r="I181" s="67" t="n"/>
+      <c r="J181" s="67" t="n"/>
+    </row>
+    <row r="182" s="85">
+      <c r="A182" s="27" t="n"/>
+      <c r="B182" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C182" s="56" t="inlineStr">
+        <is>
+          <t>Med Ball</t>
+        </is>
+      </c>
+      <c r="D182" s="63" t="inlineStr">
+        <is>
+          <t>SHOT cannot exceed 50%</t>
+        </is>
+      </c>
+      <c r="E182" s="58" t="n"/>
+      <c r="F182" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G182" s="75" t="inlineStr">
+        <is>
+          <t>An Intangible's or a Varena's SHOT = is not held to it</t>
+        </is>
+      </c>
+      <c r="H182" s="76" t="n"/>
+      <c r="I182" s="76" t="n"/>
+      <c r="J182" s="76" t="n"/>
+    </row>
+    <row r="183" s="85">
+      <c r="A183" s="27" t="n"/>
+      <c r="B183" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C183" s="56" t="inlineStr">
+        <is>
+          <t>Dishcount Ball</t>
+        </is>
+      </c>
+      <c r="D183" s="63" t="inlineStr">
+        <is>
+          <t>Discard one fewer for card costs and Clamps</t>
+        </is>
+      </c>
+      <c r="E183" s="58" t="n"/>
+      <c r="F183" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G183" s="75" t="inlineStr">
+        <is>
+          <t>Counts: Clamps, Pound Dribble, Frostbite Finish, Stepback, Turnaround Three</t>
+        </is>
+      </c>
+      <c r="H183" s="76" t="n"/>
+      <c r="I183" s="76" t="n"/>
+      <c r="J183" s="76" t="n"/>
+    </row>
+    <row r="184" s="85">
+      <c r="A184" s="27" t="n"/>
+      <c r="B184" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C184" s="56" t="inlineStr">
+        <is>
+          <t>Blight Ball</t>
+        </is>
+      </c>
+      <c r="D184" s="63" t="inlineStr">
+        <is>
+          <t>Injuries travel with the ball, and new ones join the pile. Discarding the ball takes the pile with it</t>
+        </is>
+      </c>
+      <c r="E184" s="58" t="n"/>
+      <c r="F184" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G184" s="75" t="inlineStr">
+        <is>
+          <t>Moves on any change of hands</t>
+        </is>
+      </c>
+      <c r="H184" s="76" t="n"/>
+      <c r="I184" s="76" t="n"/>
+      <c r="J184" s="76" t="n"/>
+    </row>
+    <row r="185" s="85">
+      <c r="A185" s="27" t="n"/>
+      <c r="B185" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C185" s="56" t="inlineStr">
+        <is>
+          <t>Bench Ball</t>
+        </is>
+      </c>
+      <c r="D185" s="63" t="inlineStr">
+        <is>
+          <t>Receiving it by Pass: no draw, no turn. You inbound</t>
+        </is>
+      </c>
+      <c r="E185" s="58" t="n"/>
+      <c r="F185" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="75" t="n"/>
+      <c r="H185" s="76" t="n"/>
+      <c r="I185" s="76" t="n"/>
+      <c r="J185" s="76" t="n"/>
+    </row>
+    <row r="186" s="85">
+      <c r="A186" s="27" t="n"/>
+      <c r="B186" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C186" s="56" t="inlineStr">
+        <is>
+          <t>Dishtracting Ball</t>
+        </is>
+      </c>
+      <c r="D186" s="63" t="inlineStr">
+        <is>
+          <t>Receiving it: discard 1, after the draw for turn</t>
+        </is>
+      </c>
+      <c r="E186" s="58" t="n"/>
+      <c r="F186" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" s="75" t="inlineStr">
+        <is>
+          <t>Any change of hands</t>
+        </is>
+      </c>
+      <c r="H186" s="76" t="n"/>
+      <c r="I186" s="76" t="n"/>
+      <c r="J186" s="76" t="n"/>
+    </row>
+    <row r="187" s="85">
+      <c r="A187" s="27" t="n"/>
+      <c r="B187" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C187" s="56" t="inlineStr">
+        <is>
+          <t>Hand Ball</t>
+        </is>
+      </c>
+      <c r="D187" s="63" t="inlineStr">
+        <is>
+          <t>A Pass swaps hands: yours goes with the ball, theirs comes back</t>
+        </is>
+      </c>
+      <c r="E187" s="58" t="n"/>
+      <c r="F187" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" s="75" t="n"/>
+      <c r="H187" s="76" t="n"/>
+      <c r="I187" s="76" t="n"/>
+      <c r="J187" s="76" t="n"/>
+    </row>
+    <row r="188" s="85">
+      <c r="A188" s="27" t="n"/>
+      <c r="B188" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C188" s="56" t="inlineStr">
+        <is>
+          <t>Foot Ball</t>
+        </is>
+      </c>
+      <c r="D188" s="63" t="inlineStr">
+        <is>
+          <t>Moves and Passes are not spent. They lock until your possession ends</t>
+        </is>
+      </c>
+      <c r="E188" s="58" t="n"/>
+      <c r="F188" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="75" t="n"/>
+      <c r="H188" s="76" t="n"/>
+      <c r="I188" s="76" t="n"/>
+      <c r="J188" s="76" t="n"/>
+    </row>
+    <row r="189" s="85">
+      <c r="A189" s="27" t="n"/>
+      <c r="B189" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C189" s="56" t="inlineStr">
+        <is>
+          <t>Recharge Rock</t>
+        </is>
+      </c>
+      <c r="D189" s="63" t="inlineStr">
+        <is>
+          <t>Double your draw for turn</t>
+        </is>
+      </c>
+      <c r="E189" s="58" t="n"/>
+      <c r="F189" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G189" s="75" t="n"/>
+      <c r="H189" s="76" t="n"/>
+      <c r="I189" s="76" t="n"/>
+      <c r="J189" s="76" t="n"/>
+    </row>
+    <row r="190" s="85">
+      <c r="A190" s="27" t="n"/>
+      <c r="B190" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C190" s="56" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="D190" s="63" t="inlineStr">
+        <is>
+          <t>A random Variaball from the discards goes into play. Then discard this</t>
+        </is>
+      </c>
+      <c r="E190" s="58" t="n"/>
+      <c r="F190" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="75" t="inlineStr">
+        <is>
+          <t>From the deck if the discards have none; never the ball already in play</t>
+        </is>
+      </c>
+      <c r="H190" s="76" t="n"/>
+      <c r="I190" s="76" t="n"/>
+      <c r="J190" s="76" t="n"/>
+    </row>
+    <row r="191" s="85">
+      <c r="A191" s="27" t="n"/>
+      <c r="B191" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C191" s="56" t="inlineStr">
+        <is>
+          <t>Shufflebag Ball</t>
+        </is>
+      </c>
+      <c r="D191" s="63" t="inlineStr">
+        <is>
+          <t>Every possession, the turn player shuffles their hand into the deck and draws the same number, then draws for turn</t>
+        </is>
+      </c>
+      <c r="E191" s="58" t="n"/>
+      <c r="F191" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="75" t="n"/>
+      <c r="H191" s="76" t="n"/>
+      <c r="I191" s="76" t="n"/>
+      <c r="J191" s="76" t="n"/>
+    </row>
+    <row r="192" s="85">
+      <c r="A192" s="27" t="n"/>
+      <c r="B192" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C192" s="56" t="inlineStr">
+        <is>
+          <t>Bag'n Ball</t>
+        </is>
+      </c>
+      <c r="D192" s="63" t="inlineStr">
+        <is>
+          <t>Draw 1 on activation. SHOT = 10% for each card in your hand</t>
+        </is>
+      </c>
+      <c r="E192" s="58" t="n"/>
+      <c r="F192" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="75" t="n"/>
+      <c r="H192" s="76" t="n"/>
+      <c r="I192" s="76" t="n"/>
+      <c r="J192" s="76" t="n"/>
+    </row>
+    <row r="193" s="85">
+      <c r="A193" s="27" t="n"/>
+      <c r="B193" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C193" s="56" t="inlineStr">
+        <is>
+          <t>Blaze Ball</t>
+        </is>
+      </c>
+      <c r="D193" s="63" t="inlineStr">
+        <is>
+          <t>SHOT +10% each time it's passed</t>
+        </is>
+      </c>
+      <c r="E193" s="58" t="n"/>
+      <c r="F193" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G193" s="75" t="inlineStr">
+        <is>
+          <t>Ignores every other pass modifier</t>
+        </is>
+      </c>
+      <c r="H193" s="76" t="n"/>
+      <c r="I193" s="76" t="n"/>
+      <c r="J193" s="76" t="n"/>
+    </row>
+    <row r="194" s="85">
+      <c r="A194" s="27" t="n"/>
+      <c r="B194" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C194" s="56" t="inlineStr">
+        <is>
+          <t>Snow Ball It</t>
+        </is>
+      </c>
+      <c r="D194" s="63" t="inlineStr">
+        <is>
+          <t>SHOT -10% each time it's passed</t>
+        </is>
+      </c>
+      <c r="E194" s="58" t="n"/>
+      <c r="F194" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G194" s="75" t="inlineStr">
+        <is>
+          <t>Ignores every other pass modifier</t>
+        </is>
+      </c>
+      <c r="H194" s="76" t="n"/>
+      <c r="I194" s="76" t="n"/>
+      <c r="J194" s="76" t="n"/>
+    </row>
+    <row r="195" s="85">
+      <c r="A195" s="27" t="n"/>
+      <c r="B195" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C195" s="56" t="inlineStr">
+        <is>
+          <t>Brick Ball</t>
+        </is>
+      </c>
+      <c r="D195" s="63" t="inlineStr">
+        <is>
+          <t>SHOT = 25%</t>
+        </is>
+      </c>
+      <c r="E195" s="58" t="n"/>
+      <c r="F195" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G195" s="75" t="n"/>
+      <c r="H195" s="76" t="n"/>
+      <c r="I195" s="76" t="n"/>
+      <c r="J195" s="76" t="n"/>
+    </row>
+    <row r="196" s="85">
+      <c r="A196" s="27" t="n"/>
+      <c r="B196" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C196" s="56" t="inlineStr">
+        <is>
+          <t>Monster Ball</t>
+        </is>
+      </c>
+      <c r="D196" s="63" t="inlineStr">
+        <is>
+          <t>Intangibles are absorbed into the ball. When it's discarded, players rebound for them one at a time</t>
+        </is>
+      </c>
+      <c r="E196" s="58" t="n"/>
+      <c r="F196" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="75" t="inlineStr">
+        <is>
+          <t>Swallows every Intangible already out and every one drawn while it's in play</t>
+        </is>
+      </c>
+      <c r="H196" s="76" t="n"/>
+      <c r="I196" s="76" t="n"/>
+      <c r="J196" s="76" t="n"/>
+    </row>
+    <row r="197" s="85">
+      <c r="A197" s="27" t="n"/>
+      <c r="B197" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C197" s="56" t="inlineStr">
+        <is>
+          <t>Brand New Ball</t>
+        </is>
+      </c>
+      <c r="D197" s="63" t="inlineStr">
+        <is>
+          <t>25% chance a shot attempt is a turnover instead</t>
+        </is>
+      </c>
+      <c r="E197" s="58" t="n"/>
+      <c r="F197" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G197" s="75" t="inlineStr">
+        <is>
+          <t>The round ends</t>
+        </is>
+      </c>
+      <c r="H197" s="76" t="n"/>
+      <c r="I197" s="76" t="n"/>
+      <c r="J197" s="76" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="128">
+  <mergeCells count="175">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="G4:J4"/>
-    <mergeCell ref="G135:J135"/>
+    <mergeCell ref="G182:J182"/>
+    <mergeCell ref="G188:J188"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
-    <mergeCell ref="G119:J119"/>
-    <mergeCell ref="G150:J150"/>
+    <mergeCell ref="G135:J135"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="G46:J46"/>
+    <mergeCell ref="G119:J119"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
+    <mergeCell ref="G159:J159"/>
+    <mergeCell ref="G193:J193"/>
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
+    <mergeCell ref="G161:J161"/>
+    <mergeCell ref="G5:J5"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G136:J136"/>
+    <mergeCell ref="G194:J194"/>
+    <mergeCell ref="G181:J181"/>
     <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G160:J160"/>
     <mergeCell ref="G82:J82"/>
+    <mergeCell ref="G174:J174"/>
+    <mergeCell ref="G156:J156"/>
     <mergeCell ref="G57:J57"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G137:J137"/>
+    <mergeCell ref="G66:J66"/>
     <mergeCell ref="G128:J128"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="G66:J66"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
+    <mergeCell ref="G171:J171"/>
+    <mergeCell ref="G189:J189"/>
     <mergeCell ref="G121:J121"/>
     <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
-    <mergeCell ref="G139:J139"/>
     <mergeCell ref="G108:J108"/>
     <mergeCell ref="G58:J58"/>
     <mergeCell ref="G114:J114"/>
     <mergeCell ref="G123:J123"/>
+    <mergeCell ref="G163:J163"/>
     <mergeCell ref="G110:J110"/>
+    <mergeCell ref="G168:J168"/>
+    <mergeCell ref="G113:J113"/>
     <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G113:J113"/>
     <mergeCell ref="G91:J91"/>
+    <mergeCell ref="G100:J100"/>
     <mergeCell ref="G85:J85"/>
-    <mergeCell ref="G100:J100"/>
+    <mergeCell ref="G183:J183"/>
+    <mergeCell ref="G165:J165"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="G84:J84"/>
     <mergeCell ref="G102:J102"/>
+    <mergeCell ref="G158:J158"/>
+    <mergeCell ref="G185:J185"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
+    <mergeCell ref="G86:J86"/>
     <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G86:J86"/>
+    <mergeCell ref="G178:J178"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="G61:J61"/>
     <mergeCell ref="G70:J70"/>
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G176:J176"/>
+    <mergeCell ref="G97:J97"/>
     <mergeCell ref="G125:J125"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G112:J112"/>
+    <mergeCell ref="G184:J184"/>
+    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="G191:J191"/>
     <mergeCell ref="G62:J62"/>
+    <mergeCell ref="G175:J175"/>
     <mergeCell ref="G127:J127"/>
+    <mergeCell ref="G162:J162"/>
     <mergeCell ref="G49:J49"/>
     <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G177:J177"/>
+    <mergeCell ref="G195:J195"/>
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="G104:J104"/>
     <mergeCell ref="G65:J65"/>
     <mergeCell ref="G88:J88"/>
     <mergeCell ref="G26:J26"/>
+    <mergeCell ref="G154:J154"/>
+    <mergeCell ref="G197:J197"/>
     <mergeCell ref="G35:J35"/>
     <mergeCell ref="G129:J129"/>
+    <mergeCell ref="G138:J138"/>
     <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G90:J90"/>
     <mergeCell ref="G76:J76"/>
     <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G99:J99"/>
     <mergeCell ref="G60:J60"/>
+    <mergeCell ref="G131:J131"/>
     <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G131:J131"/>
-    <mergeCell ref="G140:J140"/>
+    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="G130:J130"/>
+    <mergeCell ref="G115:J115"/>
     <mergeCell ref="G59:J59"/>
-    <mergeCell ref="G115:J115"/>
-    <mergeCell ref="G130:J130"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
+    <mergeCell ref="G169:J169"/>
+    <mergeCell ref="G179:J179"/>
+    <mergeCell ref="G132:J132"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G122:J122"/>
     <mergeCell ref="G126:J126"/>
-    <mergeCell ref="G39:J39"/>
-    <mergeCell ref="G132:J132"/>
-    <mergeCell ref="G122:J122"/>
+    <mergeCell ref="G166:J166"/>
+    <mergeCell ref="G116:J116"/>
     <mergeCell ref="G101:J101"/>
-    <mergeCell ref="G116:J116"/>
     <mergeCell ref="G103:J103"/>
     <mergeCell ref="G37:J37"/>
+    <mergeCell ref="G186:J186"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
+    <mergeCell ref="G152:J152"/>
     <mergeCell ref="G87:J87"/>
+    <mergeCell ref="G133:J133"/>
+    <mergeCell ref="G167:J167"/>
     <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G142:J142"/>
     <mergeCell ref="G80:J80"/>
-    <mergeCell ref="G95:J95"/>
     <mergeCell ref="G89:J89"/>
     <mergeCell ref="G64:J64"/>
     <mergeCell ref="G79:J79"/>
     <mergeCell ref="G73:J73"/>
     <mergeCell ref="G51:J51"/>
+    <mergeCell ref="G192:J192"/>
+    <mergeCell ref="G153:J153"/>
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="G63:J63"/>
+    <mergeCell ref="G134:J134"/>
     <mergeCell ref="G41:J41"/>
-    <mergeCell ref="G134:J134"/>
+    <mergeCell ref="G106:J106"/>
     <mergeCell ref="G50:J50"/>
-    <mergeCell ref="G106:J106"/>
+    <mergeCell ref="G164:J164"/>
+    <mergeCell ref="G173:J173"/>
     <mergeCell ref="G56:J56"/>
+    <mergeCell ref="G105:J105"/>
     <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
+    <mergeCell ref="G155:J155"/>
+    <mergeCell ref="G120:J120"/>
+    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G27:J27"/>
-    <mergeCell ref="G120:J120"/>
-    <mergeCell ref="G98:J98"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G170:J170"/>
+    <mergeCell ref="G157:J157"/>
+    <mergeCell ref="G141:J141"/>
     <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G172:J172"/>
+    <mergeCell ref="G93:J93"/>
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G190:J190"/>
+    <mergeCell ref="G187:J187"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G83:J83"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G133:J133"/>
-    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="G196:J196"/>
+    <mergeCell ref="G180:J180"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2339,7 +2339,11 @@
       <c r="F8" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="72" t="n"/>
+      <c r="G8" s="72" t="inlineStr">
+        <is>
+          <t>Dunked as the receiver's first action, it's the Alley-Oop combo: SHOT +10%. A receiver holding a dunk card is asked "Dunk It?"</t>
+        </is>
+      </c>
       <c r="H8" s="71" t="n"/>
       <c r="I8" s="71" t="n"/>
       <c r="J8" s="71" t="n"/>
@@ -2508,7 +2512,7 @@
       <c r="A15" s="21" t="n"/>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Retired Pass</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -2527,9 +2531,13 @@
         </is>
       </c>
       <c r="F15" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="72" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="72" t="inlineStr">
+        <is>
+          <t>Retired: now the Alley-Oop combo — a Lob, then any dunk card as the first action, SHOT +10%</t>
+        </is>
+      </c>
       <c r="H15" s="71" t="n"/>
       <c r="I15" s="71" t="n"/>
       <c r="J15" s="71" t="n"/>
@@ -3142,11 +3150,7 @@
 Tails: SHOT -10%</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E36" s="25" t="n"/>
       <c r="F36" s="36" t="n">
         <v>5</v>
       </c>
@@ -3172,11 +3176,7 @@
           <t>SHOT = 100%</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E37" s="6" t="n"/>
       <c r="F37" s="32" t="n">
         <v>5</v>
       </c>
@@ -3206,11 +3206,7 @@
           <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E38" s="25" t="n"/>
       <c r="F38" s="36" t="n">
         <v>5</v>
       </c>
@@ -3236,11 +3232,7 @@
           <t>SHOT -10%. Draw 1 card</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball.</t>
-        </is>
-      </c>
+      <c r="E39" s="6" t="n"/>
       <c r="F39" s="32" t="n">
         <v>10</v>
       </c>
@@ -3266,11 +3258,7 @@
           <t>SHOT -20%</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E40" s="25" t="n"/>
       <c r="F40" s="36" t="n">
         <v>3</v>
       </c>
@@ -3296,11 +3284,7 @@
           <t>SHOT -30%</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E41" s="6" t="n"/>
       <c r="F41" s="32" t="n">
         <v>3</v>
       </c>
@@ -3326,11 +3310,7 @@
           <t>SHOT = 25%</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E42" s="25" t="n"/>
       <c r="F42" s="36" t="n">
         <v>3</v>
       </c>
@@ -3358,7 +3338,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball. After a missed shot: SHOT = 100%</t>
+          <t>After a missed shot: SHOT = 100%</t>
         </is>
       </c>
       <c r="F43" s="32" t="n">
@@ -3388,7 +3368,7 @@
       </c>
       <c r="E44" s="41" t="inlineStr">
         <is>
-          <t>Shoot the ball. Shot is unaffected by Clamps</t>
+          <t>Shot is unaffected by Clamps</t>
         </is>
       </c>
       <c r="F44" s="36" t="n">
@@ -3418,7 +3398,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Shoot the ball. SHOT = 100% if SHOT &gt;= 75%</t>
+          <t>SHOT = 100% if SHOT &gt;= 75%</t>
         </is>
       </c>
       <c r="F45" s="32" t="n">
@@ -3446,11 +3426,7 @@
           <t>Discard any number of cards. SHOT +10% for each</t>
         </is>
       </c>
-      <c r="E46" s="25" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E46" s="25" t="n"/>
       <c r="F46" s="36" t="n">
         <v>1</v>
       </c>
@@ -3508,7 +3484,7 @@
       </c>
       <c r="E48" s="58" t="inlineStr">
         <is>
-          <t>Shoot the ball. Selected players receive +1 AST on a make</t>
+          <t>Selected players receive +1 AST on a make</t>
         </is>
       </c>
       <c r="F48" s="59" t="n">
@@ -3541,7 +3517,7 @@
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>Shoot the ball. Another +10% straight off your own board</t>
+          <t>Another +10% straight off your own board</t>
         </is>
       </c>
       <c r="F49" s="0" t="n">
@@ -3569,11 +3545,7 @@
           <t>Clean look only — no Clamps on you and nothing has gone off this possession. SHOT +30%</t>
         </is>
       </c>
-      <c r="E50" s="0" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E50" s="0" t="n"/>
       <c r="F50" s="0" t="n">
         <v>5</v>
       </c>
@@ -3599,11 +3571,7 @@
           <t>SHOT +15% at 50% or better, −15% under it</t>
         </is>
       </c>
-      <c r="E51" s="0" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E51" s="0" t="n"/>
       <c r="F51" s="0" t="n">
         <v>5</v>
       </c>
@@ -3629,11 +3597,7 @@
           <t>SHOT -10%</t>
         </is>
       </c>
-      <c r="E52" s="0" t="inlineStr">
-        <is>
-          <t>Shoot the ball</t>
-        </is>
-      </c>
+      <c r="E52" s="0" t="n"/>
       <c r="F52" s="0" t="n">
         <v>5</v>
       </c>
@@ -7515,23 +7479,21 @@
   </sheetData>
   <mergeCells count="175">
     <mergeCell ref="G55:J55"/>
+    <mergeCell ref="G188:J188"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G182:J182"/>
-    <mergeCell ref="G188:J188"/>
+    <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
-    <mergeCell ref="G135:J135"/>
+    <mergeCell ref="G119:J119"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="G46:J46"/>
-    <mergeCell ref="G119:J119"/>
+    <mergeCell ref="G159:J159"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
-    <mergeCell ref="G159:J159"/>
-    <mergeCell ref="G193:J193"/>
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="G161:J161"/>
-    <mergeCell ref="G5:J5"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="G136:J136"/>
     <mergeCell ref="G194:J194"/>
@@ -7542,10 +7504,11 @@
     <mergeCell ref="G174:J174"/>
     <mergeCell ref="G156:J156"/>
     <mergeCell ref="G57:J57"/>
+    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G66:J66"/>
+    <mergeCell ref="G184:J184"/>
     <mergeCell ref="G137:J137"/>
-    <mergeCell ref="G66:J66"/>
-    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
     <mergeCell ref="G171:J171"/>
@@ -7564,12 +7527,13 @@
     <mergeCell ref="G113:J113"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="G91:J91"/>
+    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G100:J100"/>
-    <mergeCell ref="G85:J85"/>
     <mergeCell ref="G183:J183"/>
     <mergeCell ref="G165:J165"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
+    <mergeCell ref="G193:J193"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="G84:J84"/>
     <mergeCell ref="G102:J102"/>
@@ -7577,8 +7541,8 @@
     <mergeCell ref="G185:J185"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
+    <mergeCell ref="G21:J21"/>
     <mergeCell ref="G86:J86"/>
-    <mergeCell ref="G21:J21"/>
     <mergeCell ref="G178:J178"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="G61:J61"/>
@@ -7590,18 +7554,17 @@
     <mergeCell ref="G125:J125"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G191:J191"/>
     <mergeCell ref="G112:J112"/>
-    <mergeCell ref="G184:J184"/>
     <mergeCell ref="G45:J45"/>
-    <mergeCell ref="G191:J191"/>
     <mergeCell ref="G62:J62"/>
     <mergeCell ref="G175:J175"/>
     <mergeCell ref="G127:J127"/>
     <mergeCell ref="G162:J162"/>
     <mergeCell ref="G49:J49"/>
     <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G195:J195"/>
     <mergeCell ref="G177:J177"/>
-    <mergeCell ref="G195:J195"/>
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="G104:J104"/>
     <mergeCell ref="G65:J65"/>
@@ -7613,27 +7576,26 @@
     <mergeCell ref="G129:J129"/>
     <mergeCell ref="G138:J138"/>
     <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G90:J90"/>
     <mergeCell ref="G76:J76"/>
     <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G90:J90"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="G131:J131"/>
     <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G124:J124"/>
+    <mergeCell ref="G59:J59"/>
+    <mergeCell ref="G115:J115"/>
     <mergeCell ref="G130:J130"/>
-    <mergeCell ref="G115:J115"/>
-    <mergeCell ref="G59:J59"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
     <mergeCell ref="G169:J169"/>
     <mergeCell ref="G179:J179"/>
+    <mergeCell ref="G126:J126"/>
     <mergeCell ref="G132:J132"/>
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="G122:J122"/>
-    <mergeCell ref="G126:J126"/>
     <mergeCell ref="G166:J166"/>
+    <mergeCell ref="G101:J101"/>
     <mergeCell ref="G116:J116"/>
-    <mergeCell ref="G101:J101"/>
     <mergeCell ref="G103:J103"/>
     <mergeCell ref="G37:J37"/>
     <mergeCell ref="G186:J186"/>
@@ -7641,9 +7603,8 @@
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
+    <mergeCell ref="G87:J87"/>
     <mergeCell ref="G152:J152"/>
-    <mergeCell ref="G87:J87"/>
-    <mergeCell ref="G133:J133"/>
     <mergeCell ref="G167:J167"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G142:J142"/>
@@ -7651,44 +7612,47 @@
     <mergeCell ref="G89:J89"/>
     <mergeCell ref="G64:J64"/>
     <mergeCell ref="G79:J79"/>
+    <mergeCell ref="G192:J192"/>
     <mergeCell ref="G73:J73"/>
     <mergeCell ref="G51:J51"/>
-    <mergeCell ref="G192:J192"/>
     <mergeCell ref="G153:J153"/>
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="G63:J63"/>
     <mergeCell ref="G134:J134"/>
     <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G50:J50"/>
     <mergeCell ref="G106:J106"/>
-    <mergeCell ref="G50:J50"/>
     <mergeCell ref="G164:J164"/>
     <mergeCell ref="G173:J173"/>
     <mergeCell ref="G56:J56"/>
     <mergeCell ref="G105:J105"/>
-    <mergeCell ref="G14:J14"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
+    <mergeCell ref="G120:J120"/>
     <mergeCell ref="G155:J155"/>
-    <mergeCell ref="G120:J120"/>
-    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="G42:J42"/>
+    <mergeCell ref="G107:J107"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="G170:J170"/>
     <mergeCell ref="G157:J157"/>
     <mergeCell ref="G141:J141"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G172:J172"/>
+    <mergeCell ref="G190:J190"/>
+    <mergeCell ref="G28:J28"/>
     <mergeCell ref="G93:J93"/>
-    <mergeCell ref="G28:J28"/>
     <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G190:J190"/>
     <mergeCell ref="G187:J187"/>
     <mergeCell ref="G69:J69"/>
     <mergeCell ref="G83:J83"/>
     <mergeCell ref="G196:J196"/>
+    <mergeCell ref="G124:J124"/>
     <mergeCell ref="G180:J180"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G133:J133"/>
+    <mergeCell ref="G14:J14"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2302,12 +2302,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Pass to player of choice. SHOT +20%</t>
+          <t>SHOT +10%. Pass to target player.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>If new player scores that turn: AST +1</t>
+          <t>Extra AST + 1 if new player scores</t>
         </is>
       </c>
       <c r="F7" s="32" t="n">
@@ -2332,16 +2332,20 @@
       </c>
       <c r="D8" s="41" t="inlineStr">
         <is>
-          <t>SHOT +20%. Pass to player of choice. They must attempt a shot as their first action.</t>
-        </is>
-      </c>
-      <c r="E8" s="26" t="n"/>
+          <t>SHOT +10%. Pass to target player. They must shoot.</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>You may add current Ball to hand while passing.</t>
+        </is>
+      </c>
       <c r="F8" s="33" t="n">
         <v>5</v>
       </c>
       <c r="G8" s="72" t="inlineStr">
         <is>
-          <t>Dunked as the receiver's first action, it's the Alley-Oop combo: SHOT +10%. A receiver holding a dunk card is asked "Dunk It?"</t>
+          <t>Dunked as the receiver's first action, it's the Alley-Oop combo: SHOT +10% extra. A receiver holding a dunk card is asked "Dunk It?". The bonus takes the Ball out of play</t>
         </is>
       </c>
       <c r="H8" s="71" t="n"/>
@@ -2362,7 +2366,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Pass Left or Right. Move 1 card from new player to next player in same direction. SHOT +20%</t>
+          <t>SHOT +10%. Pass Left or Right. Knock 1 card to next player.</t>
         </is>
       </c>
       <c r="E9" s="7" t="n"/>
@@ -2466,10 +2470,14 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Pass to random other player. SHOT +20%</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
+          <t>SHOT +10%. Pass to random other player.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>You may flip a coin while passing. If Heads, draw 1 card.</t>
+        </is>
+      </c>
       <c r="F13" s="34" t="n">
         <v>5</v>
       </c>
@@ -2492,18 +2500,18 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>Pass to player of choice. SHOT +20%</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>New players discards 1 card at random</t>
-        </is>
-      </c>
+          <t>SHOT +10%. Pass to target player. Discard 1 card from their hand while passing</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n"/>
       <c r="F14" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="72" t="n"/>
+      <c r="G14" s="72" t="inlineStr">
+        <is>
+          <t>The passer picks the card, facedown</t>
+        </is>
+      </c>
       <c r="H14" s="71" t="n"/>
       <c r="I14" s="71" t="n"/>
       <c r="J14" s="71" t="n"/>
@@ -2556,20 +2564,16 @@
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>SHOT +20%. Pass to player to Left or Right. Draw 1 card</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>If played following a Dribble: draw 1 additional and SHOT +10% more</t>
-        </is>
-      </c>
+          <t>SHOT +10%. Pass left or right. Draw 1 card while passing.</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="n"/>
       <c r="F16" s="36" t="n">
         <v>5</v>
       </c>
       <c r="G16" s="72" t="inlineStr">
         <is>
-          <t>This is the Dribble Hand-Off</t>
+          <t>Combo DHO: after a Dribble, SHOT +10% and Draw 1 extra card</t>
         </is>
       </c>
       <c r="H16" s="71" t="n"/>
@@ -2590,16 +2594,20 @@
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>SHOT +20%. Shot Clock +01. Pass to player of choice</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n"/>
+          <t>SHOT +10%. Pass to target player. Shot Clock +01.</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>You may Reset the Shot Clock at the start of your next possession</t>
+        </is>
+      </c>
       <c r="F17" s="36" t="n">
         <v>5</v>
       </c>
       <c r="G17" s="72" t="inlineStr">
         <is>
-          <t>The clock increments instead of decrementing — it does not break even</t>
+          <t>Chosen when that possession starts</t>
         </is>
       </c>
       <c r="H17" s="71" t="n"/>
@@ -2620,10 +2628,14 @@
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>SHOT +10%. Draw 2 Cards. Move all your Clamps to Receiver, and they immediately attempt a three</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n"/>
+          <t>SHOT +10%. Pass to target player. They must immediately shoot a Three. Draw 2 cards while passing.</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>You may Assign all your Clamps to new player while passing.</t>
+        </is>
+      </c>
       <c r="F18" s="36" t="n">
         <v>5</v>
       </c>
@@ -2650,7 +2662,7 @@
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>SHOT +15%. Pass to player of choice. They immediately pass it back</t>
+          <t>SHOT +10%. Pass to target player. They must immediately pass it back. (They do not play a Pass card)</t>
         </is>
       </c>
       <c r="E19" s="25" t="n"/>
@@ -2680,12 +2692,12 @@
       </c>
       <c r="D20" s="30" t="inlineStr">
         <is>
-          <t>SHOT +20%. Pass to player of choice</t>
+          <t>SHOT +10%. Pass to target player.</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>If played as first action, draw 2 cards</t>
+          <t>If played as your first action: Draw 2 cards</t>
         </is>
       </c>
       <c r="F20" s="35" t="n">
@@ -2755,18 +2767,18 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>SHOT +20%</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Following Dribble: SHOT +20%</t>
-        </is>
-      </c>
+          <t>SHOT +10%</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
       <c r="F23" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="G23" s="70" t="n"/>
+      <c r="G23" s="70" t="inlineStr">
+        <is>
+          <t>Combo: after a Dribble, SHOT +10% extra</t>
+        </is>
+      </c>
       <c r="H23" s="71" t="n"/>
       <c r="I23" s="71" t="n"/>
       <c r="J23" s="71" t="n"/>
@@ -2775,7 +2787,7 @@
       <c r="A24" s="21" t="n"/>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>Move</t>
+          <t>Retired Move</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -2790,9 +2802,13 @@
       </c>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" s="72" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="72" t="inlineStr">
+        <is>
+          <t>Retired: now the Ankle Breaker combo — Dribble then Crossover: Shot +10% extra. You may discard 1 card from target player's hand.</t>
+        </is>
+      </c>
       <c r="H24" s="71" t="n"/>
       <c r="I24" s="71" t="n"/>
       <c r="J24" s="71" t="n"/>
@@ -2841,14 +2857,10 @@
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>SHOT +20%</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>Shot Clock -1</t>
-        </is>
-      </c>
+          <t>SHOT +10%. Draw 1 card. Shot Clock -01.</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="n"/>
       <c r="F26" s="36" t="n">
         <v>5</v>
       </c>
@@ -2875,14 +2887,10 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>SHOT +20%</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Cancel all Clamps on you</t>
-        </is>
-      </c>
+          <t>SHOT +10%. Clear all clamps on you. Draw 2 cards and Shot Clock -01 for each.</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n"/>
       <c r="F27" s="32" t="n">
         <v>10</v>
       </c>
@@ -2905,10 +2913,14 @@
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>Draw 1 card. SHOT +20%. Shot Clock -1</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="n"/>
+          <t>SHOT +10%. Draw 1 card.</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>If your next action is a Shot Attempt, it has SHOT +10% extra.</t>
+        </is>
+      </c>
       <c r="F28" s="33" t="n">
         <v>5</v>
       </c>
@@ -2931,7 +2943,7 @@
       </c>
       <c r="D29" s="41" t="inlineStr">
         <is>
-          <t>Draw 2 cards then Discard 1. SHOT +20% Shot Clock -1</t>
+          <t>SHOT +10%. Draw 2 cards then Discard 1. Shot Clock -01</t>
         </is>
       </c>
       <c r="E29" s="26" t="n"/>
@@ -2957,12 +2969,12 @@
       </c>
       <c r="D30" s="41" t="inlineStr">
         <is>
-          <t>SHOT + 10%</t>
+          <t>SHOT +10%. Clear all your Clamps</t>
         </is>
       </c>
       <c r="E30" s="26" t="inlineStr">
         <is>
-          <t>If being Clamped, discard all Clamps and gain additional SHOT +20% for each</t>
+          <t>SHOT +10% for each Clamp Cleared</t>
         </is>
       </c>
       <c r="F30" s="33" t="n">
@@ -2991,12 +3003,12 @@
       </c>
       <c r="D31" s="41" t="inlineStr">
         <is>
-          <t>Draw 1 Card. SHOT +20%</t>
+          <t>SHOT +10%. Clear all your Clamps</t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
         <is>
-          <t>If being Clamped, discard all clamps and Draw 1 card and Clamp-sender discards 1card for each</t>
+          <t>Draw 1 card for each Clamp Cleared</t>
         </is>
       </c>
       <c r="F31" s="33" t="n">
@@ -3004,7 +3016,7 @@
       </c>
       <c r="G31" s="77" t="inlineStr">
         <is>
-          <t>isDribble = true</t>
+          <t>Finishes the Ankle Breaker combo off a Dribble</t>
         </is>
       </c>
       <c r="H31" s="71" t="n"/>
@@ -3025,12 +3037,12 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>SHOT +20%</t>
+          <t>SHOT +10%</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Discard 1: SHOT +20%</t>
+          <t>You may Discard 1 card for SHOT +10% extra.</t>
         </is>
       </c>
       <c r="F32" s="32" t="n">
@@ -3059,23 +3071,16 @@
       </c>
       <c r="D33" s="25" t="inlineStr">
         <is>
-          <t>Choose 1:
-Draw 1 card
-Pass to player of choice (SHOT +20%)
-SHOT +20%</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>Cannot use further Move cards</t>
-        </is>
-      </c>
+          <t>Pick 1: Draw 3 cards / Pass (+0%) / SHOT +30%. (Cannot play other Move cards this possession.)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="n"/>
       <c r="F33" s="36" t="n">
         <v>10</v>
       </c>
       <c r="G33" s="72" t="inlineStr">
         <is>
-          <t>Cannot use further Move cards applies to that possession only.</t>
+          <t>Blocks Moves played before it as well as after</t>
         </is>
       </c>
       <c r="H33" s="71" t="n"/>
@@ -3146,15 +3151,19 @@
       <c r="D36" s="25" t="inlineStr">
         <is>
           <t>Flip a coin:
-Heads: SHOT +10%
-Tails: SHOT -10%</t>
+• Heads: SHOT +25%
+• Tails: SHOT -25%</t>
         </is>
       </c>
       <c r="E36" s="25" t="n"/>
       <c r="F36" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G36" s="72" t="n"/>
+      <c r="G36" s="72" t="inlineStr">
+        <is>
+          <t>Never dunks</t>
+        </is>
+      </c>
       <c r="H36" s="71" t="n"/>
       <c r="I36" s="71" t="n"/>
       <c r="J36" s="71" t="n"/>
@@ -3173,7 +3182,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>SHOT = 100%</t>
+          <t>SHOT = 100%. (Can only be played if the Shot Clock is at 01)</t>
         </is>
       </c>
       <c r="E37" s="6" t="n"/>
@@ -3203,7 +3212,7 @@
       </c>
       <c r="D38" s="41" t="inlineStr">
         <is>
-          <t>[SHOT + 30% at 01 Shot Clock, +20% at 02, +10% at 03, +0% at 04, -10% at 05, etc.]</t>
+          <t>SHOT +60%. SHOT -10% x Shot Clock</t>
         </is>
       </c>
       <c r="E38" s="25" t="n"/>
@@ -3333,12 +3342,12 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>SHOT +20%</t>
+          <t>SHOT +10%</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>After a missed shot: SHOT = 100%</t>
+          <t>If played as your first action after a Rebound: SHOT = 100%</t>
         </is>
       </c>
       <c r="F43" s="32" t="n">
@@ -3368,13 +3377,17 @@
       </c>
       <c r="E44" s="41" t="inlineStr">
         <is>
-          <t>Shot is unaffected by Clamps</t>
+          <t>This shot is unaffected by Clamps.</t>
         </is>
       </c>
       <c r="F44" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="G44" s="72" t="n"/>
+      <c r="G44" s="72" t="inlineStr">
+        <is>
+          <t>Never dunks</t>
+        </is>
+      </c>
       <c r="H44" s="71" t="n"/>
       <c r="I44" s="71" t="n"/>
       <c r="J44" s="71" t="n"/>
@@ -3393,12 +3406,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>SHOT +20%</t>
+          <t>SHOT +25%</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>SHOT = 100% if SHOT &gt;= 75%</t>
+          <t>SHOT = 100% if final SHOT is 75% or more</t>
         </is>
       </c>
       <c r="F45" s="32" t="n">
@@ -3423,10 +3436,14 @@
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>Discard any number of cards. SHOT +10% for each</t>
-        </is>
-      </c>
-      <c r="E46" s="25" t="n"/>
+          <t>SHOT -30%.</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="inlineStr">
+        <is>
+          <t>If you have 3 or more cards in hand, you may discard them: SHOT = 100%</t>
+        </is>
+      </c>
       <c r="F46" s="36" t="n">
         <v>1</v>
       </c>
@@ -3453,7 +3470,9 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Flip a coin until you get 2 Tails. For each Heads, SHOT +5% and Draw 1 card</t>
+          <t>Flip 4 coins.
+• 3 or fewer Heads: SHOT +15% and Draw 1 card for each.
+• 4 Heads: TOV +1 (This is a Travel)</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
@@ -3479,22 +3498,14 @@
       </c>
       <c r="D48" s="57" t="inlineStr">
         <is>
-          <t>Select any number of other players. SHOT +10% for each</t>
-        </is>
-      </c>
-      <c r="E48" s="58" t="inlineStr">
-        <is>
-          <t>Selected players receive +1 AST on a make</t>
-        </is>
-      </c>
+          <t>SHOT = 100%. (Must be played as your first action and have no Clamps, Injuries, or active Whistles)</t>
+        </is>
+      </c>
+      <c r="E48" s="58" t="n"/>
       <c r="F48" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="75" t="inlineStr">
-        <is>
-          <t>Selecting none rolls off current SHOT and is still a three</t>
-        </is>
-      </c>
+      <c r="G48" s="75" t="n"/>
       <c r="H48" s="76" t="n"/>
       <c r="I48" s="76" t="n"/>
       <c r="J48" s="76" t="n"/>
@@ -3512,12 +3523,12 @@
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
-          <t>SHOT +20%</t>
+          <t>Discard up to 2 cards. SHOT +25% for each</t>
         </is>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>Another +10% straight off your own board</t>
+          <t>If played as the first action after your Rebound, you may Discard any number of cards: SHOT +10% extra for each.</t>
         </is>
       </c>
       <c r="F49" s="0" t="n">
@@ -3532,7 +3543,7 @@
     <row r="50" ht="56" customHeight="1" s="85">
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>Special Move</t>
+          <t>Retired Special Move</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -3547,11 +3558,11 @@
       </c>
       <c r="E50" s="0" t="n"/>
       <c r="F50" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>Any of the three dunks</t>
+          <t>Removed from the game (2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3579,8 @@
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>SHOT +15% at 50% or better, −15% under it</t>
+          <t>SHOT 50% or more: SHOT +25%
+SHOT less than 50%: SHOT -25%</t>
         </is>
       </c>
       <c r="E51" s="0" t="n"/>
@@ -5411,7 +5423,7 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10% upon Rebounding your own missed shot</t>
+          <t>SHOT +25% when shooting as your first action after a Rebound of your own miss.</t>
         </is>
       </c>
       <c r="E121" s="7" t="n"/>
@@ -5435,7 +5447,7 @@
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>SHOT +25% on received passes, if shooting is your first action</t>
+          <t>SHOT +25% when shooting as your first action after a Pass</t>
         </is>
       </c>
       <c r="E122" s="26" t="n"/>
@@ -5459,7 +5471,7 @@
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>SHOT x2 if attempting a shot with 1 or fewer cards in hand or Shot Clock 3 or less</t>
+          <t>SHOT = 2X if you have 1 card or fewer in hand, or the Shot Clock is 03 or less</t>
         </is>
       </c>
       <c r="E123" s="7" t="n"/>
@@ -5700,7 +5712,7 @@
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>SHOT +25% on every shot. Cannot use Move or Special Move cards, or shoot threes</t>
+          <t>SHOT +25%. Cannot play Move cards or shoot Threes</t>
         </is>
       </c>
       <c r="E133" s="26" t="n"/>
@@ -5776,7 +5788,7 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>SHOT = 60% on any six: cards in hand, Shot Clock, shot of the round, or score</t>
+          <t>SHOT = 60% on any six: cards in hand, Shot Clock, shot of the round, or Score</t>
         </is>
       </c>
       <c r="E136" s="7" t="n"/>
@@ -5804,7 +5816,7 @@
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>SHOT +25% on all Three-Point Line Shots</t>
+          <t>SHOT +25% when attempting a Three</t>
         </is>
       </c>
       <c r="E137" s="26" t="n"/>
@@ -5828,7 +5840,7 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>All Three-Point Line Shots: SHOT = 100%</t>
+          <t>SHOT = 100% when attempting a Three</t>
         </is>
       </c>
       <c r="E138" s="7" t="n"/>
@@ -5876,7 +5888,7 @@
       </c>
       <c r="D140" s="38" t="inlineStr">
         <is>
-          <t>SHOT = 100% on next shot attempt after rebounding your own miss.</t>
+          <t>SHOT = 100% when shooting as your first action after a Rebound of your own miss</t>
         </is>
       </c>
       <c r="E140" s="7" t="n"/>
@@ -6058,12 +6070,16 @@
       </c>
       <c r="D147" s="38" t="inlineStr">
         <is>
-          <t>Any 'SHOT =' shot you take becomes 100%</t>
+          <t>You may Discard this card when shooting: SHOT = 100%. All players' pts become your new total pts.</t>
         </is>
       </c>
       <c r="E147" s="7" t="n"/>
       <c r="F147" s="50" t="n"/>
-      <c r="G147" s="70" t="n"/>
+      <c r="G147" s="70" t="inlineStr">
+        <is>
+          <t>The points change comes after the make</t>
+        </is>
+      </c>
       <c r="H147" s="71" t="n"/>
       <c r="I147" s="71" t="n"/>
       <c r="J147" s="71" t="n"/>
@@ -6203,7 +6219,7 @@
       </c>
       <c r="D153" s="63" t="inlineStr">
         <is>
-          <t>SHOT +10% on every shot</t>
+          <t>SHOT +20%</t>
         </is>
       </c>
       <c r="E153" s="58" t="n"/>
@@ -6229,14 +6245,18 @@
       </c>
       <c r="D154" s="63" t="inlineStr">
         <is>
-          <t>SHOT -10% on every shot</t>
+          <t>SHOT -20%</t>
         </is>
       </c>
       <c r="E154" s="58" t="n"/>
       <c r="F154" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="G154" s="75" t="n"/>
+      <c r="G154" s="75" t="inlineStr">
+        <is>
+          <t>Always Prime Parquet's opposite</t>
+        </is>
+      </c>
       <c r="H154" s="76" t="n"/>
       <c r="I154" s="76" t="n"/>
       <c r="J154" s="76" t="n"/>
@@ -6405,7 +6425,7 @@
       </c>
       <c r="D160" s="63" t="inlineStr">
         <is>
-          <t>No threes. Every make counts 2. SHOT +10%, and dunks +10% more</t>
+          <t>SHOT +10%. Dunks +10%. Three-point shots cannot be attempted.</t>
         </is>
       </c>
       <c r="E160" s="58" t="n"/>
@@ -6697,7 +6717,9 @@
       </c>
       <c r="D170" s="63" t="inlineStr">
         <is>
-          <t>SHOT +25% and -25%, alternating each possession</t>
+          <t>Upright: SHOT +25%
+Reversed: SHOT -25%
+Turn this card at the start of each possession</t>
         </is>
       </c>
       <c r="E170" s="58" t="n"/>
@@ -6843,7 +6865,7 @@
       </c>
       <c r="D175" s="63" t="inlineStr">
         <is>
-          <t>A three can be shot as a two at double SHOT</t>
+          <t>A Three may be attempted as a two at 2X SHOT</t>
         </is>
       </c>
       <c r="E175" s="58" t="n"/>
@@ -6929,7 +6951,7 @@
       </c>
       <c r="D178" s="63" t="inlineStr">
         <is>
-          <t>SHOT = a random 0–100%, in steps of 5</t>
+          <t>SHOT = ?</t>
         </is>
       </c>
       <c r="E178" s="58" t="n"/>
@@ -6938,7 +6960,7 @@
       </c>
       <c r="G178" s="75" t="inlineStr">
         <is>
-          <t>Rolled fresh for every shot</t>
+          <t>A random 0–100%, in steps of 5</t>
         </is>
       </c>
       <c r="H178" s="76" t="n"/>
@@ -7318,7 +7340,7 @@
       </c>
       <c r="D192" s="63" t="inlineStr">
         <is>
-          <t>Draw 1 on activation. SHOT = 10% for each card in your hand</t>
+          <t>Draw 1 card when played. SHOT = 10% for each card in your hand</t>
         </is>
       </c>
       <c r="E192" s="58" t="n"/>
@@ -7344,7 +7366,7 @@
       </c>
       <c r="D193" s="63" t="inlineStr">
         <is>
-          <t>SHOT +10% each time it's passed</t>
+          <t>SHOT +10% as this Ball is Passed</t>
         </is>
       </c>
       <c r="E193" s="58" t="n"/>
@@ -7374,7 +7396,7 @@
       </c>
       <c r="D194" s="63" t="inlineStr">
         <is>
-          <t>SHOT -10% each time it's passed</t>
+          <t>SHOT -10% as this Ball is Passed</t>
         </is>
       </c>
       <c r="E194" s="58" t="n"/>
@@ -7383,7 +7405,7 @@
       </c>
       <c r="G194" s="75" t="inlineStr">
         <is>
-          <t>Ignores every other pass modifier</t>
+          <t>Blaze Ball's opposite</t>
         </is>
       </c>
       <c r="H194" s="76" t="n"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2089,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:J198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="B151" s="53">
-        <f>COUNTIF($B$152:$B$180,"Varena")</f>
+        <f>COUNTIF($B$152:$B$181,"Varena")</f>
         <v/>
       </c>
       <c r="C151" s="54" t="n"/>
@@ -7006,75 +7006,80 @@
       </c>
       <c r="C180" s="56" t="inlineStr">
         <is>
-          <t>Tick-Tock Tile</t>
+          <t>The Future</t>
         </is>
       </c>
       <c r="D180" s="63" t="inlineStr">
         <is>
-          <t>Playing any card also ticks the Shot Clock</t>
-        </is>
-      </c>
-      <c r="E180" s="58" t="n"/>
+          <t>SHOT +10% and Draw 1 card when playing a Move card.
+SHOT -10% while Passing.</t>
+        </is>
+      </c>
+      <c r="E180" s="58" t="inlineStr">
+        <is>
+          <t>You may Discard 1 card during a three attempt to make it worth four pts (at SHOT-10%)</t>
+        </is>
+      </c>
       <c r="F180" s="61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G180" s="75" t="inlineStr">
         <is>
-          <t>The tick is paid after the card resolves, so a shot at 01 still goes up</t>
+          <t>New in the SHOT audit (2026-09-14). Special Moves count as Moves</t>
         </is>
       </c>
       <c r="H180" s="76" t="n"/>
       <c r="I180" s="76" t="n"/>
       <c r="J180" s="76" t="n"/>
     </row>
-    <row r="181" ht="42" customHeight="1" s="85">
-      <c r="A181" s="52" t="inlineStr">
+    <row r="181" s="85">
+      <c r="A181" s="27" t="n"/>
+      <c r="B181" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C181" s="56" t="inlineStr">
+        <is>
+          <t>Tick-Tock Tile</t>
+        </is>
+      </c>
+      <c r="D181" s="63" t="inlineStr">
+        <is>
+          <t>Playing any card also ticks the Shot Clock</t>
+        </is>
+      </c>
+      <c r="E181" s="58" t="n"/>
+      <c r="F181" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G181" s="75" t="inlineStr">
+        <is>
+          <t>The tick is paid after the card resolves, so a shot at 01 still goes up</t>
+        </is>
+      </c>
+      <c r="H181" s="76" t="n"/>
+      <c r="I181" s="76" t="n"/>
+      <c r="J181" s="76" t="n"/>
+    </row>
+    <row r="182" ht="42" customHeight="1" s="85">
+      <c r="A182" s="52" t="inlineStr">
         <is>
           <t>Variaball</t>
         </is>
       </c>
-      <c r="B181" s="53">
-        <f>COUNTIF($B$182:$B$197,"Variaball")</f>
+      <c r="B182" s="53">
+        <f>COUNTIF($B$183:$B$198,"Variaball")</f>
         <v/>
       </c>
-      <c r="C181" s="54" t="n"/>
-      <c r="D181" s="54" t="n"/>
-      <c r="E181" s="54" t="n"/>
-      <c r="F181" s="55" t="n"/>
-      <c r="G181" s="66" t="n"/>
-      <c r="H181" s="67" t="n"/>
-      <c r="I181" s="67" t="n"/>
-      <c r="J181" s="67" t="n"/>
-    </row>
-    <row r="182" s="85">
-      <c r="A182" s="27" t="n"/>
-      <c r="B182" s="28" t="inlineStr">
-        <is>
-          <t>Variaball</t>
-        </is>
-      </c>
-      <c r="C182" s="56" t="inlineStr">
-        <is>
-          <t>Med Ball</t>
-        </is>
-      </c>
-      <c r="D182" s="63" t="inlineStr">
-        <is>
-          <t>SHOT cannot exceed 50%</t>
-        </is>
-      </c>
-      <c r="E182" s="58" t="n"/>
-      <c r="F182" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="G182" s="75" t="inlineStr">
-        <is>
-          <t>An Intangible's or a Varena's SHOT = is not held to it</t>
-        </is>
-      </c>
-      <c r="H182" s="76" t="n"/>
-      <c r="I182" s="76" t="n"/>
-      <c r="J182" s="76" t="n"/>
+      <c r="C182" s="54" t="n"/>
+      <c r="D182" s="54" t="n"/>
+      <c r="E182" s="54" t="n"/>
+      <c r="F182" s="55" t="n"/>
+      <c r="G182" s="66" t="n"/>
+      <c r="H182" s="67" t="n"/>
+      <c r="I182" s="67" t="n"/>
+      <c r="J182" s="67" t="n"/>
     </row>
     <row r="183" s="85">
       <c r="A183" s="27" t="n"/>
@@ -7085,12 +7090,12 @@
       </c>
       <c r="C183" s="56" t="inlineStr">
         <is>
-          <t>Dishcount Ball</t>
+          <t>Med Ball</t>
         </is>
       </c>
       <c r="D183" s="63" t="inlineStr">
         <is>
-          <t>Discard one fewer for card costs and Clamps</t>
+          <t>SHOT cannot exceed 50%</t>
         </is>
       </c>
       <c r="E183" s="58" t="n"/>
@@ -7099,7 +7104,7 @@
       </c>
       <c r="G183" s="75" t="inlineStr">
         <is>
-          <t>Counts: Clamps, Pound Dribble, Frostbite Finish, Stepback, Turnaround Three</t>
+          <t>An Intangible's or a Varena's SHOT = is not held to it</t>
         </is>
       </c>
       <c r="H183" s="76" t="n"/>
@@ -7115,21 +7120,21 @@
       </c>
       <c r="C184" s="56" t="inlineStr">
         <is>
-          <t>Blight Ball</t>
+          <t>Dishcount Ball</t>
         </is>
       </c>
       <c r="D184" s="63" t="inlineStr">
         <is>
-          <t>Injuries travel with the ball, and new ones join the pile. Discarding the ball takes the pile with it</t>
+          <t>Discard one fewer for card costs and Clamps</t>
         </is>
       </c>
       <c r="E184" s="58" t="n"/>
       <c r="F184" s="61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G184" s="75" t="inlineStr">
         <is>
-          <t>Moves on any change of hands</t>
+          <t>Counts: Clamps, Pound Dribble, Frostbite Finish, Stepback, Turnaround Three</t>
         </is>
       </c>
       <c r="H184" s="76" t="n"/>
@@ -7145,19 +7150,23 @@
       </c>
       <c r="C185" s="56" t="inlineStr">
         <is>
-          <t>Bench Ball</t>
+          <t>Blight Ball</t>
         </is>
       </c>
       <c r="D185" s="63" t="inlineStr">
         <is>
-          <t>Receiving it by Pass: no draw, no turn. You inbound</t>
+          <t>Injuries travel with the ball, and new ones join the pile. Discarding the ball takes the pile with it</t>
         </is>
       </c>
       <c r="E185" s="58" t="n"/>
       <c r="F185" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G185" s="75" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G185" s="75" t="inlineStr">
+        <is>
+          <t>Moves on any change of hands</t>
+        </is>
+      </c>
       <c r="H185" s="76" t="n"/>
       <c r="I185" s="76" t="n"/>
       <c r="J185" s="76" t="n"/>
@@ -7171,23 +7180,19 @@
       </c>
       <c r="C186" s="56" t="inlineStr">
         <is>
-          <t>Dishtracting Ball</t>
+          <t>Bench Ball</t>
         </is>
       </c>
       <c r="D186" s="63" t="inlineStr">
         <is>
-          <t>Receiving it: discard 1, after the draw for turn</t>
+          <t>Receiving it by Pass: no draw, no turn. You inbound</t>
         </is>
       </c>
       <c r="E186" s="58" t="n"/>
       <c r="F186" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="G186" s="75" t="inlineStr">
-        <is>
-          <t>Any change of hands</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G186" s="75" t="n"/>
       <c r="H186" s="76" t="n"/>
       <c r="I186" s="76" t="n"/>
       <c r="J186" s="76" t="n"/>
@@ -7201,19 +7206,23 @@
       </c>
       <c r="C187" s="56" t="inlineStr">
         <is>
-          <t>Hand Ball</t>
+          <t>Dishtracting Ball</t>
         </is>
       </c>
       <c r="D187" s="63" t="inlineStr">
         <is>
-          <t>A Pass swaps hands: yours goes with the ball, theirs comes back</t>
+          <t>Receiving it: discard 1, after the draw for turn</t>
         </is>
       </c>
       <c r="E187" s="58" t="n"/>
       <c r="F187" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G187" s="75" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G187" s="75" t="inlineStr">
+        <is>
+          <t>Any change of hands</t>
+        </is>
+      </c>
       <c r="H187" s="76" t="n"/>
       <c r="I187" s="76" t="n"/>
       <c r="J187" s="76" t="n"/>
@@ -7227,12 +7236,12 @@
       </c>
       <c r="C188" s="56" t="inlineStr">
         <is>
-          <t>Foot Ball</t>
+          <t>Hand Ball</t>
         </is>
       </c>
       <c r="D188" s="63" t="inlineStr">
         <is>
-          <t>Moves and Passes are not spent. They lock until your possession ends</t>
+          <t>A Pass swaps hands: yours goes with the ball, theirs comes back</t>
         </is>
       </c>
       <c r="E188" s="58" t="n"/>
@@ -7253,17 +7262,17 @@
       </c>
       <c r="C189" s="56" t="inlineStr">
         <is>
-          <t>Recharge Rock</t>
+          <t>Foot Ball</t>
         </is>
       </c>
       <c r="D189" s="63" t="inlineStr">
         <is>
-          <t>Double your draw for turn</t>
+          <t>Moves and Passes are not spent. They lock until your possession ends</t>
         </is>
       </c>
       <c r="E189" s="58" t="n"/>
       <c r="F189" s="61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G189" s="75" t="n"/>
       <c r="H189" s="76" t="n"/>
@@ -7279,23 +7288,19 @@
       </c>
       <c r="C190" s="56" t="inlineStr">
         <is>
-          <t>Variaball</t>
+          <t>Recharge Rock</t>
         </is>
       </c>
       <c r="D190" s="63" t="inlineStr">
         <is>
-          <t>A random Variaball from the discards goes into play. Then discard this</t>
+          <t>Double your draw for turn</t>
         </is>
       </c>
       <c r="E190" s="58" t="n"/>
       <c r="F190" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G190" s="75" t="inlineStr">
-        <is>
-          <t>From the deck if the discards have none; never the ball already in play</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G190" s="75" t="n"/>
       <c r="H190" s="76" t="n"/>
       <c r="I190" s="76" t="n"/>
       <c r="J190" s="76" t="n"/>
@@ -7309,19 +7314,23 @@
       </c>
       <c r="C191" s="56" t="inlineStr">
         <is>
-          <t>Shufflebag Ball</t>
+          <t>Variaball</t>
         </is>
       </c>
       <c r="D191" s="63" t="inlineStr">
         <is>
-          <t>Every possession, the turn player shuffles their hand into the deck and draws the same number, then draws for turn</t>
+          <t>A random Variaball from the discards goes into play. Then discard this</t>
         </is>
       </c>
       <c r="E191" s="58" t="n"/>
       <c r="F191" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="G191" s="75" t="n"/>
+      <c r="G191" s="75" t="inlineStr">
+        <is>
+          <t>From the deck if the discards have none; never the ball already in play</t>
+        </is>
+      </c>
       <c r="H191" s="76" t="n"/>
       <c r="I191" s="76" t="n"/>
       <c r="J191" s="76" t="n"/>
@@ -7335,12 +7344,12 @@
       </c>
       <c r="C192" s="56" t="inlineStr">
         <is>
-          <t>Bag'n Ball</t>
+          <t>Shufflebag Ball</t>
         </is>
       </c>
       <c r="D192" s="63" t="inlineStr">
         <is>
-          <t>Draw 1 card when played. SHOT = 10% for each card in your hand</t>
+          <t>Every possession, the turn player shuffles their hand into the deck and draws the same number, then draws for turn</t>
         </is>
       </c>
       <c r="E192" s="58" t="n"/>
@@ -7361,23 +7370,19 @@
       </c>
       <c r="C193" s="56" t="inlineStr">
         <is>
-          <t>Blaze Ball</t>
+          <t>Bag'n Ball</t>
         </is>
       </c>
       <c r="D193" s="63" t="inlineStr">
         <is>
-          <t>SHOT +10% as this Ball is Passed</t>
+          <t>Draw 1 card when played. SHOT = 10% for each card in your hand</t>
         </is>
       </c>
       <c r="E193" s="58" t="n"/>
       <c r="F193" s="61" t="n">
-        <v>5</v>
-      </c>
-      <c r="G193" s="75" t="inlineStr">
-        <is>
-          <t>Ignores every other pass modifier</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G193" s="75" t="n"/>
       <c r="H193" s="76" t="n"/>
       <c r="I193" s="76" t="n"/>
       <c r="J193" s="76" t="n"/>
@@ -7391,12 +7396,12 @@
       </c>
       <c r="C194" s="56" t="inlineStr">
         <is>
-          <t>Snow Ball It</t>
+          <t>Blaze Ball</t>
         </is>
       </c>
       <c r="D194" s="63" t="inlineStr">
         <is>
-          <t>SHOT -10% as this Ball is Passed</t>
+          <t>SHOT +10% as this Ball is Passed</t>
         </is>
       </c>
       <c r="E194" s="58" t="n"/>
@@ -7405,7 +7410,7 @@
       </c>
       <c r="G194" s="75" t="inlineStr">
         <is>
-          <t>Blaze Ball's opposite</t>
+          <t>Ignores every other pass modifier</t>
         </is>
       </c>
       <c r="H194" s="76" t="n"/>
@@ -7421,19 +7426,23 @@
       </c>
       <c r="C195" s="56" t="inlineStr">
         <is>
-          <t>Brick Ball</t>
+          <t>Snow Ball It</t>
         </is>
       </c>
       <c r="D195" s="63" t="inlineStr">
         <is>
-          <t>SHOT = 25%</t>
+          <t>SHOT -10% as this Ball is Passed</t>
         </is>
       </c>
       <c r="E195" s="58" t="n"/>
       <c r="F195" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="G195" s="75" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="G195" s="75" t="inlineStr">
+        <is>
+          <t>Blaze Ball's opposite</t>
+        </is>
+      </c>
       <c r="H195" s="76" t="n"/>
       <c r="I195" s="76" t="n"/>
       <c r="J195" s="76" t="n"/>
@@ -7447,23 +7456,19 @@
       </c>
       <c r="C196" s="56" t="inlineStr">
         <is>
-          <t>Monster Ball</t>
+          <t>Brick Ball</t>
         </is>
       </c>
       <c r="D196" s="63" t="inlineStr">
         <is>
-          <t>Intangibles are absorbed into the ball. When it's discarded, players rebound for them one at a time</t>
+          <t>SHOT = 25%</t>
         </is>
       </c>
       <c r="E196" s="58" t="n"/>
       <c r="F196" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" s="75" t="inlineStr">
-        <is>
-          <t>Swallows every Intangible already out and every one drawn while it's in play</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G196" s="75" t="n"/>
       <c r="H196" s="76" t="n"/>
       <c r="I196" s="76" t="n"/>
       <c r="J196" s="76" t="n"/>
@@ -7477,33 +7482,63 @@
       </c>
       <c r="C197" s="56" t="inlineStr">
         <is>
-          <t>Brand New Ball</t>
+          <t>Monster Ball</t>
         </is>
       </c>
       <c r="D197" s="63" t="inlineStr">
         <is>
-          <t>25% chance a shot attempt is a turnover instead</t>
+          <t>Intangibles are absorbed into the ball. When it's discarded, players rebound for them one at a time</t>
         </is>
       </c>
       <c r="E197" s="58" t="n"/>
       <c r="F197" s="61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G197" s="75" t="inlineStr">
         <is>
-          <t>The round ends</t>
+          <t>Swallows every Intangible already out and every one drawn while it's in play</t>
         </is>
       </c>
       <c r="H197" s="76" t="n"/>
       <c r="I197" s="76" t="n"/>
       <c r="J197" s="76" t="n"/>
     </row>
+    <row r="198" s="85">
+      <c r="A198" s="27" t="n"/>
+      <c r="B198" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C198" s="56" t="inlineStr">
+        <is>
+          <t>Brand New Ball</t>
+        </is>
+      </c>
+      <c r="D198" s="63" t="inlineStr">
+        <is>
+          <t>25% chance a shot attempt is a turnover instead</t>
+        </is>
+      </c>
+      <c r="E198" s="58" t="n"/>
+      <c r="F198" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G198" s="75" t="inlineStr">
+        <is>
+          <t>The round ends</t>
+        </is>
+      </c>
+      <c r="H198" s="76" t="n"/>
+      <c r="I198" s="76" t="n"/>
+      <c r="J198" s="76" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="175">
+  <mergeCells count="176">
     <mergeCell ref="G55:J55"/>
-    <mergeCell ref="G188:J188"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G182:J182"/>
+    <mergeCell ref="G188:J188"/>
     <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
@@ -7529,8 +7564,8 @@
     <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
+    <mergeCell ref="G137:J137"/>
     <mergeCell ref="G184:J184"/>
-    <mergeCell ref="G137:J137"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G53:J53"/>
     <mergeCell ref="G171:J171"/>
@@ -7555,9 +7590,9 @@
     <mergeCell ref="G165:J165"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
-    <mergeCell ref="G193:J193"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="G84:J84"/>
+    <mergeCell ref="G193:J193"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="G158:J158"/>
     <mergeCell ref="G185:J185"/>
@@ -7585,8 +7620,8 @@
     <mergeCell ref="G162:J162"/>
     <mergeCell ref="G49:J49"/>
     <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G177:J177"/>
     <mergeCell ref="G195:J195"/>
-    <mergeCell ref="G177:J177"/>
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="G104:J104"/>
     <mergeCell ref="G65:J65"/>
@@ -7604,11 +7639,13 @@
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="G131:J131"/>
     <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G198:J198"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G130:J130"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
+    <mergeCell ref="G180:J180"/>
     <mergeCell ref="G169:J169"/>
     <mergeCell ref="G179:J179"/>
     <mergeCell ref="G126:J126"/>
@@ -7662,16 +7699,15 @@
     <mergeCell ref="G141:J141"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G172:J172"/>
-    <mergeCell ref="G190:J190"/>
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="G93:J93"/>
     <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G190:J190"/>
+    <mergeCell ref="G69:J69"/>
     <mergeCell ref="G187:J187"/>
-    <mergeCell ref="G69:J69"/>
     <mergeCell ref="G83:J83"/>
     <mergeCell ref="G196:J196"/>
     <mergeCell ref="G124:J124"/>
-    <mergeCell ref="G180:J180"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="G133:J133"/>
     <mergeCell ref="G14:J14"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2089,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J198"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2170,39 +2170,39 @@
         </is>
       </c>
       <c r="B2" s="12">
-        <f>COUNTIF($B$5:$B$146,"Pass")</f>
+        <f>COUNTIF($B$5:$B$154,"Pass")</f>
         <v/>
       </c>
       <c r="C2" s="13">
-        <f>COUNTIF($B$5:$B$146,"Move")+COUNTIF($B$5:$B$146,"Special Move")</f>
+        <f>COUNTIF($B$5:$B$154,"Move")+COUNTIF($B$5:$B$154,"Special Move")</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>COUNTIF($B$5:$B$146,"Clamp")</f>
+        <f>COUNTIF($B$5:$B$154,"Clamp")</f>
         <v/>
       </c>
       <c r="E2" s="15">
-        <f>COUNTIF($B$5:$B$146,"Whistle")</f>
+        <f>COUNTIF($B$5:$B$154,"Whistle")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIF($B$5:$B$146,"Game Break")</f>
+        <f>COUNTIF($B$5:$B$154,"Game Break")</f>
         <v/>
       </c>
       <c r="G2" s="18">
-        <f>COUNTIF($B$5:$B$146,"Injury")</f>
+        <f>COUNTIF($B$5:$B$154,"Injury")</f>
         <v/>
       </c>
       <c r="H2" s="19">
-        <f>COUNTIF($B$5:$B$146,"Devastating Injury")</f>
+        <f>COUNTIF($B$5:$B$154,"Devastating Injury")</f>
         <v/>
       </c>
       <c r="I2" s="17">
-        <f>COUNTIF($B$5:$B$146,"Intangible")</f>
+        <f>COUNTIF($B$5:$B$154,"Intangible")</f>
         <v/>
       </c>
       <c r="J2" s="87">
-        <f>SUM(B2:E2)+COUNTIF($B$5:$B$146,"Game Break")+SUM(G2:I2)</f>
+        <f>SUM(B2:E2)+COUNTIF($B$5:$B$154,"Game Break")+SUM(G2:I2)</f>
         <v/>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="B5" s="53">
-        <f>COUNTIF($B$6:$B$150,"Pass")</f>
+        <f>COUNTIF($B$6:$B$158,"Pass")</f>
         <v/>
       </c>
       <c r="C5" s="54" t="n"/>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="B21" s="53">
-        <f>COUNTIF($B$22:$B$150,"Move")+COUNTIF($B$22:$B$150,"Special Move")</f>
+        <f>COUNTIF($B$22:$B$158,"Move")+COUNTIF($B$22:$B$158,"Special Move")</f>
         <v/>
       </c>
       <c r="C21" s="54" t="n"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G23" s="70" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="B35" s="53">
-        <f>COUNTIF($B$36:$B$150,"Special Move")</f>
+        <f>COUNTIF($B$36:$B$158,"Special Move")</f>
         <v/>
       </c>
       <c r="C35" s="54" t="n"/>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="B53" s="53">
-        <f>COUNTIF($B$54:$B$150,"Clamp")</f>
+        <f>COUNTIF($B$54:$B$158,"Clamp")</f>
         <v/>
       </c>
       <c r="C53" s="54" t="n"/>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="B62" s="53">
-        <f>COUNTIF($B$63:$B$150,"Whistle")</f>
+        <f>COUNTIF($B$63:$B$158,"Whistle")</f>
         <v/>
       </c>
       <c r="C62" s="54" t="n"/>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="B116" s="53">
-        <f>COUNTIF($B$117:$B$150,"Injury")</f>
+        <f>COUNTIF($B$117:$B$158,"Injury")</f>
         <v/>
       </c>
       <c r="C116" s="54" t="n"/>
@@ -5331,289 +5331,310 @@
       </c>
       <c r="D117" s="63" t="inlineStr">
         <is>
-          <t>Discard 1 card at the start of each turn after drawing (your choice)</t>
+          <t>SHOT -10%</t>
         </is>
       </c>
       <c r="E117" s="58" t="n"/>
       <c r="F117" s="59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G117" s="75" t="n"/>
       <c r="H117" s="76" t="n"/>
       <c r="I117" s="76" t="n"/>
       <c r="J117" s="76" t="n"/>
     </row>
-    <row r="118" ht="20" customHeight="1" s="85">
-      <c r="A118" s="52" t="inlineStr">
-        <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="B118" s="53">
-        <f>COUNTIF($B$119:$B$150,"Devastating Injury")</f>
-        <v/>
-      </c>
-      <c r="C118" s="54" t="n"/>
-      <c r="D118" s="54" t="n"/>
-      <c r="E118" s="54" t="n"/>
-      <c r="F118" s="55" t="n"/>
-      <c r="G118" s="66" t="n"/>
-      <c r="H118" s="67" t="n"/>
-      <c r="I118" s="67" t="n"/>
-      <c r="J118" s="67" t="n"/>
-    </row>
-    <row r="119" ht="28" customHeight="1" s="85">
+    <row r="118" ht="57" customHeight="1" s="85">
+      <c r="A118" s="27" t="n"/>
+      <c r="B118" s="28" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C118" s="56" t="inlineStr">
+        <is>
+          <t>Rolled Ankle</t>
+        </is>
+      </c>
+      <c r="D118" s="63" t="inlineStr">
+        <is>
+          <t>Discard 1 card to play a Move card</t>
+        </is>
+      </c>
+      <c r="E118" s="58" t="n"/>
+      <c r="F118" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G118" s="75" t="n"/>
+      <c r="H118" s="76" t="n"/>
+      <c r="I118" s="76" t="n"/>
+      <c r="J118" s="76" t="n"/>
+    </row>
+    <row r="119" ht="57" customHeight="1" s="85">
       <c r="A119" s="27" t="n"/>
       <c r="B119" s="28" t="inlineStr">
         <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="C119" s="64" t="inlineStr">
-        <is>
-          <t>Torn Achilles</t>
-        </is>
-      </c>
-      <c r="D119" s="65" t="inlineStr">
-        <is>
-          <t>Hand is locked every turn except 1 card (randomly)</t>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C119" s="56" t="inlineStr">
+        <is>
+          <t>Fractured Collarbone</t>
+        </is>
+      </c>
+      <c r="D119" s="63" t="inlineStr">
+        <is>
+          <t>Cannot attempt Three-point shots</t>
         </is>
       </c>
       <c r="E119" s="58" t="n"/>
-      <c r="F119" s="61" t="n"/>
+      <c r="F119" s="59" t="n">
+        <v>2</v>
+      </c>
       <c r="G119" s="75" t="n"/>
       <c r="H119" s="76" t="n"/>
       <c r="I119" s="76" t="n"/>
       <c r="J119" s="76" t="n"/>
     </row>
-    <row r="120" ht="42" customHeight="1" s="85">
-      <c r="A120" s="52" t="inlineStr">
+    <row r="120" ht="57" customHeight="1" s="85">
+      <c r="A120" s="27" t="n"/>
+      <c r="B120" s="28" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C120" s="56" t="inlineStr">
+        <is>
+          <t>Jammed Finger</t>
+        </is>
+      </c>
+      <c r="D120" s="63" t="inlineStr">
+        <is>
+          <t>Discard 1 card at random while receiving a Pass</t>
+        </is>
+      </c>
+      <c r="E120" s="58" t="n"/>
+      <c r="F120" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" s="75" t="n"/>
+      <c r="H120" s="76" t="n"/>
+      <c r="I120" s="76" t="n"/>
+      <c r="J120" s="76" t="n"/>
+    </row>
+    <row r="121" ht="57" customHeight="1" s="85">
+      <c r="A121" s="27" t="n"/>
+      <c r="B121" s="28" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C121" s="56" t="inlineStr">
+        <is>
+          <t>Sprained Hamstring</t>
+        </is>
+      </c>
+      <c r="D121" s="63" t="inlineStr">
+        <is>
+          <t>Your Rebound Bids are worth 1 less</t>
+        </is>
+      </c>
+      <c r="E121" s="58" t="n"/>
+      <c r="F121" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" s="75" t="n"/>
+      <c r="H121" s="76" t="n"/>
+      <c r="I121" s="76" t="n"/>
+      <c r="J121" s="76" t="n"/>
+    </row>
+    <row r="122" ht="57" customHeight="1" s="85">
+      <c r="A122" s="27" t="n"/>
+      <c r="B122" s="28" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C122" s="56" t="inlineStr">
+        <is>
+          <t>Hip Contusion</t>
+        </is>
+      </c>
+      <c r="D122" s="63" t="inlineStr">
+        <is>
+          <t>Discard 1 card at random when playing a Pass card</t>
+        </is>
+      </c>
+      <c r="E122" s="58" t="n"/>
+      <c r="F122" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" s="75" t="n"/>
+      <c r="H122" s="76" t="n"/>
+      <c r="I122" s="76" t="n"/>
+      <c r="J122" s="76" t="n"/>
+    </row>
+    <row r="123" ht="20" customHeight="1" s="85">
+      <c r="A123" s="52" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="B123" s="53">
+        <f>COUNTIF($B$124:$B$158,"Devastating Injury")</f>
+        <v/>
+      </c>
+      <c r="C123" s="54" t="n"/>
+      <c r="D123" s="54" t="n"/>
+      <c r="E123" s="54" t="n"/>
+      <c r="F123" s="55" t="n"/>
+      <c r="G123" s="66" t="n"/>
+      <c r="H123" s="67" t="n"/>
+      <c r="I123" s="67" t="n"/>
+      <c r="J123" s="67" t="n"/>
+    </row>
+    <row r="124" ht="28" customHeight="1" s="85">
+      <c r="A124" s="27" t="n"/>
+      <c r="B124" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C124" s="64" t="inlineStr">
+        <is>
+          <t>Torn Achilles</t>
+        </is>
+      </c>
+      <c r="D124" s="65" t="inlineStr">
+        <is>
+          <t>Cannot Play Dunk Cards. Can only play 1 Move card per possession</t>
+        </is>
+      </c>
+      <c r="E124" s="58" t="n"/>
+      <c r="F124" s="61" t="n"/>
+      <c r="G124" s="75" t="inlineStr">
+        <is>
+          <t>Landing one discards every other Injury, and while one is on you a new Injury is discarded</t>
+        </is>
+      </c>
+      <c r="H124" s="76" t="n"/>
+      <c r="I124" s="76" t="n"/>
+      <c r="J124" s="76" t="n"/>
+    </row>
+    <row r="125" ht="28" customHeight="1" s="85">
+      <c r="A125" s="27" t="n"/>
+      <c r="B125" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C125" s="64" t="inlineStr">
+        <is>
+          <t>Torn ACL</t>
+        </is>
+      </c>
+      <c r="D125" s="65" t="inlineStr">
+        <is>
+          <t>Cannot Play Move Cards.</t>
+        </is>
+      </c>
+      <c r="E125" s="58" t="n"/>
+      <c r="F125" s="61" t="n"/>
+      <c r="G125" s="75" t="n"/>
+      <c r="H125" s="76" t="n"/>
+      <c r="I125" s="76" t="n"/>
+      <c r="J125" s="76" t="n"/>
+    </row>
+    <row r="126" ht="28" customHeight="1" s="85">
+      <c r="A126" s="27" t="n"/>
+      <c r="B126" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C126" s="64" t="inlineStr">
+        <is>
+          <t>Torn Meniscus</t>
+        </is>
+      </c>
+      <c r="D126" s="65" t="inlineStr">
+        <is>
+          <t>Randomly Lock all but 1 Card Each Possession</t>
+        </is>
+      </c>
+      <c r="E126" s="58" t="n"/>
+      <c r="F126" s="61" t="n"/>
+      <c r="G126" s="75" t="n"/>
+      <c r="H126" s="76" t="n"/>
+      <c r="I126" s="76" t="n"/>
+      <c r="J126" s="76" t="n"/>
+    </row>
+    <row r="127" ht="28" customHeight="1" s="85">
+      <c r="A127" s="27" t="n"/>
+      <c r="B127" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C127" s="64" t="inlineStr">
+        <is>
+          <t>Patellar Tendon Tear</t>
+        </is>
+      </c>
+      <c r="D127" s="65" t="inlineStr">
+        <is>
+          <t>Cannot Draw Cards except at the start of your possession</t>
+        </is>
+      </c>
+      <c r="E127" s="58" t="n"/>
+      <c r="F127" s="61" t="n"/>
+      <c r="G127" s="75" t="n"/>
+      <c r="H127" s="76" t="n"/>
+      <c r="I127" s="76" t="n"/>
+      <c r="J127" s="76" t="n"/>
+    </row>
+    <row r="128" ht="42" customHeight="1" s="85">
+      <c r="A128" s="52" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B120" s="53">
-        <f>COUNTIF($B$121:$B$150,"Intangible")</f>
+      <c r="B128" s="53">
+        <f>COUNTIF($B$129:$B$158,"Intangible")</f>
         <v/>
       </c>
-      <c r="C120" s="54" t="n"/>
-      <c r="D120" s="54" t="n"/>
-      <c r="E120" s="54" t="n"/>
-      <c r="F120" s="55" t="n"/>
-      <c r="G120" s="66" t="n"/>
-      <c r="H120" s="67" t="n"/>
-      <c r="I120" s="67" t="n"/>
-      <c r="J120" s="67" t="n"/>
-    </row>
-    <row r="121" ht="28" customHeight="1" s="85">
-      <c r="A121" s="42" t="inlineStr">
+      <c r="C128" s="54" t="n"/>
+      <c r="D128" s="54" t="n"/>
+      <c r="E128" s="54" t="n"/>
+      <c r="F128" s="55" t="n"/>
+      <c r="G128" s="66" t="n"/>
+      <c r="H128" s="67" t="n"/>
+      <c r="I128" s="67" t="n"/>
+      <c r="J128" s="67" t="n"/>
+    </row>
+    <row r="129" ht="28" customHeight="1" s="85">
+      <c r="A129" s="42" t="inlineStr">
         <is>
           <t>All intangibles are limited to 1</t>
         </is>
       </c>
-      <c r="B121" s="22" t="inlineStr">
+      <c r="B129" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C121" s="23" t="inlineStr">
+      <c r="C129" s="23" t="inlineStr">
         <is>
           <t>Board-Crasher</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D129" s="6" t="inlineStr">
         <is>
           <t>SHOT +25% when shooting as your first action after a Rebound of your own miss.</t>
         </is>
       </c>
-      <c r="E121" s="7" t="n"/>
-      <c r="F121" s="50" t="n"/>
-      <c r="G121" s="70" t="n"/>
-      <c r="H121" s="71" t="n"/>
-      <c r="I121" s="71" t="n"/>
-      <c r="J121" s="71" t="n"/>
-    </row>
-    <row r="122" ht="28" customHeight="1" s="85">
-      <c r="A122" s="21" t="n"/>
-      <c r="B122" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C122" s="24" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D122" s="25" t="inlineStr">
-        <is>
-          <t>SHOT +25% when shooting as your first action after a Pass</t>
-        </is>
-      </c>
-      <c r="E122" s="26" t="n"/>
-      <c r="F122" s="50" t="n"/>
-      <c r="G122" s="72" t="n"/>
-      <c r="H122" s="71" t="n"/>
-      <c r="I122" s="71" t="n"/>
-      <c r="J122" s="71" t="n"/>
-    </row>
-    <row r="123" ht="56" customHeight="1" s="85">
-      <c r="A123" s="21" t="n"/>
-      <c r="B123" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C123" s="23" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>SHOT = 2X if you have 1 card or fewer in hand, or the Shot Clock is 03 or less</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="n"/>
-      <c r="F123" s="50" t="n"/>
-      <c r="G123" s="70" t="n"/>
-      <c r="H123" s="71" t="n"/>
-      <c r="I123" s="71" t="n"/>
-      <c r="J123" s="71" t="n"/>
-    </row>
-    <row r="124" ht="56" customHeight="1" s="85">
-      <c r="B124" s="0" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C124" s="0" t="inlineStr">
-        <is>
-          <t>Roswell Reach</t>
-        </is>
-      </c>
-      <c r="D124" s="0" t="inlineStr">
-        <is>
-          <t>All your Rebound bids of 1 or more count as 1 higher</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="28" customHeight="1" s="85">
-      <c r="A125" s="21" t="n"/>
-      <c r="B125" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C125" s="24" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D125" s="25" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
-        </is>
-      </c>
-      <c r="E125" s="26" t="n"/>
-      <c r="F125" s="50" t="n"/>
-      <c r="G125" s="72" t="n"/>
-      <c r="H125" s="71" t="n"/>
-      <c r="I125" s="71" t="n"/>
-      <c r="J125" s="71" t="n"/>
-    </row>
-    <row r="126" ht="28" customHeight="1" s="85">
-      <c r="A126" s="21" t="n"/>
-      <c r="B126" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C126" s="23" t="inlineStr">
-        <is>
-          <t>Southpaw Shooter</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>SHOT gains and losses are reversed</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="n"/>
-      <c r="F126" s="51" t="n"/>
-      <c r="G126" s="70" t="n"/>
-      <c r="H126" s="71" t="n"/>
-      <c r="I126" s="71" t="n"/>
-      <c r="J126" s="71" t="n"/>
-    </row>
-    <row r="127" ht="28" customHeight="1" s="85">
-      <c r="A127" s="21" t="n"/>
-      <c r="B127" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C127" s="37" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D127" s="41" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E127" s="26" t="n"/>
-      <c r="F127" s="50" t="n"/>
-      <c r="G127" s="77" t="n"/>
-      <c r="H127" s="71" t="n"/>
-      <c r="I127" s="71" t="n"/>
-      <c r="J127" s="71" t="n"/>
-    </row>
-    <row r="128" ht="28" customHeight="1" s="85">
-      <c r="A128" s="21" t="n"/>
-      <c r="B128" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C128" s="37" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D128" s="38" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="n"/>
-      <c r="F128" s="50" t="n"/>
-      <c r="G128" s="70" t="n"/>
-      <c r="H128" s="71" t="n"/>
-      <c r="I128" s="71" t="n"/>
-      <c r="J128" s="71" t="n"/>
-    </row>
-    <row r="129" ht="14" customHeight="1" s="85">
-      <c r="A129" s="21" t="n"/>
-      <c r="B129" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C129" s="24" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D129" s="25" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E129" s="26" t="n"/>
+      <c r="E129" s="7" t="n"/>
       <c r="F129" s="50" t="n"/>
-      <c r="G129" s="72" t="n"/>
+      <c r="G129" s="70" t="n"/>
       <c r="H129" s="71" t="n"/>
       <c r="I129" s="71" t="n"/>
       <c r="J129" s="71" t="n"/>
@@ -5625,78 +5646,63 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C130" s="23" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injuries you draw and draw a new card for each</t>
-        </is>
-      </c>
-      <c r="E130" s="7" t="n"/>
+      <c r="C130" s="24" t="inlineStr">
+        <is>
+          <t>Catch &amp; Shoot Specialist</t>
+        </is>
+      </c>
+      <c r="D130" s="25" t="inlineStr">
+        <is>
+          <t>SHOT +25% when shooting as your first action after a Pass</t>
+        </is>
+      </c>
+      <c r="E130" s="26" t="n"/>
       <c r="F130" s="50" t="n"/>
-      <c r="G130" s="70" t="inlineStr">
-        <is>
-          <t>Also discards any Injuries you already have (not on the card)</t>
-        </is>
-      </c>
+      <c r="G130" s="72" t="n"/>
       <c r="H130" s="71" t="n"/>
       <c r="I130" s="71" t="n"/>
       <c r="J130" s="71" t="n"/>
     </row>
-    <row r="131" ht="28" customHeight="1" s="85">
+    <row r="131" ht="56" customHeight="1" s="85">
       <c r="A131" s="21" t="n"/>
       <c r="B131" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C131" s="24" t="inlineStr">
-        <is>
-          <t>Hot Hand</t>
-        </is>
-      </c>
-      <c r="D131" s="25" t="inlineStr">
-        <is>
-          <t>SHOT +25% if you scored last round.</t>
-        </is>
-      </c>
-      <c r="E131" s="26" t="n"/>
+      <c r="C131" s="23" t="inlineStr">
+        <is>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>SHOT = 2X if you have 1 card or fewer in hand, or the Shot Clock is 03 or less</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="n"/>
       <c r="F131" s="50" t="n"/>
-      <c r="G131" s="72" t="n"/>
+      <c r="G131" s="70" t="n"/>
       <c r="H131" s="71" t="n"/>
       <c r="I131" s="71" t="n"/>
       <c r="J131" s="71" t="n"/>
     </row>
-    <row r="132" ht="28" customHeight="1" s="85">
-      <c r="A132" s="21" t="n"/>
-      <c r="B132" s="22" t="inlineStr">
+    <row r="132" ht="56" customHeight="1" s="85">
+      <c r="B132" s="0" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C132" s="23" t="inlineStr">
-        <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D132" s="38" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="n"/>
-      <c r="F132" s="50" t="n"/>
-      <c r="G132" s="70" t="inlineStr">
-        <is>
-          <t>Variaball effects still lower SHOT: the ball is altered, not the player (not on the card)</t>
-        </is>
-      </c>
-      <c r="H132" s="71" t="n"/>
-      <c r="I132" s="71" t="n"/>
-      <c r="J132" s="71" t="n"/>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t>Roswell Reach</t>
+        </is>
+      </c>
+      <c r="D132" s="0" t="inlineStr">
+        <is>
+          <t>All your Rebound bids of 1 or more count as 1 higher</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="28" customHeight="1" s="85">
       <c r="A133" s="21" t="n"/>
@@ -5707,17 +5713,17 @@
       </c>
       <c r="C133" s="24" t="inlineStr">
         <is>
-          <t>Park Shark</t>
+          <t>Floor General</t>
         </is>
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>SHOT +25%. Cannot play Move cards or shoot Threes</t>
+          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
         </is>
       </c>
       <c r="E133" s="26" t="n"/>
       <c r="F133" s="50" t="n"/>
-      <c r="G133" s="73" t="n"/>
+      <c r="G133" s="72" t="n"/>
       <c r="H133" s="71" t="n"/>
       <c r="I133" s="71" t="n"/>
       <c r="J133" s="71" t="n"/>
@@ -5731,78 +5737,70 @@
       </c>
       <c r="C134" s="23" t="inlineStr">
         <is>
-          <t>Point God</t>
+          <t>Southpaw Shooter</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="n"/>
-      <c r="F134" s="50" t="n"/>
+          <t>SHOT gains and losses are reversed</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="n"/>
+      <c r="F134" s="51" t="n"/>
       <c r="G134" s="70" t="n"/>
       <c r="H134" s="71" t="n"/>
       <c r="I134" s="71" t="n"/>
       <c r="J134" s="71" t="n"/>
     </row>
-    <row r="135" ht="56" customHeight="1" s="85">
+    <row r="135" ht="28" customHeight="1" s="85">
       <c r="A135" s="21" t="n"/>
       <c r="B135" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C135" s="24" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D135" s="25" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
+      <c r="C135" s="37" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D135" s="41" t="inlineStr">
+        <is>
+          <t>All Clamps on you grant 1 FT instead</t>
         </is>
       </c>
       <c r="E135" s="26" t="n"/>
       <c r="F135" s="50" t="n"/>
-      <c r="G135" s="73" t="inlineStr">
-        <is>
-          <t>Triggers once per act of drawing: a Draw 2 still gives only 1 extra</t>
-        </is>
-      </c>
+      <c r="G135" s="77" t="n"/>
       <c r="H135" s="71" t="n"/>
       <c r="I135" s="71" t="n"/>
       <c r="J135" s="71" t="n"/>
     </row>
-    <row r="136" ht="56" customHeight="1" s="85">
+    <row r="136" ht="28" customHeight="1" s="85">
       <c r="A136" s="21" t="n"/>
       <c r="B136" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C136" s="23" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>SHOT = 60% on any six: cards in hand, Shot Clock, shot of the round, or Score</t>
+      <c r="C136" s="37" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D136" s="38" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
         </is>
       </c>
       <c r="E136" s="7" t="n"/>
       <c r="F136" s="50" t="n"/>
-      <c r="G136" s="70" t="inlineStr">
-        <is>
-          <t>A second SHOOT (60%) button beside Shoot, shown only on a six. Ignore it when SHOT is already higher</t>
-        </is>
-      </c>
+      <c r="G136" s="70" t="n"/>
       <c r="H136" s="71" t="n"/>
       <c r="I136" s="71" t="n"/>
       <c r="J136" s="71" t="n"/>
     </row>
-    <row r="137" ht="56" customHeight="1" s="85">
+    <row r="137" ht="14" customHeight="1" s="85">
       <c r="A137" s="21" t="n"/>
       <c r="B137" s="22" t="inlineStr">
         <is>
@@ -5811,12 +5809,12 @@
       </c>
       <c r="C137" s="24" t="inlineStr">
         <is>
-          <t>Sniper</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>SHOT +25% when attempting a Three</t>
+          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
         </is>
       </c>
       <c r="E137" s="26" t="n"/>
@@ -5826,7 +5824,7 @@
       <c r="I137" s="71" t="n"/>
       <c r="J137" s="71" t="n"/>
     </row>
-    <row r="138" ht="56" customHeight="1" s="85">
+    <row r="138" ht="28" customHeight="1" s="85">
       <c r="A138" s="21" t="n"/>
       <c r="B138" s="22" t="inlineStr">
         <is>
@@ -5835,22 +5833,26 @@
       </c>
       <c r="C138" s="23" t="inlineStr">
         <is>
-          <t>Splash Cousin</t>
+          <t>Great Conditioning</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>SHOT = 100% when attempting a Three</t>
+          <t>Immediately discard all Injuries you draw and draw a new card for each</t>
         </is>
       </c>
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="50" t="n"/>
-      <c r="G138" s="70" t="n"/>
+      <c r="G138" s="70" t="inlineStr">
+        <is>
+          <t>Also discards any Injuries you already have (not on the card)</t>
+        </is>
+      </c>
       <c r="H138" s="71" t="n"/>
       <c r="I138" s="71" t="n"/>
       <c r="J138" s="71" t="n"/>
     </row>
-    <row r="139" ht="56" customHeight="1" s="85">
+    <row r="139" ht="28" customHeight="1" s="85">
       <c r="A139" s="21" t="n"/>
       <c r="B139" s="22" t="inlineStr">
         <is>
@@ -5859,12 +5861,12 @@
       </c>
       <c r="C139" s="24" t="inlineStr">
         <is>
-          <t>Competitive</t>
+          <t>Hot Hand</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
+          <t>SHOT +25% if you scored last round.</t>
         </is>
       </c>
       <c r="E139" s="26" t="n"/>
@@ -5874,7 +5876,7 @@
       <c r="I139" s="71" t="n"/>
       <c r="J139" s="71" t="n"/>
     </row>
-    <row r="140" ht="126" customHeight="1" s="85">
+    <row r="140" ht="28" customHeight="1" s="85">
       <c r="A140" s="21" t="n"/>
       <c r="B140" s="22" t="inlineStr">
         <is>
@@ -5883,26 +5885,26 @@
       </c>
       <c r="C140" s="23" t="inlineStr">
         <is>
-          <t>Lethal Shooter</t>
+          <t>Like That</t>
         </is>
       </c>
       <c r="D140" s="38" t="inlineStr">
         <is>
-          <t>SHOT = 100% when shooting as your first action after a Rebound of your own miss</t>
+          <t>Your SHOT % cannot be reduced</t>
         </is>
       </c>
       <c r="E140" s="7" t="n"/>
       <c r="F140" s="50" t="n"/>
       <c r="G140" s="70" t="inlineStr">
         <is>
-          <t>Special text: “I understand it now”</t>
+          <t>Variaball effects still lower SHOT: the ball is altered, not the player (not on the card)</t>
         </is>
       </c>
       <c r="H140" s="71" t="n"/>
       <c r="I140" s="71" t="n"/>
       <c r="J140" s="71" t="n"/>
     </row>
-    <row r="141" ht="70" customHeight="1" s="85">
+    <row r="141" ht="28" customHeight="1" s="85">
       <c r="A141" s="21" t="n"/>
       <c r="B141" s="22" t="inlineStr">
         <is>
@@ -5911,12 +5913,12 @@
       </c>
       <c r="C141" s="24" t="inlineStr">
         <is>
-          <t>Ball Pounder</t>
+          <t>Park Shark</t>
         </is>
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>Every Dribble draws 1 card but gives SHOT -10% and Shot Clock - 01</t>
+          <t>SHOT +25%. Cannot play Move cards or shoot Threes</t>
         </is>
       </c>
       <c r="E141" s="26" t="n"/>
@@ -5926,7 +5928,7 @@
       <c r="I141" s="71" t="n"/>
       <c r="J141" s="71" t="n"/>
     </row>
-    <row r="142" ht="56" customHeight="1" s="85">
+    <row r="142" ht="28" customHeight="1" s="85">
       <c r="A142" s="21" t="n"/>
       <c r="B142" s="22" t="inlineStr">
         <is>
@@ -5935,12 +5937,12 @@
       </c>
       <c r="C142" s="23" t="inlineStr">
         <is>
-          <t>Dirty Player</t>
-        </is>
-      </c>
-      <c r="D142" s="38" t="inlineStr">
-        <is>
-          <t>When sending Clamps, the clamped player discards 1 for each of your Clamps if they have any Injuries. Discard 1 whenever a Whistle triggers</t>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card following each of your passes</t>
         </is>
       </c>
       <c r="E142" s="7" t="n"/>
@@ -5950,35 +5952,35 @@
       <c r="I142" s="71" t="n"/>
       <c r="J142" s="71" t="n"/>
     </row>
-    <row r="143" s="85">
+    <row r="143" ht="56" customHeight="1" s="85">
       <c r="A143" s="21" t="n"/>
       <c r="B143" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C143" s="23" t="inlineStr">
-        <is>
-          <t>Free Agent</t>
-        </is>
-      </c>
-      <c r="D143" s="38" t="inlineStr">
-        <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="n"/>
+      <c r="C143" s="24" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D143" s="25" t="inlineStr">
+        <is>
+          <t>Draw 1 additional card after every draw effect</t>
+        </is>
+      </c>
+      <c r="E143" s="26" t="n"/>
       <c r="F143" s="50" t="n"/>
-      <c r="G143" s="70" t="inlineStr">
-        <is>
-          <t>Low priority to bring back. The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
+      <c r="G143" s="73" t="inlineStr">
+        <is>
+          <t>Triggers once per act of drawing: a Draw 2 still gives only 1 extra</t>
         </is>
       </c>
       <c r="H143" s="71" t="n"/>
       <c r="I143" s="71" t="n"/>
       <c r="J143" s="71" t="n"/>
     </row>
-    <row r="144" s="85">
+    <row r="144" ht="56" customHeight="1" s="85">
       <c r="A144" s="21" t="n"/>
       <c r="B144" s="22" t="inlineStr">
         <is>
@@ -5987,50 +5989,50 @@
       </c>
       <c r="C144" s="23" t="inlineStr">
         <is>
-          <t>Franchise Player</t>
-        </is>
-      </c>
-      <c r="D144" s="38" t="inlineStr">
-        <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>SHOT = 60% on any six: cards in hand, Shot Clock, shot of the round, or Score</t>
         </is>
       </c>
       <c r="E144" s="7" t="n"/>
       <c r="F144" s="50" t="n"/>
-      <c r="G144" s="70" t="n"/>
+      <c r="G144" s="70" t="inlineStr">
+        <is>
+          <t>A second SHOOT (60%) button beside Shoot, shown only on a six. Ignore it when SHOT is already higher</t>
+        </is>
+      </c>
       <c r="H144" s="71" t="n"/>
       <c r="I144" s="71" t="n"/>
       <c r="J144" s="71" t="n"/>
     </row>
-    <row r="145" s="85">
+    <row r="145" ht="56" customHeight="1" s="85">
       <c r="A145" s="21" t="n"/>
       <c r="B145" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C145" s="23" t="inlineStr">
-        <is>
-          <t>Fundamentalist</t>
-        </is>
-      </c>
-      <c r="D145" s="38" t="inlineStr">
-        <is>
-          <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent. Discards the current ball</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="n"/>
+      <c r="C145" s="24" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D145" s="25" t="inlineStr">
+        <is>
+          <t>SHOT +25% when attempting a Three</t>
+        </is>
+      </c>
+      <c r="E145" s="26" t="n"/>
       <c r="F145" s="50" t="n"/>
-      <c r="G145" s="70" t="inlineStr">
-        <is>
-          <t>The ball is discarded once, on activation</t>
-        </is>
-      </c>
+      <c r="G145" s="72" t="n"/>
       <c r="H145" s="71" t="n"/>
       <c r="I145" s="71" t="n"/>
       <c r="J145" s="71" t="n"/>
     </row>
-    <row r="146" s="85">
+    <row r="146" ht="56" customHeight="1" s="85">
       <c r="A146" s="21" t="n"/>
       <c r="B146" s="22" t="inlineStr">
         <is>
@@ -6039,282 +6041,277 @@
       </c>
       <c r="C146" s="23" t="inlineStr">
         <is>
-          <t>Moves At Own Pace</t>
-        </is>
-      </c>
-      <c r="D146" s="38" t="inlineStr">
-        <is>
-          <t>Cannot be called for Traveling or Shot Clock violations</t>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>SHOT = 100% when attempting a Three</t>
         </is>
       </c>
       <c r="E146" s="7" t="n"/>
-      <c r="F146" s="50" t="n">
-        <v>1</v>
-      </c>
+      <c r="F146" s="50" t="n"/>
       <c r="G146" s="70" t="n"/>
       <c r="H146" s="71" t="n"/>
       <c r="I146" s="71" t="n"/>
       <c r="J146" s="71" t="n"/>
     </row>
-    <row r="147" s="85">
+    <row r="147" ht="56" customHeight="1" s="85">
       <c r="A147" s="21" t="n"/>
       <c r="B147" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C147" s="23" t="inlineStr">
-        <is>
-          <t>Equalizer</t>
-        </is>
-      </c>
-      <c r="D147" s="38" t="inlineStr">
-        <is>
-          <t>You may Discard this card when shooting: SHOT = 100%. All players' pts become your new total pts.</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="n"/>
+      <c r="C147" s="24" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D147" s="25" t="inlineStr">
+        <is>
+          <t>All Clamps on you have no effect on SHOT %</t>
+        </is>
+      </c>
+      <c r="E147" s="26" t="n"/>
       <c r="F147" s="50" t="n"/>
-      <c r="G147" s="70" t="inlineStr">
-        <is>
-          <t>The points change comes after the make</t>
-        </is>
-      </c>
+      <c r="G147" s="72" t="n"/>
       <c r="H147" s="71" t="n"/>
       <c r="I147" s="71" t="n"/>
       <c r="J147" s="71" t="n"/>
     </row>
-    <row r="148" s="85">
-      <c r="A148" s="27" t="n"/>
-      <c r="B148" s="28" t="inlineStr">
+    <row r="148" ht="126" customHeight="1" s="85">
+      <c r="A148" s="21" t="n"/>
+      <c r="B148" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C148" s="56" t="inlineStr">
-        <is>
-          <t>Varsitile</t>
-        </is>
-      </c>
-      <c r="D148" s="63" t="inlineStr">
-        <is>
-          <t>You can play more than 1 Varena and Variaball per turn. Once per possession, you can exchange the Varena and/or ball for one in the Discards</t>
-        </is>
-      </c>
-      <c r="E148" s="58" t="n"/>
-      <c r="F148" s="61" t="n"/>
-      <c r="G148" s="75" t="inlineStr">
-        <is>
-          <t>One use can exchange both</t>
-        </is>
-      </c>
-      <c r="H148" s="76" t="n"/>
-      <c r="I148" s="76" t="n"/>
-      <c r="J148" s="76" t="n"/>
-    </row>
-    <row r="149" s="85">
-      <c r="A149" s="27" t="n"/>
-      <c r="B149" s="28" t="inlineStr">
+      <c r="C148" s="23" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D148" s="38" t="inlineStr">
+        <is>
+          <t>SHOT = 100% when shooting as your first action after a Rebound of your own miss</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="n"/>
+      <c r="F148" s="50" t="n"/>
+      <c r="G148" s="70" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H148" s="71" t="n"/>
+      <c r="I148" s="71" t="n"/>
+      <c r="J148" s="71" t="n"/>
+    </row>
+    <row r="149" ht="70" customHeight="1" s="85">
+      <c r="A149" s="21" t="n"/>
+      <c r="B149" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C149" s="56" t="inlineStr">
-        <is>
-          <t>Brawl Handler</t>
-        </is>
-      </c>
-      <c r="D149" s="63" t="inlineStr">
-        <is>
-          <t>Remove all your Clamps when you change the ball</t>
-        </is>
-      </c>
-      <c r="E149" s="58" t="n"/>
-      <c r="F149" s="61" t="n"/>
-      <c r="G149" s="75" t="n"/>
-      <c r="H149" s="76" t="n"/>
-    </row>
-    <row r="150" s="85">
-      <c r="A150" s="27" t="n"/>
-      <c r="B150" s="28" t="inlineStr">
+      <c r="C149" s="24" t="inlineStr">
+        <is>
+          <t>Ball Pounder</t>
+        </is>
+      </c>
+      <c r="D149" s="25" t="inlineStr">
+        <is>
+          <t>Every Dribble draws 1 card but gives SHOT -10% and Shot Clock - 01</t>
+        </is>
+      </c>
+      <c r="E149" s="26" t="n"/>
+      <c r="F149" s="50" t="n"/>
+      <c r="G149" s="73" t="n"/>
+      <c r="H149" s="71" t="n"/>
+      <c r="I149" s="71" t="n"/>
+      <c r="J149" s="71" t="n"/>
+    </row>
+    <row r="150" ht="56" customHeight="1" s="85">
+      <c r="A150" s="21" t="n"/>
+      <c r="B150" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C150" s="56" t="inlineStr">
-        <is>
-          <t>Baller</t>
-        </is>
-      </c>
-      <c r="D150" s="63" t="inlineStr">
-        <is>
-          <t>Draw 1 card each time you change the ball</t>
-        </is>
-      </c>
-      <c r="E150" s="58" t="n"/>
-      <c r="F150" s="61" t="n"/>
-      <c r="G150" s="75" t="n"/>
-      <c r="H150" s="76" t="n"/>
-    </row>
-    <row r="151" ht="42" customHeight="1" s="85">
-      <c r="A151" s="52" t="inlineStr">
-        <is>
-          <t>Varena</t>
-        </is>
-      </c>
-      <c r="B151" s="53">
-        <f>COUNTIF($B$152:$B$181,"Varena")</f>
-        <v/>
-      </c>
-      <c r="C151" s="54" t="n"/>
-      <c r="D151" s="54" t="n"/>
-      <c r="E151" s="54" t="n"/>
-      <c r="F151" s="55" t="n"/>
-      <c r="G151" s="66" t="n"/>
-      <c r="H151" s="67" t="n"/>
-      <c r="I151" s="67" t="n"/>
-      <c r="J151" s="67" t="n"/>
+      <c r="C150" s="23" t="inlineStr">
+        <is>
+          <t>Dirty Player</t>
+        </is>
+      </c>
+      <c r="D150" s="38" t="inlineStr">
+        <is>
+          <t>When sending Clamps, the clamped player discards 1 for each of your Clamps if they have any Injuries. Discard 1 whenever a Whistle triggers</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="n"/>
+      <c r="F150" s="50" t="n"/>
+      <c r="G150" s="70" t="n"/>
+      <c r="H150" s="71" t="n"/>
+      <c r="I150" s="71" t="n"/>
+      <c r="J150" s="71" t="n"/>
+    </row>
+    <row r="151" s="85">
+      <c r="A151" s="21" t="n"/>
+      <c r="B151" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C151" s="23" t="inlineStr">
+        <is>
+          <t>Free Agent</t>
+        </is>
+      </c>
+      <c r="D151" s="38" t="inlineStr">
+        <is>
+          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="n"/>
+      <c r="F151" s="50" t="n"/>
+      <c r="G151" s="70" t="inlineStr">
+        <is>
+          <t>Low priority to bring back. The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
+        </is>
+      </c>
+      <c r="H151" s="71" t="n"/>
+      <c r="I151" s="71" t="n"/>
+      <c r="J151" s="71" t="n"/>
     </row>
     <row r="152" s="85">
-      <c r="A152" s="27" t="n"/>
-      <c r="B152" s="28" t="inlineStr">
-        <is>
-          <t>Varena</t>
-        </is>
-      </c>
-      <c r="C152" s="56" t="inlineStr">
-        <is>
-          <t>Cardwood</t>
-        </is>
-      </c>
-      <c r="D152" s="63" t="inlineStr">
-        <is>
-          <t>Changes the court back to basic</t>
-        </is>
-      </c>
-      <c r="E152" s="58" t="n"/>
-      <c r="F152" s="61" t="n">
-        <v>5</v>
-      </c>
-      <c r="G152" s="75" t="inlineStr">
-        <is>
-          <t>Also the floor every game opens on, before anybody plays a Varena over it</t>
-        </is>
-      </c>
-      <c r="H152" s="76" t="n"/>
-      <c r="I152" s="76" t="n"/>
-      <c r="J152" s="76" t="n"/>
+      <c r="A152" s="21" t="n"/>
+      <c r="B152" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C152" s="23" t="inlineStr">
+        <is>
+          <t>Franchise Player</t>
+        </is>
+      </c>
+      <c r="D152" s="38" t="inlineStr">
+        <is>
+          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="n"/>
+      <c r="F152" s="50" t="n"/>
+      <c r="G152" s="70" t="n"/>
+      <c r="H152" s="71" t="n"/>
+      <c r="I152" s="71" t="n"/>
+      <c r="J152" s="71" t="n"/>
     </row>
     <row r="153" s="85">
-      <c r="A153" s="27" t="n"/>
-      <c r="B153" s="28" t="inlineStr">
-        <is>
-          <t>Varena</t>
-        </is>
-      </c>
-      <c r="C153" s="56" t="inlineStr">
-        <is>
-          <t>Prime Parquet</t>
-        </is>
-      </c>
-      <c r="D153" s="63" t="inlineStr">
-        <is>
-          <t>SHOT +20%</t>
-        </is>
-      </c>
-      <c r="E153" s="58" t="n"/>
-      <c r="F153" s="61" t="n">
-        <v>3</v>
-      </c>
-      <c r="G153" s="75" t="n"/>
-      <c r="H153" s="76" t="n"/>
-      <c r="I153" s="76" t="n"/>
-      <c r="J153" s="76" t="n"/>
+      <c r="A153" s="21" t="n"/>
+      <c r="B153" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C153" s="23" t="inlineStr">
+        <is>
+          <t>Fundamentalist</t>
+        </is>
+      </c>
+      <c r="D153" s="38" t="inlineStr">
+        <is>
+          <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent. Discards the current ball</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="n"/>
+      <c r="F153" s="50" t="n"/>
+      <c r="G153" s="70" t="inlineStr">
+        <is>
+          <t>The ball is discarded once, on activation</t>
+        </is>
+      </c>
+      <c r="H153" s="71" t="n"/>
+      <c r="I153" s="71" t="n"/>
+      <c r="J153" s="71" t="n"/>
     </row>
     <row r="154" s="85">
-      <c r="A154" s="27" t="n"/>
-      <c r="B154" s="28" t="inlineStr">
-        <is>
-          <t>Varena</t>
-        </is>
-      </c>
-      <c r="C154" s="56" t="inlineStr">
-        <is>
-          <t>Lacktop</t>
-        </is>
-      </c>
-      <c r="D154" s="63" t="inlineStr">
-        <is>
-          <t>SHOT -20%</t>
-        </is>
-      </c>
-      <c r="E154" s="58" t="n"/>
-      <c r="F154" s="61" t="n">
-        <v>3</v>
-      </c>
-      <c r="G154" s="75" t="inlineStr">
-        <is>
-          <t>Always Prime Parquet's opposite</t>
-        </is>
-      </c>
-      <c r="H154" s="76" t="n"/>
-      <c r="I154" s="76" t="n"/>
-      <c r="J154" s="76" t="n"/>
+      <c r="A154" s="21" t="n"/>
+      <c r="B154" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C154" s="23" t="inlineStr">
+        <is>
+          <t>Moves At Own Pace</t>
+        </is>
+      </c>
+      <c r="D154" s="38" t="inlineStr">
+        <is>
+          <t>Cannot be called for Traveling or Shot Clock violations</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="n"/>
+      <c r="F154" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="70" t="n"/>
+      <c r="H154" s="71" t="n"/>
+      <c r="I154" s="71" t="n"/>
+      <c r="J154" s="71" t="n"/>
     </row>
     <row r="155" s="85">
-      <c r="A155" s="27" t="n"/>
-      <c r="B155" s="28" t="inlineStr">
-        <is>
-          <t>Varena</t>
-        </is>
-      </c>
-      <c r="C155" s="56" t="inlineStr">
-        <is>
-          <t>Smacktop</t>
-        </is>
-      </c>
-      <c r="D155" s="63" t="inlineStr">
-        <is>
-          <t>Clear All Whistles. Whistles Cannot Be Played. All Clamps are enhanced</t>
-        </is>
-      </c>
-      <c r="E155" s="58" t="n"/>
-      <c r="F155" s="61" t="n">
-        <v>3</v>
-      </c>
-      <c r="G155" s="75" t="inlineStr">
-        <is>
-          <t>Enhanced: +10% more reduction, one more card discarded, one more card locked</t>
-        </is>
-      </c>
-      <c r="H155" s="76" t="n"/>
-      <c r="I155" s="76" t="n"/>
-      <c r="J155" s="76" t="n"/>
+      <c r="A155" s="21" t="n"/>
+      <c r="B155" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C155" s="23" t="inlineStr">
+        <is>
+          <t>Equalizer</t>
+        </is>
+      </c>
+      <c r="D155" s="38" t="inlineStr">
+        <is>
+          <t>You may Discard this card when shooting: SHOT = 100%. All players' pts become your new total pts.</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="n"/>
+      <c r="F155" s="50" t="n"/>
+      <c r="G155" s="70" t="inlineStr">
+        <is>
+          <t>The points change comes after the make</t>
+        </is>
+      </c>
+      <c r="H155" s="71" t="n"/>
+      <c r="I155" s="71" t="n"/>
+      <c r="J155" s="71" t="n"/>
     </row>
     <row r="156" s="85">
       <c r="A156" s="27" t="n"/>
       <c r="B156" s="28" t="inlineStr">
         <is>
-          <t>Varena</t>
+          <t>Intangible</t>
         </is>
       </c>
       <c r="C156" s="56" t="inlineStr">
         <is>
-          <t>Boarder Court</t>
+          <t>Varsitile</t>
         </is>
       </c>
       <c r="D156" s="63" t="inlineStr">
         <is>
-          <t>Off your own miss, your Rebound bid counts as one card more</t>
+          <t>You can play more than 1 Varena and Variaball per turn. Once per possession, you can exchange the Varena and/or ball for one in the Discards</t>
         </is>
       </c>
       <c r="E156" s="58" t="n"/>
-      <c r="F156" s="61" t="n">
-        <v>1</v>
-      </c>
+      <c r="F156" s="61" t="n"/>
       <c r="G156" s="75" t="inlineStr">
         <is>
-          <t>Still needs a bid of at least one</t>
+          <t>One use can exchange both</t>
         </is>
       </c>
       <c r="H156" s="76" t="n"/>
@@ -6325,91 +6322,64 @@
       <c r="A157" s="27" t="n"/>
       <c r="B157" s="28" t="inlineStr">
         <is>
-          <t>Varena</t>
+          <t>Intangible</t>
         </is>
       </c>
       <c r="C157" s="56" t="inlineStr">
         <is>
-          <t>Dim Dome</t>
+          <t>Brawl Handler</t>
         </is>
       </c>
       <c r="D157" s="63" t="inlineStr">
         <is>
-          <t>SHOT is hidden from everyone but the ball holder</t>
+          <t>Remove all your Clamps when you change the ball</t>
         </is>
       </c>
       <c r="E157" s="58" t="n"/>
-      <c r="F157" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" s="75" t="inlineStr">
-        <is>
-          <t>On a table, flip the % device face down</t>
-        </is>
-      </c>
+      <c r="F157" s="61" t="n"/>
+      <c r="G157" s="75" t="n"/>
       <c r="H157" s="76" t="n"/>
-      <c r="I157" s="76" t="n"/>
-      <c r="J157" s="76" t="n"/>
     </row>
     <row r="158" s="85">
       <c r="A158" s="27" t="n"/>
       <c r="B158" s="28" t="inlineStr">
         <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C158" s="56" t="inlineStr">
+        <is>
+          <t>Baller</t>
+        </is>
+      </c>
+      <c r="D158" s="63" t="inlineStr">
+        <is>
+          <t>Draw 1 card each time you change the ball</t>
+        </is>
+      </c>
+      <c r="E158" s="58" t="n"/>
+      <c r="F158" s="61" t="n"/>
+      <c r="G158" s="75" t="n"/>
+      <c r="H158" s="76" t="n"/>
+    </row>
+    <row r="159" ht="42" customHeight="1" s="85">
+      <c r="A159" s="52" t="inlineStr">
+        <is>
           <t>Varena</t>
         </is>
       </c>
-      <c r="C158" s="56" t="inlineStr">
-        <is>
-          <t>Tri-hard Tiling</t>
-        </is>
-      </c>
-      <c r="D158" s="63" t="inlineStr">
-        <is>
-          <t>Hand limit 3</t>
-        </is>
-      </c>
-      <c r="E158" s="58" t="n"/>
-      <c r="F158" s="61" t="n">
-        <v>3</v>
-      </c>
-      <c r="G158" s="75" t="inlineStr">
-        <is>
-          <t>Hands over 3 are cut to 3 when it lands (owner picks). A draw into a hand of 3 is discarded</t>
-        </is>
-      </c>
-      <c r="H158" s="76" t="n"/>
-      <c r="I158" s="76" t="n"/>
-      <c r="J158" s="76" t="n"/>
-    </row>
-    <row r="159" s="85">
-      <c r="A159" s="27" t="n"/>
-      <c r="B159" s="28" t="inlineStr">
-        <is>
-          <t>Varena</t>
-        </is>
-      </c>
-      <c r="C159" s="56" t="inlineStr">
-        <is>
-          <t>Policeum</t>
-        </is>
-      </c>
-      <c r="D159" s="63" t="inlineStr">
-        <is>
-          <t>Referees do not leave once triggered</t>
-        </is>
-      </c>
-      <c r="E159" s="58" t="n"/>
-      <c r="F159" s="61" t="n">
-        <v>3</v>
-      </c>
-      <c r="G159" s="75" t="inlineStr">
-        <is>
-          <t>A called referee stays until the floor changes. The 3-ref cap bounds it</t>
-        </is>
-      </c>
-      <c r="H159" s="76" t="n"/>
-      <c r="I159" s="76" t="n"/>
-      <c r="J159" s="76" t="n"/>
+      <c r="B159" s="53">
+        <f>COUNTIF($B$160:$B$189,"Varena")</f>
+        <v/>
+      </c>
+      <c r="C159" s="54" t="n"/>
+      <c r="D159" s="54" t="n"/>
+      <c r="E159" s="54" t="n"/>
+      <c r="F159" s="55" t="n"/>
+      <c r="G159" s="66" t="n"/>
+      <c r="H159" s="67" t="n"/>
+      <c r="I159" s="67" t="n"/>
+      <c r="J159" s="67" t="n"/>
     </row>
     <row r="160" s="85">
       <c r="A160" s="27" t="n"/>
@@ -6420,21 +6390,21 @@
       </c>
       <c r="C160" s="56" t="inlineStr">
         <is>
-          <t>Kiddie Court</t>
+          <t>Cardwood</t>
         </is>
       </c>
       <c r="D160" s="63" t="inlineStr">
         <is>
-          <t>SHOT +10%. Dunks +10%. Three-point shots cannot be attempted.</t>
+          <t>Changes the court back to basic</t>
         </is>
       </c>
       <c r="E160" s="58" t="n"/>
       <c r="F160" s="61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G160" s="75" t="inlineStr">
         <is>
-          <t>Shuts off every card that makes a three (Kick-Out)</t>
+          <t>Also the floor every game opens on, before anybody plays a Varena over it</t>
         </is>
       </c>
       <c r="H160" s="76" t="n"/>
@@ -6450,23 +6420,19 @@
       </c>
       <c r="C161" s="56" t="inlineStr">
         <is>
-          <t>Recharging Resin</t>
+          <t>Prime Parquet</t>
         </is>
       </c>
       <c r="D161" s="63" t="inlineStr">
         <is>
-          <t>Everyone refills to a hand of 5 at the start of their possession</t>
+          <t>SHOT +20%</t>
         </is>
       </c>
       <c r="E161" s="58" t="n"/>
       <c r="F161" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="G161" s="75" t="inlineStr">
-        <is>
-          <t>After the draw for turn</t>
-        </is>
-      </c>
+      <c r="G161" s="75" t="n"/>
       <c r="H161" s="76" t="n"/>
       <c r="I161" s="76" t="n"/>
       <c r="J161" s="76" t="n"/>
@@ -6480,12 +6446,12 @@
       </c>
       <c r="C162" s="56" t="inlineStr">
         <is>
-          <t>Contact Court</t>
+          <t>Lacktop</t>
         </is>
       </c>
       <c r="D162" s="63" t="inlineStr">
         <is>
-          <t>Being clamped: take 1 FT. The Clamp still lands</t>
+          <t>SHOT -20%</t>
         </is>
       </c>
       <c r="E162" s="58" t="n"/>
@@ -6494,7 +6460,7 @@
       </c>
       <c r="G162" s="75" t="inlineStr">
         <is>
-          <t>One free throw however many Clamps land</t>
+          <t>Always Prime Parquet's opposite</t>
         </is>
       </c>
       <c r="H162" s="76" t="n"/>
@@ -6510,21 +6476,21 @@
       </c>
       <c r="C163" s="56" t="inlineStr">
         <is>
-          <t>MVPiquia</t>
+          <t>Smacktop</t>
         </is>
       </c>
       <c r="D163" s="63" t="inlineStr">
         <is>
-          <t>The highest scorer refills to 5 at the start of their possession</t>
+          <t>Clear All Whistles. Whistles Cannot Be Played. All Clamps are enhanced</t>
         </is>
       </c>
       <c r="E163" s="58" t="n"/>
       <c r="F163" s="61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G163" s="75" t="inlineStr">
         <is>
-          <t>A tie for the lead counts</t>
+          <t>Enhanced: +10% more reduction, one more card discarded, one more card locked</t>
         </is>
       </c>
       <c r="H163" s="76" t="n"/>
@@ -6540,19 +6506,23 @@
       </c>
       <c r="C164" s="56" t="inlineStr">
         <is>
-          <t>Polypaypylene</t>
+          <t>Boarder Court</t>
         </is>
       </c>
       <c r="D164" s="63" t="inlineStr">
         <is>
-          <t>Making a shot: Draw 3</t>
+          <t>Off your own miss, your Rebound bid counts as one card more</t>
         </is>
       </c>
       <c r="E164" s="58" t="n"/>
       <c r="F164" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="G164" s="75" t="n"/>
+      <c r="G164" s="75" t="inlineStr">
+        <is>
+          <t>Still needs a bid of at least one</t>
+        </is>
+      </c>
       <c r="H164" s="76" t="n"/>
       <c r="I164" s="76" t="n"/>
       <c r="J164" s="76" t="n"/>
@@ -6566,21 +6536,21 @@
       </c>
       <c r="C165" s="56" t="inlineStr">
         <is>
-          <t>Recoverena</t>
+          <t>Dim Dome</t>
         </is>
       </c>
       <c r="D165" s="63" t="inlineStr">
         <is>
-          <t>Discard all Injuries. A new Injury is discarded, and that player draws 1</t>
+          <t>SHOT is hidden from everyone but the ball holder</t>
         </is>
       </c>
       <c r="E165" s="58" t="n"/>
       <c r="F165" s="61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G165" s="75" t="inlineStr">
         <is>
-          <t>Every player's Injuries go when it lands</t>
+          <t>On a table, flip the % device face down</t>
         </is>
       </c>
       <c r="H165" s="76" t="n"/>
@@ -6596,21 +6566,21 @@
       </c>
       <c r="C166" s="56" t="inlineStr">
         <is>
-          <t>Carousel Court</t>
+          <t>Tri-hard Tiling</t>
         </is>
       </c>
       <c r="D166" s="63" t="inlineStr">
         <is>
-          <t>Declare left or right. Every possession, hands move one seat that way</t>
+          <t>Hand limit 3</t>
         </is>
       </c>
       <c r="E166" s="58" t="n"/>
       <c r="F166" s="61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G166" s="75" t="inlineStr">
         <is>
-          <t>Declared by whoever plays it</t>
+          <t>Hands over 3 are cut to 3 when it lands (owner picks). A draw into a hand of 3 is discarded</t>
         </is>
       </c>
       <c r="H166" s="76" t="n"/>
@@ -6621,26 +6591,26 @@
       <c r="A167" s="27" t="n"/>
       <c r="B167" s="28" t="inlineStr">
         <is>
-          <t>Varena</t>
+          <t>Retired Varena</t>
         </is>
       </c>
       <c r="C167" s="56" t="inlineStr">
         <is>
-          <t>Traderous Tarmac</t>
+          <t>Policeum</t>
         </is>
       </c>
       <c r="D167" s="63" t="inlineStr">
         <is>
-          <t>During your turn, hand off any number of the Clamps on you to other players</t>
+          <t>Referees do not leave once triggered</t>
         </is>
       </c>
       <c r="E167" s="58" t="n"/>
       <c r="F167" s="61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" s="75" t="inlineStr">
         <is>
-          <t>The player assigns each Clamp: all to one player, one each, or any split</t>
+          <t>Out of the deck (2026-09-15): its referees could lock a game into a loop</t>
         </is>
       </c>
       <c r="H167" s="76" t="n"/>
@@ -6656,12 +6626,12 @@
       </c>
       <c r="C168" s="56" t="inlineStr">
         <is>
-          <t>Clearcoat Court</t>
+          <t>Kiddie Court</t>
         </is>
       </c>
       <c r="D168" s="63" t="inlineStr">
         <is>
-          <t>Every possession: clear all referees, Clamps, Injuries and Intangibles</t>
+          <t>SHOT +10%. Dunks +10%. Three-point shots cannot be attempted.</t>
         </is>
       </c>
       <c r="E168" s="58" t="n"/>
@@ -6670,7 +6640,7 @@
       </c>
       <c r="G168" s="75" t="inlineStr">
         <is>
-          <t>Standing Clamps only; Clamps still in the air land after the wipe</t>
+          <t>Shuts off every card that makes a three (Kick-Out)</t>
         </is>
       </c>
       <c r="H168" s="76" t="n"/>
@@ -6686,19 +6656,23 @@
       </c>
       <c r="C169" s="56" t="inlineStr">
         <is>
-          <t>Malice Palace</t>
+          <t>Recharging Resin</t>
         </is>
       </c>
       <c r="D169" s="63" t="inlineStr">
         <is>
-          <t>At the start of your possession, before your draw: discard your hand</t>
+          <t>Everyone refills to a hand of 5 at the start of their possession</t>
         </is>
       </c>
       <c r="E169" s="58" t="n"/>
       <c r="F169" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G169" s="75" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G169" s="75" t="inlineStr">
+        <is>
+          <t>After the draw for turn</t>
+        </is>
+      </c>
       <c r="H169" s="76" t="n"/>
       <c r="I169" s="76" t="n"/>
       <c r="J169" s="76" t="n"/>
@@ -6712,14 +6686,12 @@
       </c>
       <c r="C170" s="56" t="inlineStr">
         <is>
-          <t>Turnstile Tile</t>
+          <t>Contact Court</t>
         </is>
       </c>
       <c r="D170" s="63" t="inlineStr">
         <is>
-          <t>Upright: SHOT +25%
-Reversed: SHOT -25%
-Turn this card at the start of each possession</t>
+          <t>Being clamped: take 1 FT. The Clamp still lands</t>
         </is>
       </c>
       <c r="E170" s="58" t="n"/>
@@ -6728,7 +6700,7 @@
       </c>
       <c r="G170" s="75" t="inlineStr">
         <is>
-          <t>+25% the possession it lands</t>
+          <t>One free throw however many Clamps land</t>
         </is>
       </c>
       <c r="H170" s="76" t="n"/>
@@ -6744,19 +6716,23 @@
       </c>
       <c r="C171" s="56" t="inlineStr">
         <is>
-          <t>Roleplayer Polymer</t>
+          <t>MVPiquia</t>
         </is>
       </c>
       <c r="D171" s="63" t="inlineStr">
         <is>
-          <t>Every possession, everyone but the turn player draws 1</t>
+          <t>The highest scorer refills to 5 at the start of their possession</t>
         </is>
       </c>
       <c r="E171" s="58" t="n"/>
       <c r="F171" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="G171" s="75" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G171" s="75" t="inlineStr">
+        <is>
+          <t>A tie for the lead counts</t>
+        </is>
+      </c>
       <c r="H171" s="76" t="n"/>
       <c r="I171" s="76" t="n"/>
       <c r="J171" s="76" t="n"/>
@@ -6770,23 +6746,19 @@
       </c>
       <c r="C172" s="56" t="inlineStr">
         <is>
-          <t>Variaball Vinyl</t>
+          <t>Polypaypylene</t>
         </is>
       </c>
       <c r="D172" s="63" t="inlineStr">
         <is>
-          <t>The draw for turn goes to a random player each possession</t>
+          <t>Making a shot: Draw 3</t>
         </is>
       </c>
       <c r="E172" s="58" t="n"/>
       <c r="F172" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="G172" s="75" t="inlineStr">
-        <is>
-          <t>Can be the turn player</t>
-        </is>
-      </c>
+      <c r="G172" s="75" t="n"/>
       <c r="H172" s="76" t="n"/>
       <c r="I172" s="76" t="n"/>
       <c r="J172" s="76" t="n"/>
@@ -6800,12 +6772,12 @@
       </c>
       <c r="C173" s="56" t="inlineStr">
         <is>
-          <t>Gravi-Gym</t>
+          <t>Recoverena</t>
         </is>
       </c>
       <c r="D173" s="63" t="inlineStr">
         <is>
-          <t>SHOT -10%. No dunks</t>
+          <t>Discard all Injuries. A new Injury is discarded, and that player draws 1</t>
         </is>
       </c>
       <c r="E173" s="58" t="n"/>
@@ -6814,7 +6786,7 @@
       </c>
       <c r="G173" s="75" t="inlineStr">
         <is>
-          <t>Cards that dunk cannot be played</t>
+          <t>Every player's Injuries go when it lands</t>
         </is>
       </c>
       <c r="H173" s="76" t="n"/>
@@ -6830,21 +6802,21 @@
       </c>
       <c r="C174" s="56" t="inlineStr">
         <is>
-          <t>Vintage Varnish</t>
+          <t>Carousel Court</t>
         </is>
       </c>
       <c r="D174" s="63" t="inlineStr">
         <is>
-          <t>Shot Clock 14. No threes. No Variaballs. 1 Intangible per player</t>
+          <t>Declare left or right. Every possession, hands move one seat that way</t>
         </is>
       </c>
       <c r="E174" s="58" t="n"/>
       <c r="F174" s="61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G174" s="75" t="inlineStr">
         <is>
-          <t>Discards the ball in play when it lands</t>
+          <t>Declared by whoever plays it</t>
         </is>
       </c>
       <c r="H174" s="76" t="n"/>
@@ -6860,21 +6832,21 @@
       </c>
       <c r="C175" s="56" t="inlineStr">
         <is>
-          <t>S.O.S — Sell-Out Stadium</t>
+          <t>Traderous Tarmac</t>
         </is>
       </c>
       <c r="D175" s="63" t="inlineStr">
         <is>
-          <t>A Three may be attempted as a two at 2X SHOT</t>
+          <t>During your turn, hand off any number of the Clamps on you to other players</t>
         </is>
       </c>
       <c r="E175" s="58" t="n"/>
       <c r="F175" s="61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G175" s="75" t="inlineStr">
         <is>
-          <t>Keeps every other printed effect</t>
+          <t>The player assigns each Clamp: all to one player, one each, or any split</t>
         </is>
       </c>
       <c r="H175" s="76" t="n"/>
@@ -6890,21 +6862,21 @@
       </c>
       <c r="C176" s="56" t="inlineStr">
         <is>
-          <t>Grayvstone</t>
+          <t>Clearcoat Court</t>
         </is>
       </c>
       <c r="D176" s="63" t="inlineStr">
         <is>
-          <t>Each possession, the ball becomes the last Variaball in the discards</t>
+          <t>Every possession: clear all referees, Clamps, Injuries and Intangibles</t>
         </is>
       </c>
       <c r="E176" s="58" t="n"/>
       <c r="F176" s="61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G176" s="75" t="inlineStr">
         <is>
-          <t>With none there, nothing happens</t>
+          <t>Standing Clamps only; Clamps still in the air land after the wipe</t>
         </is>
       </c>
       <c r="H176" s="76" t="n"/>
@@ -6920,17 +6892,17 @@
       </c>
       <c r="C177" s="56" t="inlineStr">
         <is>
-          <t>Con-crete</t>
+          <t>Malice Palace</t>
         </is>
       </c>
       <c r="D177" s="63" t="inlineStr">
         <is>
-          <t>Move cards: SHOT -10%</t>
+          <t>At the start of your possession, before your draw: discard your hand</t>
         </is>
       </c>
       <c r="E177" s="58" t="n"/>
       <c r="F177" s="61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G177" s="75" t="n"/>
       <c r="H177" s="76" t="n"/>
@@ -6946,12 +6918,14 @@
       </c>
       <c r="C178" s="56" t="inlineStr">
         <is>
-          <t>Spazzphalt</t>
+          <t>Turnstile Tile</t>
         </is>
       </c>
       <c r="D178" s="63" t="inlineStr">
         <is>
-          <t>SHOT = ?</t>
+          <t>Upright: SHOT +25%
+Reversed: SHOT -25%
+Turn this card at the start of each possession</t>
         </is>
       </c>
       <c r="E178" s="58" t="n"/>
@@ -6960,7 +6934,7 @@
       </c>
       <c r="G178" s="75" t="inlineStr">
         <is>
-          <t>A random 0–100%, in steps of 5</t>
+          <t>+25% the possession it lands</t>
         </is>
       </c>
       <c r="H178" s="76" t="n"/>
@@ -6976,23 +6950,19 @@
       </c>
       <c r="C179" s="56" t="inlineStr">
         <is>
-          <t>Frostbite Finish</t>
+          <t>Roleplayer Polymer</t>
         </is>
       </c>
       <c r="D179" s="63" t="inlineStr">
         <is>
-          <t>Playing a Move costs discarding 1 other card</t>
+          <t>Every possession, everyone but the turn player draws 1</t>
         </is>
       </c>
       <c r="E179" s="58" t="n"/>
       <c r="F179" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="G179" s="75" t="inlineStr">
-        <is>
-          <t>The owner picks the card. A Move that is your whole hand can't be played</t>
-        </is>
-      </c>
+      <c r="G179" s="75" t="n"/>
       <c r="H179" s="76" t="n"/>
       <c r="I179" s="76" t="n"/>
       <c r="J179" s="76" t="n"/>
@@ -7006,26 +6976,21 @@
       </c>
       <c r="C180" s="56" t="inlineStr">
         <is>
-          <t>The Future</t>
+          <t>Variaball Vinyl</t>
         </is>
       </c>
       <c r="D180" s="63" t="inlineStr">
         <is>
-          <t>SHOT +10% and Draw 1 card when playing a Move card.
-SHOT -10% while Passing.</t>
-        </is>
-      </c>
-      <c r="E180" s="58" t="inlineStr">
-        <is>
-          <t>You may Discard 1 card during a three attempt to make it worth four pts (at SHOT-10%)</t>
-        </is>
-      </c>
+          <t>The draw for turn goes to a random player each possession</t>
+        </is>
+      </c>
+      <c r="E180" s="58" t="n"/>
       <c r="F180" s="61" t="n">
         <v>1</v>
       </c>
       <c r="G180" s="75" t="inlineStr">
         <is>
-          <t>New in the SHOT audit (2026-09-14). Special Moves count as Moves</t>
+          <t>Can be the turn player</t>
         </is>
       </c>
       <c r="H180" s="76" t="n"/>
@@ -7041,12 +7006,12 @@
       </c>
       <c r="C181" s="56" t="inlineStr">
         <is>
-          <t>Tick-Tock Tile</t>
+          <t>Gravi-Gym</t>
         </is>
       </c>
       <c r="D181" s="63" t="inlineStr">
         <is>
-          <t>Playing any card also ticks the Shot Clock</t>
+          <t>SHOT -10%. No dunks</t>
         </is>
       </c>
       <c r="E181" s="58" t="n"/>
@@ -7055,56 +7020,67 @@
       </c>
       <c r="G181" s="75" t="inlineStr">
         <is>
-          <t>The tick is paid after the card resolves, so a shot at 01 still goes up</t>
+          <t>Cards that dunk cannot be played</t>
         </is>
       </c>
       <c r="H181" s="76" t="n"/>
       <c r="I181" s="76" t="n"/>
       <c r="J181" s="76" t="n"/>
     </row>
-    <row r="182" ht="42" customHeight="1" s="85">
-      <c r="A182" s="52" t="inlineStr">
-        <is>
-          <t>Variaball</t>
-        </is>
-      </c>
-      <c r="B182" s="53">
-        <f>COUNTIF($B$183:$B$198,"Variaball")</f>
-        <v/>
-      </c>
-      <c r="C182" s="54" t="n"/>
-      <c r="D182" s="54" t="n"/>
-      <c r="E182" s="54" t="n"/>
-      <c r="F182" s="55" t="n"/>
-      <c r="G182" s="66" t="n"/>
-      <c r="H182" s="67" t="n"/>
-      <c r="I182" s="67" t="n"/>
-      <c r="J182" s="67" t="n"/>
+    <row r="182" s="85">
+      <c r="A182" s="27" t="n"/>
+      <c r="B182" s="28" t="inlineStr">
+        <is>
+          <t>Varena</t>
+        </is>
+      </c>
+      <c r="C182" s="56" t="inlineStr">
+        <is>
+          <t>Vintage Varnish</t>
+        </is>
+      </c>
+      <c r="D182" s="63" t="inlineStr">
+        <is>
+          <t>Shot Clock 14. No threes. No Variaballs. 1 Intangible per player</t>
+        </is>
+      </c>
+      <c r="E182" s="58" t="n"/>
+      <c r="F182" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G182" s="75" t="inlineStr">
+        <is>
+          <t>Discards the ball in play when it lands</t>
+        </is>
+      </c>
+      <c r="H182" s="76" t="n"/>
+      <c r="I182" s="76" t="n"/>
+      <c r="J182" s="76" t="n"/>
     </row>
     <row r="183" s="85">
       <c r="A183" s="27" t="n"/>
       <c r="B183" s="28" t="inlineStr">
         <is>
-          <t>Variaball</t>
+          <t>Varena</t>
         </is>
       </c>
       <c r="C183" s="56" t="inlineStr">
         <is>
-          <t>Med Ball</t>
+          <t>S.O.S — Sell-Out Stadium</t>
         </is>
       </c>
       <c r="D183" s="63" t="inlineStr">
         <is>
-          <t>SHOT cannot exceed 50%</t>
+          <t>A Three may be attempted as a two at 2X SHOT</t>
         </is>
       </c>
       <c r="E183" s="58" t="n"/>
       <c r="F183" s="61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G183" s="75" t="inlineStr">
         <is>
-          <t>An Intangible's or a Varena's SHOT = is not held to it</t>
+          <t>Keeps every other printed effect</t>
         </is>
       </c>
       <c r="H183" s="76" t="n"/>
@@ -7115,26 +7091,26 @@
       <c r="A184" s="27" t="n"/>
       <c r="B184" s="28" t="inlineStr">
         <is>
-          <t>Variaball</t>
+          <t>Varena</t>
         </is>
       </c>
       <c r="C184" s="56" t="inlineStr">
         <is>
-          <t>Dishcount Ball</t>
+          <t>Grayvstone</t>
         </is>
       </c>
       <c r="D184" s="63" t="inlineStr">
         <is>
-          <t>Discard one fewer for card costs and Clamps</t>
+          <t>Each possession, the ball becomes the last Variaball in the discards</t>
         </is>
       </c>
       <c r="E184" s="58" t="n"/>
       <c r="F184" s="61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G184" s="75" t="inlineStr">
         <is>
-          <t>Counts: Clamps, Pound Dribble, Frostbite Finish, Stepback, Turnaround Three</t>
+          <t>With none there, nothing happens</t>
         </is>
       </c>
       <c r="H184" s="76" t="n"/>
@@ -7145,28 +7121,24 @@
       <c r="A185" s="27" t="n"/>
       <c r="B185" s="28" t="inlineStr">
         <is>
-          <t>Variaball</t>
+          <t>Varena</t>
         </is>
       </c>
       <c r="C185" s="56" t="inlineStr">
         <is>
-          <t>Blight Ball</t>
+          <t>Con-crete</t>
         </is>
       </c>
       <c r="D185" s="63" t="inlineStr">
         <is>
-          <t>Injuries travel with the ball, and new ones join the pile. Discarding the ball takes the pile with it</t>
+          <t>Move cards: SHOT -10%</t>
         </is>
       </c>
       <c r="E185" s="58" t="n"/>
       <c r="F185" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="G185" s="75" t="inlineStr">
-        <is>
-          <t>Moves on any change of hands</t>
-        </is>
-      </c>
+      <c r="G185" s="75" t="n"/>
       <c r="H185" s="76" t="n"/>
       <c r="I185" s="76" t="n"/>
       <c r="J185" s="76" t="n"/>
@@ -7175,24 +7147,28 @@
       <c r="A186" s="27" t="n"/>
       <c r="B186" s="28" t="inlineStr">
         <is>
-          <t>Variaball</t>
+          <t>Varena</t>
         </is>
       </c>
       <c r="C186" s="56" t="inlineStr">
         <is>
-          <t>Bench Ball</t>
+          <t>Spazzphalt</t>
         </is>
       </c>
       <c r="D186" s="63" t="inlineStr">
         <is>
-          <t>Receiving it by Pass: no draw, no turn. You inbound</t>
+          <t>SHOT = ?</t>
         </is>
       </c>
       <c r="E186" s="58" t="n"/>
       <c r="F186" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G186" s="75" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G186" s="75" t="inlineStr">
+        <is>
+          <t>A random 0–100%, in steps of 5</t>
+        </is>
+      </c>
       <c r="H186" s="76" t="n"/>
       <c r="I186" s="76" t="n"/>
       <c r="J186" s="76" t="n"/>
@@ -7201,17 +7177,17 @@
       <c r="A187" s="27" t="n"/>
       <c r="B187" s="28" t="inlineStr">
         <is>
-          <t>Variaball</t>
+          <t>Varena</t>
         </is>
       </c>
       <c r="C187" s="56" t="inlineStr">
         <is>
-          <t>Dishtracting Ball</t>
+          <t>Frostbite Finish</t>
         </is>
       </c>
       <c r="D187" s="63" t="inlineStr">
         <is>
-          <t>Receiving it: discard 1, after the draw for turn</t>
+          <t>Playing a Move costs discarding 1 other card</t>
         </is>
       </c>
       <c r="E187" s="58" t="n"/>
@@ -7220,7 +7196,7 @@
       </c>
       <c r="G187" s="75" t="inlineStr">
         <is>
-          <t>Any change of hands</t>
+          <t>The owner picks the card. A Move that is your whole hand can't be played</t>
         </is>
       </c>
       <c r="H187" s="76" t="n"/>
@@ -7231,24 +7207,33 @@
       <c r="A188" s="27" t="n"/>
       <c r="B188" s="28" t="inlineStr">
         <is>
-          <t>Variaball</t>
+          <t>Varena</t>
         </is>
       </c>
       <c r="C188" s="56" t="inlineStr">
         <is>
-          <t>Hand Ball</t>
+          <t>The Future</t>
         </is>
       </c>
       <c r="D188" s="63" t="inlineStr">
         <is>
-          <t>A Pass swaps hands: yours goes with the ball, theirs comes back</t>
-        </is>
-      </c>
-      <c r="E188" s="58" t="n"/>
+          <t>SHOT +10% and Draw 1 card when playing a Move card.
+SHOT -10% while Passing.</t>
+        </is>
+      </c>
+      <c r="E188" s="58" t="inlineStr">
+        <is>
+          <t>You may Discard 1 card during a three attempt to make it worth four pts (at SHOT-10%)</t>
+        </is>
+      </c>
       <c r="F188" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="G188" s="75" t="n"/>
+      <c r="G188" s="75" t="inlineStr">
+        <is>
+          <t>New in the SHOT audit (2026-09-14). Special Moves count as Moves</t>
+        </is>
+      </c>
       <c r="H188" s="76" t="n"/>
       <c r="I188" s="76" t="n"/>
       <c r="J188" s="76" t="n"/>
@@ -7257,53 +7242,50 @@
       <c r="A189" s="27" t="n"/>
       <c r="B189" s="28" t="inlineStr">
         <is>
-          <t>Variaball</t>
+          <t>Varena</t>
         </is>
       </c>
       <c r="C189" s="56" t="inlineStr">
         <is>
-          <t>Foot Ball</t>
+          <t>Tick-Tock Tile</t>
         </is>
       </c>
       <c r="D189" s="63" t="inlineStr">
         <is>
-          <t>Moves and Passes are not spent. They lock until your possession ends</t>
+          <t>Playing any card also ticks the Shot Clock</t>
         </is>
       </c>
       <c r="E189" s="58" t="n"/>
       <c r="F189" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" s="75" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G189" s="75" t="inlineStr">
+        <is>
+          <t>The tick is paid after the card resolves, so a shot at 01 still goes up</t>
+        </is>
+      </c>
       <c r="H189" s="76" t="n"/>
       <c r="I189" s="76" t="n"/>
       <c r="J189" s="76" t="n"/>
     </row>
-    <row r="190" s="85">
-      <c r="A190" s="27" t="n"/>
-      <c r="B190" s="28" t="inlineStr">
+    <row r="190" ht="42" customHeight="1" s="85">
+      <c r="A190" s="52" t="inlineStr">
         <is>
           <t>Variaball</t>
         </is>
       </c>
-      <c r="C190" s="56" t="inlineStr">
-        <is>
-          <t>Recharge Rock</t>
-        </is>
-      </c>
-      <c r="D190" s="63" t="inlineStr">
-        <is>
-          <t>Double your draw for turn</t>
-        </is>
-      </c>
-      <c r="E190" s="58" t="n"/>
-      <c r="F190" s="61" t="n">
-        <v>5</v>
-      </c>
-      <c r="G190" s="75" t="n"/>
-      <c r="H190" s="76" t="n"/>
-      <c r="I190" s="76" t="n"/>
-      <c r="J190" s="76" t="n"/>
+      <c r="B190" s="53">
+        <f>COUNTIF($B$191:$B$208,"Variaball")</f>
+        <v/>
+      </c>
+      <c r="C190" s="54" t="n"/>
+      <c r="D190" s="54" t="n"/>
+      <c r="E190" s="54" t="n"/>
+      <c r="F190" s="55" t="n"/>
+      <c r="G190" s="66" t="n"/>
+      <c r="H190" s="67" t="n"/>
+      <c r="I190" s="67" t="n"/>
+      <c r="J190" s="67" t="n"/>
     </row>
     <row r="191" s="85">
       <c r="A191" s="27" t="n"/>
@@ -7314,21 +7296,21 @@
       </c>
       <c r="C191" s="56" t="inlineStr">
         <is>
-          <t>Variaball</t>
+          <t>Med Ball</t>
         </is>
       </c>
       <c r="D191" s="63" t="inlineStr">
         <is>
-          <t>A random Variaball from the discards goes into play. Then discard this</t>
+          <t>SHOT cannot exceed 50%</t>
         </is>
       </c>
       <c r="E191" s="58" t="n"/>
       <c r="F191" s="61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G191" s="75" t="inlineStr">
         <is>
-          <t>From the deck if the discards have none; never the ball already in play</t>
+          <t>An Intangible's or a Varena's SHOT = is not held to it</t>
         </is>
       </c>
       <c r="H191" s="76" t="n"/>
@@ -7344,19 +7326,23 @@
       </c>
       <c r="C192" s="56" t="inlineStr">
         <is>
-          <t>Shufflebag Ball</t>
+          <t>Dishcount Ball</t>
         </is>
       </c>
       <c r="D192" s="63" t="inlineStr">
         <is>
-          <t>Every possession, the turn player shuffles their hand into the deck and draws the same number, then draws for turn</t>
+          <t>Discard one fewer for card costs and Clamps</t>
         </is>
       </c>
       <c r="E192" s="58" t="n"/>
       <c r="F192" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G192" s="75" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G192" s="75" t="inlineStr">
+        <is>
+          <t>Counts: Clamps, Pound Dribble, Frostbite Finish, Stepback, Turnaround Three</t>
+        </is>
+      </c>
       <c r="H192" s="76" t="n"/>
       <c r="I192" s="76" t="n"/>
       <c r="J192" s="76" t="n"/>
@@ -7370,19 +7356,23 @@
       </c>
       <c r="C193" s="56" t="inlineStr">
         <is>
-          <t>Bag'n Ball</t>
+          <t>Blight Ball</t>
         </is>
       </c>
       <c r="D193" s="63" t="inlineStr">
         <is>
-          <t>Draw 1 card when played. SHOT = 10% for each card in your hand</t>
+          <t>Injuries travel with the ball, and new ones join the pile. Discarding the ball takes the pile with it</t>
         </is>
       </c>
       <c r="E193" s="58" t="n"/>
       <c r="F193" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G193" s="75" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G193" s="75" t="inlineStr">
+        <is>
+          <t>Moves on any change of hands</t>
+        </is>
+      </c>
       <c r="H193" s="76" t="n"/>
       <c r="I193" s="76" t="n"/>
       <c r="J193" s="76" t="n"/>
@@ -7396,23 +7386,19 @@
       </c>
       <c r="C194" s="56" t="inlineStr">
         <is>
-          <t>Blaze Ball</t>
+          <t>Bench Ball</t>
         </is>
       </c>
       <c r="D194" s="63" t="inlineStr">
         <is>
-          <t>SHOT +10% as this Ball is Passed</t>
+          <t>Receiving it by Pass: no draw, no turn. You inbound</t>
         </is>
       </c>
       <c r="E194" s="58" t="n"/>
       <c r="F194" s="61" t="n">
-        <v>5</v>
-      </c>
-      <c r="G194" s="75" t="inlineStr">
-        <is>
-          <t>Ignores every other pass modifier</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G194" s="75" t="n"/>
       <c r="H194" s="76" t="n"/>
       <c r="I194" s="76" t="n"/>
       <c r="J194" s="76" t="n"/>
@@ -7426,21 +7412,21 @@
       </c>
       <c r="C195" s="56" t="inlineStr">
         <is>
-          <t>Snow Ball It</t>
+          <t>Dishtracting Ball</t>
         </is>
       </c>
       <c r="D195" s="63" t="inlineStr">
         <is>
-          <t>SHOT -10% as this Ball is Passed</t>
+          <t>Receiving it: discard 1, after the draw for turn</t>
         </is>
       </c>
       <c r="E195" s="58" t="n"/>
       <c r="F195" s="61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G195" s="75" t="inlineStr">
         <is>
-          <t>Blaze Ball's opposite</t>
+          <t>Any change of hands</t>
         </is>
       </c>
       <c r="H195" s="76" t="n"/>
@@ -7456,17 +7442,17 @@
       </c>
       <c r="C196" s="56" t="inlineStr">
         <is>
-          <t>Brick Ball</t>
+          <t>Hand Ball</t>
         </is>
       </c>
       <c r="D196" s="63" t="inlineStr">
         <is>
-          <t>SHOT = 25%</t>
+          <t>A Pass swaps hands: yours goes with the ball, theirs comes back</t>
         </is>
       </c>
       <c r="E196" s="58" t="n"/>
       <c r="F196" s="61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G196" s="75" t="n"/>
       <c r="H196" s="76" t="n"/>
@@ -7482,23 +7468,19 @@
       </c>
       <c r="C197" s="56" t="inlineStr">
         <is>
-          <t>Monster Ball</t>
+          <t>Foot Ball</t>
         </is>
       </c>
       <c r="D197" s="63" t="inlineStr">
         <is>
-          <t>Intangibles are absorbed into the ball. When it's discarded, players rebound for them one at a time</t>
+          <t>Moves and Passes are not spent. They lock until your possession ends</t>
         </is>
       </c>
       <c r="E197" s="58" t="n"/>
       <c r="F197" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="G197" s="75" t="inlineStr">
-        <is>
-          <t>Swallows every Intangible already out and every one drawn while it's in play</t>
-        </is>
-      </c>
+      <c r="G197" s="75" t="n"/>
       <c r="H197" s="76" t="n"/>
       <c r="I197" s="76" t="n"/>
       <c r="J197" s="76" t="n"/>
@@ -7512,75 +7494,414 @@
       </c>
       <c r="C198" s="56" t="inlineStr">
         <is>
-          <t>Brand New Ball</t>
+          <t>Recharge Rock</t>
         </is>
       </c>
       <c r="D198" s="63" t="inlineStr">
         <is>
-          <t>25% chance a shot attempt is a turnover instead</t>
+          <t>Double your draw for turn</t>
         </is>
       </c>
       <c r="E198" s="58" t="n"/>
       <c r="F198" s="61" t="n">
-        <v>3</v>
-      </c>
-      <c r="G198" s="75" t="inlineStr">
-        <is>
-          <t>The round ends</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G198" s="75" t="n"/>
       <c r="H198" s="76" t="n"/>
       <c r="I198" s="76" t="n"/>
       <c r="J198" s="76" t="n"/>
     </row>
+    <row r="199" s="85">
+      <c r="A199" s="27" t="n"/>
+      <c r="B199" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C199" s="56" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="D199" s="63" t="inlineStr">
+        <is>
+          <t>A random Variaball from the discards goes into play. Then discard this</t>
+        </is>
+      </c>
+      <c r="E199" s="58" t="n"/>
+      <c r="F199" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" s="75" t="inlineStr">
+        <is>
+          <t>From the deck if the discards have none; never the ball already in play</t>
+        </is>
+      </c>
+      <c r="H199" s="76" t="n"/>
+      <c r="I199" s="76" t="n"/>
+      <c r="J199" s="76" t="n"/>
+    </row>
+    <row r="200" s="85">
+      <c r="A200" s="27" t="n"/>
+      <c r="B200" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C200" s="56" t="inlineStr">
+        <is>
+          <t>Shufflebag Ball</t>
+        </is>
+      </c>
+      <c r="D200" s="63" t="inlineStr">
+        <is>
+          <t>Every possession, the turn player shuffles their hand into the deck and draws the same number, then draws for turn</t>
+        </is>
+      </c>
+      <c r="E200" s="58" t="n"/>
+      <c r="F200" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="75" t="n"/>
+      <c r="H200" s="76" t="n"/>
+      <c r="I200" s="76" t="n"/>
+      <c r="J200" s="76" t="n"/>
+    </row>
+    <row r="201" s="85">
+      <c r="A201" s="27" t="n"/>
+      <c r="B201" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C201" s="56" t="inlineStr">
+        <is>
+          <t>Bag'n Ball</t>
+        </is>
+      </c>
+      <c r="D201" s="63" t="inlineStr">
+        <is>
+          <t>Draw 1 card when played. SHOT = 10% for each card in your hand</t>
+        </is>
+      </c>
+      <c r="E201" s="58" t="n"/>
+      <c r="F201" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="75" t="n"/>
+      <c r="H201" s="76" t="n"/>
+      <c r="I201" s="76" t="n"/>
+      <c r="J201" s="76" t="n"/>
+    </row>
+    <row r="202" s="85">
+      <c r="A202" s="27" t="n"/>
+      <c r="B202" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C202" s="56" t="inlineStr">
+        <is>
+          <t>Blaze Ball</t>
+        </is>
+      </c>
+      <c r="D202" s="63" t="inlineStr">
+        <is>
+          <t>SHOT +10% as this Ball is Passed</t>
+        </is>
+      </c>
+      <c r="E202" s="58" t="n"/>
+      <c r="F202" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G202" s="75" t="inlineStr">
+        <is>
+          <t>Ignores every other pass modifier</t>
+        </is>
+      </c>
+      <c r="H202" s="76" t="n"/>
+      <c r="I202" s="76" t="n"/>
+      <c r="J202" s="76" t="n"/>
+    </row>
+    <row r="203" s="85">
+      <c r="A203" s="27" t="n"/>
+      <c r="B203" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C203" s="56" t="inlineStr">
+        <is>
+          <t>Snow Ball</t>
+        </is>
+      </c>
+      <c r="D203" s="63" t="inlineStr">
+        <is>
+          <t>SHOT -10% as this Ball is Passed</t>
+        </is>
+      </c>
+      <c r="E203" s="58" t="n"/>
+      <c r="F203" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="G203" s="75" t="inlineStr">
+        <is>
+          <t>Blaze Ball's opposite</t>
+        </is>
+      </c>
+      <c r="H203" s="76" t="n"/>
+      <c r="I203" s="76" t="n"/>
+      <c r="J203" s="76" t="n"/>
+    </row>
+    <row r="204" s="85">
+      <c r="A204" s="27" t="n"/>
+      <c r="B204" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C204" s="56" t="inlineStr">
+        <is>
+          <t>Brick Ball</t>
+        </is>
+      </c>
+      <c r="D204" s="63" t="inlineStr">
+        <is>
+          <t>SHOT = 25%</t>
+        </is>
+      </c>
+      <c r="E204" s="58" t="n"/>
+      <c r="F204" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" s="75" t="n"/>
+      <c r="H204" s="76" t="n"/>
+      <c r="I204" s="76" t="n"/>
+      <c r="J204" s="76" t="n"/>
+    </row>
+    <row r="205" s="85">
+      <c r="A205" s="27" t="n"/>
+      <c r="B205" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C205" s="56" t="inlineStr">
+        <is>
+          <t>Monster Ball</t>
+        </is>
+      </c>
+      <c r="D205" s="63" t="inlineStr">
+        <is>
+          <t>Intangibles are absorbed into the ball. When it's discarded, players rebound for them one at a time</t>
+        </is>
+      </c>
+      <c r="E205" s="58" t="n"/>
+      <c r="F205" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="75" t="inlineStr">
+        <is>
+          <t>Swallows every Intangible already out and every one drawn while it's in play</t>
+        </is>
+      </c>
+      <c r="H205" s="76" t="n"/>
+      <c r="I205" s="76" t="n"/>
+      <c r="J205" s="76" t="n"/>
+    </row>
+    <row r="206" s="85">
+      <c r="A206" s="27" t="n"/>
+      <c r="B206" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C206" s="56" t="inlineStr">
+        <is>
+          <t>Brand New Ball</t>
+        </is>
+      </c>
+      <c r="D206" s="63" t="inlineStr">
+        <is>
+          <t>25% chance a shot attempt is a turnover instead</t>
+        </is>
+      </c>
+      <c r="E206" s="58" t="n"/>
+      <c r="F206" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G206" s="75" t="inlineStr">
+        <is>
+          <t>The round ends</t>
+        </is>
+      </c>
+      <c r="H206" s="76" t="n"/>
+      <c r="I206" s="76" t="n"/>
+      <c r="J206" s="76" t="n"/>
+    </row>
+    <row r="207" s="85">
+      <c r="A207" s="27" t="n"/>
+      <c r="B207" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C207" s="56" t="inlineStr">
+        <is>
+          <t>Make-or-Take Ball</t>
+        </is>
+      </c>
+      <c r="D207" s="63" t="inlineStr">
+        <is>
+          <t>Take 1 FT after missing a shot attempt.</t>
+        </is>
+      </c>
+      <c r="E207" s="58" t="n"/>
+      <c r="F207" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G207" s="75" t="n"/>
+      <c r="H207" s="76" t="n"/>
+      <c r="I207" s="76" t="n"/>
+      <c r="J207" s="76" t="n"/>
+    </row>
+    <row r="208" s="85">
+      <c r="A208" s="27" t="n"/>
+      <c r="B208" s="28" t="inlineStr">
+        <is>
+          <t>Variaball</t>
+        </is>
+      </c>
+      <c r="C208" s="56" t="inlineStr">
+        <is>
+          <t>Hero Ball</t>
+        </is>
+      </c>
+      <c r="D208" s="63" t="inlineStr">
+        <is>
+          <t>Cannot play Pass cards. Made shots grant no AST</t>
+        </is>
+      </c>
+      <c r="E208" s="58" t="n"/>
+      <c r="F208" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G208" s="75" t="n"/>
+      <c r="H208" s="76" t="n"/>
+      <c r="I208" s="76" t="n"/>
+      <c r="J208" s="76" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="176">
+  <mergeCells count="186">
     <mergeCell ref="G55:J55"/>
+    <mergeCell ref="G188:J188"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G182:J182"/>
-    <mergeCell ref="G188:J188"/>
+    <mergeCell ref="G200:J200"/>
     <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
     <mergeCell ref="G119:J119"/>
-    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G202:J202"/>
     <mergeCell ref="G46:J46"/>
-    <mergeCell ref="G159:J159"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
-    <mergeCell ref="G72:J72"/>
-    <mergeCell ref="G81:J81"/>
-    <mergeCell ref="G161:J161"/>
     <mergeCell ref="G71:J71"/>
-    <mergeCell ref="G136:J136"/>
-    <mergeCell ref="G194:J194"/>
-    <mergeCell ref="G181:J181"/>
     <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G160:J160"/>
     <mergeCell ref="G82:J82"/>
-    <mergeCell ref="G174:J174"/>
-    <mergeCell ref="G156:J156"/>
     <mergeCell ref="G57:J57"/>
     <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="G66:J66"/>
+    <mergeCell ref="G184:J184"/>
     <mergeCell ref="G137:J137"/>
-    <mergeCell ref="G184:J184"/>
-    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G171:J171"/>
     <mergeCell ref="G53:J53"/>
-    <mergeCell ref="G171:J171"/>
-    <mergeCell ref="G189:J189"/>
+    <mergeCell ref="G146:J146"/>
     <mergeCell ref="G121:J121"/>
-    <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
-    <mergeCell ref="G108:J108"/>
+    <mergeCell ref="G139:J139"/>
     <mergeCell ref="G58:J58"/>
     <mergeCell ref="G114:J114"/>
     <mergeCell ref="G123:J123"/>
-    <mergeCell ref="G163:J163"/>
     <mergeCell ref="G110:J110"/>
     <mergeCell ref="G168:J168"/>
+    <mergeCell ref="G143:J143"/>
+    <mergeCell ref="G75:J75"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G67:J67"/>
+    <mergeCell ref="G61:J61"/>
+    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G125:J125"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G112:J112"/>
+    <mergeCell ref="G62:J62"/>
+    <mergeCell ref="G127:J127"/>
+    <mergeCell ref="G65:J65"/>
+    <mergeCell ref="G201:J201"/>
+    <mergeCell ref="G129:J129"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G138:J138"/>
+    <mergeCell ref="G76:J76"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G203:J203"/>
+    <mergeCell ref="G60:J60"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G131:J131"/>
+    <mergeCell ref="G140:J140"/>
+    <mergeCell ref="G198:J198"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G169:J169"/>
+    <mergeCell ref="G126:J126"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G78:J78"/>
+    <mergeCell ref="G87:J87"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G142:J142"/>
+    <mergeCell ref="G80:J80"/>
+    <mergeCell ref="G89:J89"/>
+    <mergeCell ref="G64:J64"/>
+    <mergeCell ref="G79:J79"/>
+    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="G51:J51"/>
+    <mergeCell ref="G144:J144"/>
+    <mergeCell ref="G164:J164"/>
+    <mergeCell ref="G173:J173"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G170:J170"/>
+    <mergeCell ref="G141:J141"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G172:J172"/>
+    <mergeCell ref="G190:J190"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G83:J83"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G150:J150"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G72:J72"/>
+    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="G208:J208"/>
+    <mergeCell ref="G161:J161"/>
+    <mergeCell ref="G136:J136"/>
+    <mergeCell ref="G194:J194"/>
+    <mergeCell ref="G145:J145"/>
+    <mergeCell ref="G181:J181"/>
+    <mergeCell ref="G160:J160"/>
+    <mergeCell ref="G174:J174"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G189:J189"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G108:J108"/>
+    <mergeCell ref="G207:J207"/>
+    <mergeCell ref="G163:J163"/>
     <mergeCell ref="G113:J113"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="G91:J91"/>
@@ -7588,129 +7909,76 @@
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G183:J183"/>
     <mergeCell ref="G165:J165"/>
-    <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
+    <mergeCell ref="G84:J84"/>
     <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G84:J84"/>
     <mergeCell ref="G193:J193"/>
+    <mergeCell ref="G149:J149"/>
     <mergeCell ref="G102:J102"/>
-    <mergeCell ref="G158:J158"/>
     <mergeCell ref="G185:J185"/>
-    <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
-    <mergeCell ref="G21:J21"/>
     <mergeCell ref="G86:J86"/>
     <mergeCell ref="G178:J178"/>
-    <mergeCell ref="G67:J67"/>
-    <mergeCell ref="G61:J61"/>
-    <mergeCell ref="G70:J70"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="G23:J23"/>
     <mergeCell ref="G176:J176"/>
     <mergeCell ref="G97:J97"/>
-    <mergeCell ref="G125:J125"/>
     <mergeCell ref="G38:J38"/>
-    <mergeCell ref="G7:J7"/>
     <mergeCell ref="G191:J191"/>
-    <mergeCell ref="G112:J112"/>
-    <mergeCell ref="G45:J45"/>
-    <mergeCell ref="G62:J62"/>
     <mergeCell ref="G175:J175"/>
-    <mergeCell ref="G127:J127"/>
     <mergeCell ref="G162:J162"/>
     <mergeCell ref="G49:J49"/>
     <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G195:J195"/>
     <mergeCell ref="G177:J177"/>
-    <mergeCell ref="G195:J195"/>
     <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G204:J204"/>
     <mergeCell ref="G104:J104"/>
-    <mergeCell ref="G65:J65"/>
     <mergeCell ref="G88:J88"/>
     <mergeCell ref="G26:J26"/>
-    <mergeCell ref="G154:J154"/>
     <mergeCell ref="G197:J197"/>
     <mergeCell ref="G35:J35"/>
-    <mergeCell ref="G129:J129"/>
-    <mergeCell ref="G138:J138"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G76:J76"/>
-    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G206:J206"/>
     <mergeCell ref="G90:J90"/>
-    <mergeCell ref="G60:J60"/>
-    <mergeCell ref="G131:J131"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G198:J198"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G130:J130"/>
-    <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
-    <mergeCell ref="G180:J180"/>
-    <mergeCell ref="G169:J169"/>
     <mergeCell ref="G179:J179"/>
-    <mergeCell ref="G126:J126"/>
+    <mergeCell ref="G39:J39"/>
     <mergeCell ref="G132:J132"/>
-    <mergeCell ref="G39:J39"/>
     <mergeCell ref="G122:J122"/>
     <mergeCell ref="G166:J166"/>
     <mergeCell ref="G101:J101"/>
     <mergeCell ref="G116:J116"/>
+    <mergeCell ref="G199:J199"/>
     <mergeCell ref="G103:J103"/>
     <mergeCell ref="G37:J37"/>
     <mergeCell ref="G186:J186"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
-    <mergeCell ref="G87:J87"/>
-    <mergeCell ref="G152:J152"/>
     <mergeCell ref="G167:J167"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G142:J142"/>
-    <mergeCell ref="G80:J80"/>
-    <mergeCell ref="G89:J89"/>
-    <mergeCell ref="G64:J64"/>
-    <mergeCell ref="G79:J79"/>
     <mergeCell ref="G192:J192"/>
-    <mergeCell ref="G73:J73"/>
-    <mergeCell ref="G51:J51"/>
-    <mergeCell ref="G153:J153"/>
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="G63:J63"/>
+    <mergeCell ref="G41:J41"/>
     <mergeCell ref="G134:J134"/>
-    <mergeCell ref="G41:J41"/>
     <mergeCell ref="G50:J50"/>
     <mergeCell ref="G106:J106"/>
-    <mergeCell ref="G164:J164"/>
-    <mergeCell ref="G173:J173"/>
     <mergeCell ref="G56:J56"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
+    <mergeCell ref="G27:J27"/>
     <mergeCell ref="G120:J120"/>
-    <mergeCell ref="G155:J155"/>
-    <mergeCell ref="G27:J27"/>
     <mergeCell ref="G36:J36"/>
-    <mergeCell ref="G42:J42"/>
     <mergeCell ref="G107:J107"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G170:J170"/>
-    <mergeCell ref="G157:J157"/>
-    <mergeCell ref="G141:J141"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G172:J172"/>
-    <mergeCell ref="G28:J28"/>
     <mergeCell ref="G93:J93"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G190:J190"/>
+    <mergeCell ref="G187:J187"/>
     <mergeCell ref="G69:J69"/>
-    <mergeCell ref="G187:J187"/>
-    <mergeCell ref="G83:J83"/>
     <mergeCell ref="G196:J196"/>
+    <mergeCell ref="G205:J205"/>
     <mergeCell ref="G124:J124"/>
-    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G180:J180"/>
     <mergeCell ref="G133:J133"/>
-    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G45:J45"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D48" s="57" t="inlineStr">
         <is>
-          <t>SHOT = 100%. (Must be played as your first action and have no Clamps, Injuries, or active Whistles)</t>
+          <t>If all other players have had possession of the Ball this round: SHOT = 100%</t>
         </is>
       </c>
       <c r="E48" s="58" t="n"/>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E208" s="58" t="n"/>
       <c r="F208" s="61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G208" s="75" t="n"/>
       <c r="H208" s="76" t="n"/>
@@ -7794,21 +7794,33 @@
   </sheetData>
   <mergeCells count="186">
     <mergeCell ref="G55:J55"/>
+    <mergeCell ref="G200:J200"/>
     <mergeCell ref="G188:J188"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="G182:J182"/>
-    <mergeCell ref="G200:J200"/>
     <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
     <mergeCell ref="G119:J119"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="G150:J150"/>
     <mergeCell ref="G202:J202"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="G111:J111"/>
+    <mergeCell ref="G72:J72"/>
+    <mergeCell ref="G81:J81"/>
+    <mergeCell ref="G208:J208"/>
+    <mergeCell ref="G161:J161"/>
     <mergeCell ref="G71:J71"/>
+    <mergeCell ref="G136:J136"/>
+    <mergeCell ref="G194:J194"/>
+    <mergeCell ref="G145:J145"/>
+    <mergeCell ref="G181:J181"/>
     <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G160:J160"/>
     <mergeCell ref="G82:J82"/>
+    <mergeCell ref="G174:J174"/>
     <mergeCell ref="G57:J57"/>
     <mergeCell ref="G128:J128"/>
     <mergeCell ref="G10:J10"/>
@@ -7818,97 +7830,30 @@
     <mergeCell ref="G171:J171"/>
     <mergeCell ref="G53:J53"/>
     <mergeCell ref="G146:J146"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G189:J189"/>
     <mergeCell ref="G121:J121"/>
+    <mergeCell ref="G34:J34"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="G139:J139"/>
+    <mergeCell ref="G108:J108"/>
     <mergeCell ref="G58:J58"/>
     <mergeCell ref="G114:J114"/>
     <mergeCell ref="G123:J123"/>
+    <mergeCell ref="G207:J207"/>
+    <mergeCell ref="G163:J163"/>
     <mergeCell ref="G110:J110"/>
     <mergeCell ref="G168:J168"/>
-    <mergeCell ref="G143:J143"/>
-    <mergeCell ref="G75:J75"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G67:J67"/>
-    <mergeCell ref="G61:J61"/>
-    <mergeCell ref="G70:J70"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G125:J125"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G112:J112"/>
-    <mergeCell ref="G62:J62"/>
-    <mergeCell ref="G127:J127"/>
-    <mergeCell ref="G65:J65"/>
-    <mergeCell ref="G201:J201"/>
-    <mergeCell ref="G129:J129"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="G138:J138"/>
-    <mergeCell ref="G76:J76"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G203:J203"/>
-    <mergeCell ref="G60:J60"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G131:J131"/>
-    <mergeCell ref="G140:J140"/>
-    <mergeCell ref="G198:J198"/>
-    <mergeCell ref="G11:J11"/>
-    <mergeCell ref="G169:J169"/>
-    <mergeCell ref="G126:J126"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G78:J78"/>
-    <mergeCell ref="G87:J87"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G142:J142"/>
-    <mergeCell ref="G80:J80"/>
-    <mergeCell ref="G89:J89"/>
-    <mergeCell ref="G64:J64"/>
-    <mergeCell ref="G79:J79"/>
-    <mergeCell ref="G73:J73"/>
-    <mergeCell ref="G51:J51"/>
-    <mergeCell ref="G144:J144"/>
-    <mergeCell ref="G164:J164"/>
-    <mergeCell ref="G173:J173"/>
-    <mergeCell ref="G42:J42"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G170:J170"/>
-    <mergeCell ref="G141:J141"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="G172:J172"/>
-    <mergeCell ref="G190:J190"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G83:J83"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="G150:J150"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G72:J72"/>
-    <mergeCell ref="G81:J81"/>
-    <mergeCell ref="G208:J208"/>
-    <mergeCell ref="G161:J161"/>
-    <mergeCell ref="G136:J136"/>
-    <mergeCell ref="G194:J194"/>
-    <mergeCell ref="G145:J145"/>
-    <mergeCell ref="G181:J181"/>
-    <mergeCell ref="G160:J160"/>
-    <mergeCell ref="G174:J174"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G189:J189"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G108:J108"/>
-    <mergeCell ref="G207:J207"/>
-    <mergeCell ref="G163:J163"/>
     <mergeCell ref="G113:J113"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="G91:J91"/>
+    <mergeCell ref="G143:J143"/>
     <mergeCell ref="G85:J85"/>
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="G183:J183"/>
     <mergeCell ref="G165:J165"/>
+    <mergeCell ref="G75:J75"/>
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="G84:J84"/>
     <mergeCell ref="G22:J22"/>
@@ -7916,14 +7861,26 @@
     <mergeCell ref="G149:J149"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="G185:J185"/>
+    <mergeCell ref="G12:J12"/>
     <mergeCell ref="G77:J77"/>
+    <mergeCell ref="G21:J21"/>
     <mergeCell ref="G86:J86"/>
     <mergeCell ref="G178:J178"/>
+    <mergeCell ref="G67:J67"/>
+    <mergeCell ref="G61:J61"/>
+    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="G23:J23"/>
     <mergeCell ref="G176:J176"/>
     <mergeCell ref="G97:J97"/>
+    <mergeCell ref="G125:J125"/>
+    <mergeCell ref="G7:J7"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="G191:J191"/>
+    <mergeCell ref="G112:J112"/>
+    <mergeCell ref="G62:J62"/>
     <mergeCell ref="G175:J175"/>
+    <mergeCell ref="G127:J127"/>
     <mergeCell ref="G162:J162"/>
     <mergeCell ref="G49:J49"/>
     <mergeCell ref="G24:J24"/>
@@ -7932,17 +7889,33 @@
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="G204:J204"/>
     <mergeCell ref="G104:J104"/>
+    <mergeCell ref="G65:J65"/>
+    <mergeCell ref="G201:J201"/>
     <mergeCell ref="G88:J88"/>
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="G197:J197"/>
     <mergeCell ref="G35:J35"/>
     <mergeCell ref="G206:J206"/>
+    <mergeCell ref="G129:J129"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G138:J138"/>
+    <mergeCell ref="G76:J76"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G203:J203"/>
     <mergeCell ref="G90:J90"/>
+    <mergeCell ref="G60:J60"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G131:J131"/>
+    <mergeCell ref="G140:J140"/>
+    <mergeCell ref="G198:J198"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="G130:J130"/>
+    <mergeCell ref="G11:J11"/>
     <mergeCell ref="G117:J117"/>
+    <mergeCell ref="G169:J169"/>
     <mergeCell ref="G179:J179"/>
+    <mergeCell ref="G126:J126"/>
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="G132:J132"/>
     <mergeCell ref="G122:J122"/>
@@ -7953,30 +7926,57 @@
     <mergeCell ref="G103:J103"/>
     <mergeCell ref="G37:J37"/>
     <mergeCell ref="G186:J186"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G78:J78"/>
     <mergeCell ref="G118:J118"/>
+    <mergeCell ref="G87:J87"/>
     <mergeCell ref="G167:J167"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G142:J142"/>
+    <mergeCell ref="G80:J80"/>
+    <mergeCell ref="G89:J89"/>
+    <mergeCell ref="G64:J64"/>
+    <mergeCell ref="G79:J79"/>
     <mergeCell ref="G192:J192"/>
+    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="G51:J51"/>
+    <mergeCell ref="G144:J144"/>
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="G63:J63"/>
     <mergeCell ref="G41:J41"/>
     <mergeCell ref="G134:J134"/>
     <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G164:J164"/>
     <mergeCell ref="G106:J106"/>
+    <mergeCell ref="G173:J173"/>
     <mergeCell ref="G56:J56"/>
+    <mergeCell ref="G14:J14"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="G120:J120"/>
     <mergeCell ref="G36:J36"/>
+    <mergeCell ref="G42:J42"/>
     <mergeCell ref="G107:J107"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G170:J170"/>
+    <mergeCell ref="G141:J141"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G172:J172"/>
+    <mergeCell ref="G190:J190"/>
+    <mergeCell ref="G28:J28"/>
     <mergeCell ref="G93:J93"/>
+    <mergeCell ref="G6:J6"/>
     <mergeCell ref="G187:J187"/>
     <mergeCell ref="G69:J69"/>
+    <mergeCell ref="G83:J83"/>
     <mergeCell ref="G196:J196"/>
     <mergeCell ref="G205:J205"/>
     <mergeCell ref="G124:J124"/>
     <mergeCell ref="G180:J180"/>
+    <mergeCell ref="G5:J5"/>
     <mergeCell ref="G133:J133"/>
     <mergeCell ref="G45:J45"/>
   </mergeCells>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2206,7 +2206,6 @@
         <v/>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="20.75" customHeight="1" s="85">
       <c r="A4" s="81" t="inlineStr">
         <is>
@@ -4338,21 +4337,17 @@
       </c>
       <c r="C80" s="24" t="inlineStr">
         <is>
-          <t>Play-On</t>
+          <t>Extravagant Mechanics</t>
         </is>
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>Discard each Game Break drawn and draw again, until a card is not one</t>
+          <t>Intangible, Varena, Variaball or Special Move Played: Cancel card.</t>
         </is>
       </c>
       <c r="E80" s="26" t="n"/>
       <c r="F80" s="50" t="n"/>
-      <c r="G80" s="72" t="inlineStr">
-        <is>
-          <t>Raised where the Break lands, like Cleared to Play — nobody plays a Break</t>
-        </is>
-      </c>
+      <c r="G80" s="72" t="n"/>
       <c r="H80" s="71" t="n"/>
       <c r="I80" s="71" t="n"/>
       <c r="J80" s="71" t="n"/>
@@ -6661,7 +6656,7 @@
       </c>
       <c r="D169" s="63" t="inlineStr">
         <is>
-          <t>Everyone refills to a hand of 5 at the start of their possession</t>
+          <t>Everyone refills their hand at the start of their possession</t>
         </is>
       </c>
       <c r="E169" s="58" t="n"/>
@@ -6721,7 +6716,7 @@
       </c>
       <c r="D171" s="63" t="inlineStr">
         <is>
-          <t>The highest scorer refills to 5 at the start of their possession</t>
+          <t>The highest scorer refills their hand at the start of their possession</t>
         </is>
       </c>
       <c r="E171" s="58" t="n"/>
@@ -7779,7 +7774,7 @@
       </c>
       <c r="D208" s="63" t="inlineStr">
         <is>
-          <t>Cannot play Pass cards. Made shots grant no AST</t>
+          <t>Cannot play Pass cards. Made shots grant no AST. SHOT +25% while shooting. Draw 1 extra when this Ball is rebounded</t>
         </is>
       </c>
       <c r="E208" s="58" t="n"/>
@@ -7801,9 +7796,9 @@
     <mergeCell ref="G135:J135"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="G47:J47"/>
+    <mergeCell ref="G150:J150"/>
     <mergeCell ref="G119:J119"/>
     <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G150:J150"/>
     <mergeCell ref="G202:J202"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="G40:J40"/>

--- a/Project CardCourt_CardDB.xlsx
+++ b/Project CardCourt_CardDB.xlsx
@@ -2089,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J208"/>
+  <dimension ref="A1:J217"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="22.25" customHeight="1"/>
   <cols>
     <col width="15.5" customWidth="1" style="8" min="1" max="1"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Pass back to player who passed to you. Gains what that pass gained. If ball not received from a player, TOV +1</t>
+          <t>Pass back to last player. Gains what the pass to you gained</t>
         </is>
       </c>
       <c r="E6" s="26" t="n"/>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Pass Across. SHOT +10%</t>
+          <t>Pass Across.</t>
         </is>
       </c>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G10" s="72" t="n"/>
       <c r="H10" s="71" t="n"/>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Pass Left. SHOT +10%</t>
+          <t>Pass Left.</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G11" s="70" t="n"/>
       <c r="H11" s="71" t="n"/>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Pass Right. SHOT +10%</t>
+          <t>Pass Right.</t>
         </is>
       </c>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G12" s="72" t="n"/>
       <c r="H12" s="71" t="n"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>You may flip a coin while passing. If Heads, draw 1 card.</t>
+          <t>You may flip a coin while passing. If Heads, Draw 1 card.</t>
         </is>
       </c>
       <c r="F13" s="34" t="n">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t>Draw 1 card. SHOT -10%</t>
+          <t>Draw 2 cards. SHOT -10%</t>
         </is>
       </c>
       <c r="E22" s="26" t="n"/>
       <c r="F22" s="33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G22" s="72" t="n"/>
       <c r="H22" s="71" t="n"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
+          <t>Draw 1 card. SHOT +10%</t>
         </is>
       </c>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="32" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G23" s="70" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="D25" s="38" t="inlineStr">
         <is>
-          <t>Cancel Clamps. Take 1 FT for each. If no Clamps on you, TOV +1</t>
+          <t>Draw 1 card. Clear all Clamps. Take 1 FT for each. If no Clamps, TOV +1</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>SHOT +10%. Draw 1 card. Shot Clock -01.</t>
+          <t>SHOT +10%. Draw 2 cards. Shot Clock -01.</t>
         </is>
       </c>
       <c r="E26" s="25" t="n"/>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%. Clear all clamps on you. Draw 2 cards and Shot Clock -01 for each.</t>
+          <t>Draw 1 card. SHOT +10%. Clear all Clamps on you. Draw 2 extra cards and Shot Clock -01 for each.</t>
         </is>
       </c>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G27" s="70" t="n"/>
       <c r="H27" s="71" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>SHOT +10%. Draw 1 card.</t>
+          <t>SHOT +10%. Draw 2 cards.</t>
         </is>
       </c>
       <c r="E28" s="26" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D29" s="41" t="inlineStr">
         <is>
-          <t>SHOT +10%. Draw 2 cards then Discard 1. Shot Clock -01</t>
+          <t>SHOT +10%. Draw 3 cards then Discard 1. Shot Clock -01</t>
         </is>
       </c>
       <c r="E29" s="26" t="n"/>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="D30" s="41" t="inlineStr">
         <is>
-          <t>SHOT +10%. Clear all your Clamps</t>
+          <t>Draw 1 card. SHOT +10%. Clear all your Clamps</t>
         </is>
       </c>
       <c r="E30" s="26" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D31" s="41" t="inlineStr">
         <is>
-          <t>SHOT +10%. Clear all your Clamps</t>
+          <t>Draw 1 card. SHOT +10%. Clear all your Clamps</t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>SHOT +10%</t>
+          <t>Draw 1 card. SHOT +10%</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="F32" s="32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G32" s="70" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
       </c>
       <c r="D33" s="25" t="inlineStr">
         <is>
-          <t>Pick 1: Draw 3 cards / Pass (+0%) / SHOT +30%. (Cannot play other Move cards this possession.)</t>
+          <t>Draw 1 card, then pick 1: Draw 3 extra cards Pass (+0%) SHOT +30% (Cannot play other Move cards this possession.)</t>
         </is>
       </c>
       <c r="E33" s="25" t="n"/>
       <c r="F33" s="36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G33" s="72" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
-          <t>Offered as the ball reaches you: step aside and it carries on to the next player, Clamps and all</t>
+          <t>First action only: Step aside, dodging the ball and all Clamps. Draw 1 card.</t>
         </is>
       </c>
       <c r="E34" s="30" t="n"/>
@@ -3149,14 +3149,12 @@
       </c>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t>Flip a coin:
-• Heads: SHOT +25%
-• Tails: SHOT -25%</t>
+          <t>Flip a coin: Heads: SHOT +25% Tails: SHOT -25%</t>
         </is>
       </c>
       <c r="E36" s="25" t="n"/>
       <c r="F36" s="36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G36" s="72" t="inlineStr">
         <is>
@@ -3186,7 +3184,7 @@
       </c>
       <c r="E37" s="6" t="n"/>
       <c r="F37" s="32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G37" s="74" t="inlineStr">
         <is>
@@ -3216,7 +3214,7 @@
       </c>
       <c r="E38" s="25" t="n"/>
       <c r="F38" s="36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G38" s="72" t="n"/>
       <c r="H38" s="71" t="n"/>
@@ -3237,12 +3235,12 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>SHOT -10%. Draw 1 card</t>
+          <t>SHOT -10%. Draw 1</t>
         </is>
       </c>
       <c r="E39" s="6" t="n"/>
       <c r="F39" s="32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G39" s="70" t="n"/>
       <c r="H39" s="71" t="n"/>
@@ -3268,7 +3266,7 @@
       </c>
       <c r="E40" s="25" t="n"/>
       <c r="F40" s="36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G40" s="72" t="n"/>
       <c r="H40" s="71" t="n"/>
@@ -3294,7 +3292,7 @@
       </c>
       <c r="E41" s="6" t="n"/>
       <c r="F41" s="32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G41" s="70" t="n"/>
       <c r="H41" s="71" t="n"/>
@@ -3320,7 +3318,7 @@
       </c>
       <c r="E42" s="25" t="n"/>
       <c r="F42" s="36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="72" t="n"/>
       <c r="H42" s="71" t="n"/>
@@ -3350,7 +3348,7 @@
         </is>
       </c>
       <c r="F43" s="32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G43" s="70" t="n"/>
       <c r="H43" s="71" t="n"/>
@@ -3380,7 +3378,7 @@
         </is>
       </c>
       <c r="F44" s="36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G44" s="72" t="inlineStr">
         <is>
@@ -3414,7 +3412,7 @@
         </is>
       </c>
       <c r="F45" s="32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G45" s="70" t="n"/>
       <c r="H45" s="71" t="n"/>
@@ -3440,7 +3438,7 @@
       </c>
       <c r="E46" s="25" t="inlineStr">
         <is>
-          <t>If you have 3 or more cards in hand, you may discard them: SHOT = 100%</t>
+          <t>If you have 3 or more cards in hand, you may Discard them: SHOT = 100%</t>
         </is>
       </c>
       <c r="F46" s="36" t="n">
@@ -3469,14 +3467,12 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Flip 4 coins.
-• 3 or fewer Heads: SHOT +15% and Draw 1 card for each.
-• 4 Heads: TOV +1 (This is a Travel)</t>
+          <t>Flip 4 coins. 3 or fewer Heads: SHOT +15% and Draw 1 card for each. 4 Heads: TOV +1 (This is a Travel)</t>
         </is>
       </c>
       <c r="E47" s="7" t="n"/>
       <c r="F47" s="34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G47" s="70" t="n"/>
       <c r="H47" s="71" t="n"/>
@@ -3502,7 +3498,7 @@
       </c>
       <c r="E48" s="58" t="n"/>
       <c r="F48" s="59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G48" s="75" t="n"/>
       <c r="H48" s="76" t="n"/>
@@ -3531,7 +3527,7 @@
         </is>
       </c>
       <c r="F49" s="0" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
@@ -3578,13 +3574,12 @@
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>SHOT 50% or more: SHOT +25%
-SHOT less than 50%: SHOT -25%</t>
+          <t>SHOT 50% or more: SHOT +25% SHOT less than 50%: SHOT -25%</t>
         </is>
       </c>
       <c r="E51" s="0" t="n"/>
       <c r="F51" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
@@ -3610,7 +3605,7 @@
       </c>
       <c r="E52" s="0" t="n"/>
       <c r="F52" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G52" s="0" t="n"/>
     </row>
@@ -3647,12 +3642,12 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Next player SHOT -25% if they shoot</t>
+          <t>Target player: SHOT -25% Clear: SHOT 60% or more</t>
         </is>
       </c>
       <c r="E54" s="7" t="n"/>
       <c r="F54" s="34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G54" s="80" t="inlineStr">
         <is>
@@ -3677,12 +3672,12 @@
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>Next Player cannot play 2 random cards from hand.</t>
+          <t>Target player Lock2 Clear: 2 cards or fewer in hand</t>
         </is>
       </c>
       <c r="E55" s="26" t="n"/>
       <c r="F55" s="33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G55" s="77" t="inlineStr">
         <is>
@@ -3707,12 +3702,12 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Next player discards 2 cards at the start of their turn</t>
+          <t>Target player Discard2</t>
         </is>
       </c>
       <c r="E56" s="7" t="n"/>
       <c r="F56" s="34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G56" s="80" t="inlineStr">
         <is>
@@ -3737,12 +3732,12 @@
       </c>
       <c r="D57" s="41" t="inlineStr">
         <is>
-          <t>Next player can only play Pass cards during their turn</t>
+          <t>Target player can only Pass or Shoot Clear: Give up the ball</t>
         </is>
       </c>
       <c r="E57" s="26" t="n"/>
       <c r="F57" s="33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G57" s="77" t="inlineStr">
         <is>
@@ -3767,12 +3762,12 @@
       </c>
       <c r="D58" s="57" t="inlineStr">
         <is>
-          <t>Next player cannot play 3 random cards from hand.</t>
+          <t>Target player Lock3 Clear: 1 card or fewer in hand</t>
         </is>
       </c>
       <c r="E58" s="58" t="n"/>
       <c r="F58" s="59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G58" s="83" t="inlineStr">
         <is>
@@ -3797,12 +3792,12 @@
       </c>
       <c r="D59" s="57" t="inlineStr">
         <is>
-          <t>Player cannot attempt a three-pointer</t>
+          <t>Target player cannot attempt a Three Clear: Shot Clock 03 or less</t>
         </is>
       </c>
       <c r="E59" s="58" t="n"/>
       <c r="F59" s="59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" s="83" t="inlineStr">
         <is>
@@ -3827,7 +3822,7 @@
       </c>
       <c r="D60" s="57" t="inlineStr">
         <is>
-          <t>Cannot Shoot. If player has no playable Pass cards, TOV +1; Round ends</t>
+          <t>Target player cannot Shoot. With no playable Pass cards, TOV +1 and the round ends Clear: Give up the ball</t>
         </is>
       </c>
       <c r="E60" s="58" t="n"/>
@@ -3857,12 +3852,12 @@
       </c>
       <c r="D61" s="57" t="inlineStr">
         <is>
-          <t>SHOT - 10% each time a card is played</t>
+          <t>Target player: SHOT -10% each time a card is played Clear: 3 Move cards this possession</t>
         </is>
       </c>
       <c r="E61" s="58" t="n"/>
       <c r="F61" s="59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G61" s="83" t="n"/>
       <c r="H61" s="76" t="n"/>
@@ -3870,236 +3865,236 @@
       <c r="J61" s="76" t="n"/>
     </row>
     <row r="62" ht="30" customHeight="1" s="85">
-      <c r="A62" s="52" t="inlineStr">
+      <c r="B62" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C62" s="56" t="inlineStr">
+        <is>
+          <t>Crushing Center</t>
+        </is>
+      </c>
+      <c r="D62" s="57" t="inlineStr">
+        <is>
+          <t>Target player with 2 cards or fewer in hand: SHOT -30% Clear: 4 cards or more in hand</t>
+        </is>
+      </c>
+      <c r="E62" s="58" t="n"/>
+      <c r="F62" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" s="83" t="inlineStr">
+        <is>
+          <t>Pace defender: only bites at 2 cards or fewer. Beaten by drawing back up</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="56" customHeight="1" s="85">
+      <c r="B63" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C63" s="56" t="inlineStr">
+        <is>
+          <t>Pressing Point</t>
+        </is>
+      </c>
+      <c r="D63" s="57" t="inlineStr">
+        <is>
+          <t>Target player with 4 cards or more in hand: SHOT -30% Clear: 2 cards or fewer in hand</t>
+        </is>
+      </c>
+      <c r="E63" s="58" t="n"/>
+      <c r="F63" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G63" s="83" t="inlineStr">
+        <is>
+          <t>Pace defender: only bites at 4 cards or more. Beaten by spending down</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1" s="85">
+      <c r="B64" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C64" s="56" t="inlineStr">
+        <is>
+          <t>Lurking Wing</t>
+        </is>
+      </c>
+      <c r="D64" s="57" t="inlineStr">
+        <is>
+          <t>Target player at Shot Clock 05 or less: SHOT -25% Clear: Shot Clock 06 or more</t>
+        </is>
+      </c>
+      <c r="E64" s="58" t="n"/>
+      <c r="F64" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="G64" s="83" t="inlineStr">
+        <is>
+          <t>Only bites late on the Shot Clock. Beaten by Resetting it</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1" s="85">
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C65" s="56" t="inlineStr">
+        <is>
+          <t>Help-Side Forward</t>
+        </is>
+      </c>
+      <c r="D65" s="57" t="inlineStr">
+        <is>
+          <t>Target player: SHOT -15% Clear: 2 Move cards this possession</t>
+        </is>
+      </c>
+      <c r="E65" s="58" t="n"/>
+      <c r="F65" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="G65" s="83" t="inlineStr">
+        <is>
+          <t>Always bites. Beaten off the dribble</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1" s="85">
+      <c r="B66" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C66" s="56" t="inlineStr">
+        <is>
+          <t>Baseline Denial</t>
+        </is>
+      </c>
+      <c r="D66" s="57" t="inlineStr">
+        <is>
+          <t>Target player can only shoot a Layup Clear: 5 cards in hand</t>
+        </is>
+      </c>
+      <c r="E66" s="58" t="n"/>
+      <c r="F66" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="G66" s="83" t="inlineStr">
+        <is>
+          <t>Forcer: walks the player into a Layup, which Offensive Foul is watching</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1" s="85">
+      <c r="B67" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C67" s="56" t="inlineStr">
+        <is>
+          <t>Paint Packer</t>
+        </is>
+      </c>
+      <c r="D67" s="57" t="inlineStr">
+        <is>
+          <t>Target player can only shoot a Three Clear: 2 cards or fewer in hand</t>
+        </is>
+      </c>
+      <c r="E67" s="58" t="n"/>
+      <c r="F67" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" s="83" t="inlineStr">
+        <is>
+          <t>Forcer: walks the player into a Three, which Foot On The Line is watching</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1" s="85">
+      <c r="B68" s="28" t="inlineStr">
+        <is>
+          <t>Clamp</t>
+        </is>
+      </c>
+      <c r="C68" s="56" t="inlineStr">
+        <is>
+          <t>Rim Runner</t>
+        </is>
+      </c>
+      <c r="D68" s="57" t="inlineStr">
+        <is>
+          <t>Target player can only shoot a Dunk Clear: SHOT 40% or less</t>
+        </is>
+      </c>
+      <c r="E68" s="58" t="n"/>
+      <c r="F68" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" s="83" t="inlineStr">
+        <is>
+          <t>Forcer: walks the player into a Dunk, which Charge is watching</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="29" customHeight="1" s="85">
+      <c r="A69" s="52" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="B62" s="53">
+      <c r="B69" s="53">
         <f>COUNTIF($B$63:$B$158,"Whistle")</f>
         <v/>
       </c>
-      <c r="C62" s="54" t="n"/>
-      <c r="D62" s="54" t="n"/>
-      <c r="E62" s="54" t="n"/>
-      <c r="F62" s="55" t="n"/>
-      <c r="G62" s="66" t="n"/>
-      <c r="H62" s="67" t="n"/>
-      <c r="I62" s="67" t="n"/>
-      <c r="J62" s="67" t="n"/>
-    </row>
-    <row r="63" ht="56" customHeight="1" s="85">
-      <c r="A63" s="21" t="inlineStr">
+      <c r="C69" s="54" t="n"/>
+      <c r="D69" s="54" t="n"/>
+      <c r="E69" s="54" t="n"/>
+      <c r="F69" s="55" t="n"/>
+      <c r="G69" s="66" t="n"/>
+      <c r="H69" s="67" t="n"/>
+      <c r="I69" s="67" t="n"/>
+      <c r="J69" s="67" t="n"/>
+    </row>
+    <row r="70" ht="20" customHeight="1" s="85">
+      <c r="A70" s="21" t="inlineStr">
         <is>
           <t>All whistles are limited to 1</t>
         </is>
       </c>
-      <c r="B63" s="22" t="inlineStr">
+      <c r="B70" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C63" s="23" t="inlineStr">
+      <c r="C70" s="23" t="inlineStr">
         <is>
           <t>Back Court Violation</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Pass Card Played: Cancel that card. That player TOV +1. Move ball to player of choice</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="50" t="n"/>
-      <c r="G63" s="70" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Cancel Next Pass. TOV +1. Side-out.</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="70" t="inlineStr">
         <is>
           <t>The player who played this whistle chooses, excluding the player who played the pass but including themselves.</t>
         </is>
       </c>
-      <c r="H63" s="71" t="n"/>
-      <c r="I63" s="71" t="n"/>
-      <c r="J63" s="71" t="n"/>
-    </row>
-    <row r="64" ht="42" customHeight="1" s="85">
-      <c r="A64" s="21" t="n"/>
-      <c r="B64" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C64" s="37" t="inlineStr">
-        <is>
-          <t>Blocking Foul</t>
-        </is>
-      </c>
-      <c r="D64" s="40" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +1 FT</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="n"/>
-      <c r="F64" s="50" t="n"/>
-      <c r="G64" s="72" t="n"/>
-      <c r="H64" s="71" t="n"/>
-      <c r="I64" s="71" t="n"/>
-      <c r="J64" s="71" t="n"/>
-    </row>
-    <row r="65" ht="42" customHeight="1" s="85">
-      <c r="A65" s="21" t="n"/>
-      <c r="B65" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C65" s="23" t="inlineStr">
-        <is>
-          <t>Charge</t>
-        </is>
-      </c>
-      <c r="D65" s="39" t="inlineStr">
-        <is>
-          <t>Shot Attempt: Cancel. Shooter Inbounds</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="n"/>
-      <c r="F65" s="50" t="n"/>
-      <c r="G65" s="70" t="n"/>
-      <c r="H65" s="71" t="n"/>
-      <c r="I65" s="71" t="n"/>
-      <c r="J65" s="71" t="n"/>
-    </row>
-    <row r="66" ht="42" customHeight="1" s="85">
-      <c r="A66" s="21" t="n"/>
-      <c r="B66" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C66" s="24" t="inlineStr">
-        <is>
-          <t>Cleared to Play</t>
-        </is>
-      </c>
-      <c r="D66" s="25" t="inlineStr">
-        <is>
-          <t>Injury Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="n"/>
-      <c r="F66" s="50" t="n"/>
-      <c r="G66" s="72" t="n"/>
-      <c r="H66" s="71" t="n"/>
-      <c r="I66" s="71" t="n"/>
-      <c r="J66" s="71" t="n"/>
-    </row>
-    <row r="67" ht="28" customHeight="1" s="85">
-      <c r="A67" s="21" t="n"/>
-      <c r="B67" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C67" s="23" t="inlineStr">
-        <is>
-          <t>Coach’s Challenge</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Any Whistle Card Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>Pull a Timeout from the discards, if one is there, and take it</t>
-        </is>
-      </c>
-      <c r="F67" s="50" t="n"/>
-      <c r="G67" s="70" t="n"/>
-      <c r="H67" s="71" t="n"/>
-      <c r="I67" s="71" t="n"/>
-      <c r="J67" s="71" t="n"/>
-    </row>
-    <row r="68" ht="42" customHeight="1" s="85">
-      <c r="A68" s="21" t="n"/>
-      <c r="B68" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C68" s="37" t="inlineStr">
-        <is>
-          <t>Delay-of-Game Warning</t>
-        </is>
-      </c>
-      <c r="D68" s="41" t="inlineStr">
-        <is>
-          <t>Lower Shot Clock with a card: Cancel that card's effects</t>
-        </is>
-      </c>
-      <c r="E68" s="25" t="inlineStr">
-        <is>
-          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
-        </is>
-      </c>
-      <c r="F68" s="51" t="n"/>
-      <c r="G68" s="73" t="inlineStr">
-        <is>
-          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
-        </is>
-      </c>
-      <c r="H68" s="71" t="n"/>
-      <c r="I68" s="71" t="n"/>
-      <c r="J68" s="71" t="n"/>
-    </row>
-    <row r="69" ht="29" customHeight="1" s="85">
-      <c r="A69" s="21" t="n"/>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C69" s="23" t="inlineStr">
-        <is>
-          <t>Double Dribble</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Dribble Move Card Played (Dribble, Rhythm Dribble, etc.): Cancel card. Discard 1 card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="50" t="n"/>
-      <c r="G69" s="70" t="inlineStr">
-        <is>
-          <t>The dribbling player inbounds. The round is NOT incremented.</t>
-        </is>
-      </c>
-      <c r="H69" s="71" t="n"/>
-      <c r="I69" s="71" t="n"/>
-      <c r="J69" s="71" t="n"/>
-    </row>
-    <row r="70" ht="20" customHeight="1" s="85">
-      <c r="A70" s="21" t="n"/>
-      <c r="B70" s="22" t="inlineStr">
-        <is>
-          <t>Whistle</t>
-        </is>
-      </c>
-      <c r="C70" s="37" t="inlineStr">
-        <is>
-          <t>Flagrant Foul</t>
-        </is>
-      </c>
-      <c r="D70" s="41" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discard 1. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E70" s="26" t="n"/>
-      <c r="F70" s="50" t="n"/>
-      <c r="G70" s="72" t="n"/>
       <c r="H70" s="71" t="n"/>
       <c r="I70" s="71" t="n"/>
       <c r="J70" s="71" t="n"/>
@@ -4113,17 +4108,19 @@
       </c>
       <c r="C71" s="37" t="inlineStr">
         <is>
-          <t>Flagrant Foul II</t>
-        </is>
-      </c>
-      <c r="D71" s="38" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamper discards Bag. Clamped player +1 FT then gets ball</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="n"/>
-      <c r="F71" s="50" t="n"/>
-      <c r="G71" s="70" t="n"/>
+          <t>Blocking Foul</t>
+        </is>
+      </c>
+      <c r="D71" s="40" t="inlineStr">
+        <is>
+          <t>Next Clamp: no effect. Clamped player +1 FT</t>
+        </is>
+      </c>
+      <c r="E71" s="26" t="n"/>
+      <c r="F71" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="72" t="n"/>
       <c r="H71" s="71" t="n"/>
       <c r="I71" s="71" t="n"/>
       <c r="J71" s="71" t="n"/>
@@ -4135,19 +4132,21 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C72" s="24" t="inlineStr">
-        <is>
-          <t>Goaltending</t>
-        </is>
-      </c>
-      <c r="D72" s="25" t="inlineStr">
-        <is>
-          <t>Clamp Card Played: Cancel card. Clamped player +2 points. End round.</t>
-        </is>
-      </c>
-      <c r="E72" s="26" t="n"/>
-      <c r="F72" s="50" t="n"/>
-      <c r="G72" s="72" t="n"/>
+      <c r="C72" s="23" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="D72" s="39" t="inlineStr">
+        <is>
+          <t>Next Dunk: Cancel it. Shooter inbounds</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="70" t="n"/>
       <c r="H72" s="71" t="n"/>
       <c r="I72" s="71" t="n"/>
       <c r="J72" s="71" t="n"/>
@@ -4159,19 +4158,21 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C73" s="23" t="inlineStr">
-        <is>
-          <t>Inadvertent Whistle</t>
-        </is>
-      </c>
-      <c r="D73" s="38" t="inlineStr">
-        <is>
-          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="50" t="n"/>
-      <c r="G73" s="70" t="n"/>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>Cleared to Play</t>
+        </is>
+      </c>
+      <c r="D73" s="25" t="inlineStr">
+        <is>
+          <t>An Injury turns up: it never lands</t>
+        </is>
+      </c>
+      <c r="E73" s="26" t="n"/>
+      <c r="F73" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="72" t="n"/>
       <c r="H73" s="71" t="n"/>
       <c r="I73" s="71" t="n"/>
       <c r="J73" s="71" t="n"/>
@@ -4183,19 +4184,23 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C74" s="24" t="inlineStr">
-        <is>
-          <t>Official Review</t>
-        </is>
-      </c>
-      <c r="D74" s="41" t="inlineStr">
-        <is>
-          <t>Intangible Played: Discard all Intangibles from player.</t>
-        </is>
-      </c>
-      <c r="E74" s="26" t="n"/>
+      <c r="C74" s="23" t="inlineStr">
+        <is>
+          <t>Coach’s Challenge</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Any Whistle Card Played: Cancel card.</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Pull a Timeout from the discards, if one is there, and take it</t>
+        </is>
+      </c>
       <c r="F74" s="50" t="n"/>
-      <c r="G74" s="72" t="n"/>
+      <c r="G74" s="70" t="n"/>
       <c r="H74" s="71" t="n"/>
       <c r="I74" s="71" t="n"/>
       <c r="J74" s="71" t="n"/>
@@ -4207,21 +4212,27 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C75" s="23" t="inlineStr">
-        <is>
-          <t>Shot Clock Violation</t>
-        </is>
-      </c>
-      <c r="D75" s="38" t="inlineStr">
-        <is>
-          <t>Shot Clock is changed: TOV +1. Ball OOB</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="50" t="n"/>
-      <c r="G75" s="70" t="inlineStr">
-        <is>
-          <t>This inbound does NOT increment the round.</t>
+      <c r="C75" s="37" t="inlineStr">
+        <is>
+          <t>Delay-of-Game Warning</t>
+        </is>
+      </c>
+      <c r="D75" s="41" t="inlineStr">
+        <is>
+          <t>Cancel Next Shot-Clock card. 2nd call this round: Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E75" s="25" t="inlineStr">
+        <is>
+          <t>If 2nd time activated this round: Whistle player takes 1 FT in addition</t>
+        </is>
+      </c>
+      <c r="F75" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="73" t="inlineStr">
+        <is>
+          <t>The Shot Clock reduction still applies. Game Breaks do not count — those are game events, not cards the player activates.</t>
         </is>
       </c>
       <c r="H75" s="71" t="n"/>
@@ -4235,19 +4246,25 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C76" s="24" t="inlineStr">
-        <is>
-          <t>Technical Foul</t>
-        </is>
-      </c>
-      <c r="D76" s="41" t="inlineStr">
-        <is>
-          <t>Any Non-Whistle Card Played: Cancel card. Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E76" s="26" t="n"/>
-      <c r="F76" s="50" t="n"/>
-      <c r="G76" s="72" t="n"/>
+      <c r="C76" s="23" t="inlineStr">
+        <is>
+          <t>Double Dribble</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Cancel a Dribble. Discard 1. TOV +1</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="n"/>
+      <c r="F76" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="70" t="inlineStr">
+        <is>
+          <t>The dribbling player inbounds. The round is NOT incremented.</t>
+        </is>
+      </c>
       <c r="H76" s="71" t="n"/>
       <c r="I76" s="71" t="n"/>
       <c r="J76" s="71" t="n"/>
@@ -4259,19 +4276,21 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C77" s="23" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
-      <c r="D77" s="38" t="inlineStr">
-        <is>
-          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="50" t="n"/>
-      <c r="G77" s="70" t="n"/>
+      <c r="C77" s="37" t="inlineStr">
+        <is>
+          <t>Flagrant Foul</t>
+        </is>
+      </c>
+      <c r="D77" s="41" t="inlineStr">
+        <is>
+          <t>Next Clamp: no effect. Clamper Discards 1. Clamped player +1 FT and keeps the ball</t>
+        </is>
+      </c>
+      <c r="E77" s="26" t="n"/>
+      <c r="F77" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="72" t="n"/>
       <c r="H77" s="71" t="n"/>
       <c r="I77" s="71" t="n"/>
       <c r="J77" s="71" t="n"/>
@@ -4283,19 +4302,21 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C78" s="24" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D78" s="25" t="inlineStr">
-        <is>
-          <t>Move card played: Cancel card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E78" s="26" t="n"/>
-      <c r="F78" s="50" t="n"/>
-      <c r="G78" s="72" t="n"/>
+      <c r="C78" s="37" t="inlineStr">
+        <is>
+          <t>Flagrant Foul II</t>
+        </is>
+      </c>
+      <c r="D78" s="38" t="inlineStr">
+        <is>
+          <t>Next Clamp: no effect. Clamper Discards their bag. Clamped player +1 FT and keeps the ball</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="n"/>
+      <c r="F78" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="70" t="n"/>
       <c r="H78" s="71" t="n"/>
       <c r="I78" s="71" t="n"/>
       <c r="J78" s="71" t="n"/>
@@ -4309,21 +4330,19 @@
       </c>
       <c r="C79" s="24" t="inlineStr">
         <is>
-          <t>Clear Path Foul</t>
+          <t>Goaltending</t>
         </is>
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>On Shot, when Clamped by SHOT-reducing Clamps: Cancel those Clamps. Award the points the shot was worth. Take 1 FT</t>
+          <t>Next Clamp: Cancel it. Target player +2 PTS. End round</t>
         </is>
       </c>
       <c r="E79" s="26" t="n"/>
-      <c r="F79" s="50" t="n"/>
-      <c r="G79" s="72" t="inlineStr">
-        <is>
-          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
-        </is>
-      </c>
+      <c r="F79" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="72" t="n"/>
       <c r="H79" s="71" t="n"/>
       <c r="I79" s="71" t="n"/>
       <c r="J79" s="71" t="n"/>
@@ -4335,170 +4354,181 @@
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C80" s="24" t="inlineStr">
-        <is>
-          <t>Extravagant Mechanics</t>
-        </is>
-      </c>
-      <c r="D80" s="25" t="inlineStr">
-        <is>
-          <t>Intangible, Varena, Variaball or Special Move Played: Cancel card.</t>
-        </is>
-      </c>
-      <c r="E80" s="26" t="n"/>
+      <c r="C80" s="23" t="inlineStr">
+        <is>
+          <t>Inadvertent Whistle</t>
+        </is>
+      </c>
+      <c r="D80" s="38" t="inlineStr">
+        <is>
+          <t>Any other whistle triggers: Cancel that card. Turn player draws 1 card.</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n"/>
       <c r="F80" s="50" t="n"/>
-      <c r="G80" s="72" t="n"/>
+      <c r="G80" s="70" t="n"/>
       <c r="H80" s="71" t="n"/>
       <c r="I80" s="71" t="n"/>
       <c r="J80" s="71" t="n"/>
     </row>
     <row r="81" ht="42" customHeight="1" s="85">
-      <c r="A81" s="27" t="n"/>
-      <c r="B81" s="28" t="inlineStr">
+      <c r="A81" s="21" t="n"/>
+      <c r="B81" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C81" s="29" t="inlineStr">
-        <is>
-          <t>Crew Chief Review</t>
-        </is>
-      </c>
-      <c r="D81" s="30" t="inlineStr">
-        <is>
-          <t>Cancel a pass. The ball comes to you</t>
-        </is>
-      </c>
-      <c r="E81" s="60" t="n"/>
-      <c r="F81" s="61" t="n"/>
-      <c r="G81" s="78" t="n"/>
-      <c r="H81" s="76" t="n"/>
-      <c r="I81" s="76" t="n"/>
-      <c r="J81" s="76" t="n"/>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>Official Review</t>
+        </is>
+      </c>
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>Next Intangible: Discard all theirs</t>
+        </is>
+      </c>
+      <c r="E81" s="26" t="n"/>
+      <c r="F81" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="72" t="n"/>
+      <c r="H81" s="71" t="n"/>
+      <c r="I81" s="71" t="n"/>
+      <c r="J81" s="71" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1" s="85">
-      <c r="A82" s="27" t="n"/>
-      <c r="B82" s="28" t="inlineStr">
+      <c r="A82" s="21" t="n"/>
+      <c r="B82" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C82" s="29" t="inlineStr">
-        <is>
-          <t>Discontinued Dribble</t>
-        </is>
-      </c>
-      <c r="D82" s="30" t="inlineStr">
-        <is>
-          <t>Card Drawn: That player's possession ends immediately. They inbound</t>
-        </is>
-      </c>
-      <c r="E82" s="60" t="n"/>
-      <c r="F82" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="78" t="n"/>
-      <c r="H82" s="76" t="n"/>
-      <c r="I82" s="76" t="n"/>
-      <c r="J82" s="76" t="n"/>
+      <c r="C82" s="23" t="inlineStr">
+        <is>
+          <t>Shot Clock Violation</t>
+        </is>
+      </c>
+      <c r="D82" s="38" t="inlineStr">
+        <is>
+          <t>Shot Clock changes: TOV +1. Side-out.</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="n"/>
+      <c r="F82" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="70" t="inlineStr">
+        <is>
+          <t>This inbound does NOT increment the round.</t>
+        </is>
+      </c>
+      <c r="H82" s="71" t="n"/>
+      <c r="I82" s="71" t="n"/>
+      <c r="J82" s="71" t="n"/>
     </row>
     <row r="83" ht="28" customHeight="1" s="85">
-      <c r="A83" s="27" t="n"/>
-      <c r="B83" s="28" t="inlineStr">
+      <c r="A83" s="21" t="n"/>
+      <c r="B83" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C83" s="29" t="inlineStr">
-        <is>
-          <t>Tile Tampering</t>
-        </is>
-      </c>
-      <c r="D83" s="30" t="inlineStr">
-        <is>
-          <t>Varena Played: Cancel card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E83" s="60" t="n"/>
-      <c r="F83" s="61" t="n"/>
-      <c r="G83" s="78" t="inlineStr">
-        <is>
-          <t>The Varena's player inbounds (side-out)</t>
-        </is>
-      </c>
-      <c r="H83" s="76" t="n"/>
-      <c r="I83" s="76" t="n"/>
-      <c r="J83" s="76" t="n"/>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>Technical Foul</t>
+        </is>
+      </c>
+      <c r="D83" s="41" t="inlineStr">
+        <is>
+          <t>Next Non-Whistle: Cancel it. TOV +1</t>
+        </is>
+      </c>
+      <c r="E83" s="26" t="n"/>
+      <c r="F83" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="72" t="n"/>
+      <c r="H83" s="71" t="n"/>
+      <c r="I83" s="71" t="n"/>
+      <c r="J83" s="71" t="n"/>
     </row>
     <row r="84" ht="28" customHeight="1" s="85">
-      <c r="A84" s="27" t="n"/>
-      <c r="B84" s="28" t="inlineStr">
+      <c r="A84" s="21" t="n"/>
+      <c r="B84" s="22" t="inlineStr">
         <is>
           <t>Whistle</t>
         </is>
       </c>
-      <c r="C84" s="29" t="inlineStr">
-        <is>
-          <t>Over-Varing Evidence</t>
-        </is>
-      </c>
-      <c r="D84" s="30" t="inlineStr">
-        <is>
-          <t>Variaball Played: Cancel card. TOV +1</t>
-        </is>
-      </c>
-      <c r="E84" s="60" t="n"/>
-      <c r="F84" s="61" t="n"/>
-      <c r="G84" s="78" t="inlineStr">
-        <is>
-          <t>The Variaball's player inbounds (side-out)</t>
-        </is>
-      </c>
-      <c r="H84" s="76" t="n"/>
-      <c r="I84" s="76" t="n"/>
-      <c r="J84" s="76" t="n"/>
+      <c r="C84" s="23" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="D84" s="38" t="inlineStr">
+        <is>
+          <t>Immediate: Reset Shot Clock. You inbound. All players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="n"/>
+      <c r="F84" s="50" t="n"/>
+      <c r="G84" s="70" t="n"/>
+      <c r="H84" s="71" t="n"/>
+      <c r="I84" s="71" t="n"/>
+      <c r="J84" s="71" t="n"/>
     </row>
     <row r="85" ht="28" customHeight="1" s="85">
-      <c r="A85" s="52" t="inlineStr">
-        <is>
-          <t>Retired Game Breaks</t>
-        </is>
-      </c>
-      <c r="B85" s="53">
-        <f>COUNTIF($B$86:$B$115,"Retired Game Break")</f>
-        <v/>
-      </c>
-      <c r="C85" s="54" t="n"/>
-      <c r="D85" s="54" t="n"/>
-      <c r="E85" s="54" t="n"/>
-      <c r="F85" s="55" t="n"/>
-      <c r="G85" s="66" t="n"/>
-      <c r="H85" s="67" t="n"/>
-      <c r="I85" s="67" t="n"/>
-      <c r="J85" s="67" t="n"/>
+      <c r="A85" s="21" t="n"/>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D85" s="25" t="inlineStr">
+        <is>
+          <t>4th Move this possession: Cancel it. TOV +1. Side-out.</t>
+        </is>
+      </c>
+      <c r="E85" s="26" t="n"/>
+      <c r="F85" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="72" t="n"/>
+      <c r="H85" s="71" t="n"/>
+      <c r="I85" s="71" t="n"/>
+      <c r="J85" s="71" t="n"/>
     </row>
     <row r="86" ht="20" customHeight="1" s="85">
       <c r="A86" s="21" t="n"/>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>Retired Game Break</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="C86" s="24" t="inlineStr">
         <is>
-          <t>2-Minute Warning</t>
+          <t>Clear Path Foul</t>
         </is>
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>All players discard down to 2 or fewer cards</t>
+          <t>Shooting under a SHOT Clamp: Clear them, take the points and 1 FT</t>
         </is>
       </c>
       <c r="E86" s="26" t="n"/>
-      <c r="F86" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="72" t="n"/>
+      <c r="F86" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="72" t="inlineStr">
+        <is>
+          <t>Fires as the shot starts, before the cutscene. This DOES count as a completed round.</t>
+        </is>
+      </c>
       <c r="H86" s="71" t="n"/>
       <c r="I86" s="71" t="n"/>
       <c r="J86" s="71" t="n"/>
@@ -4507,221 +4537,206 @@
       <c r="A87" s="21" t="n"/>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C87" s="23" t="inlineStr">
-        <is>
-          <t>Benched</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>Immediately give ball to any other player.</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="n"/>
-      <c r="F87" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="74" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>Extravagant Mechanics</t>
+        </is>
+      </c>
+      <c r="D87" s="25" t="inlineStr">
+        <is>
+          <t>On Intangible, Variaball or Special Move play: Cancel it</t>
+        </is>
+      </c>
+      <c r="E87" s="26" t="n"/>
+      <c r="F87" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="72" t="n"/>
       <c r="H87" s="71" t="n"/>
       <c r="I87" s="71" t="n"/>
       <c r="J87" s="71" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1" s="85">
-      <c r="A88" s="21" t="n"/>
-      <c r="B88" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C88" s="24" t="inlineStr">
-        <is>
-          <t>Crowd Noise</t>
-        </is>
-      </c>
-      <c r="D88" s="25" t="inlineStr">
-        <is>
-          <t>Discard 1 card.</t>
-        </is>
-      </c>
-      <c r="E88" s="26" t="n"/>
-      <c r="F88" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="72" t="n"/>
-      <c r="H88" s="71" t="n"/>
-      <c r="I88" s="71" t="n"/>
-      <c r="J88" s="71" t="n"/>
+      <c r="A88" s="27" t="n"/>
+      <c r="B88" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C88" s="29" t="inlineStr">
+        <is>
+          <t>Crew Chief Review</t>
+        </is>
+      </c>
+      <c r="D88" s="30" t="inlineStr">
+        <is>
+          <t>Cancel a pass. The ball comes to you</t>
+        </is>
+      </c>
+      <c r="E88" s="60" t="n"/>
+      <c r="F88" s="61" t="n"/>
+      <c r="G88" s="78" t="n"/>
+      <c r="H88" s="76" t="n"/>
+      <c r="I88" s="76" t="n"/>
+      <c r="J88" s="76" t="n"/>
     </row>
     <row r="89" ht="42" customHeight="1" s="85">
-      <c r="A89" s="21" t="n"/>
-      <c r="B89" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C89" s="23" t="inlineStr">
-        <is>
-          <t>Designed Play</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>Draw up to a hand of 5</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="70" t="n"/>
-      <c r="H89" s="71" t="n"/>
-      <c r="I89" s="71" t="n"/>
-      <c r="J89" s="71" t="n"/>
+      <c r="A89" s="27" t="n"/>
+      <c r="B89" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C89" s="29" t="inlineStr">
+        <is>
+          <t>Discontinued Dribble</t>
+        </is>
+      </c>
+      <c r="D89" s="30" t="inlineStr">
+        <is>
+          <t>Player Draws a card: Possession ends. Side-out.</t>
+        </is>
+      </c>
+      <c r="E89" s="60" t="n"/>
+      <c r="F89" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="78" t="n"/>
+      <c r="H89" s="76" t="n"/>
+      <c r="I89" s="76" t="n"/>
+      <c r="J89" s="76" t="n"/>
     </row>
     <row r="90" ht="28" customHeight="1" s="85">
-      <c r="A90" s="21" t="n"/>
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C90" s="37" t="inlineStr">
-        <is>
-          <t>Foul</t>
-        </is>
-      </c>
-      <c r="D90" s="25" t="inlineStr">
-        <is>
-          <t>Take 1 FT</t>
-        </is>
-      </c>
-      <c r="E90" s="26" t="n"/>
-      <c r="F90" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="72" t="n"/>
-      <c r="H90" s="71" t="n"/>
-      <c r="I90" s="71" t="n"/>
-      <c r="J90" s="71" t="n"/>
+      <c r="A90" s="27" t="n"/>
+      <c r="B90" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C90" s="29" t="inlineStr">
+        <is>
+          <t>Tile Tampering</t>
+        </is>
+      </c>
+      <c r="D90" s="30" t="inlineStr">
+        <is>
+          <t>Varena Played: Cancel card. TOV +1</t>
+        </is>
+      </c>
+      <c r="E90" s="60" t="n"/>
+      <c r="F90" s="61" t="n"/>
+      <c r="G90" s="78" t="inlineStr">
+        <is>
+          <t>The Varena's player inbounds (side-out)</t>
+        </is>
+      </c>
+      <c r="H90" s="76" t="n"/>
+      <c r="I90" s="76" t="n"/>
+      <c r="J90" s="76" t="n"/>
     </row>
     <row r="91" ht="56" customHeight="1" s="85">
-      <c r="A91" s="21" t="n"/>
-      <c r="B91" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C91" s="23" t="inlineStr">
-        <is>
-          <t>MVP Vote</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards up to a hand of 7</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="70" t="n"/>
-      <c r="H91" s="71" t="n"/>
-      <c r="I91" s="71" t="n"/>
-      <c r="J91" s="71" t="n"/>
+      <c r="A91" s="27" t="n"/>
+      <c r="B91" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C91" s="29" t="inlineStr">
+        <is>
+          <t>Over-Varing Evidence</t>
+        </is>
+      </c>
+      <c r="D91" s="30" t="inlineStr">
+        <is>
+          <t>Variaball played: cancel it. TOV +1</t>
+        </is>
+      </c>
+      <c r="E91" s="60" t="n"/>
+      <c r="F91" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="78" t="inlineStr">
+        <is>
+          <t>The Variaball's player inbounds (side-out)</t>
+        </is>
+      </c>
+      <c r="H91" s="76" t="n"/>
+      <c r="I91" s="76" t="n"/>
+      <c r="J91" s="76" t="n"/>
     </row>
     <row r="92" ht="42" customHeight="1" s="85">
-      <c r="A92" s="21" t="n"/>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C92" s="24" t="inlineStr">
-        <is>
-          <t>Off Night</t>
-        </is>
-      </c>
-      <c r="D92" s="25" t="inlineStr">
-        <is>
-          <t>SHOT -20% this possession</t>
-        </is>
-      </c>
-      <c r="E92" s="26" t="n"/>
-      <c r="F92" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="72" t="n"/>
-      <c r="H92" s="71" t="n"/>
-      <c r="I92" s="71" t="n"/>
-      <c r="J92" s="71" t="n"/>
+      <c r="B92" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C92" s="29" t="inlineStr">
+        <is>
+          <t>Foot On The Line</t>
+        </is>
+      </c>
+      <c r="D92" s="30" t="inlineStr">
+        <is>
+          <t>Next Three scores 2 PTS instead</t>
+        </is>
+      </c>
+      <c r="E92" s="60" t="n"/>
+      <c r="F92" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="78" t="inlineStr">
+        <is>
+          <t>Crew: watches the Three. Downgrades rather than cancelling</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="42" customHeight="1" s="85">
-      <c r="A93" s="21" t="n"/>
-      <c r="B93" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C93" s="23" t="inlineStr">
-        <is>
-          <t>Swallowed Whistle</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>Whistle cards cannot activate this turn.</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F93" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="70" t="n"/>
-      <c r="H93" s="71" t="n"/>
-      <c r="I93" s="71" t="n"/>
-      <c r="J93" s="71" t="n"/>
+      <c r="B93" s="28" t="inlineStr">
+        <is>
+          <t>Whistle</t>
+        </is>
+      </c>
+      <c r="C93" s="29" t="inlineStr">
+        <is>
+          <t>Offensive Foul</t>
+        </is>
+      </c>
+      <c r="D93" s="30" t="inlineStr">
+        <is>
+          <t>Next Layup: Cancel it. TOV +1</t>
+        </is>
+      </c>
+      <c r="E93" s="60" t="n"/>
+      <c r="F93" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="78" t="inlineStr">
+        <is>
+          <t>Crew: watches the Layup</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="28" customHeight="1" s="85">
-      <c r="A94" s="21" t="n"/>
-      <c r="B94" s="22" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C94" s="24" t="inlineStr">
-        <is>
-          <t>Rock Fight</t>
-        </is>
-      </c>
-      <c r="D94" s="25" t="inlineStr">
-        <is>
-          <t>Players cannot shoot when SHOT is above 50%</t>
-        </is>
-      </c>
-      <c r="E94" s="25" t="inlineStr">
-        <is>
-          <t>Remains for remainder of round</t>
-        </is>
-      </c>
-      <c r="F94" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="72" t="n"/>
-      <c r="H94" s="71" t="n"/>
-      <c r="I94" s="71" t="n"/>
-      <c r="J94" s="71" t="n"/>
+      <c r="A94" s="52" t="inlineStr">
+        <is>
+          <t>Retired Game Breaks</t>
+        </is>
+      </c>
+      <c r="B94" s="53">
+        <f>COUNTIF($B$86:$B$115,"Retired Game Break")</f>
+        <v/>
+      </c>
+      <c r="C94" s="54" t="n"/>
+      <c r="D94" s="54" t="n"/>
+      <c r="E94" s="54" t="n"/>
+      <c r="F94" s="55" t="n"/>
+      <c r="G94" s="66" t="n"/>
+      <c r="H94" s="67" t="n"/>
+      <c r="I94" s="67" t="n"/>
+      <c r="J94" s="67" t="n"/>
     </row>
     <row r="95" ht="28" customHeight="1" s="85">
       <c r="A95" s="21" t="n"/>
@@ -4730,21 +4745,21 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C95" s="23" t="inlineStr">
-        <is>
-          <t>Traded Mid-Game</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>Swap hands with a random other player</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="n"/>
-      <c r="F95" s="34" t="n">
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>2-Minute Warning</t>
+        </is>
+      </c>
+      <c r="D95" s="25" t="inlineStr">
+        <is>
+          <t>All players discard down to 2 or fewer cards</t>
+        </is>
+      </c>
+      <c r="E95" s="26" t="n"/>
+      <c r="F95" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G95" s="74" t="n"/>
+      <c r="G95" s="72" t="n"/>
       <c r="H95" s="71" t="n"/>
       <c r="I95" s="71" t="n"/>
       <c r="J95" s="71" t="n"/>
@@ -4756,21 +4771,25 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C96" s="49" t="inlineStr">
-        <is>
-          <t>Salary Cap Increase</t>
-        </is>
-      </c>
-      <c r="D96" s="38" t="inlineStr">
-        <is>
-          <t>All players draw 2 cards</t>
+      <c r="C96" s="23" t="inlineStr">
+        <is>
+          <t>Benched</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Immediately give ball to any other player.</t>
         </is>
       </c>
       <c r="E96" s="7" t="n"/>
       <c r="F96" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="74" t="n"/>
+      <c r="G96" s="74" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H96" s="71" t="n"/>
       <c r="I96" s="71" t="n"/>
       <c r="J96" s="71" t="n"/>
@@ -4782,25 +4801,21 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C97" s="49" t="inlineStr">
-        <is>
-          <t>All-Swissh Selection</t>
-        </is>
-      </c>
-      <c r="D97" s="38" t="inlineStr">
-        <is>
-          <t>Draw 3 cards after your next make</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="n"/>
-      <c r="F97" s="34" t="n">
+      <c r="C97" s="24" t="inlineStr">
+        <is>
+          <t>Crowd Noise</t>
+        </is>
+      </c>
+      <c r="D97" s="25" t="inlineStr">
+        <is>
+          <t>Discard 1 card.</t>
+        </is>
+      </c>
+      <c r="E97" s="26" t="n"/>
+      <c r="F97" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G97" s="74" t="inlineStr">
-        <is>
-          <t>Arms an icon in the HUD tracking the pending draws</t>
-        </is>
-      </c>
+      <c r="G97" s="72" t="n"/>
       <c r="H97" s="71" t="n"/>
       <c r="I97" s="71" t="n"/>
       <c r="J97" s="71" t="n"/>
@@ -4812,21 +4827,21 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C98" s="49" t="inlineStr">
-        <is>
-          <t>All Star Selection</t>
-        </is>
-      </c>
-      <c r="D98" s="38" t="inlineStr">
-        <is>
-          <t>Draw 2 cards</t>
+      <c r="C98" s="23" t="inlineStr">
+        <is>
+          <t>Designed Play</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Draw up to a hand of 5</t>
         </is>
       </c>
       <c r="E98" s="7" t="n"/>
       <c r="F98" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G98" s="74" t="n"/>
+      <c r="G98" s="70" t="n"/>
       <c r="H98" s="71" t="n"/>
       <c r="I98" s="71" t="n"/>
       <c r="J98" s="71" t="n"/>
@@ -4838,25 +4853,21 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C99" s="49" t="inlineStr">
-        <is>
-          <t>Hit the Bike</t>
-        </is>
-      </c>
-      <c r="D99" s="38" t="inlineStr">
-        <is>
-          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="n"/>
-      <c r="F99" s="34" t="n">
+      <c r="C99" s="37" t="inlineStr">
+        <is>
+          <t>Foul</t>
+        </is>
+      </c>
+      <c r="D99" s="25" t="inlineStr">
+        <is>
+          <t>Take 1 FT</t>
+        </is>
+      </c>
+      <c r="E99" s="26" t="n"/>
+      <c r="F99" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G99" s="74" t="inlineStr">
-        <is>
-          <t>This is not a pass</t>
-        </is>
-      </c>
+      <c r="G99" s="72" t="n"/>
       <c r="H99" s="71" t="n"/>
       <c r="I99" s="71" t="n"/>
       <c r="J99" s="71" t="n"/>
@@ -4868,21 +4879,21 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C100" s="49" t="inlineStr">
-        <is>
-          <t>Ice Wrap</t>
-        </is>
-      </c>
-      <c r="D100" s="38" t="inlineStr">
-        <is>
-          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
+      <c r="C100" s="23" t="inlineStr">
+        <is>
+          <t>MVP Vote</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Draw 3 cards up to a hand of 7</t>
         </is>
       </c>
       <c r="E100" s="7" t="n"/>
       <c r="F100" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="74" t="n"/>
+      <c r="G100" s="70" t="n"/>
       <c r="H100" s="71" t="n"/>
       <c r="I100" s="71" t="n"/>
       <c r="J100" s="71" t="n"/>
@@ -4894,25 +4905,21 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C101" s="49" t="inlineStr">
-        <is>
-          <t>Wet Spot</t>
-        </is>
-      </c>
-      <c r="D101" s="38" t="inlineStr">
-        <is>
-          <t>All Injuries in the discards and deck are displayed. Take one</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="n"/>
-      <c r="F101" s="34" t="n">
+      <c r="C101" s="24" t="inlineStr">
+        <is>
+          <t>Off Night</t>
+        </is>
+      </c>
+      <c r="D101" s="25" t="inlineStr">
+        <is>
+          <t>SHOT -20% this possession</t>
+        </is>
+      </c>
+      <c r="E101" s="26" t="n"/>
+      <c r="F101" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G101" s="74" t="inlineStr">
-        <is>
-          <t>Deck ones are shown face down</t>
-        </is>
-      </c>
+      <c r="G101" s="72" t="n"/>
       <c r="H101" s="71" t="n"/>
       <c r="I101" s="71" t="n"/>
       <c r="J101" s="71" t="n"/>
@@ -4924,25 +4931,25 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C102" s="49" t="inlineStr">
-        <is>
-          <t>Fresh Ball</t>
-        </is>
-      </c>
-      <c r="D102" s="38" t="inlineStr">
-        <is>
-          <t>Next player does not draw at the start of their possession</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="n"/>
-      <c r="F102" s="34" t="n">
+      <c r="C102" s="23" t="inlineStr">
+        <is>
+          <t>Swallowed Whistle</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Whistle cards cannot activate this turn.</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F102" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="74" t="inlineStr">
-        <is>
-          <t>This is a bad thing in the NBA</t>
-        </is>
-      </c>
+      <c r="G102" s="70" t="n"/>
       <c r="H102" s="71" t="n"/>
       <c r="I102" s="71" t="n"/>
       <c r="J102" s="71" t="n"/>
@@ -4954,25 +4961,25 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C103" s="49" t="inlineStr">
-        <is>
-          <t>Trade Deadline</t>
-        </is>
-      </c>
-      <c r="D103" s="38" t="inlineStr">
-        <is>
-          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="34" t="n">
+      <c r="C103" s="24" t="inlineStr">
+        <is>
+          <t>Rock Fight</t>
+        </is>
+      </c>
+      <c r="D103" s="25" t="inlineStr">
+        <is>
+          <t>Players cannot shoot when SHOT is above 50%</t>
+        </is>
+      </c>
+      <c r="E103" s="25" t="inlineStr">
+        <is>
+          <t>Remains for remainder of round</t>
+        </is>
+      </c>
+      <c r="F103" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="74" t="inlineStr">
-        <is>
-          <t>The hex travels in the declared direction too</t>
-        </is>
-      </c>
+      <c r="G103" s="72" t="n"/>
       <c r="H103" s="71" t="n"/>
       <c r="I103" s="71" t="n"/>
       <c r="J103" s="71" t="n"/>
@@ -4984,14 +4991,14 @@
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C104" s="49" t="inlineStr">
-        <is>
-          <t>Floor Cleanup</t>
-        </is>
-      </c>
-      <c r="D104" s="38" t="inlineStr">
-        <is>
-          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
+      <c r="C104" s="23" t="inlineStr">
+        <is>
+          <t>Traded Mid-Game</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Swap hands with a random other player</t>
         </is>
       </c>
       <c r="E104" s="7" t="n"/>
@@ -5012,12 +5019,12 @@
       </c>
       <c r="C105" s="49" t="inlineStr">
         <is>
-          <t>Official Timeout</t>
+          <t>Salary Cap Increase</t>
         </is>
       </c>
       <c r="D105" s="38" t="inlineStr">
         <is>
-          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+          <t>All players draw 2 cards</t>
         </is>
       </c>
       <c r="E105" s="7" t="n"/>
@@ -5038,19 +5045,23 @@
       </c>
       <c r="C106" s="49" t="inlineStr">
         <is>
-          <t>Team Doctor</t>
+          <t>All-Swissh Selection</t>
         </is>
       </c>
       <c r="D106" s="38" t="inlineStr">
         <is>
-          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+          <t>Draw 3 cards after your next make</t>
         </is>
       </c>
       <c r="E106" s="7" t="n"/>
       <c r="F106" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G106" s="74" t="n"/>
+      <c r="G106" s="74" t="inlineStr">
+        <is>
+          <t>Arms an icon in the HUD tracking the pending draws</t>
+        </is>
+      </c>
       <c r="H106" s="71" t="n"/>
       <c r="I106" s="71" t="n"/>
       <c r="J106" s="71" t="n"/>
@@ -5064,12 +5075,12 @@
       </c>
       <c r="C107" s="49" t="inlineStr">
         <is>
-          <t>Altercation</t>
+          <t>All Star Selection</t>
         </is>
       </c>
       <c r="D107" s="38" t="inlineStr">
         <is>
-          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
+          <t>Draw 2 cards</t>
         </is>
       </c>
       <c r="E107" s="7" t="n"/>
@@ -5090,19 +5101,23 @@
       </c>
       <c r="C108" s="49" t="inlineStr">
         <is>
-          <t>Huge Altercation</t>
+          <t>Hit the Bike</t>
         </is>
       </c>
       <c r="D108" s="38" t="inlineStr">
         <is>
-          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
+          <t>Discard all Injuries. Draw 1 card. Give possession to another player</t>
         </is>
       </c>
       <c r="E108" s="7" t="n"/>
       <c r="F108" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="74" t="n"/>
+      <c r="G108" s="74" t="inlineStr">
+        <is>
+          <t>This is not a pass</t>
+        </is>
+      </c>
       <c r="H108" s="71" t="n"/>
       <c r="I108" s="71" t="n"/>
       <c r="J108" s="71" t="n"/>
@@ -5116,12 +5131,12 @@
       </c>
       <c r="C109" s="49" t="inlineStr">
         <is>
-          <t>Home Court Advantage</t>
+          <t>Ice Wrap</t>
         </is>
       </c>
       <c r="D109" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 25%</t>
+          <t>Draw 1 card. Discard all Injuries. If none, draw 1 additional card</t>
         </is>
       </c>
       <c r="E109" s="7" t="n"/>
@@ -5142,19 +5157,23 @@
       </c>
       <c r="C110" s="49" t="inlineStr">
         <is>
-          <t>Away Game</t>
+          <t>Wet Spot</t>
         </is>
       </c>
       <c r="D110" s="38" t="inlineStr">
         <is>
-          <t>SHOT - 10%</t>
+          <t>All Injuries in the discards and deck are displayed. Take one</t>
         </is>
       </c>
       <c r="E110" s="7" t="n"/>
       <c r="F110" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="74" t="n"/>
+      <c r="G110" s="74" t="inlineStr">
+        <is>
+          <t>Deck ones are shown face down</t>
+        </is>
+      </c>
       <c r="H110" s="71" t="n"/>
       <c r="I110" s="71" t="n"/>
       <c r="J110" s="71" t="n"/>
@@ -5168,12 +5187,12 @@
       </c>
       <c r="C111" s="49" t="inlineStr">
         <is>
-          <t>Mic'd Up</t>
+          <t>Fresh Ball</t>
         </is>
       </c>
       <c r="D111" s="38" t="inlineStr">
         <is>
-          <t>SHOT + 10% until passed or shot</t>
+          <t>Next player does not draw at the start of their possession</t>
         </is>
       </c>
       <c r="E111" s="7" t="n"/>
@@ -5182,7 +5201,7 @@
       </c>
       <c r="G111" s="74" t="inlineStr">
         <is>
-          <t>The boost is the holder's alone and does not travel with a pass</t>
+          <t>This is a bad thing in the NBA</t>
         </is>
       </c>
       <c r="H111" s="71" t="n"/>
@@ -5198,19 +5217,23 @@
       </c>
       <c r="C112" s="49" t="inlineStr">
         <is>
-          <t>In The Zone</t>
+          <t>Trade Deadline</t>
         </is>
       </c>
       <c r="D112" s="38" t="inlineStr">
         <is>
-          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+          <t>Declare Left or Right: every player passes their hand that way. The ball goes with it</t>
         </is>
       </c>
       <c r="E112" s="7" t="n"/>
       <c r="F112" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G112" s="74" t="n"/>
+      <c r="G112" s="74" t="inlineStr">
+        <is>
+          <t>The hex travels in the declared direction too</t>
+        </is>
+      </c>
       <c r="H112" s="71" t="n"/>
       <c r="I112" s="71" t="n"/>
       <c r="J112" s="71" t="n"/>
@@ -5224,12 +5247,12 @@
       </c>
       <c r="C113" s="49" t="inlineStr">
         <is>
-          <t>Role Player</t>
+          <t>Floor Cleanup</t>
         </is>
       </c>
       <c r="D113" s="38" t="inlineStr">
         <is>
-          <t>All other players draw 1 card</t>
+          <t>All players shuffle their hands into the deck and draw the same number of cards</t>
         </is>
       </c>
       <c r="E113" s="7" t="n"/>
@@ -5242,322 +5265,335 @@
       <c r="J113" s="71" t="n"/>
     </row>
     <row r="114" ht="28" customHeight="1" s="85">
-      <c r="A114" s="27" t="n"/>
-      <c r="B114" s="28" t="inlineStr">
+      <c r="A114" s="21" t="n"/>
+      <c r="B114" s="22" t="inlineStr">
         <is>
           <t>Retired Game Break</t>
         </is>
       </c>
-      <c r="C114" s="62" t="inlineStr">
+      <c r="C114" s="49" t="inlineStr">
+        <is>
+          <t>Official Timeout</t>
+        </is>
+      </c>
+      <c r="D114" s="38" t="inlineStr">
+        <is>
+          <t>At least 1 referee must be armed: discard all Injuries on all players and clear all referees. If none, all players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="n"/>
+      <c r="F114" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="74" t="n"/>
+      <c r="H114" s="71" t="n"/>
+      <c r="I114" s="71" t="n"/>
+      <c r="J114" s="71" t="n"/>
+    </row>
+    <row r="115" ht="42" customHeight="1" s="85">
+      <c r="A115" s="21" t="n"/>
+      <c r="B115" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C115" s="49" t="inlineStr">
+        <is>
+          <t>Team Doctor</t>
+        </is>
+      </c>
+      <c r="D115" s="38" t="inlineStr">
+        <is>
+          <t>Discard 1 Injury from a player of choice. Draw 2 cards if not choosing yourself</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="74" t="n"/>
+      <c r="H115" s="71" t="n"/>
+      <c r="I115" s="71" t="n"/>
+      <c r="J115" s="71" t="n"/>
+    </row>
+    <row r="116" ht="56" customHeight="1" s="85">
+      <c r="A116" s="21" t="n"/>
+      <c r="B116" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C116" s="49" t="inlineStr">
+        <is>
+          <t>Altercation</t>
+        </is>
+      </c>
+      <c r="D116" s="38" t="inlineStr">
+        <is>
+          <t>Select another player: you and that player each discard 1 card at random. Inbound the ball to a player other than that target</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="n"/>
+      <c r="F116" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="74" t="n"/>
+      <c r="H116" s="71" t="n"/>
+      <c r="I116" s="71" t="n"/>
+      <c r="J116" s="71" t="n"/>
+    </row>
+    <row r="117" ht="57" customHeight="1" s="85">
+      <c r="A117" s="21" t="n"/>
+      <c r="B117" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C117" s="49" t="inlineStr">
+        <is>
+          <t>Huge Altercation</t>
+        </is>
+      </c>
+      <c r="D117" s="38" t="inlineStr">
+        <is>
+          <t>All players discard their hands. If a ref is armed, all players receive 1 TOV. Inbound the ball</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="n"/>
+      <c r="F117" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="74" t="n"/>
+      <c r="H117" s="71" t="n"/>
+      <c r="I117" s="71" t="n"/>
+      <c r="J117" s="71" t="n"/>
+    </row>
+    <row r="118" ht="57" customHeight="1" s="85">
+      <c r="A118" s="21" t="n"/>
+      <c r="B118" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C118" s="49" t="inlineStr">
+        <is>
+          <t>Home Court Advantage</t>
+        </is>
+      </c>
+      <c r="D118" s="38" t="inlineStr">
+        <is>
+          <t>SHOT + 25%</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="74" t="n"/>
+      <c r="H118" s="71" t="n"/>
+      <c r="I118" s="71" t="n"/>
+      <c r="J118" s="71" t="n"/>
+    </row>
+    <row r="119" ht="57" customHeight="1" s="85">
+      <c r="A119" s="21" t="n"/>
+      <c r="B119" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C119" s="49" t="inlineStr">
+        <is>
+          <t>Away Game</t>
+        </is>
+      </c>
+      <c r="D119" s="38" t="inlineStr">
+        <is>
+          <t>SHOT - 10%</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="n"/>
+      <c r="F119" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="74" t="n"/>
+      <c r="H119" s="71" t="n"/>
+      <c r="I119" s="71" t="n"/>
+      <c r="J119" s="71" t="n"/>
+    </row>
+    <row r="120" ht="57" customHeight="1" s="85">
+      <c r="A120" s="21" t="n"/>
+      <c r="B120" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C120" s="49" t="inlineStr">
+        <is>
+          <t>Mic'd Up</t>
+        </is>
+      </c>
+      <c r="D120" s="38" t="inlineStr">
+        <is>
+          <t>SHOT + 10% until passed or shot</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="74" t="inlineStr">
+        <is>
+          <t>The boost is the holder's alone and does not travel with a pass</t>
+        </is>
+      </c>
+      <c r="H120" s="71" t="n"/>
+      <c r="I120" s="71" t="n"/>
+      <c r="J120" s="71" t="n"/>
+    </row>
+    <row r="121" ht="57" customHeight="1" s="85">
+      <c r="A121" s="21" t="n"/>
+      <c r="B121" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C121" s="49" t="inlineStr">
+        <is>
+          <t>In The Zone</t>
+        </is>
+      </c>
+      <c r="D121" s="38" t="inlineStr">
+        <is>
+          <t>Draw 1 card for each 10% SHOT the ball has, rounded down. Minimum 1</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="74" t="n"/>
+      <c r="H121" s="71" t="n"/>
+      <c r="I121" s="71" t="n"/>
+      <c r="J121" s="71" t="n"/>
+    </row>
+    <row r="122" ht="57" customHeight="1" s="85">
+      <c r="A122" s="21" t="n"/>
+      <c r="B122" s="22" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C122" s="49" t="inlineStr">
+        <is>
+          <t>Role Player</t>
+        </is>
+      </c>
+      <c r="D122" s="38" t="inlineStr">
+        <is>
+          <t>All other players draw 1 card</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="n"/>
+      <c r="F122" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="74" t="n"/>
+      <c r="H122" s="71" t="n"/>
+      <c r="I122" s="71" t="n"/>
+      <c r="J122" s="71" t="n"/>
+    </row>
+    <row r="123" ht="20" customHeight="1" s="85">
+      <c r="A123" s="27" t="n"/>
+      <c r="B123" s="28" t="inlineStr">
+        <is>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C123" s="62" t="inlineStr">
         <is>
           <t>Back-and-Forth Game</t>
         </is>
       </c>
-      <c r="D114" s="63" t="inlineStr">
+      <c r="D123" s="63" t="inlineStr">
         <is>
           <t>Discard the next 3 Game Breaks. Whoever draws one draws again</t>
         </is>
       </c>
-      <c r="E114" s="58" t="n"/>
-      <c r="F114" s="59" t="n">
+      <c r="E123" s="58" t="n"/>
+      <c r="F123" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="79" t="n"/>
-      <c r="H114" s="76" t="n"/>
-      <c r="I114" s="76" t="n"/>
-      <c r="J114" s="76" t="n"/>
-    </row>
-    <row r="115" ht="42" customHeight="1" s="85">
-      <c r="A115" s="27" t="n"/>
-      <c r="B115" s="28" t="inlineStr">
-        <is>
-          <t>Retired Game Break</t>
-        </is>
-      </c>
-      <c r="C115" s="62" t="inlineStr">
-        <is>
-          <t>Off the Backboard</t>
-        </is>
-      </c>
-      <c r="D115" s="63" t="inlineStr">
-        <is>
-          <t>Your next missed shot rebounds itself</t>
-        </is>
-      </c>
-      <c r="E115" s="58" t="n"/>
-      <c r="F115" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="79" t="n"/>
-      <c r="H115" s="76" t="n"/>
-      <c r="I115" s="76" t="n"/>
-      <c r="J115" s="76" t="n"/>
-    </row>
-    <row r="116" ht="56" customHeight="1" s="85">
-      <c r="A116" s="52" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="B116" s="53">
-        <f>COUNTIF($B$117:$B$158,"Injury")</f>
-        <v/>
-      </c>
-      <c r="C116" s="54" t="n"/>
-      <c r="D116" s="54" t="n"/>
-      <c r="E116" s="54" t="n"/>
-      <c r="F116" s="55" t="n"/>
-      <c r="G116" s="66" t="n"/>
-      <c r="H116" s="67" t="n"/>
-      <c r="I116" s="67" t="n"/>
-      <c r="J116" s="67" t="n"/>
-    </row>
-    <row r="117" ht="57" customHeight="1" s="85">
-      <c r="A117" s="27" t="n"/>
-      <c r="B117" s="28" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="C117" s="56" t="inlineStr">
-        <is>
-          <t>Bone Bruise</t>
-        </is>
-      </c>
-      <c r="D117" s="63" t="inlineStr">
-        <is>
-          <t>SHOT -10%</t>
-        </is>
-      </c>
-      <c r="E117" s="58" t="n"/>
-      <c r="F117" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G117" s="75" t="n"/>
-      <c r="H117" s="76" t="n"/>
-      <c r="I117" s="76" t="n"/>
-      <c r="J117" s="76" t="n"/>
-    </row>
-    <row r="118" ht="57" customHeight="1" s="85">
-      <c r="A118" s="27" t="n"/>
-      <c r="B118" s="28" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="C118" s="56" t="inlineStr">
-        <is>
-          <t>Rolled Ankle</t>
-        </is>
-      </c>
-      <c r="D118" s="63" t="inlineStr">
-        <is>
-          <t>Discard 1 card to play a Move card</t>
-        </is>
-      </c>
-      <c r="E118" s="58" t="n"/>
-      <c r="F118" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G118" s="75" t="n"/>
-      <c r="H118" s="76" t="n"/>
-      <c r="I118" s="76" t="n"/>
-      <c r="J118" s="76" t="n"/>
-    </row>
-    <row r="119" ht="57" customHeight="1" s="85">
-      <c r="A119" s="27" t="n"/>
-      <c r="B119" s="28" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="C119" s="56" t="inlineStr">
-        <is>
-          <t>Fractured Collarbone</t>
-        </is>
-      </c>
-      <c r="D119" s="63" t="inlineStr">
-        <is>
-          <t>Cannot attempt Three-point shots</t>
-        </is>
-      </c>
-      <c r="E119" s="58" t="n"/>
-      <c r="F119" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G119" s="75" t="n"/>
-      <c r="H119" s="76" t="n"/>
-      <c r="I119" s="76" t="n"/>
-      <c r="J119" s="76" t="n"/>
-    </row>
-    <row r="120" ht="57" customHeight="1" s="85">
-      <c r="A120" s="27" t="n"/>
-      <c r="B120" s="28" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="C120" s="56" t="inlineStr">
-        <is>
-          <t>Jammed Finger</t>
-        </is>
-      </c>
-      <c r="D120" s="63" t="inlineStr">
-        <is>
-          <t>Discard 1 card at random while receiving a Pass</t>
-        </is>
-      </c>
-      <c r="E120" s="58" t="n"/>
-      <c r="F120" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G120" s="75" t="n"/>
-      <c r="H120" s="76" t="n"/>
-      <c r="I120" s="76" t="n"/>
-      <c r="J120" s="76" t="n"/>
-    </row>
-    <row r="121" ht="57" customHeight="1" s="85">
-      <c r="A121" s="27" t="n"/>
-      <c r="B121" s="28" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="C121" s="56" t="inlineStr">
-        <is>
-          <t>Sprained Hamstring</t>
-        </is>
-      </c>
-      <c r="D121" s="63" t="inlineStr">
-        <is>
-          <t>Your Rebound Bids are worth 1 less</t>
-        </is>
-      </c>
-      <c r="E121" s="58" t="n"/>
-      <c r="F121" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G121" s="75" t="n"/>
-      <c r="H121" s="76" t="n"/>
-      <c r="I121" s="76" t="n"/>
-      <c r="J121" s="76" t="n"/>
-    </row>
-    <row r="122" ht="57" customHeight="1" s="85">
-      <c r="A122" s="27" t="n"/>
-      <c r="B122" s="28" t="inlineStr">
-        <is>
-          <t>Injury</t>
-        </is>
-      </c>
-      <c r="C122" s="56" t="inlineStr">
-        <is>
-          <t>Hip Contusion</t>
-        </is>
-      </c>
-      <c r="D122" s="63" t="inlineStr">
-        <is>
-          <t>Discard 1 card at random when playing a Pass card</t>
-        </is>
-      </c>
-      <c r="E122" s="58" t="n"/>
-      <c r="F122" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G122" s="75" t="n"/>
-      <c r="H122" s="76" t="n"/>
-      <c r="I122" s="76" t="n"/>
-      <c r="J122" s="76" t="n"/>
-    </row>
-    <row r="123" ht="20" customHeight="1" s="85">
-      <c r="A123" s="52" t="inlineStr">
-        <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="B123" s="53">
-        <f>COUNTIF($B$124:$B$158,"Devastating Injury")</f>
-        <v/>
-      </c>
-      <c r="C123" s="54" t="n"/>
-      <c r="D123" s="54" t="n"/>
-      <c r="E123" s="54" t="n"/>
-      <c r="F123" s="55" t="n"/>
-      <c r="G123" s="66" t="n"/>
-      <c r="H123" s="67" t="n"/>
-      <c r="I123" s="67" t="n"/>
-      <c r="J123" s="67" t="n"/>
+      <c r="G123" s="79" t="n"/>
+      <c r="H123" s="76" t="n"/>
+      <c r="I123" s="76" t="n"/>
+      <c r="J123" s="76" t="n"/>
     </row>
     <row r="124" ht="28" customHeight="1" s="85">
       <c r="A124" s="27" t="n"/>
       <c r="B124" s="28" t="inlineStr">
         <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="C124" s="64" t="inlineStr">
-        <is>
-          <t>Torn Achilles</t>
-        </is>
-      </c>
-      <c r="D124" s="65" t="inlineStr">
-        <is>
-          <t>Cannot Play Dunk Cards. Can only play 1 Move card per possession</t>
+          <t>Retired Game Break</t>
+        </is>
+      </c>
+      <c r="C124" s="62" t="inlineStr">
+        <is>
+          <t>Off the Backboard</t>
+        </is>
+      </c>
+      <c r="D124" s="63" t="inlineStr">
+        <is>
+          <t>Your next missed shot rebounds itself</t>
         </is>
       </c>
       <c r="E124" s="58" t="n"/>
-      <c r="F124" s="61" t="n"/>
-      <c r="G124" s="75" t="inlineStr">
-        <is>
-          <t>Landing one discards every other Injury, and while one is on you a new Injury is discarded</t>
-        </is>
-      </c>
+      <c r="F124" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="79" t="n"/>
       <c r="H124" s="76" t="n"/>
       <c r="I124" s="76" t="n"/>
       <c r="J124" s="76" t="n"/>
     </row>
     <row r="125" ht="28" customHeight="1" s="85">
-      <c r="A125" s="27" t="n"/>
-      <c r="B125" s="28" t="inlineStr">
-        <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="C125" s="64" t="inlineStr">
-        <is>
-          <t>Torn ACL</t>
-        </is>
-      </c>
-      <c r="D125" s="65" t="inlineStr">
-        <is>
-          <t>Cannot Play Move Cards.</t>
-        </is>
-      </c>
-      <c r="E125" s="58" t="n"/>
-      <c r="F125" s="61" t="n"/>
-      <c r="G125" s="75" t="n"/>
-      <c r="H125" s="76" t="n"/>
-      <c r="I125" s="76" t="n"/>
-      <c r="J125" s="76" t="n"/>
+      <c r="A125" s="52" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="B125" s="53">
+        <f>COUNTIF($B$117:$B$158,"Injury")</f>
+        <v/>
+      </c>
+      <c r="C125" s="54" t="n"/>
+      <c r="D125" s="54" t="n"/>
+      <c r="E125" s="54" t="n"/>
+      <c r="F125" s="55" t="n"/>
+      <c r="G125" s="66" t="n"/>
+      <c r="H125" s="67" t="n"/>
+      <c r="I125" s="67" t="n"/>
+      <c r="J125" s="67" t="n"/>
     </row>
     <row r="126" ht="28" customHeight="1" s="85">
       <c r="A126" s="27" t="n"/>
       <c r="B126" s="28" t="inlineStr">
         <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="C126" s="64" t="inlineStr">
-        <is>
-          <t>Torn Meniscus</t>
-        </is>
-      </c>
-      <c r="D126" s="65" t="inlineStr">
-        <is>
-          <t>Randomly Lock all but 1 Card Each Possession</t>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C126" s="56" t="inlineStr">
+        <is>
+          <t>Bone Bruise</t>
+        </is>
+      </c>
+      <c r="D126" s="63" t="inlineStr">
+        <is>
+          <t>SHOT -10%</t>
         </is>
       </c>
       <c r="E126" s="58" t="n"/>
-      <c r="F126" s="61" t="n"/>
+      <c r="F126" s="59" t="n">
+        <v>2</v>
+      </c>
       <c r="G126" s="75" t="n"/>
       <c r="H126" s="76" t="n"/>
       <c r="I126" s="76" t="n"/>
@@ -5567,282 +5603,304 @@
       <c r="A127" s="27" t="n"/>
       <c r="B127" s="28" t="inlineStr">
         <is>
-          <t>Devastating Injury</t>
-        </is>
-      </c>
-      <c r="C127" s="64" t="inlineStr">
-        <is>
-          <t>Patellar Tendon Tear</t>
-        </is>
-      </c>
-      <c r="D127" s="65" t="inlineStr">
-        <is>
-          <t>Cannot Draw Cards except at the start of your possession</t>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C127" s="56" t="inlineStr">
+        <is>
+          <t>Rolled Ankle</t>
+        </is>
+      </c>
+      <c r="D127" s="63" t="inlineStr">
+        <is>
+          <t>Discard 1 card to play a Move card</t>
         </is>
       </c>
       <c r="E127" s="58" t="n"/>
-      <c r="F127" s="61" t="n"/>
+      <c r="F127" s="59" t="n">
+        <v>2</v>
+      </c>
       <c r="G127" s="75" t="n"/>
       <c r="H127" s="76" t="n"/>
       <c r="I127" s="76" t="n"/>
       <c r="J127" s="76" t="n"/>
     </row>
     <row r="128" ht="42" customHeight="1" s="85">
-      <c r="A128" s="52" t="inlineStr">
+      <c r="A128" s="27" t="n"/>
+      <c r="B128" s="28" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C128" s="56" t="inlineStr">
+        <is>
+          <t>Fractured Collarbone</t>
+        </is>
+      </c>
+      <c r="D128" s="63" t="inlineStr">
+        <is>
+          <t>Cannot attempt Three-point shots</t>
+        </is>
+      </c>
+      <c r="E128" s="58" t="n"/>
+      <c r="F128" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G128" s="75" t="n"/>
+      <c r="H128" s="76" t="n"/>
+      <c r="I128" s="76" t="n"/>
+      <c r="J128" s="76" t="n"/>
+    </row>
+    <row r="129" ht="28" customHeight="1" s="85">
+      <c r="A129" s="27" t="n"/>
+      <c r="B129" s="28" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C129" s="56" t="inlineStr">
+        <is>
+          <t>Jammed Finger</t>
+        </is>
+      </c>
+      <c r="D129" s="63" t="inlineStr">
+        <is>
+          <t>Discard 1 card at random while receiving a Pass</t>
+        </is>
+      </c>
+      <c r="E129" s="58" t="n"/>
+      <c r="F129" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G129" s="75" t="n"/>
+      <c r="H129" s="76" t="n"/>
+      <c r="I129" s="76" t="n"/>
+      <c r="J129" s="76" t="n"/>
+    </row>
+    <row r="130" ht="28" customHeight="1" s="85">
+      <c r="A130" s="27" t="n"/>
+      <c r="B130" s="28" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C130" s="56" t="inlineStr">
+        <is>
+          <t>Sprained Hamstring</t>
+        </is>
+      </c>
+      <c r="D130" s="63" t="inlineStr">
+        <is>
+          <t>Your Rebound Bids are worth 1 less</t>
+        </is>
+      </c>
+      <c r="E130" s="58" t="n"/>
+      <c r="F130" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G130" s="75" t="n"/>
+      <c r="H130" s="76" t="n"/>
+      <c r="I130" s="76" t="n"/>
+      <c r="J130" s="76" t="n"/>
+    </row>
+    <row r="131" ht="56" customHeight="1" s="85">
+      <c r="A131" s="27" t="n"/>
+      <c r="B131" s="28" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="C131" s="56" t="inlineStr">
+        <is>
+          <t>Hip Contusion</t>
+        </is>
+      </c>
+      <c r="D131" s="63" t="inlineStr">
+        <is>
+          <t>Discard 1 card at random when playing a Pass card</t>
+        </is>
+      </c>
+      <c r="E131" s="58" t="n"/>
+      <c r="F131" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" s="75" t="n"/>
+      <c r="H131" s="76" t="n"/>
+      <c r="I131" s="76" t="n"/>
+      <c r="J131" s="76" t="n"/>
+    </row>
+    <row r="132" ht="56" customHeight="1" s="85">
+      <c r="A132" s="52" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="B132" s="53">
+        <f>COUNTIF($B$124:$B$158,"Devastating Injury")</f>
+        <v/>
+      </c>
+      <c r="C132" s="54" t="n"/>
+      <c r="D132" s="54" t="n"/>
+      <c r="E132" s="54" t="n"/>
+      <c r="F132" s="55" t="n"/>
+      <c r="G132" s="66" t="n"/>
+      <c r="H132" s="67" t="n"/>
+      <c r="I132" s="67" t="n"/>
+      <c r="J132" s="67" t="n"/>
+    </row>
+    <row r="133" ht="28" customHeight="1" s="85">
+      <c r="A133" s="27" t="n"/>
+      <c r="B133" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C133" s="64" t="inlineStr">
+        <is>
+          <t>Torn Achilles</t>
+        </is>
+      </c>
+      <c r="D133" s="65" t="inlineStr">
+        <is>
+          <t>Cannot Play Dunk Cards. Can only play 1 Move card per possession</t>
+        </is>
+      </c>
+      <c r="E133" s="58" t="n"/>
+      <c r="F133" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="75" t="inlineStr">
+        <is>
+          <t>Landing one discards every other Injury, and while one is on you a new Injury is discarded</t>
+        </is>
+      </c>
+      <c r="H133" s="76" t="n"/>
+      <c r="I133" s="76" t="n"/>
+      <c r="J133" s="76" t="n"/>
+    </row>
+    <row r="134" ht="28" customHeight="1" s="85">
+      <c r="A134" s="27" t="n"/>
+      <c r="B134" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C134" s="64" t="inlineStr">
+        <is>
+          <t>Torn ACL</t>
+        </is>
+      </c>
+      <c r="D134" s="65" t="inlineStr">
+        <is>
+          <t>Cannot Play Move Cards.</t>
+        </is>
+      </c>
+      <c r="E134" s="58" t="n"/>
+      <c r="F134" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="75" t="n"/>
+      <c r="H134" s="76" t="n"/>
+      <c r="I134" s="76" t="n"/>
+      <c r="J134" s="76" t="n"/>
+    </row>
+    <row r="135" ht="28" customHeight="1" s="85">
+      <c r="A135" s="27" t="n"/>
+      <c r="B135" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C135" s="64" t="inlineStr">
+        <is>
+          <t>Torn Meniscus</t>
+        </is>
+      </c>
+      <c r="D135" s="65" t="inlineStr">
+        <is>
+          <t>Randomly Lock all but 1 Card Each Possession</t>
+        </is>
+      </c>
+      <c r="E135" s="58" t="n"/>
+      <c r="F135" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="75" t="n"/>
+      <c r="H135" s="76" t="n"/>
+      <c r="I135" s="76" t="n"/>
+      <c r="J135" s="76" t="n"/>
+    </row>
+    <row r="136" ht="28" customHeight="1" s="85">
+      <c r="A136" s="27" t="n"/>
+      <c r="B136" s="28" t="inlineStr">
+        <is>
+          <t>Devastating Injury</t>
+        </is>
+      </c>
+      <c r="C136" s="64" t="inlineStr">
+        <is>
+          <t>Patellar Tendon Tear</t>
+        </is>
+      </c>
+      <c r="D136" s="65" t="inlineStr">
+        <is>
+          <t>Cannot Draw Cards except at the start of your possession</t>
+        </is>
+      </c>
+      <c r="E136" s="58" t="n"/>
+      <c r="F136" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="75" t="n"/>
+      <c r="H136" s="76" t="n"/>
+      <c r="I136" s="76" t="n"/>
+      <c r="J136" s="76" t="n"/>
+    </row>
+    <row r="137" ht="14" customHeight="1" s="85">
+      <c r="A137" s="52" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="B128" s="53">
+      <c r="B137" s="53">
         <f>COUNTIF($B$129:$B$158,"Intangible")</f>
         <v/>
       </c>
-      <c r="C128" s="54" t="n"/>
-      <c r="D128" s="54" t="n"/>
-      <c r="E128" s="54" t="n"/>
-      <c r="F128" s="55" t="n"/>
-      <c r="G128" s="66" t="n"/>
-      <c r="H128" s="67" t="n"/>
-      <c r="I128" s="67" t="n"/>
-      <c r="J128" s="67" t="n"/>
-    </row>
-    <row r="129" ht="28" customHeight="1" s="85">
-      <c r="A129" s="42" t="inlineStr">
+      <c r="C137" s="54" t="n"/>
+      <c r="D137" s="54" t="n"/>
+      <c r="E137" s="54" t="n"/>
+      <c r="F137" s="55" t="n"/>
+      <c r="G137" s="66" t="n"/>
+      <c r="H137" s="67" t="n"/>
+      <c r="I137" s="67" t="n"/>
+      <c r="J137" s="67" t="n"/>
+    </row>
+    <row r="138" ht="28" customHeight="1" s="85">
+      <c r="A138" s="42" t="inlineStr">
         <is>
           <t>All intangibles are limited to 1</t>
         </is>
       </c>
-      <c r="B129" s="22" t="inlineStr">
+      <c r="B138" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C129" s="23" t="inlineStr">
+      <c r="C138" s="23" t="inlineStr">
         <is>
           <t>Board-Crasher</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>SHOT +25% when shooting as your first action after a Rebound of your own miss.</t>
         </is>
       </c>
-      <c r="E129" s="7" t="n"/>
-      <c r="F129" s="50" t="n"/>
-      <c r="G129" s="70" t="n"/>
-      <c r="H129" s="71" t="n"/>
-      <c r="I129" s="71" t="n"/>
-      <c r="J129" s="71" t="n"/>
-    </row>
-    <row r="130" ht="28" customHeight="1" s="85">
-      <c r="A130" s="21" t="n"/>
-      <c r="B130" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C130" s="24" t="inlineStr">
-        <is>
-          <t>Catch &amp; Shoot Specialist</t>
-        </is>
-      </c>
-      <c r="D130" s="25" t="inlineStr">
-        <is>
-          <t>SHOT +25% when shooting as your first action after a Pass</t>
-        </is>
-      </c>
-      <c r="E130" s="26" t="n"/>
-      <c r="F130" s="50" t="n"/>
-      <c r="G130" s="72" t="n"/>
-      <c r="H130" s="71" t="n"/>
-      <c r="I130" s="71" t="n"/>
-      <c r="J130" s="71" t="n"/>
-    </row>
-    <row r="131" ht="56" customHeight="1" s="85">
-      <c r="A131" s="21" t="n"/>
-      <c r="B131" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C131" s="23" t="inlineStr">
-        <is>
-          <t>Clutch Gene</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>SHOT = 2X if you have 1 card or fewer in hand, or the Shot Clock is 03 or less</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="n"/>
-      <c r="F131" s="50" t="n"/>
-      <c r="G131" s="70" t="n"/>
-      <c r="H131" s="71" t="n"/>
-      <c r="I131" s="71" t="n"/>
-      <c r="J131" s="71" t="n"/>
-    </row>
-    <row r="132" ht="56" customHeight="1" s="85">
-      <c r="B132" s="0" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C132" s="0" t="inlineStr">
-        <is>
-          <t>Roswell Reach</t>
-        </is>
-      </c>
-      <c r="D132" s="0" t="inlineStr">
-        <is>
-          <t>All your Rebound bids of 1 or more count as 1 higher</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="28" customHeight="1" s="85">
-      <c r="A133" s="21" t="n"/>
-      <c r="B133" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C133" s="24" t="inlineStr">
-        <is>
-          <t>Floor General</t>
-        </is>
-      </c>
-      <c r="D133" s="25" t="inlineStr">
-        <is>
-          <t>You choose all targets of all kinds — card declarations, non auto-pass targets, and the rest. Not choices about a player's own card: which effect of a multi-effect card, or whether to feed a shot an extra discard</t>
-        </is>
-      </c>
-      <c r="E133" s="26" t="n"/>
-      <c r="F133" s="50" t="n"/>
-      <c r="G133" s="72" t="n"/>
-      <c r="H133" s="71" t="n"/>
-      <c r="I133" s="71" t="n"/>
-      <c r="J133" s="71" t="n"/>
-    </row>
-    <row r="134" ht="28" customHeight="1" s="85">
-      <c r="A134" s="21" t="n"/>
-      <c r="B134" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C134" s="23" t="inlineStr">
-        <is>
-          <t>Southpaw Shooter</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>SHOT gains and losses are reversed</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="n"/>
-      <c r="F134" s="51" t="n"/>
-      <c r="G134" s="70" t="n"/>
-      <c r="H134" s="71" t="n"/>
-      <c r="I134" s="71" t="n"/>
-      <c r="J134" s="71" t="n"/>
-    </row>
-    <row r="135" ht="28" customHeight="1" s="85">
-      <c r="A135" s="21" t="n"/>
-      <c r="B135" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C135" s="37" t="inlineStr">
-        <is>
-          <t>Freethrow Merchant</t>
-        </is>
-      </c>
-      <c r="D135" s="41" t="inlineStr">
-        <is>
-          <t>All Clamps on you grant 1 FT instead</t>
-        </is>
-      </c>
-      <c r="E135" s="26" t="n"/>
-      <c r="F135" s="50" t="n"/>
-      <c r="G135" s="77" t="n"/>
-      <c r="H135" s="71" t="n"/>
-      <c r="I135" s="71" t="n"/>
-      <c r="J135" s="71" t="n"/>
-    </row>
-    <row r="136" ht="28" customHeight="1" s="85">
-      <c r="A136" s="21" t="n"/>
-      <c r="B136" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C136" s="37" t="inlineStr">
-        <is>
-          <t>Generational Whistle</t>
-        </is>
-      </c>
-      <c r="D136" s="38" t="inlineStr">
-        <is>
-          <t>Take 1 additional FT</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="n"/>
-      <c r="F136" s="50" t="n"/>
-      <c r="G136" s="70" t="n"/>
-      <c r="H136" s="71" t="n"/>
-      <c r="I136" s="71" t="n"/>
-      <c r="J136" s="71" t="n"/>
-    </row>
-    <row r="137" ht="14" customHeight="1" s="85">
-      <c r="A137" s="21" t="n"/>
-      <c r="B137" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C137" s="24" t="inlineStr">
-        <is>
-          <t>Gravity</t>
-        </is>
-      </c>
-      <c r="D137" s="25" t="inlineStr">
-        <is>
-          <t>All Clamps automatically apply to you. +1 AST whenever another player attempts a shot</t>
-        </is>
-      </c>
-      <c r="E137" s="26" t="n"/>
-      <c r="F137" s="50" t="n"/>
-      <c r="G137" s="72" t="n"/>
-      <c r="H137" s="71" t="n"/>
-      <c r="I137" s="71" t="n"/>
-      <c r="J137" s="71" t="n"/>
-    </row>
-    <row r="138" ht="28" customHeight="1" s="85">
-      <c r="A138" s="21" t="n"/>
-      <c r="B138" s="22" t="inlineStr">
-        <is>
-          <t>Intangible</t>
-        </is>
-      </c>
-      <c r="C138" s="23" t="inlineStr">
-        <is>
-          <t>Great Conditioning</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>Immediately discard all Injuries you draw and draw a new card for each</t>
-        </is>
-      </c>
       <c r="E138" s="7" t="n"/>
-      <c r="F138" s="50" t="n"/>
-      <c r="G138" s="70" t="inlineStr">
-        <is>
-          <t>Also discards any Injuries you already have (not on the card)</t>
-        </is>
-      </c>
+      <c r="F138" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="70" t="n"/>
       <c r="H138" s="71" t="n"/>
       <c r="I138" s="71" t="n"/>
       <c r="J138" s="71" t="n"/>
@@ -5856,16 +5914,18 @@
       </c>
       <c r="C139" s="24" t="inlineStr">
         <is>
-          <t>Hot Hand</t>
+          <t>Catch &amp; Shoot Specialist</t>
         </is>
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>SHOT +25% if you scored last round.</t>
+          <t>SHOT +25% when shooting as your first action after a Pass</t>
         </is>
       </c>
       <c r="E139" s="26" t="n"/>
-      <c r="F139" s="50" t="n"/>
+      <c r="F139" s="50" t="n">
+        <v>1</v>
+      </c>
       <c r="G139" s="72" t="n"/>
       <c r="H139" s="71" t="n"/>
       <c r="I139" s="71" t="n"/>
@@ -5880,48 +5940,42 @@
       </c>
       <c r="C140" s="23" t="inlineStr">
         <is>
-          <t>Like That</t>
-        </is>
-      </c>
-      <c r="D140" s="38" t="inlineStr">
-        <is>
-          <t>Your SHOT % cannot be reduced</t>
+          <t>Clutch Gene</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>SHOT = $[2X] if you have 1 card or fewer in hand, or the Shot Clock is 03 or less</t>
         </is>
       </c>
       <c r="E140" s="7" t="n"/>
-      <c r="F140" s="50" t="n"/>
-      <c r="G140" s="70" t="inlineStr">
-        <is>
-          <t>Variaball effects still lower SHOT: the ball is altered, not the player (not on the card)</t>
-        </is>
-      </c>
+      <c r="F140" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="70" t="n"/>
       <c r="H140" s="71" t="n"/>
       <c r="I140" s="71" t="n"/>
       <c r="J140" s="71" t="n"/>
     </row>
     <row r="141" ht="28" customHeight="1" s="85">
-      <c r="A141" s="21" t="n"/>
-      <c r="B141" s="22" t="inlineStr">
+      <c r="B141" s="0" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C141" s="24" t="inlineStr">
-        <is>
-          <t>Park Shark</t>
-        </is>
-      </c>
-      <c r="D141" s="25" t="inlineStr">
-        <is>
-          <t>SHOT +25%. Cannot play Move cards or shoot Threes</t>
-        </is>
-      </c>
-      <c r="E141" s="26" t="n"/>
-      <c r="F141" s="50" t="n"/>
-      <c r="G141" s="73" t="n"/>
-      <c r="H141" s="71" t="n"/>
-      <c r="I141" s="71" t="n"/>
-      <c r="J141" s="71" t="n"/>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>Roswell Reach</t>
+        </is>
+      </c>
+      <c r="D141" s="0" t="inlineStr">
+        <is>
+          <t>Every Rebound bid you make counts as one card more</t>
+        </is>
+      </c>
+      <c r="F141" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" ht="28" customHeight="1" s="85">
       <c r="A142" s="21" t="n"/>
@@ -5930,19 +5984,21 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C142" s="23" t="inlineStr">
-        <is>
-          <t>Point God</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>Draw 1 card following each of your passes</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="n"/>
-      <c r="F142" s="50" t="n"/>
-      <c r="G142" s="70" t="n"/>
+      <c r="C142" s="24" t="inlineStr">
+        <is>
+          <t>Floor General</t>
+        </is>
+      </c>
+      <c r="D142" s="25" t="inlineStr">
+        <is>
+          <t>You name every target on the floor</t>
+        </is>
+      </c>
+      <c r="E142" s="26" t="n"/>
+      <c r="F142" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="72" t="n"/>
       <c r="H142" s="71" t="n"/>
       <c r="I142" s="71" t="n"/>
       <c r="J142" s="71" t="n"/>
@@ -5954,23 +6010,21 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C143" s="24" t="inlineStr">
-        <is>
-          <t>Shot Creator</t>
-        </is>
-      </c>
-      <c r="D143" s="25" t="inlineStr">
-        <is>
-          <t>Draw 1 additional card after every draw effect</t>
-        </is>
-      </c>
-      <c r="E143" s="26" t="n"/>
-      <c r="F143" s="50" t="n"/>
-      <c r="G143" s="73" t="inlineStr">
-        <is>
-          <t>Triggers once per act of drawing: a Draw 2 still gives only 1 extra</t>
-        </is>
-      </c>
+      <c r="C143" s="23" t="inlineStr">
+        <is>
+          <t>Southpaw Shooter</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>SHOT gains and losses are reversed</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="n"/>
+      <c r="F143" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="70" t="n"/>
       <c r="H143" s="71" t="n"/>
       <c r="I143" s="71" t="n"/>
       <c r="J143" s="71" t="n"/>
@@ -5982,23 +6036,21 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C144" s="23" t="inlineStr">
-        <is>
-          <t>Sixth Man</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>SHOT = 60% on any six: cards in hand, Shot Clock, shot of the round, or Score</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="n"/>
-      <c r="F144" s="50" t="n"/>
-      <c r="G144" s="70" t="inlineStr">
-        <is>
-          <t>A second SHOOT (60%) button beside Shoot, shown only on a six. Ignore it when SHOT is already higher</t>
-        </is>
-      </c>
+      <c r="C144" s="37" t="inlineStr">
+        <is>
+          <t>Freethrow Merchant</t>
+        </is>
+      </c>
+      <c r="D144" s="41" t="inlineStr">
+        <is>
+          <t>Any Clamp on you becomes "Take 1 FT"</t>
+        </is>
+      </c>
+      <c r="E144" s="26" t="n"/>
+      <c r="F144" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="77" t="n"/>
       <c r="H144" s="71" t="n"/>
       <c r="I144" s="71" t="n"/>
       <c r="J144" s="71" t="n"/>
@@ -6010,19 +6062,21 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C145" s="24" t="inlineStr">
-        <is>
-          <t>Sniper</t>
-        </is>
-      </c>
-      <c r="D145" s="25" t="inlineStr">
-        <is>
-          <t>SHOT +25% when attempting a Three</t>
-        </is>
-      </c>
-      <c r="E145" s="26" t="n"/>
-      <c r="F145" s="50" t="n"/>
-      <c r="G145" s="72" t="n"/>
+      <c r="C145" s="37" t="inlineStr">
+        <is>
+          <t>Generational Whistle</t>
+        </is>
+      </c>
+      <c r="D145" s="38" t="inlineStr">
+        <is>
+          <t>Take 1 additional FT</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="n"/>
+      <c r="F145" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="70" t="n"/>
       <c r="H145" s="71" t="n"/>
       <c r="I145" s="71" t="n"/>
       <c r="J145" s="71" t="n"/>
@@ -6034,19 +6088,21 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C146" s="23" t="inlineStr">
-        <is>
-          <t>Splash Cousin</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>SHOT = 100% when attempting a Three</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="n"/>
-      <c r="F146" s="50" t="n"/>
-      <c r="G146" s="70" t="n"/>
+      <c r="C146" s="24" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="D146" s="25" t="inlineStr">
+        <is>
+          <t>Every Clamp lands on you. AST +1 on anyone else's attempt</t>
+        </is>
+      </c>
+      <c r="E146" s="26" t="n"/>
+      <c r="F146" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="72" t="n"/>
       <c r="H146" s="71" t="n"/>
       <c r="I146" s="71" t="n"/>
       <c r="J146" s="71" t="n"/>
@@ -6058,19 +6114,25 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C147" s="24" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D147" s="25" t="inlineStr">
-        <is>
-          <t>All Clamps on you have no effect on SHOT %</t>
-        </is>
-      </c>
-      <c r="E147" s="26" t="n"/>
-      <c r="F147" s="50" t="n"/>
-      <c r="G147" s="72" t="n"/>
+      <c r="C147" s="23" t="inlineStr">
+        <is>
+          <t>Great Conditioning</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>Injuries never land. Draw again for each</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="n"/>
+      <c r="F147" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="70" t="inlineStr">
+        <is>
+          <t>Also discards any Injuries you already have (not on the card)</t>
+        </is>
+      </c>
       <c r="H147" s="71" t="n"/>
       <c r="I147" s="71" t="n"/>
       <c r="J147" s="71" t="n"/>
@@ -6082,23 +6144,21 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C148" s="23" t="inlineStr">
-        <is>
-          <t>Lethal Shooter</t>
-        </is>
-      </c>
-      <c r="D148" s="38" t="inlineStr">
-        <is>
-          <t>SHOT = 100% when shooting as your first action after a Rebound of your own miss</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="n"/>
-      <c r="F148" s="50" t="n"/>
-      <c r="G148" s="70" t="inlineStr">
-        <is>
-          <t>Special text: “I understand it now”</t>
-        </is>
-      </c>
+      <c r="C148" s="24" t="inlineStr">
+        <is>
+          <t>Hot Hand</t>
+        </is>
+      </c>
+      <c r="D148" s="25" t="inlineStr">
+        <is>
+          <t>SHOT +25% if you scored last round</t>
+        </is>
+      </c>
+      <c r="E148" s="26" t="n"/>
+      <c r="F148" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="72" t="n"/>
       <c r="H148" s="71" t="n"/>
       <c r="I148" s="71" t="n"/>
       <c r="J148" s="71" t="n"/>
@@ -6110,19 +6170,25 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C149" s="24" t="inlineStr">
-        <is>
-          <t>Ball Pounder</t>
-        </is>
-      </c>
-      <c r="D149" s="25" t="inlineStr">
-        <is>
-          <t>Every Dribble draws 1 card but gives SHOT -10% and Shot Clock - 01</t>
-        </is>
-      </c>
-      <c r="E149" s="26" t="n"/>
-      <c r="F149" s="50" t="n"/>
-      <c r="G149" s="73" t="n"/>
+      <c r="C149" s="23" t="inlineStr">
+        <is>
+          <t>Like That</t>
+        </is>
+      </c>
+      <c r="D149" s="38" t="inlineStr">
+        <is>
+          <t>Nothing takes your SHOT down</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="n"/>
+      <c r="F149" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="70" t="inlineStr">
+        <is>
+          <t>Variaball effects still lower SHOT: the ball is altered, not the player (not on the card)</t>
+        </is>
+      </c>
       <c r="H149" s="71" t="n"/>
       <c r="I149" s="71" t="n"/>
       <c r="J149" s="71" t="n"/>
@@ -6134,19 +6200,21 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C150" s="23" t="inlineStr">
-        <is>
-          <t>Dirty Player</t>
-        </is>
-      </c>
-      <c r="D150" s="38" t="inlineStr">
-        <is>
-          <t>When sending Clamps, the clamped player discards 1 for each of your Clamps if they have any Injuries. Discard 1 whenever a Whistle triggers</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="n"/>
-      <c r="F150" s="50" t="n"/>
-      <c r="G150" s="70" t="n"/>
+      <c r="C150" s="24" t="inlineStr">
+        <is>
+          <t>Park Shark</t>
+        </is>
+      </c>
+      <c r="D150" s="25" t="inlineStr">
+        <is>
+          <t>SHOT +25%. Cannot play Move cards or shoot Threes</t>
+        </is>
+      </c>
+      <c r="E150" s="26" t="n"/>
+      <c r="F150" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="73" t="n"/>
       <c r="H150" s="71" t="n"/>
       <c r="I150" s="71" t="n"/>
       <c r="J150" s="71" t="n"/>
@@ -6160,21 +6228,19 @@
       </c>
       <c r="C151" s="23" t="inlineStr">
         <is>
-          <t>Free Agent</t>
-        </is>
-      </c>
-      <c r="D151" s="38" t="inlineStr">
-        <is>
-          <t>Discard your hand. Play a card at random from a player of your choosing (they keep it)</t>
+          <t>Point God</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 after each of your passes</t>
         </is>
       </c>
       <c r="E151" s="7" t="n"/>
-      <c r="F151" s="50" t="n"/>
-      <c r="G151" s="70" t="inlineStr">
-        <is>
-          <t>Low priority to bring back. The discard waits for the draw chain to finish. Target is shuffled first and is affected by Floor General. Your own draws are kept. All-0 rebounds are yours; otherwise you cannot bid  [OUT OF THE DECK — the borrow button throws the answer away; back when it routes through Move.borrow]</t>
-        </is>
-      </c>
+      <c r="F151" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="70" t="n"/>
       <c r="H151" s="71" t="n"/>
       <c r="I151" s="71" t="n"/>
       <c r="J151" s="71" t="n"/>
@@ -6186,19 +6252,25 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C152" s="23" t="inlineStr">
-        <is>
-          <t>Franchise Player</t>
-        </is>
-      </c>
-      <c r="D152" s="38" t="inlineStr">
-        <is>
-          <t>When passing, choose 1 of the new player's Intangibles or a card in their hand for them to discard</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="n"/>
-      <c r="F152" s="50" t="n"/>
-      <c r="G152" s="70" t="n"/>
+      <c r="C152" s="24" t="inlineStr">
+        <is>
+          <t>Shot Creator</t>
+        </is>
+      </c>
+      <c r="D152" s="25" t="inlineStr">
+        <is>
+          <t>On Draw: Draw +1</t>
+        </is>
+      </c>
+      <c r="E152" s="26" t="n"/>
+      <c r="F152" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="73" t="inlineStr">
+        <is>
+          <t>Triggers once per act of drawing: a Draw 2 still gives only 1 extra</t>
+        </is>
+      </c>
       <c r="H152" s="71" t="n"/>
       <c r="I152" s="71" t="n"/>
       <c r="J152" s="71" t="n"/>
@@ -6212,19 +6284,21 @@
       </c>
       <c r="C153" s="23" t="inlineStr">
         <is>
-          <t>Fundamentalist</t>
-        </is>
-      </c>
-      <c r="D153" s="38" t="inlineStr">
-        <is>
-          <t>No Special Moves. Each Move once a turn. Swings, Skip Pass and Dribble are never spent. Discards the current ball</t>
+          <t>Sixth Man</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>On any six — cards in hand, Shot Clock, shot of the round, or Score — you may Shoot at SHOT = 60%</t>
         </is>
       </c>
       <c r="E153" s="7" t="n"/>
-      <c r="F153" s="50" t="n"/>
+      <c r="F153" s="50" t="n">
+        <v>1</v>
+      </c>
       <c r="G153" s="70" t="inlineStr">
         <is>
-          <t>The ball is discarded once, on activation</t>
+          <t>A second SHOOT (60%) button beside Shoot, shown only on a six. Ignore it when SHOT is already higher</t>
         </is>
       </c>
       <c r="H153" s="71" t="n"/>
@@ -6238,21 +6312,21 @@
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C154" s="23" t="inlineStr">
-        <is>
-          <t>Moves At Own Pace</t>
-        </is>
-      </c>
-      <c r="D154" s="38" t="inlineStr">
-        <is>
-          <t>Cannot be called for Traveling or Shot Clock violations</t>
-        </is>
-      </c>
-      <c r="E154" s="7" t="n"/>
+      <c r="C154" s="24" t="inlineStr">
+        <is>
+          <t>Sniper</t>
+        </is>
+      </c>
+      <c r="D154" s="25" t="inlineStr">
+        <is>
+          <t>SHOT +25% when attempting a Three</t>
+        </is>
+      </c>
+      <c r="E154" s="26" t="n"/>
       <c r="F154" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="G154" s="70" t="n"/>
+      <c r="G154" s="72" t="n"/>
       <c r="H154" s="71" t="n"/>
       <c r="I154" s="71" t="n"/>
       <c r="J154" s="71" t="n"/>
@@ -6266,277 +6340,286 @@
       </c>
       <c r="C155" s="23" t="inlineStr">
         <is>
-          <t>Equalizer</t>
-        </is>
-      </c>
-      <c r="D155" s="38" t="inlineStr">
-        <is>
-          <t>You may Discard this card when shooting: SHOT = 100%. All players' pts become your new total pts.</t>
+          <t>Splash Cousin</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>SHOT = 100% when attempting a Three</t>
         </is>
       </c>
       <c r="E155" s="7" t="n"/>
-      <c r="F155" s="50" t="n"/>
-      <c r="G155" s="70" t="inlineStr">
-        <is>
-          <t>The points change comes after the make</t>
-        </is>
-      </c>
+      <c r="F155" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="70" t="n"/>
       <c r="H155" s="71" t="n"/>
       <c r="I155" s="71" t="n"/>
       <c r="J155" s="71" t="n"/>
     </row>
     <row r="156" s="85">
-      <c r="A156" s="27" t="n"/>
-      <c r="B156" s="28" t="inlineStr">
+      <c r="A156" s="21" t="n"/>
+      <c r="B156" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C156" s="56" t="inlineStr">
-        <is>
-          <t>Varsitile</t>
-        </is>
-      </c>
-      <c r="D156" s="63" t="inlineStr">
-        <is>
-          <t>You can play more than 1 Varena and Variaball per turn. Once per possession, you can exchange the Varena and/or ball for one in the Discards</t>
-        </is>
-      </c>
-      <c r="E156" s="58" t="n"/>
-      <c r="F156" s="61" t="n"/>
-      <c r="G156" s="75" t="inlineStr">
-        <is>
-          <t>One use can exchange both</t>
-        </is>
-      </c>
-      <c r="H156" s="76" t="n"/>
-      <c r="I156" s="76" t="n"/>
-      <c r="J156" s="76" t="n"/>
+      <c r="C156" s="24" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D156" s="25" t="inlineStr">
+        <is>
+          <t>Clamps do nothing to your SHOT</t>
+        </is>
+      </c>
+      <c r="E156" s="26" t="n"/>
+      <c r="F156" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="72" t="n"/>
+      <c r="H156" s="71" t="n"/>
+      <c r="I156" s="71" t="n"/>
+      <c r="J156" s="71" t="n"/>
     </row>
     <row r="157" s="85">
-      <c r="A157" s="27" t="n"/>
-      <c r="B157" s="28" t="inlineStr">
+      <c r="A157" s="21" t="n"/>
+      <c r="B157" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C157" s="56" t="inlineStr">
-        <is>
-          <t>Brawl Handler</t>
-        </is>
-      </c>
-      <c r="D157" s="63" t="inlineStr">
-        <is>
-          <t>Remove all your Clamps when you change the ball</t>
-        </is>
-      </c>
-      <c r="E157" s="58" t="n"/>
-      <c r="F157" s="61" t="n"/>
-      <c r="G157" s="75" t="n"/>
-      <c r="H157" s="76" t="n"/>
+      <c r="C157" s="23" t="inlineStr">
+        <is>
+          <t>Lethal Shooter</t>
+        </is>
+      </c>
+      <c r="D157" s="38" t="inlineStr">
+        <is>
+          <t>SHOT = 100% when shooting as your first action after a Rebound of your own miss</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="n"/>
+      <c r="F157" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="70" t="inlineStr">
+        <is>
+          <t>Special text: “I understand it now”</t>
+        </is>
+      </c>
+      <c r="H157" s="71" t="n"/>
+      <c r="I157" s="71" t="n"/>
+      <c r="J157" s="71" t="n"/>
     </row>
     <row r="158" s="85">
-      <c r="A158" s="27" t="n"/>
-      <c r="B158" s="28" t="inlineStr">
+      <c r="A158" s="21" t="n"/>
+      <c r="B158" s="22" t="inlineStr">
         <is>
           <t>Intangible</t>
         </is>
       </c>
-      <c r="C158" s="56" t="inlineStr">
-        <is>
-          <t>Baller</t>
-        </is>
-      </c>
-      <c r="D158" s="63" t="inlineStr">
-        <is>
-          <t>Draw 1 card each time you change the ball</t>
-        </is>
-      </c>
-      <c r="E158" s="58" t="n"/>
-      <c r="F158" s="61" t="n"/>
-      <c r="G158" s="75" t="n"/>
-      <c r="H158" s="76" t="n"/>
+      <c r="C158" s="24" t="inlineStr">
+        <is>
+          <t>Ball Pounder</t>
+        </is>
+      </c>
+      <c r="D158" s="25" t="inlineStr">
+        <is>
+          <t>Every Dribble Draws 1 card but gives SHOT -10% and Shot Clock -01</t>
+        </is>
+      </c>
+      <c r="E158" s="26" t="n"/>
+      <c r="F158" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="73" t="n"/>
+      <c r="H158" s="71" t="n"/>
+      <c r="I158" s="71" t="n"/>
+      <c r="J158" s="71" t="n"/>
     </row>
     <row r="159" ht="42" customHeight="1" s="85">
-      <c r="A159" s="52" t="inlineStr">
-        <is>
-          <t>Varena</t>
-        </is>
-      </c>
-      <c r="B159" s="53">
-        <f>COUNTIF($B$160:$B$189,"Varena")</f>
-        <v/>
-      </c>
-      <c r="C159" s="54" t="n"/>
-      <c r="D159" s="54" t="n"/>
-      <c r="E159" s="54" t="n"/>
-      <c r="F159" s="55" t="n"/>
-      <c r="G159" s="66" t="n"/>
-      <c r="H159" s="67" t="n"/>
-      <c r="I159" s="67" t="n"/>
-      <c r="J159" s="67" t="n"/>
+      <c r="A159" s="21" t="n"/>
+      <c r="B159" s="22" t="inlineStr">
+        <is>
+          <t>Intangible</t>
+        </is>
+      </c>
+      <c r="C159" s="23" t="inlineStr">
+        <is>
+          <t>Dirty Player</t>
+        </is>
+      </c>
+      <c r="D159" s="38" t="inlineStr">
+        <is>
+          <t>Each of your Clamps costs an Injured player a card. Discard 1 whenever a Whistle fires</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="n"/>
+      <c r="F159" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="70" t="n"/>
+      <c r="H159" s="71" t="n"/>
+      <c r="I159" s="71" t="n"/>
+      <c r="J159" s="71" t="n"/>
     </row>
     <row r="160" s="85">
-      <c r="A160" s="27" t="n"/>
-      <c r="B160" s="28" t="inlineStr">